--- a/data/ARN.MI.xlsx
+++ b/data/ARN.MI.xlsx
@@ -38,34 +38,34 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92215049266815</t>
+    <t xml:space="preserve">1.92215013504028</t>
   </si>
   <si>
     <t xml:space="preserve">ARN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94450056552887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91736078262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9077821969986</t>
+    <t xml:space="preserve">1.94450116157532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91736030578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90778195858002</t>
   </si>
   <si>
     <t xml:space="preserve">1.8838347196579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93172907829285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91576445102692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83434414863586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83594048023224</t>
+    <t xml:space="preserve">1.93172895908356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91576421260834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83434462547302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83594059944153</t>
   </si>
   <si>
     <t xml:space="preserve">1.91097486019135</t>
@@ -77,28 +77,28 @@
     <t xml:space="preserve">1.74973130226135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71620559692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80401134490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81039702892303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79602897167206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77208185195923</t>
+    <t xml:space="preserve">1.71620547771454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80401086807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81039726734161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79602932929993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77208209037781</t>
   </si>
   <si>
     <t xml:space="preserve">1.70662665367126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69704782962799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69066202640533</t>
+    <t xml:space="preserve">1.69704759120941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69066190719604</t>
   </si>
   <si>
     <t xml:space="preserve">1.67629361152649</t>
@@ -107,85 +107,85 @@
     <t xml:space="preserve">1.70024085044861</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69864439964294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67469716072083</t>
+    <t xml:space="preserve">1.69864416122437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67469727993011</t>
   </si>
   <si>
     <t xml:space="preserve">1.66671502590179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66032898426056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81518626213074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82795798778534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86148428916931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88543117046356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89181697368622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92853593826294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95407938957214</t>
+    <t xml:space="preserve">1.66032910346985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8151867389679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82795810699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8614844083786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88543140888214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89181733131409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92853605747223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95407974720001</t>
   </si>
   <si>
     <t xml:space="preserve">1.90618562698364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86787033081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88064157962799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85190546512604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85988771915436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85509812831879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79283618927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78804659843445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78006410598755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7561172246933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76888918876648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76409947872162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78485381603241</t>
+    <t xml:space="preserve">1.86787021160126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88064193725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85190534591675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85988783836365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85509824752808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79283595085144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78804636001587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78006434440613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75611734390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7688889503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7640997171402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78485357761383</t>
   </si>
   <si>
     <t xml:space="preserve">1.77048516273499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72099483013153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73536312580109</t>
+    <t xml:space="preserve">1.72099494934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73536288738251</t>
   </si>
   <si>
     <t xml:space="preserve">1.80241453647614</t>
@@ -197,79 +197,79 @@
     <t xml:space="preserve">1.74494206905365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73217046260834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73695957660675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74334537982941</t>
+    <t xml:space="preserve">1.73217010498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73695945739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7433454990387</t>
   </si>
   <si>
     <t xml:space="preserve">1.75132775306702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68587243556976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67789018154144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65234649181366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62041747570038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64276766777039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59008431434631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60285580158234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54937434196472</t>
+    <t xml:space="preserve">1.68587267398834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67789006233215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65234661102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6204172372818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64276790618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59008419513702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60285604000092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54937422275543</t>
   </si>
   <si>
     <t xml:space="preserve">1.51185739040375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45598089694977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43682301044464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46955072879791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49748921394348</t>
+    <t xml:space="preserve">1.45598077774048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43682289123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4695508480072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49748909473419</t>
   </si>
   <si>
     <t xml:space="preserve">1.47673487663269</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47274374961853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46875262260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49669086933136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47593653202057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50626957416534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47753322124481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43841958045959</t>
+    <t xml:space="preserve">1.47274386882782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46875274181366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49669075012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47593677043915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50626969337463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47753310203552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43841946125031</t>
   </si>
   <si>
     <t xml:space="preserve">1.40090262889862</t>
@@ -278,70 +278,70 @@
     <t xml:space="preserve">1.3490172624588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30910551548004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34342980384827</t>
+    <t xml:space="preserve">1.30910539627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34342956542969</t>
   </si>
   <si>
     <t xml:space="preserve">1.32666659355164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3410347700119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31708776950836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38653433322906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39691138267517</t>
+    <t xml:space="preserve">1.34103488922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31708765029907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38653409481049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39691150188446</t>
   </si>
   <si>
     <t xml:space="preserve">1.40649020671844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30671083927155</t>
+    <t xml:space="preserve">1.30671072006226</t>
   </si>
   <si>
     <t xml:space="preserve">1.32347369194031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30591249465942</t>
+    <t xml:space="preserve">1.30591285228729</t>
   </si>
   <si>
     <t xml:space="preserve">1.31229841709137</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28994786739349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28515863418579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28595674037933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33305263519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33704364299774</t>
+    <t xml:space="preserve">1.28994798660278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28515839576721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28595650196075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33305239677429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33704376220703</t>
   </si>
   <si>
     <t xml:space="preserve">1.30112326145172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.361048579216</t>
+    <t xml:space="preserve">1.36104869842529</t>
   </si>
   <si>
     <t xml:space="preserve">1.34627258777618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35283982753754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33806371688843</t>
+    <t xml:space="preserve">1.35283958911896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33806383609772</t>
   </si>
   <si>
     <t xml:space="preserve">1.2715710401535</t>
@@ -350,16 +350,16 @@
     <t xml:space="preserve">1.28880989551544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29291427135468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30686962604523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33888447284698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34955620765686</t>
+    <t xml:space="preserve">1.29291439056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30686950683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33888459205627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34955608844757</t>
   </si>
   <si>
     <t xml:space="preserve">1.34380996227264</t>
@@ -368,34 +368,34 @@
     <t xml:space="preserve">1.33642184734344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34709358215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30522763729095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29127240180969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31425774097443</t>
+    <t xml:space="preserve">1.34709370136261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30522775650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29127252101898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31425750255585</t>
   </si>
   <si>
     <t xml:space="preserve">1.32164561748505</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26828718185425</t>
+    <t xml:space="preserve">1.26828742027283</t>
   </si>
   <si>
     <t xml:space="preserve">1.27239179611206</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28798878192902</t>
+    <t xml:space="preserve">1.28798890113831</t>
   </si>
   <si>
     <t xml:space="preserve">1.2970187664032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24858582019806</t>
+    <t xml:space="preserve">1.24858570098877</t>
   </si>
   <si>
     <t xml:space="preserve">1.32657110691071</t>
@@ -404,64 +404,64 @@
     <t xml:space="preserve">1.33231747150421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35940718650818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4201534986496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48664617538452</t>
+    <t xml:space="preserve">1.3594069480896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42015337944031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48664605617523</t>
   </si>
   <si>
     <t xml:space="preserve">1.53343737125397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51619839668274</t>
+    <t xml:space="preserve">1.51619851589203</t>
   </si>
   <si>
     <t xml:space="preserve">1.51866126060486</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43739247322083</t>
+    <t xml:space="preserve">1.43739223480225</t>
   </si>
   <si>
     <t xml:space="preserve">1.4677654504776</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43000435829163</t>
+    <t xml:space="preserve">1.43000411987305</t>
   </si>
   <si>
     <t xml:space="preserve">1.40948176383972</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44478046894073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5597060918808</t>
+    <t xml:space="preserve">1.44478034973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55970597267151</t>
   </si>
   <si>
     <t xml:space="preserve">1.61798989772797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70582604408264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74851274490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72388553619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68284070491791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67463159561157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.651646733284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64179587364197</t>
+    <t xml:space="preserve">1.70582592487335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74851262569427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72388565540314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6828408241272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67463195323944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65164661407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64179599285126</t>
   </si>
   <si>
     <t xml:space="preserve">1.67134821414948</t>
@@ -482,112 +482,112 @@
     <t xml:space="preserve">1.65821373462677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6811990737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68776631355286</t>
+    <t xml:space="preserve">1.68119895458221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68776607513428</t>
   </si>
   <si>
     <t xml:space="preserve">1.6680645942688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6500049829483</t>
+    <t xml:space="preserve">1.65000486373901</t>
   </si>
   <si>
     <t xml:space="preserve">1.66313922405243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67791521549225</t>
+    <t xml:space="preserve">1.67791533470154</t>
   </si>
   <si>
     <t xml:space="preserve">2.03746867179871</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04403567314148</t>
+    <t xml:space="preserve">2.04403591156006</t>
   </si>
   <si>
     <t xml:space="preserve">2.0391104221344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04075264930725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05224466323853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04731965065002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04239368438721</t>
+    <t xml:space="preserve">2.04075241088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0522449016571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04731941223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04239439964294</t>
   </si>
   <si>
     <t xml:space="preserve">2.19836473464966</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24105143547058</t>
+    <t xml:space="preserve">2.241051197052</t>
   </si>
   <si>
     <t xml:space="preserve">2.18851351737976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17537975311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14582753181458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00627470016479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98821496963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99313998222351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99806559085846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99642384052277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99970734119415</t>
+    <t xml:space="preserve">2.17537951469421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.145827293396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00627422332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98821473121643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99314045906067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99806571006775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9964234828949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99970769882202</t>
   </si>
   <si>
     <t xml:space="preserve">2.00299119949341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00791645050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01119995117188</t>
+    <t xml:space="preserve">2.00791621208191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01120018959045</t>
   </si>
   <si>
     <t xml:space="preserve">2.02597618103027</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03254342079163</t>
+    <t xml:space="preserve">2.03254318237305</t>
   </si>
   <si>
     <t xml:space="preserve">2.02105045318604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0194091796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02433443069458</t>
+    <t xml:space="preserve">2.01940894126892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02433466911316</t>
   </si>
   <si>
     <t xml:space="preserve">2.07687187194824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05881190299988</t>
+    <t xml:space="preserve">2.05881214141846</t>
   </si>
   <si>
     <t xml:space="preserve">2.09657335281372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14746904373169</t>
+    <t xml:space="preserve">2.14746856689453</t>
   </si>
   <si>
     <t xml:space="preserve">2.33955883979797</t>
@@ -596,34 +596,34 @@
     <t xml:space="preserve">2.27552914619446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32478284835815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27881240844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25746917724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29851412773132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26075291633606</t>
+    <t xml:space="preserve">2.32478308677673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.278813123703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25746965408325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29851388931274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26075315475464</t>
   </si>
   <si>
     <t xml:space="preserve">2.28045463562012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30672335624695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35597681999207</t>
+    <t xml:space="preserve">2.30672311782837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35597729682922</t>
   </si>
   <si>
     <t xml:space="preserve">2.34120106697083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3428430557251</t>
+    <t xml:space="preserve">2.34284281730652</t>
   </si>
   <si>
     <t xml:space="preserve">2.3477680683136</t>
@@ -632,28 +632,28 @@
     <t xml:space="preserve">2.44627594947815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39209675788879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38224577903748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38717126846313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38388752937317</t>
+    <t xml:space="preserve">2.39209651947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38224601745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38717150688171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38388776779175</t>
   </si>
   <si>
     <t xml:space="preserve">2.40523099899292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38060402870178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42164921760559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33791756629944</t>
+    <t xml:space="preserve">2.38060426712036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42164897918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33791732788086</t>
   </si>
   <si>
     <t xml:space="preserve">2.32314109802246</t>
@@ -665,19 +665,19 @@
     <t xml:space="preserve">2.41015648841858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40687298774719</t>
+    <t xml:space="preserve">2.40687251091003</t>
   </si>
   <si>
     <t xml:space="preserve">2.43806672096252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41836524009705</t>
+    <t xml:space="preserve">2.41836547851562</t>
   </si>
   <si>
     <t xml:space="preserve">2.29030513763428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34941029548645</t>
+    <t xml:space="preserve">2.34940981864929</t>
   </si>
   <si>
     <t xml:space="preserve">2.36418628692627</t>
@@ -686,19 +686,19 @@
     <t xml:space="preserve">2.37567853927612</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40194773674011</t>
+    <t xml:space="preserve">2.40194725990295</t>
   </si>
   <si>
     <t xml:space="preserve">2.35761904716492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36746954917908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37075352668762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37239503860474</t>
+    <t xml:space="preserve">2.36746978759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37075328826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37239551544189</t>
   </si>
   <si>
     <t xml:space="preserve">2.362544298172</t>
@@ -707,169 +707,169 @@
     <t xml:space="preserve">2.36582803726196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39538049697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37732028961182</t>
+    <t xml:space="preserve">2.39538025856018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3773205280304</t>
   </si>
   <si>
     <t xml:space="preserve">2.37403678894043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38881301879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39373826980591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39045476913452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41343975067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40358877182007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40030598640442</t>
+    <t xml:space="preserve">2.38881325721741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39373803138733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39045453071594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41343998908997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40358901023865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40030527114868</t>
   </si>
   <si>
     <t xml:space="preserve">2.40851449966431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42329072952271</t>
+    <t xml:space="preserve">2.42329049110413</t>
   </si>
   <si>
     <t xml:space="preserve">2.43149971961975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42000675201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35105204582214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33627557754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34612607955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43642520904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42657423019409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42985844612122</t>
+    <t xml:space="preserve">2.42000722885132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35105180740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33627533912659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34612655639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43642544746399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42657446861267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42985796928406</t>
   </si>
   <si>
     <t xml:space="preserve">2.4528431892395</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47701287269592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47867965698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49201536178589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49368190765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.475346326828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46534442901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48201417922974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46867847442627</t>
+    <t xml:space="preserve">2.47701263427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.478679895401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49201512336731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49368238449097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47534656524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46534466743469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48201370239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46867871284485</t>
   </si>
   <si>
     <t xml:space="preserve">2.45867729187012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46201109886169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45534348487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41700482368469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40867066383362</t>
+    <t xml:space="preserve">2.46201086044312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45534324645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41700506210327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40867042541504</t>
   </si>
   <si>
     <t xml:space="preserve">2.36699771881104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34199452400208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36866450309753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35366225242615</t>
+    <t xml:space="preserve">2.3419942855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36866474151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35366249084473</t>
   </si>
   <si>
     <t xml:space="preserve">2.385333776474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38366675376892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36366415023804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32532501220703</t>
+    <t xml:space="preserve">2.38366651535034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36366391181946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32532525062561</t>
   </si>
   <si>
     <t xml:space="preserve">2.31699085235596</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28531956672668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28698658943176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29698801040649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31532406806946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28365254402161</t>
+    <t xml:space="preserve">2.28531980514526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28698635101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29698777198792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31532382965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28365278244019</t>
   </si>
   <si>
     <t xml:space="preserve">2.28865313529968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29032039642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30198884010315</t>
+    <t xml:space="preserve">2.29032063484192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30198907852173</t>
   </si>
   <si>
     <t xml:space="preserve">2.30365562438965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2936544418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24198031425476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26698398590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26865029335022</t>
+    <t xml:space="preserve">2.29365420341492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24198007583618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2669837474823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2686505317688</t>
   </si>
   <si>
     <t xml:space="preserve">2.32699203491211</t>
@@ -884,34 +884,34 @@
     <t xml:space="preserve">2.24364709854126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25031471252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2253110408783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25198173522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22197723388672</t>
+    <t xml:space="preserve">2.25031495094299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22531151771545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25198149681091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2219774723053</t>
   </si>
   <si>
     <t xml:space="preserve">2.20697546005249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20030784606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16863679885864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17863821983337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16696953773499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18697261810303</t>
+    <t xml:space="preserve">2.20030760765076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16863632202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17863798141479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16696977615356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18697237968445</t>
   </si>
   <si>
     <t xml:space="preserve">2.19697403907776</t>
@@ -920,28 +920,28 @@
     <t xml:space="preserve">2.18363857269287</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18530559539795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19197368621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1753044128418</t>
+    <t xml:space="preserve">2.18530583381653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19197344779968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17530417442322</t>
   </si>
   <si>
     <t xml:space="preserve">2.14196610450745</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15363478660583</t>
+    <t xml:space="preserve">2.15363454818726</t>
   </si>
   <si>
     <t xml:space="preserve">2.1436333656311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13529872894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12696409225464</t>
+    <t xml:space="preserve">2.13529849052429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12696385383606</t>
   </si>
   <si>
     <t xml:space="preserve">2.12863111495972</t>
@@ -953,58 +953,58 @@
     <t xml:space="preserve">2.13029813766479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11862945556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37366533279419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37533164024353</t>
+    <t xml:space="preserve">2.11862969398499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37366509437561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37533259391785</t>
   </si>
   <si>
     <t xml:space="preserve">2.40700340270996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39533495903015</t>
+    <t xml:space="preserve">2.39533519744873</t>
   </si>
   <si>
     <t xml:space="preserve">2.39200091362</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49868273735046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49534916877747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5086841583252</t>
+    <t xml:space="preserve">2.49868226051331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49534893035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50868439674377</t>
   </si>
   <si>
     <t xml:space="preserve">2.51201796531677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51535153388977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51701855659485</t>
+    <t xml:space="preserve">2.51535201072693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51701879501343</t>
   </si>
   <si>
     <t xml:space="preserve">2.52368640899658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52535319328308</t>
+    <t xml:space="preserve">2.52535343170166</t>
   </si>
   <si>
     <t xml:space="preserve">2.54535579681396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53368759155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53202104568481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54035544395447</t>
+    <t xml:space="preserve">2.53368782997131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53202080726624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54035568237305</t>
   </si>
   <si>
     <t xml:space="preserve">2.52702021598816</t>
@@ -1019,67 +1019,67 @@
     <t xml:space="preserve">2.49701595306396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42700600624084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50034952163696</t>
+    <t xml:space="preserve">2.42700624465942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50034976005554</t>
   </si>
   <si>
     <t xml:space="preserve">2.50535035133362</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48368072509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45200967788696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51368522644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54202222824097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54868984222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51035118103027</t>
+    <t xml:space="preserve">2.48368096351624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45200991630554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51368474960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54202198982239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5486900806427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51035094261169</t>
   </si>
   <si>
     <t xml:space="preserve">2.52035236358643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47201228141785</t>
+    <t xml:space="preserve">2.47201251983643</t>
   </si>
   <si>
     <t xml:space="preserve">2.50201678276062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48701405525208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00041961669922</t>
+    <t xml:space="preserve">2.48701453208923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00041937828064</t>
   </si>
   <si>
     <t xml:space="preserve">2.81706070899963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75038480758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71704697608948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8087260723114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80039119720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83372974395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78372263908386</t>
+    <t xml:space="preserve">2.75038456916809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7170467376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80872631072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80039143562317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83372950553894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78372240066528</t>
   </si>
   <si>
     <t xml:space="preserve">2.84206438064575</t>
@@ -1091,19 +1091,19 @@
     <t xml:space="preserve">2.85039901733398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85873317718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89207100868225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82539534568787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72538113594055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61703324317932</t>
+    <t xml:space="preserve">2.85873341560364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89207124710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82539510726929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72538137435913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61703276634216</t>
   </si>
   <si>
     <t xml:space="preserve">2.6420361995697</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.70037770271301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65870523452759</t>
+    <t xml:space="preserve">2.65870547294617</t>
   </si>
   <si>
     <t xml:space="preserve">2.6253674030304</t>
@@ -1121,28 +1121,28 @@
     <t xml:space="preserve">2.63370180130005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59202885627747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66703939437866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70871210098267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74204993247986</t>
+    <t xml:space="preserve">2.59202909469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66703987121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70871233940125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74205017089844</t>
   </si>
   <si>
     <t xml:space="preserve">2.65037059783936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68370890617371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6003634929657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58369421958923</t>
+    <t xml:space="preserve">2.68370866775513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60036373138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58369469642639</t>
   </si>
   <si>
     <t xml:space="preserve">2.56702566146851</t>
@@ -1151,16 +1151,16 @@
     <t xml:space="preserve">2.76705384254456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73371553421021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79205703735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86706757545471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87540197372437</t>
+    <t xml:space="preserve">2.73371577262878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79205679893494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86706781387329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87540221214294</t>
   </si>
   <si>
     <t xml:space="preserve">2.88373684883118</t>
@@ -1172,10 +1172,10 @@
     <t xml:space="preserve">2.78091382980347</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72174572944641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73019790649414</t>
+    <t xml:space="preserve">2.72174549102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73019814491272</t>
   </si>
   <si>
     <t xml:space="preserve">2.77246117591858</t>
@@ -1187,16 +1187,16 @@
     <t xml:space="preserve">2.70484018325806</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68793511390686</t>
+    <t xml:space="preserve">2.68793535232544</t>
   </si>
   <si>
     <t xml:space="preserve">2.6625771522522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69638752937317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65412497520447</t>
+    <t xml:space="preserve">2.69638776779175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65412473678589</t>
   </si>
   <si>
     <t xml:space="preserve">2.60340857505798</t>
@@ -1208,28 +1208,28 @@
     <t xml:space="preserve">2.61186122894287</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5780508518219</t>
+    <t xml:space="preserve">2.57805109024048</t>
   </si>
   <si>
     <t xml:space="preserve">2.59495615959167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50197720527649</t>
+    <t xml:space="preserve">2.50197744369507</t>
   </si>
   <si>
     <t xml:space="preserve">2.4935245513916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54423999786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5611457824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58650326728821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51888227462769</t>
+    <t xml:space="preserve">2.54424047470093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56114602088928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58650350570679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51888275146484</t>
   </si>
   <si>
     <t xml:space="preserve">2.53578782081604</t>
@@ -1238,13 +1238,13 @@
     <t xml:space="preserve">2.55269289016724</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51042985916138</t>
+    <t xml:space="preserve">2.51043009757996</t>
   </si>
   <si>
     <t xml:space="preserve">2.56959819793701</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4681670665741</t>
+    <t xml:space="preserve">2.46816682815552</t>
   </si>
   <si>
     <t xml:space="preserve">2.48507213592529</t>
@@ -1253,19 +1253,19 @@
     <t xml:space="preserve">2.41745066642761</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45126128196716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39209294319153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38364052772522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27375650405884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29911422729492</t>
+    <t xml:space="preserve">2.45126152038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39209318161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38364028930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27375626564026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29911398887634</t>
   </si>
   <si>
     <t xml:space="preserve">2.36673498153687</t>
@@ -1277,28 +1277,28 @@
     <t xml:space="preserve">2.43435645103455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42590355873108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34983015060425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28220868110657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32447195053101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40899848937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45971369743347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44280910491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33292460441589</t>
+    <t xml:space="preserve">2.4259033203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34982991218567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28220915794373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32447218894958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40899801254272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45971393585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44280886650085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33292484283447</t>
   </si>
   <si>
     <t xml:space="preserve">2.34137725830078</t>
@@ -1307,7 +1307,7 @@
     <t xml:space="preserve">2.40054559707642</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37518787384033</t>
+    <t xml:space="preserve">2.37518763542175</t>
   </si>
   <si>
     <t xml:space="preserve">2.47661948204041</t>
@@ -1319,10 +1319,10 @@
     <t xml:space="preserve">2.23994588851929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29430246353149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23437643051147</t>
+    <t xml:space="preserve">2.29430222511292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23437690734863</t>
   </si>
   <si>
     <t xml:space="preserve">2.24293732643127</t>
@@ -1334,16 +1334,16 @@
     <t xml:space="preserve">2.25149846076965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27718043327332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26862001419067</t>
+    <t xml:space="preserve">2.27718091011047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26861977577209</t>
   </si>
   <si>
     <t xml:space="preserve">2.44839715957642</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37135004997253</t>
+    <t xml:space="preserve">2.37134957313538</t>
   </si>
   <si>
     <t xml:space="preserve">2.31142401695251</t>
@@ -1352,16 +1352,16 @@
     <t xml:space="preserve">2.28574156761169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26005935668945</t>
+    <t xml:space="preserve">2.26005911827087</t>
   </si>
   <si>
     <t xml:space="preserve">2.35422801971436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2258152961731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20869421958923</t>
+    <t xml:space="preserve">2.22581553459167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20869398117065</t>
   </si>
   <si>
     <t xml:space="preserve">2.30286312103271</t>
@@ -1370,10 +1370,10 @@
     <t xml:space="preserve">2.31998491287231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37991046905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.405592918396</t>
+    <t xml:space="preserve">2.37991070747375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40559315681458</t>
   </si>
   <si>
     <t xml:space="preserve">2.39703226089478</t>
@@ -1385,7 +1385,7 @@
     <t xml:space="preserve">2.38847136497498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36278891563416</t>
+    <t xml:space="preserve">2.36278915405273</t>
   </si>
   <si>
     <t xml:space="preserve">2.34566712379456</t>
@@ -1394,58 +1394,58 @@
     <t xml:space="preserve">2.20013308525085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18301129341125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4398365020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54256629943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6024923324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69666123390198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77370834350586</t>
+    <t xml:space="preserve">2.18301153182983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43983674049377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5425660610199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60249209403992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69666147232056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77370882034302</t>
   </si>
   <si>
     <t xml:space="preserve">2.63673543930054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67097854614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61961388587952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65385699272156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68810081481934</t>
+    <t xml:space="preserve">2.67097878456116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61961364746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65385723114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68810057640076</t>
   </si>
   <si>
     <t xml:space="preserve">2.64529609680176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.713782787323</t>
+    <t xml:space="preserve">2.71378302574158</t>
   </si>
   <si>
     <t xml:space="preserve">2.7223436832428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07333755493164</t>
+    <t xml:space="preserve">3.07333779335022</t>
   </si>
   <si>
     <t xml:space="preserve">3.52706170082092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59554815292358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65547442436218</t>
+    <t xml:space="preserve">3.595547914505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65547394752502</t>
   </si>
   <si>
     <t xml:space="preserve">3.58698773384094</t>
@@ -1454,40 +1454,40 @@
     <t xml:space="preserve">3.6126697063446</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53562259674072</t>
+    <t xml:space="preserve">3.53562235832214</t>
   </si>
   <si>
     <t xml:space="preserve">3.42433190345764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54418325424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56986594200134</t>
+    <t xml:space="preserve">3.54418349266052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5698664188385</t>
   </si>
   <si>
     <t xml:space="preserve">3.5527446269989</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56130504608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50994038581848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4842574596405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57842636108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.638352394104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74108266830444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16912364959717</t>
+    <t xml:space="preserve">3.56130480766296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50993967056274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48425793647766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57842659950256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63835263252258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74108195304871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16912412643433</t>
   </si>
   <si>
     <t xml:space="preserve">4.60572624206543</t>
@@ -1502,16 +1502,16 @@
     <t xml:space="preserve">4.19480657577515</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45163059234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53724002838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52011871337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58860492706299</t>
+    <t xml:space="preserve">4.45163106918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53723955154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52011823654175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58860445022583</t>
   </si>
   <si>
     <t xml:space="preserve">4.34890127182007</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">3.27879762649536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25311493873596</t>
+    <t xml:space="preserve">3.25311517715454</t>
   </si>
   <si>
     <t xml:space="preserve">2.8935604095459</t>
@@ -1544,28 +1544,28 @@
     <t xml:space="preserve">3.16750693321228</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0390944480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44145321846008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3815279006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39008831977844</t>
+    <t xml:space="preserve">3.03909397125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44145369529724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38152766227722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39008855819702</t>
   </si>
   <si>
     <t xml:space="preserve">3.84381246566772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83525133132935</t>
+    <t xml:space="preserve">3.83525156974792</t>
   </si>
   <si>
     <t xml:space="preserve">3.87805604934692</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76676511764526</t>
+    <t xml:space="preserve">3.76676440238953</t>
   </si>
   <si>
     <t xml:space="preserve">3.88661646842957</t>
@@ -1574,28 +1574,28 @@
     <t xml:space="preserve">3.85237336158752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92942118644714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95510315895081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93798160552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11775922775269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25473165512085</t>
+    <t xml:space="preserve">3.92942070960999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95510292053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93798136711121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11775875091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25473213195801</t>
   </si>
   <si>
     <t xml:space="preserve">4.22905015945435</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26329326629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28041458129883</t>
+    <t xml:space="preserve">4.26329374313354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28041505813599</t>
   </si>
   <si>
     <t xml:space="preserve">4.43450975418091</t>
@@ -1607,19 +1607,19 @@
     <t xml:space="preserve">4.00646829605103</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10919857025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15200281143188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08351612091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94654250144958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07495546340942</t>
+    <t xml:space="preserve">4.10919761657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15200233459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08351564407349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94654297828674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07495450973511</t>
   </si>
   <si>
     <t xml:space="preserve">4.02358961105347</t>
@@ -1628,61 +1628,61 @@
     <t xml:space="preserve">3.96366405487061</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13488054275513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12631988525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01664590835571</t>
+    <t xml:space="preserve">4.13488101959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12631940841675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01664638519287</t>
   </si>
   <si>
     <t xml:space="preserve">4.70845603942871</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91391563415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96528148651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94816017150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20498466491699</t>
+    <t xml:space="preserve">4.91391611099243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96528196334839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94815969467163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20498418807983</t>
   </si>
   <si>
     <t xml:space="preserve">5.56453943252563</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68439102172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95833683013916</t>
+    <t xml:space="preserve">5.68439054489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95833730697632</t>
   </si>
   <si>
     <t xml:space="preserve">5.90697240829468</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88985061645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57471704483032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.129554271698</t>
+    <t xml:space="preserve">5.88985109329224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57471656799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12955379486084</t>
   </si>
   <si>
     <t xml:space="preserve">6.4035005569458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01988077163696</t>
+    <t xml:space="preserve">7.01987934112549</t>
   </si>
   <si>
     <t xml:space="preserve">7.20821905136108</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32807064056396</t>
+    <t xml:space="preserve">7.32807016372681</t>
   </si>
   <si>
     <t xml:space="preserve">7.05412340164185</t>
@@ -1691,67 +1691,67 @@
     <t xml:space="preserve">7.00275897979736</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42397737503052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28357172012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8799033164978</t>
+    <t xml:space="preserve">7.4239764213562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28357076644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87990283966064</t>
   </si>
   <si>
     <t xml:space="preserve">6.96765661239624</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59909057617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51133728027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73949718475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84480142593384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82725095748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68684434890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66929340362549</t>
+    <t xml:space="preserve">6.59909105300903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51133680343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73949670791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.844801902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82725143432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68684482574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66929388046265</t>
   </si>
   <si>
     <t xml:space="preserve">6.45868492126465</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4060320854187</t>
+    <t xml:space="preserve">6.40603256225586</t>
   </si>
   <si>
     <t xml:space="preserve">6.31827831268311</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80970001220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17826652526855</t>
+    <t xml:space="preserve">6.80970048904419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17826700210571</t>
   </si>
   <si>
     <t xml:space="preserve">7.35377407073975</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26602029800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05541133880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07296276092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63419246673584</t>
+    <t xml:space="preserve">7.26601982116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05541086196899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07296180725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.634192943573</t>
   </si>
   <si>
     <t xml:space="preserve">6.44113349914551</t>
@@ -1766,7 +1766,7 @@
     <t xml:space="preserve">6.03746604919434</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37053680419922</t>
+    <t xml:space="preserve">5.37053632736206</t>
   </si>
   <si>
     <t xml:space="preserve">5.40563774108887</t>
@@ -1778,7 +1778,7 @@
     <t xml:space="preserve">5.65134906768799</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12521982192993</t>
+    <t xml:space="preserve">6.12522029876709</t>
   </si>
   <si>
     <t xml:space="preserve">5.96726274490356</t>
@@ -1796,16 +1796,16 @@
     <t xml:space="preserve">5.94971227645874</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86195802688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82685661315918</t>
+    <t xml:space="preserve">5.86195850372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82685708999634</t>
   </si>
   <si>
     <t xml:space="preserve">5.93216180801392</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87950897216797</t>
+    <t xml:space="preserve">5.87950801849365</t>
   </si>
   <si>
     <t xml:space="preserve">5.79175519943237</t>
@@ -1823,19 +1823,19 @@
     <t xml:space="preserve">5.70400142669678</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58114576339722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66890001296997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56359481811523</t>
+    <t xml:space="preserve">5.58114624023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66889953613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56359529495239</t>
   </si>
   <si>
     <t xml:space="preserve">5.61624765396118</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49339294433594</t>
+    <t xml:space="preserve">5.49339199066162</t>
   </si>
   <si>
     <t xml:space="preserve">5.31788444519043</t>
@@ -1844,7 +1844,7 @@
     <t xml:space="preserve">5.17747831344604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2652325630188</t>
+    <t xml:space="preserve">5.26523208618164</t>
   </si>
   <si>
     <t xml:space="preserve">5.28278303146362</t>
@@ -1856,19 +1856,19 @@
     <t xml:space="preserve">5.42318868637085</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4758415222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38808679580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5109429359436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77420425415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44073963165283</t>
+    <t xml:space="preserve">5.47584104537964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3880877494812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51094341278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77420473098755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44074010848999</t>
   </si>
   <si>
     <t xml:space="preserve">5.54604434967041</t>
@@ -1877,94 +1877,94 @@
     <t xml:space="preserve">6.23052406311035</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35338020324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1603217124939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37093162536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47623538970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42358255386353</t>
+    <t xml:space="preserve">6.35337972640991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16032123565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37093114852905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47623586654663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42358303070068</t>
   </si>
   <si>
     <t xml:space="preserve">6.54643869400024</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98520755767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33622217178345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09051275253296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16071510314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19581699371338</t>
+    <t xml:space="preserve">6.98520851135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33622312545776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0905122756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16071557998657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19581651687622</t>
   </si>
   <si>
     <t xml:space="preserve">7.00275850296021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95010566711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14316463470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12561321258545</t>
+    <t xml:space="preserve">6.95010662078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14316511154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12561368942261</t>
   </si>
   <si>
     <t xml:space="preserve">7.02030944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84519481658936</t>
+    <t xml:space="preserve">7.84519529342651</t>
   </si>
   <si>
     <t xml:space="preserve">8.3366174697876</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31906700134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42437171936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08252620697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68763160705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03864765167236</t>
+    <t xml:space="preserve">8.31906604766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42437076568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0825252532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68763256072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03864860534668</t>
   </si>
   <si>
     <t xml:space="preserve">9.30190944671631</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2763729095459</t>
+    <t xml:space="preserve">11.2763719558716</t>
   </si>
   <si>
     <t xml:space="preserve">13.1630792617798</t>
   </si>
   <si>
-    <t xml:space="preserve">13.075325012207</t>
+    <t xml:space="preserve">13.0753259658813</t>
   </si>
   <si>
     <t xml:space="preserve">13.1192035675049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8559408187866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0222806930542</t>
+    <t xml:space="preserve">12.8559417724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0222797393799</t>
   </si>
   <si>
     <t xml:space="preserve">12.1100339889526</t>
@@ -1976,13 +1976,13 @@
     <t xml:space="preserve">11.36412525177</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8814792633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1539106369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6712656021118</t>
+    <t xml:space="preserve">10.88148021698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1539115905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6712646484375</t>
   </si>
   <si>
     <t xml:space="preserve">11.7151412963867</t>
@@ -1994,7 +1994,7 @@
     <t xml:space="preserve">11.0569868087769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.495756149292</t>
+    <t xml:space="preserve">11.4957571029663</t>
   </si>
   <si>
     <t xml:space="preserve">11.4080028533936</t>
@@ -2003,40 +2003,40 @@
     <t xml:space="preserve">11.8906488418579</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8028945922852</t>
+    <t xml:space="preserve">11.8028955459595</t>
   </si>
   <si>
     <t xml:space="preserve">11.3202486038208</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6273880004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1447420120239</t>
+    <t xml:space="preserve">11.627387046814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1447401046753</t>
   </si>
   <si>
     <t xml:space="preserve">10.618218421936</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5304651260376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5743417739868</t>
+    <t xml:space="preserve">10.5304641723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5743408203125</t>
   </si>
   <si>
     <t xml:space="preserve">10.7498483657837</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6620950698853</t>
+    <t xml:space="preserve">10.6620941162109</t>
   </si>
   <si>
     <t xml:space="preserve">10.3549566268921</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78455543518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91618633270264</t>
+    <t xml:space="preserve">9.78455638885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91618728637695</t>
   </si>
   <si>
     <t xml:space="preserve">10.0916948318481</t>
@@ -2045,7 +2045,7 @@
     <t xml:space="preserve">11.2324953079224</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1886186599731</t>
+    <t xml:space="preserve">11.1886177062988</t>
   </si>
   <si>
     <t xml:space="preserve">11.1008644104004</t>
@@ -2057,7 +2057,7 @@
     <t xml:space="preserve">11.2675971984863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0218858718872</t>
+    <t xml:space="preserve">11.0218868255615</t>
   </si>
   <si>
     <t xml:space="preserve">11.2500457763672</t>
@@ -2066,7 +2066,7 @@
     <t xml:space="preserve">11.3729009628296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2851467132568</t>
+    <t xml:space="preserve">11.2851457595825</t>
   </si>
   <si>
     <t xml:space="preserve">11.1973934173584</t>
@@ -2075,25 +2075,25 @@
     <t xml:space="preserve">11.8467712402344</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9871788024902</t>
+    <t xml:space="preserve">11.9871768951416</t>
   </si>
   <si>
     <t xml:space="preserve">12.2855415344238</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2504396438599</t>
+    <t xml:space="preserve">12.2504405975342</t>
   </si>
   <si>
     <t xml:space="preserve">12.1626853942871</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4672012329102</t>
+    <t xml:space="preserve">12.4672002792358</t>
   </si>
   <si>
     <t xml:space="preserve">12.0372972488403</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0910358428955</t>
+    <t xml:space="preserve">12.0910348892212</t>
   </si>
   <si>
     <t xml:space="preserve">11.5536556243896</t>
@@ -2102,28 +2102,28 @@
     <t xml:space="preserve">11.6432199478149</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3924417495728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9446277618408</t>
+    <t xml:space="preserve">11.3924427032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9446268081665</t>
   </si>
   <si>
     <t xml:space="preserve">10.5505475997925</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6759357452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9088020324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7117614746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6580238342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9267148971558</t>
+    <t xml:space="preserve">10.6759376525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9088010787964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7117624282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6580228805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9267139434814</t>
   </si>
   <si>
     <t xml:space="preserve">11.0521030426025</t>
@@ -2132,7 +2132,7 @@
     <t xml:space="preserve">11.4999189376831</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4820051193237</t>
+    <t xml:space="preserve">11.482006072998</t>
   </si>
   <si>
     <t xml:space="preserve">11.4282674789429</t>
@@ -2141,7 +2141,7 @@
     <t xml:space="preserve">11.5715684890747</t>
   </si>
   <si>
-    <t xml:space="preserve">11.374529838562</t>
+    <t xml:space="preserve">11.3745288848877</t>
   </si>
   <si>
     <t xml:space="preserve">11.356616973877</t>
@@ -2159,13 +2159,13 @@
     <t xml:space="preserve">11.7148694992065</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7327823638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7506952285767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1805992126465</t>
+    <t xml:space="preserve">11.7327833175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7506942749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1805982589722</t>
   </si>
   <si>
     <t xml:space="preserve">12.6284151077271</t>
@@ -2174,7 +2174,7 @@
     <t xml:space="preserve">12.0731229782104</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3418121337891</t>
+    <t xml:space="preserve">12.3418130874634</t>
   </si>
   <si>
     <t xml:space="preserve">12.3597259521484</t>
@@ -2183,10 +2183,10 @@
     <t xml:space="preserve">11.6969575881958</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1268606185913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0552101135254</t>
+    <t xml:space="preserve">12.1268615722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0552110671997</t>
   </si>
   <si>
     <t xml:space="preserve">11.8581705093384</t>
@@ -2198,10 +2198,10 @@
     <t xml:space="preserve">12.2880744934082</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5925893783569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.503026008606</t>
+    <t xml:space="preserve">12.5925903320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5030269622803</t>
   </si>
   <si>
     <t xml:space="preserve">11.9835596084595</t>
@@ -2219,46 +2219,46 @@
     <t xml:space="preserve">11.284966468811</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3387041091919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8939962387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7686080932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6253070831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0014715194702</t>
+    <t xml:space="preserve">11.3387060165405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8939971923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.768609046936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6253061294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0014705657959</t>
   </si>
   <si>
     <t xml:space="preserve">12.1089487075806</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9656467437744</t>
+    <t xml:space="preserve">11.9656476974487</t>
   </si>
   <si>
     <t xml:space="preserve">12.1985120773315</t>
   </si>
   <si>
-    <t xml:space="preserve">12.43137550354</t>
+    <t xml:space="preserve">12.4313764572144</t>
   </si>
   <si>
     <t xml:space="preserve">12.2522506713867</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8612794876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8433675765991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6821527481079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7358903884888</t>
+    <t xml:space="preserve">12.8612785339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8433666229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6821537017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7358913421631</t>
   </si>
   <si>
     <t xml:space="preserve">13.3449201583862</t>
@@ -2267,43 +2267,43 @@
     <t xml:space="preserve">14.2405529022217</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0972509384155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.330117225647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4734182357788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5988054275513</t>
+    <t xml:space="preserve">14.0972518920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3301162719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4734172821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.598804473877</t>
   </si>
   <si>
     <t xml:space="preserve">13.8823003768921</t>
   </si>
   <si>
-    <t xml:space="preserve">13.864387512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5777864456177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.470308303833</t>
+    <t xml:space="preserve">13.8643865585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.577784538269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4703102111816</t>
   </si>
   <si>
     <t xml:space="preserve">13.6852607727051</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6673488616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5598735809326</t>
+    <t xml:space="preserve">13.66734790802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5598726272583</t>
   </si>
   <si>
     <t xml:space="preserve">13.6136102676392</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8285617828369</t>
+    <t xml:space="preserve">13.8285627365112</t>
   </si>
   <si>
     <t xml:space="preserve">13.953950881958</t>
@@ -2312,7 +2312,7 @@
     <t xml:space="preserve">13.4344835281372</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7210865020752</t>
+    <t xml:space="preserve">13.7210855484009</t>
   </si>
   <si>
     <t xml:space="preserve">13.5240478515625</t>
@@ -2324,43 +2324,43 @@
     <t xml:space="preserve">13.2553577423096</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4523954391479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3090944290161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2763786315918</t>
+    <t xml:space="preserve">13.4523973464966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3090953826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2763776779175</t>
   </si>
   <si>
     <t xml:space="preserve">14.4196796417236</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0256013870239</t>
+    <t xml:space="preserve">14.0256023406982</t>
   </si>
   <si>
     <t xml:space="preserve">13.756911277771</t>
   </si>
   <si>
-    <t xml:space="preserve">14.437593460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7124996185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3363304138184</t>
+    <t xml:space="preserve">14.4375925064087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7124977111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.336332321167</t>
   </si>
   <si>
     <t xml:space="preserve">17.7156066894531</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2498779296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6591281890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.316047668457</t>
+    <t xml:space="preserve">17.2498760223389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6591300964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3160457611084</t>
   </si>
   <si>
     <t xml:space="preserve">21.4503936767578</t>
@@ -2369,13 +2369,13 @@
     <t xml:space="preserve">21.5399551391602</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2116794586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9877700805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2712669372559</t>
+    <t xml:space="preserve">22.2116813659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.987771987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2712650299072</t>
   </si>
   <si>
     <t xml:space="preserve">23.017749786377</t>
@@ -2387,10 +2387,10 @@
     <t xml:space="preserve">22.1221160888672</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7342567443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8982086181641</t>
+    <t xml:space="preserve">23.7342548370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8982105255127</t>
   </si>
   <si>
     <t xml:space="preserve">22.4355869293213</t>
@@ -2402,76 +2402,76 @@
     <t xml:space="preserve">21.7190818786621</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9429912567139</t>
+    <t xml:space="preserve">21.9429893493652</t>
   </si>
   <si>
     <t xml:space="preserve">21.7638626098633</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8534297943115</t>
+    <t xml:space="preserve">21.8534278869629</t>
   </si>
   <si>
     <t xml:space="preserve">23.3312187194824</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8086452484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3463916778564</t>
+    <t xml:space="preserve">21.8086471557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3463935852051</t>
   </si>
   <si>
     <t xml:space="preserve">25.3016128540039</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2420234680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.525520324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2120475769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8837718963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4807376861572</t>
+    <t xml:space="preserve">26.2420253753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5255222320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2120494842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8837738037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4807395935059</t>
   </si>
   <si>
     <t xml:space="preserve">25.5703010559082</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1224842071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.361198425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3911762237549</t>
+    <t xml:space="preserve">25.122486114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3611965179443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3911743164062</t>
   </si>
   <si>
     <t xml:space="preserve">25.704647064209</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4211540222168</t>
+    <t xml:space="preserve">26.4211521148682</t>
   </si>
   <si>
     <t xml:space="preserve">26.0628986358643</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4659309387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1524620056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6602344512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6750373840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7794036865234</t>
+    <t xml:space="preserve">26.4659328460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1524639129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6602325439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6750354766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7794055938721</t>
   </si>
   <si>
     <t xml:space="preserve">26.5554962158203</t>
@@ -2489,22 +2489,22 @@
     <t xml:space="preserve">24.0477275848389</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9133834838867</t>
+    <t xml:space="preserve">23.9133815765381</t>
   </si>
   <si>
     <t xml:space="preserve">24.5851058959961</t>
   </si>
   <si>
-    <t xml:space="preserve">22.077335357666</t>
+    <t xml:space="preserve">22.0773334503174</t>
   </si>
   <si>
     <t xml:space="preserve">22.928186416626</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1968765258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.182071685791</t>
+    <t xml:space="preserve">23.1968746185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1820697784424</t>
   </si>
   <si>
     <t xml:space="preserve">24.2268524169922</t>
@@ -2513,7 +2513,7 @@
     <t xml:space="preserve">24.4955425262451</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3164176940918</t>
+    <t xml:space="preserve">24.3164138793945</t>
   </si>
   <si>
     <t xml:space="preserve">22.3908061981201</t>
@@ -2525,22 +2525,22 @@
     <t xml:space="preserve">23.0625305175781</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7790336608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8834037780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2416591644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1672668457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3167858123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6002807617188</t>
+    <t xml:space="preserve">23.7790355682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8834018707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2416572570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1672687530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3167839050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6002788543701</t>
   </si>
   <si>
     <t xml:space="preserve">25.615083694458</t>
@@ -2549,7 +2549,7 @@
     <t xml:space="preserve">25.4359550476074</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8985767364502</t>
+    <t xml:space="preserve">24.8985786437988</t>
   </si>
   <si>
     <t xml:space="preserve">25.9733371734619</t>
@@ -2558,7 +2558,7 @@
     <t xml:space="preserve">26.5107154846191</t>
   </si>
   <si>
-    <t xml:space="preserve">26.197244644165</t>
+    <t xml:space="preserve">26.1972427368164</t>
   </si>
   <si>
     <t xml:space="preserve">26.8689670562744</t>
@@ -2582,16 +2582,16 @@
     <t xml:space="preserve">28.9289207458496</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7050151824951</t>
+    <t xml:space="preserve">28.7050113677979</t>
   </si>
   <si>
     <t xml:space="preserve">29.7797718048096</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9885101318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.630256652832</t>
+    <t xml:space="preserve">27.9885082244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6302547454834</t>
   </si>
   <si>
     <t xml:space="preserve">27.2272205352783</t>
@@ -2603,28 +2603,28 @@
     <t xml:space="preserve">26.6898403167725</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8389892578125</t>
+    <t xml:space="preserve">25.8389911651611</t>
   </si>
   <si>
     <t xml:space="preserve">25.7942085266113</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3315868377686</t>
+    <t xml:space="preserve">26.3315887451172</t>
   </si>
   <si>
     <t xml:space="preserve">24.7194519042969</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4507579803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.599910736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4655647277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3615646362305</t>
+    <t xml:space="preserve">24.4507598876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5999088287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4655666351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3615665435791</t>
   </si>
   <si>
     <t xml:space="preserve">28.0332889556885</t>
@@ -2639,7 +2639,7 @@
     <t xml:space="preserve">27.6633834838867</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2979869842529</t>
+    <t xml:space="preserve">30.2979888916016</t>
   </si>
   <si>
     <t xml:space="preserve">26.891170501709</t>
@@ -2648,10 +2648,10 @@
     <t xml:space="preserve">27.3454132080078</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6620502471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.480354309082</t>
+    <t xml:space="preserve">29.662052154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4803524017334</t>
   </si>
   <si>
     <t xml:space="preserve">29.3440799713135</t>
@@ -2669,7 +2669,7 @@
     <t xml:space="preserve">31.0702037811279</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8885040283203</t>
+    <t xml:space="preserve">30.8885059356689</t>
   </si>
   <si>
     <t xml:space="preserve">28.9352626800537</t>
@@ -2687,28 +2687,28 @@
     <t xml:space="preserve">28.0722007751465</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4355926513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5264415740967</t>
+    <t xml:space="preserve">28.4355945587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5264434814453</t>
   </si>
   <si>
     <t xml:space="preserve">28.4810199737549</t>
   </si>
   <si>
-    <t xml:space="preserve">28.390172958374</t>
+    <t xml:space="preserve">28.3901710510254</t>
   </si>
   <si>
     <t xml:space="preserve">29.1623821258545</t>
   </si>
   <si>
-    <t xml:space="preserve">29.434928894043</t>
+    <t xml:space="preserve">29.4349308013916</t>
   </si>
   <si>
     <t xml:space="preserve">28.2538986206055</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1169586181641</t>
+    <t xml:space="preserve">29.1169567108154</t>
   </si>
   <si>
     <t xml:space="preserve">30.1162948608398</t>
@@ -2723,13 +2723,13 @@
     <t xml:space="preserve">31.479024887085</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5698699951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7969913482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7515678405762</t>
+    <t xml:space="preserve">31.5698680877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.796989440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7515659332275</t>
   </si>
   <si>
     <t xml:space="preserve">31.1156272888184</t>
@@ -2741,10 +2741,10 @@
     <t xml:space="preserve">34.6587219238281</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8410873413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4770278930664</t>
+    <t xml:space="preserve">33.8410835266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4770240783691</t>
   </si>
   <si>
     <t xml:space="preserve">34.386173248291</t>
@@ -2762,10 +2762,10 @@
     <t xml:space="preserve">34.4316024780273</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7048072814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9773597717285</t>
+    <t xml:space="preserve">33.7048110961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9773559570312</t>
   </si>
   <si>
     <t xml:space="preserve">34.931266784668</t>
@@ -2774,64 +2774,64 @@
     <t xml:space="preserve">34.5224456787109</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0682067871094</t>
+    <t xml:space="preserve">34.0682029724121</t>
   </si>
   <si>
     <t xml:space="preserve">33.7502365112305</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9319267272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2499008178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6139602661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2485694885254</t>
+    <t xml:space="preserve">33.9319305419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2499046325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6139640808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2485733032227</t>
   </si>
   <si>
     <t xml:space="preserve">36.6573867797852</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7936592102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6106300354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5645370483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.110969543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4302673339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3868408203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8871765136719</t>
+    <t xml:space="preserve">36.7936630249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6106338500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5645446777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1109657287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4302635192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3868370056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8871726989746</t>
   </si>
   <si>
     <t xml:space="preserve">33.0688743591309</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3414154052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8865089416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2044792175293</t>
+    <t xml:space="preserve">33.3414192199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8865051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2044830322266</t>
   </si>
   <si>
     <t xml:space="preserve">34.340747833252</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7508964538574</t>
+    <t xml:space="preserve">32.7509002685547</t>
   </si>
   <si>
     <t xml:space="preserve">32.6600532531738</t>
@@ -2840,7 +2840,7 @@
     <t xml:space="preserve">32.9780197143555</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7976589202881</t>
+    <t xml:space="preserve">30.7976551055908</t>
   </si>
   <si>
     <t xml:space="preserve">29.3895034790039</t>
@@ -2849,7 +2849,7 @@
     <t xml:space="preserve">29.5257778167725</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6172943115234</t>
+    <t xml:space="preserve">28.6172924041748</t>
   </si>
   <si>
     <t xml:space="preserve">28.344747543335</t>
@@ -2858,28 +2858,28 @@
     <t xml:space="preserve">30.0254440307617</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9332637786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.205810546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1149559020996</t>
+    <t xml:space="preserve">31.9332675933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2058067321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1149597167969</t>
   </si>
   <si>
     <t xml:space="preserve">32.2512359619141</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6152935028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.024112701416</t>
+    <t xml:space="preserve">31.615291595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0241088867188</t>
   </si>
   <si>
     <t xml:space="preserve">33.1142959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">32.614631652832</t>
+    <t xml:space="preserve">32.6146278381348</t>
   </si>
   <si>
     <t xml:space="preserve">31.2064743041992</t>
@@ -2891,10 +2891,10 @@
     <t xml:space="preserve">31.5244445800781</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3427467346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3420791625977</t>
+    <t xml:space="preserve">31.3427486419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3420829772949</t>
   </si>
   <si>
     <t xml:space="preserve">32.5237770080566</t>
@@ -2906,64 +2906,64 @@
     <t xml:space="preserve">32.1603889465332</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1590538024902</t>
+    <t xml:space="preserve">34.159049987793</t>
   </si>
   <si>
     <t xml:space="preserve">33.7956581115723</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9766883850098</t>
+    <t xml:space="preserve">34.976692199707</t>
   </si>
   <si>
     <t xml:space="preserve">32.9325981140137</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0234451293945</t>
+    <t xml:space="preserve">33.0234489440918</t>
   </si>
   <si>
     <t xml:space="preserve">33.5231170654297</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4783592224121</t>
+    <t xml:space="preserve">32.4783554077148</t>
   </si>
   <si>
     <t xml:space="preserve">32.4329299926758</t>
   </si>
   <si>
-    <t xml:space="preserve">31.842414855957</t>
+    <t xml:space="preserve">31.8424167633057</t>
   </si>
   <si>
     <t xml:space="preserve">31.8878402709961</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4342632293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7074756622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7068061828613</t>
+    <t xml:space="preserve">30.4342613220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7074737548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7068099975586</t>
   </si>
   <si>
     <t xml:space="preserve">30.4796886444092</t>
   </si>
   <si>
-    <t xml:space="preserve">29.616626739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8437461853027</t>
+    <t xml:space="preserve">29.6166248321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8437442779541</t>
   </si>
   <si>
     <t xml:space="preserve">29.2532329559326</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7535629272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0708675384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8898372650146</t>
+    <t xml:space="preserve">28.7535667419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0708694458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.889835357666</t>
   </si>
   <si>
     <t xml:space="preserve">28.6627159118652</t>
@@ -2978,16 +2978,16 @@
     <t xml:space="preserve">28.9806861877441</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7989902496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8891735076904</t>
+    <t xml:space="preserve">28.7989883422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8891754150391</t>
   </si>
   <si>
     <t xml:space="preserve">29.0715351104736</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2993221282959</t>
+    <t xml:space="preserve">28.2993202209473</t>
   </si>
   <si>
     <t xml:space="preserve">28.0267772674561</t>
@@ -3005,19 +3005,19 @@
     <t xml:space="preserve">28.5718688964844</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4816856384277</t>
+    <t xml:space="preserve">27.4816837310791</t>
   </si>
   <si>
     <t xml:space="preserve">27.5725345611572</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6186218261719</t>
+    <t xml:space="preserve">26.6186237335205</t>
   </si>
   <si>
     <t xml:space="preserve">27.1182918548584</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0274429321289</t>
+    <t xml:space="preserve">27.0274410247803</t>
   </si>
   <si>
     <t xml:space="preserve">26.9365921020508</t>
@@ -3026,13 +3026,13 @@
     <t xml:space="preserve">26.9820194244385</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3460788726807</t>
+    <t xml:space="preserve">26.346076965332</t>
   </si>
   <si>
     <t xml:space="preserve">25.8918361663818</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6647148132324</t>
+    <t xml:space="preserve">25.6647129058838</t>
   </si>
   <si>
     <t xml:space="preserve">26.2552280426025</t>
@@ -3041,10 +3041,10 @@
     <t xml:space="preserve">26.8457431793213</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6640491485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4369277954102</t>
+    <t xml:space="preserve">26.6640510559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4369258880615</t>
   </si>
   <si>
     <t xml:space="preserve">26.5732002258301</t>
@@ -3053,10 +3053,10 @@
     <t xml:space="preserve">26.3915023803711</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7094707489014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.527774810791</t>
+    <t xml:space="preserve">26.70947265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5277767181396</t>
   </si>
   <si>
     <t xml:space="preserve">25.9826850891113</t>
@@ -3065,10 +3065,10 @@
     <t xml:space="preserve">25.8009872436523</t>
   </si>
   <si>
-    <t xml:space="preserve">24.165714263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6660461425781</t>
+    <t xml:space="preserve">24.1657123565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6660442352295</t>
   </si>
   <si>
     <t xml:space="preserve">23.8477439880371</t>
@@ -3077,13 +3077,13 @@
     <t xml:space="preserve">25.437593460083</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7555637359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0741996765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0735340118408</t>
+    <t xml:space="preserve">25.7555618286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.074197769165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0735359191895</t>
   </si>
   <si>
     <t xml:space="preserve">27.6892356872559</t>
@@ -3092,7 +3092,7 @@
     <t xml:space="preserve">26.3419418334961</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6671504974365</t>
+    <t xml:space="preserve">26.6671524047852</t>
   </si>
   <si>
     <t xml:space="preserve">27.1317348480225</t>
@@ -3101,7 +3101,7 @@
     <t xml:space="preserve">27.6427764892578</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3396549224854</t>
+    <t xml:space="preserve">28.3396530151367</t>
   </si>
   <si>
     <t xml:space="preserve">27.8286113739014</t>
@@ -3155,7 +3155,7 @@
     <t xml:space="preserve">27.038818359375</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9458999633789</t>
+    <t xml:space="preserve">26.9459018707275</t>
   </si>
   <si>
     <t xml:space="preserve">26.760066986084</t>
@@ -3167,19 +3167,19 @@
     <t xml:space="preserve">26.2025661468506</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5742340087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4813175201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8994445800781</t>
+    <t xml:space="preserve">26.5742321014404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.481315612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8994426727295</t>
   </si>
   <si>
     <t xml:space="preserve">26.2490253448486</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7379817962646</t>
+    <t xml:space="preserve">25.7379837036133</t>
   </si>
   <si>
     <t xml:space="preserve">25.9238147735596</t>
@@ -3194,7 +3194,7 @@
     <t xml:space="preserve">27.271110534668</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2246494293213</t>
+    <t xml:space="preserve">27.2246513366699</t>
   </si>
   <si>
     <t xml:space="preserve">25.4127731323242</t>
@@ -3206,7 +3206,7 @@
     <t xml:space="preserve">24.5300617218018</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9017276763916</t>
+    <t xml:space="preserve">24.9017295837402</t>
   </si>
   <si>
     <t xml:space="preserve">25.0875625610352</t>
@@ -3215,76 +3215,76 @@
     <t xml:space="preserve">24.8088130950928</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5521488189697</t>
+    <t xml:space="preserve">25.5521469116211</t>
   </si>
   <si>
     <t xml:space="preserve">25.5056896209717</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7623519897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7158966064453</t>
+    <t xml:space="preserve">24.7623538970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7158946990967</t>
   </si>
   <si>
     <t xml:space="preserve">25.8308982849121</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0852756500244</t>
+    <t xml:space="preserve">27.085277557373</t>
   </si>
   <si>
     <t xml:space="preserve">26.7136077880859</t>
   </si>
   <si>
-    <t xml:space="preserve">26.016731262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8773555755615</t>
+    <t xml:space="preserve">26.0167331695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8773574829102</t>
   </si>
   <si>
     <t xml:space="preserve">25.7844390869141</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0631904602051</t>
+    <t xml:space="preserve">26.0631885528564</t>
   </si>
   <si>
     <t xml:space="preserve">26.1096496582031</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1340217590332</t>
+    <t xml:space="preserve">25.1340198516846</t>
   </si>
   <si>
     <t xml:space="preserve">25.0411052703857</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2977695465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4836025238037</t>
+    <t xml:space="preserve">24.2977676391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4836044311523</t>
   </si>
   <si>
     <t xml:space="preserve">24.0654773712158</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2513103485107</t>
+    <t xml:space="preserve">24.2513122558594</t>
   </si>
   <si>
     <t xml:space="preserve">24.5765209197998</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6008930206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0433902740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0898513793945</t>
+    <t xml:space="preserve">23.6008911132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0433921813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0898494720459</t>
   </si>
   <si>
     <t xml:space="preserve">22.114221572876</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0213069915771</t>
+    <t xml:space="preserve">22.0213050842285</t>
   </si>
   <si>
     <t xml:space="preserve">23.2756824493408</t>
@@ -3293,28 +3293,28 @@
     <t xml:space="preserve">23.4615173339844</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4150581359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1363067626953</t>
+    <t xml:space="preserve">23.415060043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1363086700439</t>
   </si>
   <si>
     <t xml:space="preserve">23.6473522186279</t>
   </si>
   <si>
-    <t xml:space="preserve">22.950475692749</t>
+    <t xml:space="preserve">22.9504737854004</t>
   </si>
   <si>
     <t xml:space="preserve">22.5788059234619</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2071380615234</t>
+    <t xml:space="preserve">22.2071399688721</t>
   </si>
   <si>
     <t xml:space="preserve">21.64963722229</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8598442077637</t>
+    <t xml:space="preserve">20.8598461151123</t>
   </si>
   <si>
     <t xml:space="preserve">21.0921363830566</t>
@@ -3329,7 +3329,7 @@
     <t xml:space="preserve">21.5567207336426</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7425556182861</t>
+    <t xml:space="preserve">21.7425537109375</t>
   </si>
   <si>
     <t xml:space="preserve">21.9283885955811</t>
@@ -3350,37 +3350,37 @@
     <t xml:space="preserve">21.4173450469971</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6031799316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8354721069336</t>
+    <t xml:space="preserve">21.603178024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.835470199585</t>
   </si>
   <si>
     <t xml:space="preserve">22.160680770874</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7181816101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3000545501709</t>
+    <t xml:space="preserve">22.7181835174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3000564575195</t>
   </si>
   <si>
     <t xml:space="preserve">22.3465137481689</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2535991668701</t>
+    <t xml:space="preserve">22.2535972595215</t>
   </si>
   <si>
     <t xml:space="preserve">21.881929397583</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7890129089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.182767868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5986042022705</t>
+    <t xml:space="preserve">21.7890148162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1827659606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5986061096191</t>
   </si>
   <si>
     <t xml:space="preserve">25.3663120269775</t>
@@ -3401,10 +3401,10 @@
     <t xml:space="preserve">24.4371433258057</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8796443939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2048530578613</t>
+    <t xml:space="preserve">23.8796424865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2048511505127</t>
   </si>
   <si>
     <t xml:space="preserve">23.9261016845703</t>
@@ -3413,7 +3413,7 @@
     <t xml:space="preserve">24.6694355010986</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5544338226318</t>
+    <t xml:space="preserve">23.5544357299805</t>
   </si>
   <si>
     <t xml:space="preserve">23.6938095092773</t>
@@ -3422,7 +3422,7 @@
     <t xml:space="preserve">23.3221416473389</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7867279052734</t>
+    <t xml:space="preserve">23.7867259979248</t>
   </si>
   <si>
     <t xml:space="preserve">22.8575572967529</t>
@@ -3431,7 +3431,7 @@
     <t xml:space="preserve">21.5102615356445</t>
   </si>
   <si>
-    <t xml:space="preserve">21.370885848999</t>
+    <t xml:space="preserve">21.3708877563477</t>
   </si>
   <si>
     <t xml:space="preserve">21.1850528717041</t>
@@ -3440,19 +3440,19 @@
     <t xml:space="preserve">20.7204685211182</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4881763458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9771347045898</t>
+    <t xml:space="preserve">20.4881744384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9771327972412</t>
   </si>
   <si>
     <t xml:space="preserve">20.2558822631836</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5346336364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9306755065918</t>
+    <t xml:space="preserve">20.5346355438232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9306774139404</t>
   </si>
   <si>
     <t xml:space="preserve">20.5810928344727</t>
@@ -3464,7 +3464,7 @@
     <t xml:space="preserve">20.6275520324707</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0235900878906</t>
+    <t xml:space="preserve">20.0235919952393</t>
   </si>
   <si>
     <t xml:space="preserve">18.6298370361328</t>
@@ -3482,7 +3482,7 @@
     <t xml:space="preserve">17.8772106170654</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5427093505859</t>
+    <t xml:space="preserve">17.5427112579346</t>
   </si>
   <si>
     <t xml:space="preserve">17.2453765869141</t>
@@ -3494,10 +3494,10 @@
     <t xml:space="preserve">17.5612926483154</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4126281738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.747127532959</t>
+    <t xml:space="preserve">17.4126262664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7471294403076</t>
   </si>
   <si>
     <t xml:space="preserve">17.1896266937256</t>
@@ -3518,13 +3518,13 @@
     <t xml:space="preserve">16.3162078857422</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9817085266113</t>
+    <t xml:space="preserve">15.981707572937</t>
   </si>
   <si>
     <t xml:space="preserve">16.5392074584961</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2976245880127</t>
+    <t xml:space="preserve">16.2976264953613</t>
   </si>
   <si>
     <t xml:space="preserve">16.1861248016357</t>
@@ -3536,7 +3536,7 @@
     <t xml:space="preserve">16.1489562988281</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2418746948242</t>
+    <t xml:space="preserve">16.2418727874756</t>
   </si>
   <si>
     <t xml:space="preserve">16.0746231079102</t>
@@ -69275,7 +69275,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.6493981481</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>17149</v>
@@ -69296,6 +69296,32 @@
         <v>1420</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.6495717593</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>12202</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>19.4400005340576</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>18.7399997711182</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>19.2600002288818</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>19.2999992370605</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>1398</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ARN.MI.xlsx
+++ b/data/ARN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1421" uniqueCount="1421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1422" uniqueCount="1422">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,199 +38,199 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92215013504028</t>
+    <t xml:space="preserve">1.92215037345886</t>
   </si>
   <si>
     <t xml:space="preserve">ARN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94450056552887</t>
+    <t xml:space="preserve">1.94450092315674</t>
   </si>
   <si>
     <t xml:space="preserve">1.91736054420471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90778195858002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88383483886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93172919750214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91576433181763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83434426784515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83594059944153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91097486019135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80720412731171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74973154067993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71620571613312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80401146411896</t>
+    <t xml:space="preserve">1.90778183937073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88383448123932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93172895908356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91576445102692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83434414863586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8359409570694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91097497940063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.807204246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74973142147064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71620559692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80401134490967</t>
   </si>
   <si>
     <t xml:space="preserve">1.81039702892303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79602909088135</t>
+    <t xml:space="preserve">1.79602885246277</t>
   </si>
   <si>
     <t xml:space="preserve">1.77208197116852</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70662677288055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6970477104187</t>
+    <t xml:space="preserve">1.70662653446198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69704782962799</t>
   </si>
   <si>
     <t xml:space="preserve">1.69066178798676</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67629361152649</t>
+    <t xml:space="preserve">1.67629373073578</t>
   </si>
   <si>
     <t xml:space="preserve">1.70024085044861</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69864428043365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67469716072083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66671514511108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66032910346985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81518638134003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82795822620392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86148428916931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88543128967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89181709289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92853605747223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95407962799072</t>
+    <t xml:space="preserve">1.69864439964294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67469727993011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6667149066925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66032886505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81518661975861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82795834541321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86148416996002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88543117046356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8918172121048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92853581905365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95407927036285</t>
   </si>
   <si>
     <t xml:space="preserve">1.90618538856506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86787021160126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88064169883728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85190546512604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85988759994507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85509812831879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79283583164215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78804647922516</t>
+    <t xml:space="preserve">1.86787033081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88064181804657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85190534591675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85988771915436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85509836673737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79283607006073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78804671764374</t>
   </si>
   <si>
     <t xml:space="preserve">1.78006434440613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75611710548401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76888918876648</t>
+    <t xml:space="preserve">1.75611734390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76888906955719</t>
   </si>
   <si>
     <t xml:space="preserve">1.76409959793091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7848539352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77048575878143</t>
+    <t xml:space="preserve">1.78485405445099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77048540115356</t>
   </si>
   <si>
     <t xml:space="preserve">1.72099471092224</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73536324501038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80241477489471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76250290870667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74494206905365</t>
+    <t xml:space="preserve">1.73536312580109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.802414894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76250314712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74494183063507</t>
   </si>
   <si>
     <t xml:space="preserve">1.73217010498047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73695969581604</t>
+    <t xml:space="preserve">1.73695981502533</t>
   </si>
   <si>
     <t xml:space="preserve">1.7433454990387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75132751464844</t>
+    <t xml:space="preserve">1.75132787227631</t>
   </si>
   <si>
     <t xml:space="preserve">1.68587243556976</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67789018154144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65234649181366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62041747570038</t>
+    <t xml:space="preserve">1.67789041996002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65234661102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62041735649109</t>
   </si>
   <si>
     <t xml:space="preserve">1.64276778697968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59008431434631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60285592079163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54937434196472</t>
+    <t xml:space="preserve">1.5900844335556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60285604000092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54937446117401</t>
   </si>
   <si>
     <t xml:space="preserve">1.51185739040375</t>
@@ -239,10 +239,10 @@
     <t xml:space="preserve">1.45598077774048</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43682312965393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46955096721649</t>
+    <t xml:space="preserve">1.43682301044464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4695508480072</t>
   </si>
   <si>
     <t xml:space="preserve">1.49748909473419</t>
@@ -251,22 +251,22 @@
     <t xml:space="preserve">1.47673487663269</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47274386882782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46875250339508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49669098854065</t>
+    <t xml:space="preserve">1.47274374961853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46875262260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49669075012207</t>
   </si>
   <si>
     <t xml:space="preserve">1.47593665122986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50626969337463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47753310203552</t>
+    <t xml:space="preserve">1.50626957416534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4775333404541</t>
   </si>
   <si>
     <t xml:space="preserve">1.43841958045959</t>
@@ -278,13 +278,13 @@
     <t xml:space="preserve">1.34901738166809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30910563468933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34342968463898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32666659355164</t>
+    <t xml:space="preserve">1.30910551548004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34342980384827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32666671276093</t>
   </si>
   <si>
     <t xml:space="preserve">1.34103488922119</t>
@@ -293,16 +293,16 @@
     <t xml:space="preserve">1.31708788871765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38653433322906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39691138267517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40649020671844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30671083927155</t>
+    <t xml:space="preserve">1.38653421401978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39691150188446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40649008750916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30671095848083</t>
   </si>
   <si>
     <t xml:space="preserve">1.32347369194031</t>
@@ -314,16 +314,16 @@
     <t xml:space="preserve">1.31229853630066</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28994786739349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2851585149765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28595662117004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33305275440216</t>
+    <t xml:space="preserve">1.28994798660278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28515863418579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28595674037933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33305263519287</t>
   </si>
   <si>
     <t xml:space="preserve">1.33704364299774</t>
@@ -332,7 +332,7 @@
     <t xml:space="preserve">1.30112326145172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36104869842529</t>
+    <t xml:space="preserve">1.36104893684387</t>
   </si>
   <si>
     <t xml:space="preserve">1.34627258777618</t>
@@ -341,61 +341,61 @@
     <t xml:space="preserve">1.35283982753754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33806371688843</t>
+    <t xml:space="preserve">1.33806359767914</t>
   </si>
   <si>
     <t xml:space="preserve">1.27157092094421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28880977630615</t>
+    <t xml:space="preserve">1.28880965709686</t>
   </si>
   <si>
     <t xml:space="preserve">1.29291439056396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30686950683594</t>
+    <t xml:space="preserve">1.30686962604523</t>
   </si>
   <si>
     <t xml:space="preserve">1.33888459205627</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34955620765686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34380984306335</t>
+    <t xml:space="preserve">1.34955632686615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34381020069122</t>
   </si>
   <si>
     <t xml:space="preserve">1.33642184734344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34709358215332</t>
+    <t xml:space="preserve">1.34709370136261</t>
   </si>
   <si>
     <t xml:space="preserve">1.30522787570953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29127240180969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31425750255585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32164585590363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26828753948212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27239167690277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28798890113831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29701864719391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24858558177948</t>
+    <t xml:space="preserve">1.2912722826004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31425762176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32164573669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26828730106354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27239179611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28798878192902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29701888561249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24858582019806</t>
   </si>
   <si>
     <t xml:space="preserve">1.32657110691071</t>
@@ -410,109 +410,109 @@
     <t xml:space="preserve">1.4201534986496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48664617538452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53343737125397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51619851589203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51866126060486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43739235401154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46776533126831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43000423908234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40948164463043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44478034973145</t>
+    <t xml:space="preserve">1.48664629459381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53343749046326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51619863510132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51866114139557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43739247322083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46776556968689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43000411987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40948176383972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44478046894073</t>
   </si>
   <si>
     <t xml:space="preserve">1.5597060918808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61798989772797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70582592487335</t>
+    <t xml:space="preserve">1.61799001693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70582604408264</t>
   </si>
   <si>
     <t xml:space="preserve">1.74851274490356</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72388565540314</t>
+    <t xml:space="preserve">1.72388589382172</t>
   </si>
   <si>
     <t xml:space="preserve">1.68284070491791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67463159561157</t>
+    <t xml:space="preserve">1.67463183403015</t>
   </si>
   <si>
     <t xml:space="preserve">1.651646733284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64179599285126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67134833335876</t>
+    <t xml:space="preserve">1.64179575443268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67134821414948</t>
   </si>
   <si>
     <t xml:space="preserve">1.6647812128067</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65657186508179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69597506523132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69433331489563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65821373462677</t>
+    <t xml:space="preserve">1.65657210350037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6959753036499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69433319568634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65821397304535</t>
   </si>
   <si>
     <t xml:space="preserve">1.6811990737915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68776607513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66806471347809</t>
+    <t xml:space="preserve">1.68776631355286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66806483268738</t>
   </si>
   <si>
     <t xml:space="preserve">1.6500049829483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66313922405243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67791533470154</t>
+    <t xml:space="preserve">1.66313910484314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67791545391083</t>
   </si>
   <si>
     <t xml:space="preserve">2.03746891021729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04403591156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03911066055298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04075264930725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05224514007568</t>
+    <t xml:space="preserve">2.04403614997864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03911018371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04075217247009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0522449016571</t>
   </si>
   <si>
     <t xml:space="preserve">2.04731941223145</t>
@@ -521,61 +521,61 @@
     <t xml:space="preserve">2.04239416122437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1983642578125</t>
+    <t xml:space="preserve">2.19836497306824</t>
   </si>
   <si>
     <t xml:space="preserve">2.24105167388916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18851351737976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17537975311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14582705497742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00627446174622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98821449279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99313998222351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99806571006775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99642395973206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99970722198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00299072265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00791621208191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01119995117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02597570419312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03254318237305</t>
+    <t xml:space="preserve">2.18851375579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17537951469421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14582753181458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00627470016479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98821485042572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99314022064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99806582927704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99642360210419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99970769882202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00299096107483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00791692733765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01120018959045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02597594261169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03254342079163</t>
   </si>
   <si>
     <t xml:space="preserve">2.02105045318604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01940941810608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.024334192276</t>
+    <t xml:space="preserve">2.01940894126892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02433443069458</t>
   </si>
   <si>
     <t xml:space="preserve">2.07687163352966</t>
@@ -587,13 +587,13 @@
     <t xml:space="preserve">2.09657335281372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14746904373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33955931663513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27552890777588</t>
+    <t xml:space="preserve">2.14746928215027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33955907821655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27552938461304</t>
   </si>
   <si>
     <t xml:space="preserve">2.32478332519531</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">2.26075315475464</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2804548740387</t>
+    <t xml:space="preserve">2.28045463562012</t>
   </si>
   <si>
     <t xml:space="preserve">2.30672335624695</t>
@@ -626,7 +626,7 @@
     <t xml:space="preserve">2.34284281730652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3477680683136</t>
+    <t xml:space="preserve">2.34776782989502</t>
   </si>
   <si>
     <t xml:space="preserve">2.44627594947815</t>
@@ -635,16 +635,16 @@
     <t xml:space="preserve">2.39209651947021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38224577903748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38717150688171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38388752937317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40523076057434</t>
+    <t xml:space="preserve">2.38224601745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38717103004456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38388800621033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4052312374115</t>
   </si>
   <si>
     <t xml:space="preserve">2.38060426712036</t>
@@ -656,25 +656,25 @@
     <t xml:space="preserve">2.33791756629944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32314085960388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35433506965637</t>
+    <t xml:space="preserve">2.32314133644104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35433554649353</t>
   </si>
   <si>
     <t xml:space="preserve">2.41015648841858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40687274932861</t>
+    <t xml:space="preserve">2.40687251091003</t>
   </si>
   <si>
     <t xml:space="preserve">2.4380669593811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41836547851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29030513763428</t>
+    <t xml:space="preserve">2.4183657169342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29030561447144</t>
   </si>
   <si>
     <t xml:space="preserve">2.34941005706787</t>
@@ -698,34 +698,34 @@
     <t xml:space="preserve">2.37075328826904</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37239551544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36254405975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36582803726196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3953800201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37732028961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37403655052185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38881301879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39373826980591</t>
+    <t xml:space="preserve">2.37239503860474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36254477500916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3658275604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39538025856018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3773205280304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37403702735901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38881325721741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39373803138733</t>
   </si>
   <si>
     <t xml:space="preserve">2.39045476913452</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41343975067139</t>
+    <t xml:space="preserve">2.41343998908997</t>
   </si>
   <si>
     <t xml:space="preserve">2.40358901023865</t>
@@ -737,34 +737,34 @@
     <t xml:space="preserve">2.40851473808289</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42329049110413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43149948120117</t>
+    <t xml:space="preserve">2.42329072952271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43149995803833</t>
   </si>
   <si>
     <t xml:space="preserve">2.42000722885132</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35105204582214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33627581596375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34612655639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43642544746399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42657423019409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42985773086548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45284271240234</t>
+    <t xml:space="preserve">2.35105156898499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33627557754517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34612631797791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43642497062683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42657470703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42985820770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4528431892395</t>
   </si>
   <si>
     <t xml:space="preserve">2.4770131111145</t>
@@ -773,49 +773,49 @@
     <t xml:space="preserve">2.47867965698242</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49201512336731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49368238449097</t>
+    <t xml:space="preserve">2.49201560020447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49368214607239</t>
   </si>
   <si>
     <t xml:space="preserve">2.475346326828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46534514427185</t>
+    <t xml:space="preserve">2.46534466743469</t>
   </si>
   <si>
     <t xml:space="preserve">2.48201394081116</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46867847442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45867729187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46201086044312</t>
+    <t xml:space="preserve">2.46867871284485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45867705345154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46201109886169</t>
   </si>
   <si>
     <t xml:space="preserve">2.45534372329712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41700482368469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40867042541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36699748039246</t>
+    <t xml:space="preserve">2.41700506210327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40866994857788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36699771881104</t>
   </si>
   <si>
     <t xml:space="preserve">2.3419942855835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36866450309753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35366225242615</t>
+    <t xml:space="preserve">2.36866497993469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35366249084473</t>
   </si>
   <si>
     <t xml:space="preserve">2.38533353805542</t>
@@ -824,31 +824,31 @@
     <t xml:space="preserve">2.38366651535034</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36366367340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32532525062561</t>
+    <t xml:space="preserve">2.36366391181946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32532548904419</t>
   </si>
   <si>
     <t xml:space="preserve">2.31699085235596</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28531956672668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28698658943176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29698777198792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31532406806946</t>
+    <t xml:space="preserve">2.28531932830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2869861125946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29698801040649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31532382965088</t>
   </si>
   <si>
     <t xml:space="preserve">2.28365278244019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28865313529968</t>
+    <t xml:space="preserve">2.28865337371826</t>
   </si>
   <si>
     <t xml:space="preserve">2.29032015800476</t>
@@ -863,46 +863,46 @@
     <t xml:space="preserve">2.29365420341492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24198007583618</t>
+    <t xml:space="preserve">2.24198031425476</t>
   </si>
   <si>
     <t xml:space="preserve">2.2669837474823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26865029335022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32699203491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31865739822388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31032299995422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24364709854126</t>
+    <t xml:space="preserve">2.26865077018738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32699251174927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31865787506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3103232383728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24364686012268</t>
   </si>
   <si>
     <t xml:space="preserve">2.25031471252441</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22531127929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25198125839233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2219774723053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20697522163391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20030808448792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16863679885864</t>
+    <t xml:space="preserve">2.22531151771545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25198149681091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22197723388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20697546005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20030784606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16863656044006</t>
   </si>
   <si>
     <t xml:space="preserve">2.17863821983337</t>
@@ -911,19 +911,19 @@
     <t xml:space="preserve">2.16696977615356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18697261810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1969735622406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18363881111145</t>
+    <t xml:space="preserve">2.18697237968445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19697403907776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18363904953003</t>
   </si>
   <si>
     <t xml:space="preserve">2.18530583381653</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19197344779968</t>
+    <t xml:space="preserve">2.19197297096252</t>
   </si>
   <si>
     <t xml:space="preserve">2.17530417442322</t>
@@ -932,10 +932,10 @@
     <t xml:space="preserve">2.14196610450745</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15363454818726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14363312721252</t>
+    <t xml:space="preserve">2.15363478660583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14363288879395</t>
   </si>
   <si>
     <t xml:space="preserve">2.13529872894287</t>
@@ -947,91 +947,91 @@
     <t xml:space="preserve">2.12863111495972</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12029647827148</t>
+    <t xml:space="preserve">2.12029623985291</t>
   </si>
   <si>
     <t xml:space="preserve">2.13029789924622</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11862993240356</t>
+    <t xml:space="preserve">2.11862969398499</t>
   </si>
   <si>
     <t xml:space="preserve">2.37366557121277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37533187866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40700364112854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39533495903015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39200091362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49868249893188</t>
+    <t xml:space="preserve">2.37533235549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40700340270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39533519744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39200139045715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49868273735046</t>
   </si>
   <si>
     <t xml:space="preserve">2.49534893035889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50868439674377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51201748847961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51535153388977</t>
+    <t xml:space="preserve">2.5086841583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51201844215393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51535201072693</t>
   </si>
   <si>
     <t xml:space="preserve">2.51701879501343</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52368640899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52535343170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54535603523254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53368759155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53202080726624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54035520553589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52702045440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53868865966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53702163696289</t>
+    <t xml:space="preserve">2.523686170578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5253529548645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54535579681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53368782997131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53202104568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54035544395447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52702021598816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53868818283081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53702139854431</t>
   </si>
   <si>
     <t xml:space="preserve">2.49701595306396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42700624465942</t>
+    <t xml:space="preserve">2.42700600624084</t>
   </si>
   <si>
     <t xml:space="preserve">2.50034952163696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50535035133362</t>
+    <t xml:space="preserve">2.5053505897522</t>
   </si>
   <si>
     <t xml:space="preserve">2.48368048667908</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45200991630554</t>
+    <t xml:space="preserve">2.45200943946838</t>
   </si>
   <si>
     <t xml:space="preserve">2.51368498802185</t>
@@ -1049,13 +1049,13 @@
     <t xml:space="preserve">2.52035236358643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.472012758255</t>
+    <t xml:space="preserve">2.47201228141785</t>
   </si>
   <si>
     <t xml:space="preserve">2.50201678276062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48701453208923</t>
+    <t xml:space="preserve">2.48701429367065</t>
   </si>
   <si>
     <t xml:space="preserve">3.00041961669922</t>
@@ -1064,16 +1064,16 @@
     <t xml:space="preserve">2.81706070899963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75038456916809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7170467376709</t>
+    <t xml:space="preserve">2.75038480758667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71704649925232</t>
   </si>
   <si>
     <t xml:space="preserve">2.80872583389282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80039143562317</t>
+    <t xml:space="preserve">2.80039167404175</t>
   </si>
   <si>
     <t xml:space="preserve">2.83372974395752</t>
@@ -1082,7 +1082,7 @@
     <t xml:space="preserve">2.78372263908386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84206414222717</t>
+    <t xml:space="preserve">2.84206461906433</t>
   </si>
   <si>
     <t xml:space="preserve">2.75871896743774</t>
@@ -1091,31 +1091,31 @@
     <t xml:space="preserve">2.85039854049683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85873293876648</t>
+    <t xml:space="preserve">2.85873317718506</t>
   </si>
   <si>
     <t xml:space="preserve">2.89207100868225</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82539534568787</t>
+    <t xml:space="preserve">2.82539510726929</t>
   </si>
   <si>
     <t xml:space="preserve">2.72538113594055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61703276634216</t>
+    <t xml:space="preserve">2.61703252792358</t>
   </si>
   <si>
     <t xml:space="preserve">2.64203643798828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70037794113159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65870571136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62536764144897</t>
+    <t xml:space="preserve">2.70037770271301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65870499610901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6253674030304</t>
   </si>
   <si>
     <t xml:space="preserve">2.63370180130005</t>
@@ -1127,10 +1127,10 @@
     <t xml:space="preserve">2.66703987121582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70871233940125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74204993247986</t>
+    <t xml:space="preserve">2.70871186256409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7420506477356</t>
   </si>
   <si>
     <t xml:space="preserve">2.65037083625793</t>
@@ -1139,22 +1139,22 @@
     <t xml:space="preserve">2.68370866775513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60036373138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58369469642639</t>
+    <t xml:space="preserve">2.60036325454712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58369445800781</t>
   </si>
   <si>
     <t xml:space="preserve">2.56702566146851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76705360412598</t>
+    <t xml:space="preserve">2.76705384254456</t>
   </si>
   <si>
     <t xml:space="preserve">2.73371553421021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79205679893494</t>
+    <t xml:space="preserve">2.79205727577209</t>
   </si>
   <si>
     <t xml:space="preserve">2.86706757545471</t>
@@ -1169,40 +1169,40 @@
     <t xml:space="preserve">2.77538800239563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78091382980347</t>
+    <t xml:space="preserve">2.78091406822205</t>
   </si>
   <si>
     <t xml:space="preserve">2.72174549102783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7301983833313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77246141433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64567184448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70484042167664</t>
+    <t xml:space="preserve">2.73019814491272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77246117591858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.645672082901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70484018325806</t>
   </si>
   <si>
     <t xml:space="preserve">2.68793511390686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66257739067078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69638776779175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65412449836731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60340881347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63721942901611</t>
+    <t xml:space="preserve">2.6625771522522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69638752937317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65412425994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60340857505798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63721895217896</t>
   </si>
   <si>
     <t xml:space="preserve">2.61186122894287</t>
@@ -1217,28 +1217,28 @@
     <t xml:space="preserve">2.50197744369507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49352478981018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54424071311951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5611457824707</t>
+    <t xml:space="preserve">2.4935245513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54424023628235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56114554405212</t>
   </si>
   <si>
     <t xml:space="preserve">2.58650326728821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51888227462769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53578782081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55269312858582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51043009757996</t>
+    <t xml:space="preserve">2.51888251304626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53578758239746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55269289016724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51042985916138</t>
   </si>
   <si>
     <t xml:space="preserve">2.56959843635559</t>
@@ -1250,34 +1250,34 @@
     <t xml:space="preserve">2.48507213592529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41745090484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45126128196716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39209318161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38364028930664</t>
+    <t xml:space="preserve">2.41745066642761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45126175880432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39209294319153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38364052772522</t>
   </si>
   <si>
     <t xml:space="preserve">2.27375626564026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29911398887634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36673474311829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35828256607056</t>
+    <t xml:space="preserve">2.29911422729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36673521995544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35828280448914</t>
   </si>
   <si>
     <t xml:space="preserve">2.43435597419739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4259033203125</t>
+    <t xml:space="preserve">2.42590355873108</t>
   </si>
   <si>
     <t xml:space="preserve">2.34982991218567</t>
@@ -1286,25 +1286,25 @@
     <t xml:space="preserve">2.28220891952515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32447218894958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4089982509613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45971393585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44280910491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33292460441589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34137725830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40054535865784</t>
+    <t xml:space="preserve">2.32447195053101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40899848937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45971417427063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44280886650085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33292484283447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3413770198822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.400545835495</t>
   </si>
   <si>
     <t xml:space="preserve">2.37518787384033</t>
@@ -1313,16 +1313,16 @@
     <t xml:space="preserve">2.47661948204041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30756688117981</t>
+    <t xml:space="preserve">2.30756711959839</t>
   </si>
   <si>
     <t xml:space="preserve">2.23994565010071</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29430222511292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23437643051147</t>
+    <t xml:space="preserve">2.29430246353149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23437666893005</t>
   </si>
   <si>
     <t xml:space="preserve">2.24293732643127</t>
@@ -1331,55 +1331,55 @@
     <t xml:space="preserve">2.33710670471191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25149846076965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27718067169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26861977577209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44839715957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37134981155396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31142377853394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28574156761169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26005887985229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35422825813293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22581553459167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20869374275208</t>
+    <t xml:space="preserve">2.2514979839325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27718091011047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26861953735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44839692115784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37134957313538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31142401695251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28574180603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26005911827087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35422778129578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22581577301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20869398117065</t>
   </si>
   <si>
     <t xml:space="preserve">2.30286312103271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31998467445374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37991046905518</t>
+    <t xml:space="preserve">2.31998491287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37991070747375</t>
   </si>
   <si>
     <t xml:space="preserve">2.40559315681458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3970320224762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32854533195496</t>
+    <t xml:space="preserve">2.39703226089478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32854557037354</t>
   </si>
   <si>
     <t xml:space="preserve">2.38847160339355</t>
@@ -1391,19 +1391,19 @@
     <t xml:space="preserve">2.34566736221313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20013284683228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18301153182983</t>
+    <t xml:space="preserve">2.20013308525085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18301177024841</t>
   </si>
   <si>
     <t xml:space="preserve">2.4398365020752</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54256629943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60249209403992</t>
+    <t xml:space="preserve">2.54256653785706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6024923324585</t>
   </si>
   <si>
     <t xml:space="preserve">2.69666147232056</t>
@@ -1412,10 +1412,10 @@
     <t xml:space="preserve">2.77370882034302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63673567771912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67097878456116</t>
+    <t xml:space="preserve">2.63673543930054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67097854614258</t>
   </si>
   <si>
     <t xml:space="preserve">2.61961364746094</t>
@@ -1424,31 +1424,31 @@
     <t xml:space="preserve">2.65385699272156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68810057640076</t>
+    <t xml:space="preserve">2.68810033798218</t>
   </si>
   <si>
     <t xml:space="preserve">2.64529609680176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.713782787323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7223436832428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07333755493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5270619392395</t>
+    <t xml:space="preserve">2.71378326416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72234392166138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07333779335022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52706146240234</t>
   </si>
   <si>
     <t xml:space="preserve">3.59554839134216</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6554741859436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58698773384094</t>
+    <t xml:space="preserve">3.65547442436218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58698749542236</t>
   </si>
   <si>
     <t xml:space="preserve">3.6126697063446</t>
@@ -1457,67 +1457,67 @@
     <t xml:space="preserve">3.53562259674072</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42433190345764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54418325424194</t>
+    <t xml:space="preserve">3.42433142662048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54418349266052</t>
   </si>
   <si>
     <t xml:space="preserve">3.56986594200134</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5527446269989</t>
+    <t xml:space="preserve">3.55274438858032</t>
   </si>
   <si>
     <t xml:space="preserve">3.56130504608154</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50993990898132</t>
+    <t xml:space="preserve">3.50993967056274</t>
   </si>
   <si>
     <t xml:space="preserve">3.48425769805908</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57842707633972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63835263252258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74108219146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16912364959717</t>
+    <t xml:space="preserve">3.57842659950256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.638352394104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74108195304871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16912412643433</t>
   </si>
   <si>
     <t xml:space="preserve">4.60572624206543</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15361976623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62284755706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19480609893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45163106918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53723955154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52011775970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58860445022583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34890127182007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16056346893311</t>
+    <t xml:space="preserve">5.15361928939819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62284803390503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19480657577515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45163154602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53723907470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52011823654175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58860492706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34890174865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16056394577026</t>
   </si>
   <si>
     <t xml:space="preserve">4.23761081695557</t>
@@ -1526,7 +1526,7 @@
     <t xml:space="preserve">4.29753637313843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8951780796051</t>
+    <t xml:space="preserve">3.89517688751221</t>
   </si>
   <si>
     <t xml:space="preserve">3.27879762649536</t>
@@ -1535,7 +1535,7 @@
     <t xml:space="preserve">3.25311517715454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89356064796448</t>
+    <t xml:space="preserve">2.8935604095459</t>
   </si>
   <si>
     <t xml:space="preserve">3.15894627571106</t>
@@ -1547,7 +1547,7 @@
     <t xml:space="preserve">3.0390944480896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44145345687866</t>
+    <t xml:space="preserve">3.44145369529724</t>
   </si>
   <si>
     <t xml:space="preserve">3.3815279006958</t>
@@ -1559,10 +1559,10 @@
     <t xml:space="preserve">3.84381222724915</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83525156974792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87805581092834</t>
+    <t xml:space="preserve">3.83525133132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87805604934692</t>
   </si>
   <si>
     <t xml:space="preserve">3.76676535606384</t>
@@ -1571,22 +1571,22 @@
     <t xml:space="preserve">3.88661646842957</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85237336158752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92942070960999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95510292053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93798184394836</t>
+    <t xml:space="preserve">3.8523736000061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92942142486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95510363578796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93798136711121</t>
   </si>
   <si>
     <t xml:space="preserve">4.11775875091553</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25473213195801</t>
+    <t xml:space="preserve">4.25473165512085</t>
   </si>
   <si>
     <t xml:space="preserve">4.22904968261719</t>
@@ -1595,34 +1595,34 @@
     <t xml:space="preserve">4.26329326629639</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28041505813599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43450975418091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20336675643921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00646781921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10919857025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15200233459473</t>
+    <t xml:space="preserve">4.28041458129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43450927734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20336723327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00646877288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10919809341431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15200281143188</t>
   </si>
   <si>
     <t xml:space="preserve">4.08351564407349</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94654250144958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07495498657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02359008789062</t>
+    <t xml:space="preserve">3.94654273986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07495450973511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02358913421631</t>
   </si>
   <si>
     <t xml:space="preserve">3.96366405487061</t>
@@ -1631,37 +1631,37 @@
     <t xml:space="preserve">4.13488101959229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12631988525391</t>
+    <t xml:space="preserve">4.12632036209106</t>
   </si>
   <si>
     <t xml:space="preserve">5.01664638519287</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70845651626587</t>
+    <t xml:space="preserve">4.70845556259155</t>
   </si>
   <si>
     <t xml:space="preserve">4.91391611099243</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96528100967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94816017150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20498418807983</t>
+    <t xml:space="preserve">4.96528148651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94815921783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20498466491699</t>
   </si>
   <si>
     <t xml:space="preserve">5.56453895568848</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68439054489136</t>
+    <t xml:space="preserve">5.68439102172852</t>
   </si>
   <si>
     <t xml:space="preserve">5.95833730697632</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90697193145752</t>
+    <t xml:space="preserve">5.90697240829468</t>
   </si>
   <si>
     <t xml:space="preserve">5.88985061645508</t>
@@ -1670,268 +1670,268 @@
     <t xml:space="preserve">6.57471656799316</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12955331802368</t>
+    <t xml:space="preserve">6.12955379486084</t>
   </si>
   <si>
     <t xml:space="preserve">6.4035005569458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01987981796265</t>
+    <t xml:space="preserve">7.01987934112549</t>
   </si>
   <si>
     <t xml:space="preserve">7.20821809768677</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32807064056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.054123878479</t>
+    <t xml:space="preserve">7.32807016372681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05412292480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00275897979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42397785186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28357076644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8799033164978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9676570892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59909057617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51133728027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73949670791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.844801902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82725095748901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68684482574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6692943572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45868492126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40603256225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31827783584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80970001220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17826652526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3537745475769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26602029800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05541086196899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07296228408813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63419198989868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44113445281982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30072736740112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05501651763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03746604919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37053632736206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40563821792603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52849340438843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65134906768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12521982192993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96726322174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01991510391235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91460990905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84440755844116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94971179962158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86195802688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82685661315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93216180801392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87950897216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79175519943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68645048141479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45829010009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63379812240601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70400094985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58114576339722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66890048980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56359529495239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61624717712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49339246749878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31788396835327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17747831344604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2652325630188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28278255462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35298585891724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42318868637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47584056854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38808727264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5109429359436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77420520782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44073963165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54604434967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23052453994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35338020324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16032123565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37093067169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47623538970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42358303070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54643869400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98520803451538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33622312545776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09051275253296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16071510314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19581604003906</t>
   </si>
   <si>
     <t xml:space="preserve">7.00275850296021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42397689819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28357124328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8799033164978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96765661239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59909105300903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51133680343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73949670791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84480142593384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82725143432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68684482574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66929388046265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45868444442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40603256225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31827783584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80970048904419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17826652526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3537745475769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26601982116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05541086196899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07296228408813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63419198989868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44113397598267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30072736740112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05501651763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03746604919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37053632736206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40563869476318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52849388122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65134906768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12521982192993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96726322174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01991558074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91461038589478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.844407081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94971227645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86195850372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82685661315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93216180801392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87950897216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79175519943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68645048141479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45829010009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63379812240601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70400094985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58114624023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66890001296997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56359529495239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61624765396118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49339199066162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31788444519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17747831344604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26523208618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28278303146362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35298585891724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42318868637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47584104537964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3880877494812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5109429359436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77420425415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44073963165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54604482650757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23052453994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35337972640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16032123565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37093114852905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47623586654663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42358303070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54643869400024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98520755767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33622360229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0905122756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16071557998657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19581699371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00275897979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95010662078857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14316463470459</t>
+    <t xml:space="preserve">6.95010614395142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14316511154175</t>
   </si>
   <si>
     <t xml:space="preserve">7.12561368942261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02030944824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84519529342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33661651611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31906604766846</t>
+    <t xml:space="preserve">7.02030992507935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84519577026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3366174697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31906700134277</t>
   </si>
   <si>
     <t xml:space="preserve">8.42437171936035</t>
@@ -1940,25 +1940,25 @@
     <t xml:space="preserve">9.0825252532959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68763256072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03864765167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30190944671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2763719558716</t>
+    <t xml:space="preserve">8.6876335144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03864860534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30191040039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2763729095459</t>
   </si>
   <si>
     <t xml:space="preserve">13.1630802154541</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0753259658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1192026138306</t>
+    <t xml:space="preserve">13.075325012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1192035675049</t>
   </si>
   <si>
     <t xml:space="preserve">12.8559417724609</t>
@@ -1979,19 +1979,19 @@
     <t xml:space="preserve">10.8814792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1539115905762</t>
+    <t xml:space="preserve">12.1539106369019</t>
   </si>
   <si>
     <t xml:space="preserve">11.6712646484375</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7151412963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4518804550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0569877624512</t>
+    <t xml:space="preserve">11.715142250061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4518795013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0569868087769</t>
   </si>
   <si>
     <t xml:space="preserve">11.4957571029663</t>
@@ -2000,13 +2000,13 @@
     <t xml:space="preserve">11.4080018997192</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8906488418579</t>
+    <t xml:space="preserve">11.8906478881836</t>
   </si>
   <si>
     <t xml:space="preserve">11.8028955459595</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3202505111694</t>
+    <t xml:space="preserve">11.3202476501465</t>
   </si>
   <si>
     <t xml:space="preserve">11.627387046814</t>
@@ -2015,16 +2015,16 @@
     <t xml:space="preserve">11.1447401046753</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6182193756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5304641723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5743408203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.749849319458</t>
+    <t xml:space="preserve">10.618218421936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5304651260376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5743398666382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7498483657837</t>
   </si>
   <si>
     <t xml:space="preserve">10.6620950698853</t>
@@ -2036,22 +2036,22 @@
     <t xml:space="preserve">9.78455543518066</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91618824005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0916938781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2324953079224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1886177062988</t>
+    <t xml:space="preserve">9.91618633270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0916948318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.232494354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1886186599731</t>
   </si>
   <si>
     <t xml:space="preserve">11.1008634567261</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3553495407104</t>
+    <t xml:space="preserve">11.3553504943848</t>
   </si>
   <si>
     <t xml:space="preserve">11.267596244812</t>
@@ -2066,19 +2066,19 @@
     <t xml:space="preserve">11.3729009628296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2851467132568</t>
+    <t xml:space="preserve">11.2851476669312</t>
   </si>
   <si>
     <t xml:space="preserve">11.1973934173584</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8467712402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9871778488159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2855424880981</t>
+    <t xml:space="preserve">11.8467721939087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9871788024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2855415344238</t>
   </si>
   <si>
     <t xml:space="preserve">12.2504396438599</t>
@@ -4275,6 +4275,9 @@
   </si>
   <si>
     <t xml:space="preserve">19.4400005340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1000003814697</t>
   </si>
 </sst>
 </file>
@@ -69353,7 +69356,7 @@
     </row>
     <row r="2491">
       <c r="A2491" s="1" t="n">
-        <v>45946.6495486111</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B2491" t="n">
         <v>17439</v>
@@ -69374,6 +69377,32 @@
         <v>1414</v>
       </c>
       <c r="H2491" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" s="1" t="n">
+        <v>45947.6493634259</v>
+      </c>
+      <c r="B2492" t="n">
+        <v>16773</v>
+      </c>
+      <c r="C2492" t="n">
+        <v>19.3999996185303</v>
+      </c>
+      <c r="D2492" t="n">
+        <v>18.8999996185303</v>
+      </c>
+      <c r="E2492" t="n">
+        <v>19.3999996185303</v>
+      </c>
+      <c r="F2492" t="n">
+        <v>19.1000003814697</v>
+      </c>
+      <c r="G2492" t="s">
+        <v>1421</v>
+      </c>
+      <c r="H2492" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ARN.MI.xlsx
+++ b/data/ARN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1421" uniqueCount="1421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1422" uniqueCount="1422">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,208 +38,208 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92215013504028</t>
+    <t xml:space="preserve">1.92214977741241</t>
   </si>
   <si>
     <t xml:space="preserve">ARN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94450104236603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91736090183258</t>
+    <t xml:space="preserve">1.94450092315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.917360663414</t>
   </si>
   <si>
     <t xml:space="preserve">1.90778195858002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88383495807648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93172919750214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91576457023621</t>
+    <t xml:space="preserve">1.88383460044861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93172907829285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91576433181763</t>
   </si>
   <si>
     <t xml:space="preserve">1.83434450626373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83594071865082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91097509860992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.807204246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74973106384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71620547771454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80401122570038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81039714813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79602897167206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77208185195923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70662677288055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69704782962799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69066202640533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6762934923172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7002409696579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69864428043365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67469727993011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66671502590179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66032886505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81518685817719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82795822620392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86148428916931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88543128967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89181733131409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92853629589081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95407962799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90618562698364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86787009239197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88064193725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85190510749817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85988771915436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85509812831879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79283571243286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78804659843445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78006458282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75611734390259</t>
+    <t xml:space="preserve">1.8359409570694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91097474098206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80720412731171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74973130226135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71620559692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80401134490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81039690971375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79602909088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77208197116852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70662665367126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69704759120941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69066190719604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67629373073578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70024108886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69864439964294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67469751834869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6667149066925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66032910346985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81518661975861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82795834541321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86148405075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88543117046356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89181697368622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92853593826294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95407927036285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90618538856506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86787021160126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88064169883728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85190558433533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85988783836365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85509836673737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79283595085144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78804671764374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78006434440613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7561172246933</t>
   </si>
   <si>
     <t xml:space="preserve">1.76888883113861</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7640997171402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78485369682312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77048528194427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72099459171295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73536288738251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80241465568542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76250314712524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74494183063507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73216998577118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73695957660675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7433454990387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75132751464844</t>
+    <t xml:space="preserve">1.76409983634949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78485381603241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77048552036285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72099483013153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73536324501038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80241477489471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76250278949738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74494194984436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73217034339905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73695993423462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74334561824799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7513279914856</t>
   </si>
   <si>
     <t xml:space="preserve">1.68587255477905</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67789018154144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65234649181366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6204172372818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64276802539825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59008455276489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60285615921021</t>
+    <t xml:space="preserve">1.67789006233215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65234673023224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62041711807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64276778697968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59008431434631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60285604000092</t>
   </si>
   <si>
     <t xml:space="preserve">1.54937446117401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51185727119446</t>
+    <t xml:space="preserve">1.51185739040375</t>
   </si>
   <si>
     <t xml:space="preserve">1.45598089694977</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43682312965393</t>
+    <t xml:space="preserve">1.43682324886322</t>
   </si>
   <si>
     <t xml:space="preserve">1.46955072879791</t>
@@ -251,13 +251,13 @@
     <t xml:space="preserve">1.47673487663269</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47274374961853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46875274181366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49669086933136</t>
+    <t xml:space="preserve">1.47274386882782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46875262260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49669098854065</t>
   </si>
   <si>
     <t xml:space="preserve">1.47593665122986</t>
@@ -269,22 +269,22 @@
     <t xml:space="preserve">1.47753310203552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43841946125031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40090250968933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34901738166809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30910539627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34342968463898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32666683197021</t>
+    <t xml:space="preserve">1.43841958045959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40090274810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3490172624588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30910551548004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34342956542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32666671276093</t>
   </si>
   <si>
     <t xml:space="preserve">1.34103488922119</t>
@@ -293,43 +293,43 @@
     <t xml:space="preserve">1.31708788871765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38653445243835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39691150188446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40649032592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30671083927155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32347369194031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30591249465942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31229841709137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28994786739349</t>
+    <t xml:space="preserve">1.38653433322906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39691138267517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40649020671844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30671072006226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3234738111496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30591285228729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31229865550995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2899477481842</t>
   </si>
   <si>
     <t xml:space="preserve">1.28515863418579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28595674037933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33305251598358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33704376220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30112314224243</t>
+    <t xml:space="preserve">1.28595662117004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33305239677429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33704352378845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30112326145172</t>
   </si>
   <si>
     <t xml:space="preserve">1.36104869842529</t>
@@ -338,40 +338,40 @@
     <t xml:space="preserve">1.34627258777618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35283982753754</t>
+    <t xml:space="preserve">1.35283970832825</t>
   </si>
   <si>
     <t xml:space="preserve">1.33806371688843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27157080173492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28880989551544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29291415214539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30686938762665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33888459205627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34955632686615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34380972385406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33642184734344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34709370136261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30522775650024</t>
+    <t xml:space="preserve">1.27157092094421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28880965709686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29291450977325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30686962604523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33888447284698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34955644607544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34380984306335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33642172813416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34709346294403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30522763729095</t>
   </si>
   <si>
     <t xml:space="preserve">1.29127240180969</t>
@@ -383,19 +383,19 @@
     <t xml:space="preserve">1.32164573669434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26828730106354</t>
+    <t xml:space="preserve">1.26828718185425</t>
   </si>
   <si>
     <t xml:space="preserve">1.27239179611206</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28798890113831</t>
+    <t xml:space="preserve">1.2879890203476</t>
   </si>
   <si>
     <t xml:space="preserve">1.2970187664032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24858582019806</t>
+    <t xml:space="preserve">1.24858570098877</t>
   </si>
   <si>
     <t xml:space="preserve">1.32657098770142</t>
@@ -407,64 +407,64 @@
     <t xml:space="preserve">1.3594069480896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42015337944031</t>
+    <t xml:space="preserve">1.4201534986496</t>
   </si>
   <si>
     <t xml:space="preserve">1.48664605617523</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53343749046326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51619839668274</t>
+    <t xml:space="preserve">1.53343737125397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51619863510132</t>
   </si>
   <si>
     <t xml:space="preserve">1.51866114139557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43739223480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4677654504776</t>
+    <t xml:space="preserve">1.43739235401154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46776568889618</t>
   </si>
   <si>
     <t xml:space="preserve">1.43000411987305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40948176383972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44478034973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55970597267151</t>
+    <t xml:space="preserve">1.40948164463043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44478023052216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5597060918808</t>
   </si>
   <si>
     <t xml:space="preserve">1.61798989772797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70582592487335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74851262569427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72388553619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6828408241272</t>
+    <t xml:space="preserve">1.70582616329193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74851286411285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72388577461243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68284046649933</t>
   </si>
   <si>
     <t xml:space="preserve">1.67463171482086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.651646733284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64179587364197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6713479757309</t>
+    <t xml:space="preserve">1.65164661407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64179575443268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67134821414948</t>
   </si>
   <si>
     <t xml:space="preserve">1.6647812128067</t>
@@ -476,10 +476,10 @@
     <t xml:space="preserve">1.69597518444061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69433343410492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65821373462677</t>
+    <t xml:space="preserve">1.69433319568634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65821385383606</t>
   </si>
   <si>
     <t xml:space="preserve">1.6811990737915</t>
@@ -488,10 +488,10 @@
     <t xml:space="preserve">1.68776607513428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6680645942688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65000486373901</t>
+    <t xml:space="preserve">1.66806471347809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6500049829483</t>
   </si>
   <si>
     <t xml:space="preserve">1.66313922405243</t>
@@ -500,76 +500,76 @@
     <t xml:space="preserve">1.67791545391083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03746891021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04403591156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0391104221344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04075241088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05224466323853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04731965065002</t>
+    <t xml:space="preserve">2.03746843338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04403614997864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03911066055298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04075217247009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0522449016571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04731917381287</t>
   </si>
   <si>
     <t xml:space="preserve">2.04239416122437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19836473464966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24105167388916</t>
+    <t xml:space="preserve">2.19836449623108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.241051197052</t>
   </si>
   <si>
     <t xml:space="preserve">2.18851375579834</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17537951469421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14582753181458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00627493858337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98821461200714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99314022064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99806559085846</t>
+    <t xml:space="preserve">2.17537927627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.145827293396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00627422332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98821485042572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99313986301422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99806571006775</t>
   </si>
   <si>
     <t xml:space="preserve">1.99642372131348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99970746040344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00299143791199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00791645050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01119995117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02597570419312</t>
+    <t xml:space="preserve">1.99970757961273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00299096107483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00791621208191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01120018959045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02597594261169</t>
   </si>
   <si>
     <t xml:space="preserve">2.03254342079163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02105069160461</t>
+    <t xml:space="preserve">2.02105045318604</t>
   </si>
   <si>
     <t xml:space="preserve">2.01940894126892</t>
@@ -578,10 +578,10 @@
     <t xml:space="preserve">2.02433466911316</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07687187194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05881214141846</t>
+    <t xml:space="preserve">2.07687163352966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05881190299988</t>
   </si>
   <si>
     <t xml:space="preserve">2.09657311439514</t>
@@ -593,34 +593,34 @@
     <t xml:space="preserve">2.33955883979797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27552890777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32478308677673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27881288528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25746965408325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2985143661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26075315475464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28045439720154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30672311782837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3559775352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34120082855225</t>
+    <t xml:space="preserve">2.27552914619446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32478284835815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27881264686584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25746941566467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29851412773132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26075291633606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2804548740387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30672335624695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35597681999207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34120106697083</t>
   </si>
   <si>
     <t xml:space="preserve">2.34284257888794</t>
@@ -632,13 +632,13 @@
     <t xml:space="preserve">2.44627594947815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39209628105164</t>
+    <t xml:space="preserve">2.39209651947021</t>
   </si>
   <si>
     <t xml:space="preserve">2.3822455406189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38717150688171</t>
+    <t xml:space="preserve">2.38717079162598</t>
   </si>
   <si>
     <t xml:space="preserve">2.38388776779175</t>
@@ -647,7 +647,7 @@
     <t xml:space="preserve">2.4052312374115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38060450553894</t>
+    <t xml:space="preserve">2.38060402870178</t>
   </si>
   <si>
     <t xml:space="preserve">2.42164897918701</t>
@@ -659,13 +659,13 @@
     <t xml:space="preserve">2.32314109802246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35433530807495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41015648841858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40687298774719</t>
+    <t xml:space="preserve">2.35433554649353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40687274932861</t>
   </si>
   <si>
     <t xml:space="preserve">2.4380669593811</t>
@@ -674,16 +674,16 @@
     <t xml:space="preserve">2.41836547851562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29030513763428</t>
+    <t xml:space="preserve">2.29030561447144</t>
   </si>
   <si>
     <t xml:space="preserve">2.34941005706787</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36418604850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3756787776947</t>
+    <t xml:space="preserve">2.36418628692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37567853927612</t>
   </si>
   <si>
     <t xml:space="preserve">2.40194749832153</t>
@@ -695,13 +695,13 @@
     <t xml:space="preserve">2.36746954917908</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37075304985046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37239527702332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.362544298172</t>
+    <t xml:space="preserve">2.37075328826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37239503860474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36254453659058</t>
   </si>
   <si>
     <t xml:space="preserve">2.3658275604248</t>
@@ -710,34 +710,34 @@
     <t xml:space="preserve">2.3953800201416</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37732076644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37403678894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38881278038025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39373826980591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3904550075531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41343975067139</t>
+    <t xml:space="preserve">2.37732028961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37403702735901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38881301879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39373850822449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39045476913452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41343998908997</t>
   </si>
   <si>
     <t xml:space="preserve">2.40358924865723</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40030574798584</t>
+    <t xml:space="preserve">2.40030550956726</t>
   </si>
   <si>
     <t xml:space="preserve">2.40851449966431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42329049110413</t>
+    <t xml:space="preserve">2.42329096794128</t>
   </si>
   <si>
     <t xml:space="preserve">2.43149971961975</t>
@@ -755,25 +755,25 @@
     <t xml:space="preserve">2.34612655639648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43642520904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42657446861267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42985796928406</t>
+    <t xml:space="preserve">2.43642473220825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42657399177551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42985773086548</t>
   </si>
   <si>
     <t xml:space="preserve">2.45284295082092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47701287269592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47867965698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49201488494873</t>
+    <t xml:space="preserve">2.4770131111145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.478679895401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49201512336731</t>
   </si>
   <si>
     <t xml:space="preserve">2.49368214607239</t>
@@ -788,10 +788,10 @@
     <t xml:space="preserve">2.48201370239258</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46867847442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4586775302887</t>
+    <t xml:space="preserve">2.46867871284485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45867729187012</t>
   </si>
   <si>
     <t xml:space="preserve">2.46201109886169</t>
@@ -800,16 +800,16 @@
     <t xml:space="preserve">2.45534348487854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41700458526611</t>
+    <t xml:space="preserve">2.41700482368469</t>
   </si>
   <si>
     <t xml:space="preserve">2.40867018699646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36699771881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34199404716492</t>
+    <t xml:space="preserve">2.36699748039246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3419942855835</t>
   </si>
   <si>
     <t xml:space="preserve">2.36866450309753</t>
@@ -818,43 +818,43 @@
     <t xml:space="preserve">2.35366225242615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38533353805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38366651535034</t>
+    <t xml:space="preserve">2.385333776474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38366675376892</t>
   </si>
   <si>
     <t xml:space="preserve">2.36366391181946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32532501220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31699085235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28531956672668</t>
+    <t xml:space="preserve">2.32532548904419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31699061393738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28531980514526</t>
   </si>
   <si>
     <t xml:space="preserve">2.28698658943176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29698777198792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31532382965088</t>
+    <t xml:space="preserve">2.29698801040649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31532430648804</t>
   </si>
   <si>
     <t xml:space="preserve">2.28365254402161</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28865313529968</t>
+    <t xml:space="preserve">2.28865337371826</t>
   </si>
   <si>
     <t xml:space="preserve">2.29032039642334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30198907852173</t>
+    <t xml:space="preserve">2.30198884010315</t>
   </si>
   <si>
     <t xml:space="preserve">2.30365562438965</t>
@@ -863,46 +863,46 @@
     <t xml:space="preserve">2.29365396499634</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24198031425476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26698350906372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26865077018738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32699227333069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31865739822388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31032299995422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24364733695984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25031471252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2253110408783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25198173522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2219774723053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20697593688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20030760765076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16863632202148</t>
+    <t xml:space="preserve">2.24198007583618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2669837474823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2686505317688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32699179649353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31865763664246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3103232383728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24364709854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25031447410583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22531127929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25198125839233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22197723388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20697522163391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20030784606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16863656044006</t>
   </si>
   <si>
     <t xml:space="preserve">2.17863821983337</t>
@@ -911,73 +911,73 @@
     <t xml:space="preserve">2.16696953773499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18697285652161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1969735622406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18363833427429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18530583381653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1919732093811</t>
+    <t xml:space="preserve">2.18697261810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19697380065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18363857269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18530559539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19197344779968</t>
   </si>
   <si>
     <t xml:space="preserve">2.17530417442322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14196634292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15363454818726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1436333656311</t>
+    <t xml:space="preserve">2.1419665813446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15363430976868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14363288879395</t>
   </si>
   <si>
     <t xml:space="preserve">2.13529849052429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12696385383606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12863111495972</t>
+    <t xml:space="preserve">2.12696409225464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12863087654114</t>
   </si>
   <si>
     <t xml:space="preserve">2.12029647827148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13029789924622</t>
+    <t xml:space="preserve">2.13029813766479</t>
   </si>
   <si>
     <t xml:space="preserve">2.11862969398499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37366533279419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37533211708069</t>
+    <t xml:space="preserve">2.37366557121277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37533187866211</t>
   </si>
   <si>
     <t xml:space="preserve">2.40700340270996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39533495903015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39200139045715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49868273735046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49534916877747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5086841583252</t>
+    <t xml:space="preserve">2.39533472061157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39200091362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49868249893188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49534893035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50868439674377</t>
   </si>
   <si>
     <t xml:space="preserve">2.51201772689819</t>
@@ -986,25 +986,25 @@
     <t xml:space="preserve">2.51535177230835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51701879501343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52368640899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5253529548645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54535603523254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53368759155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53202128410339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54035496711731</t>
+    <t xml:space="preserve">2.51701903343201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.523686170578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52535343170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54535579681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53368782997131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53202056884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54035568237305</t>
   </si>
   <si>
     <t xml:space="preserve">2.52702021598816</t>
@@ -1013,109 +1013,109 @@
     <t xml:space="preserve">2.53868842124939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53702187538147</t>
+    <t xml:space="preserve">2.53702139854431</t>
   </si>
   <si>
     <t xml:space="preserve">2.49701619148254</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42700624465942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50034976005554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50535035133362</t>
+    <t xml:space="preserve">2.42700600624084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50034952163696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5053505897522</t>
   </si>
   <si>
     <t xml:space="preserve">2.48368072509766</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45200943946838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51368474960327</t>
+    <t xml:space="preserve">2.45200967788696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51368498802185</t>
   </si>
   <si>
     <t xml:space="preserve">2.54202222824097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54868984222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51035118103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52035236358643</t>
+    <t xml:space="preserve">2.54868960380554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51035141944885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52035212516785</t>
   </si>
   <si>
     <t xml:space="preserve">2.47201251983643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50201678276062</t>
+    <t xml:space="preserve">2.5020170211792</t>
   </si>
   <si>
     <t xml:space="preserve">2.48701453208923</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00041913986206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81706070899963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75038433074951</t>
+    <t xml:space="preserve">3.0004198551178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81706047058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75038456916809</t>
   </si>
   <si>
     <t xml:space="preserve">2.7170467376709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80872583389282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80039191246033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83372974395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78372263908386</t>
+    <t xml:space="preserve">2.8087260723114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80039143562317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83372950553894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78372240066528</t>
   </si>
   <si>
     <t xml:space="preserve">2.84206414222717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75871896743774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85039877891541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85873341560364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89207124710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82539534568787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72538113594055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61703276634216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64203667640686</t>
+    <t xml:space="preserve">2.75871920585632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85039854049683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85873293876648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89207100868225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82539510726929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72538089752197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61703252792358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64203643798828</t>
   </si>
   <si>
     <t xml:space="preserve">2.70037794113159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65870499610901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6253674030304</t>
+    <t xml:space="preserve">2.65870547294617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62536764144897</t>
   </si>
   <si>
     <t xml:space="preserve">2.63370180130005</t>
@@ -1124,7 +1124,7 @@
     <t xml:space="preserve">2.59202909469604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66703939437866</t>
+    <t xml:space="preserve">2.66703987121582</t>
   </si>
   <si>
     <t xml:space="preserve">2.70871210098267</t>
@@ -1136,28 +1136,28 @@
     <t xml:space="preserve">2.65037059783936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68370866775513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60036373138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58369445800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56702566146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76705360412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73371577262878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79205703735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86706781387329</t>
+    <t xml:space="preserve">2.68370890617371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6003634929657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58369469642639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56702589988708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76705384254456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73371553421021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79205679893494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86706757545471</t>
   </si>
   <si>
     <t xml:space="preserve">2.87540221214294</t>
@@ -1172,7 +1172,7 @@
     <t xml:space="preserve">2.78091382980347</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72174549102783</t>
+    <t xml:space="preserve">2.72174572944641</t>
   </si>
   <si>
     <t xml:space="preserve">2.73019814491272</t>
@@ -1181,25 +1181,25 @@
     <t xml:space="preserve">2.77246117591858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.645672082901</t>
+    <t xml:space="preserve">2.64567184448242</t>
   </si>
   <si>
     <t xml:space="preserve">2.70484018325806</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68793511390686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6625771522522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69638800621033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65412425994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60340857505798</t>
+    <t xml:space="preserve">2.68793487548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66257739067078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69638776779175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65412449836731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60340905189514</t>
   </si>
   <si>
     <t xml:space="preserve">2.63721919059753</t>
@@ -1208,13 +1208,13 @@
     <t xml:space="preserve">2.61186099052429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57805061340332</t>
+    <t xml:space="preserve">2.5780508518219</t>
   </si>
   <si>
     <t xml:space="preserve">2.59495615959167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50197696685791</t>
+    <t xml:space="preserve">2.50197720527649</t>
   </si>
   <si>
     <t xml:space="preserve">2.49352478981018</t>
@@ -1223,13 +1223,13 @@
     <t xml:space="preserve">2.54424047470093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56114554405212</t>
+    <t xml:space="preserve">2.5611457824707</t>
   </si>
   <si>
     <t xml:space="preserve">2.58650350570679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51888227462769</t>
+    <t xml:space="preserve">2.51888251304626</t>
   </si>
   <si>
     <t xml:space="preserve">2.53578782081604</t>
@@ -1238,19 +1238,19 @@
     <t xml:space="preserve">2.55269312858582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5104296207428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56959795951843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46816635131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48507165908813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41745066642761</t>
+    <t xml:space="preserve">2.51043009757996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56959843635559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46816682815552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48507213592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41745090484619</t>
   </si>
   <si>
     <t xml:space="preserve">2.45126152038574</t>
@@ -1259,16 +1259,16 @@
     <t xml:space="preserve">2.39209318161011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38364052772522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27375650405884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29911398887634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36673521995544</t>
+    <t xml:space="preserve">2.38364028930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27375626564026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29911422729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36673498153687</t>
   </si>
   <si>
     <t xml:space="preserve">2.35828280448914</t>
@@ -1277,7 +1277,7 @@
     <t xml:space="preserve">2.43435621261597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4259033203125</t>
+    <t xml:space="preserve">2.42590308189392</t>
   </si>
   <si>
     <t xml:space="preserve">2.34982991218567</t>
@@ -1286,40 +1286,40 @@
     <t xml:space="preserve">2.28220891952515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32447195053101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4089982509613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45971417427063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44280886650085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33292484283447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34137725830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40054559707642</t>
+    <t xml:space="preserve">2.32447218894958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40899801254272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45971393585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44280862808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33292460441589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3413770198822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40054535865784</t>
   </si>
   <si>
     <t xml:space="preserve">2.37518787384033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47661924362183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30756688117981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23994612693787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29430246353149</t>
+    <t xml:space="preserve">2.47661948204041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30756664276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23994541168213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29430198669434</t>
   </si>
   <si>
     <t xml:space="preserve">2.23437666893005</t>
@@ -1331,19 +1331,19 @@
     <t xml:space="preserve">2.33710670471191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2514979839325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27718091011047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26862001419067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44839692115784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37134981155396</t>
+    <t xml:space="preserve">2.25149822235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27718067169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26861977577209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.448397397995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37134957313538</t>
   </si>
   <si>
     <t xml:space="preserve">2.31142401695251</t>
@@ -1355,10 +1355,10 @@
     <t xml:space="preserve">2.26005911827087</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35422801971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22581553459167</t>
+    <t xml:space="preserve">2.35422825813293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22581577301025</t>
   </si>
   <si>
     <t xml:space="preserve">2.20869374275208</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">2.30286312103271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31998491287231</t>
+    <t xml:space="preserve">2.31998443603516</t>
   </si>
   <si>
     <t xml:space="preserve">2.37991070747375</t>
@@ -1376,7 +1376,7 @@
     <t xml:space="preserve">2.40559315681458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3970320224762</t>
+    <t xml:space="preserve">2.39703226089478</t>
   </si>
   <si>
     <t xml:space="preserve">2.32854580879211</t>
@@ -1385,37 +1385,37 @@
     <t xml:space="preserve">2.38847160339355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36278891563416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34566736221313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20013332366943</t>
+    <t xml:space="preserve">2.36278915405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34566712379456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20013308525085</t>
   </si>
   <si>
     <t xml:space="preserve">2.18301153182983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4398365020752</t>
+    <t xml:space="preserve">2.43983626365662</t>
   </si>
   <si>
     <t xml:space="preserve">2.54256629943848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60249185562134</t>
+    <t xml:space="preserve">2.60249209403992</t>
   </si>
   <si>
     <t xml:space="preserve">2.69666123390198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7737090587616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63673520088196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67097878456116</t>
+    <t xml:space="preserve">2.77370858192444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63673543930054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67097854614258</t>
   </si>
   <si>
     <t xml:space="preserve">2.61961364746094</t>
@@ -1424,7 +1424,7 @@
     <t xml:space="preserve">2.65385699272156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68810033798218</t>
+    <t xml:space="preserve">2.68810057640076</t>
   </si>
   <si>
     <t xml:space="preserve">2.64529609680176</t>
@@ -1433,37 +1433,37 @@
     <t xml:space="preserve">2.71378302574158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72234392166138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07333779335022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52706146240234</t>
+    <t xml:space="preserve">2.7223436832428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07333755493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5270619392395</t>
   </si>
   <si>
     <t xml:space="preserve">3.59554815292358</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65547394752502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58698749542236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61266994476318</t>
+    <t xml:space="preserve">3.6554741859436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58698773384094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6126697063446</t>
   </si>
   <si>
     <t xml:space="preserve">3.5356228351593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42433190345764</t>
+    <t xml:space="preserve">3.42433214187622</t>
   </si>
   <si>
     <t xml:space="preserve">3.54418349266052</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56986618041992</t>
+    <t xml:space="preserve">3.56986594200134</t>
   </si>
   <si>
     <t xml:space="preserve">3.55274438858032</t>
@@ -1475,16 +1475,16 @@
     <t xml:space="preserve">3.50993990898132</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48425769805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57842659950256</t>
+    <t xml:space="preserve">3.4842574596405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57842683792114</t>
   </si>
   <si>
     <t xml:space="preserve">3.63835287094116</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74108242988586</t>
+    <t xml:space="preserve">3.74108266830444</t>
   </si>
   <si>
     <t xml:space="preserve">4.16912364959717</t>
@@ -1493,7 +1493,7 @@
     <t xml:space="preserve">4.60572624206543</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15361928939819</t>
+    <t xml:space="preserve">5.15361976623535</t>
   </si>
   <si>
     <t xml:space="preserve">4.62284803390503</t>
@@ -1502,16 +1502,16 @@
     <t xml:space="preserve">4.19480657577515</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45163106918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53724002838135</t>
+    <t xml:space="preserve">4.45163154602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53723955154419</t>
   </si>
   <si>
     <t xml:space="preserve">4.52011823654175</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58860492706299</t>
+    <t xml:space="preserve">4.58860397338867</t>
   </si>
   <si>
     <t xml:space="preserve">4.34890127182007</t>
@@ -1526,13 +1526,13 @@
     <t xml:space="preserve">4.29753637313843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89517712593079</t>
+    <t xml:space="preserve">3.89517760276794</t>
   </si>
   <si>
     <t xml:space="preserve">3.27879762649536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25311517715454</t>
+    <t xml:space="preserve">3.25311541557312</t>
   </si>
   <si>
     <t xml:space="preserve">2.8935604095459</t>
@@ -1544,7 +1544,7 @@
     <t xml:space="preserve">3.16750693321228</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03909468650818</t>
+    <t xml:space="preserve">3.0390944480896</t>
   </si>
   <si>
     <t xml:space="preserve">3.44145369529724</t>
@@ -1553,121 +1553,121 @@
     <t xml:space="preserve">3.38152766227722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39008855819702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84381222724915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83525109291077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8780562877655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76676440238953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88661694526672</t>
+    <t xml:space="preserve">3.39008831977844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84381246566772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83525156974792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87805581092834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76676511764526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88661646842957</t>
   </si>
   <si>
     <t xml:space="preserve">3.85237336158752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92942047119141</t>
+    <t xml:space="preserve">3.92942070960999</t>
   </si>
   <si>
     <t xml:space="preserve">3.95510292053223</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93798112869263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11775922775269</t>
+    <t xml:space="preserve">3.93798136711121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11775875091553</t>
   </si>
   <si>
     <t xml:space="preserve">4.25473260879517</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22905015945435</t>
+    <t xml:space="preserve">4.22904968261719</t>
   </si>
   <si>
     <t xml:space="preserve">4.26329326629639</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28041410446167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43451023101807</t>
+    <t xml:space="preserve">4.28041505813599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43450975418091</t>
   </si>
   <si>
     <t xml:space="preserve">4.20336675643921</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00646829605103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10919857025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15200233459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08351564407349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94654273986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07495450973511</t>
+    <t xml:space="preserve">4.00646781921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10919809341431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15200185775757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08351612091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94654250144958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07495546340942</t>
   </si>
   <si>
     <t xml:space="preserve">4.02359008789062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96366429328918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13488054275513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12631988525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01664590835571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70845603942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91391563415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96528100967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94815921783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20498371124268</t>
+    <t xml:space="preserve">3.96366405487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13488101959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12631940841675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01664638519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70845651626587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91391611099243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96528148651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94816017150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20498418807983</t>
   </si>
   <si>
     <t xml:space="preserve">5.56453943252563</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68439054489136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95833778381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90697240829468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88985109329224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57471656799316</t>
+    <t xml:space="preserve">5.6843900680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95833683013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90697193145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88985061645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57471704483032</t>
   </si>
   <si>
     <t xml:space="preserve">6.12955379486084</t>
@@ -1685,40 +1685,40 @@
     <t xml:space="preserve">7.32806968688965</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05412292480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00275897979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4239764213562</t>
+    <t xml:space="preserve">7.054123878479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00275850296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42397689819336</t>
   </si>
   <si>
     <t xml:space="preserve">7.28357124328613</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87990283966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9676570892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59909152984619</t>
+    <t xml:space="preserve">6.8799033164978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96765661239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59909057617188</t>
   </si>
   <si>
     <t xml:space="preserve">6.51133680343628</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73949670791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.844801902771</t>
+    <t xml:space="preserve">6.73949718475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84480237960815</t>
   </si>
   <si>
     <t xml:space="preserve">6.82725095748901</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68684530258179</t>
+    <t xml:space="preserve">6.68684482574463</t>
   </si>
   <si>
     <t xml:space="preserve">6.66929388046265</t>
@@ -1727,7 +1727,7 @@
     <t xml:space="preserve">6.45868444442749</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40603256225586</t>
+    <t xml:space="preserve">6.4060320854187</t>
   </si>
   <si>
     <t xml:space="preserve">6.31827878952026</t>
@@ -1736,19 +1736,19 @@
     <t xml:space="preserve">6.80970048904419</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17826700210571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35377407073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26601982116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05541038513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07296228408813</t>
+    <t xml:space="preserve">7.17826652526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3537745475769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26602029800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05541086196899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07296180725098</t>
   </si>
   <si>
     <t xml:space="preserve">6.63419246673584</t>
@@ -1760,22 +1760,22 @@
     <t xml:space="preserve">6.30072736740112</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05501699447632</t>
+    <t xml:space="preserve">6.05501651763916</t>
   </si>
   <si>
     <t xml:space="preserve">6.03746604919434</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37053680419922</t>
+    <t xml:space="preserve">5.37053632736206</t>
   </si>
   <si>
     <t xml:space="preserve">5.40563821792603</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52849388122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65134859085083</t>
+    <t xml:space="preserve">5.52849340438843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65134906768799</t>
   </si>
   <si>
     <t xml:space="preserve">6.12521982192993</t>
@@ -1784,16 +1784,16 @@
     <t xml:space="preserve">5.96726322174072</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01991510391235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91461038589478</t>
+    <t xml:space="preserve">6.01991558074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91461086273193</t>
   </si>
   <si>
     <t xml:space="preserve">5.844407081604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94971227645874</t>
+    <t xml:space="preserve">5.94971179962158</t>
   </si>
   <si>
     <t xml:space="preserve">5.86195802688599</t>
@@ -1805,13 +1805,13 @@
     <t xml:space="preserve">5.93216133117676</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87950897216797</t>
+    <t xml:space="preserve">5.87950849533081</t>
   </si>
   <si>
     <t xml:space="preserve">5.79175519943237</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68645095825195</t>
+    <t xml:space="preserve">5.68645048141479</t>
   </si>
   <si>
     <t xml:space="preserve">5.45829010009766</t>
@@ -1829,7 +1829,7 @@
     <t xml:space="preserve">5.66890001296997</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56359529495239</t>
+    <t xml:space="preserve">5.56359577178955</t>
   </si>
   <si>
     <t xml:space="preserve">5.61624765396118</t>
@@ -1838,55 +1838,55 @@
     <t xml:space="preserve">5.49339246749878</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31788444519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1774787902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2652325630188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28278303146362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35298585891724</t>
+    <t xml:space="preserve">5.31788396835327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17747831344604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26523208618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28278255462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35298538208008</t>
   </si>
   <si>
     <t xml:space="preserve">5.42318868637085</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47584104537964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38808727264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51094341278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77420473098755</t>
+    <t xml:space="preserve">5.47584056854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3880877494812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5109429359436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77420425415039</t>
   </si>
   <si>
     <t xml:space="preserve">5.44073963165283</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54604434967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23052501678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35337924957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16032075881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37093162536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47623586654663</t>
+    <t xml:space="preserve">5.54604482650757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23052453994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35337972640991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16032123565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37093114852905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47623538970947</t>
   </si>
   <si>
     <t xml:space="preserve">6.42358303070068</t>
@@ -1904,52 +1904,52 @@
     <t xml:space="preserve">7.0905122756958</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16071510314941</t>
+    <t xml:space="preserve">7.16071557998657</t>
   </si>
   <si>
     <t xml:space="preserve">7.19581699371338</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95010662078857</t>
+    <t xml:space="preserve">6.95010614395142</t>
   </si>
   <si>
     <t xml:space="preserve">7.14316463470459</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12561416625977</t>
+    <t xml:space="preserve">7.12561368942261</t>
   </si>
   <si>
     <t xml:space="preserve">7.02030944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84519577026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3366174697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31906604766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42437076568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08252620697021</t>
+    <t xml:space="preserve">7.8451943397522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33661651611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31906700134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42437171936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0825252532959</t>
   </si>
   <si>
     <t xml:space="preserve">8.68763256072998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03864860534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30190944671631</t>
+    <t xml:space="preserve">9.03864765167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30191040039062</t>
   </si>
   <si>
     <t xml:space="preserve">11.2763719558716</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1630811691284</t>
+    <t xml:space="preserve">13.1630802154541</t>
   </si>
   <si>
     <t xml:space="preserve">13.0753259658813</t>
@@ -1958,13 +1958,13 @@
     <t xml:space="preserve">13.1192035675049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8559408187866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0222787857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1100339889526</t>
+    <t xml:space="preserve">12.8559417724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0222806930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1100330352783</t>
   </si>
   <si>
     <t xml:space="preserve">11.9345264434814</t>
@@ -1976,19 +1976,19 @@
     <t xml:space="preserve">10.8814792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1539106369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6712636947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7151412963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4518795013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0569877624512</t>
+    <t xml:space="preserve">12.1539115905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6712656021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.715142250061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4518804550171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0569868087769</t>
   </si>
   <si>
     <t xml:space="preserve">11.4957571029663</t>
@@ -1997,55 +1997,55 @@
     <t xml:space="preserve">11.4080028533936</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8906497955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8028945922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3202486038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.627387046814</t>
+    <t xml:space="preserve">11.8906488418579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8028955459595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3202495574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6273860931396</t>
   </si>
   <si>
     <t xml:space="preserve">11.1447401046753</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6182174682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5304651260376</t>
+    <t xml:space="preserve">10.6182193756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5304641723633</t>
   </si>
   <si>
     <t xml:space="preserve">10.5743408203125</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7498483657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6620941162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3549575805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78455638885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91618728637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0916948318481</t>
+    <t xml:space="preserve">10.749849319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6620950698853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3549566268921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78455543518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91618824005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0916938781738</t>
   </si>
   <si>
     <t xml:space="preserve">11.2324953079224</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1886177062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1008634567261</t>
+    <t xml:space="preserve">11.1886167526245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1008644104004</t>
   </si>
   <si>
     <t xml:space="preserve">11.3553495407104</t>
@@ -2054,25 +2054,25 @@
     <t xml:space="preserve">11.267596244812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0218868255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2500457763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3729019165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2851476669312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1973943710327</t>
+    <t xml:space="preserve">11.0218858718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2500448226929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3729009628296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2851467132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1973934173584</t>
   </si>
   <si>
     <t xml:space="preserve">11.8467721939087</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9871768951416</t>
+    <t xml:space="preserve">11.9871778488159</t>
   </si>
   <si>
     <t xml:space="preserve">12.2855415344238</t>
@@ -2081,19 +2081,19 @@
     <t xml:space="preserve">12.2504396438599</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1626853942871</t>
+    <t xml:space="preserve">12.1626863479614</t>
   </si>
   <si>
     <t xml:space="preserve">12.4672002792358</t>
   </si>
   <si>
-    <t xml:space="preserve">12.037296295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0910348892212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5536556243896</t>
+    <t xml:space="preserve">12.0372972488403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0910358428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.553656578064</t>
   </si>
   <si>
     <t xml:space="preserve">11.6432199478149</t>
@@ -2102,16 +2102,16 @@
     <t xml:space="preserve">11.3924427032471</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9446258544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5505475997925</t>
+    <t xml:space="preserve">10.9446268081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5505466461182</t>
   </si>
   <si>
     <t xml:space="preserve">10.6759376525879</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9088020324707</t>
+    <t xml:space="preserve">10.9088010787964</t>
   </si>
   <si>
     <t xml:space="preserve">10.7117624282837</t>
@@ -2120,31 +2120,31 @@
     <t xml:space="preserve">10.6580228805542</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9267139434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0521030426025</t>
+    <t xml:space="preserve">10.9267129898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0521020889282</t>
   </si>
   <si>
     <t xml:space="preserve">11.4999179840088</t>
   </si>
   <si>
-    <t xml:space="preserve">11.482006072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4282684326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5715684890747</t>
+    <t xml:space="preserve">11.4820051193237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4282674789429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.571569442749</t>
   </si>
   <si>
     <t xml:space="preserve">11.3745288848877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.356616973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3207921981812</t>
+    <t xml:space="preserve">11.3566179275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3207931518555</t>
   </si>
   <si>
     <t xml:space="preserve">11.4461803436279</t>
@@ -2153,13 +2153,13 @@
     <t xml:space="preserve">11.464093208313</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7148694992065</t>
+    <t xml:space="preserve">11.7148704528809</t>
   </si>
   <si>
     <t xml:space="preserve">11.7327833175659</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7506952285767</t>
+    <t xml:space="preserve">11.750696182251</t>
   </si>
   <si>
     <t xml:space="preserve">12.1805992126465</t>
@@ -2171,10 +2171,10 @@
     <t xml:space="preserve">12.0731229782104</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3418130874634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3597259521484</t>
+    <t xml:space="preserve">12.3418121337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3597249984741</t>
   </si>
   <si>
     <t xml:space="preserve">11.6969575881958</t>
@@ -2186,28 +2186,28 @@
     <t xml:space="preserve">12.0552110671997</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8581705093384</t>
+    <t xml:space="preserve">11.8581714630127</t>
   </si>
   <si>
     <t xml:space="preserve">11.9298210144043</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2880744934082</t>
+    <t xml:space="preserve">12.2880754470825</t>
   </si>
   <si>
     <t xml:space="preserve">12.5925903320312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5030269622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9835605621338</t>
+    <t xml:space="preserve">12.503026008606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9835596084595</t>
   </si>
   <si>
     <t xml:space="preserve">12.3239002227783</t>
   </si>
   <si>
-    <t xml:space="preserve">10.980450630188</t>
+    <t xml:space="preserve">10.9804515838623</t>
   </si>
   <si>
     <t xml:space="preserve">11.1774892807007</t>
@@ -2216,34 +2216,34 @@
     <t xml:space="preserve">11.284966468811</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3387050628662</t>
+    <t xml:space="preserve">11.3387041091919</t>
   </si>
   <si>
     <t xml:space="preserve">11.8939962387085</t>
   </si>
   <si>
-    <t xml:space="preserve">11.768609046936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6253070831299</t>
+    <t xml:space="preserve">11.7686080932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6253061294556</t>
   </si>
   <si>
     <t xml:space="preserve">12.0014715194702</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1089487075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9656476974487</t>
+    <t xml:space="preserve">12.1089477539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9656467437744</t>
   </si>
   <si>
     <t xml:space="preserve">12.1985120773315</t>
   </si>
   <si>
-    <t xml:space="preserve">12.43137550354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2522497177124</t>
+    <t xml:space="preserve">12.4313764572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2522487640381</t>
   </si>
   <si>
     <t xml:space="preserve">12.8612785339355</t>
@@ -2255,13 +2255,13 @@
     <t xml:space="preserve">12.6821527481079</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7358913421631</t>
+    <t xml:space="preserve">12.7358903884888</t>
   </si>
   <si>
     <t xml:space="preserve">13.3449201583862</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2405519485474</t>
+    <t xml:space="preserve">14.2405529022217</t>
   </si>
   <si>
     <t xml:space="preserve">14.0972518920898</t>
@@ -2273,25 +2273,25 @@
     <t xml:space="preserve">14.4734172821045</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5988054275513</t>
+    <t xml:space="preserve">14.5988063812256</t>
   </si>
   <si>
     <t xml:space="preserve">13.8823003768921</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8643865585327</t>
+    <t xml:space="preserve">13.864387512207</t>
   </si>
   <si>
     <t xml:space="preserve">13.577784538269</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4703102111816</t>
+    <t xml:space="preserve">13.4703092575073</t>
   </si>
   <si>
     <t xml:space="preserve">13.6852607727051</t>
   </si>
   <si>
-    <t xml:space="preserve">13.66734790802</t>
+    <t xml:space="preserve">13.6673488616943</t>
   </si>
   <si>
     <t xml:space="preserve">13.5598735809326</t>
@@ -2300,7 +2300,7 @@
     <t xml:space="preserve">13.6136102676392</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8285627365112</t>
+    <t xml:space="preserve">13.8285617828369</t>
   </si>
   <si>
     <t xml:space="preserve">13.9539499282837</t>
@@ -2312,19 +2312,19 @@
     <t xml:space="preserve">13.7210855484009</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5240468978882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7031736373901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2553586959839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4523983001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3090944290161</t>
+    <t xml:space="preserve">13.5240478515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7031726837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2553577423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4523973464966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3090953826904</t>
   </si>
   <si>
     <t xml:space="preserve">14.2763786315918</t>
@@ -2336,22 +2336,22 @@
     <t xml:space="preserve">14.0256013870239</t>
   </si>
   <si>
-    <t xml:space="preserve">13.756911277771</t>
+    <t xml:space="preserve">13.7569122314453</t>
   </si>
   <si>
     <t xml:space="preserve">14.4375925064087</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7124977111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.336332321167</t>
+    <t xml:space="preserve">16.712495803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3363342285156</t>
   </si>
   <si>
     <t xml:space="preserve">17.7156066894531</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2498760223389</t>
+    <t xml:space="preserve">17.2498779296875</t>
   </si>
   <si>
     <t xml:space="preserve">19.6591281890869</t>
@@ -2366,22 +2366,22 @@
     <t xml:space="preserve">21.5399551391602</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2116813659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.987771987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2712669372559</t>
+    <t xml:space="preserve">22.2116794586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9877700805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2712650299072</t>
   </si>
   <si>
     <t xml:space="preserve">23.017749786377</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3460254669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1221179962158</t>
+    <t xml:space="preserve">22.3460273742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1221160888672</t>
   </si>
   <si>
     <t xml:space="preserve">23.7342529296875</t>
@@ -2390,109 +2390,109 @@
     <t xml:space="preserve">21.8982086181641</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4355869293213</t>
+    <t xml:space="preserve">22.4355888366699</t>
   </si>
   <si>
     <t xml:space="preserve">21.495174407959</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7190818786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9429893493652</t>
+    <t xml:space="preserve">21.7190837860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9429912567139</t>
   </si>
   <si>
     <t xml:space="preserve">21.7638645172119</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8534278869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3312187194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8086452484131</t>
+    <t xml:space="preserve">21.8534259796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3312206268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8086471557617</t>
   </si>
   <si>
     <t xml:space="preserve">25.3463935852051</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3016128540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2420234680176</t>
+    <t xml:space="preserve">25.3016109466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2420253753662</t>
   </si>
   <si>
     <t xml:space="preserve">25.525520324707</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2120494842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8837718963623</t>
+    <t xml:space="preserve">25.2120475769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8837699890137</t>
   </si>
   <si>
     <t xml:space="preserve">25.4807395935059</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5703010559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.122486114502</t>
+    <t xml:space="preserve">25.5702991485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1224842071533</t>
   </si>
   <si>
     <t xml:space="preserve">24.361198425293</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3911743164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7046489715576</t>
+    <t xml:space="preserve">25.3911762237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.704647064209</t>
   </si>
   <si>
     <t xml:space="preserve">26.4211521148682</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0628986358643</t>
+    <t xml:space="preserve">26.0629005432129</t>
   </si>
   <si>
     <t xml:space="preserve">26.4659309387207</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1524639129639</t>
+    <t xml:space="preserve">26.1524620056152</t>
   </si>
   <si>
     <t xml:space="preserve">28.6602325439453</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6750354766846</t>
+    <t xml:space="preserve">27.6750373840332</t>
   </si>
   <si>
     <t xml:space="preserve">26.7794055938721</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5554962158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9881401062012</t>
+    <t xml:space="preserve">26.5554943084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9881381988525</t>
   </si>
   <si>
     <t xml:space="preserve">25.2568302154541</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9581623077393</t>
+    <t xml:space="preserve">23.9581661224365</t>
   </si>
   <si>
     <t xml:space="preserve">24.0477275848389</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9133815765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5851058959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0773334503174</t>
+    <t xml:space="preserve">23.9133834838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5851078033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.077335357666</t>
   </si>
   <si>
     <t xml:space="preserve">22.928186416626</t>
@@ -2501,7 +2501,7 @@
     <t xml:space="preserve">23.1968765258789</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1820697784424</t>
+    <t xml:space="preserve">24.182071685791</t>
   </si>
   <si>
     <t xml:space="preserve">24.2268524169922</t>
@@ -2513,10 +2513,10 @@
     <t xml:space="preserve">24.3164138793945</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3908061981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8238182067871</t>
+    <t xml:space="preserve">22.3908081054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8238201141357</t>
   </si>
   <si>
     <t xml:space="preserve">23.0625305175781</t>
@@ -2528,7 +2528,7 @@
     <t xml:space="preserve">22.8834037780762</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2416572570801</t>
+    <t xml:space="preserve">23.2416591644287</t>
   </si>
   <si>
     <t xml:space="preserve">25.1672668457031</t>
@@ -2552,7 +2552,7 @@
     <t xml:space="preserve">25.9733352661133</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5107173919678</t>
+    <t xml:space="preserve">26.5107154846191</t>
   </si>
   <si>
     <t xml:space="preserve">26.197244644165</t>
@@ -2564,10 +2564,10 @@
     <t xml:space="preserve">26.6450595855713</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4959106445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0480937957764</t>
+    <t xml:space="preserve">27.4959125518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.048095703125</t>
   </si>
   <si>
     <t xml:space="preserve">27.9437294006348</t>
@@ -2576,31 +2576,31 @@
     <t xml:space="preserve">28.8841400146484</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9289207458496</t>
+    <t xml:space="preserve">28.9289226531982</t>
   </si>
   <si>
     <t xml:space="preserve">28.7050113677979</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7797718048096</t>
+    <t xml:space="preserve">29.7797737121582</t>
   </si>
   <si>
     <t xml:space="preserve">27.9885082244873</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6302547454834</t>
+    <t xml:space="preserve">27.630256652832</t>
   </si>
   <si>
     <t xml:space="preserve">27.2272205352783</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4063472747803</t>
+    <t xml:space="preserve">27.4063453674316</t>
   </si>
   <si>
     <t xml:space="preserve">26.6898403167725</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8389911651611</t>
+    <t xml:space="preserve">25.8389892578125</t>
   </si>
   <si>
     <t xml:space="preserve">25.79421043396</t>
@@ -2609,13 +2609,13 @@
     <t xml:space="preserve">26.3315887451172</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7194519042969</t>
+    <t xml:space="preserve">24.7194499969482</t>
   </si>
   <si>
     <t xml:space="preserve">24.4507598876953</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5999088287354</t>
+    <t xml:space="preserve">23.599910736084</t>
   </si>
   <si>
     <t xml:space="preserve">23.4655666351318</t>
@@ -2642,13 +2642,13 @@
     <t xml:space="preserve">26.891170501709</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3454132080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.662052154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4803524017334</t>
+    <t xml:space="preserve">27.3454113006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6620502471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.480354309082</t>
   </si>
   <si>
     <t xml:space="preserve">29.3440799713135</t>
@@ -2660,13 +2660,13 @@
     <t xml:space="preserve">30.5705375671387</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0247802734375</t>
+    <t xml:space="preserve">31.0247764587402</t>
   </si>
   <si>
     <t xml:space="preserve">31.0702037811279</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8885059356689</t>
+    <t xml:space="preserve">30.8885078430176</t>
   </si>
   <si>
     <t xml:space="preserve">28.9352626800537</t>
@@ -2675,7 +2675,7 @@
     <t xml:space="preserve">27.8905048370361</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9359283447266</t>
+    <t xml:space="preserve">27.9359264373779</t>
   </si>
   <si>
     <t xml:space="preserve">27.4362621307373</t>
@@ -2687,7 +2687,7 @@
     <t xml:space="preserve">28.4355945587158</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5264434814453</t>
+    <t xml:space="preserve">28.5264415740967</t>
   </si>
   <si>
     <t xml:space="preserve">28.4810199737549</t>
@@ -2720,13 +2720,13 @@
     <t xml:space="preserve">31.479024887085</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5698680877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.796989440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7515659332275</t>
+    <t xml:space="preserve">31.5698699951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7969913482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7515678405762</t>
   </si>
   <si>
     <t xml:space="preserve">31.1156272888184</t>
@@ -2738,10 +2738,10 @@
     <t xml:space="preserve">34.6587219238281</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8410835266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4770240783691</t>
+    <t xml:space="preserve">33.8410873413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4770278930664</t>
   </si>
   <si>
     <t xml:space="preserve">34.386173248291</t>
@@ -2753,13 +2753,13 @@
     <t xml:space="preserve">34.6132965087891</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3400840759277</t>
+    <t xml:space="preserve">35.340087890625</t>
   </si>
   <si>
     <t xml:space="preserve">34.4316024780273</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7048110961914</t>
+    <t xml:space="preserve">33.7048072814941</t>
   </si>
   <si>
     <t xml:space="preserve">33.9773559570312</t>
@@ -2771,58 +2771,58 @@
     <t xml:space="preserve">34.5224456787109</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0682029724121</t>
+    <t xml:space="preserve">34.0682067871094</t>
   </si>
   <si>
     <t xml:space="preserve">33.7502365112305</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9319305419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2499046325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6139640808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2485733032227</t>
+    <t xml:space="preserve">33.9319267272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2499008178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6139602661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2485694885254</t>
   </si>
   <si>
     <t xml:space="preserve">36.6573867797852</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7936630249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6106338500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5645446777344</t>
+    <t xml:space="preserve">36.7936592102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6106300354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5645408630371</t>
   </si>
   <si>
     <t xml:space="preserve">38.1109657287598</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4302635192871</t>
+    <t xml:space="preserve">36.4302673339844</t>
   </si>
   <si>
     <t xml:space="preserve">33.3868370056152</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8871726989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0688743591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3414192199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8865051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2044830322266</t>
+    <t xml:space="preserve">32.8871765136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0688705444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3414154052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8865089416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2044792175293</t>
   </si>
   <si>
     <t xml:space="preserve">34.340747833252</t>
@@ -2837,10 +2837,10 @@
     <t xml:space="preserve">32.9780197143555</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7976551055908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3895034790039</t>
+    <t xml:space="preserve">30.7976589202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3895015716553</t>
   </si>
   <si>
     <t xml:space="preserve">29.5257778167725</t>
@@ -2849,13 +2849,13 @@
     <t xml:space="preserve">28.6172924041748</t>
   </si>
   <si>
-    <t xml:space="preserve">28.344747543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0254440307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9332675933838</t>
+    <t xml:space="preserve">28.3447494506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0254421234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9332637786865</t>
   </si>
   <si>
     <t xml:space="preserve">32.2058067321777</t>
@@ -2867,7 +2867,7 @@
     <t xml:space="preserve">32.2512359619141</t>
   </si>
   <si>
-    <t xml:space="preserve">31.615291595459</t>
+    <t xml:space="preserve">31.6152896881104</t>
   </si>
   <si>
     <t xml:space="preserve">32.0241088867188</t>
@@ -2885,31 +2885,31 @@
     <t xml:space="preserve">32.0695381164551</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5244445800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3427486419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3420829772949</t>
+    <t xml:space="preserve">31.5244483947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3427467346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3420791625977</t>
   </si>
   <si>
     <t xml:space="preserve">32.5237770080566</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7054748535156</t>
+    <t xml:space="preserve">32.7054786682129</t>
   </si>
   <si>
     <t xml:space="preserve">32.1603889465332</t>
   </si>
   <si>
-    <t xml:space="preserve">34.159049987793</t>
+    <t xml:space="preserve">34.1590538024902</t>
   </si>
   <si>
     <t xml:space="preserve">33.7956581115723</t>
   </si>
   <si>
-    <t xml:space="preserve">34.976692199707</t>
+    <t xml:space="preserve">34.9766883850098</t>
   </si>
   <si>
     <t xml:space="preserve">32.9325981140137</t>
@@ -2924,7 +2924,7 @@
     <t xml:space="preserve">32.4783554077148</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4329299926758</t>
+    <t xml:space="preserve">32.432933807373</t>
   </si>
   <si>
     <t xml:space="preserve">31.8424167633057</t>
@@ -2939,13 +2939,13 @@
     <t xml:space="preserve">29.7074737548828</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7068099975586</t>
+    <t xml:space="preserve">30.70680809021</t>
   </si>
   <si>
     <t xml:space="preserve">30.4796886444092</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6166248321533</t>
+    <t xml:space="preserve">29.616626739502</t>
   </si>
   <si>
     <t xml:space="preserve">29.8437442779541</t>
@@ -2954,13 +2954,13 @@
     <t xml:space="preserve">29.2532329559326</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7535667419434</t>
+    <t xml:space="preserve">28.7535648345947</t>
   </si>
   <si>
     <t xml:space="preserve">30.0708694458008</t>
   </si>
   <si>
-    <t xml:space="preserve">28.889835357666</t>
+    <t xml:space="preserve">28.8898372650146</t>
   </si>
   <si>
     <t xml:space="preserve">28.6627159118652</t>
@@ -2984,16 +2984,16 @@
     <t xml:space="preserve">29.0715351104736</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2993202209473</t>
+    <t xml:space="preserve">28.2993221282959</t>
   </si>
   <si>
     <t xml:space="preserve">28.0267772674561</t>
   </si>
   <si>
-    <t xml:space="preserve">27.617956161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7542304992676</t>
+    <t xml:space="preserve">27.6179580688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7542324066162</t>
   </si>
   <si>
     <t xml:space="preserve">28.1176242828369</t>
@@ -3002,7 +3002,7 @@
     <t xml:space="preserve">28.5718688964844</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4816837310791</t>
+    <t xml:space="preserve">27.4816856384277</t>
   </si>
   <si>
     <t xml:space="preserve">27.5725345611572</t>
@@ -3014,7 +3014,7 @@
     <t xml:space="preserve">27.1182918548584</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0274410247803</t>
+    <t xml:space="preserve">27.0274429321289</t>
   </si>
   <si>
     <t xml:space="preserve">26.9365921020508</t>
@@ -3038,10 +3038,10 @@
     <t xml:space="preserve">26.8457431793213</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6640510559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4369258880615</t>
+    <t xml:space="preserve">26.6640491485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4369277954102</t>
   </si>
   <si>
     <t xml:space="preserve">26.5732002258301</t>
@@ -3053,7 +3053,7 @@
     <t xml:space="preserve">26.70947265625</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5277767181396</t>
+    <t xml:space="preserve">26.527774810791</t>
   </si>
   <si>
     <t xml:space="preserve">25.9826850891113</t>
@@ -3062,10 +3062,10 @@
     <t xml:space="preserve">25.8009872436523</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1657123565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6660442352295</t>
+    <t xml:space="preserve">24.165714263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6660461425781</t>
   </si>
   <si>
     <t xml:space="preserve">23.8477439880371</t>
@@ -3074,13 +3074,13 @@
     <t xml:space="preserve">25.437593460083</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7555618286133</t>
+    <t xml:space="preserve">25.7555637359619</t>
   </si>
   <si>
     <t xml:space="preserve">25.074197769165</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0735359191895</t>
+    <t xml:space="preserve">26.0735340118408</t>
   </si>
   <si>
     <t xml:space="preserve">27.6892356872559</t>
@@ -3089,7 +3089,7 @@
     <t xml:space="preserve">26.3419418334961</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6671524047852</t>
+    <t xml:space="preserve">26.6671504974365</t>
   </si>
   <si>
     <t xml:space="preserve">27.1317348480225</t>
@@ -3098,7 +3098,7 @@
     <t xml:space="preserve">27.6427764892578</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3396530151367</t>
+    <t xml:space="preserve">28.3396549224854</t>
   </si>
   <si>
     <t xml:space="preserve">27.8286113739014</t>
@@ -3152,7 +3152,7 @@
     <t xml:space="preserve">27.038818359375</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9459018707275</t>
+    <t xml:space="preserve">26.9458999633789</t>
   </si>
   <si>
     <t xml:space="preserve">26.760066986084</t>
@@ -3164,19 +3164,19 @@
     <t xml:space="preserve">26.2025661468506</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5742321014404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.481315612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8994426727295</t>
+    <t xml:space="preserve">26.5742340087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4813175201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8994445800781</t>
   </si>
   <si>
     <t xml:space="preserve">26.2490253448486</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7379837036133</t>
+    <t xml:space="preserve">25.7379817962646</t>
   </si>
   <si>
     <t xml:space="preserve">25.9238147735596</t>
@@ -3191,7 +3191,7 @@
     <t xml:space="preserve">27.271110534668</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2246513366699</t>
+    <t xml:space="preserve">27.2246494293213</t>
   </si>
   <si>
     <t xml:space="preserve">25.4127731323242</t>
@@ -3203,7 +3203,7 @@
     <t xml:space="preserve">24.5300617218018</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9017295837402</t>
+    <t xml:space="preserve">24.9017276763916</t>
   </si>
   <si>
     <t xml:space="preserve">25.0875625610352</t>
@@ -3212,76 +3212,76 @@
     <t xml:space="preserve">24.8088130950928</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5521469116211</t>
+    <t xml:space="preserve">25.5521488189697</t>
   </si>
   <si>
     <t xml:space="preserve">25.5056896209717</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7623538970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7158946990967</t>
+    <t xml:space="preserve">24.7623519897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7158966064453</t>
   </si>
   <si>
     <t xml:space="preserve">25.8308982849121</t>
   </si>
   <si>
-    <t xml:space="preserve">27.085277557373</t>
+    <t xml:space="preserve">27.0852756500244</t>
   </si>
   <si>
     <t xml:space="preserve">26.7136077880859</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0167331695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8773574829102</t>
+    <t xml:space="preserve">26.016731262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8773555755615</t>
   </si>
   <si>
     <t xml:space="preserve">25.7844390869141</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0631885528564</t>
+    <t xml:space="preserve">26.0631904602051</t>
   </si>
   <si>
     <t xml:space="preserve">26.1096496582031</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1340198516846</t>
+    <t xml:space="preserve">25.1340217590332</t>
   </si>
   <si>
     <t xml:space="preserve">25.0411052703857</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2977676391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4836044311523</t>
+    <t xml:space="preserve">24.2977695465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4836025238037</t>
   </si>
   <si>
     <t xml:space="preserve">24.0654773712158</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2513122558594</t>
+    <t xml:space="preserve">24.2513103485107</t>
   </si>
   <si>
     <t xml:space="preserve">24.5765209197998</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6008911132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0433921813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0898494720459</t>
+    <t xml:space="preserve">23.6008930206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0433902740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0898513793945</t>
   </si>
   <si>
     <t xml:space="preserve">22.114221572876</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0213050842285</t>
+    <t xml:space="preserve">22.0213069915771</t>
   </si>
   <si>
     <t xml:space="preserve">23.2756824493408</t>
@@ -3290,28 +3290,28 @@
     <t xml:space="preserve">23.4615173339844</t>
   </si>
   <si>
-    <t xml:space="preserve">23.415060043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1363086700439</t>
+    <t xml:space="preserve">23.4150581359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1363067626953</t>
   </si>
   <si>
     <t xml:space="preserve">23.6473522186279</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9504737854004</t>
+    <t xml:space="preserve">22.950475692749</t>
   </si>
   <si>
     <t xml:space="preserve">22.5788059234619</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2071399688721</t>
+    <t xml:space="preserve">22.2071380615234</t>
   </si>
   <si>
     <t xml:space="preserve">21.64963722229</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8598461151123</t>
+    <t xml:space="preserve">20.8598442077637</t>
   </si>
   <si>
     <t xml:space="preserve">21.0921363830566</t>
@@ -3326,7 +3326,7 @@
     <t xml:space="preserve">21.5567207336426</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7425537109375</t>
+    <t xml:space="preserve">21.7425556182861</t>
   </si>
   <si>
     <t xml:space="preserve">21.9283885955811</t>
@@ -3347,37 +3347,37 @@
     <t xml:space="preserve">21.4173450469971</t>
   </si>
   <si>
-    <t xml:space="preserve">21.603178024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.835470199585</t>
+    <t xml:space="preserve">21.6031799316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8354721069336</t>
   </si>
   <si>
     <t xml:space="preserve">22.160680770874</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7181835174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3000564575195</t>
+    <t xml:space="preserve">22.7181816101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3000545501709</t>
   </si>
   <si>
     <t xml:space="preserve">22.3465137481689</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2535972595215</t>
+    <t xml:space="preserve">22.2535991668701</t>
   </si>
   <si>
     <t xml:space="preserve">21.881929397583</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7890148162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1827659606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5986061096191</t>
+    <t xml:space="preserve">21.7890129089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.182767868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5986042022705</t>
   </si>
   <si>
     <t xml:space="preserve">25.3663120269775</t>
@@ -3398,10 +3398,10 @@
     <t xml:space="preserve">24.4371433258057</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8796424865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2048511505127</t>
+    <t xml:space="preserve">23.8796443939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2048530578613</t>
   </si>
   <si>
     <t xml:space="preserve">23.9261016845703</t>
@@ -3410,7 +3410,7 @@
     <t xml:space="preserve">24.6694355010986</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5544357299805</t>
+    <t xml:space="preserve">23.5544338226318</t>
   </si>
   <si>
     <t xml:space="preserve">23.6938095092773</t>
@@ -3419,7 +3419,7 @@
     <t xml:space="preserve">23.3221416473389</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7867259979248</t>
+    <t xml:space="preserve">23.7867279052734</t>
   </si>
   <si>
     <t xml:space="preserve">22.8575572967529</t>
@@ -3428,7 +3428,7 @@
     <t xml:space="preserve">21.5102615356445</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3708877563477</t>
+    <t xml:space="preserve">21.370885848999</t>
   </si>
   <si>
     <t xml:space="preserve">21.1850528717041</t>
@@ -3437,19 +3437,19 @@
     <t xml:space="preserve">20.7204685211182</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4881744384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9771327972412</t>
+    <t xml:space="preserve">20.4881763458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9771347045898</t>
   </si>
   <si>
     <t xml:space="preserve">20.2558822631836</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5346355438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9306774139404</t>
+    <t xml:space="preserve">20.5346336364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9306755065918</t>
   </si>
   <si>
     <t xml:space="preserve">20.5810928344727</t>
@@ -3461,7 +3461,7 @@
     <t xml:space="preserve">20.6275520324707</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0235919952393</t>
+    <t xml:space="preserve">20.0235900878906</t>
   </si>
   <si>
     <t xml:space="preserve">18.6298370361328</t>
@@ -3479,7 +3479,7 @@
     <t xml:space="preserve">17.8772106170654</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5427112579346</t>
+    <t xml:space="preserve">17.5427093505859</t>
   </si>
   <si>
     <t xml:space="preserve">17.2453765869141</t>
@@ -3491,10 +3491,10 @@
     <t xml:space="preserve">17.5612926483154</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4126262664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7471294403076</t>
+    <t xml:space="preserve">17.4126281738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.747127532959</t>
   </si>
   <si>
     <t xml:space="preserve">17.1896266937256</t>
@@ -3515,13 +3515,13 @@
     <t xml:space="preserve">16.3162078857422</t>
   </si>
   <si>
-    <t xml:space="preserve">15.981707572937</t>
+    <t xml:space="preserve">15.9817085266113</t>
   </si>
   <si>
     <t xml:space="preserve">16.5392074584961</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2976264953613</t>
+    <t xml:space="preserve">16.2976245880127</t>
   </si>
   <si>
     <t xml:space="preserve">16.1861248016357</t>
@@ -3533,7 +3533,7 @@
     <t xml:space="preserve">16.1489562988281</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2418727874756</t>
+    <t xml:space="preserve">16.2418746948242</t>
   </si>
   <si>
     <t xml:space="preserve">16.0746231079102</t>
@@ -4275,6 +4275,9 @@
   </si>
   <si>
     <t xml:space="preserve">19.1000003814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3199996948242</t>
   </si>
 </sst>
 </file>
@@ -69405,7 +69408,7 @@
     </row>
     <row r="2493">
       <c r="A2493" s="1" t="n">
-        <v>45950.6493055556</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2493" t="n">
         <v>17630</v>
@@ -69426,6 +69429,32 @@
         <v>1415</v>
       </c>
       <c r="H2493" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="1" t="n">
+        <v>45951.649525463</v>
+      </c>
+      <c r="B2494" t="n">
+        <v>11215</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>19.7600002288818</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>19.3199996948242</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>19.7199993133545</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>19.3199996948242</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>1421</v>
+      </c>
+      <c r="H2494" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ARN.MI.xlsx
+++ b/data/ARN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1422" uniqueCount="1422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1423" uniqueCount="1423">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,46 +38,46 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92214977741241</t>
+    <t xml:space="preserve">1.92215025424957</t>
   </si>
   <si>
     <t xml:space="preserve">ARN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94450092315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.917360663414</t>
+    <t xml:space="preserve">1.94450068473816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91736018657684</t>
   </si>
   <si>
     <t xml:space="preserve">1.90778195858002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88383460044861</t>
+    <t xml:space="preserve">1.8838347196579</t>
   </si>
   <si>
     <t xml:space="preserve">1.93172907829285</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91576433181763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83434450626373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8359409570694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91097474098206</t>
+    <t xml:space="preserve">1.91576409339905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83434462547302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83594059944153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91097486019135</t>
   </si>
   <si>
     <t xml:space="preserve">1.80720412731171</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74973130226135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71620559692383</t>
+    <t xml:space="preserve">1.74973154067993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71620571613312</t>
   </si>
   <si>
     <t xml:space="preserve">1.80401134490967</t>
@@ -86,151 +86,151 @@
     <t xml:space="preserve">1.81039690971375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79602909088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77208197116852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70662665367126</t>
+    <t xml:space="preserve">1.79602921009064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77208185195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70662653446198</t>
   </si>
   <si>
     <t xml:space="preserve">1.69704759120941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69066190719604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67629373073578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70024108886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69864439964294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67469751834869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6667149066925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66032910346985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81518661975861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82795834541321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86148405075073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88543117046356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89181697368622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92853593826294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95407927036285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90618538856506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86787021160126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88064169883728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85190558433533</t>
+    <t xml:space="preserve">1.69066226482391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67629361152649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7002409696579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69864428043365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67469727993011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66671478748322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66032886505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8151867389679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82795798778534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86148452758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88543140888214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89181733131409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92853617668152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95407950878143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90618550777435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86786997318268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88064193725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85190534591675</t>
   </si>
   <si>
     <t xml:space="preserve">1.85988783836365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85509836673737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79283595085144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78804671764374</t>
+    <t xml:space="preserve">1.85509824752808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79283618927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78804659843445</t>
   </si>
   <si>
     <t xml:space="preserve">1.78006434440613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7561172246933</t>
+    <t xml:space="preserve">1.75611710548401</t>
   </si>
   <si>
     <t xml:space="preserve">1.76888883113861</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76409983634949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78485381603241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77048552036285</t>
+    <t xml:space="preserve">1.76409959793091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78485369682312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77048540115356</t>
   </si>
   <si>
     <t xml:space="preserve">1.72099483013153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73536324501038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80241477489471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76250278949738</t>
+    <t xml:space="preserve">1.73536336421967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.802414894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76250302791595</t>
   </si>
   <si>
     <t xml:space="preserve">1.74494194984436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73217034339905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73695993423462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74334561824799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7513279914856</t>
+    <t xml:space="preserve">1.73217022418976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73695969581604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74334537982941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75132775306702</t>
   </si>
   <si>
     <t xml:space="preserve">1.68587255477905</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67789006233215</t>
+    <t xml:space="preserve">1.67789018154144</t>
   </si>
   <si>
     <t xml:space="preserve">1.65234673023224</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62041711807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64276778697968</t>
+    <t xml:space="preserve">1.6204172372818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64276802539825</t>
   </si>
   <si>
     <t xml:space="preserve">1.59008431434631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60285604000092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54937446117401</t>
+    <t xml:space="preserve">1.60285615921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54937422275543</t>
   </si>
   <si>
     <t xml:space="preserve">1.51185739040375</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">1.45598089694977</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43682324886322</t>
+    <t xml:space="preserve">1.43682312965393</t>
   </si>
   <si>
     <t xml:space="preserve">1.46955072879791</t>
@@ -251,31 +251,31 @@
     <t xml:space="preserve">1.47673487663269</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47274386882782</t>
+    <t xml:space="preserve">1.47274363040924</t>
   </si>
   <si>
     <t xml:space="preserve">1.46875262260437</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49669098854065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47593665122986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50626969337463</t>
+    <t xml:space="preserve">1.49669086933136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47593653202057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50626957416534</t>
   </si>
   <si>
     <t xml:space="preserve">1.47753310203552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43841958045959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40090274810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3490172624588</t>
+    <t xml:space="preserve">1.43841969966888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40090262889862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34901738166809</t>
   </si>
   <si>
     <t xml:space="preserve">1.30910551548004</t>
@@ -287,34 +287,34 @@
     <t xml:space="preserve">1.32666671276093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34103488922119</t>
+    <t xml:space="preserve">1.34103500843048</t>
   </si>
   <si>
     <t xml:space="preserve">1.31708788871765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38653433322906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39691138267517</t>
+    <t xml:space="preserve">1.38653421401978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39691126346588</t>
   </si>
   <si>
     <t xml:space="preserve">1.40649020671844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30671072006226</t>
+    <t xml:space="preserve">1.30671083927155</t>
   </si>
   <si>
     <t xml:space="preserve">1.3234738111496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30591285228729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31229865550995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2899477481842</t>
+    <t xml:space="preserve">1.305912733078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31229841709137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28994810581207</t>
   </si>
   <si>
     <t xml:space="preserve">1.28515863418579</t>
@@ -326,46 +326,46 @@
     <t xml:space="preserve">1.33305239677429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33704352378845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30112326145172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36104869842529</t>
+    <t xml:space="preserve">1.33704376220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30112314224243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36104881763458</t>
   </si>
   <si>
     <t xml:space="preserve">1.34627258777618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35283970832825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33806371688843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27157092094421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28880965709686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29291450977325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30686962604523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33888447284698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34955644607544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34380984306335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33642172813416</t>
+    <t xml:space="preserve">1.35283982753754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33806359767914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27157080173492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28880989551544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29291439056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30686950683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33888471126556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34955620765686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34380996227264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33642160892487</t>
   </si>
   <si>
     <t xml:space="preserve">1.34709346294403</t>
@@ -386,85 +386,85 @@
     <t xml:space="preserve">1.26828718185425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27239179611206</t>
+    <t xml:space="preserve">1.27239155769348</t>
   </si>
   <si>
     <t xml:space="preserve">1.2879890203476</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2970187664032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24858570098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32657098770142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33231723308563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3594069480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4201534986496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48664605617523</t>
+    <t xml:space="preserve">1.29701864719391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24858582019806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32657134532928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33231747150421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35940706729889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42015337944031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48664629459381</t>
   </si>
   <si>
     <t xml:space="preserve">1.53343737125397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51619863510132</t>
+    <t xml:space="preserve">1.51619827747345</t>
   </si>
   <si>
     <t xml:space="preserve">1.51866114139557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43739235401154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46776568889618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43000411987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40948164463043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44478023052216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5597060918808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61798989772797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70582616329193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74851286411285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72388577461243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68284046649933</t>
+    <t xml:space="preserve">1.43739223480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4677654504776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43000435829163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40948176383972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44478034973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55970597267151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61798977851868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70582580566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74851274490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72388565540314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68284070491791</t>
   </si>
   <si>
     <t xml:space="preserve">1.67463171482086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65164661407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64179575443268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67134821414948</t>
+    <t xml:space="preserve">1.65164685249329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64179587364197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67134809494019</t>
   </si>
   <si>
     <t xml:space="preserve">1.6647812128067</t>
@@ -473,64 +473,64 @@
     <t xml:space="preserve">1.65657198429108</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69597518444061</t>
+    <t xml:space="preserve">1.69597506523132</t>
   </si>
   <si>
     <t xml:space="preserve">1.69433319568634</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65821385383606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6811990737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68776607513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66806471347809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6500049829483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66313922405243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67791545391083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03746843338013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04403614997864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03911066055298</t>
+    <t xml:space="preserve">1.65821373462677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68119895458221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68776631355286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6680645942688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65000486373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66313910484314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67791533470154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03746914863586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04403591156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0391104221344</t>
   </si>
   <si>
     <t xml:space="preserve">2.04075217247009</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0522449016571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04731917381287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04239416122437</t>
+    <t xml:space="preserve">2.05224466323853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04731941223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04239392280579</t>
   </si>
   <si>
     <t xml:space="preserve">2.19836449623108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.241051197052</t>
+    <t xml:space="preserve">2.24105143547058</t>
   </si>
   <si>
     <t xml:space="preserve">2.18851375579834</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17537927627563</t>
+    <t xml:space="preserve">2.17537975311279</t>
   </si>
   <si>
     <t xml:space="preserve">2.145827293396</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">1.98821485042572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99313986301422</t>
+    <t xml:space="preserve">1.99314033985138</t>
   </si>
   <si>
     <t xml:space="preserve">1.99806571006775</t>
@@ -551,7 +551,7 @@
     <t xml:space="preserve">1.99642372131348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99970757961273</t>
+    <t xml:space="preserve">1.99970734119415</t>
   </si>
   <si>
     <t xml:space="preserve">2.00299096107483</t>
@@ -560,7 +560,7 @@
     <t xml:space="preserve">2.00791621208191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01120018959045</t>
+    <t xml:space="preserve">2.01120042800903</t>
   </si>
   <si>
     <t xml:space="preserve">2.02597594261169</t>
@@ -569,145 +569,145 @@
     <t xml:space="preserve">2.03254342079163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02105045318604</t>
+    <t xml:space="preserve">2.02105093002319</t>
   </si>
   <si>
     <t xml:space="preserve">2.01940894126892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02433466911316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07687163352966</t>
+    <t xml:space="preserve">2.024334192276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07687187194824</t>
   </si>
   <si>
     <t xml:space="preserve">2.05881190299988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09657311439514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14746880531311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33955883979797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27552914619446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32478284835815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27881264686584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25746941566467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29851412773132</t>
+    <t xml:space="preserve">2.0965735912323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14746904373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33955931663513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27552938461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32478308677673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.278813123703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25746917724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29851388931274</t>
   </si>
   <si>
     <t xml:space="preserve">2.26075291633606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2804548740387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30672335624695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35597681999207</t>
+    <t xml:space="preserve">2.28045439720154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30672311782837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35597705841064</t>
   </si>
   <si>
     <t xml:space="preserve">2.34120106697083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34284257888794</t>
+    <t xml:space="preserve">2.34284281730652</t>
   </si>
   <si>
     <t xml:space="preserve">2.3477680683136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44627594947815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39209651947021</t>
+    <t xml:space="preserve">2.44627571105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39209699630737</t>
   </si>
   <si>
     <t xml:space="preserve">2.3822455406189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38717079162598</t>
+    <t xml:space="preserve">2.38717103004456</t>
   </si>
   <si>
     <t xml:space="preserve">2.38388776779175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4052312374115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38060402870178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42164897918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33791756629944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32314109802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35433554649353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41015625</t>
+    <t xml:space="preserve">2.40523099899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3806037902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42164921760559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33791732788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32314133644104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35433530807495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41015648841858</t>
   </si>
   <si>
     <t xml:space="preserve">2.40687274932861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4380669593811</t>
+    <t xml:space="preserve">2.43806719779968</t>
   </si>
   <si>
     <t xml:space="preserve">2.41836547851562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29030561447144</t>
+    <t xml:space="preserve">2.29030513763428</t>
   </si>
   <si>
     <t xml:space="preserve">2.34941005706787</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36418628692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37567853927612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40194749832153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35761880874634</t>
+    <t xml:space="preserve">2.36418581008911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3756787776947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40194773674011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3576192855835</t>
   </si>
   <si>
     <t xml:space="preserve">2.36746954917908</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37075328826904</t>
+    <t xml:space="preserve">2.37075304985046</t>
   </si>
   <si>
     <t xml:space="preserve">2.37239503860474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36254453659058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3658275604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3953800201416</t>
+    <t xml:space="preserve">2.362544298172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36582803726196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39538049697876</t>
   </si>
   <si>
     <t xml:space="preserve">2.37732028961182</t>
@@ -719,7 +719,7 @@
     <t xml:space="preserve">2.38881301879883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39373850822449</t>
+    <t xml:space="preserve">2.39373826980591</t>
   </si>
   <si>
     <t xml:space="preserve">2.39045476913452</t>
@@ -728,58 +728,58 @@
     <t xml:space="preserve">2.41343998908997</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40358924865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40030550956726</t>
+    <t xml:space="preserve">2.40358948707581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40030598640442</t>
   </si>
   <si>
     <t xml:space="preserve">2.40851449966431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42329096794128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43149971961975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42000675201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35105180740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33627557754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34612655639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43642473220825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42657399177551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42985773086548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45284295082092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4770131111145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.478679895401</t>
+    <t xml:space="preserve">2.42329072952271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43149948120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42000699043274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35105204582214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33627510070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34612631797791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43642497062683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42657446861267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42985820770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4528431892395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47701287269592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47868013381958</t>
   </si>
   <si>
     <t xml:space="preserve">2.49201512336731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49368214607239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.475346326828</t>
+    <t xml:space="preserve">2.49368238449097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47534656524658</t>
   </si>
   <si>
     <t xml:space="preserve">2.46534490585327</t>
@@ -788,10 +788,10 @@
     <t xml:space="preserve">2.48201370239258</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46867871284485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45867729187012</t>
+    <t xml:space="preserve">2.46867847442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4586775302887</t>
   </si>
   <si>
     <t xml:space="preserve">2.46201109886169</t>
@@ -800,22 +800,22 @@
     <t xml:space="preserve">2.45534348487854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41700482368469</t>
+    <t xml:space="preserve">2.41700458526611</t>
   </si>
   <si>
     <t xml:space="preserve">2.40867018699646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36699748039246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3419942855835</t>
+    <t xml:space="preserve">2.36699771881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34199404716492</t>
   </si>
   <si>
     <t xml:space="preserve">2.36866450309753</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35366225242615</t>
+    <t xml:space="preserve">2.35366249084473</t>
   </si>
   <si>
     <t xml:space="preserve">2.385333776474</t>
@@ -827,13 +827,13 @@
     <t xml:space="preserve">2.36366391181946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32532548904419</t>
+    <t xml:space="preserve">2.32532501220703</t>
   </si>
   <si>
     <t xml:space="preserve">2.31699061393738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28531980514526</t>
+    <t xml:space="preserve">2.28531956672668</t>
   </si>
   <si>
     <t xml:space="preserve">2.28698658943176</t>
@@ -842,10 +842,10 @@
     <t xml:space="preserve">2.29698801040649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31532430648804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28365254402161</t>
+    <t xml:space="preserve">2.31532382965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28365278244019</t>
   </si>
   <si>
     <t xml:space="preserve">2.28865337371826</t>
@@ -857,13 +857,13 @@
     <t xml:space="preserve">2.30198884010315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30365562438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29365396499634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24198007583618</t>
+    <t xml:space="preserve">2.30365538597107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29365420341492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2419798374176</t>
   </si>
   <si>
     <t xml:space="preserve">2.2669837474823</t>
@@ -872,37 +872,37 @@
     <t xml:space="preserve">2.2686505317688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32699179649353</t>
+    <t xml:space="preserve">2.32699203491211</t>
   </si>
   <si>
     <t xml:space="preserve">2.31865763664246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3103232383728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24364709854126</t>
+    <t xml:space="preserve">2.31032347679138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24364733695984</t>
   </si>
   <si>
     <t xml:space="preserve">2.25031447410583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22531127929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25198125839233</t>
+    <t xml:space="preserve">2.22531175613403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25198149681091</t>
   </si>
   <si>
     <t xml:space="preserve">2.22197723388672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20697522163391</t>
+    <t xml:space="preserve">2.20697546005249</t>
   </si>
   <si>
     <t xml:space="preserve">2.20030784606934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16863656044006</t>
+    <t xml:space="preserve">2.16863632202148</t>
   </si>
   <si>
     <t xml:space="preserve">2.17863821983337</t>
@@ -914,10 +914,10 @@
     <t xml:space="preserve">2.18697261810303</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19697380065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18363857269287</t>
+    <t xml:space="preserve">2.1969735622406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18363881111145</t>
   </si>
   <si>
     <t xml:space="preserve">2.18530559539795</t>
@@ -929,13 +929,13 @@
     <t xml:space="preserve">2.17530417442322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1419665813446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15363430976868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14363288879395</t>
+    <t xml:space="preserve">2.14196610450745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15363454818726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14363312721252</t>
   </si>
   <si>
     <t xml:space="preserve">2.13529849052429</t>
@@ -944,7 +944,7 @@
     <t xml:space="preserve">2.12696409225464</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12863087654114</t>
+    <t xml:space="preserve">2.1286313533783</t>
   </si>
   <si>
     <t xml:space="preserve">2.12029647827148</t>
@@ -956,19 +956,19 @@
     <t xml:space="preserve">2.11862969398499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37366557121277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37533187866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40700340270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39533472061157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39200091362</t>
+    <t xml:space="preserve">2.37366533279419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37533235549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40700316429138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39533519744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39200115203857</t>
   </si>
   <si>
     <t xml:space="preserve">2.49868249893188</t>
@@ -977,31 +977,31 @@
     <t xml:space="preserve">2.49534893035889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50868439674377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51201772689819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51535177230835</t>
+    <t xml:space="preserve">2.5086841583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51201820373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51535153388977</t>
   </si>
   <si>
     <t xml:space="preserve">2.51701903343201</t>
   </si>
   <si>
-    <t xml:space="preserve">2.523686170578</t>
+    <t xml:space="preserve">2.52368664741516</t>
   </si>
   <si>
     <t xml:space="preserve">2.52535343170166</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54535579681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53368782997131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53202056884766</t>
+    <t xml:space="preserve">2.54535603523254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53368759155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53202080726624</t>
   </si>
   <si>
     <t xml:space="preserve">2.54035568237305</t>
@@ -1016,7 +1016,7 @@
     <t xml:space="preserve">2.53702139854431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49701619148254</t>
+    <t xml:space="preserve">2.49701571464539</t>
   </si>
   <si>
     <t xml:space="preserve">2.42700600624084</t>
@@ -1025,100 +1025,100 @@
     <t xml:space="preserve">2.50034952163696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5053505897522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48368072509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45200967788696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51368498802185</t>
+    <t xml:space="preserve">2.50535035133362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48368048667908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45200943946838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51368522644043</t>
   </si>
   <si>
     <t xml:space="preserve">2.54202222824097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54868960380554</t>
+    <t xml:space="preserve">2.54868984222412</t>
   </si>
   <si>
     <t xml:space="preserve">2.51035141944885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52035212516785</t>
+    <t xml:space="preserve">2.520352602005</t>
   </si>
   <si>
     <t xml:space="preserve">2.47201251983643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5020170211792</t>
+    <t xml:space="preserve">2.50201654434204</t>
   </si>
   <si>
     <t xml:space="preserve">2.48701453208923</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0004198551178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81706047058105</t>
+    <t xml:space="preserve">3.00041961669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81706070899963</t>
   </si>
   <si>
     <t xml:space="preserve">2.75038456916809</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7170467376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8087260723114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80039143562317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83372950553894</t>
+    <t xml:space="preserve">2.71704649925232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80872654914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80039167404175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83372974395752</t>
   </si>
   <si>
     <t xml:space="preserve">2.78372240066528</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84206414222717</t>
+    <t xml:space="preserve">2.84206438064575</t>
   </si>
   <si>
     <t xml:space="preserve">2.75871920585632</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85039854049683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85873293876648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89207100868225</t>
+    <t xml:space="preserve">2.85039901733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85873341560364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89207124710083</t>
   </si>
   <si>
     <t xml:space="preserve">2.82539510726929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72538089752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61703252792358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64203643798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70037794113159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65870547294617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62536764144897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63370180130005</t>
+    <t xml:space="preserve">2.72538137435913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61703300476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64203667640686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70037770271301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65870523452759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6253674030304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63370156288147</t>
   </si>
   <si>
     <t xml:space="preserve">2.59202909469604</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">2.66703987121582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70871210098267</t>
+    <t xml:space="preserve">2.70871233940125</t>
   </si>
   <si>
     <t xml:space="preserve">2.74204993247986</t>
@@ -1139,31 +1139,31 @@
     <t xml:space="preserve">2.68370890617371</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6003634929657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58369469642639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56702589988708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76705384254456</t>
+    <t xml:space="preserve">2.60036373138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58369421958923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56702542304993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76705360412598</t>
   </si>
   <si>
     <t xml:space="preserve">2.73371553421021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79205679893494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86706757545471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87540221214294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88373684883118</t>
+    <t xml:space="preserve">2.79205727577209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86706733703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87540245056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8837366104126</t>
   </si>
   <si>
     <t xml:space="preserve">2.77538824081421</t>
@@ -1181,7 +1181,7 @@
     <t xml:space="preserve">2.77246117591858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64567184448242</t>
+    <t xml:space="preserve">2.645672082901</t>
   </si>
   <si>
     <t xml:space="preserve">2.70484018325806</t>
@@ -1193,13 +1193,13 @@
     <t xml:space="preserve">2.66257739067078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69638776779175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65412449836731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60340905189514</t>
+    <t xml:space="preserve">2.69638752937317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65412473678589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60340857505798</t>
   </si>
   <si>
     <t xml:space="preserve">2.63721919059753</t>
@@ -1211,16 +1211,16 @@
     <t xml:space="preserve">2.5780508518219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59495615959167</t>
+    <t xml:space="preserve">2.59495639801025</t>
   </si>
   <si>
     <t xml:space="preserve">2.50197720527649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49352478981018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54424047470093</t>
+    <t xml:space="preserve">2.49352502822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54424023628235</t>
   </si>
   <si>
     <t xml:space="preserve">2.5611457824707</t>
@@ -1229,10 +1229,10 @@
     <t xml:space="preserve">2.58650350570679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51888251304626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53578782081604</t>
+    <t xml:space="preserve">2.51888203620911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53578758239746</t>
   </si>
   <si>
     <t xml:space="preserve">2.55269312858582</t>
@@ -1241,25 +1241,25 @@
     <t xml:space="preserve">2.51043009757996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56959843635559</t>
+    <t xml:space="preserve">2.56959795951843</t>
   </si>
   <si>
     <t xml:space="preserve">2.46816682815552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48507213592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41745090484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45126152038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39209318161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38364028930664</t>
+    <t xml:space="preserve">2.48507189750671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41745066642761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45126128196716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39209294319153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38364052772522</t>
   </si>
   <si>
     <t xml:space="preserve">2.27375626564026</t>
@@ -1271,58 +1271,58 @@
     <t xml:space="preserve">2.36673498153687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35828280448914</t>
+    <t xml:space="preserve">2.35828232765198</t>
   </si>
   <si>
     <t xml:space="preserve">2.43435621261597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42590308189392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34982991218567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28220891952515</t>
+    <t xml:space="preserve">2.42590355873108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34982967376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28220868110657</t>
   </si>
   <si>
     <t xml:space="preserve">2.32447218894958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40899801254272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45971393585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44280862808228</t>
+    <t xml:space="preserve">2.40899848937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45971417427063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44280886650085</t>
   </si>
   <si>
     <t xml:space="preserve">2.33292460441589</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3413770198822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40054535865784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37518787384033</t>
+    <t xml:space="preserve">2.34137749671936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40054559707642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37518763542175</t>
   </si>
   <si>
     <t xml:space="preserve">2.47661948204041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30756664276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23994541168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29430198669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23437666893005</t>
+    <t xml:space="preserve">2.30756711959839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23994612693787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29430246353149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23437643051147</t>
   </si>
   <si>
     <t xml:space="preserve">2.2429370880127</t>
@@ -1337,67 +1337,67 @@
     <t xml:space="preserve">2.27718067169189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26861977577209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.448397397995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37134957313538</t>
+    <t xml:space="preserve">2.26862001419067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44839715957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37134981155396</t>
   </si>
   <si>
     <t xml:space="preserve">2.31142401695251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28574156761169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26005911827087</t>
+    <t xml:space="preserve">2.28574180603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26005887985229</t>
   </si>
   <si>
     <t xml:space="preserve">2.35422825813293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22581577301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20869374275208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30286312103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31998443603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37991070747375</t>
+    <t xml:space="preserve">2.22581553459167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20869398117065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30286335945129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31998491287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37991046905518</t>
   </si>
   <si>
     <t xml:space="preserve">2.40559315681458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39703226089478</t>
+    <t xml:space="preserve">2.3970320224762</t>
   </si>
   <si>
     <t xml:space="preserve">2.32854580879211</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847160339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36278915405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34566712379456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20013308525085</t>
+    <t xml:space="preserve">2.38847136497498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36278891563416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34566736221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20013332366943</t>
   </si>
   <si>
     <t xml:space="preserve">2.18301153182983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43983626365662</t>
+    <t xml:space="preserve">2.4398365020752</t>
   </si>
   <si>
     <t xml:space="preserve">2.54256629943848</t>
@@ -1406,16 +1406,16 @@
     <t xml:space="preserve">2.60249209403992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69666123390198</t>
+    <t xml:space="preserve">2.69666147232056</t>
   </si>
   <si>
     <t xml:space="preserve">2.77370858192444</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63673543930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67097854614258</t>
+    <t xml:space="preserve">2.63673520088196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.670978307724</t>
   </si>
   <si>
     <t xml:space="preserve">2.61961364746094</t>
@@ -1424,31 +1424,31 @@
     <t xml:space="preserve">2.65385699272156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68810057640076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64529609680176</t>
+    <t xml:space="preserve">2.68810033798218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64529633522034</t>
   </si>
   <si>
     <t xml:space="preserve">2.71378302574158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7223436832428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07333755493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5270619392395</t>
+    <t xml:space="preserve">2.72234392166138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07333779335022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52706170082092</t>
   </si>
   <si>
     <t xml:space="preserve">3.59554815292358</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6554741859436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58698773384094</t>
+    <t xml:space="preserve">3.65547394752502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58698749542236</t>
   </si>
   <si>
     <t xml:space="preserve">3.6126697063446</t>
@@ -1457,10 +1457,10 @@
     <t xml:space="preserve">3.5356228351593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42433214187622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54418349266052</t>
+    <t xml:space="preserve">3.42433190345764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54418325424194</t>
   </si>
   <si>
     <t xml:space="preserve">3.56986594200134</t>
@@ -1469,31 +1469,31 @@
     <t xml:space="preserve">3.55274438858032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56130480766296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50993990898132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4842574596405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57842683792114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63835287094116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74108266830444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16912364959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60572624206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15361976623535</t>
+    <t xml:space="preserve">3.56130456924438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5099401473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48425769805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57842636108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.638352394104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74108242988586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16912412643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60572671890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15361928939819</t>
   </si>
   <si>
     <t xml:space="preserve">4.62284803390503</t>
@@ -1502,34 +1502,34 @@
     <t xml:space="preserve">4.19480657577515</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45163154602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53723955154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52011823654175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58860397338867</t>
+    <t xml:space="preserve">4.45163106918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53724002838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52011775970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58860492706299</t>
   </si>
   <si>
     <t xml:space="preserve">4.34890127182007</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16056299209595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23761034011841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29753637313843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89517760276794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27879762649536</t>
+    <t xml:space="preserve">4.16056346893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23761081695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29753684997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89517784118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27879810333252</t>
   </si>
   <si>
     <t xml:space="preserve">3.25311541557312</t>
@@ -1538,31 +1538,31 @@
     <t xml:space="preserve">2.8935604095459</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15894603729248</t>
+    <t xml:space="preserve">3.15894651412964</t>
   </si>
   <si>
     <t xml:space="preserve">3.16750693321228</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0390944480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44145369529724</t>
+    <t xml:space="preserve">3.03909468650818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44145345687866</t>
   </si>
   <si>
     <t xml:space="preserve">3.38152766227722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39008831977844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84381246566772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83525156974792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87805581092834</t>
+    <t xml:space="preserve">3.3900887966156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84381222724915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83525133132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87805604934692</t>
   </si>
   <si>
     <t xml:space="preserve">3.76676511764526</t>
@@ -1571,46 +1571,46 @@
     <t xml:space="preserve">3.88661646842957</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85237336158752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92942070960999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95510292053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93798136711121</t>
+    <t xml:space="preserve">3.8523736000061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92942118644714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95510268211365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93798112869263</t>
   </si>
   <si>
     <t xml:space="preserve">4.11775875091553</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25473260879517</t>
+    <t xml:space="preserve">4.25473213195801</t>
   </si>
   <si>
     <t xml:space="preserve">4.22904968261719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26329326629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28041505813599</t>
+    <t xml:space="preserve">4.26329278945923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28041458129883</t>
   </si>
   <si>
     <t xml:space="preserve">4.43450975418091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20336675643921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00646781921387</t>
+    <t xml:space="preserve">4.20336723327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00646829605103</t>
   </si>
   <si>
     <t xml:space="preserve">4.10919809341431</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15200185775757</t>
+    <t xml:space="preserve">4.15200281143188</t>
   </si>
   <si>
     <t xml:space="preserve">4.08351612091064</t>
@@ -1619,19 +1619,19 @@
     <t xml:space="preserve">3.94654250144958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07495546340942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02359008789062</t>
+    <t xml:space="preserve">4.07495498657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02358961105347</t>
   </si>
   <si>
     <t xml:space="preserve">3.96366405487061</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13488101959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12631940841675</t>
+    <t xml:space="preserve">4.13488054275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12631988525391</t>
   </si>
   <si>
     <t xml:space="preserve">5.01664638519287</t>
@@ -1646,7 +1646,7 @@
     <t xml:space="preserve">4.96528148651123</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94816017150879</t>
+    <t xml:space="preserve">4.94815969467163</t>
   </si>
   <si>
     <t xml:space="preserve">5.20498418807983</t>
@@ -1655,43 +1655,43 @@
     <t xml:space="preserve">5.56453943252563</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6843900680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95833683013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90697193145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88985061645508</t>
+    <t xml:space="preserve">5.68439102172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95833778381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90697240829468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88985013961792</t>
   </si>
   <si>
     <t xml:space="preserve">6.57471704483032</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12955379486084</t>
+    <t xml:space="preserve">6.12955331802368</t>
   </si>
   <si>
     <t xml:space="preserve">6.4035005569458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01987981796265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20821857452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32806968688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.054123878479</t>
+    <t xml:space="preserve">7.0198802947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20821809768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32807016372681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05412340164185</t>
   </si>
   <si>
     <t xml:space="preserve">7.00275850296021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42397689819336</t>
+    <t xml:space="preserve">7.42397737503052</t>
   </si>
   <si>
     <t xml:space="preserve">7.28357124328613</t>
@@ -1700,55 +1700,55 @@
     <t xml:space="preserve">6.8799033164978</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96765661239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59909057617188</t>
+    <t xml:space="preserve">6.9676570892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59909105300903</t>
   </si>
   <si>
     <t xml:space="preserve">6.51133680343628</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73949718475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84480237960815</t>
+    <t xml:space="preserve">6.73949670791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84480142593384</t>
   </si>
   <si>
     <t xml:space="preserve">6.82725095748901</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68684482574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66929388046265</t>
+    <t xml:space="preserve">6.68684387207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66929340362549</t>
   </si>
   <si>
     <t xml:space="preserve">6.45868444442749</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4060320854187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31827878952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80970048904419</t>
+    <t xml:space="preserve">6.40603256225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31827831268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80970001220703</t>
   </si>
   <si>
     <t xml:space="preserve">7.17826652526855</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3537745475769</t>
+    <t xml:space="preserve">7.35377359390259</t>
   </si>
   <si>
     <t xml:space="preserve">7.26602029800415</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05541086196899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07296180725098</t>
+    <t xml:space="preserve">7.05541133880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07296276092529</t>
   </si>
   <si>
     <t xml:space="preserve">6.63419246673584</t>
@@ -1760,19 +1760,19 @@
     <t xml:space="preserve">6.30072736740112</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05501651763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03746604919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37053632736206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40563821792603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52849340438843</t>
+    <t xml:space="preserve">6.05501699447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03746652603149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37053680419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40563774108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52849388122559</t>
   </si>
   <si>
     <t xml:space="preserve">5.65134906768799</t>
@@ -1781,19 +1781,19 @@
     <t xml:space="preserve">6.12521982192993</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96726322174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01991558074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91461086273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.844407081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94971179962158</t>
+    <t xml:space="preserve">5.96726274490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01991510391235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91461038589478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84440755844116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94971227645874</t>
   </si>
   <si>
     <t xml:space="preserve">5.86195802688599</t>
@@ -1802,22 +1802,22 @@
     <t xml:space="preserve">5.82685661315918</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93216133117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87950849533081</t>
+    <t xml:space="preserve">5.93216228485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87950944900513</t>
   </si>
   <si>
     <t xml:space="preserve">5.79175519943237</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68645048141479</t>
+    <t xml:space="preserve">5.68645095825195</t>
   </si>
   <si>
     <t xml:space="preserve">5.45829010009766</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63379812240601</t>
+    <t xml:space="preserve">5.63379859924316</t>
   </si>
   <si>
     <t xml:space="preserve">5.70400142669678</t>
@@ -1826,13 +1826,13 @@
     <t xml:space="preserve">5.58114624023438</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66890001296997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56359577178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61624765396118</t>
+    <t xml:space="preserve">5.66889953613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56359481811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61624717712402</t>
   </si>
   <si>
     <t xml:space="preserve">5.49339246749878</t>
@@ -1847,43 +1847,43 @@
     <t xml:space="preserve">5.26523208618164</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28278255462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35298538208008</t>
+    <t xml:space="preserve">5.28278303146362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35298585891724</t>
   </si>
   <si>
     <t xml:space="preserve">5.42318868637085</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47584056854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3880877494812</t>
+    <t xml:space="preserve">5.4758415222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38808727264404</t>
   </si>
   <si>
     <t xml:space="preserve">5.5109429359436</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77420425415039</t>
+    <t xml:space="preserve">5.77420473098755</t>
   </si>
   <si>
     <t xml:space="preserve">5.44073963165283</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54604482650757</t>
+    <t xml:space="preserve">5.54604434967041</t>
   </si>
   <si>
     <t xml:space="preserve">6.23052453994751</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35337972640991</t>
+    <t xml:space="preserve">6.35338020324707</t>
   </si>
   <si>
     <t xml:space="preserve">6.16032123565674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37093114852905</t>
+    <t xml:space="preserve">6.37093162536621</t>
   </si>
   <si>
     <t xml:space="preserve">6.47623538970947</t>
@@ -1898,7 +1898,7 @@
     <t xml:space="preserve">6.98520755767822</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33622360229492</t>
+    <t xml:space="preserve">7.33622217178345</t>
   </si>
   <si>
     <t xml:space="preserve">7.0905122756958</t>
@@ -1907,7 +1907,7 @@
     <t xml:space="preserve">7.16071557998657</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19581699371338</t>
+    <t xml:space="preserve">7.19581651687622</t>
   </si>
   <si>
     <t xml:space="preserve">6.95010614395142</t>
@@ -1922,7 +1922,7 @@
     <t xml:space="preserve">7.02030944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8451943397522</t>
+    <t xml:space="preserve">7.84519481658936</t>
   </si>
   <si>
     <t xml:space="preserve">8.33661651611328</t>
@@ -1934,7 +1934,7 @@
     <t xml:space="preserve">8.42437171936035</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0825252532959</t>
+    <t xml:space="preserve">9.08252716064453</t>
   </si>
   <si>
     <t xml:space="preserve">8.68763256072998</t>
@@ -1946,28 +1946,28 @@
     <t xml:space="preserve">9.30191040039062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2763719558716</t>
+    <t xml:space="preserve">11.2763729095459</t>
   </si>
   <si>
     <t xml:space="preserve">13.1630802154541</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0753259658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1192035675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8559417724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0222806930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1100330352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9345264434814</t>
+    <t xml:space="preserve">13.075325012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1192026138306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8559408187866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0222797393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1100339889526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9345254898071</t>
   </si>
   <si>
     <t xml:space="preserve">11.3641262054443</t>
@@ -1976,22 +1976,22 @@
     <t xml:space="preserve">10.8814792633057</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1539115905762</t>
+    <t xml:space="preserve">12.1539106369019</t>
   </si>
   <si>
     <t xml:space="preserve">11.6712656021118</t>
   </si>
   <si>
-    <t xml:space="preserve">11.715142250061</t>
+    <t xml:space="preserve">11.7151412963867</t>
   </si>
   <si>
     <t xml:space="preserve">11.4518804550171</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0569868087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4957571029663</t>
+    <t xml:space="preserve">11.0569877624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.495756149292</t>
   </si>
   <si>
     <t xml:space="preserve">11.4080028533936</t>
@@ -2000,19 +2000,19 @@
     <t xml:space="preserve">11.8906488418579</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8028955459595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3202495574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6273860931396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1447401046753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6182193756104</t>
+    <t xml:space="preserve">11.8028945922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3202476501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.627387046814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1447410583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.618218421936</t>
   </si>
   <si>
     <t xml:space="preserve">10.5304641723633</t>
@@ -2021,7 +2021,7 @@
     <t xml:space="preserve">10.5743408203125</t>
   </si>
   <si>
-    <t xml:space="preserve">10.749849319458</t>
+    <t xml:space="preserve">10.7498483657837</t>
   </si>
   <si>
     <t xml:space="preserve">10.6620950698853</t>
@@ -2030,37 +2030,37 @@
     <t xml:space="preserve">10.3549566268921</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78455543518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91618824005127</t>
+    <t xml:space="preserve">9.78455638885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91618728637695</t>
   </si>
   <si>
     <t xml:space="preserve">10.0916938781738</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2324953079224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1886167526245</t>
+    <t xml:space="preserve">11.232494354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1886186599731</t>
   </si>
   <si>
     <t xml:space="preserve">11.1008644104004</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3553495407104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.267596244812</t>
+    <t xml:space="preserve">11.3553504943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2675971984863</t>
   </si>
   <si>
     <t xml:space="preserve">11.0218858718872</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2500448226929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3729009628296</t>
+    <t xml:space="preserve">11.2500457763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3729019165039</t>
   </si>
   <si>
     <t xml:space="preserve">11.2851467132568</t>
@@ -2072,7 +2072,7 @@
     <t xml:space="preserve">11.8467721939087</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9871778488159</t>
+    <t xml:space="preserve">11.9871788024902</t>
   </si>
   <si>
     <t xml:space="preserve">12.2855415344238</t>
@@ -2081,16 +2081,16 @@
     <t xml:space="preserve">12.2504396438599</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1626863479614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4672002792358</t>
+    <t xml:space="preserve">12.1626853942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4672012329102</t>
   </si>
   <si>
     <t xml:space="preserve">12.0372972488403</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0910358428955</t>
+    <t xml:space="preserve">12.0910348892212</t>
   </si>
   <si>
     <t xml:space="preserve">11.553656578064</t>
@@ -2105,22 +2105,22 @@
     <t xml:space="preserve">10.9446268081665</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5505466461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6759376525879</t>
+    <t xml:space="preserve">10.5505475997925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6759357452393</t>
   </si>
   <si>
     <t xml:space="preserve">10.9088010787964</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7117624282837</t>
+    <t xml:space="preserve">10.7117614746094</t>
   </si>
   <si>
     <t xml:space="preserve">10.6580228805542</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9267129898071</t>
+    <t xml:space="preserve">10.9267148971558</t>
   </si>
   <si>
     <t xml:space="preserve">11.0521020889282</t>
@@ -2135,19 +2135,19 @@
     <t xml:space="preserve">11.4282674789429</t>
   </si>
   <si>
-    <t xml:space="preserve">11.571569442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3745288848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3566179275513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3207931518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4461803436279</t>
+    <t xml:space="preserve">11.5715684890747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.374529838562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.356616973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3207921981812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4461793899536</t>
   </si>
   <si>
     <t xml:space="preserve">11.464093208313</t>
@@ -2156,10 +2156,10 @@
     <t xml:space="preserve">11.7148704528809</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7327833175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.750696182251</t>
+    <t xml:space="preserve">11.7327823638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7506952285767</t>
   </si>
   <si>
     <t xml:space="preserve">12.1805992126465</t>
@@ -2174,7 +2174,7 @@
     <t xml:space="preserve">12.3418121337891</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3597249984741</t>
+    <t xml:space="preserve">12.3597259521484</t>
   </si>
   <si>
     <t xml:space="preserve">11.6969575881958</t>
@@ -2183,19 +2183,19 @@
     <t xml:space="preserve">12.1268606185913</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0552110671997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8581714630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9298210144043</t>
+    <t xml:space="preserve">12.0552091598511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8581705093384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9298219680786</t>
   </si>
   <si>
     <t xml:space="preserve">12.2880754470825</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5925903320312</t>
+    <t xml:space="preserve">12.5925893783569</t>
   </si>
   <si>
     <t xml:space="preserve">12.503026008606</t>
@@ -2204,13 +2204,13 @@
     <t xml:space="preserve">11.9835596084595</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3239002227783</t>
+    <t xml:space="preserve">12.3239011764526</t>
   </si>
   <si>
     <t xml:space="preserve">10.9804515838623</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1774892807007</t>
+    <t xml:space="preserve">11.177490234375</t>
   </si>
   <si>
     <t xml:space="preserve">11.284966468811</t>
@@ -2219,19 +2219,19 @@
     <t xml:space="preserve">11.3387041091919</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8939962387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7686080932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6253061294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0014715194702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1089477539062</t>
+    <t xml:space="preserve">11.8939952850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.768609046936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6253070831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0014724731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1089487075806</t>
   </si>
   <si>
     <t xml:space="preserve">11.9656467437744</t>
@@ -2240,16 +2240,16 @@
     <t xml:space="preserve">12.1985120773315</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4313764572144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2522487640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8612785339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8433666229248</t>
+    <t xml:space="preserve">12.43137550354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2522497177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8612794876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8433675765991</t>
   </si>
   <si>
     <t xml:space="preserve">12.6821527481079</t>
@@ -2261,19 +2261,19 @@
     <t xml:space="preserve">13.3449201583862</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2405529022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0972518920898</t>
+    <t xml:space="preserve">14.240553855896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0972509384155</t>
   </si>
   <si>
     <t xml:space="preserve">14.3301162719727</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4734172821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5988063812256</t>
+    <t xml:space="preserve">14.4734182357788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5988054275513</t>
   </si>
   <si>
     <t xml:space="preserve">13.8823003768921</t>
@@ -2282,7 +2282,7 @@
     <t xml:space="preserve">13.864387512207</t>
   </si>
   <si>
-    <t xml:space="preserve">13.577784538269</t>
+    <t xml:space="preserve">13.5777854919434</t>
   </si>
   <si>
     <t xml:space="preserve">13.4703092575073</t>
@@ -2303,25 +2303,25 @@
     <t xml:space="preserve">13.8285617828369</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9539499282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4344844818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7210855484009</t>
+    <t xml:space="preserve">13.953950881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4344835281372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7210865020752</t>
   </si>
   <si>
     <t xml:space="preserve">13.5240478515625</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7031726837158</t>
+    <t xml:space="preserve">13.7031745910645</t>
   </si>
   <si>
     <t xml:space="preserve">13.2553577423096</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4523973464966</t>
+    <t xml:space="preserve">13.4523954391479</t>
   </si>
   <si>
     <t xml:space="preserve">13.3090953826904</t>
@@ -2336,16 +2336,16 @@
     <t xml:space="preserve">14.0256013870239</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7569122314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4375925064087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.712495803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3363342285156</t>
+    <t xml:space="preserve">13.756911277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.437593460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7124977111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.336332321167</t>
   </si>
   <si>
     <t xml:space="preserve">17.7156066894531</t>
@@ -2360,7 +2360,7 @@
     <t xml:space="preserve">21.3160457611084</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4503936767578</t>
+    <t xml:space="preserve">21.4503955841064</t>
   </si>
   <si>
     <t xml:space="preserve">21.5399551391602</t>
@@ -2372,19 +2372,19 @@
     <t xml:space="preserve">21.9877700805664</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2712650299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.017749786377</t>
+    <t xml:space="preserve">21.2712669372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0177516937256</t>
   </si>
   <si>
     <t xml:space="preserve">22.3460273742676</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1221160888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7342529296875</t>
+    <t xml:space="preserve">22.1221179962158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7342567443848</t>
   </si>
   <si>
     <t xml:space="preserve">21.8982086181641</t>
@@ -2393,10 +2393,10 @@
     <t xml:space="preserve">22.4355888366699</t>
   </si>
   <si>
-    <t xml:space="preserve">21.495174407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7190837860107</t>
+    <t xml:space="preserve">21.4951725006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7190818786621</t>
   </si>
   <si>
     <t xml:space="preserve">21.9429912567139</t>
@@ -2405,22 +2405,22 @@
     <t xml:space="preserve">21.7638645172119</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8534259796143</t>
+    <t xml:space="preserve">21.8534297943115</t>
   </si>
   <si>
     <t xml:space="preserve">23.3312206268311</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8086471557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3463935852051</t>
+    <t xml:space="preserve">21.8086452484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3463916778564</t>
   </si>
   <si>
     <t xml:space="preserve">25.3016109466553</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2420253753662</t>
+    <t xml:space="preserve">26.2420234680176</t>
   </si>
   <si>
     <t xml:space="preserve">25.525520324707</t>
@@ -2429,13 +2429,13 @@
     <t xml:space="preserve">25.2120475769043</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8837699890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4807395935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5702991485596</t>
+    <t xml:space="preserve">25.8837718963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4807376861572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5703010559082</t>
   </si>
   <si>
     <t xml:space="preserve">25.1224842071533</t>
@@ -2450,16 +2450,16 @@
     <t xml:space="preserve">25.704647064209</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4211521148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0629005432129</t>
+    <t xml:space="preserve">26.4211540222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0628967285156</t>
   </si>
   <si>
     <t xml:space="preserve">26.4659309387207</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1524620056152</t>
+    <t xml:space="preserve">26.1524639129639</t>
   </si>
   <si>
     <t xml:space="preserve">28.6602325439453</t>
@@ -2468,19 +2468,19 @@
     <t xml:space="preserve">27.6750373840332</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7794055938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5554943084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9881381988525</t>
+    <t xml:space="preserve">26.7794036865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5554962158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9881401062012</t>
   </si>
   <si>
     <t xml:space="preserve">25.2568302154541</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9581661224365</t>
+    <t xml:space="preserve">23.9581623077393</t>
   </si>
   <si>
     <t xml:space="preserve">24.0477275848389</t>
@@ -2489,7 +2489,7 @@
     <t xml:space="preserve">23.9133834838867</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5851078033447</t>
+    <t xml:space="preserve">24.5851058959961</t>
   </si>
   <si>
     <t xml:space="preserve">22.077335357666</t>
@@ -2498,25 +2498,25 @@
     <t xml:space="preserve">22.928186416626</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1968765258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.182071685791</t>
+    <t xml:space="preserve">23.1968746185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1820697784424</t>
   </si>
   <si>
     <t xml:space="preserve">24.2268524169922</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4955425262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3164138793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3908081054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8238201141357</t>
+    <t xml:space="preserve">24.4955444335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3164157867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3908061981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8238182067871</t>
   </si>
   <si>
     <t xml:space="preserve">23.0625305175781</t>
@@ -2528,16 +2528,16 @@
     <t xml:space="preserve">22.8834037780762</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2416591644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1672668457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3167839050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6002788543701</t>
+    <t xml:space="preserve">23.2416572570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1672687530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3167858123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6002807617188</t>
   </si>
   <si>
     <t xml:space="preserve">25.615083694458</t>
@@ -2558,43 +2558,43 @@
     <t xml:space="preserve">26.197244644165</t>
   </si>
   <si>
-    <t xml:space="preserve">26.868968963623</t>
+    <t xml:space="preserve">26.8689670562744</t>
   </si>
   <si>
     <t xml:space="preserve">26.6450595855713</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4959125518799</t>
+    <t xml:space="preserve">27.4959106445312</t>
   </si>
   <si>
     <t xml:space="preserve">27.048095703125</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9437294006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8841400146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9289226531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7050113677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7797737121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9885082244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.630256652832</t>
+    <t xml:space="preserve">27.9437255859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8841419219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9289207458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7050151824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7797718048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9885101318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6302547454834</t>
   </si>
   <si>
     <t xml:space="preserve">27.2272205352783</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4063453674316</t>
+    <t xml:space="preserve">27.4063491821289</t>
   </si>
   <si>
     <t xml:space="preserve">26.6898403167725</t>
@@ -2603,13 +2603,13 @@
     <t xml:space="preserve">25.8389892578125</t>
   </si>
   <si>
-    <t xml:space="preserve">25.79421043396</t>
+    <t xml:space="preserve">25.7942085266113</t>
   </si>
   <si>
     <t xml:space="preserve">26.3315887451172</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7194499969482</t>
+    <t xml:space="preserve">24.7194519042969</t>
   </si>
   <si>
     <t xml:space="preserve">24.4507598876953</t>
@@ -2618,10 +2618,10 @@
     <t xml:space="preserve">23.599910736084</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4655666351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3615665435791</t>
+    <t xml:space="preserve">23.4655647277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3615646362305</t>
   </si>
   <si>
     <t xml:space="preserve">28.0332889556885</t>
@@ -2636,13 +2636,13 @@
     <t xml:space="preserve">27.6633834838867</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2979888916016</t>
+    <t xml:space="preserve">30.2979869842529</t>
   </si>
   <si>
     <t xml:space="preserve">26.891170501709</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3454113006592</t>
+    <t xml:space="preserve">27.3454132080078</t>
   </si>
   <si>
     <t xml:space="preserve">29.6620502471924</t>
@@ -2660,13 +2660,13 @@
     <t xml:space="preserve">30.5705375671387</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0247764587402</t>
+    <t xml:space="preserve">31.0247802734375</t>
   </si>
   <si>
     <t xml:space="preserve">31.0702037811279</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8885078430176</t>
+    <t xml:space="preserve">30.8885040283203</t>
   </si>
   <si>
     <t xml:space="preserve">28.9352626800537</t>
@@ -2675,7 +2675,7 @@
     <t xml:space="preserve">27.8905048370361</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9359264373779</t>
+    <t xml:space="preserve">27.9359283447266</t>
   </si>
   <si>
     <t xml:space="preserve">27.4362621307373</t>
@@ -2684,7 +2684,7 @@
     <t xml:space="preserve">28.0722007751465</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4355945587158</t>
+    <t xml:space="preserve">28.4355926513672</t>
   </si>
   <si>
     <t xml:space="preserve">28.5264415740967</t>
@@ -2693,19 +2693,19 @@
     <t xml:space="preserve">28.4810199737549</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3901710510254</t>
+    <t xml:space="preserve">28.390172958374</t>
   </si>
   <si>
     <t xml:space="preserve">29.1623821258545</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4349308013916</t>
+    <t xml:space="preserve">29.434928894043</t>
   </si>
   <si>
     <t xml:space="preserve">28.2538986206055</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1169567108154</t>
+    <t xml:space="preserve">29.1169586181641</t>
   </si>
   <si>
     <t xml:space="preserve">30.1162948608398</t>
@@ -2753,7 +2753,7 @@
     <t xml:space="preserve">34.6132965087891</t>
   </si>
   <si>
-    <t xml:space="preserve">35.340087890625</t>
+    <t xml:space="preserve">35.3400840759277</t>
   </si>
   <si>
     <t xml:space="preserve">34.4316024780273</t>
@@ -2762,7 +2762,7 @@
     <t xml:space="preserve">33.7048072814941</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9773559570312</t>
+    <t xml:space="preserve">33.9773597717285</t>
   </si>
   <si>
     <t xml:space="preserve">34.931266784668</t>
@@ -2798,22 +2798,22 @@
     <t xml:space="preserve">38.6106300354004</t>
   </si>
   <si>
-    <t xml:space="preserve">39.5645408630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1109657287598</t>
+    <t xml:space="preserve">39.5645370483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.110969543457</t>
   </si>
   <si>
     <t xml:space="preserve">36.4302673339844</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3868370056152</t>
+    <t xml:space="preserve">33.3868408203125</t>
   </si>
   <si>
     <t xml:space="preserve">32.8871765136719</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0688705444336</t>
+    <t xml:space="preserve">33.0688743591309</t>
   </si>
   <si>
     <t xml:space="preserve">33.3414154052734</t>
@@ -2828,7 +2828,7 @@
     <t xml:space="preserve">34.340747833252</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7509002685547</t>
+    <t xml:space="preserve">32.7508964538574</t>
   </si>
   <si>
     <t xml:space="preserve">32.6600532531738</t>
@@ -2840,43 +2840,43 @@
     <t xml:space="preserve">30.7976589202881</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3895015716553</t>
+    <t xml:space="preserve">29.3895034790039</t>
   </si>
   <si>
     <t xml:space="preserve">29.5257778167725</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6172924041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3447494506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0254421234131</t>
+    <t xml:space="preserve">28.6172943115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.344747543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0254440307617</t>
   </si>
   <si>
     <t xml:space="preserve">31.9332637786865</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2058067321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1149597167969</t>
+    <t xml:space="preserve">32.205810546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1149559020996</t>
   </si>
   <si>
     <t xml:space="preserve">32.2512359619141</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6152896881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0241088867188</t>
+    <t xml:space="preserve">31.6152935028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.024112701416</t>
   </si>
   <si>
     <t xml:space="preserve">33.1142959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6146278381348</t>
+    <t xml:space="preserve">32.614631652832</t>
   </si>
   <si>
     <t xml:space="preserve">31.2064743041992</t>
@@ -2885,7 +2885,7 @@
     <t xml:space="preserve">32.0695381164551</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5244483947754</t>
+    <t xml:space="preserve">31.5244445800781</t>
   </si>
   <si>
     <t xml:space="preserve">31.3427467346191</t>
@@ -2897,7 +2897,7 @@
     <t xml:space="preserve">32.5237770080566</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7054786682129</t>
+    <t xml:space="preserve">32.7054748535156</t>
   </si>
   <si>
     <t xml:space="preserve">32.1603889465332</t>
@@ -2915,31 +2915,31 @@
     <t xml:space="preserve">32.9325981140137</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0234489440918</t>
+    <t xml:space="preserve">33.0234451293945</t>
   </si>
   <si>
     <t xml:space="preserve">33.5231170654297</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4783554077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.432933807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8424167633057</t>
+    <t xml:space="preserve">32.4783592224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4329299926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.842414855957</t>
   </si>
   <si>
     <t xml:space="preserve">31.8878402709961</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4342613220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7074737548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.70680809021</t>
+    <t xml:space="preserve">30.4342632293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7074756622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7068061828613</t>
   </si>
   <si>
     <t xml:space="preserve">30.4796886444092</t>
@@ -2948,16 +2948,16 @@
     <t xml:space="preserve">29.616626739502</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8437442779541</t>
+    <t xml:space="preserve">29.8437461853027</t>
   </si>
   <si>
     <t xml:space="preserve">29.2532329559326</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7535648345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0708694458008</t>
+    <t xml:space="preserve">28.7535629272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0708675384521</t>
   </si>
   <si>
     <t xml:space="preserve">28.8898372650146</t>
@@ -2975,10 +2975,10 @@
     <t xml:space="preserve">28.9806861877441</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7989883422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8891754150391</t>
+    <t xml:space="preserve">28.7989902496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8891735076904</t>
   </si>
   <si>
     <t xml:space="preserve">29.0715351104736</t>
@@ -2990,10 +2990,10 @@
     <t xml:space="preserve">28.0267772674561</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6179580688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7542324066162</t>
+    <t xml:space="preserve">27.617956161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7542304992676</t>
   </si>
   <si>
     <t xml:space="preserve">28.1176242828369</t>
@@ -3008,7 +3008,7 @@
     <t xml:space="preserve">27.5725345611572</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6186237335205</t>
+    <t xml:space="preserve">26.6186218261719</t>
   </si>
   <si>
     <t xml:space="preserve">27.1182918548584</t>
@@ -3023,13 +3023,13 @@
     <t xml:space="preserve">26.9820194244385</t>
   </si>
   <si>
-    <t xml:space="preserve">26.346076965332</t>
+    <t xml:space="preserve">26.3460788726807</t>
   </si>
   <si>
     <t xml:space="preserve">25.8918361663818</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6647129058838</t>
+    <t xml:space="preserve">25.6647148132324</t>
   </si>
   <si>
     <t xml:space="preserve">26.2552280426025</t>
@@ -3050,7 +3050,7 @@
     <t xml:space="preserve">26.3915023803711</t>
   </si>
   <si>
-    <t xml:space="preserve">26.70947265625</t>
+    <t xml:space="preserve">26.7094707489014</t>
   </si>
   <si>
     <t xml:space="preserve">26.527774810791</t>
@@ -3077,7 +3077,7 @@
     <t xml:space="preserve">25.7555637359619</t>
   </si>
   <si>
-    <t xml:space="preserve">25.074197769165</t>
+    <t xml:space="preserve">25.0741996765137</t>
   </si>
   <si>
     <t xml:space="preserve">26.0735340118408</t>
@@ -4278,6 +4278,9 @@
   </si>
   <si>
     <t xml:space="preserve">19.3199996948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0499992370605</t>
   </si>
 </sst>
 </file>
@@ -69434,7 +69437,7 @@
     </row>
     <row r="2494">
       <c r="A2494" s="1" t="n">
-        <v>45951.649525463</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B2494" t="n">
         <v>11215</v>
@@ -69455,6 +69458,32 @@
         <v>1421</v>
       </c>
       <c r="H2494" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" s="1" t="n">
+        <v>45952.6493287037</v>
+      </c>
+      <c r="B2495" t="n">
+        <v>40852</v>
+      </c>
+      <c r="C2495" t="n">
+        <v>19.7000007629395</v>
+      </c>
+      <c r="D2495" t="n">
+        <v>19.2000007629395</v>
+      </c>
+      <c r="E2495" t="n">
+        <v>19.2800006866455</v>
+      </c>
+      <c r="F2495" t="n">
+        <v>20.0499992370605</v>
+      </c>
+      <c r="G2495" t="s">
+        <v>1422</v>
+      </c>
+      <c r="H2495" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ARN.MI.xlsx
+++ b/data/ARN.MI.xlsx
@@ -44,25 +44,25 @@
     <t xml:space="preserve">ARN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94450068473816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91736018657684</t>
+    <t xml:space="preserve">1.94450092315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91736090183258</t>
   </si>
   <si>
     <t xml:space="preserve">1.90778195858002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8838347196579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93172907829285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91576409339905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83434462547302</t>
+    <t xml:space="preserve">1.88383483886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93172883987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91576433181763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83434438705444</t>
   </si>
   <si>
     <t xml:space="preserve">1.83594059944153</t>
@@ -71,124 +71,124 @@
     <t xml:space="preserve">1.91097486019135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80720412731171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74973154067993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71620571613312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80401134490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81039690971375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79602921009064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77208185195923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70662653446198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69704759120941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69066226482391</t>
+    <t xml:space="preserve">1.807204246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74973142147064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71620547771454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80401158332825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81039714813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79602897167206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77208197116852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70662665367126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69704782962799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69066202640533</t>
   </si>
   <si>
     <t xml:space="preserve">1.67629361152649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7002409696579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69864428043365</t>
+    <t xml:space="preserve">1.70024073123932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69864439964294</t>
   </si>
   <si>
     <t xml:space="preserve">1.67469727993011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66671478748322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66032886505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8151867389679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82795798778534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86148452758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88543140888214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89181733131409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92853617668152</t>
+    <t xml:space="preserve">1.66671526432037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66032898426056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81518650054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8279584646225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86148428916931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88543117046356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8918172121048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92853605747223</t>
   </si>
   <si>
     <t xml:space="preserve">1.95407950878143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90618550777435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86786997318268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88064193725586</t>
+    <t xml:space="preserve">1.90618538856506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86787009239197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88064169883728</t>
   </si>
   <si>
     <t xml:space="preserve">1.85190534591675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85988783836365</t>
+    <t xml:space="preserve">1.85988795757294</t>
   </si>
   <si>
     <t xml:space="preserve">1.85509824752808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79283618927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78804659843445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78006434440613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75611710548401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76888883113861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76409959793091</t>
+    <t xml:space="preserve">1.79283630847931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78804683685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.780064702034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7561172246933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76888930797577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7640997171402</t>
   </si>
   <si>
     <t xml:space="preserve">1.78485369682312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77048540115356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72099483013153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73536336421967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.802414894104</t>
+    <t xml:space="preserve">1.77048552036285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72099447250366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73536324501038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80241501331329</t>
   </si>
   <si>
     <t xml:space="preserve">1.76250302791595</t>
@@ -197,13 +197,13 @@
     <t xml:space="preserve">1.74494194984436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73217022418976</t>
+    <t xml:space="preserve">1.73217034339905</t>
   </si>
   <si>
     <t xml:space="preserve">1.73695969581604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74334537982941</t>
+    <t xml:space="preserve">1.74334526062012</t>
   </si>
   <si>
     <t xml:space="preserve">1.75132775306702</t>
@@ -218,61 +218,61 @@
     <t xml:space="preserve">1.65234673023224</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6204172372818</t>
+    <t xml:space="preserve">1.62041711807251</t>
   </si>
   <si>
     <t xml:space="preserve">1.64276802539825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59008431434631</t>
+    <t xml:space="preserve">1.59008419513702</t>
   </si>
   <si>
     <t xml:space="preserve">1.60285615921021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54937422275543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51185739040375</t>
+    <t xml:space="preserve">1.54937434196472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51185727119446</t>
   </si>
   <si>
     <t xml:space="preserve">1.45598089694977</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43682312965393</t>
+    <t xml:space="preserve">1.43682324886322</t>
   </si>
   <si>
     <t xml:space="preserve">1.46955072879791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49748909473419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47673487663269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47274363040924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46875262260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49669086933136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47593653202057</t>
+    <t xml:space="preserve">1.49748921394348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47673499584198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47274386882782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46875250339508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49669075012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47593677043915</t>
   </si>
   <si>
     <t xml:space="preserve">1.50626957416534</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47753310203552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43841969966888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40090262889862</t>
+    <t xml:space="preserve">1.4775333404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43841958045959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40090250968933</t>
   </si>
   <si>
     <t xml:space="preserve">1.34901738166809</t>
@@ -287,154 +287,154 @@
     <t xml:space="preserve">1.32666671276093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34103500843048</t>
+    <t xml:space="preserve">1.34103488922119</t>
   </si>
   <si>
     <t xml:space="preserve">1.31708788871765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38653421401978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39691126346588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40649020671844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30671083927155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3234738111496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.305912733078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31229841709137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28994810581207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28515863418579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28595662117004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33305239677429</t>
+    <t xml:space="preserve">1.38653433322906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39691162109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40649032592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30671072006226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32347393035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30591261386871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31229877471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28994798660278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28515839576721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28595674037933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33305251598358</t>
   </si>
   <si>
     <t xml:space="preserve">1.33704376220703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30112314224243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36104881763458</t>
+    <t xml:space="preserve">1.30112326145172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36104893684387</t>
   </si>
   <si>
     <t xml:space="preserve">1.34627258777618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35283982753754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33806359767914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27157080173492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28880989551544</t>
+    <t xml:space="preserve">1.35283994674683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33806371688843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2715710401535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28880977630615</t>
   </si>
   <si>
     <t xml:space="preserve">1.29291439056396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30686950683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33888471126556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34955620765686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34380996227264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33642160892487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34709346294403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30522763729095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29127240180969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31425750255585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32164573669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26828718185425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27239155769348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2879890203476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29701864719391</t>
+    <t xml:space="preserve">1.30686962604523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33888447284698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34955644607544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34380984306335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33642184734344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34709358215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30522775650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29127252101898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31425762176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32164561748505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26828730106354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27239167690277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28798890113831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29701888561249</t>
   </si>
   <si>
     <t xml:space="preserve">1.24858582019806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32657134532928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33231747150421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35940706729889</t>
+    <t xml:space="preserve">1.32657110691071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33231735229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3594069480896</t>
   </si>
   <si>
     <t xml:space="preserve">1.42015337944031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48664629459381</t>
+    <t xml:space="preserve">1.48664617538452</t>
   </si>
   <si>
     <t xml:space="preserve">1.53343737125397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51619827747345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51866114139557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43739223480225</t>
+    <t xml:space="preserve">1.51619851589203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51866126060486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43739235401154</t>
   </si>
   <si>
     <t xml:space="preserve">1.4677654504776</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43000435829163</t>
+    <t xml:space="preserve">1.43000423908234</t>
   </si>
   <si>
     <t xml:space="preserve">1.40948176383972</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44478034973145</t>
+    <t xml:space="preserve">1.44478046894073</t>
   </si>
   <si>
     <t xml:space="preserve">1.55970597267151</t>
@@ -443,40 +443,40 @@
     <t xml:space="preserve">1.61798977851868</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70582580566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74851274490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72388565540314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68284070491791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67463171482086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65164685249329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64179587364197</t>
+    <t xml:space="preserve">1.70582604408264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74851262569427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72388553619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68284058570862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67463183403015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.651646733284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64179575443268</t>
   </si>
   <si>
     <t xml:space="preserve">1.67134809494019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6647812128067</t>
+    <t xml:space="preserve">1.66478097438812</t>
   </si>
   <si>
     <t xml:space="preserve">1.65657198429108</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69597506523132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69433319568634</t>
+    <t xml:space="preserve">1.69597518444061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69433331489563</t>
   </si>
   <si>
     <t xml:space="preserve">1.65821373462677</t>
@@ -485,22 +485,22 @@
     <t xml:space="preserve">1.68119895458221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68776631355286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6680645942688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65000486373901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66313910484314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67791533470154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03746914863586</t>
+    <t xml:space="preserve">1.68776607513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66806483268738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65000474452972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66313922405243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67791545391083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03746891021729</t>
   </si>
   <si>
     <t xml:space="preserve">2.04403591156006</t>
@@ -509,70 +509,70 @@
     <t xml:space="preserve">2.0391104221344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04075217247009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05224466323853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04731941223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04239392280579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19836449623108</t>
+    <t xml:space="preserve">2.04075264930725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0522449016571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04731917381287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04239416122437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1983642578125</t>
   </si>
   <si>
     <t xml:space="preserve">2.24105143547058</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18851375579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17537975311279</t>
+    <t xml:space="preserve">2.18851399421692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17537951469421</t>
   </si>
   <si>
     <t xml:space="preserve">2.145827293396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00627422332764</t>
+    <t xml:space="preserve">2.00627470016479</t>
   </si>
   <si>
     <t xml:space="preserve">1.98821485042572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99314033985138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99806571006775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99642372131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99970734119415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00299096107483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00791621208191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01120042800903</t>
+    <t xml:space="preserve">1.99313998222351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99806582927704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99642360210419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99970757961273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00299119949341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00791668891907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01119995117188</t>
   </si>
   <si>
     <t xml:space="preserve">2.02597594261169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03254342079163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02105093002319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01940894126892</t>
+    <t xml:space="preserve">2.03254318237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02105069160461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0194091796875</t>
   </si>
   <si>
     <t xml:space="preserve">2.024334192276</t>
@@ -584,46 +584,46 @@
     <t xml:space="preserve">2.05881190299988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0965735912323</t>
+    <t xml:space="preserve">2.09657311439514</t>
   </si>
   <si>
     <t xml:space="preserve">2.14746904373169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33955931663513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27552938461304</t>
+    <t xml:space="preserve">2.33955907821655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27552890777588</t>
   </si>
   <si>
     <t xml:space="preserve">2.32478308677673</t>
   </si>
   <si>
-    <t xml:space="preserve">2.278813123703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25746917724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29851388931274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26075291633606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28045439720154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30672311782837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35597705841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34120106697083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34284281730652</t>
+    <t xml:space="preserve">2.27881288528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25746941566467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29851412773132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26075267791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28045463562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30672287940979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35597729682922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34120082855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3428430557251</t>
   </si>
   <si>
     <t xml:space="preserve">2.3477680683136</t>
@@ -632,34 +632,34 @@
     <t xml:space="preserve">2.44627571105957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39209699630737</t>
+    <t xml:space="preserve">2.39209675788879</t>
   </si>
   <si>
     <t xml:space="preserve">2.3822455406189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38717103004456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38388776779175</t>
+    <t xml:space="preserve">2.38717126846313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38388752937317</t>
   </si>
   <si>
     <t xml:space="preserve">2.40523099899292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3806037902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42164921760559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33791732788086</t>
+    <t xml:space="preserve">2.38060426712036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42164897918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33791756629944</t>
   </si>
   <si>
     <t xml:space="preserve">2.32314133644104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35433530807495</t>
+    <t xml:space="preserve">2.35433554649353</t>
   </si>
   <si>
     <t xml:space="preserve">2.41015648841858</t>
@@ -668,10 +668,10 @@
     <t xml:space="preserve">2.40687274932861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43806719779968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41836547851562</t>
+    <t xml:space="preserve">2.4380669593811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4183657169342</t>
   </si>
   <si>
     <t xml:space="preserve">2.29030513763428</t>
@@ -680,43 +680,43 @@
     <t xml:space="preserve">2.34941005706787</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36418581008911</t>
+    <t xml:space="preserve">2.36418628692627</t>
   </si>
   <si>
     <t xml:space="preserve">2.3756787776947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40194773674011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3576192855835</t>
+    <t xml:space="preserve">2.40194749832153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35761880874634</t>
   </si>
   <si>
     <t xml:space="preserve">2.36746954917908</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37075304985046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37239503860474</t>
+    <t xml:space="preserve">2.37075328826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37239527702332</t>
   </si>
   <si>
     <t xml:space="preserve">2.362544298172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36582803726196</t>
+    <t xml:space="preserve">2.36582827568054</t>
   </si>
   <si>
     <t xml:space="preserve">2.39538049697876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37732028961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37403702735901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38881301879883</t>
+    <t xml:space="preserve">2.37732076644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37403726577759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38881325721741</t>
   </si>
   <si>
     <t xml:space="preserve">2.39373826980591</t>
@@ -728,22 +728,22 @@
     <t xml:space="preserve">2.41343998908997</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40358948707581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40030598640442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40851449966431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42329072952271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43149948120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42000699043274</t>
+    <t xml:space="preserve">2.40358901023865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40030574798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40851473808289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42329049110413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43149995803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42000722885132</t>
   </si>
   <si>
     <t xml:space="preserve">2.35105204582214</t>
@@ -755,19 +755,19 @@
     <t xml:space="preserve">2.34612631797791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43642497062683</t>
+    <t xml:space="preserve">2.43642520904541</t>
   </si>
   <si>
     <t xml:space="preserve">2.42657446861267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42985820770264</t>
+    <t xml:space="preserve">2.42985796928406</t>
   </si>
   <si>
     <t xml:space="preserve">2.4528431892395</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47701287269592</t>
+    <t xml:space="preserve">2.4770131111145</t>
   </si>
   <si>
     <t xml:space="preserve">2.47868013381958</t>
@@ -776,43 +776,43 @@
     <t xml:space="preserve">2.49201512336731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49368238449097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47534656524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46534490585327</t>
+    <t xml:space="preserve">2.49368214607239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47534608840942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46534442901611</t>
   </si>
   <si>
     <t xml:space="preserve">2.48201370239258</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46867847442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4586775302887</t>
+    <t xml:space="preserve">2.46867871284485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45867729187012</t>
   </si>
   <si>
     <t xml:space="preserve">2.46201109886169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45534348487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41700458526611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40867018699646</t>
+    <t xml:space="preserve">2.45534372329712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41700506210327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40867042541504</t>
   </si>
   <si>
     <t xml:space="preserve">2.36699771881104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34199404716492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36866450309753</t>
+    <t xml:space="preserve">2.34199380874634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36866474151611</t>
   </si>
   <si>
     <t xml:space="preserve">2.35366249084473</t>
@@ -836,7 +836,7 @@
     <t xml:space="preserve">2.28531956672668</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28698658943176</t>
+    <t xml:space="preserve">2.28698635101318</t>
   </si>
   <si>
     <t xml:space="preserve">2.29698801040649</t>
@@ -854,7 +854,7 @@
     <t xml:space="preserve">2.29032039642334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30198884010315</t>
+    <t xml:space="preserve">2.30198860168457</t>
   </si>
   <si>
     <t xml:space="preserve">2.30365538597107</t>
@@ -863,70 +863,70 @@
     <t xml:space="preserve">2.29365420341492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2419798374176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2669837474823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2686505317688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32699203491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31865763664246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31032347679138</t>
+    <t xml:space="preserve">2.24198007583618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26698398590088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26865029335022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32699227333069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31865739822388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31032299995422</t>
   </si>
   <si>
     <t xml:space="preserve">2.24364733695984</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25031447410583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22531175613403</t>
+    <t xml:space="preserve">2.25031471252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22531127929688</t>
   </si>
   <si>
     <t xml:space="preserve">2.25198149681091</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22197723388672</t>
+    <t xml:space="preserve">2.2219774723053</t>
   </si>
   <si>
     <t xml:space="preserve">2.20697546005249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20030784606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16863632202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17863821983337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16696953773499</t>
+    <t xml:space="preserve">2.20030736923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16863656044006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17863798141479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16696977615356</t>
   </si>
   <si>
     <t xml:space="preserve">2.18697261810303</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1969735622406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18363881111145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18530559539795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19197344779968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17530417442322</t>
+    <t xml:space="preserve">2.19697380065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18363857269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18530583381653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1919732093811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17530393600464</t>
   </si>
   <si>
     <t xml:space="preserve">2.14196610450745</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.15363454818726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14363312721252</t>
+    <t xml:space="preserve">2.1436333656311</t>
   </si>
   <si>
     <t xml:space="preserve">2.13529849052429</t>
@@ -944,7 +944,7 @@
     <t xml:space="preserve">2.12696409225464</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1286313533783</t>
+    <t xml:space="preserve">2.12863063812256</t>
   </si>
   <si>
     <t xml:space="preserve">2.12029647827148</t>
@@ -956,16 +956,16 @@
     <t xml:space="preserve">2.11862969398499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37366533279419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37533235549927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40700316429138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39533519744873</t>
+    <t xml:space="preserve">2.37366557121277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37533211708069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40700340270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39533495903015</t>
   </si>
   <si>
     <t xml:space="preserve">2.39200115203857</t>
@@ -977,73 +977,73 @@
     <t xml:space="preserve">2.49534893035889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5086841583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51201820373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51535153388977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51701903343201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52368664741516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52535343170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54535603523254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53368759155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53202080726624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54035568237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52702021598816</t>
+    <t xml:space="preserve">2.50868439674377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51201796531677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51535177230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51701879501343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52368640899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52535319328308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54535579681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53368782997131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53202104568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54035544395447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52702045440674</t>
   </si>
   <si>
     <t xml:space="preserve">2.53868842124939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53702139854431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49701571464539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42700600624084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50034952163696</t>
+    <t xml:space="preserve">2.53702116012573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49701595306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42700624465942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50034999847412</t>
   </si>
   <si>
     <t xml:space="preserve">2.50535035133362</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48368048667908</t>
+    <t xml:space="preserve">2.48368072509766</t>
   </si>
   <si>
     <t xml:space="preserve">2.45200943946838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51368522644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54202222824097</t>
+    <t xml:space="preserve">2.51368474960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54202198982239</t>
   </si>
   <si>
     <t xml:space="preserve">2.54868984222412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51035141944885</t>
+    <t xml:space="preserve">2.51035118103027</t>
   </si>
   <si>
     <t xml:space="preserve">2.520352602005</t>
@@ -1067,13 +1067,13 @@
     <t xml:space="preserve">2.75038456916809</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71704649925232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80872654914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80039167404175</t>
+    <t xml:space="preserve">2.7170467376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8087260723114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80039143562317</t>
   </si>
   <si>
     <t xml:space="preserve">2.83372974395752</t>
@@ -1082,13 +1082,13 @@
     <t xml:space="preserve">2.78372240066528</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84206438064575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75871920585632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85039901733398</t>
+    <t xml:space="preserve">2.84206414222717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75871896743774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85039877891541</t>
   </si>
   <si>
     <t xml:space="preserve">2.85873341560364</t>
@@ -1100,52 +1100,52 @@
     <t xml:space="preserve">2.82539510726929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72538137435913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61703300476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64203667640686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70037770271301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65870523452759</t>
+    <t xml:space="preserve">2.72538089752197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61703276634216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6420361995697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70037794113159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65870499610901</t>
   </si>
   <si>
     <t xml:space="preserve">2.6253674030304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63370156288147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59202909469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66703987121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70871233940125</t>
+    <t xml:space="preserve">2.63370180130005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59202885627747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66703963279724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70871210098267</t>
   </si>
   <si>
     <t xml:space="preserve">2.74204993247986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65037059783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68370890617371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60036373138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58369421958923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56702542304993</t>
+    <t xml:space="preserve">2.65037083625793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68370866775513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6003634929657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58369445800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56702566146851</t>
   </si>
   <si>
     <t xml:space="preserve">2.76705360412598</t>
@@ -1154,25 +1154,25 @@
     <t xml:space="preserve">2.73371553421021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79205727577209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86706733703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87540245056152</t>
+    <t xml:space="preserve">2.79205703735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86706757545471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87540197372437</t>
   </si>
   <si>
     <t xml:space="preserve">2.8837366104126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77538824081421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78091382980347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72174572944641</t>
+    <t xml:space="preserve">2.77538776397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78091406822205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72174549102783</t>
   </si>
   <si>
     <t xml:space="preserve">2.73019814491272</t>
@@ -1181,67 +1181,67 @@
     <t xml:space="preserve">2.77246117591858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.645672082901</t>
+    <t xml:space="preserve">2.64567160606384</t>
   </si>
   <si>
     <t xml:space="preserve">2.70484018325806</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68793487548828</t>
+    <t xml:space="preserve">2.68793511390686</t>
   </si>
   <si>
     <t xml:space="preserve">2.66257739067078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69638752937317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65412473678589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60340857505798</t>
+    <t xml:space="preserve">2.69638729095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65412449836731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6034083366394</t>
   </si>
   <si>
     <t xml:space="preserve">2.63721919059753</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61186099052429</t>
+    <t xml:space="preserve">2.61186146736145</t>
   </si>
   <si>
     <t xml:space="preserve">2.5780508518219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59495639801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50197720527649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49352502822876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54424023628235</t>
+    <t xml:space="preserve">2.59495615959167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50197696685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49352478981018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54424047470093</t>
   </si>
   <si>
     <t xml:space="preserve">2.5611457824707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58650350570679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51888203620911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53578758239746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55269312858582</t>
+    <t xml:space="preserve">2.58650326728821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51888275146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53578782081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55269265174866</t>
   </si>
   <si>
     <t xml:space="preserve">2.51043009757996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56959795951843</t>
+    <t xml:space="preserve">2.56959843635559</t>
   </si>
   <si>
     <t xml:space="preserve">2.46816682815552</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">2.48507189750671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41745066642761</t>
+    <t xml:space="preserve">2.41745090484619</t>
   </si>
   <si>
     <t xml:space="preserve">2.45126128196716</t>
@@ -1259,28 +1259,28 @@
     <t xml:space="preserve">2.39209294319153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38364052772522</t>
+    <t xml:space="preserve">2.38364028930664</t>
   </si>
   <si>
     <t xml:space="preserve">2.27375626564026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29911422729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36673498153687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35828232765198</t>
+    <t xml:space="preserve">2.29911470413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36673545837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35828256607056</t>
   </si>
   <si>
     <t xml:space="preserve">2.43435621261597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42590355873108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34982967376709</t>
+    <t xml:space="preserve">2.4259033203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34983038902283</t>
   </si>
   <si>
     <t xml:space="preserve">2.28220868110657</t>
@@ -1289,7 +1289,7 @@
     <t xml:space="preserve">2.32447218894958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40899848937988</t>
+    <t xml:space="preserve">2.4089982509613</t>
   </si>
   <si>
     <t xml:space="preserve">2.45971417427063</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">2.33292460441589</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34137749671936</t>
+    <t xml:space="preserve">2.3413770198822</t>
   </si>
   <si>
     <t xml:space="preserve">2.40054559707642</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">2.47661948204041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30756711959839</t>
+    <t xml:space="preserve">2.30756688117981</t>
   </si>
   <si>
     <t xml:space="preserve">2.23994612693787</t>
@@ -1322,19 +1322,19 @@
     <t xml:space="preserve">2.29430246353149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23437643051147</t>
+    <t xml:space="preserve">2.2343761920929</t>
   </si>
   <si>
     <t xml:space="preserve">2.2429370880127</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33710670471191</t>
+    <t xml:space="preserve">2.33710646629333</t>
   </si>
   <si>
     <t xml:space="preserve">2.25149822235107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27718067169189</t>
+    <t xml:space="preserve">2.27718114852905</t>
   </si>
   <si>
     <t xml:space="preserve">2.26862001419067</t>
@@ -1343,43 +1343,43 @@
     <t xml:space="preserve">2.44839715957642</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37134981155396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31142401695251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28574180603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26005887985229</t>
+    <t xml:space="preserve">2.37134957313538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31142377853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28574132919312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26005864143372</t>
   </si>
   <si>
     <t xml:space="preserve">2.35422825813293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22581553459167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20869398117065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30286335945129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31998491287231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37991046905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40559315681458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3970320224762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32854580879211</t>
+    <t xml:space="preserve">2.22581577301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20869374275208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30286312103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31998467445374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37991094589233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.405592918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39703249931335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32854604721069</t>
   </si>
   <si>
     <t xml:space="preserve">2.38847136497498</t>
@@ -1391,40 +1391,40 @@
     <t xml:space="preserve">2.34566736221313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20013332366943</t>
+    <t xml:space="preserve">2.20013308525085</t>
   </si>
   <si>
     <t xml:space="preserve">2.18301153182983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4398365020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54256629943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60249209403992</t>
+    <t xml:space="preserve">2.43983626365662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54256653785706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6024923324585</t>
   </si>
   <si>
     <t xml:space="preserve">2.69666147232056</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77370858192444</t>
+    <t xml:space="preserve">2.7737090587616</t>
   </si>
   <si>
     <t xml:space="preserve">2.63673520088196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.670978307724</t>
+    <t xml:space="preserve">2.67097878456116</t>
   </si>
   <si>
     <t xml:space="preserve">2.61961364746094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65385699272156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68810033798218</t>
+    <t xml:space="preserve">2.65385723114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68810057640076</t>
   </si>
   <si>
     <t xml:space="preserve">2.64529633522034</t>
@@ -1445,13 +1445,13 @@
     <t xml:space="preserve">3.59554815292358</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65547394752502</t>
+    <t xml:space="preserve">3.65547347068787</t>
   </si>
   <si>
     <t xml:space="preserve">3.58698749542236</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6126697063446</t>
+    <t xml:space="preserve">3.61266994476318</t>
   </si>
   <si>
     <t xml:space="preserve">3.5356228351593</t>
@@ -1460,7 +1460,7 @@
     <t xml:space="preserve">3.42433190345764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54418325424194</t>
+    <t xml:space="preserve">3.54418349266052</t>
   </si>
   <si>
     <t xml:space="preserve">3.56986594200134</t>
@@ -1469,19 +1469,19 @@
     <t xml:space="preserve">3.55274438858032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56130456924438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5099401473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48425769805908</t>
+    <t xml:space="preserve">3.56130480766296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50993967056274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48425817489624</t>
   </si>
   <si>
     <t xml:space="preserve">3.57842636108398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.638352394104</t>
+    <t xml:space="preserve">3.63835263252258</t>
   </si>
   <si>
     <t xml:space="preserve">3.74108242988586</t>
@@ -1490,25 +1490,25 @@
     <t xml:space="preserve">4.16912412643433</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60572671890259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15361928939819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62284803390503</t>
+    <t xml:space="preserve">4.60572624206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15361976623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62284755706787</t>
   </si>
   <si>
     <t xml:space="preserve">4.19480657577515</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45163106918335</t>
+    <t xml:space="preserve">4.45163154602051</t>
   </si>
   <si>
     <t xml:space="preserve">4.53724002838135</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52011775970459</t>
+    <t xml:space="preserve">4.52011728286743</t>
   </si>
   <si>
     <t xml:space="preserve">4.58860492706299</t>
@@ -1526,25 +1526,25 @@
     <t xml:space="preserve">4.29753684997559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89517784118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27879810333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25311541557312</t>
+    <t xml:space="preserve">3.89517760276794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27879738807678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25311517715454</t>
   </si>
   <si>
     <t xml:space="preserve">2.8935604095459</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15894651412964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16750693321228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03909468650818</t>
+    <t xml:space="preserve">3.15894603729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16750717163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0390944480896</t>
   </si>
   <si>
     <t xml:space="preserve">3.44145345687866</t>
@@ -1553,82 +1553,82 @@
     <t xml:space="preserve">3.38152766227722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3900887966156</t>
+    <t xml:space="preserve">3.39008855819702</t>
   </si>
   <si>
     <t xml:space="preserve">3.84381222724915</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83525133132935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87805604934692</t>
+    <t xml:space="preserve">3.8352518081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87805581092834</t>
   </si>
   <si>
     <t xml:space="preserve">3.76676511764526</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88661646842957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8523736000061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92942118644714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95510268211365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93798112869263</t>
+    <t xml:space="preserve">3.88661599159241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85237336158752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92942142486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95510339736938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93798160552979</t>
   </si>
   <si>
     <t xml:space="preserve">4.11775875091553</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25473213195801</t>
+    <t xml:space="preserve">4.25473165512085</t>
   </si>
   <si>
     <t xml:space="preserve">4.22904968261719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26329278945923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28041458129883</t>
+    <t xml:space="preserve">4.26329326629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28041410446167</t>
   </si>
   <si>
     <t xml:space="preserve">4.43450975418091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20336723327637</t>
+    <t xml:space="preserve">4.20336675643921</t>
   </si>
   <si>
     <t xml:space="preserve">4.00646829605103</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10919809341431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15200281143188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08351612091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94654250144958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07495498657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02358961105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96366405487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13488054275513</t>
+    <t xml:space="preserve">4.10919857025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15200185775757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08351564407349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94654273986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07495450973511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02358913421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96366429328918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13488101959229</t>
   </si>
   <si>
     <t xml:space="preserve">4.12631988525391</t>
@@ -1640,67 +1640,67 @@
     <t xml:space="preserve">4.70845651626587</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91391611099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96528148651123</t>
+    <t xml:space="preserve">4.91391563415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96528053283691</t>
   </si>
   <si>
     <t xml:space="preserve">4.94815969467163</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20498418807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56453943252563</t>
+    <t xml:space="preserve">5.20498466491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56453895568848</t>
   </si>
   <si>
     <t xml:space="preserve">5.68439102172852</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95833778381348</t>
+    <t xml:space="preserve">5.95833730697632</t>
   </si>
   <si>
     <t xml:space="preserve">5.90697240829468</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88985013961792</t>
+    <t xml:space="preserve">5.88985109329224</t>
   </si>
   <si>
     <t xml:space="preserve">6.57471704483032</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12955331802368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4035005569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0198802947998</t>
+    <t xml:space="preserve">6.12955379486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40350103378296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01987934112549</t>
   </si>
   <si>
     <t xml:space="preserve">7.20821809768677</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32807016372681</t>
+    <t xml:space="preserve">7.32807064056396</t>
   </si>
   <si>
     <t xml:space="preserve">7.05412340164185</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00275850296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42397737503052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28357124328613</t>
+    <t xml:space="preserve">7.00275897979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42397689819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28357172012329</t>
   </si>
   <si>
     <t xml:space="preserve">6.8799033164978</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9676570892334</t>
+    <t xml:space="preserve">6.96765661239624</t>
   </si>
   <si>
     <t xml:space="preserve">6.59909105300903</t>
@@ -1712,13 +1712,13 @@
     <t xml:space="preserve">6.73949670791626</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84480142593384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82725095748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68684387207031</t>
+    <t xml:space="preserve">6.844801902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82725048065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68684482574463</t>
   </si>
   <si>
     <t xml:space="preserve">6.66929340362549</t>
@@ -1727,28 +1727,28 @@
     <t xml:space="preserve">6.45868444442749</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40603256225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31827831268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80970001220703</t>
+    <t xml:space="preserve">6.4060320854187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31827783584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80970048904419</t>
   </si>
   <si>
     <t xml:space="preserve">7.17826652526855</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35377359390259</t>
+    <t xml:space="preserve">7.35377407073975</t>
   </si>
   <si>
     <t xml:space="preserve">7.26602029800415</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05541133880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07296276092529</t>
+    <t xml:space="preserve">7.05541086196899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07296228408813</t>
   </si>
   <si>
     <t xml:space="preserve">6.63419246673584</t>
@@ -1760,19 +1760,19 @@
     <t xml:space="preserve">6.30072736740112</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05501699447632</t>
+    <t xml:space="preserve">6.05501651763916</t>
   </si>
   <si>
     <t xml:space="preserve">6.03746652603149</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37053680419922</t>
+    <t xml:space="preserve">5.37053632736206</t>
   </si>
   <si>
     <t xml:space="preserve">5.40563774108887</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52849388122559</t>
+    <t xml:space="preserve">5.52849435806274</t>
   </si>
   <si>
     <t xml:space="preserve">5.65134906768799</t>
@@ -1790,22 +1790,22 @@
     <t xml:space="preserve">5.91461038589478</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84440755844116</t>
+    <t xml:space="preserve">5.844407081604</t>
   </si>
   <si>
     <t xml:space="preserve">5.94971227645874</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86195802688599</t>
+    <t xml:space="preserve">5.86195755004883</t>
   </si>
   <si>
     <t xml:space="preserve">5.82685661315918</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93216228485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87950944900513</t>
+    <t xml:space="preserve">5.93216180801392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87950897216797</t>
   </si>
   <si>
     <t xml:space="preserve">5.79175519943237</t>
@@ -1829,22 +1829,22 @@
     <t xml:space="preserve">5.66889953613281</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56359481811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61624717712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49339246749878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31788396835327</t>
+    <t xml:space="preserve">5.56359529495239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61624765396118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49339151382446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31788492202759</t>
   </si>
   <si>
     <t xml:space="preserve">5.17747831344604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26523208618164</t>
+    <t xml:space="preserve">5.2652325630188</t>
   </si>
   <si>
     <t xml:space="preserve">5.28278303146362</t>
@@ -1853,7 +1853,7 @@
     <t xml:space="preserve">5.35298585891724</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42318868637085</t>
+    <t xml:space="preserve">5.42318916320801</t>
   </si>
   <si>
     <t xml:space="preserve">5.4758415222168</t>
@@ -1862,13 +1862,13 @@
     <t xml:space="preserve">5.38808727264404</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5109429359436</t>
+    <t xml:space="preserve">5.51094341278076</t>
   </si>
   <si>
     <t xml:space="preserve">5.77420473098755</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44073963165283</t>
+    <t xml:space="preserve">5.44073915481567</t>
   </si>
   <si>
     <t xml:space="preserve">5.54604434967041</t>
@@ -1877,19 +1877,19 @@
     <t xml:space="preserve">6.23052453994751</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35338020324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16032123565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37093162536621</t>
+    <t xml:space="preserve">6.35337924957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1603217124939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37093114852905</t>
   </si>
   <si>
     <t xml:space="preserve">6.47623538970947</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42358303070068</t>
+    <t xml:space="preserve">6.42358350753784</t>
   </si>
   <si>
     <t xml:space="preserve">6.54643869400024</t>
@@ -1898,22 +1898,22 @@
     <t xml:space="preserve">6.98520755767822</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33622217178345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0905122756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16071557998657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19581651687622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95010614395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14316463470459</t>
+    <t xml:space="preserve">7.33622264862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09051179885864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16071510314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19581699371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95010662078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14316558837891</t>
   </si>
   <si>
     <t xml:space="preserve">7.12561368942261</t>
@@ -1925,22 +1925,22 @@
     <t xml:space="preserve">7.84519481658936</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33661651611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31906700134277</t>
+    <t xml:space="preserve">8.33661842346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31906604766846</t>
   </si>
   <si>
     <t xml:space="preserve">8.42437171936035</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08252716064453</t>
+    <t xml:space="preserve">9.08252620697021</t>
   </si>
   <si>
     <t xml:space="preserve">8.68763256072998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03864765167236</t>
+    <t xml:space="preserve">9.038649559021</t>
   </si>
   <si>
     <t xml:space="preserve">9.30191040039062</t>
@@ -1952,10 +1952,10 @@
     <t xml:space="preserve">13.1630802154541</t>
   </si>
   <si>
-    <t xml:space="preserve">13.075325012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1192026138306</t>
+    <t xml:space="preserve">13.0753259658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1192035675049</t>
   </si>
   <si>
     <t xml:space="preserve">12.8559408187866</t>
@@ -1964,31 +1964,31 @@
     <t xml:space="preserve">12.0222797393799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1100339889526</t>
+    <t xml:space="preserve">12.1100330352783</t>
   </si>
   <si>
     <t xml:space="preserve">11.9345254898071</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3641262054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8814792633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1539106369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6712656021118</t>
+    <t xml:space="preserve">11.36412525177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8814783096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1539115905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6712636947632</t>
   </si>
   <si>
     <t xml:space="preserve">11.7151412963867</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4518804550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0569877624512</t>
+    <t xml:space="preserve">11.4518795013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0569887161255</t>
   </si>
   <si>
     <t xml:space="preserve">11.495756149292</t>
@@ -1997,67 +1997,67 @@
     <t xml:space="preserve">11.4080028533936</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8906488418579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8028945922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3202476501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.627387046814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1447410583496</t>
+    <t xml:space="preserve">11.8906497955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8028955459595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3202495574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6273880004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1447401046753</t>
   </si>
   <si>
     <t xml:space="preserve">10.618218421936</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5304641723633</t>
+    <t xml:space="preserve">10.5304651260376</t>
   </si>
   <si>
     <t xml:space="preserve">10.5743408203125</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7498483657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6620950698853</t>
+    <t xml:space="preserve">10.749849319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6620941162109</t>
   </si>
   <si>
     <t xml:space="preserve">10.3549566268921</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78455638885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91618728637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0916938781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.232494354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1886186599731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1008644104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3553504943848</t>
+    <t xml:space="preserve">9.78455543518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91618633270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0916948318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2324953079224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1886177062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1008634567261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3553495407104</t>
   </si>
   <si>
     <t xml:space="preserve">11.2675971984863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0218858718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2500457763672</t>
+    <t xml:space="preserve">11.0218868255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2500448226929</t>
   </si>
   <si>
     <t xml:space="preserve">11.3729019165039</t>
@@ -2066,13 +2066,13 @@
     <t xml:space="preserve">11.2851467132568</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1973934173584</t>
+    <t xml:space="preserve">11.1973924636841</t>
   </si>
   <si>
     <t xml:space="preserve">11.8467721939087</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9871788024902</t>
+    <t xml:space="preserve">11.9871768951416</t>
   </si>
   <si>
     <t xml:space="preserve">12.2855415344238</t>
@@ -2084,7 +2084,7 @@
     <t xml:space="preserve">12.1626853942871</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4672012329102</t>
+    <t xml:space="preserve">12.4672002792358</t>
   </si>
   <si>
     <t xml:space="preserve">12.0372972488403</t>
@@ -2093,7 +2093,7 @@
     <t xml:space="preserve">12.0910348892212</t>
   </si>
   <si>
-    <t xml:space="preserve">11.553656578064</t>
+    <t xml:space="preserve">11.5536556243896</t>
   </si>
   <si>
     <t xml:space="preserve">11.6432199478149</t>
@@ -2108,28 +2108,28 @@
     <t xml:space="preserve">10.5505475997925</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6759357452393</t>
+    <t xml:space="preserve">10.6759376525879</t>
   </si>
   <si>
     <t xml:space="preserve">10.9088010787964</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7117614746094</t>
+    <t xml:space="preserve">10.7117624282837</t>
   </si>
   <si>
     <t xml:space="preserve">10.6580228805542</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9267148971558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0521020889282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4999179840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4820051193237</t>
+    <t xml:space="preserve">10.9267139434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0521030426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4999189376831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.482006072998</t>
   </si>
   <si>
     <t xml:space="preserve">11.4282674789429</t>
@@ -2138,7 +2138,7 @@
     <t xml:space="preserve">11.5715684890747</t>
   </si>
   <si>
-    <t xml:space="preserve">11.374529838562</t>
+    <t xml:space="preserve">11.3745288848877</t>
   </si>
   <si>
     <t xml:space="preserve">11.356616973877</t>
@@ -2153,16 +2153,16 @@
     <t xml:space="preserve">11.464093208313</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7148704528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7327823638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7506952285767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1805992126465</t>
+    <t xml:space="preserve">11.7148694992065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7327833175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7506942749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1805982589722</t>
   </si>
   <si>
     <t xml:space="preserve">12.6284151077271</t>
@@ -2171,7 +2171,7 @@
     <t xml:space="preserve">12.0731229782104</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3418121337891</t>
+    <t xml:space="preserve">12.3418130874634</t>
   </si>
   <si>
     <t xml:space="preserve">12.3597259521484</t>
@@ -2180,31 +2180,31 @@
     <t xml:space="preserve">11.6969575881958</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1268606185913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0552091598511</t>
+    <t xml:space="preserve">12.1268615722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0552110671997</t>
   </si>
   <si>
     <t xml:space="preserve">11.8581705093384</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9298219680786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2880754470825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5925893783569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.503026008606</t>
+    <t xml:space="preserve">11.9298210144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2880744934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5925903320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5030269622803</t>
   </si>
   <si>
     <t xml:space="preserve">11.9835596084595</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3239011764526</t>
+    <t xml:space="preserve">12.3239002227783</t>
   </si>
   <si>
     <t xml:space="preserve">10.9804515838623</t>
@@ -2216,91 +2216,91 @@
     <t xml:space="preserve">11.284966468811</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3387041091919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8939952850342</t>
+    <t xml:space="preserve">11.3387060165405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8939971923828</t>
   </si>
   <si>
     <t xml:space="preserve">11.768609046936</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6253070831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0014724731445</t>
+    <t xml:space="preserve">11.6253061294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0014705657959</t>
   </si>
   <si>
     <t xml:space="preserve">12.1089487075806</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9656467437744</t>
+    <t xml:space="preserve">11.9656476974487</t>
   </si>
   <si>
     <t xml:space="preserve">12.1985120773315</t>
   </si>
   <si>
-    <t xml:space="preserve">12.43137550354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2522497177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8612794876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8433675765991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6821527481079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7358903884888</t>
+    <t xml:space="preserve">12.4313764572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2522506713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8612785339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8433666229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6821537017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7358913421631</t>
   </si>
   <si>
     <t xml:space="preserve">13.3449201583862</t>
   </si>
   <si>
-    <t xml:space="preserve">14.240553855896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0972509384155</t>
+    <t xml:space="preserve">14.2405529022217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0972518920898</t>
   </si>
   <si>
     <t xml:space="preserve">14.3301162719727</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4734182357788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5988054275513</t>
+    <t xml:space="preserve">14.4734172821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.598804473877</t>
   </si>
   <si>
     <t xml:space="preserve">13.8823003768921</t>
   </si>
   <si>
-    <t xml:space="preserve">13.864387512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5777854919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4703092575073</t>
+    <t xml:space="preserve">13.8643865585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.577784538269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4703102111816</t>
   </si>
   <si>
     <t xml:space="preserve">13.6852607727051</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6673488616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5598735809326</t>
+    <t xml:space="preserve">13.66734790802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5598726272583</t>
   </si>
   <si>
     <t xml:space="preserve">13.6136102676392</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8285617828369</t>
+    <t xml:space="preserve">13.8285627365112</t>
   </si>
   <si>
     <t xml:space="preserve">13.953950881958</t>
@@ -2309,7 +2309,7 @@
     <t xml:space="preserve">13.4344835281372</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7210865020752</t>
+    <t xml:space="preserve">13.7210855484009</t>
   </si>
   <si>
     <t xml:space="preserve">13.5240478515625</t>
@@ -2321,25 +2321,25 @@
     <t xml:space="preserve">13.2553577423096</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4523954391479</t>
+    <t xml:space="preserve">13.4523973464966</t>
   </si>
   <si>
     <t xml:space="preserve">13.3090953826904</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2763786315918</t>
+    <t xml:space="preserve">14.2763776779175</t>
   </si>
   <si>
     <t xml:space="preserve">14.4196796417236</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0256013870239</t>
+    <t xml:space="preserve">14.0256023406982</t>
   </si>
   <si>
     <t xml:space="preserve">13.756911277771</t>
   </si>
   <si>
-    <t xml:space="preserve">14.437593460083</t>
+    <t xml:space="preserve">14.4375925064087</t>
   </si>
   <si>
     <t xml:space="preserve">16.7124977111816</t>
@@ -2351,112 +2351,112 @@
     <t xml:space="preserve">17.7156066894531</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2498779296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6591281890869</t>
+    <t xml:space="preserve">17.2498760223389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6591300964355</t>
   </si>
   <si>
     <t xml:space="preserve">21.3160457611084</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4503955841064</t>
+    <t xml:space="preserve">21.4503936767578</t>
   </si>
   <si>
     <t xml:space="preserve">21.5399551391602</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2116794586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9877700805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2712669372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0177516937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3460273742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1221179962158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7342567443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8982086181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4355888366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4951725006104</t>
+    <t xml:space="preserve">22.2116813659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.987771987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2712650299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.017749786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3460254669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1221160888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7342548370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8982105255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4355869293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.495174407959</t>
   </si>
   <si>
     <t xml:space="preserve">21.7190818786621</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9429912567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7638645172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8534297943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3312206268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8086452484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3463916778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3016109466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2420234680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.525520324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2120475769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8837718963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4807376861572</t>
+    <t xml:space="preserve">21.9429893493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7638626098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8534278869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3312187194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8086471557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3463935852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3016128540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2420253753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5255222320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2120494842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8837738037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4807395935059</t>
   </si>
   <si>
     <t xml:space="preserve">25.5703010559082</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1224842071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.361198425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3911762237549</t>
+    <t xml:space="preserve">25.122486114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3611965179443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3911743164062</t>
   </si>
   <si>
     <t xml:space="preserve">25.704647064209</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4211540222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0628967285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4659309387207</t>
+    <t xml:space="preserve">26.4211521148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0628986358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4659328460693</t>
   </si>
   <si>
     <t xml:space="preserve">26.1524639129639</t>
@@ -2465,10 +2465,10 @@
     <t xml:space="preserve">28.6602325439453</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6750373840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7794036865234</t>
+    <t xml:space="preserve">27.6750354766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7794055938721</t>
   </si>
   <si>
     <t xml:space="preserve">26.5554962158203</t>
@@ -2486,13 +2486,13 @@
     <t xml:space="preserve">24.0477275848389</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9133834838867</t>
+    <t xml:space="preserve">23.9133815765381</t>
   </si>
   <si>
     <t xml:space="preserve">24.5851058959961</t>
   </si>
   <si>
-    <t xml:space="preserve">22.077335357666</t>
+    <t xml:space="preserve">22.0773334503174</t>
   </si>
   <si>
     <t xml:space="preserve">22.928186416626</t>
@@ -2507,10 +2507,10 @@
     <t xml:space="preserve">24.2268524169922</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4955444335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3164157867432</t>
+    <t xml:space="preserve">24.4955425262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3164138793945</t>
   </si>
   <si>
     <t xml:space="preserve">22.3908061981201</t>
@@ -2525,7 +2525,7 @@
     <t xml:space="preserve">23.7790355682373</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8834037780762</t>
+    <t xml:space="preserve">22.8834018707275</t>
   </si>
   <si>
     <t xml:space="preserve">23.2416572570801</t>
@@ -2534,28 +2534,28 @@
     <t xml:space="preserve">25.1672687530518</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3167858123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6002807617188</t>
+    <t xml:space="preserve">27.3167839050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6002788543701</t>
   </si>
   <si>
     <t xml:space="preserve">25.615083694458</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4359569549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8985767364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9733352661133</t>
+    <t xml:space="preserve">25.4359550476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8985786437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9733371734619</t>
   </si>
   <si>
     <t xml:space="preserve">26.5107154846191</t>
   </si>
   <si>
-    <t xml:space="preserve">26.197244644165</t>
+    <t xml:space="preserve">26.1972427368164</t>
   </si>
   <si>
     <t xml:space="preserve">26.8689670562744</t>
@@ -2570,22 +2570,22 @@
     <t xml:space="preserve">27.048095703125</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9437255859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8841419219971</t>
+    <t xml:space="preserve">27.9437274932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8841400146484</t>
   </si>
   <si>
     <t xml:space="preserve">28.9289207458496</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7050151824951</t>
+    <t xml:space="preserve">28.7050113677979</t>
   </si>
   <si>
     <t xml:space="preserve">29.7797718048096</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9885101318359</t>
+    <t xml:space="preserve">27.9885082244873</t>
   </si>
   <si>
     <t xml:space="preserve">27.6302547454834</t>
@@ -2600,7 +2600,7 @@
     <t xml:space="preserve">26.6898403167725</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8389892578125</t>
+    <t xml:space="preserve">25.8389911651611</t>
   </si>
   <si>
     <t xml:space="preserve">25.7942085266113</t>
@@ -2615,13 +2615,13 @@
     <t xml:space="preserve">24.4507598876953</t>
   </si>
   <si>
-    <t xml:space="preserve">23.599910736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4655647277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3615646362305</t>
+    <t xml:space="preserve">23.5999088287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4655666351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3615665435791</t>
   </si>
   <si>
     <t xml:space="preserve">28.0332889556885</t>
@@ -2636,7 +2636,7 @@
     <t xml:space="preserve">27.6633834838867</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2979869842529</t>
+    <t xml:space="preserve">30.2979888916016</t>
   </si>
   <si>
     <t xml:space="preserve">26.891170501709</t>
@@ -2645,10 +2645,10 @@
     <t xml:space="preserve">27.3454132080078</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6620502471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.480354309082</t>
+    <t xml:space="preserve">29.662052154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4803524017334</t>
   </si>
   <si>
     <t xml:space="preserve">29.3440799713135</t>
@@ -2666,7 +2666,7 @@
     <t xml:space="preserve">31.0702037811279</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8885040283203</t>
+    <t xml:space="preserve">30.8885059356689</t>
   </si>
   <si>
     <t xml:space="preserve">28.9352626800537</t>
@@ -2684,28 +2684,28 @@
     <t xml:space="preserve">28.0722007751465</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4355926513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5264415740967</t>
+    <t xml:space="preserve">28.4355945587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5264434814453</t>
   </si>
   <si>
     <t xml:space="preserve">28.4810199737549</t>
   </si>
   <si>
-    <t xml:space="preserve">28.390172958374</t>
+    <t xml:space="preserve">28.3901710510254</t>
   </si>
   <si>
     <t xml:space="preserve">29.1623821258545</t>
   </si>
   <si>
-    <t xml:space="preserve">29.434928894043</t>
+    <t xml:space="preserve">29.4349308013916</t>
   </si>
   <si>
     <t xml:space="preserve">28.2538986206055</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1169586181641</t>
+    <t xml:space="preserve">29.1169567108154</t>
   </si>
   <si>
     <t xml:space="preserve">30.1162948608398</t>
@@ -2720,13 +2720,13 @@
     <t xml:space="preserve">31.479024887085</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5698699951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7969913482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7515678405762</t>
+    <t xml:space="preserve">31.5698680877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.796989440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7515659332275</t>
   </si>
   <si>
     <t xml:space="preserve">31.1156272888184</t>
@@ -2738,10 +2738,10 @@
     <t xml:space="preserve">34.6587219238281</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8410873413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4770278930664</t>
+    <t xml:space="preserve">33.8410835266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4770240783691</t>
   </si>
   <si>
     <t xml:space="preserve">34.386173248291</t>
@@ -2759,10 +2759,10 @@
     <t xml:space="preserve">34.4316024780273</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7048072814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9773597717285</t>
+    <t xml:space="preserve">33.7048110961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9773559570312</t>
   </si>
   <si>
     <t xml:space="preserve">34.931266784668</t>
@@ -2771,64 +2771,64 @@
     <t xml:space="preserve">34.5224456787109</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0682067871094</t>
+    <t xml:space="preserve">34.0682029724121</t>
   </si>
   <si>
     <t xml:space="preserve">33.7502365112305</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9319267272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2499008178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6139602661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2485694885254</t>
+    <t xml:space="preserve">33.9319305419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2499046325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6139640808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2485733032227</t>
   </si>
   <si>
     <t xml:space="preserve">36.6573867797852</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7936592102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6106300354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5645370483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.110969543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4302673339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3868408203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8871765136719</t>
+    <t xml:space="preserve">36.7936630249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6106338500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5645446777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1109657287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4302635192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3868370056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8871726989746</t>
   </si>
   <si>
     <t xml:space="preserve">33.0688743591309</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3414154052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8865089416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2044792175293</t>
+    <t xml:space="preserve">33.3414192199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8865051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2044830322266</t>
   </si>
   <si>
     <t xml:space="preserve">34.340747833252</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7508964538574</t>
+    <t xml:space="preserve">32.7509002685547</t>
   </si>
   <si>
     <t xml:space="preserve">32.6600532531738</t>
@@ -2837,7 +2837,7 @@
     <t xml:space="preserve">32.9780197143555</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7976589202881</t>
+    <t xml:space="preserve">30.7976551055908</t>
   </si>
   <si>
     <t xml:space="preserve">29.3895034790039</t>
@@ -2846,7 +2846,7 @@
     <t xml:space="preserve">29.5257778167725</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6172943115234</t>
+    <t xml:space="preserve">28.6172924041748</t>
   </si>
   <si>
     <t xml:space="preserve">28.344747543335</t>
@@ -2855,28 +2855,28 @@
     <t xml:space="preserve">30.0254440307617</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9332637786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.205810546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1149559020996</t>
+    <t xml:space="preserve">31.9332675933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2058067321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1149597167969</t>
   </si>
   <si>
     <t xml:space="preserve">32.2512359619141</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6152935028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.024112701416</t>
+    <t xml:space="preserve">31.615291595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0241088867188</t>
   </si>
   <si>
     <t xml:space="preserve">33.1142959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">32.614631652832</t>
+    <t xml:space="preserve">32.6146278381348</t>
   </si>
   <si>
     <t xml:space="preserve">31.2064743041992</t>
@@ -2888,10 +2888,10 @@
     <t xml:space="preserve">31.5244445800781</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3427467346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3420791625977</t>
+    <t xml:space="preserve">31.3427486419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3420829772949</t>
   </si>
   <si>
     <t xml:space="preserve">32.5237770080566</t>
@@ -2903,64 +2903,64 @@
     <t xml:space="preserve">32.1603889465332</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1590538024902</t>
+    <t xml:space="preserve">34.159049987793</t>
   </si>
   <si>
     <t xml:space="preserve">33.7956581115723</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9766883850098</t>
+    <t xml:space="preserve">34.976692199707</t>
   </si>
   <si>
     <t xml:space="preserve">32.9325981140137</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0234451293945</t>
+    <t xml:space="preserve">33.0234489440918</t>
   </si>
   <si>
     <t xml:space="preserve">33.5231170654297</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4783592224121</t>
+    <t xml:space="preserve">32.4783554077148</t>
   </si>
   <si>
     <t xml:space="preserve">32.4329299926758</t>
   </si>
   <si>
-    <t xml:space="preserve">31.842414855957</t>
+    <t xml:space="preserve">31.8424167633057</t>
   </si>
   <si>
     <t xml:space="preserve">31.8878402709961</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4342632293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7074756622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7068061828613</t>
+    <t xml:space="preserve">30.4342613220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7074737548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7068099975586</t>
   </si>
   <si>
     <t xml:space="preserve">30.4796886444092</t>
   </si>
   <si>
-    <t xml:space="preserve">29.616626739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8437461853027</t>
+    <t xml:space="preserve">29.6166248321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8437442779541</t>
   </si>
   <si>
     <t xml:space="preserve">29.2532329559326</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7535629272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0708675384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8898372650146</t>
+    <t xml:space="preserve">28.7535667419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0708694458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.889835357666</t>
   </si>
   <si>
     <t xml:space="preserve">28.6627159118652</t>
@@ -2975,16 +2975,16 @@
     <t xml:space="preserve">28.9806861877441</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7989902496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8891735076904</t>
+    <t xml:space="preserve">28.7989883422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8891754150391</t>
   </si>
   <si>
     <t xml:space="preserve">29.0715351104736</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2993221282959</t>
+    <t xml:space="preserve">28.2993202209473</t>
   </si>
   <si>
     <t xml:space="preserve">28.0267772674561</t>
@@ -3002,19 +3002,19 @@
     <t xml:space="preserve">28.5718688964844</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4816856384277</t>
+    <t xml:space="preserve">27.4816837310791</t>
   </si>
   <si>
     <t xml:space="preserve">27.5725345611572</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6186218261719</t>
+    <t xml:space="preserve">26.6186237335205</t>
   </si>
   <si>
     <t xml:space="preserve">27.1182918548584</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0274429321289</t>
+    <t xml:space="preserve">27.0274410247803</t>
   </si>
   <si>
     <t xml:space="preserve">26.9365921020508</t>
@@ -3023,13 +3023,13 @@
     <t xml:space="preserve">26.9820194244385</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3460788726807</t>
+    <t xml:space="preserve">26.346076965332</t>
   </si>
   <si>
     <t xml:space="preserve">25.8918361663818</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6647148132324</t>
+    <t xml:space="preserve">25.6647129058838</t>
   </si>
   <si>
     <t xml:space="preserve">26.2552280426025</t>
@@ -3038,10 +3038,10 @@
     <t xml:space="preserve">26.8457431793213</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6640491485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4369277954102</t>
+    <t xml:space="preserve">26.6640510559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4369258880615</t>
   </si>
   <si>
     <t xml:space="preserve">26.5732002258301</t>
@@ -3050,10 +3050,10 @@
     <t xml:space="preserve">26.3915023803711</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7094707489014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.527774810791</t>
+    <t xml:space="preserve">26.70947265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5277767181396</t>
   </si>
   <si>
     <t xml:space="preserve">25.9826850891113</t>
@@ -3062,10 +3062,10 @@
     <t xml:space="preserve">25.8009872436523</t>
   </si>
   <si>
-    <t xml:space="preserve">24.165714263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6660461425781</t>
+    <t xml:space="preserve">24.1657123565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6660442352295</t>
   </si>
   <si>
     <t xml:space="preserve">23.8477439880371</t>
@@ -3074,13 +3074,13 @@
     <t xml:space="preserve">25.437593460083</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7555637359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0741996765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0735340118408</t>
+    <t xml:space="preserve">25.7555618286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.074197769165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0735359191895</t>
   </si>
   <si>
     <t xml:space="preserve">27.6892356872559</t>
@@ -3089,7 +3089,7 @@
     <t xml:space="preserve">26.3419418334961</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6671504974365</t>
+    <t xml:space="preserve">26.6671524047852</t>
   </si>
   <si>
     <t xml:space="preserve">27.1317348480225</t>
@@ -3098,7 +3098,7 @@
     <t xml:space="preserve">27.6427764892578</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3396549224854</t>
+    <t xml:space="preserve">28.3396530151367</t>
   </si>
   <si>
     <t xml:space="preserve">27.8286113739014</t>
@@ -3152,7 +3152,7 @@
     <t xml:space="preserve">27.038818359375</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9458999633789</t>
+    <t xml:space="preserve">26.9459018707275</t>
   </si>
   <si>
     <t xml:space="preserve">26.760066986084</t>
@@ -3164,19 +3164,19 @@
     <t xml:space="preserve">26.2025661468506</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5742340087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4813175201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8994445800781</t>
+    <t xml:space="preserve">26.5742321014404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.481315612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8994426727295</t>
   </si>
   <si>
     <t xml:space="preserve">26.2490253448486</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7379817962646</t>
+    <t xml:space="preserve">25.7379837036133</t>
   </si>
   <si>
     <t xml:space="preserve">25.9238147735596</t>
@@ -3191,7 +3191,7 @@
     <t xml:space="preserve">27.271110534668</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2246494293213</t>
+    <t xml:space="preserve">27.2246513366699</t>
   </si>
   <si>
     <t xml:space="preserve">25.4127731323242</t>
@@ -3203,7 +3203,7 @@
     <t xml:space="preserve">24.5300617218018</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9017276763916</t>
+    <t xml:space="preserve">24.9017295837402</t>
   </si>
   <si>
     <t xml:space="preserve">25.0875625610352</t>
@@ -3212,76 +3212,76 @@
     <t xml:space="preserve">24.8088130950928</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5521488189697</t>
+    <t xml:space="preserve">25.5521469116211</t>
   </si>
   <si>
     <t xml:space="preserve">25.5056896209717</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7623519897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7158966064453</t>
+    <t xml:space="preserve">24.7623538970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7158946990967</t>
   </si>
   <si>
     <t xml:space="preserve">25.8308982849121</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0852756500244</t>
+    <t xml:space="preserve">27.085277557373</t>
   </si>
   <si>
     <t xml:space="preserve">26.7136077880859</t>
   </si>
   <si>
-    <t xml:space="preserve">26.016731262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8773555755615</t>
+    <t xml:space="preserve">26.0167331695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8773574829102</t>
   </si>
   <si>
     <t xml:space="preserve">25.7844390869141</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0631904602051</t>
+    <t xml:space="preserve">26.0631885528564</t>
   </si>
   <si>
     <t xml:space="preserve">26.1096496582031</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1340217590332</t>
+    <t xml:space="preserve">25.1340198516846</t>
   </si>
   <si>
     <t xml:space="preserve">25.0411052703857</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2977695465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4836025238037</t>
+    <t xml:space="preserve">24.2977676391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4836044311523</t>
   </si>
   <si>
     <t xml:space="preserve">24.0654773712158</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2513103485107</t>
+    <t xml:space="preserve">24.2513122558594</t>
   </si>
   <si>
     <t xml:space="preserve">24.5765209197998</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6008930206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0433902740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0898513793945</t>
+    <t xml:space="preserve">23.6008911132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0433921813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0898494720459</t>
   </si>
   <si>
     <t xml:space="preserve">22.114221572876</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0213069915771</t>
+    <t xml:space="preserve">22.0213050842285</t>
   </si>
   <si>
     <t xml:space="preserve">23.2756824493408</t>
@@ -3290,28 +3290,28 @@
     <t xml:space="preserve">23.4615173339844</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4150581359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1363067626953</t>
+    <t xml:space="preserve">23.415060043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1363086700439</t>
   </si>
   <si>
     <t xml:space="preserve">23.6473522186279</t>
   </si>
   <si>
-    <t xml:space="preserve">22.950475692749</t>
+    <t xml:space="preserve">22.9504737854004</t>
   </si>
   <si>
     <t xml:space="preserve">22.5788059234619</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2071380615234</t>
+    <t xml:space="preserve">22.2071399688721</t>
   </si>
   <si>
     <t xml:space="preserve">21.64963722229</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8598442077637</t>
+    <t xml:space="preserve">20.8598461151123</t>
   </si>
   <si>
     <t xml:space="preserve">21.0921363830566</t>
@@ -3326,7 +3326,7 @@
     <t xml:space="preserve">21.5567207336426</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7425556182861</t>
+    <t xml:space="preserve">21.7425537109375</t>
   </si>
   <si>
     <t xml:space="preserve">21.9283885955811</t>
@@ -3347,37 +3347,37 @@
     <t xml:space="preserve">21.4173450469971</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6031799316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8354721069336</t>
+    <t xml:space="preserve">21.603178024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.835470199585</t>
   </si>
   <si>
     <t xml:space="preserve">22.160680770874</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7181816101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3000545501709</t>
+    <t xml:space="preserve">22.7181835174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3000564575195</t>
   </si>
   <si>
     <t xml:space="preserve">22.3465137481689</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2535991668701</t>
+    <t xml:space="preserve">22.2535972595215</t>
   </si>
   <si>
     <t xml:space="preserve">21.881929397583</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7890129089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.182767868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5986042022705</t>
+    <t xml:space="preserve">21.7890148162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1827659606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5986061096191</t>
   </si>
   <si>
     <t xml:space="preserve">25.3663120269775</t>
@@ -3398,10 +3398,10 @@
     <t xml:space="preserve">24.4371433258057</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8796443939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2048530578613</t>
+    <t xml:space="preserve">23.8796424865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2048511505127</t>
   </si>
   <si>
     <t xml:space="preserve">23.9261016845703</t>
@@ -3410,7 +3410,7 @@
     <t xml:space="preserve">24.6694355010986</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5544338226318</t>
+    <t xml:space="preserve">23.5544357299805</t>
   </si>
   <si>
     <t xml:space="preserve">23.6938095092773</t>
@@ -3419,7 +3419,7 @@
     <t xml:space="preserve">23.3221416473389</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7867279052734</t>
+    <t xml:space="preserve">23.7867259979248</t>
   </si>
   <si>
     <t xml:space="preserve">22.8575572967529</t>
@@ -3428,7 +3428,7 @@
     <t xml:space="preserve">21.5102615356445</t>
   </si>
   <si>
-    <t xml:space="preserve">21.370885848999</t>
+    <t xml:space="preserve">21.3708877563477</t>
   </si>
   <si>
     <t xml:space="preserve">21.1850528717041</t>
@@ -3437,19 +3437,19 @@
     <t xml:space="preserve">20.7204685211182</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4881763458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9771347045898</t>
+    <t xml:space="preserve">20.4881744384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9771327972412</t>
   </si>
   <si>
     <t xml:space="preserve">20.2558822631836</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5346336364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9306755065918</t>
+    <t xml:space="preserve">20.5346355438232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9306774139404</t>
   </si>
   <si>
     <t xml:space="preserve">20.5810928344727</t>
@@ -3461,7 +3461,7 @@
     <t xml:space="preserve">20.6275520324707</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0235900878906</t>
+    <t xml:space="preserve">20.0235919952393</t>
   </si>
   <si>
     <t xml:space="preserve">18.6298370361328</t>
@@ -3479,7 +3479,7 @@
     <t xml:space="preserve">17.8772106170654</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5427093505859</t>
+    <t xml:space="preserve">17.5427112579346</t>
   </si>
   <si>
     <t xml:space="preserve">17.2453765869141</t>
@@ -3491,10 +3491,10 @@
     <t xml:space="preserve">17.5612926483154</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4126281738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.747127532959</t>
+    <t xml:space="preserve">17.4126262664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7471294403076</t>
   </si>
   <si>
     <t xml:space="preserve">17.1896266937256</t>
@@ -3515,13 +3515,13 @@
     <t xml:space="preserve">16.3162078857422</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9817085266113</t>
+    <t xml:space="preserve">15.981707572937</t>
   </si>
   <si>
     <t xml:space="preserve">16.5392074584961</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2976245880127</t>
+    <t xml:space="preserve">16.2976264953613</t>
   </si>
   <si>
     <t xml:space="preserve">16.1861248016357</t>
@@ -3533,7 +3533,7 @@
     <t xml:space="preserve">16.1489562988281</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2418746948242</t>
+    <t xml:space="preserve">16.2418727874756</t>
   </si>
   <si>
     <t xml:space="preserve">16.0746231079102</t>
@@ -69463,13 +69463,13 @@
     </row>
     <row r="2495">
       <c r="A2495" s="1" t="n">
-        <v>45952.6493287037</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B2495" t="n">
         <v>40852</v>
       </c>
       <c r="C2495" t="n">
-        <v>19.7000007629395</v>
+        <v>20.0499992370605</v>
       </c>
       <c r="D2495" t="n">
         <v>19.2000007629395</v>
@@ -69484,6 +69484,32 @@
         <v>1422</v>
       </c>
       <c r="H2495" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" s="1" t="n">
+        <v>45953.649537037</v>
+      </c>
+      <c r="B2496" t="n">
+        <v>49076</v>
+      </c>
+      <c r="C2496" t="n">
+        <v>20.7000007629395</v>
+      </c>
+      <c r="D2496" t="n">
+        <v>19.7800006866455</v>
+      </c>
+      <c r="E2496" t="n">
+        <v>19.8600006103516</v>
+      </c>
+      <c r="F2496" t="n">
+        <v>20.2000007629395</v>
+      </c>
+      <c r="G2496" t="s">
+        <v>1382</v>
+      </c>
+      <c r="H2496" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ARN.MI.xlsx
+++ b/data/ARN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1425" uniqueCount="1425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1426" uniqueCount="1426">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,115 +38,115 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9221498966217</t>
+    <t xml:space="preserve">1.92215001583099</t>
   </si>
   <si>
     <t xml:space="preserve">ARN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94450116157532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91736078262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90778243541718</t>
+    <t xml:space="preserve">1.94450056552887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91736042499542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90778207778931</t>
   </si>
   <si>
     <t xml:space="preserve">1.88383483886719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93172931671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91576457023621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83434414863586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83594083786011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91097509860992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80720388889313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74973130226135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71620559692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80401146411896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81039690971375</t>
+    <t xml:space="preserve">1.93172907829285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91576433181763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83434426784515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8359409570694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91097474098206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.807204246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74973118305206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71620535850525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80401134490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81039726734161</t>
   </si>
   <si>
     <t xml:space="preserve">1.79602909088135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77208173274994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70662665367126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69704759120941</t>
+    <t xml:space="preserve">1.7720822095871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70662677288055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6970477104187</t>
   </si>
   <si>
     <t xml:space="preserve">1.69066190719604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67629373073578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70024085044861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69864416122437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67469716072083</t>
+    <t xml:space="preserve">1.6762934923172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70024061203003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69864428043365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67469727993011</t>
   </si>
   <si>
     <t xml:space="preserve">1.66671514511108</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66032898426056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81518650054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8279584646225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86148452758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88543128967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8918172121048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92853581905365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95407927036285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90618538856506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8678697347641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88064157962799</t>
+    <t xml:space="preserve">1.66032910346985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8151867389679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82795798778534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86148428916931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88543152809143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89181697368622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92853569984436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95407962799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90618550777435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86787009239197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88064181804657</t>
   </si>
   <si>
     <t xml:space="preserve">1.85190546512604</t>
@@ -155,16 +155,16 @@
     <t xml:space="preserve">1.85988795757294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85509836673737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79283583164215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78804671764374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78006446361542</t>
+    <t xml:space="preserve">1.85509824752808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79283618927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78804647922516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78006422519684</t>
   </si>
   <si>
     <t xml:space="preserve">1.75611734390259</t>
@@ -173,97 +173,97 @@
     <t xml:space="preserve">1.7688889503479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76409947872162</t>
+    <t xml:space="preserve">1.76409983634949</t>
   </si>
   <si>
     <t xml:space="preserve">1.78485369682312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77048552036285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72099483013153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73536312580109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.802414894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76250302791595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74494183063507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73217022418976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73695957660675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74334561824799</t>
+    <t xml:space="preserve">1.77048528194427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72099506855011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7353630065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80241465568542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76250290870667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74494230747223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73217034339905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73695969581604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74334537982941</t>
   </si>
   <si>
     <t xml:space="preserve">1.75132787227631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68587255477905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67789030075073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65234661102295</t>
+    <t xml:space="preserve">1.68587267398834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67789041996002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65234649181366</t>
   </si>
   <si>
     <t xml:space="preserve">1.6204172372818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64276790618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5900844335556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60285604000092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54937434196472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51185739040375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45598089694977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43682301044464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4695508480072</t>
+    <t xml:space="preserve">1.64276778697968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59008431434631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60285592079163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54937422275543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51185727119446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45598077774048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43682312965393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46955072879791</t>
   </si>
   <si>
     <t xml:space="preserve">1.49748909473419</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47673487663269</t>
+    <t xml:space="preserve">1.4767347574234</t>
   </si>
   <si>
     <t xml:space="preserve">1.47274386882782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46875274181366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49669063091278</t>
+    <t xml:space="preserve">1.46875262260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49669075012207</t>
   </si>
   <si>
     <t xml:space="preserve">1.47593665122986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50626945495605</t>
+    <t xml:space="preserve">1.50626957416534</t>
   </si>
   <si>
     <t xml:space="preserve">1.47753310203552</t>
@@ -278,16 +278,16 @@
     <t xml:space="preserve">1.34901738166809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30910563468933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34342980384827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32666647434235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34103488922119</t>
+    <t xml:space="preserve">1.30910551548004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34342956542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32666671276093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34103500843048</t>
   </si>
   <si>
     <t xml:space="preserve">1.31708776950836</t>
@@ -299,37 +299,37 @@
     <t xml:space="preserve">1.39691150188446</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40649008750916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30671083927155</t>
+    <t xml:space="preserve">1.40649020671844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30671095848083</t>
   </si>
   <si>
     <t xml:space="preserve">1.32347357273102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30591261386871</t>
+    <t xml:space="preserve">1.305912733078</t>
   </si>
   <si>
     <t xml:space="preserve">1.31229853630066</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28994786739349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28515863418579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28595674037933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33305263519287</t>
+    <t xml:space="preserve">1.28994798660278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2851585149765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28595662117004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33305275440216</t>
   </si>
   <si>
     <t xml:space="preserve">1.33704376220703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30112338066101</t>
+    <t xml:space="preserve">1.30112314224243</t>
   </si>
   <si>
     <t xml:space="preserve">1.36104881763458</t>
@@ -338,43 +338,43 @@
     <t xml:space="preserve">1.34627270698547</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35283994674683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33806347846985</t>
+    <t xml:space="preserve">1.35283970832825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33806359767914</t>
   </si>
   <si>
     <t xml:space="preserve">1.27157092094421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28880989551544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29291415214539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30686938762665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33888459205627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34955620765686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34380996227264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33642208576202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34709358215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30522787570953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29127264022827</t>
+    <t xml:space="preserve">1.28880977630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29291439056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30686950683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33888447284698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34955632686615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34380984306335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33642184734344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34709370136261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30522775650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29127252101898</t>
   </si>
   <si>
     <t xml:space="preserve">1.31425750255585</t>
@@ -383,7 +383,7 @@
     <t xml:space="preserve">1.32164585590363</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26828742027283</t>
+    <t xml:space="preserve">1.26828753948212</t>
   </si>
   <si>
     <t xml:space="preserve">1.27239179611206</t>
@@ -392,22 +392,22 @@
     <t xml:space="preserve">1.28798890113831</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2970187664032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24858570098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32657098770142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33231723308563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35940682888031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4201534986496</t>
+    <t xml:space="preserve">1.29701900482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24858582019806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32657122612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33231735229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3594069480896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42015337944031</t>
   </si>
   <si>
     <t xml:space="preserve">1.48664617538452</t>
@@ -416,10 +416,10 @@
     <t xml:space="preserve">1.53343737125397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51619851589203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51866102218628</t>
+    <t xml:space="preserve">1.51619863510132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51866126060486</t>
   </si>
   <si>
     <t xml:space="preserve">1.43739247322083</t>
@@ -428,34 +428,34 @@
     <t xml:space="preserve">1.46776556968689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43000411987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40948188304901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44478023052216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5597060918808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61798977851868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70582616329193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74851262569427</t>
+    <t xml:space="preserve">1.43000423908234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40948176383972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44478034973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55970597267151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61799001693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70582604408264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74851274490356</t>
   </si>
   <si>
     <t xml:space="preserve">1.72388577461243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6828408241272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67463159561157</t>
+    <t xml:space="preserve">1.68284094333649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67463183403015</t>
   </si>
   <si>
     <t xml:space="preserve">1.65164661407471</t>
@@ -464,172 +464,172 @@
     <t xml:space="preserve">1.64179587364197</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67134833335876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6647812128067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65657198429108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69597506523132</t>
+    <t xml:space="preserve">1.67134821414948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66478109359741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6565717458725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69597494602203</t>
   </si>
   <si>
     <t xml:space="preserve">1.69433331489563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65821397304535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68119895458221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68776619434357</t>
+    <t xml:space="preserve">1.65821373462677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6811990737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68776631355286</t>
   </si>
   <si>
     <t xml:space="preserve">1.66806483268738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6500049829483</t>
+    <t xml:space="preserve">1.65000486373901</t>
   </si>
   <si>
     <t xml:space="preserve">1.66313922405243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67791533470154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03746843338013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04403567314148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03911018371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04075241088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05224466323853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04731965065002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04239392280579</t>
+    <t xml:space="preserve">1.67791545391083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03746891021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04403614997864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03911066055298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04075217247009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05224514007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0473198890686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04239416122437</t>
   </si>
   <si>
     <t xml:space="preserve">2.19836449623108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24105143547058</t>
+    <t xml:space="preserve">2.241051197052</t>
   </si>
   <si>
     <t xml:space="preserve">2.18851375579834</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17537975311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14582753181458</t>
+    <t xml:space="preserve">2.17537951469421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14582705497742</t>
   </si>
   <si>
     <t xml:space="preserve">2.00627470016479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98821461200714</t>
+    <t xml:space="preserve">1.98821473121643</t>
   </si>
   <si>
     <t xml:space="preserve">1.99313998222351</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99806547164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99642360210419</t>
+    <t xml:space="preserve">1.99806571006775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99642372131348</t>
   </si>
   <si>
     <t xml:space="preserve">1.99970769882202</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00299096107483</t>
+    <t xml:space="preserve">2.00299072265625</t>
   </si>
   <si>
     <t xml:space="preserve">2.00791645050049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01120018959045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02597618103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03254342079163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02105093002319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0194091796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.024334192276</t>
+    <t xml:space="preserve">2.01119995117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02597594261169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03254318237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02105069160461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01940894126892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02433443069458</t>
   </si>
   <si>
     <t xml:space="preserve">2.07687163352966</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05881190299988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09657335281372</t>
+    <t xml:space="preserve">2.05881214141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09657287597656</t>
   </si>
   <si>
     <t xml:space="preserve">2.14746904373169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33955883979797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27552914619446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32478284835815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27881264686584</t>
+    <t xml:space="preserve">2.33955931663513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27552938461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32478308677673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27881288528442</t>
   </si>
   <si>
     <t xml:space="preserve">2.25746941566467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29851412773132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26075291633606</t>
+    <t xml:space="preserve">2.29851388931274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26075315475464</t>
   </si>
   <si>
     <t xml:space="preserve">2.28045463562012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30672335624695</t>
+    <t xml:space="preserve">2.30672287940979</t>
   </si>
   <si>
     <t xml:space="preserve">2.35597705841064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34120059013367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34284257888794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34776782989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44627594947815</t>
+    <t xml:space="preserve">2.34120082855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3428430557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3477680683136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44627571105957</t>
   </si>
   <si>
     <t xml:space="preserve">2.39209675788879</t>
@@ -641,7 +641,7 @@
     <t xml:space="preserve">2.38717103004456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38388752937317</t>
+    <t xml:space="preserve">2.38388776779175</t>
   </si>
   <si>
     <t xml:space="preserve">2.40523099899292</t>
@@ -650,82 +650,82 @@
     <t xml:space="preserve">2.38060426712036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42164897918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33791756629944</t>
+    <t xml:space="preserve">2.42164921760559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33791732788086</t>
   </si>
   <si>
     <t xml:space="preserve">2.32314109802246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35433554649353</t>
+    <t xml:space="preserve">2.35433530807495</t>
   </si>
   <si>
     <t xml:space="preserve">2.41015648841858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40687227249146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43806672096252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4183657169342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29030537605286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34940981864929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36418557167053</t>
+    <t xml:space="preserve">2.40687251091003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4380669593811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41836500167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29030513763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34941005706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36418628692627</t>
   </si>
   <si>
     <t xml:space="preserve">2.37567901611328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40194749832153</t>
+    <t xml:space="preserve">2.40194725990295</t>
   </si>
   <si>
     <t xml:space="preserve">2.35761880874634</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36746954917908</t>
+    <t xml:space="preserve">2.36746978759766</t>
   </si>
   <si>
     <t xml:space="preserve">2.37075328826904</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37239480018616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36254405975342</t>
+    <t xml:space="preserve">2.37239551544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36254453659058</t>
   </si>
   <si>
     <t xml:space="preserve">2.36582803726196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39538025856018</t>
+    <t xml:space="preserve">2.3953800201416</t>
   </si>
   <si>
     <t xml:space="preserve">2.3773205280304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37403678894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38881325721741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39373850822449</t>
+    <t xml:space="preserve">2.37403702735901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38881301879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39373826980591</t>
   </si>
   <si>
     <t xml:space="preserve">2.3904550075531</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41343998908997</t>
+    <t xml:space="preserve">2.41343975067139</t>
   </si>
   <si>
     <t xml:space="preserve">2.40358901023865</t>
@@ -734,7 +734,7 @@
     <t xml:space="preserve">2.40030550956726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40851449966431</t>
+    <t xml:space="preserve">2.40851426124573</t>
   </si>
   <si>
     <t xml:space="preserve">2.42329072952271</t>
@@ -743,40 +743,40 @@
     <t xml:space="preserve">2.43149948120117</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42000699043274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35105204582214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33627581596375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34612655639648</t>
+    <t xml:space="preserve">2.4200074672699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35105180740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33627557754517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34612631797791</t>
   </si>
   <si>
     <t xml:space="preserve">2.43642520904541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42657470703125</t>
+    <t xml:space="preserve">2.42657423019409</t>
   </si>
   <si>
     <t xml:space="preserve">2.42985796928406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45284271240234</t>
+    <t xml:space="preserve">2.4528431892395</t>
   </si>
   <si>
     <t xml:space="preserve">2.4770131111145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47868013381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49201512336731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49368238449097</t>
+    <t xml:space="preserve">2.47867965698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49201536178589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49368190765381</t>
   </si>
   <si>
     <t xml:space="preserve">2.47534608840942</t>
@@ -785,40 +785,40 @@
     <t xml:space="preserve">2.46534466743469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48201370239258</t>
+    <t xml:space="preserve">2.48201394081116</t>
   </si>
   <si>
     <t xml:space="preserve">2.46867847442627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45867729187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46201133728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45534372329712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41700506210327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40866994857788</t>
+    <t xml:space="preserve">2.45867705345154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46201086044312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45534324645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41700482368469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40867042541504</t>
   </si>
   <si>
     <t xml:space="preserve">2.36699771881104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34199404716492</t>
+    <t xml:space="preserve">2.3419942855835</t>
   </si>
   <si>
     <t xml:space="preserve">2.36866474151611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35366225242615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38533353805542</t>
+    <t xml:space="preserve">2.35366249084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.385333776474</t>
   </si>
   <si>
     <t xml:space="preserve">2.38366651535034</t>
@@ -827,34 +827,34 @@
     <t xml:space="preserve">2.36366391181946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32532548904419</t>
+    <t xml:space="preserve">2.32532525062561</t>
   </si>
   <si>
     <t xml:space="preserve">2.31699061393738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28531956672668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28698635101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29698801040649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31532382965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28365254402161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28865313529968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29032039642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30198907852173</t>
+    <t xml:space="preserve">2.28531932830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28698658943176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29698777198792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3153235912323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28365278244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28865361213684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29032015800476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30198884010315</t>
   </si>
   <si>
     <t xml:space="preserve">2.30365562438965</t>
@@ -863,7 +863,7 @@
     <t xml:space="preserve">2.29365420341492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24198031425476</t>
+    <t xml:space="preserve">2.24198007583618</t>
   </si>
   <si>
     <t xml:space="preserve">2.26698350906372</t>
@@ -878,34 +878,34 @@
     <t xml:space="preserve">2.31865739822388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3103232383728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24364733695984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25031495094299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22531151771545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25198173522949</t>
+    <t xml:space="preserve">2.31032347679138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24364709854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25031447410583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22531127929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25198149681091</t>
   </si>
   <si>
     <t xml:space="preserve">2.22197723388672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20697522163391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20030760765076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16863679885864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17863845825195</t>
+    <t xml:space="preserve">2.20697546005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20030784606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16863656044006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17863798141479</t>
   </si>
   <si>
     <t xml:space="preserve">2.16696977615356</t>
@@ -917,16 +917,16 @@
     <t xml:space="preserve">2.19697380065918</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18363857269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18530583381653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1919732093811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17530417442322</t>
+    <t xml:space="preserve">2.18363881111145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18530559539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19197368621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17530393600464</t>
   </si>
   <si>
     <t xml:space="preserve">2.14196634292603</t>
@@ -935,43 +935,43 @@
     <t xml:space="preserve">2.15363478660583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14363312721252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13529849052429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12696433067322</t>
+    <t xml:space="preserve">2.1436333656311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13529872894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12696409225464</t>
   </si>
   <si>
     <t xml:space="preserve">2.12863111495972</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12029671669006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13029766082764</t>
+    <t xml:space="preserve">2.12029647827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13029789924622</t>
   </si>
   <si>
     <t xml:space="preserve">2.11862993240356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37366557121277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37533187866211</t>
+    <t xml:space="preserve">2.37366533279419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37533235549927</t>
   </si>
   <si>
     <t xml:space="preserve">2.40700340270996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39533495903015</t>
+    <t xml:space="preserve">2.39533519744873</t>
   </si>
   <si>
     <t xml:space="preserve">2.39200115203857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49868297576904</t>
+    <t xml:space="preserve">2.49868249893188</t>
   </si>
   <si>
     <t xml:space="preserve">2.49534893035889</t>
@@ -980,13 +980,13 @@
     <t xml:space="preserve">2.5086841583252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51201796531677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51535153388977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51701855659485</t>
+    <t xml:space="preserve">2.51201772689819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51535201072693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51701879501343</t>
   </si>
   <si>
     <t xml:space="preserve">2.523686170578</t>
@@ -1001,10 +1001,10 @@
     <t xml:space="preserve">2.53368759155273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53202080726624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54035544395447</t>
+    <t xml:space="preserve">2.53202056884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54035568237305</t>
   </si>
   <si>
     <t xml:space="preserve">2.52702021598816</t>
@@ -1016,28 +1016,28 @@
     <t xml:space="preserve">2.53702139854431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49701571464539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42700624465942</t>
+    <t xml:space="preserve">2.49701595306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42700600624084</t>
   </si>
   <si>
     <t xml:space="preserve">2.50034976005554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50535035133362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48368096351624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45200943946838</t>
+    <t xml:space="preserve">2.5053505897522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48368048667908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45200967788696</t>
   </si>
   <si>
     <t xml:space="preserve">2.51368474960327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54202222824097</t>
+    <t xml:space="preserve">2.54202175140381</t>
   </si>
   <si>
     <t xml:space="preserve">2.5486900806427</t>
@@ -1046,16 +1046,16 @@
     <t xml:space="preserve">2.51035118103027</t>
   </si>
   <si>
-    <t xml:space="preserve">2.520352602005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47201251983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50201678276062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48701453208923</t>
+    <t xml:space="preserve">2.52035212516785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47201228141785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50201654434204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48701477050781</t>
   </si>
   <si>
     <t xml:space="preserve">3.00041961669922</t>
@@ -1064,13 +1064,13 @@
     <t xml:space="preserve">2.81706047058105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75038433074951</t>
+    <t xml:space="preserve">2.75038456916809</t>
   </si>
   <si>
     <t xml:space="preserve">2.71704649925232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8087260723114</t>
+    <t xml:space="preserve">2.80872631072998</t>
   </si>
   <si>
     <t xml:space="preserve">2.80039167404175</t>
@@ -1079,118 +1079,118 @@
     <t xml:space="preserve">2.83372974395752</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78372240066528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84206438064575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75871920585632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85039901733398</t>
+    <t xml:space="preserve">2.78372263908386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84206461906433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75871872901917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85039877891541</t>
   </si>
   <si>
     <t xml:space="preserve">2.85873341560364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89207124710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82539510726929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72538089752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61703276634216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64203667640686</t>
+    <t xml:space="preserve">2.89207148551941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82539534568787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72538113594055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61703300476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6420361995697</t>
   </si>
   <si>
     <t xml:space="preserve">2.70037746429443</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65870523452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62536716461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63370180130005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59202909469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66703987121582</t>
+    <t xml:space="preserve">2.65870547294617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6253674030304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63370203971863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59202933311462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66703963279724</t>
   </si>
   <si>
     <t xml:space="preserve">2.70871210098267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74205017089844</t>
+    <t xml:space="preserve">2.74204993247986</t>
   </si>
   <si>
     <t xml:space="preserve">2.65037083625793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68370890617371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60036373138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58369469642639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56702542304993</t>
+    <t xml:space="preserve">2.68370842933655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6003634929657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58369493484497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56702566146851</t>
   </si>
   <si>
     <t xml:space="preserve">2.76705384254456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73371577262878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79205703735352</t>
+    <t xml:space="preserve">2.73371601104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79205727577209</t>
   </si>
   <si>
     <t xml:space="preserve">2.86706781387329</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87540197372437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8837366104126</t>
+    <t xml:space="preserve">2.87540245056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88373684883118</t>
   </si>
   <si>
     <t xml:space="preserve">2.77538824081421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78091382980347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72174572944641</t>
+    <t xml:space="preserve">2.78091359138489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72174549102783</t>
   </si>
   <si>
     <t xml:space="preserve">2.73019814491272</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77246117591858</t>
+    <t xml:space="preserve">2.77246141433716</t>
   </si>
   <si>
     <t xml:space="preserve">2.64567184448242</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70484066009521</t>
+    <t xml:space="preserve">2.70484018325806</t>
   </si>
   <si>
     <t xml:space="preserve">2.68793511390686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66257691383362</t>
+    <t xml:space="preserve">2.66257739067078</t>
   </si>
   <si>
     <t xml:space="preserve">2.69638776779175</t>
@@ -1199,22 +1199,22 @@
     <t xml:space="preserve">2.65412473678589</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60340857505798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63721942901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61186122894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5780508518219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59495639801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50197720527649</t>
+    <t xml:space="preserve">2.60340881347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63721919059753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61186146736145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57805061340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59495615959167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50197744369507</t>
   </si>
   <si>
     <t xml:space="preserve">2.49352478981018</t>
@@ -1226,28 +1226,28 @@
     <t xml:space="preserve">2.56114554405212</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58650374412537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51888251304626</t>
+    <t xml:space="preserve">2.58650350570679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51888227462769</t>
   </si>
   <si>
     <t xml:space="preserve">2.53578782081604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55269265174866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51042985916138</t>
+    <t xml:space="preserve">2.55269312858582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5104296207428</t>
   </si>
   <si>
     <t xml:space="preserve">2.56959819793701</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4681670665741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48507189750671</t>
+    <t xml:space="preserve">2.46816682815552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48507213592529</t>
   </si>
   <si>
     <t xml:space="preserve">2.41745066642761</t>
@@ -1256,52 +1256,52 @@
     <t xml:space="preserve">2.45126152038574</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39209270477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3836407661438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27375650405884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29911398887634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36673521995544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35828280448914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43435597419739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42590355873108</t>
+    <t xml:space="preserve">2.39209318161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38364028930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27375626564026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29911375045776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36673498153687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35828232765198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43435621261597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4259033203125</t>
   </si>
   <si>
     <t xml:space="preserve">2.34982967376709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28220915794373</t>
+    <t xml:space="preserve">2.28220868110657</t>
   </si>
   <si>
     <t xml:space="preserve">2.32447218894958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40899801254272</t>
+    <t xml:space="preserve">2.4089982509613</t>
   </si>
   <si>
     <t xml:space="preserve">2.45971417427063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44280862808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33292508125305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34137725830078</t>
+    <t xml:space="preserve">2.44280886650085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33292484283447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3413770198822</t>
   </si>
   <si>
     <t xml:space="preserve">2.40054559707642</t>
@@ -1310,16 +1310,16 @@
     <t xml:space="preserve">2.37518787384033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47661948204041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30756688117981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23994588851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29430246353149</t>
+    <t xml:space="preserve">2.47661924362183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30756664276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23994565010071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29430222511292</t>
   </si>
   <si>
     <t xml:space="preserve">2.23437643051147</t>
@@ -1337,31 +1337,31 @@
     <t xml:space="preserve">2.27718067169189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26862001419067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.448397397995</t>
+    <t xml:space="preserve">2.26861953735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44839692115784</t>
   </si>
   <si>
     <t xml:space="preserve">2.37134957313538</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31142401695251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28574132919312</t>
+    <t xml:space="preserve">2.31142377853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28574156761169</t>
   </si>
   <si>
     <t xml:space="preserve">2.26005911827087</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35422801971436</t>
+    <t xml:space="preserve">2.35422825813293</t>
   </si>
   <si>
     <t xml:space="preserve">2.22581553459167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20869421958923</t>
+    <t xml:space="preserve">2.20869398117065</t>
   </si>
   <si>
     <t xml:space="preserve">2.30286312103271</t>
@@ -1373,37 +1373,37 @@
     <t xml:space="preserve">2.37991046905518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.405592918396</t>
+    <t xml:space="preserve">2.40559315681458</t>
   </si>
   <si>
     <t xml:space="preserve">2.3970320224762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32854580879211</t>
+    <t xml:space="preserve">2.32854533195496</t>
   </si>
   <si>
     <t xml:space="preserve">2.38847136497498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36278891563416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34566712379456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20013332366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18301153182983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43983626365662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54256629943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60249185562134</t>
+    <t xml:space="preserve">2.36278915405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34566736221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20013308525085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18301177024841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4398365020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5425660610199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60249209403992</t>
   </si>
   <si>
     <t xml:space="preserve">2.69666147232056</t>
@@ -1412,7 +1412,7 @@
     <t xml:space="preserve">2.77370858192444</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63673520088196</t>
+    <t xml:space="preserve">2.63673567771912</t>
   </si>
   <si>
     <t xml:space="preserve">2.67097854614258</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">2.61961364746094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65385699272156</t>
+    <t xml:space="preserve">2.65385723114014</t>
   </si>
   <si>
     <t xml:space="preserve">2.68810057640076</t>
@@ -1430,25 +1430,25 @@
     <t xml:space="preserve">2.64529633522034</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71378302574158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7223436832428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07333779335022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52706146240234</t>
+    <t xml:space="preserve">2.713782787323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72234392166138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07333755493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52706170082092</t>
   </si>
   <si>
     <t xml:space="preserve">3.59554839134216</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65547442436218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58698797225952</t>
+    <t xml:space="preserve">3.65547394752502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58698773384094</t>
   </si>
   <si>
     <t xml:space="preserve">3.6126697063446</t>
@@ -1469,25 +1469,25 @@
     <t xml:space="preserve">3.55274438858032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56130504608154</t>
+    <t xml:space="preserve">3.56130480766296</t>
   </si>
   <si>
     <t xml:space="preserve">3.5099401473999</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48425793647766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57842659950256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.638352394104</t>
+    <t xml:space="preserve">3.4842574596405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57842683792114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63835263252258</t>
   </si>
   <si>
     <t xml:space="preserve">3.74108219146729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16912364959717</t>
+    <t xml:space="preserve">4.16912412643433</t>
   </si>
   <si>
     <t xml:space="preserve">4.60572624206543</t>
@@ -1496,7 +1496,7 @@
     <t xml:space="preserve">5.15361928939819</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62284803390503</t>
+    <t xml:space="preserve">4.62284755706787</t>
   </si>
   <si>
     <t xml:space="preserve">4.19480609893799</t>
@@ -1505,22 +1505,22 @@
     <t xml:space="preserve">4.45163106918335</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53724002838135</t>
+    <t xml:space="preserve">4.53723907470703</t>
   </si>
   <si>
     <t xml:space="preserve">4.52011823654175</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58860492706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34890174865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16056394577026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23761081695557</t>
+    <t xml:space="preserve">4.58860445022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34890127182007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16056346893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23761034011841</t>
   </si>
   <si>
     <t xml:space="preserve">4.29753637313843</t>
@@ -1529,52 +1529,52 @@
     <t xml:space="preserve">3.89517784118652</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27879738807678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25311517715454</t>
+    <t xml:space="preserve">3.27879762649536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25311493873596</t>
   </si>
   <si>
     <t xml:space="preserve">2.89356017112732</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15894603729248</t>
+    <t xml:space="preserve">3.15894627571106</t>
   </si>
   <si>
     <t xml:space="preserve">3.16750693321228</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03909468650818</t>
+    <t xml:space="preserve">3.03909420967102</t>
   </si>
   <si>
     <t xml:space="preserve">3.44145369529724</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38152766227722</t>
+    <t xml:space="preserve">3.3815279006958</t>
   </si>
   <si>
     <t xml:space="preserve">3.3900887966156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84381222724915</t>
+    <t xml:space="preserve">3.84381246566772</t>
   </si>
   <si>
     <t xml:space="preserve">3.83525156974792</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8780562877655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76676511764526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88661670684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85237312316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92942094802856</t>
+    <t xml:space="preserve">3.87805604934692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76676464080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88661646842957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85237336158752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92942070960999</t>
   </si>
   <si>
     <t xml:space="preserve">3.95510292053223</t>
@@ -1583,19 +1583,19 @@
     <t xml:space="preserve">3.93798184394836</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11775970458984</t>
+    <t xml:space="preserve">4.11775922775269</t>
   </si>
   <si>
     <t xml:space="preserve">4.25473213195801</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22904968261719</t>
+    <t xml:space="preserve">4.22905015945435</t>
   </si>
   <si>
     <t xml:space="preserve">4.26329326629639</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28041458129883</t>
+    <t xml:space="preserve">4.28041505813599</t>
   </si>
   <si>
     <t xml:space="preserve">4.43450975418091</t>
@@ -1604,13 +1604,13 @@
     <t xml:space="preserve">4.20336723327637</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00646781921387</t>
+    <t xml:space="preserve">4.00646877288818</t>
   </si>
   <si>
     <t xml:space="preserve">4.10919809341431</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15200281143188</t>
+    <t xml:space="preserve">4.15200233459473</t>
   </si>
   <si>
     <t xml:space="preserve">4.08351612091064</t>
@@ -1619,7 +1619,7 @@
     <t xml:space="preserve">3.94654202461243</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07495450973511</t>
+    <t xml:space="preserve">4.07495498657227</t>
   </si>
   <si>
     <t xml:space="preserve">4.02358961105347</t>
@@ -1637,40 +1637,40 @@
     <t xml:space="preserve">5.01664590835571</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70845603942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91391563415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96528100967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94815921783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20498371124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56453943252563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68439102172852</t>
+    <t xml:space="preserve">4.70845651626587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91391611099243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96528148651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94815969467163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20498418807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56453895568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68439054489136</t>
   </si>
   <si>
     <t xml:space="preserve">5.95833730697632</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90697240829468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88985013961792</t>
+    <t xml:space="preserve">5.90697288513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88985109329224</t>
   </si>
   <si>
     <t xml:space="preserve">6.57471656799316</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12955379486084</t>
+    <t xml:space="preserve">6.12955331802368</t>
   </si>
   <si>
     <t xml:space="preserve">6.4035005569458</t>
@@ -1682,10 +1682,10 @@
     <t xml:space="preserve">7.20821857452393</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32807016372681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05412292480469</t>
+    <t xml:space="preserve">7.32807064056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05412340164185</t>
   </si>
   <si>
     <t xml:space="preserve">7.00275897979736</t>
@@ -1694,25 +1694,25 @@
     <t xml:space="preserve">7.42397689819336</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28357124328613</t>
+    <t xml:space="preserve">7.28357076644897</t>
   </si>
   <si>
     <t xml:space="preserve">6.8799033164978</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9676570892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59909105300903</t>
+    <t xml:space="preserve">6.96765661239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59909057617188</t>
   </si>
   <si>
     <t xml:space="preserve">6.51133680343628</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7394962310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84480142593384</t>
+    <t xml:space="preserve">6.73949670791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.844801902771</t>
   </si>
   <si>
     <t xml:space="preserve">6.82725143432617</t>
@@ -1721,28 +1721,28 @@
     <t xml:space="preserve">6.68684482574463</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66929340362549</t>
+    <t xml:space="preserve">6.66929388046265</t>
   </si>
   <si>
     <t xml:space="preserve">6.45868492126465</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40603256225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31827878952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80970048904419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17826652526855</t>
+    <t xml:space="preserve">6.4060320854187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31827831268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80970096588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17826700210571</t>
   </si>
   <si>
     <t xml:space="preserve">7.3537745475769</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26602029800415</t>
+    <t xml:space="preserve">7.26601982116699</t>
   </si>
   <si>
     <t xml:space="preserve">7.05541133880615</t>
@@ -1751,76 +1751,76 @@
     <t xml:space="preserve">7.07296228408813</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63419198989868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44113397598267</t>
+    <t xml:space="preserve">6.63419246673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44113349914551</t>
   </si>
   <si>
     <t xml:space="preserve">6.30072736740112</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05501651763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03746557235718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37053680419922</t>
+    <t xml:space="preserve">6.05501699447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03746604919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37053632736206</t>
   </si>
   <si>
     <t xml:space="preserve">5.40563821792603</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52849388122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65134954452515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12521982192993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96726274490356</t>
+    <t xml:space="preserve">5.52849340438843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65134906768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12522029876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96726322174072</t>
   </si>
   <si>
     <t xml:space="preserve">6.01991558074951</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91460990905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.844407081604</t>
+    <t xml:space="preserve">5.91461086273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84440755844116</t>
   </si>
   <si>
     <t xml:space="preserve">5.94971227645874</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86195802688599</t>
+    <t xml:space="preserve">5.86195850372314</t>
   </si>
   <si>
     <t xml:space="preserve">5.82685661315918</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93216133117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87950944900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79175519943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68645048141479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45829010009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63379859924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70400142669678</t>
+    <t xml:space="preserve">5.93216180801392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87950897216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79175567626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68645000457764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45829057693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63379812240601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70400094985962</t>
   </si>
   <si>
     <t xml:space="preserve">5.58114624023438</t>
@@ -1835,55 +1835,55 @@
     <t xml:space="preserve">5.61624717712402</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49339246749878</t>
+    <t xml:space="preserve">5.49339199066162</t>
   </si>
   <si>
     <t xml:space="preserve">5.31788444519043</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17747783660889</t>
+    <t xml:space="preserve">5.17747831344604</t>
   </si>
   <si>
     <t xml:space="preserve">5.26523208618164</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28278255462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35298585891724</t>
+    <t xml:space="preserve">5.28278303146362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35298538208008</t>
   </si>
   <si>
     <t xml:space="preserve">5.42318916320801</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47584104537964</t>
+    <t xml:space="preserve">5.47584056854248</t>
   </si>
   <si>
     <t xml:space="preserve">5.3880877494812</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51094341278076</t>
+    <t xml:space="preserve">5.5109429359436</t>
   </si>
   <si>
     <t xml:space="preserve">5.77420473098755</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44074058532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54604482650757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23052453994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35337972640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1603217124939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37093114852905</t>
+    <t xml:space="preserve">5.44074010848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54604434967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23052406311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35338020324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16032123565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37093067169189</t>
   </si>
   <si>
     <t xml:space="preserve">6.47623586654663</t>
@@ -1892,7 +1892,7 @@
     <t xml:space="preserve">6.42358303070068</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54643869400024</t>
+    <t xml:space="preserve">6.54643821716309</t>
   </si>
   <si>
     <t xml:space="preserve">6.98520803451538</t>
@@ -1907,25 +1907,25 @@
     <t xml:space="preserve">7.16071557998657</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19581747055054</t>
+    <t xml:space="preserve">7.19581699371338</t>
   </si>
   <si>
     <t xml:space="preserve">7.00275850296021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95010614395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14316558837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12561416625977</t>
+    <t xml:space="preserve">6.95010662078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14316463470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12561368942261</t>
   </si>
   <si>
     <t xml:space="preserve">7.02030944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84519577026367</t>
+    <t xml:space="preserve">7.8451943397522</t>
   </si>
   <si>
     <t xml:space="preserve">8.3366174697876</t>
@@ -1937,7 +1937,7 @@
     <t xml:space="preserve">8.42437171936035</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08252620697021</t>
+    <t xml:space="preserve">9.0825252532959</t>
   </si>
   <si>
     <t xml:space="preserve">8.68763160705566</t>
@@ -1946,13 +1946,13 @@
     <t xml:space="preserve">9.03864860534668</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30191040039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2763710021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1630802154541</t>
+    <t xml:space="preserve">9.30190944671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2763719558716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1630792617798</t>
   </si>
   <si>
     <t xml:space="preserve">13.0753259658813</t>
@@ -1961,79 +1961,79 @@
     <t xml:space="preserve">13.1192026138306</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8559408187866</t>
+    <t xml:space="preserve">12.8559417724609</t>
   </si>
   <si>
     <t xml:space="preserve">12.0222797393799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1100330352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9345254898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.36412525177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8814811706543</t>
+    <t xml:space="preserve">12.1100339889526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9345264434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3641262054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.88148021698</t>
   </si>
   <si>
     <t xml:space="preserve">12.1539115905762</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6712636947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.715142250061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4518804550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0569877624512</t>
+    <t xml:space="preserve">11.6712656021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7151412963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4518795013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0569868087769</t>
   </si>
   <si>
     <t xml:space="preserve">11.4957571029663</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4080028533936</t>
+    <t xml:space="preserve">11.4080018997192</t>
   </si>
   <si>
     <t xml:space="preserve">11.8906497955322</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8028955459595</t>
+    <t xml:space="preserve">11.8028945922852</t>
   </si>
   <si>
     <t xml:space="preserve">11.3202495574951</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6273880004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1447410583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6182174682617</t>
+    <t xml:space="preserve">11.627387046814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1447401046753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.618218421936</t>
   </si>
   <si>
     <t xml:space="preserve">10.5304641723633</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5743417739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7498483657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6620941162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3549556732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78455543518066</t>
+    <t xml:space="preserve">10.5743408203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.749849319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6620950698853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3549566268921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78455638885498</t>
   </si>
   <si>
     <t xml:space="preserve">9.91618728637695</t>
@@ -2045,25 +2045,25 @@
     <t xml:space="preserve">11.232494354248</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1886177062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1008634567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3553495407104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2675971984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0218868255615</t>
+    <t xml:space="preserve">11.1886186599731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1008644104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3553504943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.267596244812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0218858718872</t>
   </si>
   <si>
     <t xml:space="preserve">11.2500457763672</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3729009628296</t>
+    <t xml:space="preserve">11.3729000091553</t>
   </si>
   <si>
     <t xml:space="preserve">11.2851467132568</t>
@@ -2075,13 +2075,13 @@
     <t xml:space="preserve">11.8467712402344</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9871778488159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2855415344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2504396438599</t>
+    <t xml:space="preserve">11.9871768951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2855424880981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2504405975342</t>
   </si>
   <si>
     <t xml:space="preserve">12.1626853942871</t>
@@ -2093,34 +2093,34 @@
     <t xml:space="preserve">12.0372982025146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0910358428955</t>
+    <t xml:space="preserve">12.0910348892212</t>
   </si>
   <si>
     <t xml:space="preserve">11.553656578064</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6432199478149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3924417495728</t>
+    <t xml:space="preserve">11.6432189941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3924427032471</t>
   </si>
   <si>
     <t xml:space="preserve">10.9446268081665</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5505485534668</t>
+    <t xml:space="preserve">10.5505475997925</t>
   </si>
   <si>
     <t xml:space="preserve">10.6759366989136</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9088010787964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7117614746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6580238342285</t>
+    <t xml:space="preserve">10.9088020324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7117624282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6580228805542</t>
   </si>
   <si>
     <t xml:space="preserve">10.9267129898071</t>
@@ -2129,22 +2129,22 @@
     <t xml:space="preserve">11.0521030426025</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4999189376831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4820051193237</t>
+    <t xml:space="preserve">11.4999179840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.482006072998</t>
   </si>
   <si>
     <t xml:space="preserve">11.4282674789429</t>
   </si>
   <si>
-    <t xml:space="preserve">11.571569442749</t>
+    <t xml:space="preserve">11.5715684890747</t>
   </si>
   <si>
     <t xml:space="preserve">11.3745288848877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3566179275513</t>
+    <t xml:space="preserve">11.356616973877</t>
   </si>
   <si>
     <t xml:space="preserve">11.3207921981812</t>
@@ -2153,16 +2153,16 @@
     <t xml:space="preserve">11.4461803436279</t>
   </si>
   <si>
-    <t xml:space="preserve">11.464093208313</t>
+    <t xml:space="preserve">11.4640922546387</t>
   </si>
   <si>
     <t xml:space="preserve">11.7148694992065</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7327823638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.750696182251</t>
+    <t xml:space="preserve">11.7327833175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7506952285767</t>
   </si>
   <si>
     <t xml:space="preserve">12.1805992126465</t>
@@ -2171,16 +2171,16 @@
     <t xml:space="preserve">12.6284151077271</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0731220245361</t>
+    <t xml:space="preserve">12.0731229782104</t>
   </si>
   <si>
     <t xml:space="preserve">12.3418121337891</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3597249984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6969585418701</t>
+    <t xml:space="preserve">12.3597259521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6969575881958</t>
   </si>
   <si>
     <t xml:space="preserve">12.1268606185913</t>
@@ -2189,7 +2189,7 @@
     <t xml:space="preserve">12.0552110671997</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8581714630127</t>
+    <t xml:space="preserve">11.8581705093384</t>
   </si>
   <si>
     <t xml:space="preserve">11.9298219680786</t>
@@ -2204,19 +2204,19 @@
     <t xml:space="preserve">12.5030269622803</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9835605621338</t>
+    <t xml:space="preserve">11.9835596084595</t>
   </si>
   <si>
     <t xml:space="preserve">12.3239002227783</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9804515838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.177490234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2849674224854</t>
+    <t xml:space="preserve">10.9804525375366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1774892807007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.284966468811</t>
   </si>
   <si>
     <t xml:space="preserve">11.3387050628662</t>
@@ -2225,7 +2225,7 @@
     <t xml:space="preserve">11.8939962387085</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7686080932617</t>
+    <t xml:space="preserve">11.768609046936</t>
   </si>
   <si>
     <t xml:space="preserve">11.6253061294556</t>
@@ -2234,49 +2234,49 @@
     <t xml:space="preserve">12.0014724731445</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1089477539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9656457901001</t>
+    <t xml:space="preserve">12.1089487075806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9656476974487</t>
   </si>
   <si>
     <t xml:space="preserve">12.1985120773315</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4313764572144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2522497177124</t>
+    <t xml:space="preserve">12.43137550354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2522506713867</t>
   </si>
   <si>
     <t xml:space="preserve">12.8612785339355</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8433675765991</t>
+    <t xml:space="preserve">12.8433666229248</t>
   </si>
   <si>
     <t xml:space="preserve">12.6821527481079</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7358913421631</t>
+    <t xml:space="preserve">12.7358922958374</t>
   </si>
   <si>
     <t xml:space="preserve">13.3449201583862</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2405529022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0972528457642</t>
+    <t xml:space="preserve">14.2405519485474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0972509384155</t>
   </si>
   <si>
     <t xml:space="preserve">14.3301162719727</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4734163284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5988054275513</t>
+    <t xml:space="preserve">14.4734172821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5988063812256</t>
   </si>
   <si>
     <t xml:space="preserve">13.8823003768921</t>
@@ -2285,37 +2285,37 @@
     <t xml:space="preserve">13.864387512207</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5777854919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4703102111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6852607727051</t>
+    <t xml:space="preserve">13.577784538269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4703092575073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6852617263794</t>
   </si>
   <si>
     <t xml:space="preserve">13.6673488616943</t>
   </si>
   <si>
-    <t xml:space="preserve">13.559871673584</t>
+    <t xml:space="preserve">13.5598726272583</t>
   </si>
   <si>
     <t xml:space="preserve">13.6136102676392</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8285617828369</t>
+    <t xml:space="preserve">13.8285627365112</t>
   </si>
   <si>
     <t xml:space="preserve">13.953950881958</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344844818115</t>
+    <t xml:space="preserve">13.4344835281372</t>
   </si>
   <si>
     <t xml:space="preserve">13.7210865020752</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5240478515625</t>
+    <t xml:space="preserve">13.5240468978882</t>
   </si>
   <si>
     <t xml:space="preserve">13.7031745910645</t>
@@ -2327,7 +2327,7 @@
     <t xml:space="preserve">13.4523973464966</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3090944290161</t>
+    <t xml:space="preserve">13.3090953826904</t>
   </si>
   <si>
     <t xml:space="preserve">14.2763776779175</t>
@@ -2336,16 +2336,16 @@
     <t xml:space="preserve">14.4196796417236</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0256004333496</t>
+    <t xml:space="preserve">14.0256013870239</t>
   </si>
   <si>
     <t xml:space="preserve">13.756911277771</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4375944137573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7124996185303</t>
+    <t xml:space="preserve">14.437593460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7124977111816</t>
   </si>
   <si>
     <t xml:space="preserve">16.336332321167</t>
@@ -2360,16 +2360,16 @@
     <t xml:space="preserve">19.6591281890869</t>
   </si>
   <si>
-    <t xml:space="preserve">21.316047668457</t>
+    <t xml:space="preserve">21.3160457611084</t>
   </si>
   <si>
     <t xml:space="preserve">21.4503936767578</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5399570465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2116794586182</t>
+    <t xml:space="preserve">21.5399551391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2116813659668</t>
   </si>
   <si>
     <t xml:space="preserve">21.987771987915</t>
@@ -2381,25 +2381,25 @@
     <t xml:space="preserve">23.017749786377</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3460254669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1221179962158</t>
+    <t xml:space="preserve">22.3460235595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1221160888672</t>
   </si>
   <si>
     <t xml:space="preserve">23.7342548370361</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8982105255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4355869293213</t>
+    <t xml:space="preserve">21.8982086181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4355888366699</t>
   </si>
   <si>
     <t xml:space="preserve">21.495174407959</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7190799713135</t>
+    <t xml:space="preserve">21.7190818786621</t>
   </si>
   <si>
     <t xml:space="preserve">21.9429912567139</t>
@@ -2411,7 +2411,7 @@
     <t xml:space="preserve">21.8534259796143</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3312187194824</t>
+    <t xml:space="preserve">23.3312206268311</t>
   </si>
   <si>
     <t xml:space="preserve">21.8086471557617</t>
@@ -2426,10 +2426,10 @@
     <t xml:space="preserve">26.2420253753662</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5255184173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2120494842529</t>
+    <t xml:space="preserve">25.525520324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2120456695557</t>
   </si>
   <si>
     <t xml:space="preserve">25.8837718963623</t>
@@ -2447,19 +2447,19 @@
     <t xml:space="preserve">24.361198425293</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3911743164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7046489715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4211502075195</t>
+    <t xml:space="preserve">25.3911762237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.704647064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4211521148682</t>
   </si>
   <si>
     <t xml:space="preserve">26.0628986358643</t>
   </si>
   <si>
-    <t xml:space="preserve">26.465934753418</t>
+    <t xml:space="preserve">26.4659328460693</t>
   </si>
   <si>
     <t xml:space="preserve">26.1524620056152</t>
@@ -2468,7 +2468,7 @@
     <t xml:space="preserve">28.6602325439453</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6750373840332</t>
+    <t xml:space="preserve">27.6750354766846</t>
   </si>
   <si>
     <t xml:space="preserve">26.7794036865234</t>
@@ -2477,16 +2477,16 @@
     <t xml:space="preserve">26.5554962158203</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9881401062012</t>
+    <t xml:space="preserve">24.9881381988525</t>
   </si>
   <si>
     <t xml:space="preserve">25.2568302154541</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9581642150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0477256774902</t>
+    <t xml:space="preserve">23.9581623077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0477275848389</t>
   </si>
   <si>
     <t xml:space="preserve">23.9133815765381</t>
@@ -2498,28 +2498,28 @@
     <t xml:space="preserve">22.077335357666</t>
   </si>
   <si>
-    <t xml:space="preserve">22.928186416626</t>
+    <t xml:space="preserve">22.9281845092773</t>
   </si>
   <si>
     <t xml:space="preserve">23.1968765258789</t>
   </si>
   <si>
-    <t xml:space="preserve">24.182071685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2268505096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4955425262451</t>
+    <t xml:space="preserve">24.1820697784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2268543243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4955444335938</t>
   </si>
   <si>
     <t xml:space="preserve">24.3164138793945</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3908061981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8238182067871</t>
+    <t xml:space="preserve">22.3908081054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8238201141357</t>
   </si>
   <si>
     <t xml:space="preserve">23.0625305175781</t>
@@ -2528,25 +2528,25 @@
     <t xml:space="preserve">23.7790355682373</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8834018707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2416572570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1672668457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3167819976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6002807617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6150817871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4359569549561</t>
+    <t xml:space="preserve">22.8834037780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2416591644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1672687530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3167839050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6002788543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.615083694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4359550476074</t>
   </si>
   <si>
     <t xml:space="preserve">24.8985767364502</t>
@@ -2561,28 +2561,28 @@
     <t xml:space="preserve">26.197244644165</t>
   </si>
   <si>
-    <t xml:space="preserve">26.868968963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6450595855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4959125518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.048095703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9437255859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8841419219971</t>
+    <t xml:space="preserve">26.8689670562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6450576782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4959106445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0480937957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9437274932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8841400146484</t>
   </si>
   <si>
     <t xml:space="preserve">28.9289207458496</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7050151824951</t>
+    <t xml:space="preserve">28.7050132751465</t>
   </si>
   <si>
     <t xml:space="preserve">29.7797737121582</t>
@@ -2606,25 +2606,25 @@
     <t xml:space="preserve">25.8389911651611</t>
   </si>
   <si>
-    <t xml:space="preserve">25.79421043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3315868377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7194499969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4507598876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5999126434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4655647277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3615646362305</t>
+    <t xml:space="preserve">25.7942085266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3315887451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7194519042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4507617950439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.599910736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4655666351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3615665435791</t>
   </si>
   <si>
     <t xml:space="preserve">28.0332889556885</t>
@@ -2642,7 +2642,7 @@
     <t xml:space="preserve">30.2979869842529</t>
   </si>
   <si>
-    <t xml:space="preserve">26.891170501709</t>
+    <t xml:space="preserve">26.8911685943604</t>
   </si>
   <si>
     <t xml:space="preserve">27.3454132080078</t>
@@ -2663,10 +2663,10 @@
     <t xml:space="preserve">30.57053565979</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0247821807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0702018737793</t>
+    <t xml:space="preserve">31.0247802734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0702037811279</t>
   </si>
   <si>
     <t xml:space="preserve">30.8885059356689</t>
@@ -2681,19 +2681,19 @@
     <t xml:space="preserve">27.9359283447266</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4362602233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0722007751465</t>
+    <t xml:space="preserve">27.4362621307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0722026824951</t>
   </si>
   <si>
     <t xml:space="preserve">28.4355945587158</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5264415740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4810199737549</t>
+    <t xml:space="preserve">28.5264434814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4810180664062</t>
   </si>
   <si>
     <t xml:space="preserve">28.3901710510254</t>
@@ -2705,22 +2705,22 @@
     <t xml:space="preserve">29.434928894043</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2538986206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1169605255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1162948608398</t>
+    <t xml:space="preserve">28.2538967132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1169586181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1162929534912</t>
   </si>
   <si>
     <t xml:space="preserve">30.9793529510498</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1610488891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.479024887085</t>
+    <t xml:space="preserve">31.1610507965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4790210723877</t>
   </si>
   <si>
     <t xml:space="preserve">31.5698719024658</t>
@@ -2729,7 +2729,7 @@
     <t xml:space="preserve">31.7969932556152</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7515678405762</t>
+    <t xml:space="preserve">31.7515697479248</t>
   </si>
   <si>
     <t xml:space="preserve">31.1156272888184</t>
@@ -2744,43 +2744,43 @@
     <t xml:space="preserve">33.8410835266113</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4770278930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.386173248291</t>
+    <t xml:space="preserve">34.4770240783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3861770629883</t>
   </si>
   <si>
     <t xml:space="preserve">34.5678672790527</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6132926940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.340087890625</t>
+    <t xml:space="preserve">34.6132965087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3400840759277</t>
   </si>
   <si>
     <t xml:space="preserve">34.4316024780273</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7048072814941</t>
+    <t xml:space="preserve">33.7048110961914</t>
   </si>
   <si>
     <t xml:space="preserve">33.9773559570312</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9312705993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5224494934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0682067871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7502326965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9319305419922</t>
+    <t xml:space="preserve">34.931266784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5224456787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0682029724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7502365112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9319343566895</t>
   </si>
   <si>
     <t xml:space="preserve">34.2499008178711</t>
@@ -2795,16 +2795,16 @@
     <t xml:space="preserve">36.6573867797852</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7936592102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6106300354004</t>
+    <t xml:space="preserve">36.7936630249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6106338500977</t>
   </si>
   <si>
     <t xml:space="preserve">39.5645408630371</t>
   </si>
   <si>
-    <t xml:space="preserve">38.1109657287598</t>
+    <t xml:space="preserve">38.110969543457</t>
   </si>
   <si>
     <t xml:space="preserve">36.4302635192871</t>
@@ -2819,13 +2819,13 @@
     <t xml:space="preserve">33.0688743591309</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3414154052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8865089416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2044792175293</t>
+    <t xml:space="preserve">33.3414192199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8865051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2044830322266</t>
   </si>
   <si>
     <t xml:space="preserve">34.340747833252</t>
@@ -2840,16 +2840,16 @@
     <t xml:space="preserve">32.9780197143555</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7976570129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3895034790039</t>
+    <t xml:space="preserve">30.7976551055908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3895053863525</t>
   </si>
   <si>
     <t xml:space="preserve">29.5257778167725</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6172904968262</t>
+    <t xml:space="preserve">28.6172924041748</t>
   </si>
   <si>
     <t xml:space="preserve">28.3447456359863</t>
@@ -2876,7 +2876,7 @@
     <t xml:space="preserve">32.024112701416</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1142997741699</t>
+    <t xml:space="preserve">33.1142959594727</t>
   </si>
   <si>
     <t xml:space="preserve">32.614631652832</t>
@@ -2888,10 +2888,10 @@
     <t xml:space="preserve">32.0695381164551</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5244464874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3427467346191</t>
+    <t xml:space="preserve">31.5244483947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3427486419678</t>
   </si>
   <si>
     <t xml:space="preserve">32.3420829772949</t>
@@ -2900,13 +2900,13 @@
     <t xml:space="preserve">32.5237770080566</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7054786682129</t>
+    <t xml:space="preserve">32.7054748535156</t>
   </si>
   <si>
     <t xml:space="preserve">32.1603851318359</t>
   </si>
   <si>
-    <t xml:space="preserve">34.159049987793</t>
+    <t xml:space="preserve">34.1590538024902</t>
   </si>
   <si>
     <t xml:space="preserve">33.7956581115723</t>
@@ -2915,7 +2915,7 @@
     <t xml:space="preserve">34.976692199707</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9325942993164</t>
+    <t xml:space="preserve">32.9325981140137</t>
   </si>
   <si>
     <t xml:space="preserve">33.0234451293945</t>
@@ -2933,37 +2933,37 @@
     <t xml:space="preserve">31.8424167633057</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8878383636475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4342651367188</t>
+    <t xml:space="preserve">31.8878364562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4342632293701</t>
   </si>
   <si>
     <t xml:space="preserve">29.7074756622314</t>
   </si>
   <si>
-    <t xml:space="preserve">30.70680809021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4796867370605</t>
+    <t xml:space="preserve">30.7068099975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4796886444092</t>
   </si>
   <si>
     <t xml:space="preserve">29.6166248321533</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8437442779541</t>
+    <t xml:space="preserve">29.8437461853027</t>
   </si>
   <si>
     <t xml:space="preserve">29.2532329559326</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7535629272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0708656311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8898372650146</t>
+    <t xml:space="preserve">28.7535648345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0708675384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.889835357666</t>
   </si>
   <si>
     <t xml:space="preserve">28.6627159118652</t>
@@ -2972,13 +2972,13 @@
     <t xml:space="preserve">28.8444137573242</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7081432342529</t>
+    <t xml:space="preserve">28.7081413269043</t>
   </si>
   <si>
     <t xml:space="preserve">28.9806861877441</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7989902496338</t>
+    <t xml:space="preserve">28.7989883422852</t>
   </si>
   <si>
     <t xml:space="preserve">29.8891735076904</t>
@@ -3005,10 +3005,10 @@
     <t xml:space="preserve">28.5718688964844</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4816856384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5725345611572</t>
+    <t xml:space="preserve">27.4816837310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5725326538086</t>
   </si>
   <si>
     <t xml:space="preserve">26.6186237335205</t>
@@ -3020,7 +3020,7 @@
     <t xml:space="preserve">27.0274410247803</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9365940093994</t>
+    <t xml:space="preserve">26.9365921020508</t>
   </si>
   <si>
     <t xml:space="preserve">26.9820194244385</t>
@@ -3029,13 +3029,13 @@
     <t xml:space="preserve">26.3460788726807</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8918342590332</t>
+    <t xml:space="preserve">25.8918361663818</t>
   </si>
   <si>
     <t xml:space="preserve">25.6647148132324</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2552299499512</t>
+    <t xml:space="preserve">26.2552280426025</t>
   </si>
   <si>
     <t xml:space="preserve">26.8457450866699</t>
@@ -3056,10 +3056,10 @@
     <t xml:space="preserve">26.70947265625</t>
   </si>
   <si>
-    <t xml:space="preserve">26.527774810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9826831817627</t>
+    <t xml:space="preserve">26.5277767181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9826850891113</t>
   </si>
   <si>
     <t xml:space="preserve">25.8009872436523</t>
@@ -3068,13 +3068,13 @@
     <t xml:space="preserve">24.1657123565674</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6660442352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8477458953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.437593460083</t>
+    <t xml:space="preserve">23.6660461425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8477439880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4375953674316</t>
   </si>
   <si>
     <t xml:space="preserve">25.7555637359619</t>
@@ -4287,6 +4287,9 @@
   </si>
   <si>
     <t xml:space="preserve">20.6499996185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21</t>
   </si>
 </sst>
 </file>
@@ -69573,7 +69576,7 @@
     </row>
     <row r="2499">
       <c r="A2499" s="1" t="n">
-        <v>45958.6912152778</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B2499" t="n">
         <v>29568</v>
@@ -69594,6 +69597,32 @@
         <v>1424</v>
       </c>
       <c r="H2499" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2500">
+      <c r="A2500" s="1" t="n">
+        <v>45959.691099537</v>
+      </c>
+      <c r="B2500" t="n">
+        <v>33326</v>
+      </c>
+      <c r="C2500" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="D2500" t="n">
+        <v>20.2999992370605</v>
+      </c>
+      <c r="E2500" t="n">
+        <v>20.7000007629395</v>
+      </c>
+      <c r="F2500" t="n">
+        <v>21</v>
+      </c>
+      <c r="G2500" t="s">
+        <v>1425</v>
+      </c>
+      <c r="H2500" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ARN.MI.xlsx
+++ b/data/ARN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1425" uniqueCount="1425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1426" uniqueCount="1426">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92215049266815</t>
+    <t xml:space="preserve">1.92215013504028</t>
   </si>
   <si>
     <t xml:space="preserve">ARN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94450056552887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91736054420471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90778172016144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88383495807648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93172895908356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91576433181763</t>
+    <t xml:space="preserve">1.94450104236603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.917360663414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90778195858002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8838347196579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93172883987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91576409339905</t>
   </si>
   <si>
     <t xml:space="preserve">1.83434438705444</t>
@@ -68,118 +68,118 @@
     <t xml:space="preserve">1.83594059944153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91097509860992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80720412731171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74973142147064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71620583534241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80401146411896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81039702892303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79602885246277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77208173274994</t>
+    <t xml:space="preserve">1.91097497940063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.807204246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74973130226135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71620535850525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80401134490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81039714813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79602921009064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77208209037781</t>
   </si>
   <si>
     <t xml:space="preserve">1.70662665367126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69704759120941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69066166877747</t>
+    <t xml:space="preserve">1.69704782962799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69066190719604</t>
   </si>
   <si>
     <t xml:space="preserve">1.67629361152649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70024085044861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69864451885223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67469727993011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66671502590179</t>
+    <t xml:space="preserve">1.70024073123932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69864428043365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6746973991394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66671478748322</t>
   </si>
   <si>
     <t xml:space="preserve">1.66032886505127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8151867389679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82795822620392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86148428916931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88543105125427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89181745052338</t>
+    <t xml:space="preserve">1.81518685817719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82795858383179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8614844083786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88543128967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89181709289551</t>
   </si>
   <si>
     <t xml:space="preserve">1.92853605747223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95407927036285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90618526935577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86786997318268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88064169883728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85190558433533</t>
+    <t xml:space="preserve">1.95407938957214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90618562698364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86786985397339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88064217567444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85190546512604</t>
   </si>
   <si>
     <t xml:space="preserve">1.85988783836365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85509824752808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79283618927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78804671764374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78006434440613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75611710548401</t>
+    <t xml:space="preserve">1.85509836673737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79283607006073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78804659843445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78006422519684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7561172246933</t>
   </si>
   <si>
     <t xml:space="preserve">1.76888906955719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76409947872162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7848539352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77048552036285</t>
+    <t xml:space="preserve">1.76409935951233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78485381603241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77048563957214</t>
   </si>
   <si>
     <t xml:space="preserve">1.72099471092224</t>
@@ -188,34 +188,34 @@
     <t xml:space="preserve">1.73536312580109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80241477489471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76250326633453</t>
+    <t xml:space="preserve">1.802414894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76250314712524</t>
   </si>
   <si>
     <t xml:space="preserve">1.74494194984436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73217010498047</t>
+    <t xml:space="preserve">1.73217046260834</t>
   </si>
   <si>
     <t xml:space="preserve">1.73695981502533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7433454990387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75132787227631</t>
+    <t xml:space="preserve">1.74334537982941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7513279914856</t>
   </si>
   <si>
     <t xml:space="preserve">1.68587255477905</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67789030075073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65234661102295</t>
+    <t xml:space="preserve">1.67789018154144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65234649181366</t>
   </si>
   <si>
     <t xml:space="preserve">1.6204172372818</t>
@@ -224,16 +224,16 @@
     <t xml:space="preserve">1.64276778697968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5900844335556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60285604000092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54937434196472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51185750961304</t>
+    <t xml:space="preserve">1.59008419513702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60285580158234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54937422275543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51185739040375</t>
   </si>
   <si>
     <t xml:space="preserve">1.45598077774048</t>
@@ -242,19 +242,19 @@
     <t xml:space="preserve">1.43682324886322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46955072879791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49748921394348</t>
+    <t xml:space="preserve">1.4695508480072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4974889755249</t>
   </si>
   <si>
     <t xml:space="preserve">1.47673499584198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47274374961853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46875250339508</t>
+    <t xml:space="preserve">1.47274363040924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46875274181366</t>
   </si>
   <si>
     <t xml:space="preserve">1.49669086933136</t>
@@ -269,97 +269,97 @@
     <t xml:space="preserve">1.47753322124481</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43841969966888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40090250968933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3490172624588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30910563468933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3434294462204</t>
+    <t xml:space="preserve">1.43841958045959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40090274810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34901738166809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30910551548004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34342956542969</t>
   </si>
   <si>
     <t xml:space="preserve">1.32666683197021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34103500843048</t>
+    <t xml:space="preserve">1.3410347700119</t>
   </si>
   <si>
     <t xml:space="preserve">1.31708788871765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38653457164764</t>
+    <t xml:space="preserve">1.38653433322906</t>
   </si>
   <si>
     <t xml:space="preserve">1.39691138267517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40649020671844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30671083927155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32347393035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30591261386871</t>
+    <t xml:space="preserve">1.40649008750916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30671072006226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3234738111496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.305912733078</t>
   </si>
   <si>
     <t xml:space="preserve">1.31229853630066</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2899477481842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28515839576721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28595685958862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33305275440216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33704352378845</t>
+    <t xml:space="preserve">1.28994810581207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2851585149765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28595662117004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33305263519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33704376220703</t>
   </si>
   <si>
     <t xml:space="preserve">1.30112326145172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36104893684387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34627258777618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35283982753754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33806371688843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27157080173492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28880989551544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29291439056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30686974525452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33888459205627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34955632686615</t>
+    <t xml:space="preserve">1.36104869842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34627246856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35283970832825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33806383609772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27157092094421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28880977630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29291427135468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30686950683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3388843536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34955620765686</t>
   </si>
   <si>
     <t xml:space="preserve">1.34380996227264</t>
@@ -371,46 +371,46 @@
     <t xml:space="preserve">1.34709346294403</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30522775650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29127252101898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31425762176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32164561748505</t>
+    <t xml:space="preserve">1.30522787570953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29127240180969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31425750255585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32164573669434</t>
   </si>
   <si>
     <t xml:space="preserve">1.26828730106354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27239167690277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28798890113831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2970187664032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24858570098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32657110691071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33231735229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3594069480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42015361785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48664617538452</t>
+    <t xml:space="preserve">1.27239179611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28798866271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29701888561249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24858582019806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32657122612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33231723308563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35940706729889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4201534986496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48664605617523</t>
   </si>
   <si>
     <t xml:space="preserve">1.53343737125397</t>
@@ -419,16 +419,16 @@
     <t xml:space="preserve">1.51619851589203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51866126060486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43739235401154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4677654504776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43000423908234</t>
+    <t xml:space="preserve">1.51866114139557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43739223480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46776556968689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43000411987305</t>
   </si>
   <si>
     <t xml:space="preserve">1.40948164463043</t>
@@ -437,13 +437,13 @@
     <t xml:space="preserve">1.44478046894073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55970597267151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61798977851868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70582616329193</t>
+    <t xml:space="preserve">1.5597060918808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61798965930939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70582592487335</t>
   </si>
   <si>
     <t xml:space="preserve">1.74851262569427</t>
@@ -476,10 +476,10 @@
     <t xml:space="preserve">1.69597506523132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69433331489563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65821385383606</t>
+    <t xml:space="preserve">1.69433307647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65821373462677</t>
   </si>
   <si>
     <t xml:space="preserve">1.68119895458221</t>
@@ -488,13 +488,13 @@
     <t xml:space="preserve">1.68776619434357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6680645942688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6500049829483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66313934326172</t>
+    <t xml:space="preserve">1.66806471347809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65000474452972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66313922405243</t>
   </si>
   <si>
     <t xml:space="preserve">1.67791545391083</t>
@@ -506,16 +506,16 @@
     <t xml:space="preserve">2.04403591156006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03911066055298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04075217247009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0522449016571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04731965065002</t>
+    <t xml:space="preserve">2.03911018371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04075241088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05224514007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04731917381287</t>
   </si>
   <si>
     <t xml:space="preserve">2.04239416122437</t>
@@ -533,58 +533,58 @@
     <t xml:space="preserve">2.17537975311279</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14582753181458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00627446174622</t>
+    <t xml:space="preserve">2.14582705497742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00627422332764</t>
   </si>
   <si>
     <t xml:space="preserve">1.98821473121643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9931401014328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99806559085846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99642395973206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99970746040344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00299119949341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00791668891907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01120018959045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02597618103027</t>
+    <t xml:space="preserve">1.99314022064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99806535243988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99642372131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99970769882202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00299096107483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00791645050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01119995117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02597594261169</t>
   </si>
   <si>
     <t xml:space="preserve">2.03254318237305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02105045318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0194091796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.024334192276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07687187194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05881214141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09657311439514</t>
+    <t xml:space="preserve">2.02105069160461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01940894126892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02433443069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07687211036682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0588116645813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09657335281372</t>
   </si>
   <si>
     <t xml:space="preserve">2.14746904373169</t>
@@ -596,25 +596,25 @@
     <t xml:space="preserve">2.27552890777588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32478308677673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27881264686584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25746917724609</t>
+    <t xml:space="preserve">2.32478284835815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.278813123703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25746965408325</t>
   </si>
   <si>
     <t xml:space="preserve">2.29851412773132</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26075315475464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28045439720154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30672335624695</t>
+    <t xml:space="preserve">2.26075267791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28045463562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30672311782837</t>
   </si>
   <si>
     <t xml:space="preserve">2.35597705841064</t>
@@ -623,19 +623,19 @@
     <t xml:space="preserve">2.34120106697083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34284234046936</t>
+    <t xml:space="preserve">2.3428430557251</t>
   </si>
   <si>
     <t xml:space="preserve">2.34776782989502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44627571105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39209675788879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38224530220032</t>
+    <t xml:space="preserve">2.44627594947815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39209699630737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38224577903748</t>
   </si>
   <si>
     <t xml:space="preserve">2.38717126846313</t>
@@ -644,85 +644,85 @@
     <t xml:space="preserve">2.38388776779175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40523076057434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38060450553894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42164874076843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33791756629944</t>
+    <t xml:space="preserve">2.40523147583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38060402870178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42164921760559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33791732788086</t>
   </si>
   <si>
     <t xml:space="preserve">2.32314109802246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35433506965637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41015625</t>
+    <t xml:space="preserve">2.35433530807495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41015648841858</t>
   </si>
   <si>
     <t xml:space="preserve">2.40687274932861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43806672096252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41836524009705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29030513763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34941005706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36418628692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3756787776947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40194773674011</t>
+    <t xml:space="preserve">2.43806719779968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4183657169342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29030537605286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34940958023071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36418604850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37567901611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40194749832153</t>
   </si>
   <si>
     <t xml:space="preserve">2.35761904716492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36746954917908</t>
+    <t xml:space="preserve">2.36746978759766</t>
   </si>
   <si>
     <t xml:space="preserve">2.37075328826904</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37239551544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.362544298172</t>
+    <t xml:space="preserve">2.37239527702332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36254382133484</t>
   </si>
   <si>
     <t xml:space="preserve">2.36582779884338</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39538049697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37732028961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37403655052185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38881325721741</t>
+    <t xml:space="preserve">2.3953800201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3773205280304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37403678894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38881301879883</t>
   </si>
   <si>
     <t xml:space="preserve">2.39373826980591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39045453071594</t>
+    <t xml:space="preserve">2.3904550075531</t>
   </si>
   <si>
     <t xml:space="preserve">2.41343975067139</t>
@@ -731,31 +731,31 @@
     <t xml:space="preserve">2.40358901023865</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40030598640442</t>
+    <t xml:space="preserve">2.40030550956726</t>
   </si>
   <si>
     <t xml:space="preserve">2.40851473808289</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42329096794128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43149971961975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42000699043274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35105180740356</t>
+    <t xml:space="preserve">2.42329049110413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43149948120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42000722885132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35105204582214</t>
   </si>
   <si>
     <t xml:space="preserve">2.33627533912659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34612631797791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43642520904541</t>
+    <t xml:space="preserve">2.34612655639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43642473220825</t>
   </si>
   <si>
     <t xml:space="preserve">2.42657446861267</t>
@@ -767,34 +767,34 @@
     <t xml:space="preserve">2.45284295082092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47701287269592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.478679895401</t>
+    <t xml:space="preserve">2.4770131111145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47868013381958</t>
   </si>
   <si>
     <t xml:space="preserve">2.49201512336731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49368214607239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.475346326828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46534466743469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48201417922974</t>
+    <t xml:space="preserve">2.49368238449097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47534656524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46534442901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48201322555542</t>
   </si>
   <si>
     <t xml:space="preserve">2.46867847442627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45867729187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46201109886169</t>
+    <t xml:space="preserve">2.4586775302887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46201086044312</t>
   </si>
   <si>
     <t xml:space="preserve">2.45534348487854</t>
@@ -803,43 +803,43 @@
     <t xml:space="preserve">2.41700482368469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40867066383362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36699771881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3419942855835</t>
+    <t xml:space="preserve">2.40867042541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36699795722961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34199404716492</t>
   </si>
   <si>
     <t xml:space="preserve">2.36866474151611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35366225242615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38533353805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38366627693176</t>
+    <t xml:space="preserve">2.35366249084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.385333776474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38366651535034</t>
   </si>
   <si>
     <t xml:space="preserve">2.36366391181946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32532501220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31699109077454</t>
+    <t xml:space="preserve">2.32532525062561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3169903755188</t>
   </si>
   <si>
     <t xml:space="preserve">2.28531980514526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28698682785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29698824882507</t>
+    <t xml:space="preserve">2.28698658943176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29698777198792</t>
   </si>
   <si>
     <t xml:space="preserve">2.31532382965088</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">2.28865337371826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29032063484192</t>
+    <t xml:space="preserve">2.29031991958618</t>
   </si>
   <si>
     <t xml:space="preserve">2.30198836326599</t>
@@ -860,13 +860,13 @@
     <t xml:space="preserve">2.30365562438965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29365420341492</t>
+    <t xml:space="preserve">2.2936544418335</t>
   </si>
   <si>
     <t xml:space="preserve">2.24198031425476</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26698398590088</t>
+    <t xml:space="preserve">2.2669837474823</t>
   </si>
   <si>
     <t xml:space="preserve">2.2686505317688</t>
@@ -875,22 +875,22 @@
     <t xml:space="preserve">2.32699227333069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31865763664246</t>
+    <t xml:space="preserve">2.31865739822388</t>
   </si>
   <si>
     <t xml:space="preserve">2.3103232383728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24364709854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25031471252441</t>
+    <t xml:space="preserve">2.24364733695984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25031447410583</t>
   </si>
   <si>
     <t xml:space="preserve">2.2253110408783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25198173522949</t>
+    <t xml:space="preserve">2.25198149681091</t>
   </si>
   <si>
     <t xml:space="preserve">2.2219774723053</t>
@@ -899,28 +899,28 @@
     <t xml:space="preserve">2.20697522163391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20030808448792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16863656044006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17863845825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16696929931641</t>
+    <t xml:space="preserve">2.20030760765076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16863703727722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17863821983337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16696953773499</t>
   </si>
   <si>
     <t xml:space="preserve">2.18697261810303</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1969735622406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18363881111145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18530559539795</t>
+    <t xml:space="preserve">2.19697427749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18363857269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18530583381653</t>
   </si>
   <si>
     <t xml:space="preserve">2.19197344779968</t>
@@ -929,46 +929,46 @@
     <t xml:space="preserve">2.17530417442322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14196610450745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15363454818726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1436333656311</t>
+    <t xml:space="preserve">2.14196634292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15363430976868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14363288879395</t>
   </si>
   <si>
     <t xml:space="preserve">2.13529872894287</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1269645690918</t>
+    <t xml:space="preserve">2.12696433067322</t>
   </si>
   <si>
     <t xml:space="preserve">2.12863111495972</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12029647827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13029789924622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11862993240356</t>
+    <t xml:space="preserve">2.12029623985291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13029813766479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11862945556641</t>
   </si>
   <si>
     <t xml:space="preserve">2.37366533279419</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37533211708069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40700364112854</t>
+    <t xml:space="preserve">2.37533235549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40700316429138</t>
   </si>
   <si>
     <t xml:space="preserve">2.39533519744873</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39200091362</t>
+    <t xml:space="preserve">2.39200115203857</t>
   </si>
   <si>
     <t xml:space="preserve">2.49868273735046</t>
@@ -977,64 +977,64 @@
     <t xml:space="preserve">2.49534916877747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5086841583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51201796531677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51535177230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51701879501343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52368640899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52535319328308</t>
+    <t xml:space="preserve">2.50868439674377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51201820373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51535153388977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51701855659485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.523686170578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52535367012024</t>
   </si>
   <si>
     <t xml:space="preserve">2.54535627365112</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53368782997131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53202104568481</t>
+    <t xml:space="preserve">2.53368735313416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53202128410339</t>
   </si>
   <si>
     <t xml:space="preserve">2.54035544395447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52702021598816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53868842124939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53702139854431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49701595306396</t>
+    <t xml:space="preserve">2.52702045440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53868865966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53702163696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49701571464539</t>
   </si>
   <si>
     <t xml:space="preserve">2.42700600624084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50034976005554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50535035133362</t>
+    <t xml:space="preserve">2.50034952163696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5053505897522</t>
   </si>
   <si>
     <t xml:space="preserve">2.48368048667908</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45200991630554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51368474960327</t>
+    <t xml:space="preserve">2.45200943946838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51368498802185</t>
   </si>
   <si>
     <t xml:space="preserve">2.54202222824097</t>
@@ -1043,25 +1043,25 @@
     <t xml:space="preserve">2.54868984222412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51035141944885</t>
+    <t xml:space="preserve">2.51035118103027</t>
   </si>
   <si>
     <t xml:space="preserve">2.52035236358643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47201251983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50201678276062</t>
+    <t xml:space="preserve">2.47201228141785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50201630592346</t>
   </si>
   <si>
     <t xml:space="preserve">2.48701429367065</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00041961669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81706047058105</t>
+    <t xml:space="preserve">3.0004198551178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81706070899963</t>
   </si>
   <si>
     <t xml:space="preserve">2.75038456916809</t>
@@ -1070,25 +1070,25 @@
     <t xml:space="preserve">2.7170467376709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8087260723114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80039191246033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83372974395752</t>
+    <t xml:space="preserve">2.80872631072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80039119720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8337299823761</t>
   </si>
   <si>
     <t xml:space="preserve">2.78372287750244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84206390380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75871896743774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85039877891541</t>
+    <t xml:space="preserve">2.84206414222717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7587194442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85039854049683</t>
   </si>
   <si>
     <t xml:space="preserve">2.85873317718506</t>
@@ -1097,16 +1097,16 @@
     <t xml:space="preserve">2.89207124710083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82539558410645</t>
+    <t xml:space="preserve">2.82539534568787</t>
   </si>
   <si>
     <t xml:space="preserve">2.72538137435913</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61703252792358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64203643798828</t>
+    <t xml:space="preserve">2.61703276634216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6420361995697</t>
   </si>
   <si>
     <t xml:space="preserve">2.70037746429443</t>
@@ -1115,43 +1115,43 @@
     <t xml:space="preserve">2.65870523452759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62536716461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63370180130005</t>
+    <t xml:space="preserve">2.6253674030304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63370156288147</t>
   </si>
   <si>
     <t xml:space="preserve">2.59202909469604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6670401096344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70871186256409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74205017089844</t>
+    <t xml:space="preserve">2.66703963279724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70871233940125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74204993247986</t>
   </si>
   <si>
     <t xml:space="preserve">2.65037083625793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68370842933655</t>
+    <t xml:space="preserve">2.68370866775513</t>
   </si>
   <si>
     <t xml:space="preserve">2.6003634929657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58369493484497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56702566146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7670533657074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73371601104736</t>
+    <t xml:space="preserve">2.58369445800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56702613830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76705384254456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73371553421021</t>
   </si>
   <si>
     <t xml:space="preserve">2.79205703735352</t>
@@ -1160,16 +1160,16 @@
     <t xml:space="preserve">2.86706781387329</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87540221214294</t>
+    <t xml:space="preserve">2.8754026889801</t>
   </si>
   <si>
     <t xml:space="preserve">2.88373684883118</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77538824081421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78091406822205</t>
+    <t xml:space="preserve">2.77538800239563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78091359138489</t>
   </si>
   <si>
     <t xml:space="preserve">2.72174549102783</t>
@@ -1184,28 +1184,28 @@
     <t xml:space="preserve">2.645672082901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70483994483948</t>
+    <t xml:space="preserve">2.70484018325806</t>
   </si>
   <si>
     <t xml:space="preserve">2.68793511390686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6625771522522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69638776779175</t>
+    <t xml:space="preserve">2.66257739067078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69638752937317</t>
   </si>
   <si>
     <t xml:space="preserve">2.65412449836731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60340881347656</t>
+    <t xml:space="preserve">2.60340905189514</t>
   </si>
   <si>
     <t xml:space="preserve">2.63721895217896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61186122894287</t>
+    <t xml:space="preserve">2.61186146736145</t>
   </si>
   <si>
     <t xml:space="preserve">2.5780508518219</t>
@@ -1223,49 +1223,49 @@
     <t xml:space="preserve">2.54424047470093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5611457824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58650374412537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51888251304626</t>
+    <t xml:space="preserve">2.56114602088928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58650326728821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51888227462769</t>
   </si>
   <si>
     <t xml:space="preserve">2.53578758239746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55269312858582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51042985916138</t>
+    <t xml:space="preserve">2.55269289016724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51043009757996</t>
   </si>
   <si>
     <t xml:space="preserve">2.56959795951843</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46816682815552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48507189750671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41745090484619</t>
+    <t xml:space="preserve">2.46816658973694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48507213592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41745066642761</t>
   </si>
   <si>
     <t xml:space="preserve">2.45126152038574</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39209270477295</t>
+    <t xml:space="preserve">2.39209294319153</t>
   </si>
   <si>
     <t xml:space="preserve">2.38364052772522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27375650405884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29911398887634</t>
+    <t xml:space="preserve">2.27375626564026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29911422729492</t>
   </si>
   <si>
     <t xml:space="preserve">2.36673521995544</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">2.35828256607056</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43435645103455</t>
+    <t xml:space="preserve">2.43435621261597</t>
   </si>
   <si>
     <t xml:space="preserve">2.42590355873108</t>
@@ -1283,49 +1283,49 @@
     <t xml:space="preserve">2.34982967376709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28220891952515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32447195053101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40899801254272</t>
+    <t xml:space="preserve">2.28220868110657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32447218894958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40899848937988</t>
   </si>
   <si>
     <t xml:space="preserve">2.45971417427063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44280886650085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33292484283447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34137725830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40054559707642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37518787384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47661948204041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30756688117981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23994588851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29430270195007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2343761920929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24293732643127</t>
+    <t xml:space="preserve">2.44280910491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33292460441589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34137749671936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.400545835495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37518763542175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47661900520325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30756664276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23994612693787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29430222511292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23437666893005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24293684959412</t>
   </si>
   <si>
     <t xml:space="preserve">2.33710646629333</t>
@@ -1334,7 +1334,7 @@
     <t xml:space="preserve">2.25149846076965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27718091011047</t>
+    <t xml:space="preserve">2.27718067169189</t>
   </si>
   <si>
     <t xml:space="preserve">2.26862001419067</t>
@@ -1346,25 +1346,25 @@
     <t xml:space="preserve">2.37134981155396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31142377853394</t>
+    <t xml:space="preserve">2.31142401695251</t>
   </si>
   <si>
     <t xml:space="preserve">2.28574156761169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26005911827087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35422825813293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22581577301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20869398117065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30286335945129</t>
+    <t xml:space="preserve">2.26005887985229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35422801971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2258152961731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20869421958923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30286312103271</t>
   </si>
   <si>
     <t xml:space="preserve">2.31998491287231</t>
@@ -1373,58 +1373,58 @@
     <t xml:space="preserve">2.37991046905518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40559315681458</t>
+    <t xml:space="preserve">2.405592918396</t>
   </si>
   <si>
     <t xml:space="preserve">2.39703226089478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32854533195496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38847160339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36278915405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34566712379456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20013308525085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18301153182983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43983602523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5425660610199</t>
+    <t xml:space="preserve">2.32854557037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38847136497498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36278891563416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34566736221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20013332366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18301105499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4398365020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54256653785706</t>
   </si>
   <si>
     <t xml:space="preserve">2.60249209403992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69666147232056</t>
+    <t xml:space="preserve">2.69666171073914</t>
   </si>
   <si>
     <t xml:space="preserve">2.77370882034302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63673543930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67097878456116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61961388587952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65385723114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68810081481934</t>
+    <t xml:space="preserve">2.63673567771912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67097854614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61961364746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65385699272156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68810033798218</t>
   </si>
   <si>
     <t xml:space="preserve">2.64529633522034</t>
@@ -1436,16 +1436,16 @@
     <t xml:space="preserve">2.72234392166138</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07333755493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52706170082092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59554839134216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65547442436218</t>
+    <t xml:space="preserve">3.07333779335022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52706146240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.595547914505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65547394752502</t>
   </si>
   <si>
     <t xml:space="preserve">3.58698773384094</t>
@@ -1454,34 +1454,34 @@
     <t xml:space="preserve">3.61266994476318</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53562259674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42433190345764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54418349266052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56986594200134</t>
+    <t xml:space="preserve">3.53562307357788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42433166503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54418301582336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56986618041992</t>
   </si>
   <si>
     <t xml:space="preserve">3.55274438858032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56130504608154</t>
+    <t xml:space="preserve">3.56130480766296</t>
   </si>
   <si>
     <t xml:space="preserve">3.5099401473999</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48425793647766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57842683792114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63835263252258</t>
+    <t xml:space="preserve">3.4842574596405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57842659950256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63835287094116</t>
   </si>
   <si>
     <t xml:space="preserve">3.74108242988586</t>
@@ -1490,28 +1490,28 @@
     <t xml:space="preserve">4.16912364959717</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60572671890259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15361928939819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62284755706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19480609893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45163154602051</t>
+    <t xml:space="preserve">4.60572624206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15361976623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62284803390503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19480657577515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45163059234619</t>
   </si>
   <si>
     <t xml:space="preserve">4.53724002838135</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52011823654175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58860540390015</t>
+    <t xml:space="preserve">4.52011775970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58860445022583</t>
   </si>
   <si>
     <t xml:space="preserve">4.34890127182007</t>
@@ -1520,67 +1520,67 @@
     <t xml:space="preserve">4.16056346893311</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23760986328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29753637313843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8951780796051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27879762649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25311493873596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89356064796448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15894603729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16750693321228</t>
+    <t xml:space="preserve">4.23761034011841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29753684997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89517712593079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27879738807678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25311517715454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8935604095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15894627571106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1675066947937</t>
   </si>
   <si>
     <t xml:space="preserve">3.0390944480896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44145345687866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38152766227722</t>
+    <t xml:space="preserve">3.44145369529724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3815279006958</t>
   </si>
   <si>
     <t xml:space="preserve">3.39008855819702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84381222724915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83525156974792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87805581092834</t>
+    <t xml:space="preserve">3.84381246566772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83525133132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8780562877655</t>
   </si>
   <si>
     <t xml:space="preserve">3.76676464080811</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88661694526672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85237383842468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92942142486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95510244369507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93798208236694</t>
+    <t xml:space="preserve">3.88661670684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85237336158752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92942047119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95510315895081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93798160552979</t>
   </si>
   <si>
     <t xml:space="preserve">4.11775922775269</t>
@@ -1592,13 +1592,13 @@
     <t xml:space="preserve">4.22904968261719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26329326629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28041410446167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43450927734375</t>
+    <t xml:space="preserve">4.26329278945923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28041505813599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43450975418091</t>
   </si>
   <si>
     <t xml:space="preserve">4.20336675643921</t>
@@ -1607,10 +1607,10 @@
     <t xml:space="preserve">4.00646781921387</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10919857025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15200233459473</t>
+    <t xml:space="preserve">4.10919809341431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15200281143188</t>
   </si>
   <si>
     <t xml:space="preserve">4.08351612091064</t>
@@ -1619,31 +1619,31 @@
     <t xml:space="preserve">3.94654273986816</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07495498657227</t>
+    <t xml:space="preserve">4.07495450973511</t>
   </si>
   <si>
     <t xml:space="preserve">4.02358961105347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96366405487061</t>
+    <t xml:space="preserve">3.96366453170776</t>
   </si>
   <si>
     <t xml:space="preserve">4.13488054275513</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12632036209106</t>
+    <t xml:space="preserve">4.12631988525391</t>
   </si>
   <si>
     <t xml:space="preserve">5.01664590835571</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70845651626587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91391611099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96528148651123</t>
+    <t xml:space="preserve">4.70845603942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91391658782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96528100967407</t>
   </si>
   <si>
     <t xml:space="preserve">4.94815969467163</t>
@@ -1655,22 +1655,22 @@
     <t xml:space="preserve">5.56453943252563</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68439054489136</t>
+    <t xml:space="preserve">5.68439102172852</t>
   </si>
   <si>
     <t xml:space="preserve">5.95833730697632</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90697193145752</t>
+    <t xml:space="preserve">5.90697288513184</t>
   </si>
   <si>
     <t xml:space="preserve">5.88985061645508</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57471656799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12955331802368</t>
+    <t xml:space="preserve">6.57471704483032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.129554271698</t>
   </si>
   <si>
     <t xml:space="preserve">6.4035005569458</t>
@@ -1679,19 +1679,19 @@
     <t xml:space="preserve">7.0198802947998</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20821809768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32806968688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05412340164185</t>
+    <t xml:space="preserve">7.20821857452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32807016372681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05412292480469</t>
   </si>
   <si>
     <t xml:space="preserve">7.00275850296021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4239764213562</t>
+    <t xml:space="preserve">7.42397785186768</t>
   </si>
   <si>
     <t xml:space="preserve">7.28357124328613</t>
@@ -1700,10 +1700,10 @@
     <t xml:space="preserve">6.8799033164978</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9676570892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59909105300903</t>
+    <t xml:space="preserve">6.96765661239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59909057617188</t>
   </si>
   <si>
     <t xml:space="preserve">6.51133728027344</t>
@@ -1718,37 +1718,37 @@
     <t xml:space="preserve">6.82725095748901</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68684482574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66929340362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45868539810181</t>
+    <t xml:space="preserve">6.68684434890747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66929388046265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45868492126465</t>
   </si>
   <si>
     <t xml:space="preserve">6.40603256225586</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31827878952026</t>
+    <t xml:space="preserve">6.31827831268311</t>
   </si>
   <si>
     <t xml:space="preserve">6.80970001220703</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17826652526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3537745475769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26602029800415</t>
+    <t xml:space="preserve">7.17826700210571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35377407073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26602077484131</t>
   </si>
   <si>
     <t xml:space="preserve">7.05541086196899</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07296276092529</t>
+    <t xml:space="preserve">7.07296228408813</t>
   </si>
   <si>
     <t xml:space="preserve">6.63419198989868</t>
@@ -1757,82 +1757,82 @@
     <t xml:space="preserve">6.44113397598267</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30072736740112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05501651763916</t>
+    <t xml:space="preserve">6.30072784423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.055016040802</t>
   </si>
   <si>
     <t xml:space="preserve">6.03746604919434</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37053680419922</t>
+    <t xml:space="preserve">5.37053632736206</t>
   </si>
   <si>
     <t xml:space="preserve">5.40563821792603</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52849388122559</t>
+    <t xml:space="preserve">5.52849340438843</t>
   </si>
   <si>
     <t xml:space="preserve">5.65134906768799</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12522029876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96726322174072</t>
+    <t xml:space="preserve">6.12521934509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96726274490356</t>
   </si>
   <si>
     <t xml:space="preserve">6.01991558074951</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91460990905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.844407081604</t>
+    <t xml:space="preserve">5.91461038589478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84440755844116</t>
   </si>
   <si>
     <t xml:space="preserve">5.94971179962158</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86195802688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82685661315918</t>
+    <t xml:space="preserve">5.86195755004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82685708999634</t>
   </si>
   <si>
     <t xml:space="preserve">5.93216180801392</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87950897216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79175519943237</t>
+    <t xml:space="preserve">5.87950849533081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79175472259521</t>
   </si>
   <si>
     <t xml:space="preserve">5.68645048141479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45829010009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63379859924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70400142669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58114624023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66890001296997</t>
+    <t xml:space="preserve">5.45829057693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63379812240601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70400094985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58114576339722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66890048980713</t>
   </si>
   <si>
     <t xml:space="preserve">5.56359529495239</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61624717712402</t>
+    <t xml:space="preserve">5.61624765396118</t>
   </si>
   <si>
     <t xml:space="preserve">5.49339246749878</t>
@@ -1841,10 +1841,10 @@
     <t xml:space="preserve">5.31788444519043</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17747831344604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26523160934448</t>
+    <t xml:space="preserve">5.17747783660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26523208618164</t>
   </si>
   <si>
     <t xml:space="preserve">5.28278255462646</t>
@@ -1853,7 +1853,7 @@
     <t xml:space="preserve">5.35298633575439</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42318916320801</t>
+    <t xml:space="preserve">5.42318868637085</t>
   </si>
   <si>
     <t xml:space="preserve">5.47584104537964</t>
@@ -1871,7 +1871,7 @@
     <t xml:space="preserve">5.44074010848999</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54604530334473</t>
+    <t xml:space="preserve">5.54604434967041</t>
   </si>
   <si>
     <t xml:space="preserve">6.23052453994751</t>
@@ -1898,58 +1898,58 @@
     <t xml:space="preserve">6.98520803451538</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33622360229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0905122756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16071557998657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19581699371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95010662078857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14316558837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12561416625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02030944824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84519481658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33661651611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31906509399414</t>
+    <t xml:space="preserve">7.33622312545776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09051275253296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16071510314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19581651687622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95010566711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14316511154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12561368942261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02030992507935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84519529342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33661842346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31906700134277</t>
   </si>
   <si>
     <t xml:space="preserve">8.42437171936035</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08252620697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68763160705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.038649559021</t>
+    <t xml:space="preserve">9.0825252532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6876335144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03864860534668</t>
   </si>
   <si>
     <t xml:space="preserve">9.30191040039062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2763719558716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1630802154541</t>
+    <t xml:space="preserve">11.2763729095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1630792617798</t>
   </si>
   <si>
     <t xml:space="preserve">13.0753259658813</t>
@@ -1958,16 +1958,16 @@
     <t xml:space="preserve">13.1192035675049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8559408187866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0222797393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1100330352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9345264434814</t>
+    <t xml:space="preserve">12.8559417724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0222806930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.110032081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9345254898071</t>
   </si>
   <si>
     <t xml:space="preserve">11.36412525177</t>
@@ -1976,10 +1976,10 @@
     <t xml:space="preserve">10.88148021698</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1539115905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6712646484375</t>
+    <t xml:space="preserve">12.1539106369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6712656021118</t>
   </si>
   <si>
     <t xml:space="preserve">11.7151412963867</t>
@@ -1988,49 +1988,49 @@
     <t xml:space="preserve">11.4518795013428</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0569877624512</t>
+    <t xml:space="preserve">11.0569868087769</t>
   </si>
   <si>
     <t xml:space="preserve">11.4957571029663</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4080028533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8906497955322</t>
+    <t xml:space="preserve">11.4080018997192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8906488418579</t>
   </si>
   <si>
     <t xml:space="preserve">11.8028945922852</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3202486038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6273880004883</t>
+    <t xml:space="preserve">11.3202476501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.627387046814</t>
   </si>
   <si>
     <t xml:space="preserve">11.1447401046753</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6182174682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.530463218689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5743398666382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.749849319458</t>
+    <t xml:space="preserve">10.618218421936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5304641723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5743408203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7498483657837</t>
   </si>
   <si>
     <t xml:space="preserve">10.6620941162109</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3549566268921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78455638885498</t>
+    <t xml:space="preserve">10.3549556732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78455543518066</t>
   </si>
   <si>
     <t xml:space="preserve">9.91618728637695</t>
@@ -2039,61 +2039,61 @@
     <t xml:space="preserve">10.0916948318481</t>
   </si>
   <si>
-    <t xml:space="preserve">11.232494354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1886177062988</t>
+    <t xml:space="preserve">11.2324953079224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1886186599731</t>
   </si>
   <si>
     <t xml:space="preserve">11.1008634567261</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3553495407104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2675971984863</t>
+    <t xml:space="preserve">11.3553504943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.267596244812</t>
   </si>
   <si>
     <t xml:space="preserve">11.0218868255615</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2500457763672</t>
+    <t xml:space="preserve">11.2500448226929</t>
   </si>
   <si>
     <t xml:space="preserve">11.3729009628296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2851476669312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1973934173584</t>
+    <t xml:space="preserve">11.2851467132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1973943710327</t>
   </si>
   <si>
     <t xml:space="preserve">11.8467721939087</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9871768951416</t>
+    <t xml:space="preserve">11.9871788024902</t>
   </si>
   <si>
     <t xml:space="preserve">12.2855415344238</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2504405975342</t>
+    <t xml:space="preserve">12.2504386901855</t>
   </si>
   <si>
     <t xml:space="preserve">12.1626853942871</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4672012329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0372982025146</t>
+    <t xml:space="preserve">12.4672002792358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0372972488403</t>
   </si>
   <si>
     <t xml:space="preserve">12.0910358428955</t>
   </si>
   <si>
-    <t xml:space="preserve">11.553656578064</t>
+    <t xml:space="preserve">11.5536556243896</t>
   </si>
   <si>
     <t xml:space="preserve">11.6432199478149</t>
@@ -2105,7 +2105,7 @@
     <t xml:space="preserve">10.9446268081665</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5505485534668</t>
+    <t xml:space="preserve">10.5505466461182</t>
   </si>
   <si>
     <t xml:space="preserve">10.6759366989136</t>
@@ -2120,10 +2120,10 @@
     <t xml:space="preserve">10.6580238342285</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9267129898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0521020889282</t>
+    <t xml:space="preserve">10.9267139434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0521030426025</t>
   </si>
   <si>
     <t xml:space="preserve">11.4999189376831</t>
@@ -2132,13 +2132,13 @@
     <t xml:space="preserve">11.4820051193237</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4282684326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.571569442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3745288848877</t>
+    <t xml:space="preserve">11.4282674789429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5715684890747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.374529838562</t>
   </si>
   <si>
     <t xml:space="preserve">11.3566179275513</t>
@@ -2147,7 +2147,7 @@
     <t xml:space="preserve">11.3207921981812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4461803436279</t>
+    <t xml:space="preserve">11.4461793899536</t>
   </si>
   <si>
     <t xml:space="preserve">11.464093208313</t>
@@ -2162,7 +2162,7 @@
     <t xml:space="preserve">11.750696182251</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1805992126465</t>
+    <t xml:space="preserve">12.1805982589722</t>
   </si>
   <si>
     <t xml:space="preserve">12.6284151077271</t>
@@ -2177,7 +2177,7 @@
     <t xml:space="preserve">12.3597259521484</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6969575881958</t>
+    <t xml:space="preserve">11.6969566345215</t>
   </si>
   <si>
     <t xml:space="preserve">12.1268615722656</t>
@@ -2189,10 +2189,10 @@
     <t xml:space="preserve">11.8581705093384</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9298219680786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2880754470825</t>
+    <t xml:space="preserve">11.9298210144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2880744934082</t>
   </si>
   <si>
     <t xml:space="preserve">12.5925893783569</t>
@@ -2207,10 +2207,10 @@
     <t xml:space="preserve">12.3239002227783</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9804525375366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1774892807007</t>
+    <t xml:space="preserve">10.9804515838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.177490234375</t>
   </si>
   <si>
     <t xml:space="preserve">11.284966468811</t>
@@ -2225,13 +2225,13 @@
     <t xml:space="preserve">11.7686080932617</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6253051757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0014724731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1089477539062</t>
+    <t xml:space="preserve">11.6253061294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0014715194702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1089487075806</t>
   </si>
   <si>
     <t xml:space="preserve">11.9656467437744</t>
@@ -2249,13 +2249,13 @@
     <t xml:space="preserve">12.8612794876099</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8433666229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6821517944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7358913421631</t>
+    <t xml:space="preserve">12.8433675765991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6821537017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7358903884888</t>
   </si>
   <si>
     <t xml:space="preserve">13.3449201583862</t>
@@ -2264,16 +2264,16 @@
     <t xml:space="preserve">14.2405529022217</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0972518920898</t>
+    <t xml:space="preserve">14.0972509384155</t>
   </si>
   <si>
     <t xml:space="preserve">14.3301162719727</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4734172821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5988054275513</t>
+    <t xml:space="preserve">14.4734182357788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5988063812256</t>
   </si>
   <si>
     <t xml:space="preserve">13.8823003768921</t>
@@ -2285,25 +2285,25 @@
     <t xml:space="preserve">13.5777854919434</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4703102111816</t>
+    <t xml:space="preserve">13.4703092575073</t>
   </si>
   <si>
     <t xml:space="preserve">13.6852607727051</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6673498153687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5598726272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6136102676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8285617828369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9539518356323</t>
+    <t xml:space="preserve">13.6673488616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5598735809326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6136093139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8285627365112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.953950881958</t>
   </si>
   <si>
     <t xml:space="preserve">13.4344844818115</t>
@@ -2312,10 +2312,10 @@
     <t xml:space="preserve">13.7210865020752</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5240468978882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7031745910645</t>
+    <t xml:space="preserve">13.5240478515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7031736373901</t>
   </si>
   <si>
     <t xml:space="preserve">13.2553577423096</t>
@@ -2324,22 +2324,22 @@
     <t xml:space="preserve">13.4523963928223</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3090944290161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2763776779175</t>
+    <t xml:space="preserve">13.3090953826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2763786315918</t>
   </si>
   <si>
     <t xml:space="preserve">14.4196796417236</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0256013870239</t>
+    <t xml:space="preserve">14.0256023406982</t>
   </si>
   <si>
     <t xml:space="preserve">13.756911277771</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4375944137573</t>
+    <t xml:space="preserve">14.437593460083</t>
   </si>
   <si>
     <t xml:space="preserve">16.7124977111816</t>
@@ -2351,7 +2351,7 @@
     <t xml:space="preserve">17.7156066894531</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2498760223389</t>
+    <t xml:space="preserve">17.2498779296875</t>
   </si>
   <si>
     <t xml:space="preserve">19.6591281890869</t>
@@ -2363,13 +2363,13 @@
     <t xml:space="preserve">21.4503936767578</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5399570465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2116794586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.987771987915</t>
+    <t xml:space="preserve">21.5399532318115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2116775512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9877700805664</t>
   </si>
   <si>
     <t xml:space="preserve">21.2712669372559</t>
@@ -2378,10 +2378,10 @@
     <t xml:space="preserve">23.017749786377</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3460254669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1221179962158</t>
+    <t xml:space="preserve">22.3460273742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1221160888672</t>
   </si>
   <si>
     <t xml:space="preserve">23.7342548370361</t>
@@ -2396,22 +2396,22 @@
     <t xml:space="preserve">21.495174407959</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7190818786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9429931640625</t>
+    <t xml:space="preserve">21.7190837860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9429912567139</t>
   </si>
   <si>
     <t xml:space="preserve">21.7638645172119</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8534259796143</t>
+    <t xml:space="preserve">21.8534278869629</t>
   </si>
   <si>
     <t xml:space="preserve">23.3312206268311</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8086452484131</t>
+    <t xml:space="preserve">21.8086471557617</t>
   </si>
   <si>
     <t xml:space="preserve">25.3463916778564</t>
@@ -2420,7 +2420,7 @@
     <t xml:space="preserve">25.3016128540039</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2420253753662</t>
+    <t xml:space="preserve">26.2420234680176</t>
   </si>
   <si>
     <t xml:space="preserve">25.525520324707</t>
@@ -2429,34 +2429,34 @@
     <t xml:space="preserve">25.2120475769043</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8837718963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4807376861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5703010559082</t>
+    <t xml:space="preserve">25.8837699890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4807395935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5702991485596</t>
   </si>
   <si>
     <t xml:space="preserve">25.1224842071533</t>
   </si>
   <si>
-    <t xml:space="preserve">24.361198425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3911743164062</t>
+    <t xml:space="preserve">24.3611965179443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3911762237549</t>
   </si>
   <si>
     <t xml:space="preserve">25.704647064209</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4211521148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0628986358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.465934753418</t>
+    <t xml:space="preserve">26.4211540222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0629005432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4659309387207</t>
   </si>
   <si>
     <t xml:space="preserve">26.1524620056152</t>
@@ -2465,16 +2465,16 @@
     <t xml:space="preserve">28.6602325439453</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6750354766846</t>
+    <t xml:space="preserve">27.6750373840332</t>
   </si>
   <si>
     <t xml:space="preserve">26.7794036865234</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5554962158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9881381988525</t>
+    <t xml:space="preserve">26.5554943084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9881401062012</t>
   </si>
   <si>
     <t xml:space="preserve">25.2568302154541</t>
@@ -2486,10 +2486,10 @@
     <t xml:space="preserve">24.0477275848389</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9133815765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5851058959961</t>
+    <t xml:space="preserve">23.9133834838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5851078033447</t>
   </si>
   <si>
     <t xml:space="preserve">22.077335357666</t>
@@ -2498,7 +2498,7 @@
     <t xml:space="preserve">22.928186416626</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1968746185303</t>
+    <t xml:space="preserve">23.1968765258789</t>
   </si>
   <si>
     <t xml:space="preserve">24.182071685791</t>
@@ -2510,13 +2510,13 @@
     <t xml:space="preserve">24.4955425262451</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3164138793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3908061981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8238182067871</t>
+    <t xml:space="preserve">24.3164157867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3908081054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8238201141357</t>
   </si>
   <si>
     <t xml:space="preserve">23.0625305175781</t>
@@ -2531,10 +2531,10 @@
     <t xml:space="preserve">23.2416591644287</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1672687530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3167819976807</t>
+    <t xml:space="preserve">25.1672668457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3167858123779</t>
   </si>
   <si>
     <t xml:space="preserve">26.6002788543701</t>
@@ -2543,13 +2543,13 @@
     <t xml:space="preserve">25.615083694458</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4359550476074</t>
+    <t xml:space="preserve">25.4359569549561</t>
   </si>
   <si>
     <t xml:space="preserve">24.8985767364502</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9733371734619</t>
+    <t xml:space="preserve">25.9733352661133</t>
   </si>
   <si>
     <t xml:space="preserve">26.5107154846191</t>
@@ -2564,46 +2564,46 @@
     <t xml:space="preserve">26.6450595855713</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4959106445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0480937957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9437255859375</t>
+    <t xml:space="preserve">27.4959125518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.048095703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9437274932861</t>
   </si>
   <si>
     <t xml:space="preserve">28.8841400146484</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9289207458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7050151824951</t>
+    <t xml:space="preserve">28.9289226531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7050132751465</t>
   </si>
   <si>
     <t xml:space="preserve">29.7797737121582</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9885063171387</t>
+    <t xml:space="preserve">27.9885101318359</t>
   </si>
   <si>
     <t xml:space="preserve">27.630256652832</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2272205352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4063491821289</t>
+    <t xml:space="preserve">27.2272186279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4063472747803</t>
   </si>
   <si>
     <t xml:space="preserve">26.6898403167725</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8389930725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.79421043396</t>
+    <t xml:space="preserve">25.8389892578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7942085266113</t>
   </si>
   <si>
     <t xml:space="preserve">26.3315868377686</t>
@@ -2612,10 +2612,10 @@
     <t xml:space="preserve">24.7194519042969</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4507598876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5999126434326</t>
+    <t xml:space="preserve">24.4507579803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.599910736084</t>
   </si>
   <si>
     <t xml:space="preserve">23.4655647277832</t>
@@ -2624,7 +2624,7 @@
     <t xml:space="preserve">27.3615646362305</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0332908630371</t>
+    <t xml:space="preserve">28.0332870483398</t>
   </si>
   <si>
     <t xml:space="preserve">27.8541641235352</t>
@@ -2645,7 +2645,7 @@
     <t xml:space="preserve">27.3454132080078</t>
   </si>
   <si>
-    <t xml:space="preserve">29.662052154541</t>
+    <t xml:space="preserve">29.6620502471924</t>
   </si>
   <si>
     <t xml:space="preserve">29.480354309082</t>
@@ -2654,19 +2654,19 @@
     <t xml:space="preserve">29.3440799713135</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5251121520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.57053565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0247821807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0702018737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8885059356689</t>
+    <t xml:space="preserve">30.525110244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5705375671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0247802734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0702037811279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8885040283203</t>
   </si>
   <si>
     <t xml:space="preserve">28.9352626800537</t>
@@ -2678,13 +2678,13 @@
     <t xml:space="preserve">27.9359283447266</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4362602233887</t>
+    <t xml:space="preserve">27.4362621307373</t>
   </si>
   <si>
     <t xml:space="preserve">28.0722007751465</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4355945587158</t>
+    <t xml:space="preserve">28.4355926513672</t>
   </si>
   <si>
     <t xml:space="preserve">28.5264415740967</t>
@@ -2693,7 +2693,7 @@
     <t xml:space="preserve">28.4810199737549</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3901710510254</t>
+    <t xml:space="preserve">28.390172958374</t>
   </si>
   <si>
     <t xml:space="preserve">29.1623821258545</t>
@@ -2705,7 +2705,7 @@
     <t xml:space="preserve">28.2538986206055</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1169605255127</t>
+    <t xml:space="preserve">29.1169586181641</t>
   </si>
   <si>
     <t xml:space="preserve">30.1162948608398</t>
@@ -2714,16 +2714,16 @@
     <t xml:space="preserve">30.9793529510498</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1610488891602</t>
+    <t xml:space="preserve">31.1610507965088</t>
   </si>
   <si>
     <t xml:space="preserve">31.479024887085</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5698719024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7969932556152</t>
+    <t xml:space="preserve">31.5698699951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7969913482666</t>
   </si>
   <si>
     <t xml:space="preserve">31.7515678405762</t>
@@ -2732,13 +2732,13 @@
     <t xml:space="preserve">31.1156272888184</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2505645751953</t>
+    <t xml:space="preserve">33.2505683898926</t>
   </si>
   <si>
     <t xml:space="preserve">34.6587219238281</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8410835266113</t>
+    <t xml:space="preserve">33.8410873413086</t>
   </si>
   <si>
     <t xml:space="preserve">34.4770278930664</t>
@@ -2750,10 +2750,10 @@
     <t xml:space="preserve">34.5678672790527</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6132926940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.340087890625</t>
+    <t xml:space="preserve">34.6132965087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3400840759277</t>
   </si>
   <si>
     <t xml:space="preserve">34.4316024780273</t>
@@ -2762,31 +2762,31 @@
     <t xml:space="preserve">33.7048072814941</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9773559570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9312705993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5224494934082</t>
+    <t xml:space="preserve">33.9773597717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.931266784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5224456787109</t>
   </si>
   <si>
     <t xml:space="preserve">34.0682067871094</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7502326965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9319305419922</t>
+    <t xml:space="preserve">33.7502365112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9319267272949</t>
   </si>
   <si>
     <t xml:space="preserve">34.2499008178711</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6139640808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2485733032227</t>
+    <t xml:space="preserve">33.6139602661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2485694885254</t>
   </si>
   <si>
     <t xml:space="preserve">36.6573867797852</t>
@@ -2798,13 +2798,13 @@
     <t xml:space="preserve">38.6106300354004</t>
   </si>
   <si>
-    <t xml:space="preserve">39.5645408630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1109657287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4302635192871</t>
+    <t xml:space="preserve">39.5645370483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.110969543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4302673339844</t>
   </si>
   <si>
     <t xml:space="preserve">33.3868408203125</t>
@@ -2828,7 +2828,7 @@
     <t xml:space="preserve">34.340747833252</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7509002685547</t>
+    <t xml:space="preserve">32.7508964538574</t>
   </si>
   <si>
     <t xml:space="preserve">32.6600532531738</t>
@@ -2837,7 +2837,7 @@
     <t xml:space="preserve">32.9780197143555</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7976570129395</t>
+    <t xml:space="preserve">30.7976589202881</t>
   </si>
   <si>
     <t xml:space="preserve">29.3895034790039</t>
@@ -2846,13 +2846,13 @@
     <t xml:space="preserve">29.5257778167725</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6172904968262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3447456359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0254459381104</t>
+    <t xml:space="preserve">28.6172943115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.344747543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0254440307617</t>
   </si>
   <si>
     <t xml:space="preserve">31.9332637786865</t>
@@ -2867,13 +2867,13 @@
     <t xml:space="preserve">32.2512359619141</t>
   </si>
   <si>
-    <t xml:space="preserve">31.615291595459</t>
+    <t xml:space="preserve">31.6152935028076</t>
   </si>
   <si>
     <t xml:space="preserve">32.024112701416</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1142997741699</t>
+    <t xml:space="preserve">33.1142959594727</t>
   </si>
   <si>
     <t xml:space="preserve">32.614631652832</t>
@@ -2885,34 +2885,34 @@
     <t xml:space="preserve">32.0695381164551</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5244464874268</t>
+    <t xml:space="preserve">31.5244445800781</t>
   </si>
   <si>
     <t xml:space="preserve">31.3427467346191</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3420829772949</t>
+    <t xml:space="preserve">32.3420791625977</t>
   </si>
   <si>
     <t xml:space="preserve">32.5237770080566</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7054786682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1603851318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.159049987793</t>
+    <t xml:space="preserve">32.7054748535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1603889465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1590538024902</t>
   </si>
   <si>
     <t xml:space="preserve">33.7956581115723</t>
   </si>
   <si>
-    <t xml:space="preserve">34.976692199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9325942993164</t>
+    <t xml:space="preserve">34.9766883850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9325981140137</t>
   </si>
   <si>
     <t xml:space="preserve">33.0234451293945</t>
@@ -2921,34 +2921,34 @@
     <t xml:space="preserve">33.5231170654297</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4783554077148</t>
+    <t xml:space="preserve">32.4783592224121</t>
   </si>
   <si>
     <t xml:space="preserve">32.4329299926758</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8424167633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8878383636475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4342651367188</t>
+    <t xml:space="preserve">31.842414855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8878402709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4342632293701</t>
   </si>
   <si>
     <t xml:space="preserve">29.7074756622314</t>
   </si>
   <si>
-    <t xml:space="preserve">30.70680809021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4796867370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6166248321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8437442779541</t>
+    <t xml:space="preserve">30.7068061828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4796886444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.616626739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8437461853027</t>
   </si>
   <si>
     <t xml:space="preserve">29.2532329559326</t>
@@ -2957,7 +2957,7 @@
     <t xml:space="preserve">28.7535629272461</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0708656311035</t>
+    <t xml:space="preserve">30.0708675384521</t>
   </si>
   <si>
     <t xml:space="preserve">28.8898372650146</t>
@@ -2969,7 +2969,7 @@
     <t xml:space="preserve">28.8444137573242</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7081432342529</t>
+    <t xml:space="preserve">28.7081413269043</t>
   </si>
   <si>
     <t xml:space="preserve">28.9806861877441</t>
@@ -2990,7 +2990,7 @@
     <t xml:space="preserve">28.0267772674561</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6179580688477</t>
+    <t xml:space="preserve">27.617956161499</t>
   </si>
   <si>
     <t xml:space="preserve">27.7542304992676</t>
@@ -3008,16 +3008,16 @@
     <t xml:space="preserve">27.5725345611572</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6186237335205</t>
+    <t xml:space="preserve">26.6186218261719</t>
   </si>
   <si>
     <t xml:space="preserve">27.1182918548584</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0274410247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9365940093994</t>
+    <t xml:space="preserve">27.0274429321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9365921020508</t>
   </si>
   <si>
     <t xml:space="preserve">26.9820194244385</t>
@@ -3026,16 +3026,16 @@
     <t xml:space="preserve">26.3460788726807</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8918342590332</t>
+    <t xml:space="preserve">25.8918361663818</t>
   </si>
   <si>
     <t xml:space="preserve">25.6647148132324</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2552299499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8457450866699</t>
+    <t xml:space="preserve">26.2552280426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8457431793213</t>
   </si>
   <si>
     <t xml:space="preserve">26.6640491485596</t>
@@ -3047,28 +3047,28 @@
     <t xml:space="preserve">26.5732002258301</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3915004730225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.70947265625</t>
+    <t xml:space="preserve">26.3915023803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7094707489014</t>
   </si>
   <si>
     <t xml:space="preserve">26.527774810791</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9826831817627</t>
+    <t xml:space="preserve">25.9826850891113</t>
   </si>
   <si>
     <t xml:space="preserve">25.8009872436523</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1657123565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6660442352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8477458953857</t>
+    <t xml:space="preserve">24.165714263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6660461425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8477439880371</t>
   </si>
   <si>
     <t xml:space="preserve">25.437593460083</t>
@@ -3077,7 +3077,7 @@
     <t xml:space="preserve">25.7555637359619</t>
   </si>
   <si>
-    <t xml:space="preserve">25.074197769165</t>
+    <t xml:space="preserve">25.0741996765137</t>
   </si>
   <si>
     <t xml:space="preserve">26.0735340118408</t>
@@ -3089,7 +3089,7 @@
     <t xml:space="preserve">26.3419418334961</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6671524047852</t>
+    <t xml:space="preserve">26.6671504974365</t>
   </si>
   <si>
     <t xml:space="preserve">27.1317348480225</t>
@@ -3098,7 +3098,7 @@
     <t xml:space="preserve">27.6427764892578</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3396530151367</t>
+    <t xml:space="preserve">28.3396549224854</t>
   </si>
   <si>
     <t xml:space="preserve">27.8286113739014</t>
@@ -3152,7 +3152,7 @@
     <t xml:space="preserve">27.038818359375</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9459018707275</t>
+    <t xml:space="preserve">26.9458999633789</t>
   </si>
   <si>
     <t xml:space="preserve">26.760066986084</t>
@@ -3164,19 +3164,19 @@
     <t xml:space="preserve">26.2025661468506</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5742321014404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.481315612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8994426727295</t>
+    <t xml:space="preserve">26.5742340087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4813175201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8994445800781</t>
   </si>
   <si>
     <t xml:space="preserve">26.2490253448486</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7379837036133</t>
+    <t xml:space="preserve">25.7379817962646</t>
   </si>
   <si>
     <t xml:space="preserve">25.9238147735596</t>
@@ -3191,7 +3191,7 @@
     <t xml:space="preserve">27.271110534668</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2246513366699</t>
+    <t xml:space="preserve">27.2246494293213</t>
   </si>
   <si>
     <t xml:space="preserve">25.4127731323242</t>
@@ -3203,7 +3203,7 @@
     <t xml:space="preserve">24.5300617218018</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9017295837402</t>
+    <t xml:space="preserve">24.9017276763916</t>
   </si>
   <si>
     <t xml:space="preserve">25.0875625610352</t>
@@ -3212,76 +3212,76 @@
     <t xml:space="preserve">24.8088130950928</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5521469116211</t>
+    <t xml:space="preserve">25.5521488189697</t>
   </si>
   <si>
     <t xml:space="preserve">25.5056896209717</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7623538970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7158946990967</t>
+    <t xml:space="preserve">24.7623519897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7158966064453</t>
   </si>
   <si>
     <t xml:space="preserve">25.8308982849121</t>
   </si>
   <si>
-    <t xml:space="preserve">27.085277557373</t>
+    <t xml:space="preserve">27.0852756500244</t>
   </si>
   <si>
     <t xml:space="preserve">26.7136077880859</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0167331695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8773574829102</t>
+    <t xml:space="preserve">26.016731262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8773555755615</t>
   </si>
   <si>
     <t xml:space="preserve">25.7844390869141</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0631885528564</t>
+    <t xml:space="preserve">26.0631904602051</t>
   </si>
   <si>
     <t xml:space="preserve">26.1096496582031</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1340198516846</t>
+    <t xml:space="preserve">25.1340217590332</t>
   </si>
   <si>
     <t xml:space="preserve">25.0411052703857</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2977676391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4836044311523</t>
+    <t xml:space="preserve">24.2977695465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4836025238037</t>
   </si>
   <si>
     <t xml:space="preserve">24.0654773712158</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2513122558594</t>
+    <t xml:space="preserve">24.2513103485107</t>
   </si>
   <si>
     <t xml:space="preserve">24.5765209197998</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6008911132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0433921813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0898494720459</t>
+    <t xml:space="preserve">23.6008930206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0433902740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0898513793945</t>
   </si>
   <si>
     <t xml:space="preserve">22.114221572876</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0213050842285</t>
+    <t xml:space="preserve">22.0213069915771</t>
   </si>
   <si>
     <t xml:space="preserve">23.2756824493408</t>
@@ -3290,28 +3290,28 @@
     <t xml:space="preserve">23.4615173339844</t>
   </si>
   <si>
-    <t xml:space="preserve">23.415060043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1363086700439</t>
+    <t xml:space="preserve">23.4150581359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1363067626953</t>
   </si>
   <si>
     <t xml:space="preserve">23.6473522186279</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9504737854004</t>
+    <t xml:space="preserve">22.950475692749</t>
   </si>
   <si>
     <t xml:space="preserve">22.5788059234619</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2071399688721</t>
+    <t xml:space="preserve">22.2071380615234</t>
   </si>
   <si>
     <t xml:space="preserve">21.64963722229</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8598461151123</t>
+    <t xml:space="preserve">20.8598442077637</t>
   </si>
   <si>
     <t xml:space="preserve">21.0921363830566</t>
@@ -3326,7 +3326,7 @@
     <t xml:space="preserve">21.5567207336426</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7425537109375</t>
+    <t xml:space="preserve">21.7425556182861</t>
   </si>
   <si>
     <t xml:space="preserve">21.9283885955811</t>
@@ -3347,37 +3347,37 @@
     <t xml:space="preserve">21.4173450469971</t>
   </si>
   <si>
-    <t xml:space="preserve">21.603178024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.835470199585</t>
+    <t xml:space="preserve">21.6031799316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8354721069336</t>
   </si>
   <si>
     <t xml:space="preserve">22.160680770874</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7181835174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3000564575195</t>
+    <t xml:space="preserve">22.7181816101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3000545501709</t>
   </si>
   <si>
     <t xml:space="preserve">22.3465137481689</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2535972595215</t>
+    <t xml:space="preserve">22.2535991668701</t>
   </si>
   <si>
     <t xml:space="preserve">21.881929397583</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7890148162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1827659606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5986061096191</t>
+    <t xml:space="preserve">21.7890129089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.182767868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5986042022705</t>
   </si>
   <si>
     <t xml:space="preserve">25.3663120269775</t>
@@ -3398,10 +3398,10 @@
     <t xml:space="preserve">24.4371433258057</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8796424865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2048511505127</t>
+    <t xml:space="preserve">23.8796443939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2048530578613</t>
   </si>
   <si>
     <t xml:space="preserve">23.9261016845703</t>
@@ -3410,7 +3410,7 @@
     <t xml:space="preserve">24.6694355010986</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5544357299805</t>
+    <t xml:space="preserve">23.5544338226318</t>
   </si>
   <si>
     <t xml:space="preserve">23.6938095092773</t>
@@ -3419,7 +3419,7 @@
     <t xml:space="preserve">23.3221416473389</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7867259979248</t>
+    <t xml:space="preserve">23.7867279052734</t>
   </si>
   <si>
     <t xml:space="preserve">22.8575572967529</t>
@@ -3428,7 +3428,7 @@
     <t xml:space="preserve">21.5102615356445</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3708877563477</t>
+    <t xml:space="preserve">21.370885848999</t>
   </si>
   <si>
     <t xml:space="preserve">21.1850528717041</t>
@@ -3437,19 +3437,19 @@
     <t xml:space="preserve">20.7204685211182</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4881744384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9771327972412</t>
+    <t xml:space="preserve">20.4881763458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9771347045898</t>
   </si>
   <si>
     <t xml:space="preserve">20.2558822631836</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5346355438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9306774139404</t>
+    <t xml:space="preserve">20.5346336364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9306755065918</t>
   </si>
   <si>
     <t xml:space="preserve">20.5810928344727</t>
@@ -3461,7 +3461,7 @@
     <t xml:space="preserve">20.6275520324707</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0235919952393</t>
+    <t xml:space="preserve">20.0235900878906</t>
   </si>
   <si>
     <t xml:space="preserve">18.6298370361328</t>
@@ -3479,7 +3479,7 @@
     <t xml:space="preserve">17.8772106170654</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5427112579346</t>
+    <t xml:space="preserve">17.5427093505859</t>
   </si>
   <si>
     <t xml:space="preserve">17.2453765869141</t>
@@ -3491,10 +3491,10 @@
     <t xml:space="preserve">17.5612926483154</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4126262664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7471294403076</t>
+    <t xml:space="preserve">17.4126281738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.747127532959</t>
   </si>
   <si>
     <t xml:space="preserve">17.1896266937256</t>
@@ -3515,13 +3515,13 @@
     <t xml:space="preserve">16.3162078857422</t>
   </si>
   <si>
-    <t xml:space="preserve">15.981707572937</t>
+    <t xml:space="preserve">15.9817085266113</t>
   </si>
   <si>
     <t xml:space="preserve">16.5392074584961</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2976264953613</t>
+    <t xml:space="preserve">16.2976245880127</t>
   </si>
   <si>
     <t xml:space="preserve">16.1861248016357</t>
@@ -3533,7 +3533,7 @@
     <t xml:space="preserve">16.1489562988281</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2418727874756</t>
+    <t xml:space="preserve">16.2418746948242</t>
   </si>
   <si>
     <t xml:space="preserve">16.0746231079102</t>
@@ -4287,6 +4287,9 @@
   </si>
   <si>
     <t xml:space="preserve">21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5499992370605</t>
   </si>
 </sst>
 </file>
@@ -69625,7 +69628,7 @@
     </row>
     <row r="2501">
       <c r="A2501" s="1" t="n">
-        <v>45960.6910300926</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B2501" t="n">
         <v>33832</v>
@@ -69646,6 +69649,32 @@
         <v>1380</v>
       </c>
       <c r="H2501" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" s="1" t="n">
+        <v>45961.6909837963</v>
+      </c>
+      <c r="B2502" t="n">
+        <v>29934</v>
+      </c>
+      <c r="C2502" t="n">
+        <v>21.3999996185303</v>
+      </c>
+      <c r="D2502" t="n">
+        <v>20.3999996185303</v>
+      </c>
+      <c r="E2502" t="n">
+        <v>21.3999996185303</v>
+      </c>
+      <c r="F2502" t="n">
+        <v>20.5499992370605</v>
+      </c>
+      <c r="G2502" t="s">
+        <v>1425</v>
+      </c>
+      <c r="H2502" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ARN.MI.xlsx
+++ b/data/ARN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1426" uniqueCount="1426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1427" uniqueCount="1427">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,67 +38,67 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92215013504028</t>
+    <t xml:space="preserve">1.92215037345886</t>
   </si>
   <si>
     <t xml:space="preserve">ARN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94450104236603</t>
+    <t xml:space="preserve">1.94450056552887</t>
   </si>
   <si>
     <t xml:space="preserve">1.917360663414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90778195858002</t>
+    <t xml:space="preserve">1.90778255462646</t>
   </si>
   <si>
     <t xml:space="preserve">1.8838347196579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93172883987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91576409339905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83434438705444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83594059944153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91097497940063</t>
+    <t xml:space="preserve">1.93172943592072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91576421260834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83434391021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83594083786011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91097521781921</t>
   </si>
   <si>
     <t xml:space="preserve">1.807204246521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74973130226135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71620535850525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80401134490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81039714813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79602921009064</t>
+    <t xml:space="preserve">1.74973118305206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71620571613312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80401122570038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81039690971375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79602909088135</t>
   </si>
   <si>
     <t xml:space="preserve">1.77208209037781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70662665367126</t>
+    <t xml:space="preserve">1.70662677288055</t>
   </si>
   <si>
     <t xml:space="preserve">1.69704782962799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69066190719604</t>
+    <t xml:space="preserve">1.69066178798676</t>
   </si>
   <si>
     <t xml:space="preserve">1.67629361152649</t>
@@ -110,55 +110,55 @@
     <t xml:space="preserve">1.69864428043365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6746973991394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66671478748322</t>
+    <t xml:space="preserve">1.67469751834869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6667149066925</t>
   </si>
   <si>
     <t xml:space="preserve">1.66032886505127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81518685817719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82795858383179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8614844083786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88543128967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89181709289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92853605747223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95407938957214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90618562698364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86786985397339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88064217567444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85190546512604</t>
+    <t xml:space="preserve">1.81518650054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82795810699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86148428916931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88543152809143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89181697368622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92853629589081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95407974720001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90618538856506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86787021160126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88064169883728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85190522670746</t>
   </si>
   <si>
     <t xml:space="preserve">1.85988783836365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85509836673737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79283607006073</t>
+    <t xml:space="preserve">1.8550980091095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79283618927002</t>
   </si>
   <si>
     <t xml:space="preserve">1.78804659843445</t>
@@ -170,25 +170,25 @@
     <t xml:space="preserve">1.7561172246933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76888906955719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76409935951233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78485381603241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77048563957214</t>
+    <t xml:space="preserve">1.7688889503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76409959793091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78485369682312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77048552036285</t>
   </si>
   <si>
     <t xml:space="preserve">1.72099471092224</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73536312580109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.802414894104</t>
+    <t xml:space="preserve">1.73536324501038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80241465568542</t>
   </si>
   <si>
     <t xml:space="preserve">1.76250314712524</t>
@@ -197,214 +197,214 @@
     <t xml:space="preserve">1.74494194984436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73217046260834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73695981502533</t>
+    <t xml:space="preserve">1.73217010498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73695957660675</t>
   </si>
   <si>
     <t xml:space="preserve">1.74334537982941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7513279914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68587255477905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67789018154144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65234649181366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6204172372818</t>
+    <t xml:space="preserve">1.75132775306702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68587243556976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67789006233215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65234661102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62041711807251</t>
   </si>
   <si>
     <t xml:space="preserve">1.64276778697968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59008419513702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60285580158234</t>
+    <t xml:space="preserve">1.59008431434631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60285604000092</t>
   </si>
   <si>
     <t xml:space="preserve">1.54937422275543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51185739040375</t>
+    <t xml:space="preserve">1.51185727119446</t>
   </si>
   <si>
     <t xml:space="preserve">1.45598077774048</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43682324886322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4695508480072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4974889755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47673499584198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47274363040924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46875274181366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49669086933136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47593665122986</t>
+    <t xml:space="preserve">1.43682301044464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46955072879791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49748933315277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47673511505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47274386882782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46875250339508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49669098854065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47593688964844</t>
   </si>
   <si>
     <t xml:space="preserve">1.50626957416534</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47753322124481</t>
+    <t xml:space="preserve">1.4775333404541</t>
   </si>
   <si>
     <t xml:space="preserve">1.43841958045959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40090274810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34901738166809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30910551548004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34342956542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32666683197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3410347700119</t>
+    <t xml:space="preserve">1.40090250968933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3490172624588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30910563468933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34342968463898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32666671276093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34103488922119</t>
   </si>
   <si>
     <t xml:space="preserve">1.31708788871765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38653433322906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39691138267517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40649008750916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30671072006226</t>
+    <t xml:space="preserve">1.38653445243835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39691162109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40649032592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30671083927155</t>
   </si>
   <si>
     <t xml:space="preserve">1.3234738111496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.305912733078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31229853630066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28994810581207</t>
+    <t xml:space="preserve">1.30591261386871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31229865550995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28994798660278</t>
   </si>
   <si>
     <t xml:space="preserve">1.2851585149765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28595662117004</t>
+    <t xml:space="preserve">1.28595674037933</t>
   </si>
   <si>
     <t xml:space="preserve">1.33305263519287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33704376220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30112326145172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36104869842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34627246856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35283970832825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33806383609772</t>
+    <t xml:space="preserve">1.33704352378845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30112314224243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36104881763458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34627258777618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35283982753754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33806371688843</t>
   </si>
   <si>
     <t xml:space="preserve">1.27157092094421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28880977630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29291427135468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30686950683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3388843536377</t>
+    <t xml:space="preserve">1.28880989551544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29291415214539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30686938762665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33888447284698</t>
   </si>
   <si>
     <t xml:space="preserve">1.34955620765686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34380996227264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33642184734344</t>
+    <t xml:space="preserve">1.34380984306335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33642196655273</t>
   </si>
   <si>
     <t xml:space="preserve">1.34709346294403</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30522787570953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29127240180969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31425750255585</t>
+    <t xml:space="preserve">1.30522775650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29127252101898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31425762176514</t>
   </si>
   <si>
     <t xml:space="preserve">1.32164573669434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26828730106354</t>
+    <t xml:space="preserve">1.26828742027283</t>
   </si>
   <si>
     <t xml:space="preserve">1.27239179611206</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28798866271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29701888561249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24858582019806</t>
+    <t xml:space="preserve">1.28798890113831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2970187664032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24858570098877</t>
   </si>
   <si>
     <t xml:space="preserve">1.32657122612</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33231723308563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35940706729889</t>
+    <t xml:space="preserve">1.33231747150421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3594069480896</t>
   </si>
   <si>
     <t xml:space="preserve">1.4201534986496</t>
@@ -413,37 +413,37 @@
     <t xml:space="preserve">1.48664605617523</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53343737125397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51619851589203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51866114139557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43739223480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46776556968689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43000411987305</t>
+    <t xml:space="preserve">1.53343749046326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51619863510132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51866137981415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43739247322083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4677654504776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43000423908234</t>
   </si>
   <si>
     <t xml:space="preserve">1.40948164463043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44478046894073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5597060918808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61798965930939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70582592487335</t>
+    <t xml:space="preserve">1.44478034973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55970597267151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61798989772797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70582604408264</t>
   </si>
   <si>
     <t xml:space="preserve">1.74851262569427</t>
@@ -455,34 +455,34 @@
     <t xml:space="preserve">1.6828408241272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67463171482086</t>
+    <t xml:space="preserve">1.67463183403015</t>
   </si>
   <si>
     <t xml:space="preserve">1.651646733284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64179587364197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67134821414948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66478109359741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65657198429108</t>
+    <t xml:space="preserve">1.64179575443268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67134833335876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6647812128067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65657210350037</t>
   </si>
   <si>
     <t xml:space="preserve">1.69597506523132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69433307647705</t>
+    <t xml:space="preserve">1.69433343410492</t>
   </si>
   <si>
     <t xml:space="preserve">1.65821373462677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68119895458221</t>
+    <t xml:space="preserve">1.6811990737915</t>
   </si>
   <si>
     <t xml:space="preserve">1.68776619434357</t>
@@ -491,166 +491,166 @@
     <t xml:space="preserve">1.66806471347809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65000474452972</t>
+    <t xml:space="preserve">1.6500049829483</t>
   </si>
   <si>
     <t xml:space="preserve">1.66313922405243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67791545391083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03746867179871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04403591156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03911018371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04075241088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05224514007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04731917381287</t>
+    <t xml:space="preserve">1.67791533470154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03746891021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04403614997864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0391104221344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04075217247009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0522449016571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04731941223145</t>
   </si>
   <si>
     <t xml:space="preserve">2.04239416122437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19836449623108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24105143547058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18851399421692</t>
+    <t xml:space="preserve">2.19836473464966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24105167388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18851375579834</t>
   </si>
   <si>
     <t xml:space="preserve">2.17537975311279</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14582705497742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00627422332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98821473121643</t>
+    <t xml:space="preserve">2.145827293396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00627446174622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98821496963501</t>
   </si>
   <si>
     <t xml:space="preserve">1.99314022064209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99806535243988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99642372131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99970769882202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00299096107483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00791645050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01119995117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02597594261169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03254318237305</t>
+    <t xml:space="preserve">1.99806547164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9964234828949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99970746040344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00299072265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00791668891907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01120018959045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02597570419312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03254342079163</t>
   </si>
   <si>
     <t xml:space="preserve">2.02105069160461</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01940894126892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02433443069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07687211036682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0588116645813</t>
+    <t xml:space="preserve">2.01940870285034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.024334192276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07687163352966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05881237983704</t>
   </si>
   <si>
     <t xml:space="preserve">2.09657335281372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14746904373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33955907821655</t>
+    <t xml:space="preserve">2.14746880531311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33955883979797</t>
   </si>
   <si>
     <t xml:space="preserve">2.27552890777588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32478284835815</t>
+    <t xml:space="preserve">2.32478332519531</t>
   </si>
   <si>
     <t xml:space="preserve">2.278813123703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25746965408325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29851412773132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26075267791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28045463562012</t>
+    <t xml:space="preserve">2.25746941566467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2985143661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26075291633606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2804548740387</t>
   </si>
   <si>
     <t xml:space="preserve">2.30672311782837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35597705841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34120106697083</t>
+    <t xml:space="preserve">2.35597729682922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34120082855225</t>
   </si>
   <si>
     <t xml:space="preserve">2.3428430557251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34776782989502</t>
+    <t xml:space="preserve">2.34776830673218</t>
   </si>
   <si>
     <t xml:space="preserve">2.44627594947815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39209699630737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38224577903748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38717126846313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38388776779175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40523147583008</t>
+    <t xml:space="preserve">2.39209675788879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3822455406189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38717103004456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38388752937317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40523099899292</t>
   </si>
   <si>
     <t xml:space="preserve">2.38060402870178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42164921760559</t>
+    <t xml:space="preserve">2.42164874076843</t>
   </si>
   <si>
     <t xml:space="preserve">2.33791732788086</t>
@@ -659,10 +659,10 @@
     <t xml:space="preserve">2.32314109802246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35433530807495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41015648841858</t>
+    <t xml:space="preserve">2.35433554649353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41015625</t>
   </si>
   <si>
     <t xml:space="preserve">2.40687274932861</t>
@@ -674,43 +674,43 @@
     <t xml:space="preserve">2.4183657169342</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29030537605286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34940958023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36418604850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37567901611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40194749832153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35761904716492</t>
+    <t xml:space="preserve">2.29030513763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34941005706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36418628692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3756787776947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40194725990295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35761880874634</t>
   </si>
   <si>
     <t xml:space="preserve">2.36746978759766</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37075328826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37239527702332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36254382133484</t>
+    <t xml:space="preserve">2.37075352668762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37239551544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.362544298172</t>
   </si>
   <si>
     <t xml:space="preserve">2.36582779884338</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3953800201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3773205280304</t>
+    <t xml:space="preserve">2.39538025856018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37732028961182</t>
   </si>
   <si>
     <t xml:space="preserve">2.37403678894043</t>
@@ -719,10 +719,10 @@
     <t xml:space="preserve">2.38881301879883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39373826980591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3904550075531</t>
+    <t xml:space="preserve">2.39373850822449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39045453071594</t>
   </si>
   <si>
     <t xml:space="preserve">2.41343975067139</t>
@@ -734,10 +734,10 @@
     <t xml:space="preserve">2.40030550956726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40851473808289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42329049110413</t>
+    <t xml:space="preserve">2.40851449966431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42329025268555</t>
   </si>
   <si>
     <t xml:space="preserve">2.43149948120117</t>
@@ -746,19 +746,19 @@
     <t xml:space="preserve">2.42000722885132</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35105204582214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33627533912659</t>
+    <t xml:space="preserve">2.35105180740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33627557754517</t>
   </si>
   <si>
     <t xml:space="preserve">2.34612655639648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43642473220825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42657446861267</t>
+    <t xml:space="preserve">2.43642544746399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42657423019409</t>
   </si>
   <si>
     <t xml:space="preserve">2.42985773086548</t>
@@ -773,46 +773,46 @@
     <t xml:space="preserve">2.47868013381958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49201512336731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49368238449097</t>
+    <t xml:space="preserve">2.49201536178589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49368166923523</t>
   </si>
   <si>
     <t xml:space="preserve">2.47534656524658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46534442901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48201322555542</t>
+    <t xml:space="preserve">2.46534490585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.482013463974</t>
   </si>
   <si>
     <t xml:space="preserve">2.46867847442627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4586775302887</t>
+    <t xml:space="preserve">2.45867729187012</t>
   </si>
   <si>
     <t xml:space="preserve">2.46201086044312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45534348487854</t>
+    <t xml:space="preserve">2.45534372329712</t>
   </si>
   <si>
     <t xml:space="preserve">2.41700482368469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40867042541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36699795722961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34199404716492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36866474151611</t>
+    <t xml:space="preserve">2.40867066383362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36699771881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3419942855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36866450309753</t>
   </si>
   <si>
     <t xml:space="preserve">2.35366249084473</t>
@@ -821,106 +821,106 @@
     <t xml:space="preserve">2.385333776474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38366651535034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36366391181946</t>
+    <t xml:space="preserve">2.3836669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36366367340088</t>
   </si>
   <si>
     <t xml:space="preserve">2.32532525062561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3169903755188</t>
+    <t xml:space="preserve">2.31699085235596</t>
   </si>
   <si>
     <t xml:space="preserve">2.28531980514526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28698658943176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29698777198792</t>
+    <t xml:space="preserve">2.28698635101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29698824882507</t>
   </si>
   <si>
     <t xml:space="preserve">2.31532382965088</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28365254402161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28865337371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29031991958618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30198836326599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30365562438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2936544418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24198031425476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2669837474823</t>
+    <t xml:space="preserve">2.28365230560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28865313529968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2903208732605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30198884010315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30365538597107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29365420341492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24198055267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26698398590088</t>
   </si>
   <si>
     <t xml:space="preserve">2.2686505317688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32699227333069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31865739822388</t>
+    <t xml:space="preserve">2.32699203491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31865763664246</t>
   </si>
   <si>
     <t xml:space="preserve">2.3103232383728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24364733695984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25031447410583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2253110408783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25198149681091</t>
+    <t xml:space="preserve">2.24364709854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25031495094299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22531127929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25198125839233</t>
   </si>
   <si>
     <t xml:space="preserve">2.2219774723053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20697522163391</t>
+    <t xml:space="preserve">2.20697546005249</t>
   </si>
   <si>
     <t xml:space="preserve">2.20030760765076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16863703727722</t>
+    <t xml:space="preserve">2.16863656044006</t>
   </si>
   <si>
     <t xml:space="preserve">2.17863821983337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16696953773499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18697261810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19697427749634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18363857269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18530583381653</t>
+    <t xml:space="preserve">2.16696977615356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18697237968445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1969735622406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18363881111145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18530559539795</t>
   </si>
   <si>
     <t xml:space="preserve">2.19197344779968</t>
@@ -929,43 +929,43 @@
     <t xml:space="preserve">2.17530417442322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14196634292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15363430976868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14363288879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13529872894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12696433067322</t>
+    <t xml:space="preserve">2.14196610450745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15363454818726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14363312721252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13529896736145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12696409225464</t>
   </si>
   <si>
     <t xml:space="preserve">2.12863111495972</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12029623985291</t>
+    <t xml:space="preserve">2.12029647827148</t>
   </si>
   <si>
     <t xml:space="preserve">2.13029813766479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11862945556641</t>
+    <t xml:space="preserve">2.11862969398499</t>
   </si>
   <si>
     <t xml:space="preserve">2.37366533279419</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37533235549927</t>
+    <t xml:space="preserve">2.37533187866211</t>
   </si>
   <si>
     <t xml:space="preserve">2.40700316429138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39533519744873</t>
+    <t xml:space="preserve">2.39533472061157</t>
   </si>
   <si>
     <t xml:space="preserve">2.39200115203857</t>
@@ -974,91 +974,91 @@
     <t xml:space="preserve">2.49868273735046</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49534916877747</t>
+    <t xml:space="preserve">2.49534893035889</t>
   </si>
   <si>
     <t xml:space="preserve">2.50868439674377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51201820373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51535153388977</t>
+    <t xml:space="preserve">2.51201772689819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51535177230835</t>
   </si>
   <si>
     <t xml:space="preserve">2.51701855659485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.523686170578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52535367012024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54535627365112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53368735313416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53202128410339</t>
+    <t xml:space="preserve">2.52368640899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5253529548645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54535555839539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53368759155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53202080726624</t>
   </si>
   <si>
     <t xml:space="preserve">2.54035544395447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52702045440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53868865966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53702163696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49701571464539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42700600624084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50034952163696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5053505897522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48368048667908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45200943946838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51368498802185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54202222824097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54868984222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51035118103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52035236358643</t>
+    <t xml:space="preserve">2.52702069282532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53868842124939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53702116012573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49701619148254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42700576782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50034976005554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50535035133362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48368096351624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45200991630554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51368474960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54202198982239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5486900806427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51035141944885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52035212516785</t>
   </si>
   <si>
     <t xml:space="preserve">2.47201228141785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50201630592346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48701429367065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0004198551178</t>
+    <t xml:space="preserve">2.50201654434204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48701477050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00041961669922</t>
   </si>
   <si>
     <t xml:space="preserve">2.81706070899963</t>
@@ -1070,46 +1070,46 @@
     <t xml:space="preserve">2.7170467376709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80872631072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80039119720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8337299823761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78372287750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84206414222717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7587194442749</t>
+    <t xml:space="preserve">2.8087260723114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80039167404175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83372974395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78372263908386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84206461906433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75871896743774</t>
   </si>
   <si>
     <t xml:space="preserve">2.85039854049683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85873317718506</t>
+    <t xml:space="preserve">2.85873341560364</t>
   </si>
   <si>
     <t xml:space="preserve">2.89207124710083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82539534568787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72538137435913</t>
+    <t xml:space="preserve">2.82539510726929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72538089752197</t>
   </si>
   <si>
     <t xml:space="preserve">2.61703276634216</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6420361995697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70037746429443</t>
+    <t xml:space="preserve">2.64203643798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70037794113159</t>
   </si>
   <si>
     <t xml:space="preserve">2.65870523452759</t>
@@ -1118,7 +1118,7 @@
     <t xml:space="preserve">2.6253674030304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63370156288147</t>
+    <t xml:space="preserve">2.63370203971863</t>
   </si>
   <si>
     <t xml:space="preserve">2.59202909469604</t>
@@ -1127,46 +1127,46 @@
     <t xml:space="preserve">2.66703963279724</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70871233940125</t>
+    <t xml:space="preserve">2.70871257781982</t>
   </si>
   <si>
     <t xml:space="preserve">2.74204993247986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65037083625793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68370866775513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6003634929657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58369445800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56702613830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76705384254456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73371553421021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79205703735352</t>
+    <t xml:space="preserve">2.65037059783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68370842933655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60036325454712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58369493484497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56702566146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76705360412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73371577262878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79205679893494</t>
   </si>
   <si>
     <t xml:space="preserve">2.86706781387329</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8754026889801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88373684883118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77538800239563</t>
+    <t xml:space="preserve">2.87540221214294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8837366104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77538847923279</t>
   </si>
   <si>
     <t xml:space="preserve">2.78091359138489</t>
@@ -1178,10 +1178,10 @@
     <t xml:space="preserve">2.73019814491272</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77246117591858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.645672082901</t>
+    <t xml:space="preserve">2.77246141433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64567232131958</t>
   </si>
   <si>
     <t xml:space="preserve">2.70484018325806</t>
@@ -1190,16 +1190,16 @@
     <t xml:space="preserve">2.68793511390686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66257739067078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69638752937317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65412449836731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60340905189514</t>
+    <t xml:space="preserve">2.6625771522522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69638776779175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65412473678589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60340881347656</t>
   </si>
   <si>
     <t xml:space="preserve">2.63721895217896</t>
@@ -1208,13 +1208,13 @@
     <t xml:space="preserve">2.61186146736145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5780508518219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5949559211731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50197720527649</t>
+    <t xml:space="preserve">2.57805061340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59495615959167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50197744369507</t>
   </si>
   <si>
     <t xml:space="preserve">2.49352478981018</t>
@@ -1223,37 +1223,37 @@
     <t xml:space="preserve">2.54424047470093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56114602088928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58650326728821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51888227462769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53578758239746</t>
+    <t xml:space="preserve">2.56114554405212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58650374412537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51888251304626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53578782081604</t>
   </si>
   <si>
     <t xml:space="preserve">2.55269289016724</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51043009757996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56959795951843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46816658973694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48507213592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41745066642761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45126152038574</t>
+    <t xml:space="preserve">2.51042985916138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56959843635559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46816682815552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48507189750671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41745090484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45126128196716</t>
   </si>
   <si>
     <t xml:space="preserve">2.39209294319153</t>
@@ -1262,10 +1262,10 @@
     <t xml:space="preserve">2.38364052772522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27375626564026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29911422729492</t>
+    <t xml:space="preserve">2.27375650405884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2991144657135</t>
   </si>
   <si>
     <t xml:space="preserve">2.36673521995544</t>
@@ -1274,157 +1274,157 @@
     <t xml:space="preserve">2.35828256607056</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43435621261597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42590355873108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34982967376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28220868110657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32447218894958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40899848937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45971417427063</t>
+    <t xml:space="preserve">2.43435573577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4259033203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34982991218567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28220891952515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32447195053101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40899801254272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45971393585205</t>
   </si>
   <si>
     <t xml:space="preserve">2.44280910491943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33292460441589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34137749671936</t>
+    <t xml:space="preserve">2.33292484283447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3413770198822</t>
   </si>
   <si>
     <t xml:space="preserve">2.400545835495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37518763542175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47661900520325</t>
+    <t xml:space="preserve">2.37518787384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47661948204041</t>
   </si>
   <si>
     <t xml:space="preserve">2.30756664276123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23994612693787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29430222511292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23437666893005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24293684959412</t>
+    <t xml:space="preserve">2.23994588851929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29430198669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23437643051147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2429370880127</t>
   </si>
   <si>
     <t xml:space="preserve">2.33710646629333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25149846076965</t>
+    <t xml:space="preserve">2.25149822235107</t>
   </si>
   <si>
     <t xml:space="preserve">2.27718067169189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26862001419067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44839692115784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37134981155396</t>
+    <t xml:space="preserve">2.26861977577209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44839715957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3713493347168</t>
   </si>
   <si>
     <t xml:space="preserve">2.31142401695251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28574156761169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26005887985229</t>
+    <t xml:space="preserve">2.28574180603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26005911827087</t>
   </si>
   <si>
     <t xml:space="preserve">2.35422801971436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2258152961731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20869421958923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30286312103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31998491287231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37991046905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.405592918396</t>
+    <t xml:space="preserve">2.22581553459167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20869374275208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30286335945129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31998467445374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37991070747375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40559315681458</t>
   </si>
   <si>
     <t xml:space="preserve">2.39703226089478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32854557037354</t>
+    <t xml:space="preserve">2.32854580879211</t>
   </si>
   <si>
     <t xml:space="preserve">2.38847136497498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36278891563416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34566736221313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20013332366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18301105499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4398365020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54256653785706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60249209403992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69666171073914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77370882034302</t>
+    <t xml:space="preserve">2.36278915405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34566712379456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20013308525085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18301153182983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43983626365662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54256629943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6024923324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69666123390198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77370858192444</t>
   </si>
   <si>
     <t xml:space="preserve">2.63673567771912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67097854614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61961364746094</t>
+    <t xml:space="preserve">2.670978307724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61961388587952</t>
   </si>
   <si>
     <t xml:space="preserve">2.65385699272156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68810033798218</t>
+    <t xml:space="preserve">2.68810057640076</t>
   </si>
   <si>
     <t xml:space="preserve">2.64529633522034</t>
@@ -1433,16 +1433,16 @@
     <t xml:space="preserve">2.71378302574158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72234392166138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07333779335022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52706146240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.595547914505</t>
+    <t xml:space="preserve">2.7223436832428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07333755493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52706170082092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59554815292358</t>
   </si>
   <si>
     <t xml:space="preserve">3.65547394752502</t>
@@ -1451,19 +1451,19 @@
     <t xml:space="preserve">3.58698773384094</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61266994476318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53562307357788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42433166503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54418301582336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56986618041992</t>
+    <t xml:space="preserve">3.6126697063446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5356228351593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42433214187622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54418349266052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56986594200134</t>
   </si>
   <si>
     <t xml:space="preserve">3.55274438858032</t>
@@ -1472,46 +1472,46 @@
     <t xml:space="preserve">3.56130480766296</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5099401473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4842574596405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57842659950256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63835287094116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74108242988586</t>
+    <t xml:space="preserve">3.50993990898132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48425769805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57842683792114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63835263252258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74108290672302</t>
   </si>
   <si>
     <t xml:space="preserve">4.16912364959717</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60572624206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15361976623535</t>
+    <t xml:space="preserve">4.60572671890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15361928939819</t>
   </si>
   <si>
     <t xml:space="preserve">4.62284803390503</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19480657577515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45163059234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53724002838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52011775970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58860445022583</t>
+    <t xml:space="preserve">4.1948070526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45163106918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53723955154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52011823654175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58860397338867</t>
   </si>
   <si>
     <t xml:space="preserve">4.34890127182007</t>
@@ -1523,25 +1523,25 @@
     <t xml:space="preserve">4.23761034011841</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29753684997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89517712593079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27879738807678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25311517715454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8935604095459</t>
+    <t xml:space="preserve">4.29753589630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89517760276794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27879762649536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25311541557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89356017112732</t>
   </si>
   <si>
     <t xml:space="preserve">3.15894627571106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1675066947937</t>
+    <t xml:space="preserve">3.16750693321228</t>
   </si>
   <si>
     <t xml:space="preserve">3.0390944480896</t>
@@ -1553,40 +1553,40 @@
     <t xml:space="preserve">3.3815279006958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39008855819702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84381246566772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83525133132935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8780562877655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76676464080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88661670684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85237336158752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92942047119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95510315895081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93798160552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11775922775269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25473213195801</t>
+    <t xml:space="preserve">3.39008831977844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84381294250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83525156974792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87805604934692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76676487922668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88661623001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85237312316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92942070960999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95510292053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93798136711121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11775875091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25473260879517</t>
   </si>
   <si>
     <t xml:space="preserve">4.22904968261719</t>
@@ -1604,70 +1604,70 @@
     <t xml:space="preserve">4.20336675643921</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00646781921387</t>
+    <t xml:space="preserve">4.00646829605103</t>
   </si>
   <si>
     <t xml:space="preserve">4.10919809341431</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15200281143188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08351612091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94654273986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07495450973511</t>
+    <t xml:space="preserve">4.15200233459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08351564407349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94654250144958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07495498657227</t>
   </si>
   <si>
     <t xml:space="preserve">4.02358961105347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96366453170776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13488054275513</t>
+    <t xml:space="preserve">3.96366405487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13488101959229</t>
   </si>
   <si>
     <t xml:space="preserve">4.12631988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01664590835571</t>
+    <t xml:space="preserve">5.01664638519287</t>
   </si>
   <si>
     <t xml:space="preserve">4.70845603942871</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91391658782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96528100967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94815969467163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20498418807983</t>
+    <t xml:space="preserve">4.91391611099243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96528148651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94816017150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20498466491699</t>
   </si>
   <si>
     <t xml:space="preserve">5.56453943252563</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68439102172852</t>
+    <t xml:space="preserve">5.68439054489136</t>
   </si>
   <si>
     <t xml:space="preserve">5.95833730697632</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90697288513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88985061645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57471704483032</t>
+    <t xml:space="preserve">5.90697240829468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88985109329224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57471656799316</t>
   </si>
   <si>
     <t xml:space="preserve">6.129554271698</t>
@@ -1676,7 +1676,7 @@
     <t xml:space="preserve">6.4035005569458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0198802947998</t>
+    <t xml:space="preserve">7.01987981796265</t>
   </si>
   <si>
     <t xml:space="preserve">7.20821857452393</t>
@@ -1685,82 +1685,82 @@
     <t xml:space="preserve">7.32807016372681</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05412292480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00275850296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42397785186768</t>
+    <t xml:space="preserve">7.05412340164185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00275897979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4239764213562</t>
   </si>
   <si>
     <t xml:space="preserve">7.28357124328613</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8799033164978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96765661239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59909057617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51133728027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73949670791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84480142593384</t>
+    <t xml:space="preserve">6.87990283966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9676570892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59909009933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51133680343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73949718475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84480237960815</t>
   </si>
   <si>
     <t xml:space="preserve">6.82725095748901</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68684434890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66929388046265</t>
+    <t xml:space="preserve">6.68684482574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6692943572998</t>
   </si>
   <si>
     <t xml:space="preserve">6.45868492126465</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40603256225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31827831268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80970001220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17826700210571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35377407073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26602077484131</t>
+    <t xml:space="preserve">6.4060320854187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31827878952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80970048904419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17826652526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3537745475769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26602029800415</t>
   </si>
   <si>
     <t xml:space="preserve">7.05541086196899</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07296228408813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63419198989868</t>
+    <t xml:space="preserve">7.07296180725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.634192943573</t>
   </si>
   <si>
     <t xml:space="preserve">6.44113397598267</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30072784423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.055016040802</t>
+    <t xml:space="preserve">6.30072736740112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05501651763916</t>
   </si>
   <si>
     <t xml:space="preserve">6.03746604919434</t>
@@ -1778,37 +1778,37 @@
     <t xml:space="preserve">5.65134906768799</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12521934509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96726274490356</t>
+    <t xml:space="preserve">6.12521982192993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96726322174072</t>
   </si>
   <si>
     <t xml:space="preserve">6.01991558074951</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91461038589478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84440755844116</t>
+    <t xml:space="preserve">5.91461086273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.844407081604</t>
   </si>
   <si>
     <t xml:space="preserve">5.94971179962158</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86195755004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82685708999634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93216180801392</t>
+    <t xml:space="preserve">5.86195802688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82685661315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93216133117676</t>
   </si>
   <si>
     <t xml:space="preserve">5.87950849533081</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79175472259521</t>
+    <t xml:space="preserve">5.79175519943237</t>
   </si>
   <si>
     <t xml:space="preserve">5.68645048141479</t>
@@ -1820,13 +1820,13 @@
     <t xml:space="preserve">5.63379812240601</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70400094985962</t>
+    <t xml:space="preserve">5.70400142669678</t>
   </si>
   <si>
     <t xml:space="preserve">5.58114576339722</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66890048980713</t>
+    <t xml:space="preserve">5.66890001296997</t>
   </si>
   <si>
     <t xml:space="preserve">5.56359529495239</t>
@@ -1838,10 +1838,10 @@
     <t xml:space="preserve">5.49339246749878</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31788444519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17747783660889</t>
+    <t xml:space="preserve">5.31788396835327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17747831344604</t>
   </si>
   <si>
     <t xml:space="preserve">5.26523208618164</t>
@@ -1850,43 +1850,43 @@
     <t xml:space="preserve">5.28278255462646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35298633575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42318868637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47584104537964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38808727264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51094341278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77420473098755</t>
+    <t xml:space="preserve">5.35298585891724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42318916320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47584056854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3880877494812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5109429359436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77420425415039</t>
   </si>
   <si>
     <t xml:space="preserve">5.44074010848999</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54604434967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23052453994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35338020324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1603217124939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37093067169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47623538970947</t>
+    <t xml:space="preserve">5.54604482650757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23052406311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35337972640991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16032123565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37093162536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47623586654663</t>
   </si>
   <si>
     <t xml:space="preserve">6.42358303070068</t>
@@ -1898,22 +1898,22 @@
     <t xml:space="preserve">6.98520803451538</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33622312545776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09051275253296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16071510314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19581651687622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95010566711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14316511154175</t>
+    <t xml:space="preserve">7.33622360229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0905122756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16071557998657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19581699371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95010662078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14316463470459</t>
   </si>
   <si>
     <t xml:space="preserve">7.12561368942261</t>
@@ -1922,31 +1922,31 @@
     <t xml:space="preserve">7.02030992507935</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84519529342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33661842346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31906700134277</t>
+    <t xml:space="preserve">7.8451943397522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33661651611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31906604766846</t>
   </si>
   <si>
     <t xml:space="preserve">8.42437171936035</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0825252532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6876335144043</t>
+    <t xml:space="preserve">9.08252620697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68763160705566</t>
   </si>
   <si>
     <t xml:space="preserve">9.03864860534668</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30191040039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2763729095459</t>
+    <t xml:space="preserve">9.30190944671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2763719558716</t>
   </si>
   <si>
     <t xml:space="preserve">13.1630792617798</t>
@@ -1964,13 +1964,13 @@
     <t xml:space="preserve">12.0222806930542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.110032081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9345254898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.36412525177</t>
+    <t xml:space="preserve">12.1100330352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9345264434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3641262054443</t>
   </si>
   <si>
     <t xml:space="preserve">10.88148021698</t>
@@ -1979,13 +1979,13 @@
     <t xml:space="preserve">12.1539106369019</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6712656021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7151412963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4518795013428</t>
+    <t xml:space="preserve">11.6712646484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.715142250061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4518804550171</t>
   </si>
   <si>
     <t xml:space="preserve">11.0569868087769</t>
@@ -1994,16 +1994,16 @@
     <t xml:space="preserve">11.4957571029663</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4080018997192</t>
+    <t xml:space="preserve">11.4080028533936</t>
   </si>
   <si>
     <t xml:space="preserve">11.8906488418579</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8028945922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3202476501465</t>
+    <t xml:space="preserve">11.8028955459595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3202495574951</t>
   </si>
   <si>
     <t xml:space="preserve">11.627387046814</t>
@@ -2021,16 +2021,16 @@
     <t xml:space="preserve">10.5743408203125</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7498483657837</t>
+    <t xml:space="preserve">10.749849319458</t>
   </si>
   <si>
     <t xml:space="preserve">10.6620941162109</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3549556732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78455543518066</t>
+    <t xml:space="preserve">10.3549566268921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78455638885498</t>
   </si>
   <si>
     <t xml:space="preserve">9.91618728637695</t>
@@ -2042,10 +2042,10 @@
     <t xml:space="preserve">11.2324953079224</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1886186599731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1008634567261</t>
+    <t xml:space="preserve">11.1886177062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1008644104004</t>
   </si>
   <si>
     <t xml:space="preserve">11.3553504943848</t>
@@ -2054,7 +2054,7 @@
     <t xml:space="preserve">11.267596244812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0218868255615</t>
+    <t xml:space="preserve">11.0218858718872</t>
   </si>
   <si>
     <t xml:space="preserve">11.2500448226929</t>
@@ -2066,25 +2066,25 @@
     <t xml:space="preserve">11.2851467132568</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1973943710327</t>
+    <t xml:space="preserve">11.1973934173584</t>
   </si>
   <si>
     <t xml:space="preserve">11.8467721939087</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9871788024902</t>
+    <t xml:space="preserve">11.9871778488159</t>
   </si>
   <si>
     <t xml:space="preserve">12.2855415344238</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2504386901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1626853942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4672002792358</t>
+    <t xml:space="preserve">12.2504396438599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1626863479614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4672012329102</t>
   </si>
   <si>
     <t xml:space="preserve">12.0372972488403</t>
@@ -2093,40 +2093,40 @@
     <t xml:space="preserve">12.0910358428955</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5536556243896</t>
+    <t xml:space="preserve">11.553656578064</t>
   </si>
   <si>
     <t xml:space="preserve">11.6432199478149</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3924427032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9446268081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5505466461182</t>
+    <t xml:space="preserve">11.3924417495728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9446277618408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5505475997925</t>
   </si>
   <si>
     <t xml:space="preserve">10.6759366989136</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9088010787964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7117614746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6580238342285</t>
+    <t xml:space="preserve">10.9088020324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7117624282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6580228805542</t>
   </si>
   <si>
     <t xml:space="preserve">10.9267139434814</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0521030426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4999189376831</t>
+    <t xml:space="preserve">11.0521020889282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4999179840088</t>
   </si>
   <si>
     <t xml:space="preserve">11.4820051193237</t>
@@ -2135,34 +2135,34 @@
     <t xml:space="preserve">11.4282674789429</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5715684890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.374529838562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3566179275513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3207921981812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4461793899536</t>
+    <t xml:space="preserve">11.571569442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3745288848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.356616973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3207931518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4461803436279</t>
   </si>
   <si>
     <t xml:space="preserve">11.464093208313</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7148704528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7327823638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.750696182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1805982589722</t>
+    <t xml:space="preserve">11.7148694992065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7327833175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7506952285767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1805992126465</t>
   </si>
   <si>
     <t xml:space="preserve">12.6284151077271</t>
@@ -2174,28 +2174,28 @@
     <t xml:space="preserve">12.3418121337891</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3597259521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6969566345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1268615722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0552101135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8581705093384</t>
+    <t xml:space="preserve">12.3597249984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6969585418701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.126859664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0552110671997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8581714630127</t>
   </si>
   <si>
     <t xml:space="preserve">11.9298210144043</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2880744934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5925893783569</t>
+    <t xml:space="preserve">12.2880754470825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5925903320312</t>
   </si>
   <si>
     <t xml:space="preserve">12.503026008606</t>
@@ -2210,7 +2210,7 @@
     <t xml:space="preserve">10.9804515838623</t>
   </si>
   <si>
-    <t xml:space="preserve">11.177490234375</t>
+    <t xml:space="preserve">11.1774892807007</t>
   </si>
   <si>
     <t xml:space="preserve">11.284966468811</t>
@@ -2225,13 +2225,13 @@
     <t xml:space="preserve">11.7686080932617</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6253061294556</t>
+    <t xml:space="preserve">11.6253070831299</t>
   </si>
   <si>
     <t xml:space="preserve">12.0014715194702</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1089487075806</t>
+    <t xml:space="preserve">12.1089477539062</t>
   </si>
   <si>
     <t xml:space="preserve">11.9656467437744</t>
@@ -2240,19 +2240,19 @@
     <t xml:space="preserve">12.1985120773315</t>
   </si>
   <si>
-    <t xml:space="preserve">12.43137550354</t>
+    <t xml:space="preserve">12.4313764572144</t>
   </si>
   <si>
     <t xml:space="preserve">12.2522497177124</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8612794876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8433675765991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6821537017822</t>
+    <t xml:space="preserve">12.8612785339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8433666229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6821517944336</t>
   </si>
   <si>
     <t xml:space="preserve">12.7358903884888</t>
@@ -2264,16 +2264,16 @@
     <t xml:space="preserve">14.2405529022217</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0972509384155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3301162719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4734182357788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5988063812256</t>
+    <t xml:space="preserve">14.0972518920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.330117225647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4734172821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5988054275513</t>
   </si>
   <si>
     <t xml:space="preserve">13.8823003768921</t>
@@ -2285,7 +2285,7 @@
     <t xml:space="preserve">13.5777854919434</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4703092575073</t>
+    <t xml:space="preserve">13.470308303833</t>
   </si>
   <si>
     <t xml:space="preserve">13.6852607727051</t>
@@ -2297,19 +2297,19 @@
     <t xml:space="preserve">13.5598735809326</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6136093139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8285627365112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.953950881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4344844818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7210865020752</t>
+    <t xml:space="preserve">13.6136112213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8285608291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9539499282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4344835281372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7210855484009</t>
   </si>
   <si>
     <t xml:space="preserve">13.5240478515625</t>
@@ -2324,7 +2324,7 @@
     <t xml:space="preserve">13.4523963928223</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3090953826904</t>
+    <t xml:space="preserve">13.3090944290161</t>
   </si>
   <si>
     <t xml:space="preserve">14.2763786315918</t>
@@ -2333,13 +2333,13 @@
     <t xml:space="preserve">14.4196796417236</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0256023406982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.756911277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.437593460083</t>
+    <t xml:space="preserve">14.0256004333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7569122314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4375925064087</t>
   </si>
   <si>
     <t xml:space="preserve">16.7124977111816</t>
@@ -2357,28 +2357,28 @@
     <t xml:space="preserve">19.6591281890869</t>
   </si>
   <si>
-    <t xml:space="preserve">21.316047668457</t>
+    <t xml:space="preserve">21.3160457611084</t>
   </si>
   <si>
     <t xml:space="preserve">21.4503936767578</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5399532318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2116775512695</t>
+    <t xml:space="preserve">21.5399570465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2116813659668</t>
   </si>
   <si>
     <t xml:space="preserve">21.9877700805664</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2712669372559</t>
+    <t xml:space="preserve">21.2712650299072</t>
   </si>
   <si>
     <t xml:space="preserve">23.017749786377</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3460273742676</t>
+    <t xml:space="preserve">22.3460254669189</t>
   </si>
   <si>
     <t xml:space="preserve">22.1221160888672</t>
@@ -2390,58 +2390,58 @@
     <t xml:space="preserve">21.8982086181641</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4355888366699</t>
+    <t xml:space="preserve">22.4355869293213</t>
   </si>
   <si>
     <t xml:space="preserve">21.495174407959</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7190837860107</t>
+    <t xml:space="preserve">21.7190818786621</t>
   </si>
   <si>
     <t xml:space="preserve">21.9429912567139</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7638645172119</t>
+    <t xml:space="preserve">21.7638626098633</t>
   </si>
   <si>
     <t xml:space="preserve">21.8534278869629</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3312206268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8086471557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3463916778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3016128540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2420234680176</t>
+    <t xml:space="preserve">23.3312187194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8086452484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3463935852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3016109466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2420253753662</t>
   </si>
   <si>
     <t xml:space="preserve">25.525520324707</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2120475769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8837699890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4807395935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5702991485596</t>
+    <t xml:space="preserve">25.2120494842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8837718963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4807376861572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5703010559082</t>
   </si>
   <si>
     <t xml:space="preserve">25.1224842071533</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3611965179443</t>
+    <t xml:space="preserve">24.361198425293</t>
   </si>
   <si>
     <t xml:space="preserve">25.3911762237549</t>
@@ -2450,10 +2450,10 @@
     <t xml:space="preserve">25.704647064209</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4211540222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0629005432129</t>
+    <t xml:space="preserve">26.4211521148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0628986358643</t>
   </si>
   <si>
     <t xml:space="preserve">26.4659309387207</t>
@@ -2462,19 +2462,19 @@
     <t xml:space="preserve">26.1524620056152</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6602325439453</t>
+    <t xml:space="preserve">28.6602344512939</t>
   </si>
   <si>
     <t xml:space="preserve">27.6750373840332</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7794036865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5554943084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9881401062012</t>
+    <t xml:space="preserve">26.7794055938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5554962158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9881381988525</t>
   </si>
   <si>
     <t xml:space="preserve">25.2568302154541</t>
@@ -2489,7 +2489,7 @@
     <t xml:space="preserve">23.9133834838867</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5851078033447</t>
+    <t xml:space="preserve">24.5851058959961</t>
   </si>
   <si>
     <t xml:space="preserve">22.077335357666</t>
@@ -2513,10 +2513,10 @@
     <t xml:space="preserve">24.3164157867432</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3908081054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8238201141357</t>
+    <t xml:space="preserve">22.3908061981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8238182067871</t>
   </si>
   <si>
     <t xml:space="preserve">23.0625305175781</t>
@@ -2525,7 +2525,7 @@
     <t xml:space="preserve">23.7790355682373</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8834018707275</t>
+    <t xml:space="preserve">22.8834056854248</t>
   </si>
   <si>
     <t xml:space="preserve">23.2416591644287</t>
@@ -2534,16 +2534,16 @@
     <t xml:space="preserve">25.1672668457031</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3167858123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6002788543701</t>
+    <t xml:space="preserve">27.3167839050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6002807617188</t>
   </si>
   <si>
     <t xml:space="preserve">25.615083694458</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4359569549561</t>
+    <t xml:space="preserve">25.4359550476074</t>
   </si>
   <si>
     <t xml:space="preserve">24.8985767364502</t>
@@ -2558,19 +2558,19 @@
     <t xml:space="preserve">26.197244644165</t>
   </si>
   <si>
-    <t xml:space="preserve">26.868968963623</t>
+    <t xml:space="preserve">26.8689670562744</t>
   </si>
   <si>
     <t xml:space="preserve">26.6450595855713</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4959125518799</t>
+    <t xml:space="preserve">27.4959106445312</t>
   </si>
   <si>
     <t xml:space="preserve">27.048095703125</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9437274932861</t>
+    <t xml:space="preserve">27.9437294006348</t>
   </si>
   <si>
     <t xml:space="preserve">28.8841400146484</t>
@@ -2582,16 +2582,16 @@
     <t xml:space="preserve">28.7050132751465</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7797737121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9885101318359</t>
+    <t xml:space="preserve">29.7797718048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9885082244873</t>
   </si>
   <si>
     <t xml:space="preserve">27.630256652832</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2272186279297</t>
+    <t xml:space="preserve">27.227222442627</t>
   </si>
   <si>
     <t xml:space="preserve">27.4063472747803</t>
@@ -2603,28 +2603,28 @@
     <t xml:space="preserve">25.8389892578125</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7942085266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3315868377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7194519042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4507579803467</t>
+    <t xml:space="preserve">25.79421043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3315887451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7194499969482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4507598876953</t>
   </si>
   <si>
     <t xml:space="preserve">23.599910736084</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4655647277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3615646362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0332870483398</t>
+    <t xml:space="preserve">23.4655666351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3615665435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0332908630371</t>
   </si>
   <si>
     <t xml:space="preserve">27.8541641235352</t>
@@ -2636,13 +2636,13 @@
     <t xml:space="preserve">27.6633834838867</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2979869842529</t>
+    <t xml:space="preserve">30.2979888916016</t>
   </si>
   <si>
     <t xml:space="preserve">26.891170501709</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3454132080078</t>
+    <t xml:space="preserve">27.3454113006592</t>
   </si>
   <si>
     <t xml:space="preserve">29.6620502471924</t>
@@ -2660,13 +2660,13 @@
     <t xml:space="preserve">30.5705375671387</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0247802734375</t>
+    <t xml:space="preserve">31.0247764587402</t>
   </si>
   <si>
     <t xml:space="preserve">31.0702037811279</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8885040283203</t>
+    <t xml:space="preserve">30.8885078430176</t>
   </si>
   <si>
     <t xml:space="preserve">28.9352626800537</t>
@@ -2675,7 +2675,7 @@
     <t xml:space="preserve">27.8905048370361</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9359283447266</t>
+    <t xml:space="preserve">27.9359264373779</t>
   </si>
   <si>
     <t xml:space="preserve">27.4362621307373</t>
@@ -2684,7 +2684,7 @@
     <t xml:space="preserve">28.0722007751465</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4355926513672</t>
+    <t xml:space="preserve">28.4355945587158</t>
   </si>
   <si>
     <t xml:space="preserve">28.5264415740967</t>
@@ -2693,19 +2693,19 @@
     <t xml:space="preserve">28.4810199737549</t>
   </si>
   <si>
-    <t xml:space="preserve">28.390172958374</t>
+    <t xml:space="preserve">28.3901710510254</t>
   </si>
   <si>
     <t xml:space="preserve">29.1623821258545</t>
   </si>
   <si>
-    <t xml:space="preserve">29.434928894043</t>
+    <t xml:space="preserve">29.4349308013916</t>
   </si>
   <si>
     <t xml:space="preserve">28.2538986206055</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1169586181641</t>
+    <t xml:space="preserve">29.1169567108154</t>
   </si>
   <si>
     <t xml:space="preserve">30.1162948608398</t>
@@ -2753,7 +2753,7 @@
     <t xml:space="preserve">34.6132965087891</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3400840759277</t>
+    <t xml:space="preserve">35.340087890625</t>
   </si>
   <si>
     <t xml:space="preserve">34.4316024780273</t>
@@ -2762,7 +2762,7 @@
     <t xml:space="preserve">33.7048072814941</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9773597717285</t>
+    <t xml:space="preserve">33.9773559570312</t>
   </si>
   <si>
     <t xml:space="preserve">34.931266784668</t>
@@ -2798,22 +2798,22 @@
     <t xml:space="preserve">38.6106300354004</t>
   </si>
   <si>
-    <t xml:space="preserve">39.5645370483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.110969543457</t>
+    <t xml:space="preserve">39.5645408630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1109657287598</t>
   </si>
   <si>
     <t xml:space="preserve">36.4302673339844</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3868408203125</t>
+    <t xml:space="preserve">33.3868370056152</t>
   </si>
   <si>
     <t xml:space="preserve">32.8871765136719</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0688743591309</t>
+    <t xml:space="preserve">33.0688705444336</t>
   </si>
   <si>
     <t xml:space="preserve">33.3414154052734</t>
@@ -2828,7 +2828,7 @@
     <t xml:space="preserve">34.340747833252</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7508964538574</t>
+    <t xml:space="preserve">32.7509002685547</t>
   </si>
   <si>
     <t xml:space="preserve">32.6600532531738</t>
@@ -2840,43 +2840,43 @@
     <t xml:space="preserve">30.7976589202881</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3895034790039</t>
+    <t xml:space="preserve">29.3895015716553</t>
   </si>
   <si>
     <t xml:space="preserve">29.5257778167725</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6172943115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.344747543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0254440307617</t>
+    <t xml:space="preserve">28.6172924041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3447494506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0254421234131</t>
   </si>
   <si>
     <t xml:space="preserve">31.9332637786865</t>
   </si>
   <si>
-    <t xml:space="preserve">32.205810546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1149559020996</t>
+    <t xml:space="preserve">32.2058067321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1149597167969</t>
   </si>
   <si>
     <t xml:space="preserve">32.2512359619141</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6152935028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.024112701416</t>
+    <t xml:space="preserve">31.6152896881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0241088867188</t>
   </si>
   <si>
     <t xml:space="preserve">33.1142959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">32.614631652832</t>
+    <t xml:space="preserve">32.6146278381348</t>
   </si>
   <si>
     <t xml:space="preserve">31.2064743041992</t>
@@ -2885,7 +2885,7 @@
     <t xml:space="preserve">32.0695381164551</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5244445800781</t>
+    <t xml:space="preserve">31.5244483947754</t>
   </si>
   <si>
     <t xml:space="preserve">31.3427467346191</t>
@@ -2897,7 +2897,7 @@
     <t xml:space="preserve">32.5237770080566</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7054748535156</t>
+    <t xml:space="preserve">32.7054786682129</t>
   </si>
   <si>
     <t xml:space="preserve">32.1603889465332</t>
@@ -2915,31 +2915,31 @@
     <t xml:space="preserve">32.9325981140137</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0234451293945</t>
+    <t xml:space="preserve">33.0234489440918</t>
   </si>
   <si>
     <t xml:space="preserve">33.5231170654297</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4783592224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4329299926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.842414855957</t>
+    <t xml:space="preserve">32.4783554077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.432933807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8424167633057</t>
   </si>
   <si>
     <t xml:space="preserve">31.8878402709961</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4342632293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7074756622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7068061828613</t>
+    <t xml:space="preserve">30.4342613220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7074737548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.70680809021</t>
   </si>
   <si>
     <t xml:space="preserve">30.4796886444092</t>
@@ -2948,16 +2948,16 @@
     <t xml:space="preserve">29.616626739502</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8437461853027</t>
+    <t xml:space="preserve">29.8437442779541</t>
   </si>
   <si>
     <t xml:space="preserve">29.2532329559326</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7535629272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0708675384521</t>
+    <t xml:space="preserve">28.7535648345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0708694458008</t>
   </si>
   <si>
     <t xml:space="preserve">28.8898372650146</t>
@@ -2975,10 +2975,10 @@
     <t xml:space="preserve">28.9806861877441</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7989902496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8891735076904</t>
+    <t xml:space="preserve">28.7989883422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8891754150391</t>
   </si>
   <si>
     <t xml:space="preserve">29.0715351104736</t>
@@ -2990,10 +2990,10 @@
     <t xml:space="preserve">28.0267772674561</t>
   </si>
   <si>
-    <t xml:space="preserve">27.617956161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7542304992676</t>
+    <t xml:space="preserve">27.6179580688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7542324066162</t>
   </si>
   <si>
     <t xml:space="preserve">28.1176242828369</t>
@@ -3008,7 +3008,7 @@
     <t xml:space="preserve">27.5725345611572</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6186218261719</t>
+    <t xml:space="preserve">26.6186237335205</t>
   </si>
   <si>
     <t xml:space="preserve">27.1182918548584</t>
@@ -3023,13 +3023,13 @@
     <t xml:space="preserve">26.9820194244385</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3460788726807</t>
+    <t xml:space="preserve">26.346076965332</t>
   </si>
   <si>
     <t xml:space="preserve">25.8918361663818</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6647148132324</t>
+    <t xml:space="preserve">25.6647129058838</t>
   </si>
   <si>
     <t xml:space="preserve">26.2552280426025</t>
@@ -3050,7 +3050,7 @@
     <t xml:space="preserve">26.3915023803711</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7094707489014</t>
+    <t xml:space="preserve">26.70947265625</t>
   </si>
   <si>
     <t xml:space="preserve">26.527774810791</t>
@@ -3077,7 +3077,7 @@
     <t xml:space="preserve">25.7555637359619</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0741996765137</t>
+    <t xml:space="preserve">25.074197769165</t>
   </si>
   <si>
     <t xml:space="preserve">26.0735340118408</t>
@@ -4290,6 +4290,9 @@
   </si>
   <si>
     <t xml:space="preserve">20.5499992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1000003814697</t>
   </si>
 </sst>
 </file>
@@ -69654,7 +69657,7 @@
     </row>
     <row r="2502">
       <c r="A2502" s="1" t="n">
-        <v>45961.6909837963</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B2502" t="n">
         <v>29934</v>
@@ -69675,6 +69678,32 @@
         <v>1425</v>
       </c>
       <c r="H2502" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" s="1" t="n">
+        <v>45964.6909953704</v>
+      </c>
+      <c r="B2503" t="n">
+        <v>28264</v>
+      </c>
+      <c r="C2503" t="n">
+        <v>20.6000003814697</v>
+      </c>
+      <c r="D2503" t="n">
+        <v>19.7000007629395</v>
+      </c>
+      <c r="E2503" t="n">
+        <v>20.6000003814697</v>
+      </c>
+      <c r="F2503" t="n">
+        <v>20.1000003814697</v>
+      </c>
+      <c r="G2503" t="s">
+        <v>1426</v>
+      </c>
+      <c r="H2503" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ARN.MI.xlsx
+++ b/data/ARN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1429" uniqueCount="1429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1430" uniqueCount="1430">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,49 +38,49 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92215025424957</t>
+    <t xml:space="preserve">1.92215061187744</t>
   </si>
   <si>
     <t xml:space="preserve">ARN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94450104236603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91736090183258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90778195858002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8838347196579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93172943592072</t>
+    <t xml:space="preserve">1.94450080394745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91736078262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90778183937073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88383495807648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93172895908356</t>
   </si>
   <si>
     <t xml:space="preserve">1.91576433181763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83434426784515</t>
+    <t xml:space="preserve">1.83434438705444</t>
   </si>
   <si>
     <t xml:space="preserve">1.83594071865082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91097438335419</t>
+    <t xml:space="preserve">1.91097462177277</t>
   </si>
   <si>
     <t xml:space="preserve">1.80720412731171</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74973106384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71620559692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80401134490967</t>
+    <t xml:space="preserve">1.74973118305206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71620547771454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80401122570038</t>
   </si>
   <si>
     <t xml:space="preserve">1.81039714813232</t>
@@ -104,10 +104,10 @@
     <t xml:space="preserve">1.67629373073578</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70024085044861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69864416122437</t>
+    <t xml:space="preserve">1.7002409696579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69864439964294</t>
   </si>
   <si>
     <t xml:space="preserve">1.67469727993011</t>
@@ -119,91 +119,91 @@
     <t xml:space="preserve">1.66032898426056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81518661975861</t>
+    <t xml:space="preserve">1.81518626213074</t>
   </si>
   <si>
     <t xml:space="preserve">1.82795834541321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86148416996002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88543152809143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89181709289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92853581905365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95407915115356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90618538856506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8678697347641</t>
+    <t xml:space="preserve">1.86148428916931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88543128967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89181697368622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92853569984436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95407938957214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90618526935577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86787033081055</t>
   </si>
   <si>
     <t xml:space="preserve">1.88064181804657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85190534591675</t>
+    <t xml:space="preserve">1.85190498828888</t>
   </si>
   <si>
     <t xml:space="preserve">1.85988759994507</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85509824752808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79283607006073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78804683685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78006446361542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7561172246933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7688889503479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7640997171402</t>
+    <t xml:space="preserve">1.85509836673737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79283618927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78804671764374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78006434440613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75611734390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76888883113861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76409935951233</t>
   </si>
   <si>
     <t xml:space="preserve">1.78485381603241</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77048552036285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72099459171295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7353630065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80241477489471</t>
+    <t xml:space="preserve">1.77048540115356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72099471092224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73536336421967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80241453647614</t>
   </si>
   <si>
     <t xml:space="preserve">1.76250314712524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74494206905365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73217010498047</t>
+    <t xml:space="preserve">1.74494194984436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73217022418976</t>
   </si>
   <si>
     <t xml:space="preserve">1.73695981502533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74334526062012</t>
+    <t xml:space="preserve">1.74334561824799</t>
   </si>
   <si>
     <t xml:space="preserve">1.75132763385773</t>
@@ -218,13 +218,13 @@
     <t xml:space="preserve">1.65234661102295</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62041711807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64276790618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5900844335556</t>
+    <t xml:space="preserve">1.6204172372818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64276814460754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59008431434631</t>
   </si>
   <si>
     <t xml:space="preserve">1.60285580158234</t>
@@ -236,19 +236,19 @@
     <t xml:space="preserve">1.51185727119446</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45598077774048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43682324886322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4695508480072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49748909473419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47673511505127</t>
+    <t xml:space="preserve">1.45598101615906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43682312965393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46955072879791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49748921394348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47673499584198</t>
   </si>
   <si>
     <t xml:space="preserve">1.47274374961853</t>
@@ -260,40 +260,40 @@
     <t xml:space="preserve">1.49669086933136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47593653202057</t>
+    <t xml:space="preserve">1.47593677043915</t>
   </si>
   <si>
     <t xml:space="preserve">1.50626981258392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47753298282623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43841958045959</t>
+    <t xml:space="preserve">1.47753322124481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43841946125031</t>
   </si>
   <si>
     <t xml:space="preserve">1.40090262889862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34901750087738</t>
+    <t xml:space="preserve">1.34901738166809</t>
   </si>
   <si>
     <t xml:space="preserve">1.30910539627075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34342980384827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32666671276093</t>
+    <t xml:space="preserve">1.34342968463898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32666683197021</t>
   </si>
   <si>
     <t xml:space="preserve">1.34103500843048</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31708788871765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38653445243835</t>
+    <t xml:space="preserve">1.31708800792694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38653433322906</t>
   </si>
   <si>
     <t xml:space="preserve">1.39691150188446</t>
@@ -302,10 +302,10 @@
     <t xml:space="preserve">1.40649020671844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30671083927155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3234738111496</t>
+    <t xml:space="preserve">1.30671072006226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32347393035889</t>
   </si>
   <si>
     <t xml:space="preserve">1.30591261386871</t>
@@ -320,43 +320,43 @@
     <t xml:space="preserve">1.2851585149765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28595650196075</t>
+    <t xml:space="preserve">1.28595662117004</t>
   </si>
   <si>
     <t xml:space="preserve">1.33305251598358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33704388141632</t>
+    <t xml:space="preserve">1.33704376220703</t>
   </si>
   <si>
     <t xml:space="preserve">1.30112314224243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36104881763458</t>
+    <t xml:space="preserve">1.36104893684387</t>
   </si>
   <si>
     <t xml:space="preserve">1.34627246856689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35283994674683</t>
+    <t xml:space="preserve">1.35283982753754</t>
   </si>
   <si>
     <t xml:space="preserve">1.33806359767914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27157080173492</t>
+    <t xml:space="preserve">1.27157068252563</t>
   </si>
   <si>
     <t xml:space="preserve">1.28880977630615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29291427135468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30686962604523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33888459205627</t>
+    <t xml:space="preserve">1.29291439056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30686974525452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33888483047485</t>
   </si>
   <si>
     <t xml:space="preserve">1.34955620765686</t>
@@ -365,16 +365,16 @@
     <t xml:space="preserve">1.34380984306335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33642184734344</t>
+    <t xml:space="preserve">1.33642196655273</t>
   </si>
   <si>
     <t xml:space="preserve">1.34709358215332</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30522787570953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2912722826004</t>
+    <t xml:space="preserve">1.30522775650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29127240180969</t>
   </si>
   <si>
     <t xml:space="preserve">1.31425762176514</t>
@@ -386,31 +386,31 @@
     <t xml:space="preserve">1.26828730106354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27239203453064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28798890113831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29701888561249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24858593940735</t>
+    <t xml:space="preserve">1.27239179611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2879890203476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2970187664032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24858582019806</t>
   </si>
   <si>
     <t xml:space="preserve">1.32657122612</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33231723308563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35940718650818</t>
+    <t xml:space="preserve">1.33231747150421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35940706729889</t>
   </si>
   <si>
     <t xml:space="preserve">1.4201534986496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48664605617523</t>
+    <t xml:space="preserve">1.48664617538452</t>
   </si>
   <si>
     <t xml:space="preserve">1.53343737125397</t>
@@ -422,7 +422,7 @@
     <t xml:space="preserve">1.51866126060486</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43739247322083</t>
+    <t xml:space="preserve">1.43739235401154</t>
   </si>
   <si>
     <t xml:space="preserve">1.4677654504776</t>
@@ -431,40 +431,40 @@
     <t xml:space="preserve">1.43000423908234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40948188304901</t>
+    <t xml:space="preserve">1.4094820022583</t>
   </si>
   <si>
     <t xml:space="preserve">1.44478034973145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55970597267151</t>
+    <t xml:space="preserve">1.5597060918808</t>
   </si>
   <si>
     <t xml:space="preserve">1.61798977851868</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70582616329193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74851262569427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72388577461243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6828408241272</t>
+    <t xml:space="preserve">1.70582604408264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74851286411285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72388565540314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68284106254578</t>
   </si>
   <si>
     <t xml:space="preserve">1.67463183403015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.651646733284</t>
+    <t xml:space="preserve">1.65164697170258</t>
   </si>
   <si>
     <t xml:space="preserve">1.64179587364197</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67134821414948</t>
+    <t xml:space="preserve">1.67134833335876</t>
   </si>
   <si>
     <t xml:space="preserve">1.6647812128067</t>
@@ -473,19 +473,19 @@
     <t xml:space="preserve">1.65657186508179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69597506523132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69433331489563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65821373462677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68119895458221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68776607513428</t>
+    <t xml:space="preserve">1.69597518444061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69433319568634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65821385383606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6811990737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68776619434357</t>
   </si>
   <si>
     <t xml:space="preserve">1.6680645942688</t>
@@ -497,34 +497,34 @@
     <t xml:space="preserve">1.66313922405243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67791533470154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03746938705444</t>
+    <t xml:space="preserve">1.67791545391083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03746867179871</t>
   </si>
   <si>
     <t xml:space="preserve">2.04403614997864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03911018371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04075264930725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0522449016571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04731941223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04239392280579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19836497306824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24105143547058</t>
+    <t xml:space="preserve">2.0391104221344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04075217247009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05224514007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04731965065002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04239368438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19836521148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24105167388916</t>
   </si>
   <si>
     <t xml:space="preserve">2.18851399421692</t>
@@ -533,88 +533,88 @@
     <t xml:space="preserve">2.17537951469421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14582705497742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00627493858337</t>
+    <t xml:space="preserve">2.145827293396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00627470016479</t>
   </si>
   <si>
     <t xml:space="preserve">1.98821485042572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99313998222351</t>
+    <t xml:space="preserve">1.99314022064209</t>
   </si>
   <si>
     <t xml:space="preserve">1.99806559085846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99642372131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99970769882202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00299096107483</t>
+    <t xml:space="preserve">1.99642395973206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99970746040344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00299119949341</t>
   </si>
   <si>
     <t xml:space="preserve">2.00791621208191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0111997127533</t>
+    <t xml:space="preserve">2.01119995117188</t>
   </si>
   <si>
     <t xml:space="preserve">2.02597594261169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03254294395447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02105093002319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0194091796875</t>
+    <t xml:space="preserve">2.03254318237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02105069160461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01940894126892</t>
   </si>
   <si>
     <t xml:space="preserve">2.02433443069458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07687187194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05881190299988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09657382965088</t>
+    <t xml:space="preserve">2.07687139511108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0588116645813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0965735912323</t>
   </si>
   <si>
     <t xml:space="preserve">2.14746904373169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33955931663513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27552938461304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32478332519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.278813123703</t>
+    <t xml:space="preserve">2.33955907821655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27552914619446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32478308677673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27881264686584</t>
   </si>
   <si>
     <t xml:space="preserve">2.25746965408325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29851388931274</t>
+    <t xml:space="preserve">2.29851412773132</t>
   </si>
   <si>
     <t xml:space="preserve">2.26075315475464</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28045463562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30672311782837</t>
+    <t xml:space="preserve">2.28045415878296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30672335624695</t>
   </si>
   <si>
     <t xml:space="preserve">2.35597705841064</t>
@@ -626,13 +626,13 @@
     <t xml:space="preserve">2.34284281730652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3477680683136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44627594947815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39209651947021</t>
+    <t xml:space="preserve">2.34776830673218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44627618789673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39209675788879</t>
   </si>
   <si>
     <t xml:space="preserve">2.38224577903748</t>
@@ -650,13 +650,13 @@
     <t xml:space="preserve">2.38060402870178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42164897918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33791756629944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32314133644104</t>
+    <t xml:space="preserve">2.42164921760559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33791732788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32314085960388</t>
   </si>
   <si>
     <t xml:space="preserve">2.35433506965637</t>
@@ -665,46 +665,46 @@
     <t xml:space="preserve">2.41015648841858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40687274932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43806672096252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41836524009705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29030513763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34940981864929</t>
+    <t xml:space="preserve">2.40687251091003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4380669593811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41836547851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29030537605286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34941005706787</t>
   </si>
   <si>
     <t xml:space="preserve">2.36418604850769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3756787776947</t>
+    <t xml:space="preserve">2.37567853927612</t>
   </si>
   <si>
     <t xml:space="preserve">2.40194749832153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35761833190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36746978759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37075352668762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37239527702332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.362544298172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36582779884338</t>
+    <t xml:space="preserve">2.35761880874634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36746954917908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37075304985046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37239480018616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36254453659058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36582803726196</t>
   </si>
   <si>
     <t xml:space="preserve">2.39538025856018</t>
@@ -713,7 +713,7 @@
     <t xml:space="preserve">2.37732005119324</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37403655052185</t>
+    <t xml:space="preserve">2.37403678894043</t>
   </si>
   <si>
     <t xml:space="preserve">2.38881301879883</t>
@@ -722,37 +722,37 @@
     <t xml:space="preserve">2.39373826980591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39045524597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41343975067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40358924865723</t>
+    <t xml:space="preserve">2.3904550075531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41343998908997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40358901023865</t>
   </si>
   <si>
     <t xml:space="preserve">2.40030574798584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40851426124573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42329072952271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43149971961975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42000722885132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35105180740356</t>
+    <t xml:space="preserve">2.40851473808289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42329049110413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43149948120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4200074672699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35105156898499</t>
   </si>
   <si>
     <t xml:space="preserve">2.33627557754517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34612655639648</t>
+    <t xml:space="preserve">2.34612631797791</t>
   </si>
   <si>
     <t xml:space="preserve">2.43642497062683</t>
@@ -761,16 +761,16 @@
     <t xml:space="preserve">2.42657446861267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42985820770264</t>
+    <t xml:space="preserve">2.42985773086548</t>
   </si>
   <si>
     <t xml:space="preserve">2.45284295082092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47701334953308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47868013381958</t>
+    <t xml:space="preserve">2.4770131111145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.478679895401</t>
   </si>
   <si>
     <t xml:space="preserve">2.49201512336731</t>
@@ -788,10 +788,10 @@
     <t xml:space="preserve">2.48201370239258</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46867895126343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45867705345154</t>
+    <t xml:space="preserve">2.46867871284485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45867729187012</t>
   </si>
   <si>
     <t xml:space="preserve">2.46201086044312</t>
@@ -800,46 +800,46 @@
     <t xml:space="preserve">2.45534324645996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41700506210327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40867042541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36699748039246</t>
+    <t xml:space="preserve">2.41700482368469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40866994857788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36699771881104</t>
   </si>
   <si>
     <t xml:space="preserve">2.3419942855835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36866450309753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35366249084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38533353805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38366627693176</t>
+    <t xml:space="preserve">2.36866474151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35366225242615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.385333776474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38366651535034</t>
   </si>
   <si>
     <t xml:space="preserve">2.36366415023804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32532525062561</t>
+    <t xml:space="preserve">2.32532501220703</t>
   </si>
   <si>
     <t xml:space="preserve">2.31699061393738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28531980514526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2869861125946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29698801040649</t>
+    <t xml:space="preserve">2.28532004356384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28698658943176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29698777198792</t>
   </si>
   <si>
     <t xml:space="preserve">2.31532382965088</t>
@@ -848,31 +848,31 @@
     <t xml:space="preserve">2.28365278244019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28865337371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29032039642334</t>
+    <t xml:space="preserve">2.28865361213684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29032063484192</t>
   </si>
   <si>
     <t xml:space="preserve">2.30198884010315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30365538597107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29365420341492</t>
+    <t xml:space="preserve">2.30365562438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2936544418335</t>
   </si>
   <si>
     <t xml:space="preserve">2.24198031425476</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26698350906372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2686505317688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32699227333069</t>
+    <t xml:space="preserve">2.2669837474823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26865029335022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32699203491211</t>
   </si>
   <si>
     <t xml:space="preserve">2.31865739822388</t>
@@ -884,7 +884,7 @@
     <t xml:space="preserve">2.24364709854126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25031471252441</t>
+    <t xml:space="preserve">2.25031495094299</t>
   </si>
   <si>
     <t xml:space="preserve">2.22531127929688</t>
@@ -893,19 +893,19 @@
     <t xml:space="preserve">2.25198173522949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2219774723053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20697569847107</t>
+    <t xml:space="preserve">2.22197771072388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20697546005249</t>
   </si>
   <si>
     <t xml:space="preserve">2.20030760765076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16863632202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17863798141479</t>
+    <t xml:space="preserve">2.16863679885864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17863821983337</t>
   </si>
   <si>
     <t xml:space="preserve">2.16696953773499</t>
@@ -914,22 +914,22 @@
     <t xml:space="preserve">2.18697285652161</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19697380065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18363857269287</t>
+    <t xml:space="preserve">2.19697403907776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18363881111145</t>
   </si>
   <si>
     <t xml:space="preserve">2.18530583381653</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19197344779968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17530417442322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14196586608887</t>
+    <t xml:space="preserve">2.19197368621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1753044128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14196634292603</t>
   </si>
   <si>
     <t xml:space="preserve">2.15363454818726</t>
@@ -944,28 +944,28 @@
     <t xml:space="preserve">2.12696409225464</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1286313533783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12029647827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13029789924622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11862969398499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37366557121277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37533235549927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40700340270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39533519744873</t>
+    <t xml:space="preserve">2.12863111495972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12029671669006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13029813766479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11862993240356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37366509437561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37533187866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40700316429138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39533495903015</t>
   </si>
   <si>
     <t xml:space="preserve">2.39200115203857</t>
@@ -977,10 +977,10 @@
     <t xml:space="preserve">2.49534893035889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5086841583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51201772689819</t>
+    <t xml:space="preserve">2.50868391990662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51201796531677</t>
   </si>
   <si>
     <t xml:space="preserve">2.51535153388977</t>
@@ -989,13 +989,13 @@
     <t xml:space="preserve">2.51701879501343</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52368640899658</t>
+    <t xml:space="preserve">2.523686170578</t>
   </si>
   <si>
     <t xml:space="preserve">2.52535319328308</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54535579681396</t>
+    <t xml:space="preserve">2.54535603523254</t>
   </si>
   <si>
     <t xml:space="preserve">2.53368759155273</t>
@@ -1004,19 +1004,19 @@
     <t xml:space="preserve">2.53202080726624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54035520553589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52702045440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53868889808655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53702187538147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49701619148254</t>
+    <t xml:space="preserve">2.54035544395447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52702021598816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53868865966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53702163696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49701595306396</t>
   </si>
   <si>
     <t xml:space="preserve">2.427006483078</t>
@@ -1025,13 +1025,13 @@
     <t xml:space="preserve">2.50034976005554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5053505897522</t>
+    <t xml:space="preserve">2.50535035133362</t>
   </si>
   <si>
     <t xml:space="preserve">2.48368048667908</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45200943946838</t>
+    <t xml:space="preserve">2.4520092010498</t>
   </si>
   <si>
     <t xml:space="preserve">2.51368474960327</t>
@@ -1043,55 +1043,55 @@
     <t xml:space="preserve">2.54868984222412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51035118103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52035236358643</t>
+    <t xml:space="preserve">2.51035094261169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.520352602005</t>
   </si>
   <si>
     <t xml:space="preserve">2.47201251983643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50201678276062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48701477050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00041961669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81706094741821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75038456916809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71704649925232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8087260723114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80039191246033</t>
+    <t xml:space="preserve">2.50201654434204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48701453208923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00041937828064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81706070899963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75038480758667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71704697608948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80872583389282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80039167404175</t>
   </si>
   <si>
     <t xml:space="preserve">2.83372974395752</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78372287750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84206438064575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75871920585632</t>
+    <t xml:space="preserve">2.78372263908386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84206414222717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75871896743774</t>
   </si>
   <si>
     <t xml:space="preserve">2.85039877891541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85873341560364</t>
+    <t xml:space="preserve">2.85873317718506</t>
   </si>
   <si>
     <t xml:space="preserve">2.89207100868225</t>
@@ -1103,13 +1103,13 @@
     <t xml:space="preserve">2.72538113594055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61703276634216</t>
+    <t xml:space="preserve">2.61703300476074</t>
   </si>
   <si>
     <t xml:space="preserve">2.64203643798828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70037746429443</t>
+    <t xml:space="preserve">2.70037770271301</t>
   </si>
   <si>
     <t xml:space="preserve">2.65870547294617</t>
@@ -1121,64 +1121,64 @@
     <t xml:space="preserve">2.63370203971863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59202909469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66703939437866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70871210098267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74204993247986</t>
+    <t xml:space="preserve">2.59202933311462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66703963279724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70871233940125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74205040931702</t>
   </si>
   <si>
     <t xml:space="preserve">2.65037083625793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68370866775513</t>
+    <t xml:space="preserve">2.68370890617371</t>
   </si>
   <si>
     <t xml:space="preserve">2.60036373138428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58369493484497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56702566146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76705360412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73371553421021</t>
+    <t xml:space="preserve">2.58369469642639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56702542304993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76705384254456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73371529579163</t>
   </si>
   <si>
     <t xml:space="preserve">2.79205703735352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86706781387329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87540197372437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8837366104126</t>
+    <t xml:space="preserve">2.86706733703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87540221214294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88373684883118</t>
   </si>
   <si>
     <t xml:space="preserve">2.77538824081421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78091382980347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72174549102783</t>
+    <t xml:space="preserve">2.78091406822205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72174572944641</t>
   </si>
   <si>
     <t xml:space="preserve">2.7301983833313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77246141433716</t>
+    <t xml:space="preserve">2.7724609375</t>
   </si>
   <si>
     <t xml:space="preserve">2.64567184448242</t>
@@ -1190,67 +1190,67 @@
     <t xml:space="preserve">2.68793487548828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6625771522522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69638752937317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65412425994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60340857505798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63721919059753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61186122894287</t>
+    <t xml:space="preserve">2.66257691383362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69638776779175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65412449836731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60340881347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63721895217896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61186146736145</t>
   </si>
   <si>
     <t xml:space="preserve">2.5780508518219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59495615959167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50197744369507</t>
+    <t xml:space="preserve">2.5949559211731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50197720527649</t>
   </si>
   <si>
     <t xml:space="preserve">2.4935245513916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54424071311951</t>
+    <t xml:space="preserve">2.54424047470093</t>
   </si>
   <si>
     <t xml:space="preserve">2.5611457824707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58650326728821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51888251304626</t>
+    <t xml:space="preserve">2.58650350570679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51888275146484</t>
   </si>
   <si>
     <t xml:space="preserve">2.53578782081604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55269312858582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51042985916138</t>
+    <t xml:space="preserve">2.55269289016724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5104296207428</t>
   </si>
   <si>
     <t xml:space="preserve">2.56959819793701</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46816682815552</t>
+    <t xml:space="preserve">2.46816635131836</t>
   </si>
   <si>
     <t xml:space="preserve">2.48507189750671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41745090484619</t>
+    <t xml:space="preserve">2.41745114326477</t>
   </si>
   <si>
     <t xml:space="preserve">2.45126152038574</t>
@@ -1259,22 +1259,22 @@
     <t xml:space="preserve">2.39209318161011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38364052772522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27375650405884</t>
+    <t xml:space="preserve">2.3836407661438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27375626564026</t>
   </si>
   <si>
     <t xml:space="preserve">2.29911422729492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36673545837402</t>
+    <t xml:space="preserve">2.36673521995544</t>
   </si>
   <si>
     <t xml:space="preserve">2.35828256607056</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43435645103455</t>
+    <t xml:space="preserve">2.43435621261597</t>
   </si>
   <si>
     <t xml:space="preserve">2.4259033203125</t>
@@ -1283,7 +1283,7 @@
     <t xml:space="preserve">2.34982991218567</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28220891952515</t>
+    <t xml:space="preserve">2.28220915794373</t>
   </si>
   <si>
     <t xml:space="preserve">2.32447218894958</t>
@@ -1295,28 +1295,28 @@
     <t xml:space="preserve">2.45971417427063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44280910491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33292484283447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3413770198822</t>
+    <t xml:space="preserve">2.44280886650085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33292436599731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34137725830078</t>
   </si>
   <si>
     <t xml:space="preserve">2.40054559707642</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37518811225891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47661924362183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30756688117981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23994612693787</t>
+    <t xml:space="preserve">2.37518787384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47661972045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30756664276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23994588851929</t>
   </si>
   <si>
     <t xml:space="preserve">2.29430246353149</t>
@@ -1325,7 +1325,7 @@
     <t xml:space="preserve">2.23437643051147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2429370880127</t>
+    <t xml:space="preserve">2.24293732643127</t>
   </si>
   <si>
     <t xml:space="preserve">2.33710646629333</t>
@@ -1334,31 +1334,31 @@
     <t xml:space="preserve">2.25149822235107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27718091011047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26861977577209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44839715957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37134957313538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31142377853394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28574156761169</t>
+    <t xml:space="preserve">2.27718067169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26862001419067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.448397397995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37134981155396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31142401695251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28574180603027</t>
   </si>
   <si>
     <t xml:space="preserve">2.26005887985229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35422801971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22581577301025</t>
+    <t xml:space="preserve">2.35422825813293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22581553459167</t>
   </si>
   <si>
     <t xml:space="preserve">2.20869374275208</t>
@@ -1379,13 +1379,13 @@
     <t xml:space="preserve">2.39703226089478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32854557037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38847160339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36278891563416</t>
+    <t xml:space="preserve">2.32854580879211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38847136497498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36278867721558</t>
   </si>
   <si>
     <t xml:space="preserve">2.34566736221313</t>
@@ -1397,13 +1397,13 @@
     <t xml:space="preserve">2.18301153182983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4398365020752</t>
+    <t xml:space="preserve">2.43983626365662</t>
   </si>
   <si>
     <t xml:space="preserve">2.54256629943848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60249185562134</t>
+    <t xml:space="preserve">2.60249209403992</t>
   </si>
   <si>
     <t xml:space="preserve">2.69666123390198</t>
@@ -1418,22 +1418,22 @@
     <t xml:space="preserve">2.67097854614258</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61961364746094</t>
+    <t xml:space="preserve">2.61961388587952</t>
   </si>
   <si>
     <t xml:space="preserve">2.65385723114014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68810033798218</t>
+    <t xml:space="preserve">2.68810057640076</t>
   </si>
   <si>
     <t xml:space="preserve">2.64529633522034</t>
   </si>
   <si>
-    <t xml:space="preserve">2.713782787323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72234392166138</t>
+    <t xml:space="preserve">2.71378302574158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7223436832428</t>
   </si>
   <si>
     <t xml:space="preserve">3.07333755493164</t>
@@ -1442,13 +1442,13 @@
     <t xml:space="preserve">3.52706170082092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59554839134216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65547394752502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58698773384094</t>
+    <t xml:space="preserve">3.59554862976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65547442436218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58698797225952</t>
   </si>
   <si>
     <t xml:space="preserve">3.61266946792603</t>
@@ -1463,25 +1463,25 @@
     <t xml:space="preserve">3.54418325424194</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56986594200134</t>
+    <t xml:space="preserve">3.56986570358276</t>
   </si>
   <si>
     <t xml:space="preserve">3.55274438858032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56130480766296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50993990898132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48425769805908</t>
+    <t xml:space="preserve">3.56130504608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5099401473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48425793647766</t>
   </si>
   <si>
     <t xml:space="preserve">3.57842659950256</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63835263252258</t>
+    <t xml:space="preserve">3.63835287094116</t>
   </si>
   <si>
     <t xml:space="preserve">3.74108242988586</t>
@@ -1496,16 +1496,16 @@
     <t xml:space="preserve">5.15361928939819</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62284755706787</t>
+    <t xml:space="preserve">4.62284803390503</t>
   </si>
   <si>
     <t xml:space="preserve">4.19480609893799</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45163154602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53723955154419</t>
+    <t xml:space="preserve">4.45163106918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53724002838135</t>
   </si>
   <si>
     <t xml:space="preserve">4.52011775970459</t>
@@ -1514,13 +1514,13 @@
     <t xml:space="preserve">4.58860492706299</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34890127182007</t>
+    <t xml:space="preserve">4.34890174865723</t>
   </si>
   <si>
     <t xml:space="preserve">4.16056346893311</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23760986328125</t>
+    <t xml:space="preserve">4.23761081695557</t>
   </si>
   <si>
     <t xml:space="preserve">4.29753637313843</t>
@@ -1529,28 +1529,28 @@
     <t xml:space="preserve">3.89517760276794</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27879786491394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25311517715454</t>
+    <t xml:space="preserve">3.27879762649536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25311541557312</t>
   </si>
   <si>
     <t xml:space="preserve">2.8935604095459</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15894627571106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16750693321228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0390944480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44145369529724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3815279006958</t>
+    <t xml:space="preserve">3.15894603729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1675066947937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03909468650818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44145345687866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38152766227722</t>
   </si>
   <si>
     <t xml:space="preserve">3.3900887966156</t>
@@ -1559,37 +1559,37 @@
     <t xml:space="preserve">3.84381175041199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83525156974792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8780562877655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76676487922668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88661599159241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85237336158752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92942142486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95510339736938</t>
+    <t xml:space="preserve">3.83525133132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87805581092834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76676511764526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88661646842957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8523736000061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92942094802856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95510292053223</t>
   </si>
   <si>
     <t xml:space="preserve">3.93798160552979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11775875091553</t>
+    <t xml:space="preserve">4.11775922775269</t>
   </si>
   <si>
     <t xml:space="preserve">4.25473213195801</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22905015945435</t>
+    <t xml:space="preserve">4.22904968261719</t>
   </si>
   <si>
     <t xml:space="preserve">4.26329326629639</t>
@@ -1604,10 +1604,10 @@
     <t xml:space="preserve">4.20336675643921</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00646877288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10919857025146</t>
+    <t xml:space="preserve">4.00646829605103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10919809341431</t>
   </si>
   <si>
     <t xml:space="preserve">4.15200233459473</t>
@@ -1616,46 +1616,46 @@
     <t xml:space="preserve">4.08351564407349</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94654178619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07495498657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02359008789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96366381645203</t>
+    <t xml:space="preserve">3.94654226303101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07495546340942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02358961105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96366429328918</t>
   </si>
   <si>
     <t xml:space="preserve">4.13488054275513</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12632036209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01664638519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70845603942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91391611099243</t>
+    <t xml:space="preserve">4.12632083892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01664686203003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70845651626587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91391563415527</t>
   </si>
   <si>
     <t xml:space="preserve">4.96528100967407</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94815969467163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20498371124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56453895568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68439054489136</t>
+    <t xml:space="preserve">4.94815921783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20498418807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56453943252563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68439102172852</t>
   </si>
   <si>
     <t xml:space="preserve">5.95833778381348</t>
@@ -1664,25 +1664,25 @@
     <t xml:space="preserve">5.90697240829468</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88985109329224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57471656799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12955331802368</t>
+    <t xml:space="preserve">5.88985013961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57471704483032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12955379486084</t>
   </si>
   <si>
     <t xml:space="preserve">6.4035005569458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01987981796265</t>
+    <t xml:space="preserve">7.0198802947998</t>
   </si>
   <si>
     <t xml:space="preserve">7.20821809768677</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32807064056396</t>
+    <t xml:space="preserve">7.32807016372681</t>
   </si>
   <si>
     <t xml:space="preserve">7.05412340164185</t>
@@ -1694,13 +1694,13 @@
     <t xml:space="preserve">7.42397689819336</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28357124328613</t>
+    <t xml:space="preserve">7.28357172012329</t>
   </si>
   <si>
     <t xml:space="preserve">6.8799033164978</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9676570892334</t>
+    <t xml:space="preserve">6.96765661239624</t>
   </si>
   <si>
     <t xml:space="preserve">6.59909105300903</t>
@@ -1724,10 +1724,10 @@
     <t xml:space="preserve">6.66929388046265</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45868444442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4060320854187</t>
+    <t xml:space="preserve">6.45868492126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40603256225586</t>
   </si>
   <si>
     <t xml:space="preserve">6.31827831268311</t>
@@ -1739,7 +1739,7 @@
     <t xml:space="preserve">7.17826700210571</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35377407073975</t>
+    <t xml:space="preserve">7.3537745475769</t>
   </si>
   <si>
     <t xml:space="preserve">7.26601982116699</t>
@@ -1748,13 +1748,13 @@
     <t xml:space="preserve">7.05541086196899</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07296276092529</t>
+    <t xml:space="preserve">7.07296228408813</t>
   </si>
   <si>
     <t xml:space="preserve">6.63419198989868</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44113397598267</t>
+    <t xml:space="preserve">6.44113445281982</t>
   </si>
   <si>
     <t xml:space="preserve">6.30072736740112</t>
@@ -1772,7 +1772,7 @@
     <t xml:space="preserve">5.40563821792603</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52849388122559</t>
+    <t xml:space="preserve">5.52849435806274</t>
   </si>
   <si>
     <t xml:space="preserve">5.65134859085083</t>
@@ -1787,13 +1787,13 @@
     <t xml:space="preserve">6.01991558074951</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91461038589478</t>
+    <t xml:space="preserve">5.91460990905762</t>
   </si>
   <si>
     <t xml:space="preserve">5.84440755844116</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94971227645874</t>
+    <t xml:space="preserve">5.9497127532959</t>
   </si>
   <si>
     <t xml:space="preserve">5.86195802688599</t>
@@ -1802,19 +1802,19 @@
     <t xml:space="preserve">5.82685661315918</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93216133117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87950944900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79175567626953</t>
+    <t xml:space="preserve">5.93216180801392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87950897216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79175519943237</t>
   </si>
   <si>
     <t xml:space="preserve">5.68645048141479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45829010009766</t>
+    <t xml:space="preserve">5.45829057693481</t>
   </si>
   <si>
     <t xml:space="preserve">5.63379812240601</t>
@@ -1835,43 +1835,43 @@
     <t xml:space="preserve">5.61624717712402</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49339199066162</t>
+    <t xml:space="preserve">5.49339246749878</t>
   </si>
   <si>
     <t xml:space="preserve">5.31788444519043</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17747831344604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2652325630188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28278303146362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35298538208008</t>
+    <t xml:space="preserve">5.17747783660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26523208618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28278255462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35298585891724</t>
   </si>
   <si>
     <t xml:space="preserve">5.42318916320801</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47584104537964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38808727264404</t>
+    <t xml:space="preserve">5.4758415222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38808679580688</t>
   </si>
   <si>
     <t xml:space="preserve">5.5109429359436</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77420473098755</t>
+    <t xml:space="preserve">5.77420425415039</t>
   </si>
   <si>
     <t xml:space="preserve">5.44073963165283</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54604434967041</t>
+    <t xml:space="preserve">5.54604482650757</t>
   </si>
   <si>
     <t xml:space="preserve">6.23052453994751</t>
@@ -1889,22 +1889,22 @@
     <t xml:space="preserve">6.47623586654663</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42358303070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54643821716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98520755767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33622312545776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0905122756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16071510314941</t>
+    <t xml:space="preserve">6.42358350753784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54643869400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98520708084106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33622360229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09051179885864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16071557998657</t>
   </si>
   <si>
     <t xml:space="preserve">7.19581699371338</t>
@@ -1916,7 +1916,7 @@
     <t xml:space="preserve">6.95010662078857</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14316463470459</t>
+    <t xml:space="preserve">7.14316511154175</t>
   </si>
   <si>
     <t xml:space="preserve">7.12561368942261</t>
@@ -1925,7 +1925,7 @@
     <t xml:space="preserve">7.02030944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84519481658936</t>
+    <t xml:space="preserve">7.84519577026367</t>
   </si>
   <si>
     <t xml:space="preserve">8.3366174697876</t>
@@ -1937,16 +1937,16 @@
     <t xml:space="preserve">8.42437171936035</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08252620697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68763160705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03864860534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30190944671631</t>
+    <t xml:space="preserve">9.0825252532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68763256072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03864765167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30191040039062</t>
   </si>
   <si>
     <t xml:space="preserve">11.2763719558716</t>
@@ -1961,10 +1961,10 @@
     <t xml:space="preserve">13.1192026138306</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8559417724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0222787857056</t>
+    <t xml:space="preserve">12.8559408187866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0222797393799</t>
   </si>
   <si>
     <t xml:space="preserve">12.1100339889526</t>
@@ -1982,16 +1982,16 @@
     <t xml:space="preserve">12.1539115905762</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6712646484375</t>
+    <t xml:space="preserve">11.6712636947632</t>
   </si>
   <si>
     <t xml:space="preserve">11.7151412963867</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4518795013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0569877624512</t>
+    <t xml:space="preserve">11.4518804550171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0569887161255</t>
   </si>
   <si>
     <t xml:space="preserve">11.4957571029663</t>
@@ -2000,10 +2000,10 @@
     <t xml:space="preserve">11.4080018997192</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8906507492065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8028945922852</t>
+    <t xml:space="preserve">11.8906497955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8028955459595</t>
   </si>
   <si>
     <t xml:space="preserve">11.3202495574951</t>
@@ -2015,13 +2015,13 @@
     <t xml:space="preserve">11.1447401046753</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6182174682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5304651260376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5743408203125</t>
+    <t xml:space="preserve">10.618218421936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5304641723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5743398666382</t>
   </si>
   <si>
     <t xml:space="preserve">10.749849319458</t>
@@ -2030,16 +2030,16 @@
     <t xml:space="preserve">10.6620941162109</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3549566268921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78455638885498</t>
+    <t xml:space="preserve">10.3549556732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78455543518066</t>
   </si>
   <si>
     <t xml:space="preserve">9.91618728637695</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0916948318481</t>
+    <t xml:space="preserve">10.0916938781738</t>
   </si>
   <si>
     <t xml:space="preserve">11.232494354248</t>
@@ -2060,19 +2060,19 @@
     <t xml:space="preserve">11.0218858718872</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2500457763672</t>
+    <t xml:space="preserve">11.2500448226929</t>
   </si>
   <si>
     <t xml:space="preserve">11.3729009628296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2851476669312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1973934173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8467721939087</t>
+    <t xml:space="preserve">11.2851467132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1973943710327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8467712402344</t>
   </si>
   <si>
     <t xml:space="preserve">11.9871768951416</t>
@@ -2084,13 +2084,13 @@
     <t xml:space="preserve">12.2504396438599</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1626853942871</t>
+    <t xml:space="preserve">12.1626863479614</t>
   </si>
   <si>
     <t xml:space="preserve">12.4672012329102</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0372982025146</t>
+    <t xml:space="preserve">12.0372972488403</t>
   </si>
   <si>
     <t xml:space="preserve">12.0910348892212</t>
@@ -2105,7 +2105,7 @@
     <t xml:space="preserve">11.3924427032471</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9446268081665</t>
+    <t xml:space="preserve">10.9446258544922</t>
   </si>
   <si>
     <t xml:space="preserve">10.5505475997925</t>
@@ -2129,7 +2129,7 @@
     <t xml:space="preserve">11.0521030426025</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4999179840088</t>
+    <t xml:space="preserve">11.4999189376831</t>
   </si>
   <si>
     <t xml:space="preserve">11.482006072998</t>
@@ -2138,7 +2138,7 @@
     <t xml:space="preserve">11.4282674789429</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5715684890747</t>
+    <t xml:space="preserve">11.571569442749</t>
   </si>
   <si>
     <t xml:space="preserve">11.3745288848877</t>
@@ -2153,7 +2153,7 @@
     <t xml:space="preserve">11.4461803436279</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4640922546387</t>
+    <t xml:space="preserve">11.464093208313</t>
   </si>
   <si>
     <t xml:space="preserve">11.7148694992065</t>
@@ -2171,16 +2171,16 @@
     <t xml:space="preserve">12.6284151077271</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0731229782104</t>
+    <t xml:space="preserve">12.0731220245361</t>
   </si>
   <si>
     <t xml:space="preserve">12.3418121337891</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3597259521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6969575881958</t>
+    <t xml:space="preserve">12.3597249984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6969585418701</t>
   </si>
   <si>
     <t xml:space="preserve">12.1268606185913</t>
@@ -2192,31 +2192,31 @@
     <t xml:space="preserve">11.8581705093384</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9298219680786</t>
+    <t xml:space="preserve">11.9298210144043</t>
   </si>
   <si>
     <t xml:space="preserve">12.2880754470825</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5925893783569</t>
+    <t xml:space="preserve">12.5925903320312</t>
   </si>
   <si>
     <t xml:space="preserve">12.5030269622803</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9835596084595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3239002227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9804525375366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1774892807007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.284966468811</t>
+    <t xml:space="preserve">11.9835605621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.323899269104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9804515838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.177490234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2849674224854</t>
   </si>
   <si>
     <t xml:space="preserve">11.3387050628662</t>
@@ -2255,10 +2255,10 @@
     <t xml:space="preserve">12.8433666229248</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6821527481079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7358922958374</t>
+    <t xml:space="preserve">12.6821537017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7358913421631</t>
   </si>
   <si>
     <t xml:space="preserve">13.3449201583862</t>
@@ -2267,7 +2267,7 @@
     <t xml:space="preserve">14.2405519485474</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0972509384155</t>
+    <t xml:space="preserve">14.0972518920898</t>
   </si>
   <si>
     <t xml:space="preserve">14.3301162719727</t>
@@ -2279,16 +2279,16 @@
     <t xml:space="preserve">14.5988063812256</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8823003768921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.864387512207</t>
+    <t xml:space="preserve">13.8823013305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8643865585327</t>
   </si>
   <si>
     <t xml:space="preserve">13.577784538269</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4703092575073</t>
+    <t xml:space="preserve">13.4703102111816</t>
   </si>
   <si>
     <t xml:space="preserve">13.6852617263794</t>
@@ -2303,7 +2303,7 @@
     <t xml:space="preserve">13.6136102676392</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8285627365112</t>
+    <t xml:space="preserve">13.8285617828369</t>
   </si>
   <si>
     <t xml:space="preserve">13.953950881958</t>
@@ -2312,13 +2312,13 @@
     <t xml:space="preserve">13.4344835281372</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7210865020752</t>
+    <t xml:space="preserve">13.7210855484009</t>
   </si>
   <si>
     <t xml:space="preserve">13.5240468978882</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7031745910645</t>
+    <t xml:space="preserve">13.7031736373901</t>
   </si>
   <si>
     <t xml:space="preserve">13.2553577423096</t>
@@ -2327,7 +2327,7 @@
     <t xml:space="preserve">13.4523973464966</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3090953826904</t>
+    <t xml:space="preserve">13.3090944290161</t>
   </si>
   <si>
     <t xml:space="preserve">14.2763776779175</t>
@@ -2345,13 +2345,13 @@
     <t xml:space="preserve">14.437593460083</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7124977111816</t>
+    <t xml:space="preserve">16.7124996185303</t>
   </si>
   <si>
     <t xml:space="preserve">16.336332321167</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7156066894531</t>
+    <t xml:space="preserve">17.7156047821045</t>
   </si>
   <si>
     <t xml:space="preserve">17.2498760223389</t>
@@ -2363,7 +2363,7 @@
     <t xml:space="preserve">21.3160457611084</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4503936767578</t>
+    <t xml:space="preserve">21.4503917694092</t>
   </si>
   <si>
     <t xml:space="preserve">21.5399551391602</t>
@@ -2378,7 +2378,7 @@
     <t xml:space="preserve">21.2712669372559</t>
   </si>
   <si>
-    <t xml:space="preserve">23.017749786377</t>
+    <t xml:space="preserve">23.0177516937256</t>
   </si>
   <si>
     <t xml:space="preserve">22.3460235595703</t>
@@ -2393,7 +2393,7 @@
     <t xml:space="preserve">21.8982086181641</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4355888366699</t>
+    <t xml:space="preserve">22.4355869293213</t>
   </si>
   <si>
     <t xml:space="preserve">21.495174407959</t>
@@ -2423,13 +2423,13 @@
     <t xml:space="preserve">25.3016128540039</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2420253753662</t>
+    <t xml:space="preserve">26.2420234680176</t>
   </si>
   <si>
     <t xml:space="preserve">25.525520324707</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2120456695557</t>
+    <t xml:space="preserve">25.2120475769043</t>
   </si>
   <si>
     <t xml:space="preserve">25.8837718963623</t>
@@ -2453,7 +2453,7 @@
     <t xml:space="preserve">25.704647064209</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4211521148682</t>
+    <t xml:space="preserve">26.4211502075195</t>
   </si>
   <si>
     <t xml:space="preserve">26.0628986358643</t>
@@ -2462,13 +2462,13 @@
     <t xml:space="preserve">26.4659328460693</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1524620056152</t>
+    <t xml:space="preserve">26.1524639129639</t>
   </si>
   <si>
     <t xml:space="preserve">28.6602325439453</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6750354766846</t>
+    <t xml:space="preserve">27.6750373840332</t>
   </si>
   <si>
     <t xml:space="preserve">26.7794036865234</t>
@@ -2477,7 +2477,7 @@
     <t xml:space="preserve">26.5554962158203</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9881381988525</t>
+    <t xml:space="preserve">24.9881401062012</t>
   </si>
   <si>
     <t xml:space="preserve">25.2568302154541</t>
@@ -2486,7 +2486,7 @@
     <t xml:space="preserve">23.9581623077393</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0477275848389</t>
+    <t xml:space="preserve">24.0477256774902</t>
   </si>
   <si>
     <t xml:space="preserve">23.9133815765381</t>
@@ -2498,7 +2498,7 @@
     <t xml:space="preserve">22.077335357666</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9281845092773</t>
+    <t xml:space="preserve">22.928186416626</t>
   </si>
   <si>
     <t xml:space="preserve">23.1968765258789</t>
@@ -2507,19 +2507,19 @@
     <t xml:space="preserve">24.1820697784424</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2268543243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4955444335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3164138793945</t>
+    <t xml:space="preserve">24.2268524169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4955425262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3164157867432</t>
   </si>
   <si>
     <t xml:space="preserve">22.3908081054688</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8238201141357</t>
+    <t xml:space="preserve">23.8238182067871</t>
   </si>
   <si>
     <t xml:space="preserve">23.0625305175781</t>
@@ -2528,7 +2528,7 @@
     <t xml:space="preserve">23.7790355682373</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8834037780762</t>
+    <t xml:space="preserve">22.8834018707275</t>
   </si>
   <si>
     <t xml:space="preserve">23.2416591644287</t>
@@ -2540,10 +2540,10 @@
     <t xml:space="preserve">27.3167839050293</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6002788543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.615083694458</t>
+    <t xml:space="preserve">26.6002807617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6150817871094</t>
   </si>
   <si>
     <t xml:space="preserve">25.4359550476074</t>
@@ -2588,16 +2588,16 @@
     <t xml:space="preserve">29.7797737121582</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9885082244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.630256652832</t>
+    <t xml:space="preserve">27.9885101318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6302547454834</t>
   </si>
   <si>
     <t xml:space="preserve">27.2272205352783</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4063491821289</t>
+    <t xml:space="preserve">27.4063472747803</t>
   </si>
   <si>
     <t xml:space="preserve">26.6898403167725</t>
@@ -2612,10 +2612,10 @@
     <t xml:space="preserve">26.3315887451172</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7194519042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4507617950439</t>
+    <t xml:space="preserve">24.7194499969482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4507598876953</t>
   </si>
   <si>
     <t xml:space="preserve">23.599910736084</t>
@@ -2630,7 +2630,7 @@
     <t xml:space="preserve">28.0332889556885</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8541641235352</t>
+    <t xml:space="preserve">27.8541622161865</t>
   </si>
   <si>
     <t xml:space="preserve">28.163049697876</t>
@@ -4299,6 +4299,9 @@
   </si>
   <si>
     <t xml:space="preserve">20.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8199996948242</t>
   </si>
 </sst>
 </file>
@@ -69715,7 +69718,7 @@
     </row>
     <row r="2504">
       <c r="A2504" s="1" t="n">
-        <v>45965.6911111111</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B2504" t="n">
         <v>11358</v>
@@ -69736,6 +69739,32 @@
         <v>1428</v>
       </c>
       <c r="H2504" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2505">
+      <c r="A2505" s="1" t="n">
+        <v>45966.6912615741</v>
+      </c>
+      <c r="B2505" t="n">
+        <v>24780</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>21.3999996185303</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>19.7399997711182</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>20.2000007629395</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>19.8199996948242</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>1429</v>
+      </c>
+      <c r="H2505" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ARN.MI.xlsx
+++ b/data/ARN.MI.xlsx
@@ -38,232 +38,232 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92215025424957</t>
+    <t xml:space="preserve">1.92215013504028</t>
   </si>
   <si>
     <t xml:space="preserve">ARN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94450068473816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.917360663414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90778195858002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88383519649506</t>
+    <t xml:space="preserve">1.94450104236603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91736090183258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90778183937073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88383448123932</t>
   </si>
   <si>
     <t xml:space="preserve">1.93172919750214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91576433181763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83434426784515</t>
+    <t xml:space="preserve">1.91576421260834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83434450626373</t>
   </si>
   <si>
     <t xml:space="preserve">1.8359409570694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91097462177277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80720400810242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74973118305206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71620547771454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80401134490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8103973865509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79602909088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7720822095871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70662665367126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6970477104187</t>
+    <t xml:space="preserve">1.91097521781921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80720412731171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74973106384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71620571613312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80401146411896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81039702892303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79602897167206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77208197116852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70662653446198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69704759120941</t>
   </si>
   <si>
     <t xml:space="preserve">1.69066202640533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67629373073578</t>
+    <t xml:space="preserve">1.67629361152649</t>
   </si>
   <si>
     <t xml:space="preserve">1.70024085044861</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69864451885223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67469716072083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66671478748322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66032898426056</t>
+    <t xml:space="preserve">1.69864439964294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67469727993011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66671502590179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66032886505127</t>
   </si>
   <si>
     <t xml:space="preserve">1.8151867389679</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82795822620392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86148416996002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88543140888214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89181685447693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92853581905365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95407950878143</t>
+    <t xml:space="preserve">1.82795834541321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8614844083786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88543128967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89181709289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92853605747223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9540798664093</t>
   </si>
   <si>
     <t xml:space="preserve">1.90618538856506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8678697347641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88064193725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85190546512604</t>
+    <t xml:space="preserve">1.86787021160126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88064181804657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85190558433533</t>
   </si>
   <si>
     <t xml:space="preserve">1.85988783836365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85509848594666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79283618927002</t>
+    <t xml:space="preserve">1.85509836673737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79283595085144</t>
   </si>
   <si>
     <t xml:space="preserve">1.78804671764374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78006422519684</t>
+    <t xml:space="preserve">1.78006446361542</t>
   </si>
   <si>
     <t xml:space="preserve">1.75611734390259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76888906955719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76409959793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78485381603241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77048552036285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72099483013153</t>
+    <t xml:space="preserve">1.76888859272003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76409947872162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78485357761383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77048540115356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72099471092224</t>
   </si>
   <si>
     <t xml:space="preserve">1.73536312580109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.802414894104</t>
+    <t xml:space="preserve">1.80241465568542</t>
   </si>
   <si>
     <t xml:space="preserve">1.76250326633453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74494194984436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73217010498047</t>
+    <t xml:space="preserve">1.74494183063507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73216998577118</t>
   </si>
   <si>
     <t xml:space="preserve">1.73695969581604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74334561824799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75132775306702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68587267398834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67789030075073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65234649181366</t>
+    <t xml:space="preserve">1.7433454990387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75132763385773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68587231636047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67789006233215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65234661102295</t>
   </si>
   <si>
     <t xml:space="preserve">1.6204172372818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64276790618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5900844335556</t>
+    <t xml:space="preserve">1.64276814460754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59008431434631</t>
   </si>
   <si>
     <t xml:space="preserve">1.60285592079163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54937422275543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51185727119446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45598077774048</t>
+    <t xml:space="preserve">1.54937446117401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51185739040375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45598101615906</t>
   </si>
   <si>
     <t xml:space="preserve">1.43682312965393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46955060958862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49748921394348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4767347574234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47274386882782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46875250339508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49669063091278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47593653202057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50626969337463</t>
+    <t xml:space="preserve">1.46955072879791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4974889755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47673499584198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47274363040924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46875262260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49669086933136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47593688964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50626957416534</t>
   </si>
   <si>
     <t xml:space="preserve">1.47753322124481</t>
@@ -272,40 +272,40 @@
     <t xml:space="preserve">1.43841958045959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40090262889862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3490172624588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30910575389862</t>
+    <t xml:space="preserve">1.40090250968933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34901762008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30910551548004</t>
   </si>
   <si>
     <t xml:space="preserve">1.34342956542969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32666671276093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34103488922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31708788871765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38653433322906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39691138267517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40649020671844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30671083927155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3234738111496</t>
+    <t xml:space="preserve">1.32666659355164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34103500843048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31708800792694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38653457164764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39691162109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40649032592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30671072006226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32347369194031</t>
   </si>
   <si>
     <t xml:space="preserve">1.30591261386871</t>
@@ -317,16 +317,16 @@
     <t xml:space="preserve">1.28994798660278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2851585149765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28595674037933</t>
+    <t xml:space="preserve">1.28515839576721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28595662117004</t>
   </si>
   <si>
     <t xml:space="preserve">1.33305263519287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33704376220703</t>
+    <t xml:space="preserve">1.33704388141632</t>
   </si>
   <si>
     <t xml:space="preserve">1.30112326145172</t>
@@ -341,94 +341,94 @@
     <t xml:space="preserve">1.35283982753754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33806359767914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27157092094421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28880977630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29291439056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30686962604523</t>
+    <t xml:space="preserve">1.33806371688843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27157080173492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28880989551544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29291427135468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30686938762665</t>
   </si>
   <si>
     <t xml:space="preserve">1.33888447284698</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34955632686615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34380996227264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33642196655273</t>
+    <t xml:space="preserve">1.34955620765686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34380984306335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33642184734344</t>
   </si>
   <si>
     <t xml:space="preserve">1.34709358215332</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30522775650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2912722826004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31425738334656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32164585590363</t>
+    <t xml:space="preserve">1.30522787570953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29127252101898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31425750255585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32164573669434</t>
   </si>
   <si>
     <t xml:space="preserve">1.26828730106354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27239167690277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2879890203476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29701888561249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24858582019806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32657134532928</t>
+    <t xml:space="preserve">1.27239179611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28798890113831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2970187664032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24858593940735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32657110691071</t>
   </si>
   <si>
     <t xml:space="preserve">1.33231735229492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35940718650818</t>
+    <t xml:space="preserve">1.35940706729889</t>
   </si>
   <si>
     <t xml:space="preserve">1.42015337944031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48664605617523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53343749046326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51619851589203</t>
+    <t xml:space="preserve">1.48664617538452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53343737125397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51619839668274</t>
   </si>
   <si>
     <t xml:space="preserve">1.51866126060486</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43739247322083</t>
+    <t xml:space="preserve">1.43739223480225</t>
   </si>
   <si>
     <t xml:space="preserve">1.46776556968689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43000423908234</t>
+    <t xml:space="preserve">1.43000411987305</t>
   </si>
   <si>
     <t xml:space="preserve">1.40948176383972</t>
@@ -437,43 +437,43 @@
     <t xml:space="preserve">1.44478034973145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55970597267151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61798977851868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70582616329193</t>
+    <t xml:space="preserve">1.5597060918808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61798989772797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70582580566406</t>
   </si>
   <si>
     <t xml:space="preserve">1.74851274490356</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72388577461243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68284094333649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67463183403015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65164661407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64179575443268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67134821414948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6647812128067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65657186508179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69597518444061</t>
+    <t xml:space="preserve">1.72388553619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6828408241272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67463171482086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65164685249329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64179587364197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67134809494019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66478109359741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65657198429108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69597506523132</t>
   </si>
   <si>
     <t xml:space="preserve">1.69433331489563</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">1.65821397304535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6811990737915</t>
+    <t xml:space="preserve">1.68119895458221</t>
   </si>
   <si>
     <t xml:space="preserve">1.68776619434357</t>
@@ -491,10 +491,10 @@
     <t xml:space="preserve">1.66806471347809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65000510215759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66313910484314</t>
+    <t xml:space="preserve">1.6500049829483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66313922405243</t>
   </si>
   <si>
     <t xml:space="preserve">1.67791545391083</t>
@@ -503,79 +503,79 @@
     <t xml:space="preserve">2.03746867179871</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04403614997864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03911018371582</t>
+    <t xml:space="preserve">2.04403591156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0391104221344</t>
   </si>
   <si>
     <t xml:space="preserve">2.04075241088867</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0522449016571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04731941223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04239416122437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19836473464966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24105143547058</t>
+    <t xml:space="preserve">2.05224514007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04731965065002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04239392280579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19836449623108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.241051197052</t>
   </si>
   <si>
     <t xml:space="preserve">2.18851399421692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17537975311279</t>
+    <t xml:space="preserve">2.17537951469421</t>
   </si>
   <si>
     <t xml:space="preserve">2.14582753181458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00627493858337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98821473121643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9931401014328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99806582927704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99642372131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99970746040344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00299096107483</t>
+    <t xml:space="preserve">2.00627446174622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98821461200714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99313998222351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99806559085846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9964234828949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99970769882202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00299143791199</t>
   </si>
   <si>
     <t xml:space="preserve">2.00791668891907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01119995117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02597618103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03254342079163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02105045318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0194091796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02433443069458</t>
+    <t xml:space="preserve">2.0111997127533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02597594261169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03254365921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02105069160461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01940894126892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.024334192276</t>
   </si>
   <si>
     <t xml:space="preserve">2.07687163352966</t>
@@ -584,58 +584,58 @@
     <t xml:space="preserve">2.05881190299988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09657311439514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14746880531311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33955931663513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27552914619446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32478332519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27881264686584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25746965408325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29851388931274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26075267791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2804548740387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30672311782837</t>
+    <t xml:space="preserve">2.09657335281372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14746856689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33955860137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27552890777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32478308677673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27881288528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25746941566467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29851412773132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26075291633606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28045439720154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30672335624695</t>
   </si>
   <si>
     <t xml:space="preserve">2.35597729682922</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34120059013367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34284281730652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3477680683136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44627571105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39209675788879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38224601745605</t>
+    <t xml:space="preserve">2.34120106697083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3428430557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34776830673218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44627618789673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39209651947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38224577903748</t>
   </si>
   <si>
     <t xml:space="preserve">2.38717150688171</t>
@@ -644,67 +644,67 @@
     <t xml:space="preserve">2.38388776779175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40523099899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38060402870178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42164897918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33791732788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32314133644104</t>
+    <t xml:space="preserve">2.4052312374115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38060426712036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42164921760559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33791780471802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32314109802246</t>
   </si>
   <si>
     <t xml:space="preserve">2.35433506965637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41015648841858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40687274932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43806672096252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41836547851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29030513763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34941005706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36418604850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37567901611328</t>
+    <t xml:space="preserve">2.41015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40687251091003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43806648254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4183657169342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29030537605286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34940981864929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36418557167053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37567853927612</t>
   </si>
   <si>
     <t xml:space="preserve">2.40194749832153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35761880874634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36747002601624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37075257301331</t>
+    <t xml:space="preserve">2.35761857032776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36746954917908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37075352668762</t>
   </si>
   <si>
     <t xml:space="preserve">2.37239527702332</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36254405975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3658275604248</t>
+    <t xml:space="preserve">2.362544298172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36582803726196</t>
   </si>
   <si>
     <t xml:space="preserve">2.39538025856018</t>
@@ -716,34 +716,34 @@
     <t xml:space="preserve">2.37403678894043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38881301879883</t>
+    <t xml:space="preserve">2.38881325721741</t>
   </si>
   <si>
     <t xml:space="preserve">2.39373850822449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3904550075531</t>
+    <t xml:space="preserve">2.39045476913452</t>
   </si>
   <si>
     <t xml:space="preserve">2.41343998908997</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40358924865723</t>
+    <t xml:space="preserve">2.40358877182007</t>
   </si>
   <si>
     <t xml:space="preserve">2.40030574798584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40851426124573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42329096794128</t>
+    <t xml:space="preserve">2.40851497650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42329072952271</t>
   </si>
   <si>
     <t xml:space="preserve">2.43149971961975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4200074672699</t>
+    <t xml:space="preserve">2.42000675201416</t>
   </si>
   <si>
     <t xml:space="preserve">2.35105180740356</t>
@@ -752,34 +752,34 @@
     <t xml:space="preserve">2.33627533912659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34612631797791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43642497062683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42657423019409</t>
+    <t xml:space="preserve">2.34612607955933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43642544746399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42657470703125</t>
   </si>
   <si>
     <t xml:space="preserve">2.42985796928406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45284295082092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47701287269592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47868013381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49201536178589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49368214607239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.475346326828</t>
+    <t xml:space="preserve">2.4528431892395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4770131111145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.478679895401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49201512336731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49368190765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47534608840942</t>
   </si>
   <si>
     <t xml:space="preserve">2.46534466743469</t>
@@ -788,28 +788,28 @@
     <t xml:space="preserve">2.48201394081116</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46867847442627</t>
+    <t xml:space="preserve">2.46867871284485</t>
   </si>
   <si>
     <t xml:space="preserve">2.4586775302887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46201109886169</t>
+    <t xml:space="preserve">2.46201086044312</t>
   </si>
   <si>
     <t xml:space="preserve">2.45534348487854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41700458526611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40867042541504</t>
+    <t xml:space="preserve">2.41700506210327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40867018699646</t>
   </si>
   <si>
     <t xml:space="preserve">2.36699771881104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3419942855835</t>
+    <t xml:space="preserve">2.34199380874634</t>
   </si>
   <si>
     <t xml:space="preserve">2.36866450309753</t>
@@ -818,73 +818,73 @@
     <t xml:space="preserve">2.35366249084473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.385333776474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38366651535034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36366367340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32532525062561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31699085235596</t>
+    <t xml:space="preserve">2.38533353805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38366627693176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36366415023804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32532501220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31699061393738</t>
   </si>
   <si>
     <t xml:space="preserve">2.28531980514526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28698635101318</t>
+    <t xml:space="preserve">2.28698658943176</t>
   </si>
   <si>
     <t xml:space="preserve">2.29698801040649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31532406806946</t>
+    <t xml:space="preserve">2.31532382965088</t>
   </si>
   <si>
     <t xml:space="preserve">2.28365278244019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28865361213684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29032063484192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30198836326599</t>
+    <t xml:space="preserve">2.28865337371826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29032015800476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30198884010315</t>
   </si>
   <si>
     <t xml:space="preserve">2.30365538597107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29365372657776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24198007583618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26698350906372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26865029335022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32699251174927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31865787506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31032347679138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24364709854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25031447410583</t>
+    <t xml:space="preserve">2.29365420341492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24198031425476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2669837474823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2686505317688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32699227333069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31865763664246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31032299995422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24364733695984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25031495094299</t>
   </si>
   <si>
     <t xml:space="preserve">2.22531127929688</t>
@@ -896,16 +896,16 @@
     <t xml:space="preserve">2.22197771072388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20697546005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20030760765076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16863679885864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17863845825195</t>
+    <t xml:space="preserve">2.20697522163391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20030784606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16863656044006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17863821983337</t>
   </si>
   <si>
     <t xml:space="preserve">2.16696953773499</t>
@@ -917,19 +917,19 @@
     <t xml:space="preserve">2.19697380065918</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18363881111145</t>
+    <t xml:space="preserve">2.18363857269287</t>
   </si>
   <si>
     <t xml:space="preserve">2.18530583381653</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1919732093811</t>
+    <t xml:space="preserve">2.19197344779968</t>
   </si>
   <si>
     <t xml:space="preserve">2.17530417442322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14196634292603</t>
+    <t xml:space="preserve">2.14196610450745</t>
   </si>
   <si>
     <t xml:space="preserve">2.15363454818726</t>
@@ -938,31 +938,31 @@
     <t xml:space="preserve">2.1436333656311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13529872894287</t>
+    <t xml:space="preserve">2.13529896736145</t>
   </si>
   <si>
     <t xml:space="preserve">2.12696433067322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12863087654114</t>
+    <t xml:space="preserve">2.12863111495972</t>
   </si>
   <si>
     <t xml:space="preserve">2.12029671669006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13029766082764</t>
+    <t xml:space="preserve">2.13029813766479</t>
   </si>
   <si>
     <t xml:space="preserve">2.11862969398499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37366533279419</t>
+    <t xml:space="preserve">2.37366509437561</t>
   </si>
   <si>
     <t xml:space="preserve">2.37533211708069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4070029258728</t>
+    <t xml:space="preserve">2.40700364112854</t>
   </si>
   <si>
     <t xml:space="preserve">2.39533519744873</t>
@@ -971,13 +971,13 @@
     <t xml:space="preserve">2.39200115203857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49868297576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49534869194031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5086841583252</t>
+    <t xml:space="preserve">2.49868249893188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49534893035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50868439674377</t>
   </si>
   <si>
     <t xml:space="preserve">2.51201796531677</t>
@@ -989,13 +989,13 @@
     <t xml:space="preserve">2.51701879501343</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52368640899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52535343170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54535627365112</t>
+    <t xml:space="preserve">2.52368664741516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52535319328308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54535579681396</t>
   </si>
   <si>
     <t xml:space="preserve">2.53368759155273</t>
@@ -1004,19 +1004,19 @@
     <t xml:space="preserve">2.53202104568481</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54035520553589</t>
+    <t xml:space="preserve">2.54035544395447</t>
   </si>
   <si>
     <t xml:space="preserve">2.52702021598816</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53868842124939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53702139854431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49701619148254</t>
+    <t xml:space="preserve">2.53868865966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53702163696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49701595306396</t>
   </si>
   <si>
     <t xml:space="preserve">2.42700624465942</t>
@@ -1028,19 +1028,19 @@
     <t xml:space="preserve">2.50535035133362</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48368048667908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45200943946838</t>
+    <t xml:space="preserve">2.48368072509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4520092010498</t>
   </si>
   <si>
     <t xml:space="preserve">2.51368474960327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54202222824097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54868984222412</t>
+    <t xml:space="preserve">2.54202246665955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54868960380554</t>
   </si>
   <si>
     <t xml:space="preserve">2.51035118103027</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">2.52035212516785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47201251983643</t>
+    <t xml:space="preserve">2.472012758255</t>
   </si>
   <si>
     <t xml:space="preserve">2.50201678276062</t>
@@ -1067,31 +1067,31 @@
     <t xml:space="preserve">2.75038456916809</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71704649925232</t>
+    <t xml:space="preserve">2.7170467376709</t>
   </si>
   <si>
     <t xml:space="preserve">2.80872583389282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80039167404175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8337299823761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78372263908386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84206461906433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75871896743774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85039877891541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85873341560364</t>
+    <t xml:space="preserve">2.80039143562317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83373022079468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78372287750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84206414222717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7587194442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85039854049683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85873317718506</t>
   </si>
   <si>
     <t xml:space="preserve">2.89207124710083</t>
@@ -1100,31 +1100,31 @@
     <t xml:space="preserve">2.82539534568787</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72538137435913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61703252792358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6420361995697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70037770271301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65870547294617</t>
+    <t xml:space="preserve">2.72538113594055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61703276634216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64203643798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70037794113159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65870523452759</t>
   </si>
   <si>
     <t xml:space="preserve">2.62536716461182</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63370203971863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59202909469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66703987121582</t>
+    <t xml:space="preserve">2.63370180130005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59202933311462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66703939437866</t>
   </si>
   <si>
     <t xml:space="preserve">2.70871210098267</t>
@@ -1136,7 +1136,7 @@
     <t xml:space="preserve">2.65037083625793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68370890617371</t>
+    <t xml:space="preserve">2.68370866775513</t>
   </si>
   <si>
     <t xml:space="preserve">2.60036373138428</t>
@@ -1151,55 +1151,55 @@
     <t xml:space="preserve">2.76705360412598</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73371577262878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79205727577209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86706781387329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87540197372437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88373637199402</t>
+    <t xml:space="preserve">2.73371553421021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79205679893494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86706757545471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87540221214294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88373684883118</t>
   </si>
   <si>
     <t xml:space="preserve">2.77538824081421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78091406822205</t>
+    <t xml:space="preserve">2.78091359138489</t>
   </si>
   <si>
     <t xml:space="preserve">2.72174549102783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73019790649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77246141433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.645672082901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70483994483948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68793487548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6625771522522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69638800621033</t>
+    <t xml:space="preserve">2.73019814491272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77246117591858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64567184448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70484042167664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68793511390686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66257691383362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69638776779175</t>
   </si>
   <si>
     <t xml:space="preserve">2.65412449836731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60340881347656</t>
+    <t xml:space="preserve">2.60340857505798</t>
   </si>
   <si>
     <t xml:space="preserve">2.63721895217896</t>
@@ -1208,28 +1208,28 @@
     <t xml:space="preserve">2.61186122894287</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57805061340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59495615959167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50197720527649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4935245513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54424023628235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5611457824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58650350570679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51888227462769</t>
+    <t xml:space="preserve">2.5780508518219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59495639801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50197696685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49352478981018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54424071311951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56114554405212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58650326728821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51888275146484</t>
   </si>
   <si>
     <t xml:space="preserve">2.53578782081604</t>
@@ -1238,25 +1238,25 @@
     <t xml:space="preserve">2.55269312858582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51043009757996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56959819793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46816658973694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48507213592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41745090484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45126128196716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39209294319153</t>
+    <t xml:space="preserve">2.5104296207428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56959843635559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46816682815552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48507189750671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41745114326477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45126152038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39209318161011</t>
   </si>
   <si>
     <t xml:space="preserve">2.38364052772522</t>
@@ -1265,19 +1265,19 @@
     <t xml:space="preserve">2.27375650405884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2991144657135</t>
+    <t xml:space="preserve">2.29911422729492</t>
   </si>
   <si>
     <t xml:space="preserve">2.36673545837402</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35828232765198</t>
+    <t xml:space="preserve">2.35828256607056</t>
   </si>
   <si>
     <t xml:space="preserve">2.43435621261597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42590355873108</t>
+    <t xml:space="preserve">2.4259033203125</t>
   </si>
   <si>
     <t xml:space="preserve">2.34982991218567</t>
@@ -1286,13 +1286,13 @@
     <t xml:space="preserve">2.28220891952515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32447242736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40899848937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45971417427063</t>
+    <t xml:space="preserve">2.32447218894958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4089982509613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45971393585205</t>
   </si>
   <si>
     <t xml:space="preserve">2.44280910491943</t>
@@ -1310,7 +1310,7 @@
     <t xml:space="preserve">2.37518763542175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47661948204041</t>
+    <t xml:space="preserve">2.47661924362183</t>
   </si>
   <si>
     <t xml:space="preserve">2.30756664276123</t>
@@ -1319,16 +1319,16 @@
     <t xml:space="preserve">2.23994588851929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29430246353149</t>
+    <t xml:space="preserve">2.29430222511292</t>
   </si>
   <si>
     <t xml:space="preserve">2.23437643051147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24293732643127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33710622787476</t>
+    <t xml:space="preserve">2.2429370880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33710646629333</t>
   </si>
   <si>
     <t xml:space="preserve">2.25149846076965</t>
@@ -1340,7 +1340,7 @@
     <t xml:space="preserve">2.26862001419067</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44839692115784</t>
+    <t xml:space="preserve">2.448397397995</t>
   </si>
   <si>
     <t xml:space="preserve">2.37134957313538</t>
@@ -1352,22 +1352,22 @@
     <t xml:space="preserve">2.28574156761169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26005911827087</t>
+    <t xml:space="preserve">2.26005887985229</t>
   </si>
   <si>
     <t xml:space="preserve">2.35422825813293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2258152961731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20869398117065</t>
+    <t xml:space="preserve">2.22581577301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20869374275208</t>
   </si>
   <si>
     <t xml:space="preserve">2.30286335945129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31998491287231</t>
+    <t xml:space="preserve">2.31998467445374</t>
   </si>
   <si>
     <t xml:space="preserve">2.37991070747375</t>
@@ -1376,7 +1376,7 @@
     <t xml:space="preserve">2.405592918396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39703226089478</t>
+    <t xml:space="preserve">2.39703249931335</t>
   </si>
   <si>
     <t xml:space="preserve">2.32854580879211</t>
@@ -1385,7 +1385,7 @@
     <t xml:space="preserve">2.38847136497498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36278915405273</t>
+    <t xml:space="preserve">2.36278891563416</t>
   </si>
   <si>
     <t xml:space="preserve">2.34566712379456</t>
@@ -1394,7 +1394,7 @@
     <t xml:space="preserve">2.20013308525085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18301153182983</t>
+    <t xml:space="preserve">2.18301129341125</t>
   </si>
   <si>
     <t xml:space="preserve">2.43983626365662</t>
@@ -1406,28 +1406,28 @@
     <t xml:space="preserve">2.6024923324585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69666147232056</t>
+    <t xml:space="preserve">2.69666123390198</t>
   </si>
   <si>
     <t xml:space="preserve">2.77370882034302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63673543930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67097878456116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61961388587952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65385746955872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68810081481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64529633522034</t>
+    <t xml:space="preserve">2.63673520088196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67097854614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61961364746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65385723114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68810057640076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64529609680176</t>
   </si>
   <si>
     <t xml:space="preserve">2.71378302574158</t>
@@ -1436,46 +1436,46 @@
     <t xml:space="preserve">2.72234392166138</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07333755493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52706146240234</t>
+    <t xml:space="preserve">3.07333779335022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5270619392395</t>
   </si>
   <si>
     <t xml:space="preserve">3.59554839134216</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6554741859436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58698773384094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6126697063446</t>
+    <t xml:space="preserve">3.65547394752502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58698797225952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61266946792603</t>
   </si>
   <si>
     <t xml:space="preserve">3.5356228351593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42433190345764</t>
+    <t xml:space="preserve">3.42433214187622</t>
   </si>
   <si>
     <t xml:space="preserve">3.54418349266052</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56986618041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55274438858032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56130504608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50994038581848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48425793647766</t>
+    <t xml:space="preserve">3.56986570358276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55274415016174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56130480766296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50993967056274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48425769805908</t>
   </si>
   <si>
     <t xml:space="preserve">3.57842659950256</t>
@@ -1484,16 +1484,16 @@
     <t xml:space="preserve">3.638352394104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74108195304871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16912317276001</t>
+    <t xml:space="preserve">3.74108290672302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16912364959717</t>
   </si>
   <si>
     <t xml:space="preserve">4.60572671890259</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15361928939819</t>
+    <t xml:space="preserve">5.15361976623535</t>
   </si>
   <si>
     <t xml:space="preserve">4.62284755706787</t>
@@ -1502,25 +1502,25 @@
     <t xml:space="preserve">4.19480609893799</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45163059234619</t>
+    <t xml:space="preserve">4.45163154602051</t>
   </si>
   <si>
     <t xml:space="preserve">4.53724002838135</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52011823654175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58860492706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34890127182007</t>
+    <t xml:space="preserve">4.52011775970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58860445022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34890174865723</t>
   </si>
   <si>
     <t xml:space="preserve">4.16056346893311</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23760986328125</t>
+    <t xml:space="preserve">4.23761081695557</t>
   </si>
   <si>
     <t xml:space="preserve">4.29753637313843</t>
@@ -1529,13 +1529,13 @@
     <t xml:space="preserve">3.89517760276794</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27879738807678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25311493873596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8935604095459</t>
+    <t xml:space="preserve">3.27879762649536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25311517715454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89356064796448</t>
   </si>
   <si>
     <t xml:space="preserve">3.15894627571106</t>
@@ -1553,40 +1553,40 @@
     <t xml:space="preserve">3.38152766227722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39008831977844</t>
+    <t xml:space="preserve">3.39008855819702</t>
   </si>
   <si>
     <t xml:space="preserve">3.84381222724915</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83525156974792</t>
+    <t xml:space="preserve">3.8352518081665</t>
   </si>
   <si>
     <t xml:space="preserve">3.87805581092834</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76676487922668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88661646842957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85237383842468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92942142486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95510292053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93798208236694</t>
+    <t xml:space="preserve">3.76676511764526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88661694526672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8523736000061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92942047119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95510339736938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93798160552979</t>
   </si>
   <si>
     <t xml:space="preserve">4.11775875091553</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25473213195801</t>
+    <t xml:space="preserve">4.25473165512085</t>
   </si>
   <si>
     <t xml:space="preserve">4.22904968261719</t>
@@ -1598,10 +1598,10 @@
     <t xml:space="preserve">4.28041458129883</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43450975418091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20336723327637</t>
+    <t xml:space="preserve">4.43450927734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20336675643921</t>
   </si>
   <si>
     <t xml:space="preserve">4.00646829605103</t>
@@ -1610,22 +1610,22 @@
     <t xml:space="preserve">4.10919857025146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15200281143188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08351564407349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94654226303101</t>
+    <t xml:space="preserve">4.15200233459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08351516723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94654273986816</t>
   </si>
   <si>
     <t xml:space="preserve">4.07495450973511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02358913421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96366405487061</t>
+    <t xml:space="preserve">4.02358961105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96366381645203</t>
   </si>
   <si>
     <t xml:space="preserve">4.13488101959229</t>
@@ -1634,25 +1634,25 @@
     <t xml:space="preserve">4.12631988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01664638519287</t>
+    <t xml:space="preserve">5.01664590835571</t>
   </si>
   <si>
     <t xml:space="preserve">4.70845651626587</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91391611099243</t>
+    <t xml:space="preserve">4.91391563415527</t>
   </si>
   <si>
     <t xml:space="preserve">4.96528100967407</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94816017150879</t>
+    <t xml:space="preserve">4.94815969467163</t>
   </si>
   <si>
     <t xml:space="preserve">5.20498466491699</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56453943252563</t>
+    <t xml:space="preserve">5.56453895568848</t>
   </si>
   <si>
     <t xml:space="preserve">5.68439054489136</t>
@@ -1661,22 +1661,22 @@
     <t xml:space="preserve">5.95833730697632</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90697193145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88985013961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57471609115601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12955331802368</t>
+    <t xml:space="preserve">5.90697240829468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88985061645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57471656799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12955379486084</t>
   </si>
   <si>
     <t xml:space="preserve">6.4035005569458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01988077163696</t>
+    <t xml:space="preserve">7.01987934112549</t>
   </si>
   <si>
     <t xml:space="preserve">7.20821809768677</t>
@@ -1685,10 +1685,10 @@
     <t xml:space="preserve">7.32807064056396</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05412292480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00275850296021</t>
+    <t xml:space="preserve">7.054123878479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00275897979736</t>
   </si>
   <si>
     <t xml:space="preserve">7.42397689819336</t>
@@ -1706,16 +1706,16 @@
     <t xml:space="preserve">6.59909105300903</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51133680343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7394962310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84480142593384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82725143432617</t>
+    <t xml:space="preserve">6.51133632659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73949670791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.844801902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82725048065186</t>
   </si>
   <si>
     <t xml:space="preserve">6.68684482574463</t>
@@ -1724,13 +1724,13 @@
     <t xml:space="preserve">6.66929340362549</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45868492126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40603256225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31827878952026</t>
+    <t xml:space="preserve">6.45868444442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4060320854187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31827831268311</t>
   </si>
   <si>
     <t xml:space="preserve">6.80970048904419</t>
@@ -1739,19 +1739,19 @@
     <t xml:space="preserve">7.17826652526855</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3537745475769</t>
+    <t xml:space="preserve">7.35377407073975</t>
   </si>
   <si>
     <t xml:space="preserve">7.26602029800415</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05541133880615</t>
+    <t xml:space="preserve">7.05541086196899</t>
   </si>
   <si>
     <t xml:space="preserve">7.07296228408813</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63419198989868</t>
+    <t xml:space="preserve">6.63419246673584</t>
   </si>
   <si>
     <t xml:space="preserve">6.44113397598267</t>
@@ -1763,31 +1763,31 @@
     <t xml:space="preserve">6.05501651763916</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03746557235718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37053680419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40563821792603</t>
+    <t xml:space="preserve">6.03746604919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37053632736206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40563774108887</t>
   </si>
   <si>
     <t xml:space="preserve">5.52849388122559</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65134954452515</t>
+    <t xml:space="preserve">5.65134906768799</t>
   </si>
   <si>
     <t xml:space="preserve">6.12521982192993</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96726274490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01991558074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91460990905762</t>
+    <t xml:space="preserve">5.96726322174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01991510391235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91461038589478</t>
   </si>
   <si>
     <t xml:space="preserve">5.844407081604</t>
@@ -1802,10 +1802,10 @@
     <t xml:space="preserve">5.82685661315918</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93216133117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87950944900513</t>
+    <t xml:space="preserve">5.93216180801392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87950897216797</t>
   </si>
   <si>
     <t xml:space="preserve">5.79175519943237</t>
@@ -1814,10 +1814,10 @@
     <t xml:space="preserve">5.68645048141479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45829010009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63379859924316</t>
+    <t xml:space="preserve">5.45829057693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63379812240601</t>
   </si>
   <si>
     <t xml:space="preserve">5.70400142669678</t>
@@ -1832,7 +1832,7 @@
     <t xml:space="preserve">5.56359529495239</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61624717712402</t>
+    <t xml:space="preserve">5.61624765396118</t>
   </si>
   <si>
     <t xml:space="preserve">5.49339246749878</t>
@@ -1847,10 +1847,10 @@
     <t xml:space="preserve">5.26523208618164</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28278255462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35298585891724</t>
+    <t xml:space="preserve">5.28278303146362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35298633575439</t>
   </si>
   <si>
     <t xml:space="preserve">5.42318916320801</t>
@@ -1862,19 +1862,19 @@
     <t xml:space="preserve">5.3880877494812</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51094341278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77420473098755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44074058532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54604482650757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23052453994751</t>
+    <t xml:space="preserve">5.5109429359436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77420425415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44073915481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54604434967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23052501678467</t>
   </si>
   <si>
     <t xml:space="preserve">6.35337972640991</t>
@@ -1886,46 +1886,46 @@
     <t xml:space="preserve">6.37093114852905</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47623586654663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42358303070068</t>
+    <t xml:space="preserve">6.47623538970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42358350753784</t>
   </si>
   <si>
     <t xml:space="preserve">6.54643869400024</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98520803451538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33622312545776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0905122756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16071557998657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19581747055054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95010614395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14316558837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12561416625977</t>
+    <t xml:space="preserve">6.98520755767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33622360229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09051179885864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16071510314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19581699371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95010662078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14316463470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12561368942261</t>
   </si>
   <si>
     <t xml:space="preserve">7.02030944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84519577026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3366174697876</t>
+    <t xml:space="preserve">7.84519386291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33661842346191</t>
   </si>
   <si>
     <t xml:space="preserve">8.31906604766846</t>
@@ -1937,7 +1937,7 @@
     <t xml:space="preserve">9.08252620697021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68763160705566</t>
+    <t xml:space="preserve">8.68763256072998</t>
   </si>
   <si>
     <t xml:space="preserve">9.03864860534668</t>
@@ -1946,16 +1946,16 @@
     <t xml:space="preserve">9.30191040039062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2763710021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1630802154541</t>
+    <t xml:space="preserve">11.2763729095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1630811691284</t>
   </si>
   <si>
     <t xml:space="preserve">13.0753259658813</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1192026138306</t>
+    <t xml:space="preserve">13.1192035675049</t>
   </si>
   <si>
     <t xml:space="preserve">12.8559408187866</t>
@@ -1967,25 +1967,25 @@
     <t xml:space="preserve">12.1100330352783</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9345254898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.36412525177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8814811706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1539115905762</t>
+    <t xml:space="preserve">11.9345264434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3641262054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8814783096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1539106369019</t>
   </si>
   <si>
     <t xml:space="preserve">11.6712636947632</t>
   </si>
   <si>
-    <t xml:space="preserve">11.715142250061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4518804550171</t>
+    <t xml:space="preserve">11.7151412963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4518795013428</t>
   </si>
   <si>
     <t xml:space="preserve">11.0569877624512</t>
@@ -2003,25 +2003,25 @@
     <t xml:space="preserve">11.8028955459595</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3202495574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6273880004883</t>
+    <t xml:space="preserve">11.3202486038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.627387046814</t>
   </si>
   <si>
     <t xml:space="preserve">11.1447410583496</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6182174682617</t>
+    <t xml:space="preserve">10.618218421936</t>
   </si>
   <si>
     <t xml:space="preserve">10.5304641723633</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5743417739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7498483657837</t>
+    <t xml:space="preserve">10.5743398666382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.749849319458</t>
   </si>
   <si>
     <t xml:space="preserve">10.6620941162109</t>
@@ -2033,13 +2033,13 @@
     <t xml:space="preserve">9.78455543518066</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91618728637695</t>
+    <t xml:space="preserve">9.91618633270264</t>
   </si>
   <si>
     <t xml:space="preserve">10.0916948318481</t>
   </si>
   <si>
-    <t xml:space="preserve">11.232494354248</t>
+    <t xml:space="preserve">11.2324953079224</t>
   </si>
   <si>
     <t xml:space="preserve">11.1886177062988</t>
@@ -2051,97 +2051,97 @@
     <t xml:space="preserve">11.3553495407104</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2675971984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0218868255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2500457763672</t>
+    <t xml:space="preserve">11.267596244812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0218858718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2500448226929</t>
   </si>
   <si>
     <t xml:space="preserve">11.3729009628296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2851467132568</t>
+    <t xml:space="preserve">11.2851476669312</t>
   </si>
   <si>
     <t xml:space="preserve">11.1973934173584</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8467712402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9871778488159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2855415344238</t>
+    <t xml:space="preserve">11.8467721939087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9871768951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2855405807495</t>
   </si>
   <si>
     <t xml:space="preserve">12.2504396438599</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1626853942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4672012329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0372982025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0910358428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.553656578064</t>
+    <t xml:space="preserve">12.1626863479614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4672002792358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.037296295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0910348892212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5536556243896</t>
   </si>
   <si>
     <t xml:space="preserve">11.6432199478149</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3924417495728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9446268081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5505485534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6759366989136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9088010787964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7117614746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6580238342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9267129898071</t>
+    <t xml:space="preserve">11.3924427032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9446258544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5505475997925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6759376525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9088020324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7117624282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6580228805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9267139434814</t>
   </si>
   <si>
     <t xml:space="preserve">11.0521030426025</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4999189376831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4820051193237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4282674789429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.571569442749</t>
+    <t xml:space="preserve">11.4999179840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.482006072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4282684326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5715684890747</t>
   </si>
   <si>
     <t xml:space="preserve">11.3745288848877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3566179275513</t>
+    <t xml:space="preserve">11.356616973877</t>
   </si>
   <si>
     <t xml:space="preserve">11.3207921981812</t>
@@ -2156,10 +2156,10 @@
     <t xml:space="preserve">11.7148694992065</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7327823638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.750696182251</t>
+    <t xml:space="preserve">11.7327833175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7506952285767</t>
   </si>
   <si>
     <t xml:space="preserve">12.1805992126465</t>
@@ -2168,16 +2168,16 @@
     <t xml:space="preserve">12.6284151077271</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0731220245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3418121337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3597249984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6969585418701</t>
+    <t xml:space="preserve">12.0731229782104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3418130874634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3597259521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6969575881958</t>
   </si>
   <si>
     <t xml:space="preserve">12.1268606185913</t>
@@ -2186,16 +2186,16 @@
     <t xml:space="preserve">12.0552110671997</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8581714630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9298219680786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2880754470825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5925893783569</t>
+    <t xml:space="preserve">11.8581705093384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9298210144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2880744934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5925903320312</t>
   </si>
   <si>
     <t xml:space="preserve">12.5030269622803</t>
@@ -2207,13 +2207,13 @@
     <t xml:space="preserve">12.3239002227783</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9804515838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.177490234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2849674224854</t>
+    <t xml:space="preserve">10.980450630188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1774892807007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.284966468811</t>
   </si>
   <si>
     <t xml:space="preserve">11.3387050628662</t>
@@ -2222,25 +2222,25 @@
     <t xml:space="preserve">11.8939962387085</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7686080932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6253061294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0014724731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1089477539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9656457901001</t>
+    <t xml:space="preserve">11.768609046936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6253070831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0014715194702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1089487075806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9656476974487</t>
   </si>
   <si>
     <t xml:space="preserve">12.1985120773315</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4313764572144</t>
+    <t xml:space="preserve">12.43137550354</t>
   </si>
   <si>
     <t xml:space="preserve">12.2522497177124</t>
@@ -2249,7 +2249,7 @@
     <t xml:space="preserve">12.8612785339355</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8433675765991</t>
+    <t xml:space="preserve">12.8433666229248</t>
   </si>
   <si>
     <t xml:space="preserve">12.6821527481079</t>
@@ -2261,16 +2261,16 @@
     <t xml:space="preserve">13.3449201583862</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2405529022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0972528457642</t>
+    <t xml:space="preserve">14.2405519485474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0972518920898</t>
   </si>
   <si>
     <t xml:space="preserve">14.3301162719727</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4734163284302</t>
+    <t xml:space="preserve">14.4734172821045</t>
   </si>
   <si>
     <t xml:space="preserve">14.5988054275513</t>
@@ -2279,10 +2279,10 @@
     <t xml:space="preserve">13.8823003768921</t>
   </si>
   <si>
-    <t xml:space="preserve">13.864387512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5777854919434</t>
+    <t xml:space="preserve">13.8643865585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.577784538269</t>
   </si>
   <si>
     <t xml:space="preserve">13.4703102111816</t>
@@ -2291,58 +2291,58 @@
     <t xml:space="preserve">13.6852607727051</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6673488616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.559871673584</t>
+    <t xml:space="preserve">13.66734790802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5598735809326</t>
   </si>
   <si>
     <t xml:space="preserve">13.6136102676392</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8285617828369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.953950881958</t>
+    <t xml:space="preserve">13.8285627365112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9539499282837</t>
   </si>
   <si>
     <t xml:space="preserve">13.4344844818115</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7210865020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5240478515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7031745910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2553577423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4523973464966</t>
+    <t xml:space="preserve">13.7210855484009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5240468978882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7031736373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2553586959839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4523983001709</t>
   </si>
   <si>
     <t xml:space="preserve">13.3090944290161</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2763776779175</t>
+    <t xml:space="preserve">14.2763786315918</t>
   </si>
   <si>
     <t xml:space="preserve">14.4196796417236</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0256004333496</t>
+    <t xml:space="preserve">14.0256013870239</t>
   </si>
   <si>
     <t xml:space="preserve">13.756911277771</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4375944137573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7124996185303</t>
+    <t xml:space="preserve">14.4375925064087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7124977111816</t>
   </si>
   <si>
     <t xml:space="preserve">16.336332321167</t>
@@ -2357,16 +2357,16 @@
     <t xml:space="preserve">19.6591281890869</t>
   </si>
   <si>
-    <t xml:space="preserve">21.316047668457</t>
+    <t xml:space="preserve">21.3160457611084</t>
   </si>
   <si>
     <t xml:space="preserve">21.4503936767578</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5399570465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2116794586182</t>
+    <t xml:space="preserve">21.5399551391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2116813659668</t>
   </si>
   <si>
     <t xml:space="preserve">21.987771987915</t>
@@ -2384,10 +2384,10 @@
     <t xml:space="preserve">22.1221179962158</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7342548370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8982105255127</t>
+    <t xml:space="preserve">23.7342529296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8982086181641</t>
   </si>
   <si>
     <t xml:space="preserve">22.4355869293213</t>
@@ -2396,34 +2396,34 @@
     <t xml:space="preserve">21.495174407959</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7190799713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9429912567139</t>
+    <t xml:space="preserve">21.7190818786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9429893493652</t>
   </si>
   <si>
     <t xml:space="preserve">21.7638645172119</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8534259796143</t>
+    <t xml:space="preserve">21.8534278869629</t>
   </si>
   <si>
     <t xml:space="preserve">23.3312187194824</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8086471557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3463916778564</t>
+    <t xml:space="preserve">21.8086452484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3463935852051</t>
   </si>
   <si>
     <t xml:space="preserve">25.3016128540039</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2420253753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5255184173584</t>
+    <t xml:space="preserve">26.2420234680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.525520324707</t>
   </si>
   <si>
     <t xml:space="preserve">25.2120494842529</t>
@@ -2432,13 +2432,13 @@
     <t xml:space="preserve">25.8837718963623</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4807376861572</t>
+    <t xml:space="preserve">25.4807395935059</t>
   </si>
   <si>
     <t xml:space="preserve">25.5703010559082</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1224842071533</t>
+    <t xml:space="preserve">25.122486114502</t>
   </si>
   <si>
     <t xml:space="preserve">24.361198425293</t>
@@ -2450,25 +2450,25 @@
     <t xml:space="preserve">25.7046489715576</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4211502075195</t>
+    <t xml:space="preserve">26.4211521148682</t>
   </si>
   <si>
     <t xml:space="preserve">26.0628986358643</t>
   </si>
   <si>
-    <t xml:space="preserve">26.465934753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1524620056152</t>
+    <t xml:space="preserve">26.4659309387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1524639129639</t>
   </si>
   <si>
     <t xml:space="preserve">28.6602325439453</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6750373840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7794036865234</t>
+    <t xml:space="preserve">27.6750354766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7794055938721</t>
   </si>
   <si>
     <t xml:space="preserve">26.5554962158203</t>
@@ -2480,10 +2480,10 @@
     <t xml:space="preserve">25.2568302154541</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9581642150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0477256774902</t>
+    <t xml:space="preserve">23.9581623077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0477275848389</t>
   </si>
   <si>
     <t xml:space="preserve">23.9133815765381</t>
@@ -2492,7 +2492,7 @@
     <t xml:space="preserve">24.5851058959961</t>
   </si>
   <si>
-    <t xml:space="preserve">22.077335357666</t>
+    <t xml:space="preserve">22.0773334503174</t>
   </si>
   <si>
     <t xml:space="preserve">22.928186416626</t>
@@ -2501,10 +2501,10 @@
     <t xml:space="preserve">23.1968765258789</t>
   </si>
   <si>
-    <t xml:space="preserve">24.182071685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2268505096436</t>
+    <t xml:space="preserve">24.1820697784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2268524169922</t>
   </si>
   <si>
     <t xml:space="preserve">24.4955425262451</t>
@@ -2525,7 +2525,7 @@
     <t xml:space="preserve">23.7790355682373</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8834018707275</t>
+    <t xml:space="preserve">22.8834037780762</t>
   </si>
   <si>
     <t xml:space="preserve">23.2416572570801</t>
@@ -2534,13 +2534,13 @@
     <t xml:space="preserve">25.1672668457031</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3167819976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6002807617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6150817871094</t>
+    <t xml:space="preserve">27.3167839050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6002788543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.615083694458</t>
   </si>
   <si>
     <t xml:space="preserve">25.4359569549561</t>
@@ -2549,10 +2549,10 @@
     <t xml:space="preserve">24.8985767364502</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9733371734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5107154846191</t>
+    <t xml:space="preserve">25.9733352661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5107173919678</t>
   </si>
   <si>
     <t xml:space="preserve">26.197244644165</t>
@@ -2564,37 +2564,37 @@
     <t xml:space="preserve">26.6450595855713</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4959125518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.048095703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9437255859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8841419219971</t>
+    <t xml:space="preserve">27.4959106445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0480937957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9437294006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8841400146484</t>
   </si>
   <si>
     <t xml:space="preserve">28.9289207458496</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7050151824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7797737121582</t>
+    <t xml:space="preserve">28.7050113677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7797718048096</t>
   </si>
   <si>
     <t xml:space="preserve">27.9885082244873</t>
   </si>
   <si>
-    <t xml:space="preserve">27.630256652832</t>
+    <t xml:space="preserve">27.6302547454834</t>
   </si>
   <si>
     <t xml:space="preserve">27.2272205352783</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4063491821289</t>
+    <t xml:space="preserve">27.4063472747803</t>
   </si>
   <si>
     <t xml:space="preserve">26.6898403167725</t>
@@ -2606,22 +2606,22 @@
     <t xml:space="preserve">25.79421043396</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3315868377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7194499969482</t>
+    <t xml:space="preserve">26.3315887451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7194519042969</t>
   </si>
   <si>
     <t xml:space="preserve">24.4507598876953</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5999126434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4655647277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3615646362305</t>
+    <t xml:space="preserve">23.5999088287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4655666351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3615665435791</t>
   </si>
   <si>
     <t xml:space="preserve">28.0332889556885</t>
@@ -2636,7 +2636,7 @@
     <t xml:space="preserve">27.6633834838867</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2979869842529</t>
+    <t xml:space="preserve">30.2979888916016</t>
   </si>
   <si>
     <t xml:space="preserve">26.891170501709</t>
@@ -2648,22 +2648,22 @@
     <t xml:space="preserve">29.662052154541</t>
   </si>
   <si>
-    <t xml:space="preserve">29.480354309082</t>
+    <t xml:space="preserve">29.4803524017334</t>
   </si>
   <si>
     <t xml:space="preserve">29.3440799713135</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5251121520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.57053565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0247821807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0702018737793</t>
+    <t xml:space="preserve">30.525110244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5705375671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0247802734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0702037811279</t>
   </si>
   <si>
     <t xml:space="preserve">30.8885059356689</t>
@@ -2678,7 +2678,7 @@
     <t xml:space="preserve">27.9359283447266</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4362602233887</t>
+    <t xml:space="preserve">27.4362621307373</t>
   </si>
   <si>
     <t xml:space="preserve">28.0722007751465</t>
@@ -2687,7 +2687,7 @@
     <t xml:space="preserve">28.4355945587158</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5264415740967</t>
+    <t xml:space="preserve">28.5264434814453</t>
   </si>
   <si>
     <t xml:space="preserve">28.4810199737549</t>
@@ -2699,13 +2699,13 @@
     <t xml:space="preserve">29.1623821258545</t>
   </si>
   <si>
-    <t xml:space="preserve">29.434928894043</t>
+    <t xml:space="preserve">29.4349308013916</t>
   </si>
   <si>
     <t xml:space="preserve">28.2538986206055</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1169605255127</t>
+    <t xml:space="preserve">29.1169567108154</t>
   </si>
   <si>
     <t xml:space="preserve">30.1162948608398</t>
@@ -2714,25 +2714,25 @@
     <t xml:space="preserve">30.9793529510498</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1610488891602</t>
+    <t xml:space="preserve">31.1610507965088</t>
   </si>
   <si>
     <t xml:space="preserve">31.479024887085</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5698719024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7969932556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7515678405762</t>
+    <t xml:space="preserve">31.5698680877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.796989440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7515659332275</t>
   </si>
   <si>
     <t xml:space="preserve">31.1156272888184</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2505645751953</t>
+    <t xml:space="preserve">33.2505683898926</t>
   </si>
   <si>
     <t xml:space="preserve">34.6587219238281</t>
@@ -2741,7 +2741,7 @@
     <t xml:space="preserve">33.8410835266113</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4770278930664</t>
+    <t xml:space="preserve">34.4770240783691</t>
   </si>
   <si>
     <t xml:space="preserve">34.386173248291</t>
@@ -2750,37 +2750,37 @@
     <t xml:space="preserve">34.5678672790527</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6132926940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.340087890625</t>
+    <t xml:space="preserve">34.6132965087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3400840759277</t>
   </si>
   <si>
     <t xml:space="preserve">34.4316024780273</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7048072814941</t>
+    <t xml:space="preserve">33.7048110961914</t>
   </si>
   <si>
     <t xml:space="preserve">33.9773559570312</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9312705993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5224494934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0682067871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7502326965332</t>
+    <t xml:space="preserve">34.931266784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5224456787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0682029724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7502365112305</t>
   </si>
   <si>
     <t xml:space="preserve">33.9319305419922</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2499008178711</t>
+    <t xml:space="preserve">34.2499046325684</t>
   </si>
   <si>
     <t xml:space="preserve">33.6139640808105</t>
@@ -2792,13 +2792,13 @@
     <t xml:space="preserve">36.6573867797852</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7936592102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6106300354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5645408630371</t>
+    <t xml:space="preserve">36.7936630249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6106338500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5645446777344</t>
   </si>
   <si>
     <t xml:space="preserve">38.1109657287598</t>
@@ -2807,22 +2807,22 @@
     <t xml:space="preserve">36.4302635192871</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3868408203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8871765136719</t>
+    <t xml:space="preserve">33.3868370056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8871726989746</t>
   </si>
   <si>
     <t xml:space="preserve">33.0688743591309</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3414154052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8865089416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2044792175293</t>
+    <t xml:space="preserve">33.3414192199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8865051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2044830322266</t>
   </si>
   <si>
     <t xml:space="preserve">34.340747833252</t>
@@ -2837,7 +2837,7 @@
     <t xml:space="preserve">32.9780197143555</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7976570129395</t>
+    <t xml:space="preserve">30.7976551055908</t>
   </si>
   <si>
     <t xml:space="preserve">29.3895034790039</t>
@@ -2846,22 +2846,22 @@
     <t xml:space="preserve">29.5257778167725</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6172904968262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3447456359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0254459381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9332637786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.205810546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1149559020996</t>
+    <t xml:space="preserve">28.6172924041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.344747543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0254440307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9332675933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2058067321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1149597167969</t>
   </si>
   <si>
     <t xml:space="preserve">32.2512359619141</t>
@@ -2870,13 +2870,13 @@
     <t xml:space="preserve">31.615291595459</t>
   </si>
   <si>
-    <t xml:space="preserve">32.024112701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1142997741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.614631652832</t>
+    <t xml:space="preserve">32.0241088867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1142959594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6146278381348</t>
   </si>
   <si>
     <t xml:space="preserve">31.2064743041992</t>
@@ -2885,10 +2885,10 @@
     <t xml:space="preserve">32.0695381164551</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5244464874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3427467346191</t>
+    <t xml:space="preserve">31.5244445800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3427486419678</t>
   </si>
   <si>
     <t xml:space="preserve">32.3420829772949</t>
@@ -2897,10 +2897,10 @@
     <t xml:space="preserve">32.5237770080566</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7054786682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1603851318359</t>
+    <t xml:space="preserve">32.7054748535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1603889465332</t>
   </si>
   <si>
     <t xml:space="preserve">34.159049987793</t>
@@ -2912,10 +2912,10 @@
     <t xml:space="preserve">34.976692199707</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9325942993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0234451293945</t>
+    <t xml:space="preserve">32.9325981140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0234489440918</t>
   </si>
   <si>
     <t xml:space="preserve">33.5231170654297</t>
@@ -2930,19 +2930,19 @@
     <t xml:space="preserve">31.8424167633057</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8878383636475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4342651367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7074756622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.70680809021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4796867370605</t>
+    <t xml:space="preserve">31.8878402709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4342613220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7074737548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7068099975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4796886444092</t>
   </si>
   <si>
     <t xml:space="preserve">29.6166248321533</t>
@@ -2954,13 +2954,13 @@
     <t xml:space="preserve">29.2532329559326</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7535629272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0708656311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8898372650146</t>
+    <t xml:space="preserve">28.7535667419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0708694458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.889835357666</t>
   </si>
   <si>
     <t xml:space="preserve">28.6627159118652</t>
@@ -2969,28 +2969,28 @@
     <t xml:space="preserve">28.8444137573242</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7081432342529</t>
+    <t xml:space="preserve">28.7081413269043</t>
   </si>
   <si>
     <t xml:space="preserve">28.9806861877441</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7989902496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8891735076904</t>
+    <t xml:space="preserve">28.7989883422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8891754150391</t>
   </si>
   <si>
     <t xml:space="preserve">29.0715351104736</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2993221282959</t>
+    <t xml:space="preserve">28.2993202209473</t>
   </si>
   <si>
     <t xml:space="preserve">28.0267772674561</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6179580688477</t>
+    <t xml:space="preserve">27.617956161499</t>
   </si>
   <si>
     <t xml:space="preserve">27.7542304992676</t>
@@ -3002,7 +3002,7 @@
     <t xml:space="preserve">28.5718688964844</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4816856384277</t>
+    <t xml:space="preserve">27.4816837310791</t>
   </si>
   <si>
     <t xml:space="preserve">27.5725345611572</t>
@@ -3017,46 +3017,46 @@
     <t xml:space="preserve">27.0274410247803</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9365940093994</t>
+    <t xml:space="preserve">26.9365921020508</t>
   </si>
   <si>
     <t xml:space="preserve">26.9820194244385</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3460788726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8918342590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6647148132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2552299499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8457450866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6640491485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4369277954102</t>
+    <t xml:space="preserve">26.346076965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8918361663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6647129058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2552280426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8457431793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6640510559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4369258880615</t>
   </si>
   <si>
     <t xml:space="preserve">26.5732002258301</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3915004730225</t>
+    <t xml:space="preserve">26.3915023803711</t>
   </si>
   <si>
     <t xml:space="preserve">26.70947265625</t>
   </si>
   <si>
-    <t xml:space="preserve">26.527774810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9826831817627</t>
+    <t xml:space="preserve">26.5277767181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9826850891113</t>
   </si>
   <si>
     <t xml:space="preserve">25.8009872436523</t>
@@ -3068,19 +3068,19 @@
     <t xml:space="preserve">23.6660442352295</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8477458953857</t>
+    <t xml:space="preserve">23.8477439880371</t>
   </si>
   <si>
     <t xml:space="preserve">25.437593460083</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7555637359619</t>
+    <t xml:space="preserve">25.7555618286133</t>
   </si>
   <si>
     <t xml:space="preserve">25.074197769165</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0735340118408</t>
+    <t xml:space="preserve">26.0735359191895</t>
   </si>
   <si>
     <t xml:space="preserve">27.6892356872559</t>
@@ -69738,25 +69738,25 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45967.6912268518</v>
+        <v>45968.6912731481</v>
       </c>
       <c r="B2505" t="n">
-        <v>14402</v>
+        <v>11495</v>
       </c>
       <c r="C2505" t="n">
-        <v>19.9200000762939</v>
+        <v>19.7600002288818</v>
       </c>
       <c r="D2505" t="n">
+        <v>19.2199993133545</v>
+      </c>
+      <c r="E2505" t="n">
         <v>19.5</v>
       </c>
-      <c r="E2505" t="n">
-        <v>19.8999996185303</v>
-      </c>
       <c r="F2505" t="n">
-        <v>19.5</v>
+        <v>19.2999992370605</v>
       </c>
       <c r="G2505" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>

--- a/data/ARN.MI.xlsx
+++ b/data/ARN.MI.xlsx
@@ -38,133 +38,133 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92215013504028</t>
+    <t xml:space="preserve">1.92215001583099</t>
   </si>
   <si>
     <t xml:space="preserve">ARN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94450080394745</t>
+    <t xml:space="preserve">1.94450068473816</t>
   </si>
   <si>
     <t xml:space="preserve">1.91736078262329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90778183937073</t>
+    <t xml:space="preserve">1.90778195858002</t>
   </si>
   <si>
     <t xml:space="preserve">1.88383483886719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93172943592072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91576397418976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83434402942657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83594059944153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91097486019135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80720448493958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74973106384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71620559692383</t>
+    <t xml:space="preserve">1.93172883987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91576421260834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83434414863586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83594083786011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91097462177277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.807204246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74973130226135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71620571613312</t>
   </si>
   <si>
     <t xml:space="preserve">1.80401122570038</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81039726734161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79602921009064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77208209037781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70662677288055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69704782962799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69066202640533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6762934923172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7002409696579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69864428043365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67469727993011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66671466827393</t>
+    <t xml:space="preserve">1.81039714813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79602909088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77208197116852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70662689208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6970477104187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69066178798676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67629373073578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70024108886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69864439964294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67469716072083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66671502590179</t>
   </si>
   <si>
     <t xml:space="preserve">1.66032898426056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81518650054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82795834541321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86148416996002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88543128967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89181685447693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92853605747223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95407938957214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90618538856506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86787021160126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88064181804657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85190522670746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85988771915436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85509860515594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79283618927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78804659843445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78006410598755</t>
+    <t xml:space="preserve">1.81518626213074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82795858383179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8614844083786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88543140888214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89181756973267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92853569984436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95407927036285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90618503093719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86786997318268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88064193725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85190558433533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85988759994507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85509812831879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79283630847931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78804671764374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78006422519684</t>
   </si>
   <si>
     <t xml:space="preserve">1.7561172246933</t>
@@ -173,115 +173,115 @@
     <t xml:space="preserve">1.76888883113861</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76409959793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78485381603241</t>
+    <t xml:space="preserve">1.76409935951233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78485405445099</t>
   </si>
   <si>
     <t xml:space="preserve">1.77048540115356</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72099459171295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73536312580109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80241477489471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76250326633453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74494206905365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73217022418976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73695957660675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74334561824799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75132775306702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68587279319763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67789018154144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65234661102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6204172372818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64276790618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5900844335556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60285592079163</t>
+    <t xml:space="preserve">1.72099483013153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73536288738251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80241441726685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76250302791595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74494218826294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73217034339905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73695969581604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74334537982941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7513279914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68587255477905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67789006233215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65234673023224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62041735649109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64276778697968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59008431434631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60285580158234</t>
   </si>
   <si>
     <t xml:space="preserve">1.54937434196472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51185739040375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45598089694977</t>
+    <t xml:space="preserve">1.51185715198517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45598077774048</t>
   </si>
   <si>
     <t xml:space="preserve">1.43682324886322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4695508480072</t>
+    <t xml:space="preserve">1.46955060958862</t>
   </si>
   <si>
     <t xml:space="preserve">1.49748909473419</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47673511505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47274374961853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46875262260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49669098854065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47593677043915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50626969337463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4775333404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43841969966888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40090250968933</t>
+    <t xml:space="preserve">1.47673499584198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47274363040924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46875250339508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49669075012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47593665122986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50626957416534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47753322124481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43841958045959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40090274810791</t>
   </si>
   <si>
     <t xml:space="preserve">1.34901738166809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30910563468933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34342956542969</t>
+    <t xml:space="preserve">1.30910551548004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34342968463898</t>
   </si>
   <si>
     <t xml:space="preserve">1.32666671276093</t>
@@ -293,28 +293,28 @@
     <t xml:space="preserve">1.31708800792694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38653445243835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39691126346588</t>
+    <t xml:space="preserve">1.38653457164764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39691162109375</t>
   </si>
   <si>
     <t xml:space="preserve">1.40649032592773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30671072006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3234738111496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30591261386871</t>
+    <t xml:space="preserve">1.30671095848083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32347393035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30591285228729</t>
   </si>
   <si>
     <t xml:space="preserve">1.31229853630066</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28994798660278</t>
+    <t xml:space="preserve">1.28994786739349</t>
   </si>
   <si>
     <t xml:space="preserve">1.28515863418579</t>
@@ -323,19 +323,19 @@
     <t xml:space="preserve">1.28595674037933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33305251598358</t>
+    <t xml:space="preserve">1.33305263519287</t>
   </si>
   <si>
     <t xml:space="preserve">1.33704388141632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30112314224243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36104869842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34627270698547</t>
+    <t xml:space="preserve">1.30112326145172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36104881763458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34627258777618</t>
   </si>
   <si>
     <t xml:space="preserve">1.35283970832825</t>
@@ -344,73 +344,73 @@
     <t xml:space="preserve">1.33806359767914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27157092094421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28880965709686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29291450977325</t>
+    <t xml:space="preserve">1.27157080173492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28880977630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29291427135468</t>
   </si>
   <si>
     <t xml:space="preserve">1.30686962604523</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3388843536377</t>
+    <t xml:space="preserve">1.33888459205627</t>
   </si>
   <si>
     <t xml:space="preserve">1.34955620765686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34381008148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33642184734344</t>
+    <t xml:space="preserve">1.34380984306335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33642196655273</t>
   </si>
   <si>
     <t xml:space="preserve">1.34709358215332</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30522763729095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2912722826004</t>
+    <t xml:space="preserve">1.30522775650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29127252101898</t>
   </si>
   <si>
     <t xml:space="preserve">1.31425750255585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32164573669434</t>
+    <t xml:space="preserve">1.32164561748505</t>
   </si>
   <si>
     <t xml:space="preserve">1.26828730106354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27239191532135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28798890113831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2970187664032</t>
+    <t xml:space="preserve">1.27239167690277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28798878192902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29701888561249</t>
   </si>
   <si>
     <t xml:space="preserve">1.24858593940735</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32657110691071</t>
+    <t xml:space="preserve">1.32657098770142</t>
   </si>
   <si>
     <t xml:space="preserve">1.33231735229492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3594069480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42015361785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48664629459381</t>
+    <t xml:space="preserve">1.35940706729889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4201534986496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4866464138031</t>
   </si>
   <si>
     <t xml:space="preserve">1.53343749046326</t>
@@ -419,64 +419,64 @@
     <t xml:space="preserve">1.51619851589203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51866114139557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43739247322083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46776568889618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43000411987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40948164463043</t>
+    <t xml:space="preserve">1.51866137981415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43739235401154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4677654504776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43000400066376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40948176383972</t>
   </si>
   <si>
     <t xml:space="preserve">1.44478023052216</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55970621109009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61798977851868</t>
+    <t xml:space="preserve">1.5597060918808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61798989772797</t>
   </si>
   <si>
     <t xml:space="preserve">1.70582604408264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74851262569427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72388541698456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6828408241272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67463183403015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.651646733284</t>
+    <t xml:space="preserve">1.74851274490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72388577461243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68284070491791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67463171482086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65164661407471</t>
   </si>
   <si>
     <t xml:space="preserve">1.64179587364197</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67134833335876</t>
+    <t xml:space="preserve">1.67134821414948</t>
   </si>
   <si>
     <t xml:space="preserve">1.66478109359741</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65657210350037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69597494602203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69433307647705</t>
+    <t xml:space="preserve">1.65657198429108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69597518444061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69433319568634</t>
   </si>
   <si>
     <t xml:space="preserve">1.65821385383606</t>
@@ -488,7 +488,7 @@
     <t xml:space="preserve">1.68776619434357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66806447505951</t>
+    <t xml:space="preserve">1.66806471347809</t>
   </si>
   <si>
     <t xml:space="preserve">1.65000474452972</t>
@@ -500,31 +500,31 @@
     <t xml:space="preserve">1.67791533470154</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03746914863586</t>
+    <t xml:space="preserve">2.03746891021729</t>
   </si>
   <si>
     <t xml:space="preserve">2.04403591156006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03910994529724</t>
+    <t xml:space="preserve">2.0391104221344</t>
   </si>
   <si>
     <t xml:space="preserve">2.04075264930725</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0522449016571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04731941223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04239344596863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19836497306824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24105143547058</t>
+    <t xml:space="preserve">2.05224466323853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04731965065002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04239416122437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19836449623108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.241051197052</t>
   </si>
   <si>
     <t xml:space="preserve">2.18851375579834</t>
@@ -533,28 +533,28 @@
     <t xml:space="preserve">2.17537951469421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14582753181458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00627470016479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98821485042572</t>
+    <t xml:space="preserve">2.145827293396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00627446174622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98821461200714</t>
   </si>
   <si>
     <t xml:space="preserve">1.99314022064209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99806535243988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99642395973206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99970769882202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00299072265625</t>
+    <t xml:space="preserve">1.99806559085846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99642360210419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99970734119415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00299096107483</t>
   </si>
   <si>
     <t xml:space="preserve">2.00791645050049</t>
@@ -563,22 +563,22 @@
     <t xml:space="preserve">2.01119995117188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02597594261169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03254318237305</t>
+    <t xml:space="preserve">2.02597618103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03254342079163</t>
   </si>
   <si>
     <t xml:space="preserve">2.02105069160461</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01940894126892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02433490753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07687163352966</t>
+    <t xml:space="preserve">2.0194091796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.024334192276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07687187194824</t>
   </si>
   <si>
     <t xml:space="preserve">2.05881214141846</t>
@@ -587,10 +587,10 @@
     <t xml:space="preserve">2.09657311439514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14746856689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33955907821655</t>
+    <t xml:space="preserve">2.14746904373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33955883979797</t>
   </si>
   <si>
     <t xml:space="preserve">2.27552938461304</t>
@@ -608,52 +608,52 @@
     <t xml:space="preserve">2.2985143661499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26075315475464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28045439720154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30672359466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35597705841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34120082855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34284257888794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34776830673218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44627618789673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39209675788879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3822455406189</t>
+    <t xml:space="preserve">2.26075291633606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2804548740387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30672311782837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35597729682922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34120106697083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3428430557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34776782989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44627571105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39209651947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38224577903748</t>
   </si>
   <si>
     <t xml:space="preserve">2.38717126846313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38388752937317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40523147583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38060426712036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42164921760559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33791708946228</t>
+    <t xml:space="preserve">2.38388776779175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40523099899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3806037902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42164874076843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33791756629944</t>
   </si>
   <si>
     <t xml:space="preserve">2.32314133644104</t>
@@ -662,19 +662,19 @@
     <t xml:space="preserve">2.35433530807495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41015648841858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40687251091003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43806648254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41836547851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2903048992157</t>
+    <t xml:space="preserve">2.41015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40687274932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43806672096252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4183657169342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29030561447144</t>
   </si>
   <si>
     <t xml:space="preserve">2.34940981864929</t>
@@ -689,46 +689,46 @@
     <t xml:space="preserve">2.40194749832153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35761904716492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36746954917908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37075304985046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37239527702332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36254453659058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36582779884338</t>
+    <t xml:space="preserve">2.35761857032776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36746978759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37075328826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37239503860474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36254405975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36582827568054</t>
   </si>
   <si>
     <t xml:space="preserve">2.39538025856018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37732028961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37403655052185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38881301879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39373850822449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39045476913452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41344022750854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40358924865723</t>
+    <t xml:space="preserve">2.3773205280304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37403678894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38881325721741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39373826980591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39045453071594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41344046592712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40358877182007</t>
   </si>
   <si>
     <t xml:space="preserve">2.40030574798584</t>
@@ -737,13 +737,13 @@
     <t xml:space="preserve">2.40851449966431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42329049110413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43149948120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42000699043274</t>
+    <t xml:space="preserve">2.42329025268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43149995803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4200074672699</t>
   </si>
   <si>
     <t xml:space="preserve">2.35105180740356</t>
@@ -752,19 +752,19 @@
     <t xml:space="preserve">2.33627533912659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34612631797791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43642473220825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42657399177551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42985773086548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4528431892395</t>
+    <t xml:space="preserve">2.34612607955933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43642497062683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42657423019409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42985820770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45284295082092</t>
   </si>
   <si>
     <t xml:space="preserve">2.4770131111145</t>
@@ -779,19 +779,19 @@
     <t xml:space="preserve">2.49368214607239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.475346326828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46534466743469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48201370239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46867871284485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4586775302887</t>
+    <t xml:space="preserve">2.47534608840942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46534442901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.482013463974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46867847442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45867705345154</t>
   </si>
   <si>
     <t xml:space="preserve">2.46201109886169</t>
@@ -800,13 +800,13 @@
     <t xml:space="preserve">2.45534348487854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41700482368469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4086709022522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36699771881104</t>
+    <t xml:space="preserve">2.41700506210327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40867018699646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36699748039246</t>
   </si>
   <si>
     <t xml:space="preserve">2.3419942855835</t>
@@ -821,19 +821,19 @@
     <t xml:space="preserve">2.38533353805542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38366675376892</t>
+    <t xml:space="preserve">2.38366651535034</t>
   </si>
   <si>
     <t xml:space="preserve">2.36366367340088</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32532501220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31699109077454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28531980514526</t>
+    <t xml:space="preserve">2.32532525062561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31699061393738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28531956672668</t>
   </si>
   <si>
     <t xml:space="preserve">2.28698658943176</t>
@@ -842,13 +842,13 @@
     <t xml:space="preserve">2.29698801040649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31532382965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28365278244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28865361213684</t>
+    <t xml:space="preserve">2.31532406806946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28365254402161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28865313529968</t>
   </si>
   <si>
     <t xml:space="preserve">2.29032015800476</t>
@@ -860,40 +860,40 @@
     <t xml:space="preserve">2.30365562438965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29365396499634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24198031425476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2669837474823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26865029335022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32699203491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31865739822388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3103232383728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24364686012268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25031471252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22531151771545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25198149681091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22197723388672</t>
+    <t xml:space="preserve">2.29365420341492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24198007583618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26698398590088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2686505317688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32699227333069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31865763664246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31032371520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24364709854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25031495094299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22531127929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25198125839233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2219774723053</t>
   </si>
   <si>
     <t xml:space="preserve">2.20697546005249</t>
@@ -905,7 +905,7 @@
     <t xml:space="preserve">2.16863656044006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17863821983337</t>
+    <t xml:space="preserve">2.17863798141479</t>
   </si>
   <si>
     <t xml:space="preserve">2.16696977615356</t>
@@ -914,10 +914,10 @@
     <t xml:space="preserve">2.18697237968445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19697427749634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18363881111145</t>
+    <t xml:space="preserve">2.19697403907776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18363857269287</t>
   </si>
   <si>
     <t xml:space="preserve">2.18530583381653</t>
@@ -929,13 +929,13 @@
     <t xml:space="preserve">2.17530417442322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14196586608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15363454818726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14363360404968</t>
+    <t xml:space="preserve">2.14196610450745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15363478660583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14363312721252</t>
   </si>
   <si>
     <t xml:space="preserve">2.13529849052429</t>
@@ -944,46 +944,46 @@
     <t xml:space="preserve">2.12696433067322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12863111495972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12029623985291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13029789924622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11862993240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37366533279419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37533235549927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40700316429138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39533519744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39200139045715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49868249893188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49534893035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5086841583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51201820373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51535201072693</t>
+    <t xml:space="preserve">2.12863087654114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12029647827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13029813766479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11862945556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37366557121277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37533211708069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40700340270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39533495903015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39200115203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49868273735046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49534916877747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50868439674377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51201796531677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51535153388977</t>
   </si>
   <si>
     <t xml:space="preserve">2.51701879501343</t>
@@ -998,7 +998,7 @@
     <t xml:space="preserve">2.54535603523254</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53368759155273</t>
+    <t xml:space="preserve">2.53368735313416</t>
   </si>
   <si>
     <t xml:space="preserve">2.53202104568481</t>
@@ -1007,7 +1007,7 @@
     <t xml:space="preserve">2.54035544395447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52702021598816</t>
+    <t xml:space="preserve">2.52702045440674</t>
   </si>
   <si>
     <t xml:space="preserve">2.53868842124939</t>
@@ -1016,52 +1016,52 @@
     <t xml:space="preserve">2.53702139854431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49701619148254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42700624465942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50034976005554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5053505897522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48368072509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45200943946838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51368474960327</t>
+    <t xml:space="preserve">2.49701595306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42700600624084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5003502368927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50535011291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48368048667908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4520092010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51368522644043</t>
   </si>
   <si>
     <t xml:space="preserve">2.54202222824097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5486900806427</t>
+    <t xml:space="preserve">2.54868984222412</t>
   </si>
   <si>
     <t xml:space="preserve">2.51035118103027</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52035212516785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47201251983643</t>
+    <t xml:space="preserve">2.52035236358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47201228141785</t>
   </si>
   <si>
     <t xml:space="preserve">2.50201654434204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48701453208923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00041961669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81706047058105</t>
+    <t xml:space="preserve">2.48701429367065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00041937828064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81706094741821</t>
   </si>
   <si>
     <t xml:space="preserve">2.75038456916809</t>
@@ -1073,37 +1073,37 @@
     <t xml:space="preserve">2.8087260723114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80039167404175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83372974395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78372263908386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84206438064575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75871920585632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85039877891541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85873365402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89207124710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82539534568787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72538089752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61703276634216</t>
+    <t xml:space="preserve">2.80039191246033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83372950553894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7837221622467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84206414222717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75871896743774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85039901733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85873317718506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89207100868225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82539510726929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72538113594055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61703300476074</t>
   </si>
   <si>
     <t xml:space="preserve">2.6420361995697</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.70037770271301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65870499610901</t>
+    <t xml:space="preserve">2.65870475769043</t>
   </si>
   <si>
     <t xml:space="preserve">2.62536716461182</t>
@@ -1121,22 +1121,22 @@
     <t xml:space="preserve">2.63370180130005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59202885627747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66703987121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70871186256409</t>
+    <t xml:space="preserve">2.59202909469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66703963279724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70871210098267</t>
   </si>
   <si>
     <t xml:space="preserve">2.74205017089844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65037035942078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68370890617371</t>
+    <t xml:space="preserve">2.65037083625793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68370866775513</t>
   </si>
   <si>
     <t xml:space="preserve">2.60036373138428</t>
@@ -1151,22 +1151,22 @@
     <t xml:space="preserve">2.76705360412598</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73371577262878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79205703735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86706757545471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87540221214294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88373684883118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77538824081421</t>
+    <t xml:space="preserve">2.73371553421021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79205679893494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86706781387329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87540197372437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8837366104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77538776397705</t>
   </si>
   <si>
     <t xml:space="preserve">2.78091406822205</t>
@@ -1175,34 +1175,34 @@
     <t xml:space="preserve">2.72174549102783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7301983833313</t>
+    <t xml:space="preserve">2.73019814491272</t>
   </si>
   <si>
     <t xml:space="preserve">2.77246117591858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64567160606384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70484042167664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68793487548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6625771522522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69638752937317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65412449836731</t>
+    <t xml:space="preserve">2.64567184448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70484018325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68793511390686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66257739067078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69638729095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65412473678589</t>
   </si>
   <si>
     <t xml:space="preserve">2.60340857505798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63721895217896</t>
+    <t xml:space="preserve">2.63721919059753</t>
   </si>
   <si>
     <t xml:space="preserve">2.61186122894287</t>
@@ -1217,7 +1217,7 @@
     <t xml:space="preserve">2.50197720527649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49352478981018</t>
+    <t xml:space="preserve">2.49352431297302</t>
   </si>
   <si>
     <t xml:space="preserve">2.54424047470093</t>
@@ -1229,16 +1229,16 @@
     <t xml:space="preserve">2.58650326728821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51888251304626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53578782081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55269312858582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5104296207428</t>
+    <t xml:space="preserve">2.51888227462769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53578805923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55269289016724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51042985916138</t>
   </si>
   <si>
     <t xml:space="preserve">2.56959795951843</t>
@@ -1250,31 +1250,31 @@
     <t xml:space="preserve">2.48507213592529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41745090484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45126152038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39209342002869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3836407661438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27375674247742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29911422729492</t>
+    <t xml:space="preserve">2.41745066642761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45126175880432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39209270477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38364028930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27375626564026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2991144657135</t>
   </si>
   <si>
     <t xml:space="preserve">2.36673521995544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35828256607056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43435668945312</t>
+    <t xml:space="preserve">2.35828280448914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43435645103455</t>
   </si>
   <si>
     <t xml:space="preserve">2.42590355873108</t>
@@ -1286,28 +1286,28 @@
     <t xml:space="preserve">2.28220891952515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32447242736816</t>
+    <t xml:space="preserve">2.32447218894958</t>
   </si>
   <si>
     <t xml:space="preserve">2.4089982509613</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45971417427063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44280934333801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33292484283447</t>
+    <t xml:space="preserve">2.45971441268921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44280886650085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33292460441589</t>
   </si>
   <si>
     <t xml:space="preserve">2.34137725830078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.400545835495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37518811225891</t>
+    <t xml:space="preserve">2.40054559707642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37518787384033</t>
   </si>
   <si>
     <t xml:space="preserve">2.47661948204041</t>
@@ -1316,58 +1316,58 @@
     <t xml:space="preserve">2.30756664276123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23994588851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29430222511292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2343761920929</t>
+    <t xml:space="preserve">2.23994612693787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29430246353149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23437643051147</t>
   </si>
   <si>
     <t xml:space="preserve">2.2429370880127</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33710646629333</t>
+    <t xml:space="preserve">2.33710622787476</t>
   </si>
   <si>
     <t xml:space="preserve">2.25149846076965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27718067169189</t>
+    <t xml:space="preserve">2.27718091011047</t>
   </si>
   <si>
     <t xml:space="preserve">2.26862001419067</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44839715957642</t>
+    <t xml:space="preserve">2.44839692115784</t>
   </si>
   <si>
     <t xml:space="preserve">2.37134981155396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31142377853394</t>
+    <t xml:space="preserve">2.31142401695251</t>
   </si>
   <si>
     <t xml:space="preserve">2.28574156761169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26005887985229</t>
+    <t xml:space="preserve">2.26005911827087</t>
   </si>
   <si>
     <t xml:space="preserve">2.35422825813293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22581577301025</t>
+    <t xml:space="preserve">2.22581553459167</t>
   </si>
   <si>
     <t xml:space="preserve">2.20869398117065</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30286359786987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31998467445374</t>
+    <t xml:space="preserve">2.30286312103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31998443603516</t>
   </si>
   <si>
     <t xml:space="preserve">2.37991046905518</t>
@@ -1379,10 +1379,10 @@
     <t xml:space="preserve">2.39703226089478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32854557037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38847136497498</t>
+    <t xml:space="preserve">2.32854580879211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38847160339355</t>
   </si>
   <si>
     <t xml:space="preserve">2.36278891563416</t>
@@ -1397,13 +1397,13 @@
     <t xml:space="preserve">2.18301153182983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4398365020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5425660610199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6024923324585</t>
+    <t xml:space="preserve">2.43983626365662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54256629943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60249185562134</t>
   </si>
   <si>
     <t xml:space="preserve">2.69666147232056</t>
@@ -1415,25 +1415,25 @@
     <t xml:space="preserve">2.63673543930054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67097854614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61961388587952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65385723114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68810033798218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64529633522034</t>
+    <t xml:space="preserve">2.67097878456116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61961364746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65385675430298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68810081481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64529609680176</t>
   </si>
   <si>
     <t xml:space="preserve">2.71378302574158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7223436832428</t>
+    <t xml:space="preserve">2.72234392166138</t>
   </si>
   <si>
     <t xml:space="preserve">3.07333755493164</t>
@@ -1442,46 +1442,46 @@
     <t xml:space="preserve">3.52706170082092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59554862976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65547442436218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58698797225952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61266946792603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5356228351593</t>
+    <t xml:space="preserve">3.59554839134216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6554741859436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58698749542236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61267018318176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53562259674072</t>
   </si>
   <si>
     <t xml:space="preserve">3.42433190345764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54418325424194</t>
+    <t xml:space="preserve">3.54418349266052</t>
   </si>
   <si>
     <t xml:space="preserve">3.56986594200134</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5527446269989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56130480766296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50993990898132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48425793647766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57842659950256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63835287094116</t>
+    <t xml:space="preserve">3.55274415016174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56130504608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5099401473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48425769805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57842636108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.638352394104</t>
   </si>
   <si>
     <t xml:space="preserve">3.74108242988586</t>
@@ -1490,43 +1490,43 @@
     <t xml:space="preserve">4.16912412643433</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60572719573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15361928939819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62284755706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19480562210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45163154602051</t>
+    <t xml:space="preserve">4.60572624206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15361976623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62284803390503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19480657577515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45163106918335</t>
   </si>
   <si>
     <t xml:space="preserve">4.53724002838135</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52011775970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58860445022583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34890174865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16056346893311</t>
+    <t xml:space="preserve">4.52011823654175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58860492706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34890127182007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16056299209595</t>
   </si>
   <si>
     <t xml:space="preserve">4.23761034011841</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29753589630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8951780796051</t>
+    <t xml:space="preserve">4.29753732681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89517712593079</t>
   </si>
   <si>
     <t xml:space="preserve">3.27879738807678</t>
@@ -1538,46 +1538,46 @@
     <t xml:space="preserve">2.89356064796448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15894627571106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1675066947937</t>
+    <t xml:space="preserve">3.1589457988739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16750717163086</t>
   </si>
   <si>
     <t xml:space="preserve">3.0390944480896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44145369529724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38152766227722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3900887966156</t>
+    <t xml:space="preserve">3.44145321846008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38152742385864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39008831977844</t>
   </si>
   <si>
     <t xml:space="preserve">3.84381222724915</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83525133132935</t>
+    <t xml:space="preserve">3.8352518081665</t>
   </si>
   <si>
     <t xml:space="preserve">3.87805581092834</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76676464080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88661646842957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8523736000061</t>
+    <t xml:space="preserve">3.76676511764526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88661670684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85237383842468</t>
   </si>
   <si>
     <t xml:space="preserve">3.92942094802856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95510292053223</t>
+    <t xml:space="preserve">3.95510339736938</t>
   </si>
   <si>
     <t xml:space="preserve">3.93798208236694</t>
@@ -1586,52 +1586,52 @@
     <t xml:space="preserve">4.11775922775269</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25473260879517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22905015945435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26329326629639</t>
+    <t xml:space="preserve">4.25473165512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22904920578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26329278945923</t>
   </si>
   <si>
     <t xml:space="preserve">4.28041410446167</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43450975418091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20336675643921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00646829605103</t>
+    <t xml:space="preserve">4.43450927734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20336723327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00646781921387</t>
   </si>
   <si>
     <t xml:space="preserve">4.10919857025146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15200185775757</t>
+    <t xml:space="preserve">4.15200233459473</t>
   </si>
   <si>
     <t xml:space="preserve">4.08351564407349</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94654226303101</t>
+    <t xml:space="preserve">3.94654273986816</t>
   </si>
   <si>
     <t xml:space="preserve">4.07495498657227</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02359008789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96366429328918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13488101959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12632036209106</t>
+    <t xml:space="preserve">4.02358913421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96366453170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13488054275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12631988525391</t>
   </si>
   <si>
     <t xml:space="preserve">5.01664638519287</t>
@@ -1640,298 +1640,298 @@
     <t xml:space="preserve">4.70845651626587</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91391563415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96528100967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94815921783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20498466491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56453895568848</t>
+    <t xml:space="preserve">4.91391611099243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96528148651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94815969467163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20498371124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56453943252563</t>
   </si>
   <si>
     <t xml:space="preserve">5.68439054489136</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95833778381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90697240829468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88985061645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57471704483032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12955331802368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40350103378296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01987981796265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20821857452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32807016372681</t>
+    <t xml:space="preserve">5.95833730697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90697193145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88985109329224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57471656799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12955379486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4035005569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0198802947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20821809768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32806968688965</t>
   </si>
   <si>
     <t xml:space="preserve">7.05412340164185</t>
   </si>
   <si>
+    <t xml:space="preserve">7.00275850296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42397737503052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28357076644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87990379333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96765661239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59909057617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51133680343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73949670791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84480142593384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82725095748901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68684434890747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66929388046265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45868492126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40603256225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31827783584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80970048904419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17826652526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35377407073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26602029800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05541038513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07296228408813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63419198989868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44113397598267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30072736740112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05501651763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03746652603149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37053632736206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40563821792603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52849388122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65134906768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12521982192993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96726274490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01991510391235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91461038589478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.844407081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94971227645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86195755004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82685661315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93216180801392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87950897216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79175519943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68645048141479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45829057693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63379812240601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70400142669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58114624023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66890001296997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56359529495239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61624765396118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49339199066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31788444519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17747783660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2652325630188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28278303146362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35298585891724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42318868637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47584104537964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38808727264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51094341278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77420473098755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44073915481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54604434967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23052453994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35337972640991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1603217124939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37093114852905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47623491287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42358303070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54643869400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98520755767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33622264862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0905122756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16071510314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19581699371338</t>
+  </si>
+  <si>
     <t xml:space="preserve">7.00275897979736</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4239764213562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28357172012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8799033164978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96765661239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59909105300903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51133680343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73949670791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.844801902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82725095748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68684434890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66929340362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45868492126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40603256225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31827831268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80970048904419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17826700210571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3537745475769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26601982116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05541086196899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07296228408813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63419198989868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44113445281982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30072736740112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05501699447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03746604919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37053680419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40563821792603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52849435806274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65134859085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12521982192993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96726322174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01991558074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91460990905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84440755844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94971227645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86195802688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82685661315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93216180801392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87950897216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79175519943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68645048141479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45829010009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63379859924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70400094985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58114624023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66890001296997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56359529495239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61624717712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49339246749878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31788444519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17747783660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26523208618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28278255462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35298585891724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42318916320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47584104537964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38808727264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5109429359436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77420473098755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44073963165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54604482650757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23052453994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35337972640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16032123565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37093114852905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47623586654663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42358303070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54643869400024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98520755767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33622360229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0905122756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16071510314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19581699371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00275802612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95010662078857</t>
+    <t xml:space="preserve">6.95010614395142</t>
   </si>
   <si>
     <t xml:space="preserve">7.14316511154175</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12561368942261</t>
+    <t xml:space="preserve">7.12561416625977</t>
   </si>
   <si>
     <t xml:space="preserve">7.02030944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84519481658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3366174697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31906604766846</t>
+    <t xml:space="preserve">7.84519577026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33661842346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31906700134277</t>
   </si>
   <si>
     <t xml:space="preserve">8.42437171936035</t>
@@ -1943,22 +1943,22 @@
     <t xml:space="preserve">8.68763256072998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03864765167236</t>
+    <t xml:space="preserve">9.03864860534668</t>
   </si>
   <si>
     <t xml:space="preserve">9.30191040039062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2763719558716</t>
+    <t xml:space="preserve">11.2763729095459</t>
   </si>
   <si>
     <t xml:space="preserve">13.1630802154541</t>
   </si>
   <si>
-    <t xml:space="preserve">13.075325012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1192026138306</t>
+    <t xml:space="preserve">13.0753259658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1192035675049</t>
   </si>
   <si>
     <t xml:space="preserve">12.8559408187866</t>
@@ -1967,16 +1967,16 @@
     <t xml:space="preserve">12.0222797393799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1100339889526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9345264434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3641262054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8814792633057</t>
+    <t xml:space="preserve">12.1100330352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9345254898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.36412525177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8814783096313</t>
   </si>
   <si>
     <t xml:space="preserve">12.1539115905762</t>
@@ -1991,13 +1991,13 @@
     <t xml:space="preserve">11.4518795013428</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0569887161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4957571029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4080018997192</t>
+    <t xml:space="preserve">11.0569877624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.495756149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4080028533936</t>
   </si>
   <si>
     <t xml:space="preserve">11.8906497955322</t>
@@ -2009,7 +2009,7 @@
     <t xml:space="preserve">11.3202486038208</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6273889541626</t>
+    <t xml:space="preserve">11.6273880004883</t>
   </si>
   <si>
     <t xml:space="preserve">11.1447401046753</t>
@@ -2018,22 +2018,22 @@
     <t xml:space="preserve">10.618218421936</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5304641723633</t>
+    <t xml:space="preserve">10.5304651260376</t>
   </si>
   <si>
     <t xml:space="preserve">10.5743398666382</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7498502731323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6620941162109</t>
+    <t xml:space="preserve">10.749849319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6620950698853</t>
   </si>
   <si>
     <t xml:space="preserve">10.3549556732178</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78455638885498</t>
+    <t xml:space="preserve">9.78455448150635</t>
   </si>
   <si>
     <t xml:space="preserve">9.91618728637695</t>
@@ -2042,7 +2042,7 @@
     <t xml:space="preserve">10.0916948318481</t>
   </si>
   <si>
-    <t xml:space="preserve">11.232494354248</t>
+    <t xml:space="preserve">11.2324953079224</t>
   </si>
   <si>
     <t xml:space="preserve">11.1886186599731</t>
@@ -2054,13 +2054,13 @@
     <t xml:space="preserve">11.3553495407104</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2675971984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0218858718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2500457763672</t>
+    <t xml:space="preserve">11.267596244812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0218868255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2500448226929</t>
   </si>
   <si>
     <t xml:space="preserve">11.3729009628296</t>
@@ -2069,13 +2069,13 @@
     <t xml:space="preserve">11.2851476669312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1973934173584</t>
+    <t xml:space="preserve">11.1973924636841</t>
   </si>
   <si>
     <t xml:space="preserve">11.8467721939087</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9871778488159</t>
+    <t xml:space="preserve">11.9871768951416</t>
   </si>
   <si>
     <t xml:space="preserve">12.2855415344238</t>
@@ -2087,7 +2087,7 @@
     <t xml:space="preserve">12.1626853942871</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4672012329102</t>
+    <t xml:space="preserve">12.4672002792358</t>
   </si>
   <si>
     <t xml:space="preserve">12.0372972488403</t>
@@ -2096,25 +2096,25 @@
     <t xml:space="preserve">12.0910348892212</t>
   </si>
   <si>
-    <t xml:space="preserve">11.553656578064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6432189941406</t>
+    <t xml:space="preserve">11.5536556243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6432199478149</t>
   </si>
   <si>
     <t xml:space="preserve">11.3924427032471</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9446258544922</t>
+    <t xml:space="preserve">10.9446268081665</t>
   </si>
   <si>
     <t xml:space="preserve">10.5505475997925</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6759366989136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9088020324707</t>
+    <t xml:space="preserve">10.6759376525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9088010787964</t>
   </si>
   <si>
     <t xml:space="preserve">10.7117624282837</t>
@@ -2123,7 +2123,7 @@
     <t xml:space="preserve">10.6580228805542</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9267129898071</t>
+    <t xml:space="preserve">10.9267139434814</t>
   </si>
   <si>
     <t xml:space="preserve">11.0521030426025</t>
@@ -2138,7 +2138,7 @@
     <t xml:space="preserve">11.4282674789429</t>
   </si>
   <si>
-    <t xml:space="preserve">11.571569442749</t>
+    <t xml:space="preserve">11.5715684890747</t>
   </si>
   <si>
     <t xml:space="preserve">11.3745288848877</t>
@@ -2150,7 +2150,7 @@
     <t xml:space="preserve">11.3207921981812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4461803436279</t>
+    <t xml:space="preserve">11.4461793899536</t>
   </si>
   <si>
     <t xml:space="preserve">11.464093208313</t>
@@ -2162,28 +2162,28 @@
     <t xml:space="preserve">11.7327833175659</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7506952285767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1805992126465</t>
+    <t xml:space="preserve">11.7506942749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1805982589722</t>
   </si>
   <si>
     <t xml:space="preserve">12.6284151077271</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0731220245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3418121337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3597249984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6969585418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1268606185913</t>
+    <t xml:space="preserve">12.0731229782104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3418130874634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3597259521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6969575881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1268615722656</t>
   </si>
   <si>
     <t xml:space="preserve">12.0552110671997</t>
@@ -2195,7 +2195,7 @@
     <t xml:space="preserve">11.9298210144043</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2880754470825</t>
+    <t xml:space="preserve">12.2880744934082</t>
   </si>
   <si>
     <t xml:space="preserve">12.5925903320312</t>
@@ -2204,10 +2204,10 @@
     <t xml:space="preserve">12.5030269622803</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9835605621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.323899269104</t>
+    <t xml:space="preserve">11.9835596084595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3239002227783</t>
   </si>
   <si>
     <t xml:space="preserve">10.9804515838623</t>
@@ -2216,13 +2216,13 @@
     <t xml:space="preserve">11.177490234375</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2849674224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3387050628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8939962387085</t>
+    <t xml:space="preserve">11.284966468811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3387060165405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8939971923828</t>
   </si>
   <si>
     <t xml:space="preserve">11.768609046936</t>
@@ -2231,7 +2231,7 @@
     <t xml:space="preserve">11.6253061294556</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0014724731445</t>
+    <t xml:space="preserve">12.0014705657959</t>
   </si>
   <si>
     <t xml:space="preserve">12.1089487075806</t>
@@ -2243,7 +2243,7 @@
     <t xml:space="preserve">12.1985120773315</t>
   </si>
   <si>
-    <t xml:space="preserve">12.43137550354</t>
+    <t xml:space="preserve">12.4313764572144</t>
   </si>
   <si>
     <t xml:space="preserve">12.2522506713867</t>
@@ -2264,7 +2264,7 @@
     <t xml:space="preserve">13.3449201583862</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2405519485474</t>
+    <t xml:space="preserve">14.2405529022217</t>
   </si>
   <si>
     <t xml:space="preserve">14.0972518920898</t>
@@ -2276,10 +2276,10 @@
     <t xml:space="preserve">14.4734172821045</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5988063812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8823013305664</t>
+    <t xml:space="preserve">14.598804473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8823003768921</t>
   </si>
   <si>
     <t xml:space="preserve">13.8643865585327</t>
@@ -2291,10 +2291,10 @@
     <t xml:space="preserve">13.4703102111816</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6852617263794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6673488616943</t>
+    <t xml:space="preserve">13.6852607727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.66734790802</t>
   </si>
   <si>
     <t xml:space="preserve">13.5598726272583</t>
@@ -2303,7 +2303,7 @@
     <t xml:space="preserve">13.6136102676392</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8285617828369</t>
+    <t xml:space="preserve">13.8285627365112</t>
   </si>
   <si>
     <t xml:space="preserve">13.953950881958</t>
@@ -2315,10 +2315,10 @@
     <t xml:space="preserve">13.7210855484009</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5240468978882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7031736373901</t>
+    <t xml:space="preserve">13.5240478515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7031745910645</t>
   </si>
   <si>
     <t xml:space="preserve">13.2553577423096</t>
@@ -2327,7 +2327,7 @@
     <t xml:space="preserve">13.4523973464966</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3090944290161</t>
+    <t xml:space="preserve">13.3090953826904</t>
   </si>
   <si>
     <t xml:space="preserve">14.2763776779175</t>
@@ -2336,34 +2336,34 @@
     <t xml:space="preserve">14.4196796417236</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0256013870239</t>
+    <t xml:space="preserve">14.0256023406982</t>
   </si>
   <si>
     <t xml:space="preserve">13.756911277771</t>
   </si>
   <si>
-    <t xml:space="preserve">14.437593460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7124996185303</t>
+    <t xml:space="preserve">14.4375925064087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7124977111816</t>
   </si>
   <si>
     <t xml:space="preserve">16.336332321167</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7156047821045</t>
+    <t xml:space="preserve">17.7156066894531</t>
   </si>
   <si>
     <t xml:space="preserve">17.2498760223389</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6591281890869</t>
+    <t xml:space="preserve">19.6591300964355</t>
   </si>
   <si>
     <t xml:space="preserve">21.3160457611084</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4503917694092</t>
+    <t xml:space="preserve">21.4503936767578</t>
   </si>
   <si>
     <t xml:space="preserve">21.5399551391602</t>
@@ -2375,13 +2375,13 @@
     <t xml:space="preserve">21.987771987915</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2712669372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0177516937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3460235595703</t>
+    <t xml:space="preserve">21.2712650299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.017749786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3460254669189</t>
   </si>
   <si>
     <t xml:space="preserve">22.1221160888672</t>
@@ -2390,7 +2390,7 @@
     <t xml:space="preserve">23.7342548370361</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8982086181641</t>
+    <t xml:space="preserve">21.8982105255127</t>
   </si>
   <si>
     <t xml:space="preserve">22.4355869293213</t>
@@ -2402,58 +2402,58 @@
     <t xml:space="preserve">21.7190818786621</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9429912567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7638645172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8534259796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3312206268311</t>
+    <t xml:space="preserve">21.9429893493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7638626098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8534278869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3312187194824</t>
   </si>
   <si>
     <t xml:space="preserve">21.8086471557617</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3463916778564</t>
+    <t xml:space="preserve">25.3463935852051</t>
   </si>
   <si>
     <t xml:space="preserve">25.3016128540039</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2420234680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.525520324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2120475769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8837718963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4807376861572</t>
+    <t xml:space="preserve">26.2420253753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5255222320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2120494842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8837738037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4807395935059</t>
   </si>
   <si>
     <t xml:space="preserve">25.5703010559082</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1224842071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.361198425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3911762237549</t>
+    <t xml:space="preserve">25.122486114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3611965179443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3911743164062</t>
   </si>
   <si>
     <t xml:space="preserve">25.704647064209</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4211502075195</t>
+    <t xml:space="preserve">26.4211521148682</t>
   </si>
   <si>
     <t xml:space="preserve">26.0628986358643</t>
@@ -2468,10 +2468,10 @@
     <t xml:space="preserve">28.6602325439453</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6750373840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7794036865234</t>
+    <t xml:space="preserve">27.6750354766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7794055938721</t>
   </si>
   <si>
     <t xml:space="preserve">26.5554962158203</t>
@@ -2486,7 +2486,7 @@
     <t xml:space="preserve">23.9581623077393</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0477256774902</t>
+    <t xml:space="preserve">24.0477275848389</t>
   </si>
   <si>
     <t xml:space="preserve">23.9133815765381</t>
@@ -2495,13 +2495,13 @@
     <t xml:space="preserve">24.5851058959961</t>
   </si>
   <si>
-    <t xml:space="preserve">22.077335357666</t>
+    <t xml:space="preserve">22.0773334503174</t>
   </si>
   <si>
     <t xml:space="preserve">22.928186416626</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1968765258789</t>
+    <t xml:space="preserve">23.1968746185303</t>
   </si>
   <si>
     <t xml:space="preserve">24.1820697784424</t>
@@ -2513,10 +2513,10 @@
     <t xml:space="preserve">24.4955425262451</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3164157867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3908081054688</t>
+    <t xml:space="preserve">24.3164138793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3908061981201</t>
   </si>
   <si>
     <t xml:space="preserve">23.8238182067871</t>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">22.8834018707275</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2416591644287</t>
+    <t xml:space="preserve">23.2416572570801</t>
   </si>
   <si>
     <t xml:space="preserve">25.1672687530518</t>
@@ -2540,16 +2540,16 @@
     <t xml:space="preserve">27.3167839050293</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6002807617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6150817871094</t>
+    <t xml:space="preserve">26.6002788543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.615083694458</t>
   </si>
   <si>
     <t xml:space="preserve">25.4359550476074</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8985767364502</t>
+    <t xml:space="preserve">24.8985786437988</t>
   </si>
   <si>
     <t xml:space="preserve">25.9733371734619</t>
@@ -2558,19 +2558,19 @@
     <t xml:space="preserve">26.5107154846191</t>
   </si>
   <si>
-    <t xml:space="preserve">26.197244644165</t>
+    <t xml:space="preserve">26.1972427368164</t>
   </si>
   <si>
     <t xml:space="preserve">26.8689670562744</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6450576782227</t>
+    <t xml:space="preserve">26.6450595855713</t>
   </si>
   <si>
     <t xml:space="preserve">27.4959106445312</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0480937957764</t>
+    <t xml:space="preserve">27.048095703125</t>
   </si>
   <si>
     <t xml:space="preserve">27.9437274932861</t>
@@ -2582,13 +2582,13 @@
     <t xml:space="preserve">28.9289207458496</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7050132751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7797737121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9885101318359</t>
+    <t xml:space="preserve">28.7050113677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7797718048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9885082244873</t>
   </si>
   <si>
     <t xml:space="preserve">27.6302547454834</t>
@@ -2597,7 +2597,7 @@
     <t xml:space="preserve">27.2272205352783</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4063472747803</t>
+    <t xml:space="preserve">27.4063491821289</t>
   </si>
   <si>
     <t xml:space="preserve">26.6898403167725</t>
@@ -2612,13 +2612,13 @@
     <t xml:space="preserve">26.3315887451172</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7194499969482</t>
+    <t xml:space="preserve">24.7194519042969</t>
   </si>
   <si>
     <t xml:space="preserve">24.4507598876953</t>
   </si>
   <si>
-    <t xml:space="preserve">23.599910736084</t>
+    <t xml:space="preserve">23.5999088287354</t>
   </si>
   <si>
     <t xml:space="preserve">23.4655666351318</t>
@@ -2630,7 +2630,7 @@
     <t xml:space="preserve">28.0332889556885</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8541622161865</t>
+    <t xml:space="preserve">27.8541641235352</t>
   </si>
   <si>
     <t xml:space="preserve">28.163049697876</t>
@@ -2639,10 +2639,10 @@
     <t xml:space="preserve">27.6633834838867</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2979869842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8911685943604</t>
+    <t xml:space="preserve">30.2979888916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.891170501709</t>
   </si>
   <si>
     <t xml:space="preserve">27.3454132080078</t>
@@ -2651,16 +2651,16 @@
     <t xml:space="preserve">29.662052154541</t>
   </si>
   <si>
-    <t xml:space="preserve">29.480354309082</t>
+    <t xml:space="preserve">29.4803524017334</t>
   </si>
   <si>
     <t xml:space="preserve">29.3440799713135</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5251121520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.57053565979</t>
+    <t xml:space="preserve">30.525110244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5705375671387</t>
   </si>
   <si>
     <t xml:space="preserve">31.0247802734375</t>
@@ -2684,7 +2684,7 @@
     <t xml:space="preserve">27.4362621307373</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0722026824951</t>
+    <t xml:space="preserve">28.0722007751465</t>
   </si>
   <si>
     <t xml:space="preserve">28.4355945587158</t>
@@ -2693,7 +2693,7 @@
     <t xml:space="preserve">28.5264434814453</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4810180664062</t>
+    <t xml:space="preserve">28.4810199737549</t>
   </si>
   <si>
     <t xml:space="preserve">28.3901710510254</t>
@@ -2702,16 +2702,16 @@
     <t xml:space="preserve">29.1623821258545</t>
   </si>
   <si>
-    <t xml:space="preserve">29.434928894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2538967132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1169586181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1162929534912</t>
+    <t xml:space="preserve">29.4349308013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2538986206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1169567108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1162948608398</t>
   </si>
   <si>
     <t xml:space="preserve">30.9793529510498</t>
@@ -2720,22 +2720,22 @@
     <t xml:space="preserve">31.1610507965088</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4790210723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5698719024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7969932556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7515697479248</t>
+    <t xml:space="preserve">31.479024887085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5698680877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.796989440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7515659332275</t>
   </si>
   <si>
     <t xml:space="preserve">31.1156272888184</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2505645751953</t>
+    <t xml:space="preserve">33.2505683898926</t>
   </si>
   <si>
     <t xml:space="preserve">34.6587219238281</t>
@@ -2747,7 +2747,7 @@
     <t xml:space="preserve">34.4770240783691</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3861770629883</t>
+    <t xml:space="preserve">34.386173248291</t>
   </si>
   <si>
     <t xml:space="preserve">34.5678672790527</t>
@@ -2780,10 +2780,10 @@
     <t xml:space="preserve">33.7502365112305</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9319343566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2499008178711</t>
+    <t xml:space="preserve">33.9319305419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2499046325684</t>
   </si>
   <si>
     <t xml:space="preserve">33.6139640808105</t>
@@ -2801,19 +2801,19 @@
     <t xml:space="preserve">38.6106338500977</t>
   </si>
   <si>
-    <t xml:space="preserve">39.5645408630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.110969543457</t>
+    <t xml:space="preserve">39.5645446777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1109657287598</t>
   </si>
   <si>
     <t xml:space="preserve">36.4302635192871</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3868408203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8871765136719</t>
+    <t xml:space="preserve">33.3868370056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8871726989746</t>
   </si>
   <si>
     <t xml:space="preserve">33.0688743591309</t>
@@ -2843,7 +2843,7 @@
     <t xml:space="preserve">30.7976551055908</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3895053863525</t>
+    <t xml:space="preserve">29.3895034790039</t>
   </si>
   <si>
     <t xml:space="preserve">29.5257778167725</t>
@@ -2852,19 +2852,19 @@
     <t xml:space="preserve">28.6172924041748</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3447456359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0254459381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9332637786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.205810546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1149559020996</t>
+    <t xml:space="preserve">28.344747543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0254440307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9332675933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2058067321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1149597167969</t>
   </si>
   <si>
     <t xml:space="preserve">32.2512359619141</t>
@@ -2873,13 +2873,13 @@
     <t xml:space="preserve">31.615291595459</t>
   </si>
   <si>
-    <t xml:space="preserve">32.024112701416</t>
+    <t xml:space="preserve">32.0241088867188</t>
   </si>
   <si>
     <t xml:space="preserve">33.1142959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">32.614631652832</t>
+    <t xml:space="preserve">32.6146278381348</t>
   </si>
   <si>
     <t xml:space="preserve">31.2064743041992</t>
@@ -2888,7 +2888,7 @@
     <t xml:space="preserve">32.0695381164551</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5244483947754</t>
+    <t xml:space="preserve">31.5244445800781</t>
   </si>
   <si>
     <t xml:space="preserve">31.3427486419678</t>
@@ -2903,10 +2903,10 @@
     <t xml:space="preserve">32.7054748535156</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1603851318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1590538024902</t>
+    <t xml:space="preserve">32.1603889465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.159049987793</t>
   </si>
   <si>
     <t xml:space="preserve">33.7956581115723</t>
@@ -2918,7 +2918,7 @@
     <t xml:space="preserve">32.9325981140137</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0234451293945</t>
+    <t xml:space="preserve">33.0234489440918</t>
   </si>
   <si>
     <t xml:space="preserve">33.5231170654297</t>
@@ -2933,13 +2933,13 @@
     <t xml:space="preserve">31.8424167633057</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8878364562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4342632293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7074756622314</t>
+    <t xml:space="preserve">31.8878402709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4342613220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7074737548828</t>
   </si>
   <si>
     <t xml:space="preserve">30.7068099975586</t>
@@ -2951,16 +2951,16 @@
     <t xml:space="preserve">29.6166248321533</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8437461853027</t>
+    <t xml:space="preserve">29.8437442779541</t>
   </si>
   <si>
     <t xml:space="preserve">29.2532329559326</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7535648345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0708675384521</t>
+    <t xml:space="preserve">28.7535667419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0708694458008</t>
   </si>
   <si>
     <t xml:space="preserve">28.889835357666</t>
@@ -2981,19 +2981,19 @@
     <t xml:space="preserve">28.7989883422852</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8891735076904</t>
+    <t xml:space="preserve">29.8891754150391</t>
   </si>
   <si>
     <t xml:space="preserve">29.0715351104736</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2993221282959</t>
+    <t xml:space="preserve">28.2993202209473</t>
   </si>
   <si>
     <t xml:space="preserve">28.0267772674561</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6179580688477</t>
+    <t xml:space="preserve">27.617956161499</t>
   </si>
   <si>
     <t xml:space="preserve">27.7542304992676</t>
@@ -3008,7 +3008,7 @@
     <t xml:space="preserve">27.4816837310791</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5725326538086</t>
+    <t xml:space="preserve">27.5725345611572</t>
   </si>
   <si>
     <t xml:space="preserve">26.6186237335205</t>
@@ -3026,31 +3026,31 @@
     <t xml:space="preserve">26.9820194244385</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3460788726807</t>
+    <t xml:space="preserve">26.346076965332</t>
   </si>
   <si>
     <t xml:space="preserve">25.8918361663818</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6647148132324</t>
+    <t xml:space="preserve">25.6647129058838</t>
   </si>
   <si>
     <t xml:space="preserve">26.2552280426025</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8457450866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6640491485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4369277954102</t>
+    <t xml:space="preserve">26.8457431793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6640510559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4369258880615</t>
   </si>
   <si>
     <t xml:space="preserve">26.5732002258301</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3915004730225</t>
+    <t xml:space="preserve">26.3915023803711</t>
   </si>
   <si>
     <t xml:space="preserve">26.70947265625</t>
@@ -3068,22 +3068,22 @@
     <t xml:space="preserve">24.1657123565674</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6660461425781</t>
+    <t xml:space="preserve">23.6660442352295</t>
   </si>
   <si>
     <t xml:space="preserve">23.8477439880371</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4375953674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7555637359619</t>
+    <t xml:space="preserve">25.437593460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7555618286133</t>
   </si>
   <si>
     <t xml:space="preserve">25.074197769165</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0735340118408</t>
+    <t xml:space="preserve">26.0735359191895</t>
   </si>
   <si>
     <t xml:space="preserve">27.6892356872559</t>
@@ -69822,7 +69822,7 @@
     </row>
     <row r="2508">
       <c r="A2508" s="1" t="n">
-        <v>45971.6939930556</v>
+        <v>45971.3333333333</v>
       </c>
       <c r="B2508" t="n">
         <v>20376</v>
@@ -69831,7 +69831,7 @@
         <v>20</v>
       </c>
       <c r="D2508" t="n">
-        <v>19.0400009155273</v>
+        <v>19</v>
       </c>
       <c r="E2508" t="n">
         <v>19.3600006103516</v>
@@ -69843,6 +69843,32 @@
         <v>1389</v>
       </c>
       <c r="H2508" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2509">
+      <c r="A2509" s="1" t="n">
+        <v>45972.6911689815</v>
+      </c>
+      <c r="B2509" t="n">
+        <v>20206</v>
+      </c>
+      <c r="C2509" t="n">
+        <v>19.1800003051758</v>
+      </c>
+      <c r="D2509" t="n">
+        <v>18.5599994659424</v>
+      </c>
+      <c r="E2509" t="n">
+        <v>18.8999996185303</v>
+      </c>
+      <c r="F2509" t="n">
+        <v>18.6399993896484</v>
+      </c>
+      <c r="G2509" t="s">
+        <v>1404</v>
+      </c>
+      <c r="H2509" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ARN.MI.xlsx
+++ b/data/ARN.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92215001583099</t>
+    <t xml:space="preserve">1.92215049266815</t>
   </si>
   <si>
     <t xml:space="preserve">ARN.MI</t>
@@ -47,163 +47,163 @@
     <t xml:space="preserve">1.94450068473816</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91736078262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90778195858002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88383483886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93172883987427</t>
+    <t xml:space="preserve">1.91736054420471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90778183937073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88383507728577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93172872066498</t>
   </si>
   <si>
     <t xml:space="preserve">1.91576421260834</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83434414863586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83594083786011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91097462177277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.807204246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74973130226135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71620571613312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80401122570038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81039714813232</t>
+    <t xml:space="preserve">1.83434450626373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83594048023224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91097486019135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80720412731171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74973118305206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71620523929596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80401134490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81039726734161</t>
   </si>
   <si>
     <t xml:space="preserve">1.79602909088135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77208197116852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70662689208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6970477104187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69066178798676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67629373073578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70024108886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69864439964294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67469716072083</t>
+    <t xml:space="preserve">1.77208185195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70662665367126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69704735279083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69066190719604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6762934923172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70024073123932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69864451885223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6746973991394</t>
   </si>
   <si>
     <t xml:space="preserve">1.66671502590179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66032898426056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81518626213074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82795858383179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8614844083786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88543140888214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89181756973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92853569984436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95407927036285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90618503093719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86786997318268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88064193725586</t>
+    <t xml:space="preserve">1.66032886505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81518661975861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82795822620392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86148428916931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88543128967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8918172121048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92853581905365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95407950878143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90618538856506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86787045001984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88064181804657</t>
   </si>
   <si>
     <t xml:space="preserve">1.85190558433533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85988759994507</t>
+    <t xml:space="preserve">1.85988795757294</t>
   </si>
   <si>
     <t xml:space="preserve">1.85509812831879</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79283630847931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78804671764374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78006422519684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7561172246933</t>
+    <t xml:space="preserve">1.79283618927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78804659843445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78006434440613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75611710548401</t>
   </si>
   <si>
     <t xml:space="preserve">1.76888883113861</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76409935951233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78485405445099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77048540115356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72099483013153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73536288738251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80241441726685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76250302791595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74494218826294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73217034339905</t>
+    <t xml:space="preserve">1.76409959793091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78485369682312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77048528194427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72099506855011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73536312580109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80241453647614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76250314712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74494242668152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73217022418976</t>
   </si>
   <si>
     <t xml:space="preserve">1.73695969581604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74334537982941</t>
+    <t xml:space="preserve">1.74334526062012</t>
   </si>
   <si>
     <t xml:space="preserve">1.7513279914856</t>
@@ -212,103 +212,103 @@
     <t xml:space="preserve">1.68587255477905</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67789006233215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65234673023224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62041735649109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64276778697968</t>
+    <t xml:space="preserve">1.67789030075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65234661102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6204172372818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64276766777039</t>
   </si>
   <si>
     <t xml:space="preserve">1.59008431434631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60285580158234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54937434196472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51185715198517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45598077774048</t>
+    <t xml:space="preserve">1.60285604000092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54937446117401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51185739040375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45598065853119</t>
   </si>
   <si>
     <t xml:space="preserve">1.43682324886322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46955060958862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49748909473419</t>
+    <t xml:space="preserve">1.4695508480072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4974889755249</t>
   </si>
   <si>
     <t xml:space="preserve">1.47673499584198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47274363040924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46875250339508</t>
+    <t xml:space="preserve">1.47274386882782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46875274181366</t>
   </si>
   <si>
     <t xml:space="preserve">1.49669075012207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47593665122986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50626957416534</t>
+    <t xml:space="preserve">1.47593677043915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50626945495605</t>
   </si>
   <si>
     <t xml:space="preserve">1.47753322124481</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43841958045959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40090274810791</t>
+    <t xml:space="preserve">1.43841981887817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4009028673172</t>
   </si>
   <si>
     <t xml:space="preserve">1.34901738166809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30910551548004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34342968463898</t>
+    <t xml:space="preserve">1.30910563468933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34342956542969</t>
   </si>
   <si>
     <t xml:space="preserve">1.32666671276093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34103500843048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31708800792694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38653457164764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39691162109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40649032592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30671095848083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32347393035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30591285228729</t>
+    <t xml:space="preserve">1.34103488922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31708788871765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38653433322906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39691150188446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40649044513702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30671072006226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3234738111496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30591261386871</t>
   </si>
   <si>
     <t xml:space="preserve">1.31229853630066</t>
@@ -320,28 +320,28 @@
     <t xml:space="preserve">1.28515863418579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28595674037933</t>
+    <t xml:space="preserve">1.28595662117004</t>
   </si>
   <si>
     <t xml:space="preserve">1.33305263519287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33704388141632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30112326145172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36104881763458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34627258777618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35283970832825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33806359767914</t>
+    <t xml:space="preserve">1.33704376220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30112314224243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36104893684387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34627246856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35283982753754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33806371688843</t>
   </si>
   <si>
     <t xml:space="preserve">1.27157080173492</t>
@@ -356,16 +356,16 @@
     <t xml:space="preserve">1.30686962604523</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33888459205627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34955620765686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34380984306335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33642196655273</t>
+    <t xml:space="preserve">1.33888471126556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34955608844757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34380996227264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33642184734344</t>
   </si>
   <si>
     <t xml:space="preserve">1.34709358215332</t>
@@ -380,25 +380,25 @@
     <t xml:space="preserve">1.31425750255585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32164561748505</t>
+    <t xml:space="preserve">1.32164573669434</t>
   </si>
   <si>
     <t xml:space="preserve">1.26828730106354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27239167690277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28798878192902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29701888561249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24858593940735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32657098770142</t>
+    <t xml:space="preserve">1.27239179611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2879890203476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29701900482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24858582019806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32657110691071</t>
   </si>
   <si>
     <t xml:space="preserve">1.33231735229492</t>
@@ -410,7 +410,7 @@
     <t xml:space="preserve">1.4201534986496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4866464138031</t>
+    <t xml:space="preserve">1.48664617538452</t>
   </si>
   <si>
     <t xml:space="preserve">1.53343749046326</t>
@@ -419,7 +419,7 @@
     <t xml:space="preserve">1.51619851589203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51866137981415</t>
+    <t xml:space="preserve">1.51866126060486</t>
   </si>
   <si>
     <t xml:space="preserve">1.43739235401154</t>
@@ -428,106 +428,106 @@
     <t xml:space="preserve">1.4677654504776</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43000400066376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40948176383972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44478023052216</t>
+    <t xml:space="preserve">1.43000423908234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40948188304901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44478058815002</t>
   </si>
   <si>
     <t xml:space="preserve">1.5597060918808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61798989772797</t>
+    <t xml:space="preserve">1.61798977851868</t>
   </si>
   <si>
     <t xml:space="preserve">1.70582604408264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74851274490356</t>
+    <t xml:space="preserve">1.74851286411285</t>
   </si>
   <si>
     <t xml:space="preserve">1.72388577461243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68284070491791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67463171482086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65164661407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64179587364197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67134821414948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66478109359741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65657198429108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69597518444061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69433319568634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65821385383606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68119919300079</t>
+    <t xml:space="preserve">1.68284094333649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67463183403015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.651646733284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64179611206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67134809494019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66478097438812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65657186508179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69597506523132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69433331489563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65821361541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6811990737915</t>
   </si>
   <si>
     <t xml:space="preserve">1.68776619434357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66806471347809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65000474452972</t>
+    <t xml:space="preserve">1.6680645942688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65000510215759</t>
   </si>
   <si>
     <t xml:space="preserve">1.66313922405243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67791533470154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03746891021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04403591156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0391104221344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04075264930725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05224466323853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04731965065002</t>
+    <t xml:space="preserve">1.67791545391083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03746867179871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04403614997864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03911066055298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04075241088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05224514007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04731941223145</t>
   </si>
   <si>
     <t xml:space="preserve">2.04239416122437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19836449623108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.241051197052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18851375579834</t>
+    <t xml:space="preserve">2.19836497306824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24105143547058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18851399421692</t>
   </si>
   <si>
     <t xml:space="preserve">2.17537951469421</t>
@@ -536,7 +536,7 @@
     <t xml:space="preserve">2.145827293396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00627446174622</t>
+    <t xml:space="preserve">2.00627470016479</t>
   </si>
   <si>
     <t xml:space="preserve">1.98821461200714</t>
@@ -545,13 +545,13 @@
     <t xml:space="preserve">1.99314022064209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99806559085846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99642360210419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99970734119415</t>
+    <t xml:space="preserve">1.99806547164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99642384052277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99970746040344</t>
   </si>
   <si>
     <t xml:space="preserve">2.00299096107483</t>
@@ -560,7 +560,7 @@
     <t xml:space="preserve">2.00791645050049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01119995117188</t>
+    <t xml:space="preserve">2.0111997127533</t>
   </si>
   <si>
     <t xml:space="preserve">2.02597618103027</t>
@@ -569,25 +569,25 @@
     <t xml:space="preserve">2.03254342079163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02105069160461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0194091796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.024334192276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07687187194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05881214141846</t>
+    <t xml:space="preserve">2.02105045318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01940870285034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02433443069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07687163352966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05881190299988</t>
   </si>
   <si>
     <t xml:space="preserve">2.09657311439514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14746904373169</t>
+    <t xml:space="preserve">2.14746880531311</t>
   </si>
   <si>
     <t xml:space="preserve">2.33955883979797</t>
@@ -596,52 +596,52 @@
     <t xml:space="preserve">2.27552938461304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32478284835815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27881288528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25746989250183</t>
+    <t xml:space="preserve">2.32478308677673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27881264686584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25746941566467</t>
   </si>
   <si>
     <t xml:space="preserve">2.2985143661499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26075291633606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2804548740387</t>
+    <t xml:space="preserve">2.26075315475464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28045439720154</t>
   </si>
   <si>
     <t xml:space="preserve">2.30672311782837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35597729682922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34120106697083</t>
+    <t xml:space="preserve">2.35597705841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34120082855225</t>
   </si>
   <si>
     <t xml:space="preserve">2.3428430557251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34776782989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44627571105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39209651947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38224577903748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38717126846313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38388776779175</t>
+    <t xml:space="preserve">2.3477680683136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44627594947815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39209628105164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3822455406189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38717150688171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38388752937317</t>
   </si>
   <si>
     <t xml:space="preserve">2.40523099899292</t>
@@ -650,37 +650,37 @@
     <t xml:space="preserve">2.3806037902832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42164874076843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33791756629944</t>
+    <t xml:space="preserve">2.42164897918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33791732788086</t>
   </si>
   <si>
     <t xml:space="preserve">2.32314133644104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35433530807495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41015625</t>
+    <t xml:space="preserve">2.35433554649353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41015672683716</t>
   </si>
   <si>
     <t xml:space="preserve">2.40687274932861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43806672096252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4183657169342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29030561447144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34940981864929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36418652534485</t>
+    <t xml:space="preserve">2.4380669593811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41836547851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29030537605286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34941005706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36418628692627</t>
   </si>
   <si>
     <t xml:space="preserve">2.37567853927612</t>
@@ -698,16 +698,16 @@
     <t xml:space="preserve">2.37075328826904</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37239503860474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36254405975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36582827568054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39538025856018</t>
+    <t xml:space="preserve">2.37239527702332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36254477500916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36582803726196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39537978172302</t>
   </si>
   <si>
     <t xml:space="preserve">2.3773205280304</t>
@@ -716,34 +716,34 @@
     <t xml:space="preserve">2.37403678894043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38881325721741</t>
+    <t xml:space="preserve">2.38881301879883</t>
   </si>
   <si>
     <t xml:space="preserve">2.39373826980591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39045453071594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41344046592712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40358877182007</t>
+    <t xml:space="preserve">2.39045476913452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41343975067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40358901023865</t>
   </si>
   <si>
     <t xml:space="preserve">2.40030574798584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40851449966431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42329025268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43149995803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4200074672699</t>
+    <t xml:space="preserve">2.40851473808289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42329049110413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43149948120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42000699043274</t>
   </si>
   <si>
     <t xml:space="preserve">2.35105180740356</t>
@@ -752,22 +752,22 @@
     <t xml:space="preserve">2.33627533912659</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34612607955933</t>
+    <t xml:space="preserve">2.34612631797791</t>
   </si>
   <si>
     <t xml:space="preserve">2.43642497062683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42657423019409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42985820770264</t>
+    <t xml:space="preserve">2.42657446861267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42985773086548</t>
   </si>
   <si>
     <t xml:space="preserve">2.45284295082092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4770131111145</t>
+    <t xml:space="preserve">2.47701334953308</t>
   </si>
   <si>
     <t xml:space="preserve">2.478679895401</t>
@@ -776,97 +776,97 @@
     <t xml:space="preserve">2.49201512336731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49368214607239</t>
+    <t xml:space="preserve">2.49368190765381</t>
   </si>
   <si>
     <t xml:space="preserve">2.47534608840942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46534442901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.482013463974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46867847442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45867705345154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46201109886169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45534348487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41700506210327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40867018699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36699748039246</t>
+    <t xml:space="preserve">2.46534466743469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48201394081116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46867823600769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4586775302887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46201133728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45534324645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41700458526611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40866994857788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36699771881104</t>
   </si>
   <si>
     <t xml:space="preserve">2.3419942855835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36866474151611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35366249084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38533353805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38366651535034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36366367340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32532525062561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31699061393738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28531956672668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28698658943176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29698801040649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31532406806946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28365254402161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28865313529968</t>
+    <t xml:space="preserve">2.36866497993469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35366225242615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.385333776474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38366675376892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36366391181946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32532501220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31699085235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28531980514526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28698635101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29698777198792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31532382965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28365278244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28865361213684</t>
   </si>
   <si>
     <t xml:space="preserve">2.29032015800476</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30198860168457</t>
+    <t xml:space="preserve">2.30198884010315</t>
   </si>
   <si>
     <t xml:space="preserve">2.30365562438965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29365420341492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24198007583618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26698398590088</t>
+    <t xml:space="preserve">2.2936544418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24198031425476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26698350906372</t>
   </si>
   <si>
     <t xml:space="preserve">2.2686505317688</t>
@@ -878,31 +878,31 @@
     <t xml:space="preserve">2.31865763664246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31032371520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24364709854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25031495094299</t>
+    <t xml:space="preserve">2.31032347679138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24364733695984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25031471252441</t>
   </si>
   <si>
     <t xml:space="preserve">2.22531127929688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25198125839233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2219774723053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20697546005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20030784606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16863656044006</t>
+    <t xml:space="preserve">2.25198149681091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22197723388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20697498321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20030760765076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16863679885864</t>
   </si>
   <si>
     <t xml:space="preserve">2.17863798141479</t>
@@ -911,16 +911,16 @@
     <t xml:space="preserve">2.16696977615356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18697237968445</t>
+    <t xml:space="preserve">2.18697261810303</t>
   </si>
   <si>
     <t xml:space="preserve">2.19697403907776</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18363857269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18530583381653</t>
+    <t xml:space="preserve">2.18363881111145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18530535697937</t>
   </si>
   <si>
     <t xml:space="preserve">2.19197344779968</t>
@@ -932,31 +932,31 @@
     <t xml:space="preserve">2.14196610450745</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15363478660583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14363312721252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13529849052429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12696433067322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12863087654114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12029647827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13029813766479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11862945556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37366557121277</t>
+    <t xml:space="preserve">2.15363502502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14363360404968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13529872894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12696385383606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12863111495972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12029623985291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13029766082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11862969398499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37366533279419</t>
   </si>
   <si>
     <t xml:space="preserve">2.37533211708069</t>
@@ -971,25 +971,25 @@
     <t xml:space="preserve">2.39200115203857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49868273735046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49534916877747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50868439674377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51201796531677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51535153388977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51701879501343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52368640899658</t>
+    <t xml:space="preserve">2.49868249893188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49534893035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5086841583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51201820373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51535201072693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51701903343201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52368593215942</t>
   </si>
   <si>
     <t xml:space="preserve">2.52535319328308</t>
@@ -1007,7 +1007,7 @@
     <t xml:space="preserve">2.54035544395447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52702045440674</t>
+    <t xml:space="preserve">2.52702021598816</t>
   </si>
   <si>
     <t xml:space="preserve">2.53868842124939</t>
@@ -1016,55 +1016,55 @@
     <t xml:space="preserve">2.53702139854431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49701595306396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42700600624084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5003502368927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50535011291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48368048667908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4520092010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51368522644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54202222824097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54868984222412</t>
+    <t xml:space="preserve">2.49701619148254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42700624465942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50034976005554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5053505897522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48368072509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45200967788696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51368474960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54202246665955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5486900806427</t>
   </si>
   <si>
     <t xml:space="preserve">2.51035118103027</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52035236358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47201228141785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50201654434204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48701429367065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00041937828064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81706094741821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75038456916809</t>
+    <t xml:space="preserve">2.520352602005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47201251983643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50201678276062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48701477050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00041961669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81706070899963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75038504600525</t>
   </si>
   <si>
     <t xml:space="preserve">2.7170467376709</t>
@@ -1076,28 +1076,28 @@
     <t xml:space="preserve">2.80039191246033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83372950553894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7837221622467</t>
+    <t xml:space="preserve">2.83372974395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78372240066528</t>
   </si>
   <si>
     <t xml:space="preserve">2.84206414222717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75871896743774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85039901733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85873317718506</t>
+    <t xml:space="preserve">2.75871920585632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85039877891541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85873341560364</t>
   </si>
   <si>
     <t xml:space="preserve">2.89207100868225</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82539510726929</t>
+    <t xml:space="preserve">2.82539534568787</t>
   </si>
   <si>
     <t xml:space="preserve">2.72538113594055</t>
@@ -1109,22 +1109,22 @@
     <t xml:space="preserve">2.6420361995697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70037770271301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65870475769043</t>
+    <t xml:space="preserve">2.70037746429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65870499610901</t>
   </si>
   <si>
     <t xml:space="preserve">2.62536716461182</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63370180130005</t>
+    <t xml:space="preserve">2.63370203971863</t>
   </si>
   <si>
     <t xml:space="preserve">2.59202909469604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66703963279724</t>
+    <t xml:space="preserve">2.66703987121582</t>
   </si>
   <si>
     <t xml:space="preserve">2.70871210098267</t>
@@ -1139,7 +1139,7 @@
     <t xml:space="preserve">2.68370866775513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60036373138428</t>
+    <t xml:space="preserve">2.6003634929657</t>
   </si>
   <si>
     <t xml:space="preserve">2.58369445800781</t>
@@ -1154,133 +1154,133 @@
     <t xml:space="preserve">2.73371553421021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79205679893494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86706781387329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87540197372437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8837366104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77538776397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78091406822205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72174549102783</t>
+    <t xml:space="preserve">2.79205727577209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86706733703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87540221214294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88373684883118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77538800239563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78091382980347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72174572944641</t>
   </si>
   <si>
     <t xml:space="preserve">2.73019814491272</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77246117591858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64567184448242</t>
+    <t xml:space="preserve">2.7724609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.645672082901</t>
   </si>
   <si>
     <t xml:space="preserve">2.70484018325806</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68793511390686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66257739067078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69638729095459</t>
+    <t xml:space="preserve">2.68793487548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66257691383362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69638752937317</t>
   </si>
   <si>
     <t xml:space="preserve">2.65412473678589</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60340857505798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63721919059753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61186122894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5780508518219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5949559211731</t>
+    <t xml:space="preserve">2.60340881347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63721942901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61186146736145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57805061340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59495615959167</t>
   </si>
   <si>
     <t xml:space="preserve">2.50197720527649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49352431297302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54424047470093</t>
+    <t xml:space="preserve">2.49352478981018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54424023628235</t>
   </si>
   <si>
     <t xml:space="preserve">2.5611457824707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58650326728821</t>
+    <t xml:space="preserve">2.58650350570679</t>
   </si>
   <si>
     <t xml:space="preserve">2.51888227462769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53578805923462</t>
+    <t xml:space="preserve">2.53578782081604</t>
   </si>
   <si>
     <t xml:space="preserve">2.55269289016724</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51042985916138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56959795951843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46816682815552</t>
+    <t xml:space="preserve">2.5104296207428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56959819793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46816635131836</t>
   </si>
   <si>
     <t xml:space="preserve">2.48507213592529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41745066642761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45126175880432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39209270477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38364028930664</t>
+    <t xml:space="preserve">2.41745090484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45126152038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39209318161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38364052772522</t>
   </si>
   <si>
     <t xml:space="preserve">2.27375626564026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2991144657135</t>
+    <t xml:space="preserve">2.29911422729492</t>
   </si>
   <si>
     <t xml:space="preserve">2.36673521995544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35828280448914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43435645103455</t>
+    <t xml:space="preserve">2.35828232765198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43435621261597</t>
   </si>
   <si>
     <t xml:space="preserve">2.42590355873108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34982991218567</t>
+    <t xml:space="preserve">2.34982967376709</t>
   </si>
   <si>
     <t xml:space="preserve">2.28220891952515</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">2.4089982509613</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45971441268921</t>
+    <t xml:space="preserve">2.45971417427063</t>
   </si>
   <si>
     <t xml:space="preserve">2.44280886650085</t>
@@ -1307,7 +1307,7 @@
     <t xml:space="preserve">2.40054559707642</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37518787384033</t>
+    <t xml:space="preserve">2.37518811225891</t>
   </si>
   <si>
     <t xml:space="preserve">2.47661948204041</t>
@@ -1316,31 +1316,31 @@
     <t xml:space="preserve">2.30756664276123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23994612693787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29430246353149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23437643051147</t>
+    <t xml:space="preserve">2.23994565010071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29430270195007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23437666893005</t>
   </si>
   <si>
     <t xml:space="preserve">2.2429370880127</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33710622787476</t>
+    <t xml:space="preserve">2.33710646629333</t>
   </si>
   <si>
     <t xml:space="preserve">2.25149846076965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27718091011047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26862001419067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44839692115784</t>
+    <t xml:space="preserve">2.27718067169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26861977577209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.448397397995</t>
   </si>
   <si>
     <t xml:space="preserve">2.37134981155396</t>
@@ -1355,7 +1355,7 @@
     <t xml:space="preserve">2.26005911827087</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35422825813293</t>
+    <t xml:space="preserve">2.35422801971436</t>
   </si>
   <si>
     <t xml:space="preserve">2.22581553459167</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">2.30286312103271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31998443603516</t>
+    <t xml:space="preserve">2.31998467445374</t>
   </si>
   <si>
     <t xml:space="preserve">2.37991046905518</t>
@@ -1376,40 +1376,40 @@
     <t xml:space="preserve">2.40559315681458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39703226089478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32854580879211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38847160339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36278891563416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34566712379456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20013308525085</t>
+    <t xml:space="preserve">2.3970320224762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32854557037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3884711265564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36278867721558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34566736221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20013332366943</t>
   </si>
   <si>
     <t xml:space="preserve">2.18301153182983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43983626365662</t>
+    <t xml:space="preserve">2.4398365020752</t>
   </si>
   <si>
     <t xml:space="preserve">2.54256629943848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60249185562134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69666147232056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77370882034302</t>
+    <t xml:space="preserve">2.60249209403992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69666123390198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77370858192444</t>
   </si>
   <si>
     <t xml:space="preserve">2.63673543930054</t>
@@ -1421,37 +1421,37 @@
     <t xml:space="preserve">2.61961364746094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65385675430298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68810081481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64529609680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71378302574158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72234392166138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07333755493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52706170082092</t>
+    <t xml:space="preserve">2.65385699272156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68810057640076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64529633522034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.713782787323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7223436832428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07333779335022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52706146240234</t>
   </si>
   <si>
     <t xml:space="preserve">3.59554839134216</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6554741859436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58698749542236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61267018318176</t>
+    <t xml:space="preserve">3.65547442436218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58698797225952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61266994476318</t>
   </si>
   <si>
     <t xml:space="preserve">3.53562259674072</t>
@@ -1460,10 +1460,10 @@
     <t xml:space="preserve">3.42433190345764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54418349266052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56986594200134</t>
+    <t xml:space="preserve">3.54418325424194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56986570358276</t>
   </si>
   <si>
     <t xml:space="preserve">3.55274415016174</t>
@@ -1478,166 +1478,166 @@
     <t xml:space="preserve">3.48425769805908</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57842636108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.638352394104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74108242988586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16912412643433</t>
+    <t xml:space="preserve">3.57842659950256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63835263252258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74108219146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16912317276001</t>
   </si>
   <si>
     <t xml:space="preserve">4.60572624206543</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15361976623535</t>
+    <t xml:space="preserve">5.15361928939819</t>
   </si>
   <si>
     <t xml:space="preserve">4.62284803390503</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19480657577515</t>
+    <t xml:space="preserve">4.19480609893799</t>
   </si>
   <si>
     <t xml:space="preserve">4.45163106918335</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53724002838135</t>
+    <t xml:space="preserve">4.53723955154419</t>
   </si>
   <si>
     <t xml:space="preserve">4.52011823654175</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58860492706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34890127182007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16056299209595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23761034011841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29753732681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89517712593079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27879738807678</t>
+    <t xml:space="preserve">4.58860540390015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34890174865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16056346893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23761081695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29753637313843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89517760276794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27879762649536</t>
   </si>
   <si>
     <t xml:space="preserve">3.25311517715454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89356064796448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1589457988739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16750717163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0390944480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44145321846008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38152742385864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39008831977844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84381222724915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8352518081665</t>
+    <t xml:space="preserve">2.8935604095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15894627571106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1675066947937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03909468650818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44145345687866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38152766227722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39008903503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84381198883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83525109291077</t>
   </si>
   <si>
     <t xml:space="preserve">3.87805581092834</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76676511764526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88661670684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85237383842468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92942094802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95510339736938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93798208236694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11775922775269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25473165512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22904920578003</t>
+    <t xml:space="preserve">3.76676535606384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88661646842957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8523736000061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92942142486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95510268211365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93798160552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11775875091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25473213195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22904968261719</t>
   </si>
   <si>
     <t xml:space="preserve">4.26329278945923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28041410446167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43450927734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20336723327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00646781921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10919857025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15200233459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08351564407349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94654273986816</t>
+    <t xml:space="preserve">4.28041458129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43450975418091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20336771011353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00646829605103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10919809341431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15200281143188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08351612091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94654178619385</t>
   </si>
   <si>
     <t xml:space="preserve">4.07495498657227</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02358913421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96366453170776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13488054275513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12631988525391</t>
+    <t xml:space="preserve">4.02358961105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96366405487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13488101959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12632036209106</t>
   </si>
   <si>
     <t xml:space="preserve">5.01664638519287</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70845651626587</t>
+    <t xml:space="preserve">4.70845603942871</t>
   </si>
   <si>
     <t xml:space="preserve">4.91391611099243</t>
@@ -1646,25 +1646,25 @@
     <t xml:space="preserve">4.96528148651123</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94815969467163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20498371124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56453943252563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68439054489136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95833730697632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90697193145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88985109329224</t>
+    <t xml:space="preserve">4.94815921783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20498418807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56453990936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68439102172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95833778381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90697240829468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88985013961792</t>
   </si>
   <si>
     <t xml:space="preserve">6.57471656799316</t>
@@ -1682,28 +1682,28 @@
     <t xml:space="preserve">7.20821809768677</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32806968688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05412340164185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00275850296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42397737503052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28357076644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87990379333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96765661239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59909057617188</t>
+    <t xml:space="preserve">7.32807016372681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05412292480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00275945663452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42397689819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28357124328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8799033164978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9676570892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59909105300903</t>
   </si>
   <si>
     <t xml:space="preserve">6.51133680343628</t>
@@ -1715,16 +1715,16 @@
     <t xml:space="preserve">6.84480142593384</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82725095748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68684434890747</t>
+    <t xml:space="preserve">6.82725143432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68684482574463</t>
   </si>
   <si>
     <t xml:space="preserve">6.66929388046265</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45868492126465</t>
+    <t xml:space="preserve">6.45868444442749</t>
   </si>
   <si>
     <t xml:space="preserve">6.40603256225586</t>
@@ -1739,13 +1739,13 @@
     <t xml:space="preserve">7.17826652526855</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35377407073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26602029800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05541038513184</t>
+    <t xml:space="preserve">7.3537745475769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26601982116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05541086196899</t>
   </si>
   <si>
     <t xml:space="preserve">7.07296228408813</t>
@@ -1754,7 +1754,7 @@
     <t xml:space="preserve">6.63419198989868</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44113397598267</t>
+    <t xml:space="preserve">6.44113445281982</t>
   </si>
   <si>
     <t xml:space="preserve">6.30072736740112</t>
@@ -1763,7 +1763,7 @@
     <t xml:space="preserve">6.05501651763916</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03746652603149</t>
+    <t xml:space="preserve">6.03746604919434</t>
   </si>
   <si>
     <t xml:space="preserve">5.37053632736206</t>
@@ -1781,13 +1781,13 @@
     <t xml:space="preserve">6.12521982192993</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96726274490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01991510391235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91461038589478</t>
+    <t xml:space="preserve">5.96726322174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01991558074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91460990905762</t>
   </si>
   <si>
     <t xml:space="preserve">5.844407081604</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">5.94971227645874</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86195755004883</t>
+    <t xml:space="preserve">5.86195850372314</t>
   </si>
   <si>
     <t xml:space="preserve">5.82685661315918</t>
@@ -1811,25 +1811,25 @@
     <t xml:space="preserve">5.79175519943237</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68645048141479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45829057693481</t>
+    <t xml:space="preserve">5.68645095825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45829010009766</t>
   </si>
   <si>
     <t xml:space="preserve">5.63379812240601</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70400142669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58114624023438</t>
+    <t xml:space="preserve">5.70400094985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58114576339722</t>
   </si>
   <si>
     <t xml:space="preserve">5.66890001296997</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56359529495239</t>
+    <t xml:space="preserve">5.56359481811523</t>
   </si>
   <si>
     <t xml:space="preserve">5.61624765396118</t>
@@ -1841,7 +1841,7 @@
     <t xml:space="preserve">5.31788444519043</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17747783660889</t>
+    <t xml:space="preserve">5.17747831344604</t>
   </si>
   <si>
     <t xml:space="preserve">5.2652325630188</t>
@@ -1850,7 +1850,7 @@
     <t xml:space="preserve">5.28278303146362</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35298585891724</t>
+    <t xml:space="preserve">5.35298633575439</t>
   </si>
   <si>
     <t xml:space="preserve">5.42318868637085</t>
@@ -1862,16 +1862,16 @@
     <t xml:space="preserve">5.38808727264404</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51094341278076</t>
+    <t xml:space="preserve">5.5109429359436</t>
   </si>
   <si>
     <t xml:space="preserve">5.77420473098755</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44073915481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54604434967041</t>
+    <t xml:space="preserve">5.44074010848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54604482650757</t>
   </si>
   <si>
     <t xml:space="preserve">6.23052453994751</t>
@@ -1880,13 +1880,13 @@
     <t xml:space="preserve">6.35337972640991</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1603217124939</t>
+    <t xml:space="preserve">6.16032123565674</t>
   </si>
   <si>
     <t xml:space="preserve">6.37093114852905</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47623491287231</t>
+    <t xml:space="preserve">6.47623586654663</t>
   </si>
   <si>
     <t xml:space="preserve">6.42358303070068</t>
@@ -1898,58 +1898,58 @@
     <t xml:space="preserve">6.98520755767822</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33622264862061</t>
+    <t xml:space="preserve">7.33622360229492</t>
   </si>
   <si>
     <t xml:space="preserve">7.0905122756958</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16071510314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19581699371338</t>
+    <t xml:space="preserve">7.16071557998657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19581651687622</t>
   </si>
   <si>
     <t xml:space="preserve">7.00275897979736</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95010614395142</t>
+    <t xml:space="preserve">6.95010662078857</t>
   </si>
   <si>
     <t xml:space="preserve">7.14316511154175</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12561416625977</t>
+    <t xml:space="preserve">7.12561368942261</t>
   </si>
   <si>
     <t xml:space="preserve">7.02030944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84519577026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33661842346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31906700134277</t>
+    <t xml:space="preserve">7.84519529342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3366174697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31906509399414</t>
   </si>
   <si>
     <t xml:space="preserve">8.42437171936035</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08252620697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68763256072998</t>
+    <t xml:space="preserve">9.0825252532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6876335144043</t>
   </si>
   <si>
     <t xml:space="preserve">9.03864860534668</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30191040039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2763729095459</t>
+    <t xml:space="preserve">9.30190944671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2763719558716</t>
   </si>
   <si>
     <t xml:space="preserve">13.1630802154541</t>
@@ -1958,10 +1958,10 @@
     <t xml:space="preserve">13.0753259658813</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1192035675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8559408187866</t>
+    <t xml:space="preserve">13.1192016601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8559417724609</t>
   </si>
   <si>
     <t xml:space="preserve">12.0222797393799</t>
@@ -1970,13 +1970,13 @@
     <t xml:space="preserve">12.1100330352783</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9345254898071</t>
+    <t xml:space="preserve">11.9345264434814</t>
   </si>
   <si>
     <t xml:space="preserve">11.36412525177</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8814783096313</t>
+    <t xml:space="preserve">10.88148021698</t>
   </si>
   <si>
     <t xml:space="preserve">12.1539115905762</t>
@@ -1988,25 +1988,25 @@
     <t xml:space="preserve">11.7151412963867</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4518795013428</t>
+    <t xml:space="preserve">11.4518804550171</t>
   </si>
   <si>
     <t xml:space="preserve">11.0569877624512</t>
   </si>
   <si>
-    <t xml:space="preserve">11.495756149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4080028533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8906497955322</t>
+    <t xml:space="preserve">11.4957571029663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4080018997192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8906488418579</t>
   </si>
   <si>
     <t xml:space="preserve">11.8028955459595</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3202486038208</t>
+    <t xml:space="preserve">11.3202495574951</t>
   </si>
   <si>
     <t xml:space="preserve">11.6273880004883</t>
@@ -2024,22 +2024,22 @@
     <t xml:space="preserve">10.5743398666382</t>
   </si>
   <si>
-    <t xml:space="preserve">10.749849319458</t>
+    <t xml:space="preserve">10.7498483657837</t>
   </si>
   <si>
     <t xml:space="preserve">10.6620950698853</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3549556732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78455448150635</t>
+    <t xml:space="preserve">10.3549566268921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78455638885498</t>
   </si>
   <si>
     <t xml:space="preserve">9.91618728637695</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0916948318481</t>
+    <t xml:space="preserve">10.0916938781738</t>
   </si>
   <si>
     <t xml:space="preserve">11.2324953079224</t>
@@ -2048,7 +2048,7 @@
     <t xml:space="preserve">11.1886186599731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1008634567261</t>
+    <t xml:space="preserve">11.1008625030518</t>
   </si>
   <si>
     <t xml:space="preserve">11.3553495407104</t>
@@ -2057,28 +2057,28 @@
     <t xml:space="preserve">11.267596244812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0218868255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2500448226929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3729009628296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2851476669312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1973924636841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8467721939087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9871768951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2855415344238</t>
+    <t xml:space="preserve">11.0218858718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2500457763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3729019165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2851467132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1973934173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8467712402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9871778488159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2855424880981</t>
   </si>
   <si>
     <t xml:space="preserve">12.2504396438599</t>
@@ -2087,37 +2087,37 @@
     <t xml:space="preserve">12.1626853942871</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4672002792358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0372972488403</t>
+    <t xml:space="preserve">12.4672012329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0372982025146</t>
   </si>
   <si>
     <t xml:space="preserve">12.0910348892212</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5536556243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6432199478149</t>
+    <t xml:space="preserve">11.5536575317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6432189941406</t>
   </si>
   <si>
     <t xml:space="preserve">11.3924427032471</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9446268081665</t>
+    <t xml:space="preserve">10.9446258544922</t>
   </si>
   <si>
     <t xml:space="preserve">10.5505475997925</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6759376525879</t>
+    <t xml:space="preserve">10.6759366989136</t>
   </si>
   <si>
     <t xml:space="preserve">10.9088010787964</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7117624282837</t>
+    <t xml:space="preserve">10.7117614746094</t>
   </si>
   <si>
     <t xml:space="preserve">10.6580228805542</t>
@@ -2129,7 +2129,7 @@
     <t xml:space="preserve">11.0521030426025</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4999189376831</t>
+    <t xml:space="preserve">11.4999179840088</t>
   </si>
   <si>
     <t xml:space="preserve">11.482006072998</t>
@@ -2138,7 +2138,7 @@
     <t xml:space="preserve">11.4282674789429</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5715684890747</t>
+    <t xml:space="preserve">11.571569442749</t>
   </si>
   <si>
     <t xml:space="preserve">11.3745288848877</t>
@@ -2147,46 +2147,46 @@
     <t xml:space="preserve">11.356616973877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3207921981812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4461793899536</t>
+    <t xml:space="preserve">11.3207931518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4461803436279</t>
   </si>
   <si>
     <t xml:space="preserve">11.464093208313</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7148694992065</t>
+    <t xml:space="preserve">11.7148704528809</t>
   </si>
   <si>
     <t xml:space="preserve">11.7327833175659</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7506942749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1805982589722</t>
+    <t xml:space="preserve">11.750696182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1805992126465</t>
   </si>
   <si>
     <t xml:space="preserve">12.6284151077271</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0731229782104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3418130874634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3597259521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6969575881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1268615722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0552110671997</t>
+    <t xml:space="preserve">12.0731220245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3418111801147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3597249984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6969585418701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1268606185913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0552101135254</t>
   </si>
   <si>
     <t xml:space="preserve">11.8581705093384</t>
@@ -2195,13 +2195,13 @@
     <t xml:space="preserve">11.9298210144043</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2880744934082</t>
+    <t xml:space="preserve">12.2880754470825</t>
   </si>
   <si>
     <t xml:space="preserve">12.5925903320312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5030269622803</t>
+    <t xml:space="preserve">12.503026008606</t>
   </si>
   <si>
     <t xml:space="preserve">11.9835596084595</t>
@@ -2216,22 +2216,22 @@
     <t xml:space="preserve">11.177490234375</t>
   </si>
   <si>
-    <t xml:space="preserve">11.284966468811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3387060165405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8939971923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.768609046936</t>
+    <t xml:space="preserve">11.2849674224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3387050628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8939962387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7686080932617</t>
   </si>
   <si>
     <t xml:space="preserve">11.6253061294556</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0014705657959</t>
+    <t xml:space="preserve">12.0014724731445</t>
   </si>
   <si>
     <t xml:space="preserve">12.1089487075806</t>
@@ -2240,7 +2240,7 @@
     <t xml:space="preserve">11.9656476974487</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1985120773315</t>
+    <t xml:space="preserve">12.1985111236572</t>
   </si>
   <si>
     <t xml:space="preserve">12.4313764572144</t>
@@ -2264,10 +2264,10 @@
     <t xml:space="preserve">13.3449201583862</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2405529022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0972518920898</t>
+    <t xml:space="preserve">14.2405519485474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0972509384155</t>
   </si>
   <si>
     <t xml:space="preserve">14.3301162719727</t>
@@ -2276,7 +2276,7 @@
     <t xml:space="preserve">14.4734172821045</t>
   </si>
   <si>
-    <t xml:space="preserve">14.598804473877</t>
+    <t xml:space="preserve">14.5988054275513</t>
   </si>
   <si>
     <t xml:space="preserve">13.8823003768921</t>
@@ -2294,7 +2294,7 @@
     <t xml:space="preserve">13.6852607727051</t>
   </si>
   <si>
-    <t xml:space="preserve">13.66734790802</t>
+    <t xml:space="preserve">13.6673488616943</t>
   </si>
   <si>
     <t xml:space="preserve">13.5598726272583</t>
@@ -2303,25 +2303,25 @@
     <t xml:space="preserve">13.6136102676392</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8285627365112</t>
+    <t xml:space="preserve">13.8285617828369</t>
   </si>
   <si>
     <t xml:space="preserve">13.953950881958</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344835281372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7210855484009</t>
+    <t xml:space="preserve">13.4344844818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7210865020752</t>
   </si>
   <si>
     <t xml:space="preserve">13.5240478515625</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7031745910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2553577423096</t>
+    <t xml:space="preserve">13.7031736373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2553567886353</t>
   </si>
   <si>
     <t xml:space="preserve">13.4523973464966</t>
@@ -2336,25 +2336,25 @@
     <t xml:space="preserve">14.4196796417236</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0256023406982</t>
+    <t xml:space="preserve">14.0256013870239</t>
   </si>
   <si>
     <t xml:space="preserve">13.756911277771</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4375925064087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7124977111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.336332321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7156066894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2498760223389</t>
+    <t xml:space="preserve">14.437593460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7124996185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3363342285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7156047821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2498779296875</t>
   </si>
   <si>
     <t xml:space="preserve">19.6591300964355</t>
@@ -2363,19 +2363,19 @@
     <t xml:space="preserve">21.3160457611084</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4503936767578</t>
+    <t xml:space="preserve">21.4503917694092</t>
   </si>
   <si>
     <t xml:space="preserve">21.5399551391602</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2116813659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.987771987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2712650299072</t>
+    <t xml:space="preserve">22.2116794586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9877700805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2712669372559</t>
   </si>
   <si>
     <t xml:space="preserve">23.017749786377</t>
@@ -2390,34 +2390,34 @@
     <t xml:space="preserve">23.7342548370361</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8982105255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4355869293213</t>
+    <t xml:space="preserve">21.8982086181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4355888366699</t>
   </si>
   <si>
     <t xml:space="preserve">21.495174407959</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7190818786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9429893493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7638626098633</t>
+    <t xml:space="preserve">21.7190837860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9429912567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7638645172119</t>
   </si>
   <si>
     <t xml:space="preserve">21.8534278869629</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3312187194824</t>
+    <t xml:space="preserve">23.3312206268311</t>
   </si>
   <si>
     <t xml:space="preserve">21.8086471557617</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3463935852051</t>
+    <t xml:space="preserve">25.3463916778564</t>
   </si>
   <si>
     <t xml:space="preserve">25.3016128540039</t>
@@ -2426,28 +2426,28 @@
     <t xml:space="preserve">26.2420253753662</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5255222320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2120494842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8837738037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4807395935059</t>
+    <t xml:space="preserve">25.525520324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2120456695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8837699890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4807376861572</t>
   </si>
   <si>
     <t xml:space="preserve">25.5703010559082</t>
   </si>
   <si>
-    <t xml:space="preserve">25.122486114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3611965179443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3911743164062</t>
+    <t xml:space="preserve">25.1224842071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.361198425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3911762237549</t>
   </si>
   <si>
     <t xml:space="preserve">25.704647064209</t>
@@ -2456,7 +2456,7 @@
     <t xml:space="preserve">26.4211521148682</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0628986358643</t>
+    <t xml:space="preserve">26.0629005432129</t>
   </si>
   <si>
     <t xml:space="preserve">26.4659328460693</t>
@@ -2468,13 +2468,13 @@
     <t xml:space="preserve">28.6602325439453</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6750354766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7794055938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5554962158203</t>
+    <t xml:space="preserve">27.6750392913818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7794036865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5554943084717</t>
   </si>
   <si>
     <t xml:space="preserve">24.9881401062012</t>
@@ -2486,7 +2486,7 @@
     <t xml:space="preserve">23.9581623077393</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0477275848389</t>
+    <t xml:space="preserve">24.0477256774902</t>
   </si>
   <si>
     <t xml:space="preserve">23.9133815765381</t>
@@ -2495,7 +2495,7 @@
     <t xml:space="preserve">24.5851058959961</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0773334503174</t>
+    <t xml:space="preserve">22.077335357666</t>
   </si>
   <si>
     <t xml:space="preserve">22.928186416626</t>
@@ -2510,19 +2510,19 @@
     <t xml:space="preserve">24.2268524169922</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4955425262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3164138793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3908061981201</t>
+    <t xml:space="preserve">24.4955406188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3164157867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3908081054688</t>
   </si>
   <si>
     <t xml:space="preserve">23.8238182067871</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0625305175781</t>
+    <t xml:space="preserve">23.0625324249268</t>
   </si>
   <si>
     <t xml:space="preserve">23.7790355682373</t>
@@ -2531,13 +2531,13 @@
     <t xml:space="preserve">22.8834018707275</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2416572570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1672687530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3167839050293</t>
+    <t xml:space="preserve">23.2416591644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1672668457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3167819976807</t>
   </si>
   <si>
     <t xml:space="preserve">26.6002788543701</t>
@@ -2546,58 +2546,58 @@
     <t xml:space="preserve">25.615083694458</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4359550476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8985786437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9733371734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5107154846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1972427368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8689670562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6450595855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4959106445312</t>
+    <t xml:space="preserve">25.4359569549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8985767364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9733352661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5107135772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.197244644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.868968963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6450576782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4959125518799</t>
   </si>
   <si>
     <t xml:space="preserve">27.048095703125</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9437274932861</t>
+    <t xml:space="preserve">27.9437255859375</t>
   </si>
   <si>
     <t xml:space="preserve">28.8841400146484</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9289207458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7050113677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7797718048096</t>
+    <t xml:space="preserve">28.9289226531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7050132751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7797737121582</t>
   </si>
   <si>
     <t xml:space="preserve">27.9885082244873</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6302547454834</t>
+    <t xml:space="preserve">27.630256652832</t>
   </si>
   <si>
     <t xml:space="preserve">27.2272205352783</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4063491821289</t>
+    <t xml:space="preserve">27.4063472747803</t>
   </si>
   <si>
     <t xml:space="preserve">26.6898403167725</t>
@@ -2606,31 +2606,31 @@
     <t xml:space="preserve">25.8389911651611</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7942085266113</t>
+    <t xml:space="preserve">25.7942066192627</t>
   </si>
   <si>
     <t xml:space="preserve">26.3315887451172</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7194519042969</t>
+    <t xml:space="preserve">24.7194499969482</t>
   </si>
   <si>
     <t xml:space="preserve">24.4507598876953</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5999088287354</t>
+    <t xml:space="preserve">23.599910736084</t>
   </si>
   <si>
     <t xml:space="preserve">23.4655666351318</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3615665435791</t>
+    <t xml:space="preserve">27.3615646362305</t>
   </si>
   <si>
     <t xml:space="preserve">28.0332889556885</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8541641235352</t>
+    <t xml:space="preserve">27.8541622161865</t>
   </si>
   <si>
     <t xml:space="preserve">28.163049697876</t>
@@ -2639,10 +2639,10 @@
     <t xml:space="preserve">27.6633834838867</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2979888916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.891170501709</t>
+    <t xml:space="preserve">30.2979869842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8911685943604</t>
   </si>
   <si>
     <t xml:space="preserve">27.3454132080078</t>
@@ -2651,16 +2651,16 @@
     <t xml:space="preserve">29.662052154541</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4803524017334</t>
+    <t xml:space="preserve">29.480354309082</t>
   </si>
   <si>
     <t xml:space="preserve">29.3440799713135</t>
   </si>
   <si>
-    <t xml:space="preserve">30.525110244751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5705375671387</t>
+    <t xml:space="preserve">30.5251121520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.57053565979</t>
   </si>
   <si>
     <t xml:space="preserve">31.0247802734375</t>
@@ -2684,7 +2684,7 @@
     <t xml:space="preserve">27.4362621307373</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0722007751465</t>
+    <t xml:space="preserve">28.0722026824951</t>
   </si>
   <si>
     <t xml:space="preserve">28.4355945587158</t>
@@ -2693,7 +2693,7 @@
     <t xml:space="preserve">28.5264434814453</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4810199737549</t>
+    <t xml:space="preserve">28.4810180664062</t>
   </si>
   <si>
     <t xml:space="preserve">28.3901710510254</t>
@@ -2702,16 +2702,16 @@
     <t xml:space="preserve">29.1623821258545</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4349308013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2538986206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1169567108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1162948608398</t>
+    <t xml:space="preserve">29.434928894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2538967132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1169586181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1162929534912</t>
   </si>
   <si>
     <t xml:space="preserve">30.9793529510498</t>
@@ -2720,22 +2720,22 @@
     <t xml:space="preserve">31.1610507965088</t>
   </si>
   <si>
-    <t xml:space="preserve">31.479024887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5698680877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.796989440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7515659332275</t>
+    <t xml:space="preserve">31.4790210723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5698719024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7969932556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7515697479248</t>
   </si>
   <si>
     <t xml:space="preserve">31.1156272888184</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2505683898926</t>
+    <t xml:space="preserve">33.2505645751953</t>
   </si>
   <si>
     <t xml:space="preserve">34.6587219238281</t>
@@ -2747,7 +2747,7 @@
     <t xml:space="preserve">34.4770240783691</t>
   </si>
   <si>
-    <t xml:space="preserve">34.386173248291</t>
+    <t xml:space="preserve">34.3861770629883</t>
   </si>
   <si>
     <t xml:space="preserve">34.5678672790527</t>
@@ -2780,10 +2780,10 @@
     <t xml:space="preserve">33.7502365112305</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9319305419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2499046325684</t>
+    <t xml:space="preserve">33.9319343566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2499008178711</t>
   </si>
   <si>
     <t xml:space="preserve">33.6139640808105</t>
@@ -2801,19 +2801,19 @@
     <t xml:space="preserve">38.6106338500977</t>
   </si>
   <si>
-    <t xml:space="preserve">39.5645446777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1109657287598</t>
+    <t xml:space="preserve">39.5645408630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.110969543457</t>
   </si>
   <si>
     <t xml:space="preserve">36.4302635192871</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3868370056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8871726989746</t>
+    <t xml:space="preserve">33.3868408203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8871765136719</t>
   </si>
   <si>
     <t xml:space="preserve">33.0688743591309</t>
@@ -2843,7 +2843,7 @@
     <t xml:space="preserve">30.7976551055908</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3895034790039</t>
+    <t xml:space="preserve">29.3895053863525</t>
   </si>
   <si>
     <t xml:space="preserve">29.5257778167725</t>
@@ -2852,19 +2852,19 @@
     <t xml:space="preserve">28.6172924041748</t>
   </si>
   <si>
-    <t xml:space="preserve">28.344747543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0254440307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9332675933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2058067321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1149597167969</t>
+    <t xml:space="preserve">28.3447456359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0254459381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9332637786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.205810546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1149559020996</t>
   </si>
   <si>
     <t xml:space="preserve">32.2512359619141</t>
@@ -2873,13 +2873,13 @@
     <t xml:space="preserve">31.615291595459</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0241088867188</t>
+    <t xml:space="preserve">32.024112701416</t>
   </si>
   <si>
     <t xml:space="preserve">33.1142959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6146278381348</t>
+    <t xml:space="preserve">32.614631652832</t>
   </si>
   <si>
     <t xml:space="preserve">31.2064743041992</t>
@@ -2888,7 +2888,7 @@
     <t xml:space="preserve">32.0695381164551</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5244445800781</t>
+    <t xml:space="preserve">31.5244483947754</t>
   </si>
   <si>
     <t xml:space="preserve">31.3427486419678</t>
@@ -2903,10 +2903,10 @@
     <t xml:space="preserve">32.7054748535156</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1603889465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.159049987793</t>
+    <t xml:space="preserve">32.1603851318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1590538024902</t>
   </si>
   <si>
     <t xml:space="preserve">33.7956581115723</t>
@@ -2918,7 +2918,7 @@
     <t xml:space="preserve">32.9325981140137</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0234489440918</t>
+    <t xml:space="preserve">33.0234451293945</t>
   </si>
   <si>
     <t xml:space="preserve">33.5231170654297</t>
@@ -2933,13 +2933,13 @@
     <t xml:space="preserve">31.8424167633057</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8878402709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4342613220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7074737548828</t>
+    <t xml:space="preserve">31.8878364562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4342632293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7074756622314</t>
   </si>
   <si>
     <t xml:space="preserve">30.7068099975586</t>
@@ -2951,16 +2951,16 @@
     <t xml:space="preserve">29.6166248321533</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8437442779541</t>
+    <t xml:space="preserve">29.8437461853027</t>
   </si>
   <si>
     <t xml:space="preserve">29.2532329559326</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7535667419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0708694458008</t>
+    <t xml:space="preserve">28.7535648345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0708675384521</t>
   </si>
   <si>
     <t xml:space="preserve">28.889835357666</t>
@@ -2981,19 +2981,19 @@
     <t xml:space="preserve">28.7989883422852</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8891754150391</t>
+    <t xml:space="preserve">29.8891735076904</t>
   </si>
   <si>
     <t xml:space="preserve">29.0715351104736</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2993202209473</t>
+    <t xml:space="preserve">28.2993221282959</t>
   </si>
   <si>
     <t xml:space="preserve">28.0267772674561</t>
   </si>
   <si>
-    <t xml:space="preserve">27.617956161499</t>
+    <t xml:space="preserve">27.6179580688477</t>
   </si>
   <si>
     <t xml:space="preserve">27.7542304992676</t>
@@ -3008,7 +3008,7 @@
     <t xml:space="preserve">27.4816837310791</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5725345611572</t>
+    <t xml:space="preserve">27.5725326538086</t>
   </si>
   <si>
     <t xml:space="preserve">26.6186237335205</t>
@@ -3026,31 +3026,31 @@
     <t xml:space="preserve">26.9820194244385</t>
   </si>
   <si>
-    <t xml:space="preserve">26.346076965332</t>
+    <t xml:space="preserve">26.3460788726807</t>
   </si>
   <si>
     <t xml:space="preserve">25.8918361663818</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6647129058838</t>
+    <t xml:space="preserve">25.6647148132324</t>
   </si>
   <si>
     <t xml:space="preserve">26.2552280426025</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8457431793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6640510559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4369258880615</t>
+    <t xml:space="preserve">26.8457450866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6640491485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4369277954102</t>
   </si>
   <si>
     <t xml:space="preserve">26.5732002258301</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3915023803711</t>
+    <t xml:space="preserve">26.3915004730225</t>
   </si>
   <si>
     <t xml:space="preserve">26.70947265625</t>
@@ -3068,22 +3068,22 @@
     <t xml:space="preserve">24.1657123565674</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6660442352295</t>
+    <t xml:space="preserve">23.6660461425781</t>
   </si>
   <si>
     <t xml:space="preserve">23.8477439880371</t>
   </si>
   <si>
-    <t xml:space="preserve">25.437593460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7555618286133</t>
+    <t xml:space="preserve">25.4375953674316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7555637359619</t>
   </si>
   <si>
     <t xml:space="preserve">25.074197769165</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0735359191895</t>
+    <t xml:space="preserve">26.0735340118408</t>
   </si>
   <si>
     <t xml:space="preserve">27.6892356872559</t>
@@ -69848,7 +69848,7 @@
     </row>
     <row r="2509">
       <c r="A2509" s="1" t="n">
-        <v>45972.6911689815</v>
+        <v>45972.3333333333</v>
       </c>
       <c r="B2509" t="n">
         <v>20206</v>
@@ -69869,6 +69869,32 @@
         <v>1404</v>
       </c>
       <c r="H2509" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2510">
+      <c r="A2510" s="1" t="n">
+        <v>45973.6910648148</v>
+      </c>
+      <c r="B2510" t="n">
+        <v>36615</v>
+      </c>
+      <c r="C2510" t="n">
+        <v>19.3799991607666</v>
+      </c>
+      <c r="D2510" t="n">
+        <v>18.7000007629395</v>
+      </c>
+      <c r="E2510" t="n">
+        <v>19</v>
+      </c>
+      <c r="F2510" t="n">
+        <v>18.7199993133545</v>
+      </c>
+      <c r="G2510" t="s">
+        <v>1407</v>
+      </c>
+      <c r="H2510" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ARN.MI.xlsx
+++ b/data/ARN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1431" uniqueCount="1431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1432" uniqueCount="1432">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92215013504028</t>
+    <t xml:space="preserve">1.92215001583099</t>
   </si>
   <si>
     <t xml:space="preserve">ARN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94450080394745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.917360663414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90778183937073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8838347196579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93172895908356</t>
+    <t xml:space="preserve">1.94450068473816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91736078262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90778172016144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88383483886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93172907829285</t>
   </si>
   <si>
     <t xml:space="preserve">1.91576433181763</t>
@@ -68,22 +68,22 @@
     <t xml:space="preserve">1.83594083786011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91097474098206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.807204246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74973142147064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71620571613312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80401146411896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81039726734161</t>
+    <t xml:space="preserve">1.91097497940063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80720400810242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74973106384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71620547771454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80401134490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81039714813232</t>
   </si>
   <si>
     <t xml:space="preserve">1.79602921009064</t>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">1.77208197116852</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70662677288055</t>
+    <t xml:space="preserve">1.70662641525269</t>
   </si>
   <si>
     <t xml:space="preserve">1.69704759120941</t>
@@ -101,13 +101,13 @@
     <t xml:space="preserve">1.69066190719604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6762934923172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70024085044861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69864416122437</t>
+    <t xml:space="preserve">1.67629361152649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7002409696579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69864439964294</t>
   </si>
   <si>
     <t xml:space="preserve">1.67469727993011</t>
@@ -119,115 +119,115 @@
     <t xml:space="preserve">1.66032898426056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81518638134003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8279584646225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86148416996002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88543093204498</t>
+    <t xml:space="preserve">1.81518661975861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82795822620392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86148428916931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88543140888214</t>
   </si>
   <si>
     <t xml:space="preserve">1.8918172121048</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92853605747223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95407938957214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90618562698364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86787009239197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88064181804657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85190546512604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85988795757294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85509812831879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79283595085144</t>
+    <t xml:space="preserve">1.92853581905365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95407950878143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90618550777435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86786985397339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88064193725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85190534591675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85988783836365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85509836673737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79283618927002</t>
   </si>
   <si>
     <t xml:space="preserve">1.78804636001587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78006434440613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7561172246933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76888906955719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7640997171402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78485381603241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77048540115356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72099494934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73536312580109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.802414894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76250302791595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74494206905365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73217022418976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73695993423462</t>
+    <t xml:space="preserve">1.78006446361542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75611734390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76888883113861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76409947872162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78485369682312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77048528194427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72099459171295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7353630065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80241477489471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76250314712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74494194984436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73217034339905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73695957660675</t>
   </si>
   <si>
     <t xml:space="preserve">1.74334537982941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75132787227631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68587267398834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67789018154144</t>
+    <t xml:space="preserve">1.75132775306702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68587255477905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67789006233215</t>
   </si>
   <si>
     <t xml:space="preserve">1.65234661102295</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62041747570038</t>
+    <t xml:space="preserve">1.62041735649109</t>
   </si>
   <si>
     <t xml:space="preserve">1.64276790618896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5900844335556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60285604000092</t>
+    <t xml:space="preserve">1.59008419513702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60285592079163</t>
   </si>
   <si>
     <t xml:space="preserve">1.54937434196472</t>
@@ -236,13 +236,13 @@
     <t xml:space="preserve">1.51185727119446</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45598077774048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43682301044464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4695508480072</t>
+    <t xml:space="preserve">1.45598089694977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43682324886322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46955072879791</t>
   </si>
   <si>
     <t xml:space="preserve">1.49748909473419</t>
@@ -251,31 +251,31 @@
     <t xml:space="preserve">1.47673487663269</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47274374961853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46875250339508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49669086933136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47593677043915</t>
+    <t xml:space="preserve">1.47274363040924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46875262260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49669075012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47593665122986</t>
   </si>
   <si>
     <t xml:space="preserve">1.50626957416534</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47753322124481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43841981887817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40090262889862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3490172624588</t>
+    <t xml:space="preserve">1.47753310203552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43841969966888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40090250968933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34901738166809</t>
   </si>
   <si>
     <t xml:space="preserve">1.30910563468933</t>
@@ -284,34 +284,34 @@
     <t xml:space="preserve">1.34342968463898</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32666671276093</t>
+    <t xml:space="preserve">1.32666683197021</t>
   </si>
   <si>
     <t xml:space="preserve">1.34103500843048</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31708788871765</t>
+    <t xml:space="preserve">1.31708776950836</t>
   </si>
   <si>
     <t xml:space="preserve">1.38653445243835</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39691150188446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40649020671844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30671060085297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32347369194031</t>
+    <t xml:space="preserve">1.39691162109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40649032592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30671083927155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32347393035889</t>
   </si>
   <si>
     <t xml:space="preserve">1.305912733078</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31229865550995</t>
+    <t xml:space="preserve">1.31229853630066</t>
   </si>
   <si>
     <t xml:space="preserve">1.28994798660278</t>
@@ -320,19 +320,19 @@
     <t xml:space="preserve">1.28515839576721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28595674037933</t>
+    <t xml:space="preserve">1.28595662117004</t>
   </si>
   <si>
     <t xml:space="preserve">1.33305263519287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33704388141632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30112338066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36104869842529</t>
+    <t xml:space="preserve">1.33704376220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30112326145172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36104893684387</t>
   </si>
   <si>
     <t xml:space="preserve">1.34627258777618</t>
@@ -341,31 +341,31 @@
     <t xml:space="preserve">1.35283982753754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33806371688843</t>
+    <t xml:space="preserve">1.33806359767914</t>
   </si>
   <si>
     <t xml:space="preserve">1.27157092094421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28881001472473</t>
+    <t xml:space="preserve">1.28880977630615</t>
   </si>
   <si>
     <t xml:space="preserve">1.29291427135468</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30686974525452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33888471126556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34955632686615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34380972385406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33642172813416</t>
+    <t xml:space="preserve">1.30686950683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33888447284698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34955608844757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34380984306335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33642184734344</t>
   </si>
   <si>
     <t xml:space="preserve">1.34709346294403</t>
@@ -374,43 +374,43 @@
     <t xml:space="preserve">1.30522775650024</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29127264022827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31425762176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32164549827576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26828742027283</t>
+    <t xml:space="preserve">1.29127252101898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31425750255585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32164561748505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26828730106354</t>
   </si>
   <si>
     <t xml:space="preserve">1.27239179611206</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28798890113831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2970187664032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24858570098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32657122612</t>
+    <t xml:space="preserve">1.28798878192902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29701888561249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24858582019806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32657098770142</t>
   </si>
   <si>
     <t xml:space="preserve">1.33231735229492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3594069480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4201534986496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48664617538452</t>
+    <t xml:space="preserve">1.35940682888031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42015326023102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48664605617523</t>
   </si>
   <si>
     <t xml:space="preserve">1.53343737125397</t>
@@ -425,46 +425,46 @@
     <t xml:space="preserve">1.43739235401154</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46776556968689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43000423908234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40948188304901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44478034973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5597060918808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61798989772797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70582592487335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74851262569427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72388541698456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6828408241272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67463171482086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65164685249329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64179599285126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67134821414948</t>
+    <t xml:space="preserve">1.46776568889618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43000411987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40948176383972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44478023052216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55970585346222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61798977851868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70582580566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74851286411285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72388565540314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68284070491791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67463183403015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65164661407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64179587364197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67134809494019</t>
   </si>
   <si>
     <t xml:space="preserve">1.66478109359741</t>
@@ -473,10 +473,10 @@
     <t xml:space="preserve">1.65657186508179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69597506523132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69433319568634</t>
+    <t xml:space="preserve">1.69597494602203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69433331489563</t>
   </si>
   <si>
     <t xml:space="preserve">1.65821385383606</t>
@@ -485,7 +485,7 @@
     <t xml:space="preserve">1.6811990737915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68776619434357</t>
+    <t xml:space="preserve">1.68776607513428</t>
   </si>
   <si>
     <t xml:space="preserve">1.66806471347809</t>
@@ -494,28 +494,28 @@
     <t xml:space="preserve">1.6500049829483</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66313910484314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67791521549225</t>
+    <t xml:space="preserve">1.66313922405243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67791545391083</t>
   </si>
   <si>
     <t xml:space="preserve">2.03746891021729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04403567314148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0391104221344</t>
+    <t xml:space="preserve">2.04403591156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03911066055298</t>
   </si>
   <si>
     <t xml:space="preserve">2.04075241088867</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0522449016571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04731965065002</t>
+    <t xml:space="preserve">2.05224514007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04731941223145</t>
   </si>
   <si>
     <t xml:space="preserve">2.04239416122437</t>
@@ -527,37 +527,37 @@
     <t xml:space="preserve">2.241051197052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18851375579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17537999153137</t>
+    <t xml:space="preserve">2.18851351737976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17537975311279</t>
   </si>
   <si>
     <t xml:space="preserve">2.145827293396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00627446174622</t>
+    <t xml:space="preserve">2.00627470016479</t>
   </si>
   <si>
     <t xml:space="preserve">1.9882150888443</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99313974380493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99806582927704</t>
+    <t xml:space="preserve">1.99314022064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99806559085846</t>
   </si>
   <si>
     <t xml:space="preserve">1.99642360210419</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99970757961273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00299119949341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00791645050049</t>
+    <t xml:space="preserve">1.99970734119415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00299096107483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00791668891907</t>
   </si>
   <si>
     <t xml:space="preserve">2.0111997127533</t>
@@ -566,10 +566,10 @@
     <t xml:space="preserve">2.02597618103027</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03254318237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02105069160461</t>
+    <t xml:space="preserve">2.03254342079163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02105045318604</t>
   </si>
   <si>
     <t xml:space="preserve">2.0194091796875</t>
@@ -578,76 +578,76 @@
     <t xml:space="preserve">2.02433443069458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07687187194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05881190299988</t>
+    <t xml:space="preserve">2.07687163352966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05881214141846</t>
   </si>
   <si>
     <t xml:space="preserve">2.09657335281372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14746904373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33955907821655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27552914619446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32478308677673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27881264686584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25746941566467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2985143661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26075267791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2804548740387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30672335624695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35597729682922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34120082855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34284281730652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34776782989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44627571105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39209651947021</t>
+    <t xml:space="preserve">2.14746880531311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33955883979797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27552890777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32478284835815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.278813123703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25746965408325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29851484298706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26075291633606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28045463562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30672311782837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35597681999207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3412013053894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3428430557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3477680683136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44627594947815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39209675788879</t>
   </si>
   <si>
     <t xml:space="preserve">2.38224577903748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38717150688171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38388752937317</t>
+    <t xml:space="preserve">2.38717126846313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38388776779175</t>
   </si>
   <si>
     <t xml:space="preserve">2.40523099899292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38060426712036</t>
+    <t xml:space="preserve">2.38060402870178</t>
   </si>
   <si>
     <t xml:space="preserve">2.42164874076843</t>
@@ -656,55 +656,55 @@
     <t xml:space="preserve">2.33791732788086</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32314157485962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35433554649353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41015648841858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40687274932861</t>
+    <t xml:space="preserve">2.32314133644104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35433506965637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41015672683716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40687298774719</t>
   </si>
   <si>
     <t xml:space="preserve">2.43806648254395</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41836547851562</t>
+    <t xml:space="preserve">2.41836524009705</t>
   </si>
   <si>
     <t xml:space="preserve">2.29030513763428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34941005706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36418628692627</t>
+    <t xml:space="preserve">2.34940981864929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36418652534485</t>
   </si>
   <si>
     <t xml:space="preserve">2.3756787776947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40194749832153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35761904716492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36746954917908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37075328826904</t>
+    <t xml:space="preserve">2.40194725990295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35761880874634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36746978759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37075281143188</t>
   </si>
   <si>
     <t xml:space="preserve">2.37239503860474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36254405975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36582779884338</t>
+    <t xml:space="preserve">2.362544298172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36582827568054</t>
   </si>
   <si>
     <t xml:space="preserve">2.39538025856018</t>
@@ -713,13 +713,13 @@
     <t xml:space="preserve">2.3773205280304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37403702735901</t>
+    <t xml:space="preserve">2.37403678894043</t>
   </si>
   <si>
     <t xml:space="preserve">2.38881325721741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39373850822449</t>
+    <t xml:space="preserve">2.39373826980591</t>
   </si>
   <si>
     <t xml:space="preserve">2.39045453071594</t>
@@ -728,82 +728,82 @@
     <t xml:space="preserve">2.41343998908997</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40358924865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40030550956726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40851449966431</t>
+    <t xml:space="preserve">2.40358901023865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40030574798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40851473808289</t>
   </si>
   <si>
     <t xml:space="preserve">2.42329049110413</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43149971961975</t>
+    <t xml:space="preserve">2.43149995803833</t>
   </si>
   <si>
     <t xml:space="preserve">2.42000722885132</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35105204582214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33627533912659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34612584114075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43642520904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42657446861267</t>
+    <t xml:space="preserve">2.35105180740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33627510070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34612631797791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43642497062683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42657470703125</t>
   </si>
   <si>
     <t xml:space="preserve">2.42985820770264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45284342765808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47701287269592</t>
+    <t xml:space="preserve">2.45284295082092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47701334953308</t>
   </si>
   <si>
     <t xml:space="preserve">2.478679895401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49201512336731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49368214607239</t>
+    <t xml:space="preserve">2.49201536178589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49368238449097</t>
   </si>
   <si>
     <t xml:space="preserve">2.47534608840942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46534466743469</t>
+    <t xml:space="preserve">2.46534490585327</t>
   </si>
   <si>
     <t xml:space="preserve">2.482013463974</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46867823600769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45867729187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46201109886169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45534348487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41700482368469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40867042541504</t>
+    <t xml:space="preserve">2.46867847442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4586775302887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46201086044312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45534324645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41700506210327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40867018699646</t>
   </si>
   <si>
     <t xml:space="preserve">2.36699771881104</t>
@@ -812,16 +812,16 @@
     <t xml:space="preserve">2.34199404716492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36866450309753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35366249084473</t>
+    <t xml:space="preserve">2.36866474151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35366225242615</t>
   </si>
   <si>
     <t xml:space="preserve">2.38533353805542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38366675376892</t>
+    <t xml:space="preserve">2.3836669921875</t>
   </si>
   <si>
     <t xml:space="preserve">2.36366391181946</t>
@@ -830,31 +830,31 @@
     <t xml:space="preserve">2.32532477378845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31699109077454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28531956672668</t>
+    <t xml:space="preserve">2.31699061393738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28531980514526</t>
   </si>
   <si>
     <t xml:space="preserve">2.28698658943176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29698801040649</t>
+    <t xml:space="preserve">2.29698777198792</t>
   </si>
   <si>
     <t xml:space="preserve">2.31532406806946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28365278244019</t>
+    <t xml:space="preserve">2.28365230560303</t>
   </si>
   <si>
     <t xml:space="preserve">2.28865337371826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29031991958618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30198884010315</t>
+    <t xml:space="preserve">2.29032015800476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30198860168457</t>
   </si>
   <si>
     <t xml:space="preserve">2.30365562438965</t>
@@ -866,28 +866,28 @@
     <t xml:space="preserve">2.24198007583618</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26698350906372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2686505317688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32699203491211</t>
+    <t xml:space="preserve">2.2669837474823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26865077018738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32699227333069</t>
   </si>
   <si>
     <t xml:space="preserve">2.31865763664246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31032299995422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24364733695984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25031495094299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22531151771545</t>
+    <t xml:space="preserve">2.31032347679138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24364709854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25031471252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22531127929688</t>
   </si>
   <si>
     <t xml:space="preserve">2.25198173522949</t>
@@ -896,70 +896,70 @@
     <t xml:space="preserve">2.22197723388672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20697522163391</t>
+    <t xml:space="preserve">2.20697546005249</t>
   </si>
   <si>
     <t xml:space="preserve">2.20030784606934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16863679885864</t>
+    <t xml:space="preserve">2.16863656044006</t>
   </si>
   <si>
     <t xml:space="preserve">2.17863821983337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16696953773499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18697285652161</t>
+    <t xml:space="preserve">2.16696977615356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18697237968445</t>
   </si>
   <si>
     <t xml:space="preserve">2.19697380065918</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18363881111145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18530559539795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1919732093811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17530369758606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14196634292603</t>
+    <t xml:space="preserve">2.18363857269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18530583381653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19197344779968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17530417442322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14196586608887</t>
   </si>
   <si>
     <t xml:space="preserve">2.15363454818726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14363312721252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13529896736145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12696409225464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12863111495972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12029671669006</t>
+    <t xml:space="preserve">2.14363360404968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13529849052429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12696433067322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12863087654114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12029647827148</t>
   </si>
   <si>
     <t xml:space="preserve">2.13029813766479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11862969398499</t>
+    <t xml:space="preserve">2.11862945556641</t>
   </si>
   <si>
     <t xml:space="preserve">2.37366533279419</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37533164024353</t>
+    <t xml:space="preserve">2.37533211708069</t>
   </si>
   <si>
     <t xml:space="preserve">2.40700340270996</t>
@@ -971,16 +971,16 @@
     <t xml:space="preserve">2.39200091362</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49868249893188</t>
+    <t xml:space="preserve">2.49868273735046</t>
   </si>
   <si>
     <t xml:space="preserve">2.49534869194031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50868391990662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51201748847961</t>
+    <t xml:space="preserve">2.50868439674377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51201772689819</t>
   </si>
   <si>
     <t xml:space="preserve">2.51535153388977</t>
@@ -989,16 +989,16 @@
     <t xml:space="preserve">2.51701879501343</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52368688583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52535319328308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54535603523254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53368759155273</t>
+    <t xml:space="preserve">2.523686170578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5253529548645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54535555839539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53368782997131</t>
   </si>
   <si>
     <t xml:space="preserve">2.53202080726624</t>
@@ -1007,10 +1007,10 @@
     <t xml:space="preserve">2.54035544395447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52701997756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53868842124939</t>
+    <t xml:space="preserve">2.52702045440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53868818283081</t>
   </si>
   <si>
     <t xml:space="preserve">2.53702163696289</t>
@@ -1019,10 +1019,10 @@
     <t xml:space="preserve">2.49701595306396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42700624465942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50034952163696</t>
+    <t xml:space="preserve">2.42700600624084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50034976005554</t>
   </si>
   <si>
     <t xml:space="preserve">2.50535035133362</t>
@@ -1031,10 +1031,10 @@
     <t xml:space="preserve">2.48368072509766</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45200943946838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51368474960327</t>
+    <t xml:space="preserve">2.45200967788696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51368522644043</t>
   </si>
   <si>
     <t xml:space="preserve">2.54202222824097</t>
@@ -1049,13 +1049,13 @@
     <t xml:space="preserve">2.520352602005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47201251983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50201678276062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48701429367065</t>
+    <t xml:space="preserve">2.472012758255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50201630592346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48701453208923</t>
   </si>
   <si>
     <t xml:space="preserve">3.00041961669922</t>
@@ -1064,43 +1064,43 @@
     <t xml:space="preserve">2.81706094741821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75038480758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71704649925232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8087260723114</t>
+    <t xml:space="preserve">2.75038456916809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71704697608948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80872631072998</t>
   </si>
   <si>
     <t xml:space="preserve">2.80039167404175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83372974395752</t>
+    <t xml:space="preserve">2.8337299823761</t>
   </si>
   <si>
     <t xml:space="preserve">2.78372263908386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84206414222717</t>
+    <t xml:space="preserve">2.84206438064575</t>
   </si>
   <si>
     <t xml:space="preserve">2.75871896743774</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85039830207825</t>
+    <t xml:space="preserve">2.85039854049683</t>
   </si>
   <si>
     <t xml:space="preserve">2.85873341560364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89207124710083</t>
+    <t xml:space="preserve">2.89207148551941</t>
   </si>
   <si>
     <t xml:space="preserve">2.82539510726929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72538137435913</t>
+    <t xml:space="preserve">2.72538113594055</t>
   </si>
   <si>
     <t xml:space="preserve">2.61703300476074</t>
@@ -1112,31 +1112,31 @@
     <t xml:space="preserve">2.70037746429443</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65870547294617</t>
+    <t xml:space="preserve">2.65870499610901</t>
   </si>
   <si>
     <t xml:space="preserve">2.62536716461182</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63370156288147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59202885627747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66703987121582</t>
+    <t xml:space="preserve">2.63370180130005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59202909469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66703963279724</t>
   </si>
   <si>
     <t xml:space="preserve">2.70871210098267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74205017089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65037059783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68370866775513</t>
+    <t xml:space="preserve">2.74204969406128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65037083625793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68370890617371</t>
   </si>
   <si>
     <t xml:space="preserve">2.6003634929657</t>
@@ -1145,13 +1145,13 @@
     <t xml:space="preserve">2.58369469642639</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56702589988708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76705360412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73371577262878</t>
+    <t xml:space="preserve">2.56702566146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76705384254456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73371601104736</t>
   </si>
   <si>
     <t xml:space="preserve">2.79205703735352</t>
@@ -1166,10 +1166,10 @@
     <t xml:space="preserve">2.88373684883118</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77538800239563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78091406822205</t>
+    <t xml:space="preserve">2.77538776397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78091359138489</t>
   </si>
   <si>
     <t xml:space="preserve">2.72174572944641</t>
@@ -1178,10 +1178,10 @@
     <t xml:space="preserve">2.7301983833313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77246141433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64567184448242</t>
+    <t xml:space="preserve">2.77246165275574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.645672082901</t>
   </si>
   <si>
     <t xml:space="preserve">2.70484018325806</t>
@@ -1190,28 +1190,28 @@
     <t xml:space="preserve">2.68793511390686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66257739067078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69638729095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65412449836731</t>
+    <t xml:space="preserve">2.6625771522522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69638752937317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65412473678589</t>
   </si>
   <si>
     <t xml:space="preserve">2.60340857505798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63721919059753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61186122894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57805109024048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5949559211731</t>
+    <t xml:space="preserve">2.63721895217896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61186146736145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5780508518219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59495615959167</t>
   </si>
   <si>
     <t xml:space="preserve">2.50197720527649</t>
@@ -1229,16 +1229,16 @@
     <t xml:space="preserve">2.58650326728821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51888275146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53578782081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55269265174866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51043009757996</t>
+    <t xml:space="preserve">2.51888251304626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53578758239746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55269289016724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51042985916138</t>
   </si>
   <si>
     <t xml:space="preserve">2.56959843635559</t>
@@ -1247,10 +1247,10 @@
     <t xml:space="preserve">2.46816682815552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48507213592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41745090484619</t>
+    <t xml:space="preserve">2.48507189750671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41745114326477</t>
   </si>
   <si>
     <t xml:space="preserve">2.45126175880432</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">2.39209294319153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38364028930664</t>
+    <t xml:space="preserve">2.38364052772522</t>
   </si>
   <si>
     <t xml:space="preserve">2.27375626564026</t>
@@ -1268,31 +1268,31 @@
     <t xml:space="preserve">2.29911422729492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36673521995544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35828280448914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43435645103455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42590355873108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34983015060425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28220891952515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32447195053101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40899848937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45971441268921</t>
+    <t xml:space="preserve">2.36673545837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35828232765198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43435621261597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4259033203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34982991218567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28220868110657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32447218894958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4089982509613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45971417427063</t>
   </si>
   <si>
     <t xml:space="preserve">2.44280886650085</t>
@@ -1307,10 +1307,10 @@
     <t xml:space="preserve">2.400545835495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37518787384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47661948204041</t>
+    <t xml:space="preserve">2.37518763542175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47661924362183</t>
   </si>
   <si>
     <t xml:space="preserve">2.30756711959839</t>
@@ -1319,19 +1319,19 @@
     <t xml:space="preserve">2.23994588851929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29430246353149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23437666893005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24293732643127</t>
+    <t xml:space="preserve">2.29430222511292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23437643051147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2429370880127</t>
   </si>
   <si>
     <t xml:space="preserve">2.33710670471191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25149822235107</t>
+    <t xml:space="preserve">2.25149846076965</t>
   </si>
   <si>
     <t xml:space="preserve">2.27718067169189</t>
@@ -1340,22 +1340,22 @@
     <t xml:space="preserve">2.26861977577209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44839715957642</t>
+    <t xml:space="preserve">2.448397397995</t>
   </si>
   <si>
     <t xml:space="preserve">2.37134981155396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31142401695251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28574180603027</t>
+    <t xml:space="preserve">2.31142377853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28574156761169</t>
   </si>
   <si>
     <t xml:space="preserve">2.26005911827087</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35422801971436</t>
+    <t xml:space="preserve">2.35422825813293</t>
   </si>
   <si>
     <t xml:space="preserve">2.22581553459167</t>
@@ -1370,52 +1370,52 @@
     <t xml:space="preserve">2.31998491287231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37991070747375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40559315681458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39703226089478</t>
+    <t xml:space="preserve">2.37991046905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.405592918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39703249931335</t>
   </si>
   <si>
     <t xml:space="preserve">2.32854557037354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38847160339355</t>
+    <t xml:space="preserve">2.3884711265564</t>
   </si>
   <si>
     <t xml:space="preserve">2.36278891563416</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34566736221313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20013308525085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18301153182983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4398365020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54256653785706</t>
+    <t xml:space="preserve">2.34566688537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20013284683228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18301105499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43983626365662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54256629943848</t>
   </si>
   <si>
     <t xml:space="preserve">2.6024923324585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69666147232056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77370882034302</t>
+    <t xml:space="preserve">2.69666123390198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77370858192444</t>
   </si>
   <si>
     <t xml:space="preserve">2.63673543930054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67097878456116</t>
+    <t xml:space="preserve">2.67097854614258</t>
   </si>
   <si>
     <t xml:space="preserve">2.61961364746094</t>
@@ -1424,13 +1424,13 @@
     <t xml:space="preserve">2.65385699272156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68810057640076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64529609680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71378326416016</t>
+    <t xml:space="preserve">2.68810081481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64529633522034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71378302574158</t>
   </si>
   <si>
     <t xml:space="preserve">2.72234392166138</t>
@@ -1439,7 +1439,7 @@
     <t xml:space="preserve">3.07333779335022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52706170082092</t>
+    <t xml:space="preserve">3.5270619392395</t>
   </si>
   <si>
     <t xml:space="preserve">3.59554839134216</t>
@@ -1448,34 +1448,34 @@
     <t xml:space="preserve">3.6554741859436</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58698749542236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6126697063446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53562259674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42433166503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54418325424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56986594200134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55274415016174</t>
+    <t xml:space="preserve">3.58698797225952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61266946792603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5356228351593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42433190345764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54418349266052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56986570358276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55274438858032</t>
   </si>
   <si>
     <t xml:space="preserve">3.56130480766296</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50993967056274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48425769805908</t>
+    <t xml:space="preserve">3.50993990898132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4842574596405</t>
   </si>
   <si>
     <t xml:space="preserve">3.57842659950256</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">3.638352394104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74108219146729</t>
+    <t xml:space="preserve">3.74108290672302</t>
   </si>
   <si>
     <t xml:space="preserve">4.16912364959717</t>
@@ -1496,7 +1496,7 @@
     <t xml:space="preserve">5.15361976623535</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62284803390503</t>
+    <t xml:space="preserve">4.62284755706787</t>
   </si>
   <si>
     <t xml:space="preserve">4.19480657577515</t>
@@ -1511,28 +1511,28 @@
     <t xml:space="preserve">4.52011823654175</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58860492706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34890127182007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16056346893311</t>
+    <t xml:space="preserve">4.58860445022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34890174865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16056299209595</t>
   </si>
   <si>
     <t xml:space="preserve">4.23761081695557</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29753684997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89517712593079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27879738807678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25311517715454</t>
+    <t xml:space="preserve">4.29753637313843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89517784118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27879762649536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25311493873596</t>
   </si>
   <si>
     <t xml:space="preserve">2.89356064796448</t>
@@ -1544,7 +1544,7 @@
     <t xml:space="preserve">3.1675066947937</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03909420967102</t>
+    <t xml:space="preserve">3.0390944480896</t>
   </si>
   <si>
     <t xml:space="preserve">3.44145345687866</t>
@@ -1556,13 +1556,13 @@
     <t xml:space="preserve">3.39008855819702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84381198883057</t>
+    <t xml:space="preserve">3.84381246566772</t>
   </si>
   <si>
     <t xml:space="preserve">3.83525133132935</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87805604934692</t>
+    <t xml:space="preserve">3.87805557250977</t>
   </si>
   <si>
     <t xml:space="preserve">3.76676511764526</t>
@@ -1571,19 +1571,19 @@
     <t xml:space="preserve">3.88661646842957</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8523736000061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92942118644714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95510363578796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93798136711121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11775922775269</t>
+    <t xml:space="preserve">3.85237336158752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92942070960999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95510268211365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93798160552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11775875091553</t>
   </si>
   <si>
     <t xml:space="preserve">4.25473165512085</t>
@@ -1595,7 +1595,7 @@
     <t xml:space="preserve">4.26329326629639</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28041505813599</t>
+    <t xml:space="preserve">4.28041458129883</t>
   </si>
   <si>
     <t xml:space="preserve">4.43450927734375</t>
@@ -1604,25 +1604,25 @@
     <t xml:space="preserve">4.20336723327637</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00646877288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10919857025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15200233459473</t>
+    <t xml:space="preserve">4.00646781921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10919809341431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15200281143188</t>
   </si>
   <si>
     <t xml:space="preserve">4.08351564407349</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94654226303101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07495498657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02358913421631</t>
+    <t xml:space="preserve">3.94654273986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07495450973511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02358961105347</t>
   </si>
   <si>
     <t xml:space="preserve">3.96366405487061</t>
@@ -1634,13 +1634,13 @@
     <t xml:space="preserve">4.12631988525391</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01664638519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70845603942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91391611099243</t>
+    <t xml:space="preserve">5.01664590835571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70845651626587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91391563415527</t>
   </si>
   <si>
     <t xml:space="preserve">4.96528148651123</t>
@@ -1652,7 +1652,7 @@
     <t xml:space="preserve">5.20498466491699</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56453895568848</t>
+    <t xml:space="preserve">5.56453943252563</t>
   </si>
   <si>
     <t xml:space="preserve">5.68439102172852</t>
@@ -1661,43 +1661,43 @@
     <t xml:space="preserve">5.95833683013916</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90697240829468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88985109329224</t>
+    <t xml:space="preserve">5.90697288513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88985061645508</t>
   </si>
   <si>
     <t xml:space="preserve">6.57471656799316</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12955379486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4035005569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01987934112549</t>
+    <t xml:space="preserve">6.129554271698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40350008010864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01987981796265</t>
   </si>
   <si>
     <t xml:space="preserve">7.20821809768677</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32807016372681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05412340164185</t>
+    <t xml:space="preserve">7.32807064056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.054123878479</t>
   </si>
   <si>
     <t xml:space="preserve">7.00275850296021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42397737503052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28357076644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87990283966064</t>
+    <t xml:space="preserve">7.42397689819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28357172012329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8799033164978</t>
   </si>
   <si>
     <t xml:space="preserve">6.9676570892334</t>
@@ -1718,58 +1718,58 @@
     <t xml:space="preserve">6.82725095748901</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68684434890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66929388046265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45868444442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4060320854187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31827783584595</t>
+    <t xml:space="preserve">6.68684482574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66929340362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45868492126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40603256225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31827878952026</t>
   </si>
   <si>
     <t xml:space="preserve">6.80970001220703</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17826652526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35377407073975</t>
+    <t xml:space="preserve">7.1782660484314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3537745475769</t>
   </si>
   <si>
     <t xml:space="preserve">7.26602029800415</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05541086196899</t>
+    <t xml:space="preserve">7.05541133880615</t>
   </si>
   <si>
     <t xml:space="preserve">7.07296228408813</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63419198989868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44113397598267</t>
+    <t xml:space="preserve">6.63419246673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44113349914551</t>
   </si>
   <si>
     <t xml:space="preserve">6.30072736740112</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05501651763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03746604919434</t>
+    <t xml:space="preserve">6.05501699447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03746557235718</t>
   </si>
   <si>
     <t xml:space="preserve">5.37053632736206</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40563821792603</t>
+    <t xml:space="preserve">5.40563774108887</t>
   </si>
   <si>
     <t xml:space="preserve">5.52849340438843</t>
@@ -1778,37 +1778,37 @@
     <t xml:space="preserve">5.65134906768799</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12521934509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96726322174072</t>
+    <t xml:space="preserve">6.12522029876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96726274490356</t>
   </si>
   <si>
     <t xml:space="preserve">6.01991558074951</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91461038589478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84440755844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94971227645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86195802688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82685708999634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93216228485107</t>
+    <t xml:space="preserve">5.91461086273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84440660476685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9497127532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86195850372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82685661315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93216180801392</t>
   </si>
   <si>
     <t xml:space="preserve">5.87950944900513</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79175519943237</t>
+    <t xml:space="preserve">5.79175472259521</t>
   </si>
   <si>
     <t xml:space="preserve">5.68645095825195</t>
@@ -1820,37 +1820,37 @@
     <t xml:space="preserve">5.63379812240601</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70400094985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58114624023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66890048980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56359577178955</t>
+    <t xml:space="preserve">5.70400190353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58114576339722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66890001296997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56359529495239</t>
   </si>
   <si>
     <t xml:space="preserve">5.61624765396118</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49339246749878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31788396835327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1774787902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2652325630188</t>
+    <t xml:space="preserve">5.49339294433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31788444519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17747831344604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26523208618164</t>
   </si>
   <si>
     <t xml:space="preserve">5.28278303146362</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35298633575439</t>
+    <t xml:space="preserve">5.35298585891724</t>
   </si>
   <si>
     <t xml:space="preserve">5.42318868637085</t>
@@ -1862,10 +1862,10 @@
     <t xml:space="preserve">5.38808727264404</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51094341278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77420520782471</t>
+    <t xml:space="preserve">5.5109429359436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77420377731323</t>
   </si>
   <si>
     <t xml:space="preserve">5.44073963165283</t>
@@ -1883,7 +1883,7 @@
     <t xml:space="preserve">6.16032123565674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37093067169189</t>
+    <t xml:space="preserve">6.37093114852905</t>
   </si>
   <si>
     <t xml:space="preserve">6.47623538970947</t>
@@ -1892,7 +1892,7 @@
     <t xml:space="preserve">6.42358303070068</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54643821716309</t>
+    <t xml:space="preserve">6.54643869400024</t>
   </si>
   <si>
     <t xml:space="preserve">6.98520755767822</t>
@@ -1907,13 +1907,13 @@
     <t xml:space="preserve">7.16071557998657</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19581604003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95010614395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14316511154175</t>
+    <t xml:space="preserve">7.19581651687622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95010662078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14316463470459</t>
   </si>
   <si>
     <t xml:space="preserve">7.12561368942261</t>
@@ -1922,7 +1922,7 @@
     <t xml:space="preserve">7.02030944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84519577026367</t>
+    <t xml:space="preserve">7.84519481658936</t>
   </si>
   <si>
     <t xml:space="preserve">8.3366174697876</t>
@@ -1931,25 +1931,25 @@
     <t xml:space="preserve">8.31906700134277</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42437171936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08252429962158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6876335144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03864860534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30191040039062</t>
+    <t xml:space="preserve">8.42437076568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08252716064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68763256072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03864765167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30190944671631</t>
   </si>
   <si>
     <t xml:space="preserve">11.2763729095459</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1630802154541</t>
+    <t xml:space="preserve">13.1630811691284</t>
   </si>
   <si>
     <t xml:space="preserve">13.075325012207</t>
@@ -1964,13 +1964,13 @@
     <t xml:space="preserve">12.0222806930542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1100330352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9345264434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.36412525177</t>
+    <t xml:space="preserve">12.1100339889526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9345254898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3641262054443</t>
   </si>
   <si>
     <t xml:space="preserve">10.8814792633057</t>
@@ -1979,13 +1979,13 @@
     <t xml:space="preserve">12.1539106369019</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6712656021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.715142250061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4518795013428</t>
+    <t xml:space="preserve">11.6712646484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7151412963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4518804550171</t>
   </si>
   <si>
     <t xml:space="preserve">11.0569868087769</t>
@@ -1994,31 +1994,31 @@
     <t xml:space="preserve">11.4957571029663</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4080018997192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8906478881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8028955459595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3202486038208</t>
+    <t xml:space="preserve">11.4080038070679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8906497955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8028945922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3202476501465</t>
   </si>
   <si>
     <t xml:space="preserve">11.627387046814</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1447410583496</t>
+    <t xml:space="preserve">11.1447420120239</t>
   </si>
   <si>
     <t xml:space="preserve">10.618218421936</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5304651260376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5743398666382</t>
+    <t xml:space="preserve">10.5304641723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5743408203125</t>
   </si>
   <si>
     <t xml:space="preserve">10.7498483657837</t>
@@ -2027,7 +2027,7 @@
     <t xml:space="preserve">10.6620941162109</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3549575805664</t>
+    <t xml:space="preserve">10.3549566268921</t>
   </si>
   <si>
     <t xml:space="preserve">9.78455543518066</t>
@@ -2042,19 +2042,19 @@
     <t xml:space="preserve">11.2324953079224</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1886186599731</t>
+    <t xml:space="preserve">11.1886177062988</t>
   </si>
   <si>
     <t xml:space="preserve">11.1008634567261</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3553504943848</t>
+    <t xml:space="preserve">11.3553495407104</t>
   </si>
   <si>
     <t xml:space="preserve">11.267596244812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0218868255615</t>
+    <t xml:space="preserve">11.0218858718872</t>
   </si>
   <si>
     <t xml:space="preserve">11.2500457763672</t>
@@ -2063,31 +2063,31 @@
     <t xml:space="preserve">11.3729019165039</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2851476669312</t>
+    <t xml:space="preserve">11.2851467132568</t>
   </si>
   <si>
     <t xml:space="preserve">11.1973934173584</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8467721939087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9871788024902</t>
+    <t xml:space="preserve">11.8467712402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9871778488159</t>
   </si>
   <si>
     <t xml:space="preserve">12.2855415344238</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2504386901855</t>
+    <t xml:space="preserve">12.2504405975342</t>
   </si>
   <si>
     <t xml:space="preserve">12.1626853942871</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4672002792358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0372982025146</t>
+    <t xml:space="preserve">12.4672012329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0372972488403</t>
   </si>
   <si>
     <t xml:space="preserve">12.0910358428955</t>
@@ -2099,10 +2099,10 @@
     <t xml:space="preserve">11.6432199478149</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3924427032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9446268081665</t>
+    <t xml:space="preserve">11.3924417495728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9446277618408</t>
   </si>
   <si>
     <t xml:space="preserve">10.5505475997925</t>
@@ -2111,25 +2111,25 @@
     <t xml:space="preserve">10.6759366989136</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9088010787964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7117605209351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6580238342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9267129898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0521030426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4999189376831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.482006072998</t>
+    <t xml:space="preserve">10.9088020324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7117624282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6580228805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9267139434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0521020889282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4999179840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4820051193237</t>
   </si>
   <si>
     <t xml:space="preserve">11.4282674789429</t>
@@ -2141,34 +2141,34 @@
     <t xml:space="preserve">11.3745288848877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3566179275513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3207921981812</t>
+    <t xml:space="preserve">11.356616973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3207931518555</t>
   </si>
   <si>
     <t xml:space="preserve">11.4461803436279</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4640922546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7148704528809</t>
+    <t xml:space="preserve">11.464093208313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7148694992065</t>
   </si>
   <si>
     <t xml:space="preserve">11.7327833175659</t>
   </si>
   <si>
-    <t xml:space="preserve">11.750696182251</t>
+    <t xml:space="preserve">11.7506952285767</t>
   </si>
   <si>
     <t xml:space="preserve">12.1805992126465</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6284160614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0731220245361</t>
+    <t xml:space="preserve">12.6284151077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0731229782104</t>
   </si>
   <si>
     <t xml:space="preserve">12.3418121337891</t>
@@ -2177,16 +2177,16 @@
     <t xml:space="preserve">12.3597249984741</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6969575881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1268606185913</t>
+    <t xml:space="preserve">11.6969585418701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.126859664917</t>
   </si>
   <si>
     <t xml:space="preserve">12.0552110671997</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8581705093384</t>
+    <t xml:space="preserve">11.8581714630127</t>
   </si>
   <si>
     <t xml:space="preserve">11.9298210144043</t>
@@ -2198,7 +2198,7 @@
     <t xml:space="preserve">12.5925903320312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5030269622803</t>
+    <t xml:space="preserve">12.503026008606</t>
   </si>
   <si>
     <t xml:space="preserve">11.9835596084595</t>
@@ -2210,13 +2210,13 @@
     <t xml:space="preserve">10.9804515838623</t>
   </si>
   <si>
-    <t xml:space="preserve">11.177490234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2849674224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3387050628662</t>
+    <t xml:space="preserve">11.1774892807007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.284966468811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3387041091919</t>
   </si>
   <si>
     <t xml:space="preserve">11.8939962387085</t>
@@ -2225,10 +2225,10 @@
     <t xml:space="preserve">11.7686080932617</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6253051757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0014724731445</t>
+    <t xml:space="preserve">11.6253070831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0014715194702</t>
   </si>
   <si>
     <t xml:space="preserve">12.1089477539062</t>
@@ -2243,7 +2243,7 @@
     <t xml:space="preserve">12.4313764572144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2522506713867</t>
+    <t xml:space="preserve">12.2522497177124</t>
   </si>
   <si>
     <t xml:space="preserve">12.8612785339355</t>
@@ -2252,10 +2252,10 @@
     <t xml:space="preserve">12.8433666229248</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6821527481079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7358913421631</t>
+    <t xml:space="preserve">12.6821517944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7358903884888</t>
   </si>
   <si>
     <t xml:space="preserve">13.3449201583862</t>
@@ -2267,7 +2267,7 @@
     <t xml:space="preserve">14.0972518920898</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3301162719727</t>
+    <t xml:space="preserve">14.330117225647</t>
   </si>
   <si>
     <t xml:space="preserve">14.4734172821045</t>
@@ -2279,13 +2279,13 @@
     <t xml:space="preserve">13.8823003768921</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8643865585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.577784538269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4703102111816</t>
+    <t xml:space="preserve">13.864387512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5777854919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.470308303833</t>
   </si>
   <si>
     <t xml:space="preserve">13.6852607727051</t>
@@ -2294,55 +2294,55 @@
     <t xml:space="preserve">13.6673488616943</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5598726272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6136102676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8285617828369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.953950881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4344844818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7210865020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5240468978882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7031745910645</t>
+    <t xml:space="preserve">13.5598735809326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6136112213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8285608291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9539499282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4344835281372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7210855484009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5240478515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7031736373901</t>
   </si>
   <si>
     <t xml:space="preserve">13.2553577423096</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4523973464966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3090953826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2763776779175</t>
+    <t xml:space="preserve">13.4523963928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3090944290161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2763786315918</t>
   </si>
   <si>
     <t xml:space="preserve">14.4196796417236</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0256013870239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7569103240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.437593460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7124996185303</t>
+    <t xml:space="preserve">14.0256004333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7569122314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4375925064087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7124977111816</t>
   </si>
   <si>
     <t xml:space="preserve">16.336332321167</t>
@@ -2351,31 +2351,31 @@
     <t xml:space="preserve">17.7156066894531</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2498760223389</t>
+    <t xml:space="preserve">17.2498779296875</t>
   </si>
   <si>
     <t xml:space="preserve">19.6591281890869</t>
   </si>
   <si>
-    <t xml:space="preserve">21.316047668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4503917694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5399551391602</t>
+    <t xml:space="preserve">21.3160457611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4503936767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5399570465088</t>
   </si>
   <si>
     <t xml:space="preserve">22.2116813659668</t>
   </si>
   <si>
-    <t xml:space="preserve">21.987771987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2712669372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0177478790283</t>
+    <t xml:space="preserve">21.9877700805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2712650299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.017749786377</t>
   </si>
   <si>
     <t xml:space="preserve">22.3460254669189</t>
@@ -2387,10 +2387,10 @@
     <t xml:space="preserve">23.7342548370361</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8982105255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4355888366699</t>
+    <t xml:space="preserve">21.8982086181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4355869293213</t>
   </si>
   <si>
     <t xml:space="preserve">21.495174407959</t>
@@ -2402,43 +2402,43 @@
     <t xml:space="preserve">21.9429912567139</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7638645172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8534259796143</t>
+    <t xml:space="preserve">21.7638626098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8534278869629</t>
   </si>
   <si>
     <t xml:space="preserve">23.3312187194824</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8086471557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3463916778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3016128540039</t>
+    <t xml:space="preserve">21.8086452484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3463935852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3016109466553</t>
   </si>
   <si>
     <t xml:space="preserve">26.2420253753662</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5255184173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2120475769043</t>
+    <t xml:space="preserve">25.525520324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2120494842529</t>
   </si>
   <si>
     <t xml:space="preserve">25.8837718963623</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4807395935059</t>
+    <t xml:space="preserve">25.4807376861572</t>
   </si>
   <si>
     <t xml:space="preserve">25.5703010559082</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1224822998047</t>
+    <t xml:space="preserve">25.1224842071533</t>
   </si>
   <si>
     <t xml:space="preserve">24.361198425293</t>
@@ -2450,19 +2450,19 @@
     <t xml:space="preserve">25.704647064209</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4211502075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0629005432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4659328460693</t>
+    <t xml:space="preserve">26.4211521148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0628986358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4659309387207</t>
   </si>
   <si>
     <t xml:space="preserve">26.1524620056152</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6602325439453</t>
+    <t xml:space="preserve">28.6602344512939</t>
   </si>
   <si>
     <t xml:space="preserve">27.6750373840332</t>
@@ -2474,28 +2474,28 @@
     <t xml:space="preserve">26.5554962158203</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9881401062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2568321228027</t>
+    <t xml:space="preserve">24.9881381988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2568302154541</t>
   </si>
   <si>
     <t xml:space="preserve">23.9581642150879</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0477256774902</t>
+    <t xml:space="preserve">24.0477275848389</t>
   </si>
   <si>
     <t xml:space="preserve">23.9133834838867</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5851078033447</t>
+    <t xml:space="preserve">24.5851058959961</t>
   </si>
   <si>
     <t xml:space="preserve">22.077335357666</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9281845092773</t>
+    <t xml:space="preserve">22.928186416626</t>
   </si>
   <si>
     <t xml:space="preserve">23.1968765258789</t>
@@ -2504,28 +2504,28 @@
     <t xml:space="preserve">24.182071685791</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2268505096436</t>
+    <t xml:space="preserve">24.2268524169922</t>
   </si>
   <si>
     <t xml:space="preserve">24.4955425262451</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3164138793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3908081054688</t>
+    <t xml:space="preserve">24.3164157867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3908061981201</t>
   </si>
   <si>
     <t xml:space="preserve">23.8238182067871</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0625324249268</t>
+    <t xml:space="preserve">23.0625305175781</t>
   </si>
   <si>
     <t xml:space="preserve">23.7790355682373</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8834037780762</t>
+    <t xml:space="preserve">22.8834056854248</t>
   </si>
   <si>
     <t xml:space="preserve">23.2416591644287</t>
@@ -2534,16 +2534,16 @@
     <t xml:space="preserve">25.1672668457031</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3167819976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6002788543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6150817871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4359569549561</t>
+    <t xml:space="preserve">27.3167839050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6002807617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.615083694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4359550476074</t>
   </si>
   <si>
     <t xml:space="preserve">24.8985767364502</t>
@@ -2558,19 +2558,19 @@
     <t xml:space="preserve">26.197244644165</t>
   </si>
   <si>
-    <t xml:space="preserve">26.868968963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6450576782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4959125518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0480937957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9437255859375</t>
+    <t xml:space="preserve">26.8689670562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6450595855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4959106445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.048095703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9437294006348</t>
   </si>
   <si>
     <t xml:space="preserve">28.8841400146484</t>
@@ -2579,10 +2579,10 @@
     <t xml:space="preserve">28.9289226531982</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7050151824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7797756195068</t>
+    <t xml:space="preserve">28.7050132751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7797718048096</t>
   </si>
   <si>
     <t xml:space="preserve">27.9885082244873</t>
@@ -2591,19 +2591,19 @@
     <t xml:space="preserve">27.630256652832</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2272205352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4063491821289</t>
+    <t xml:space="preserve">27.227222442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4063472747803</t>
   </si>
   <si>
     <t xml:space="preserve">26.6898403167725</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8389911651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7942085266113</t>
+    <t xml:space="preserve">25.8389892578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.79421043396</t>
   </si>
   <si>
     <t xml:space="preserve">26.3315887451172</t>
@@ -2612,7 +2612,7 @@
     <t xml:space="preserve">24.7194499969482</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4507579803467</t>
+    <t xml:space="preserve">24.4507598876953</t>
   </si>
   <si>
     <t xml:space="preserve">23.599910736084</t>
@@ -2621,10 +2621,10 @@
     <t xml:space="preserve">23.4655666351318</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3615646362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0332889556885</t>
+    <t xml:space="preserve">27.3615665435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0332908630371</t>
   </si>
   <si>
     <t xml:space="preserve">27.8541641235352</t>
@@ -2636,16 +2636,16 @@
     <t xml:space="preserve">27.6633834838867</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2979869842529</t>
+    <t xml:space="preserve">30.2979888916016</t>
   </si>
   <si>
     <t xml:space="preserve">26.891170501709</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3454132080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.662052154541</t>
+    <t xml:space="preserve">27.3454113006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6620502471924</t>
   </si>
   <si>
     <t xml:space="preserve">29.480354309082</t>
@@ -2654,19 +2654,19 @@
     <t xml:space="preserve">29.3440799713135</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5251121520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.57053565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0247821807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0702018737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8885059356689</t>
+    <t xml:space="preserve">30.525110244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5705375671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0247764587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0702037811279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8885078430176</t>
   </si>
   <si>
     <t xml:space="preserve">28.9352626800537</t>
@@ -2675,10 +2675,10 @@
     <t xml:space="preserve">27.8905048370361</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9359283447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4362602233887</t>
+    <t xml:space="preserve">27.9359264373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4362621307373</t>
   </si>
   <si>
     <t xml:space="preserve">28.0722007751465</t>
@@ -2699,13 +2699,13 @@
     <t xml:space="preserve">29.1623821258545</t>
   </si>
   <si>
-    <t xml:space="preserve">29.434928894043</t>
+    <t xml:space="preserve">29.4349308013916</t>
   </si>
   <si>
     <t xml:space="preserve">28.2538986206055</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1169605255127</t>
+    <t xml:space="preserve">29.1169567108154</t>
   </si>
   <si>
     <t xml:space="preserve">30.1162948608398</t>
@@ -2714,16 +2714,16 @@
     <t xml:space="preserve">30.9793529510498</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1610488891602</t>
+    <t xml:space="preserve">31.1610507965088</t>
   </si>
   <si>
     <t xml:space="preserve">31.479024887085</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5698719024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7969932556152</t>
+    <t xml:space="preserve">31.5698699951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7969913482666</t>
   </si>
   <si>
     <t xml:space="preserve">31.7515678405762</t>
@@ -2732,13 +2732,13 @@
     <t xml:space="preserve">31.1156272888184</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2505645751953</t>
+    <t xml:space="preserve">33.2505683898926</t>
   </si>
   <si>
     <t xml:space="preserve">34.6587219238281</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8410835266113</t>
+    <t xml:space="preserve">33.8410873413086</t>
   </si>
   <si>
     <t xml:space="preserve">34.4770278930664</t>
@@ -2750,7 +2750,7 @@
     <t xml:space="preserve">34.5678672790527</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6132926940918</t>
+    <t xml:space="preserve">34.6132965087891</t>
   </si>
   <si>
     <t xml:space="preserve">35.340087890625</t>
@@ -2765,28 +2765,28 @@
     <t xml:space="preserve">33.9773559570312</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9312705993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5224494934082</t>
+    <t xml:space="preserve">34.931266784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5224456787109</t>
   </si>
   <si>
     <t xml:space="preserve">34.0682067871094</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7502326965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9319305419922</t>
+    <t xml:space="preserve">33.7502365112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9319267272949</t>
   </si>
   <si>
     <t xml:space="preserve">34.2499008178711</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6139640808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2485733032227</t>
+    <t xml:space="preserve">33.6139602661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2485694885254</t>
   </si>
   <si>
     <t xml:space="preserve">36.6573867797852</t>
@@ -2804,16 +2804,16 @@
     <t xml:space="preserve">38.1109657287598</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4302635192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3868408203125</t>
+    <t xml:space="preserve">36.4302673339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3868370056152</t>
   </si>
   <si>
     <t xml:space="preserve">32.8871765136719</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0688743591309</t>
+    <t xml:space="preserve">33.0688705444336</t>
   </si>
   <si>
     <t xml:space="preserve">33.3414154052734</t>
@@ -2837,46 +2837,46 @@
     <t xml:space="preserve">32.9780197143555</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7976570129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3895034790039</t>
+    <t xml:space="preserve">30.7976589202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3895015716553</t>
   </si>
   <si>
     <t xml:space="preserve">29.5257778167725</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6172904968262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3447456359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0254459381104</t>
+    <t xml:space="preserve">28.6172924041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3447494506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0254421234131</t>
   </si>
   <si>
     <t xml:space="preserve">31.9332637786865</t>
   </si>
   <si>
-    <t xml:space="preserve">32.205810546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1149559020996</t>
+    <t xml:space="preserve">32.2058067321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1149597167969</t>
   </si>
   <si>
     <t xml:space="preserve">32.2512359619141</t>
   </si>
   <si>
-    <t xml:space="preserve">31.615291595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.024112701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1142997741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.614631652832</t>
+    <t xml:space="preserve">31.6152896881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0241088867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1142959594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6146278381348</t>
   </si>
   <si>
     <t xml:space="preserve">31.2064743041992</t>
@@ -2885,13 +2885,13 @@
     <t xml:space="preserve">32.0695381164551</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5244464874268</t>
+    <t xml:space="preserve">31.5244483947754</t>
   </si>
   <si>
     <t xml:space="preserve">31.3427467346191</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3420829772949</t>
+    <t xml:space="preserve">32.3420791625977</t>
   </si>
   <si>
     <t xml:space="preserve">32.5237770080566</t>
@@ -2900,22 +2900,22 @@
     <t xml:space="preserve">32.7054786682129</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1603851318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.159049987793</t>
+    <t xml:space="preserve">32.1603889465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1590538024902</t>
   </si>
   <si>
     <t xml:space="preserve">33.7956581115723</t>
   </si>
   <si>
-    <t xml:space="preserve">34.976692199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9325942993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0234451293945</t>
+    <t xml:space="preserve">34.9766883850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9325981140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0234489440918</t>
   </si>
   <si>
     <t xml:space="preserve">33.5231170654297</t>
@@ -2924,28 +2924,28 @@
     <t xml:space="preserve">32.4783554077148</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4329299926758</t>
+    <t xml:space="preserve">32.432933807373</t>
   </si>
   <si>
     <t xml:space="preserve">31.8424167633057</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8878383636475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4342651367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7074756622314</t>
+    <t xml:space="preserve">31.8878402709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4342613220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7074737548828</t>
   </si>
   <si>
     <t xml:space="preserve">30.70680809021</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4796867370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6166248321533</t>
+    <t xml:space="preserve">30.4796886444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.616626739502</t>
   </si>
   <si>
     <t xml:space="preserve">29.8437442779541</t>
@@ -2954,10 +2954,10 @@
     <t xml:space="preserve">29.2532329559326</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7535629272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0708656311035</t>
+    <t xml:space="preserve">28.7535648345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0708694458008</t>
   </si>
   <si>
     <t xml:space="preserve">28.8898372650146</t>
@@ -2969,16 +2969,16 @@
     <t xml:space="preserve">28.8444137573242</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7081432342529</t>
+    <t xml:space="preserve">28.7081413269043</t>
   </si>
   <si>
     <t xml:space="preserve">28.9806861877441</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7989902496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8891735076904</t>
+    <t xml:space="preserve">28.7989883422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8891754150391</t>
   </si>
   <si>
     <t xml:space="preserve">29.0715351104736</t>
@@ -2993,7 +2993,7 @@
     <t xml:space="preserve">27.6179580688477</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7542304992676</t>
+    <t xml:space="preserve">27.7542324066162</t>
   </si>
   <si>
     <t xml:space="preserve">28.1176242828369</t>
@@ -3014,28 +3014,28 @@
     <t xml:space="preserve">27.1182918548584</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0274410247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9365940093994</t>
+    <t xml:space="preserve">27.0274429321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9365921020508</t>
   </si>
   <si>
     <t xml:space="preserve">26.9820194244385</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3460788726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8918342590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6647148132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2552299499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8457450866699</t>
+    <t xml:space="preserve">26.346076965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8918361663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6647129058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2552280426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8457431793213</t>
   </si>
   <si>
     <t xml:space="preserve">26.6640491485596</t>
@@ -3047,7 +3047,7 @@
     <t xml:space="preserve">26.5732002258301</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3915004730225</t>
+    <t xml:space="preserve">26.3915023803711</t>
   </si>
   <si>
     <t xml:space="preserve">26.70947265625</t>
@@ -3056,19 +3056,19 @@
     <t xml:space="preserve">26.527774810791</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9826831817627</t>
+    <t xml:space="preserve">25.9826850891113</t>
   </si>
   <si>
     <t xml:space="preserve">25.8009872436523</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1657123565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6660442352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8477458953857</t>
+    <t xml:space="preserve">24.165714263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6660461425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8477439880371</t>
   </si>
   <si>
     <t xml:space="preserve">25.437593460083</t>
@@ -3089,7 +3089,7 @@
     <t xml:space="preserve">26.3419418334961</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6671524047852</t>
+    <t xml:space="preserve">26.6671504974365</t>
   </si>
   <si>
     <t xml:space="preserve">27.1317348480225</t>
@@ -3098,7 +3098,7 @@
     <t xml:space="preserve">27.6427764892578</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3396530151367</t>
+    <t xml:space="preserve">28.3396549224854</t>
   </si>
   <si>
     <t xml:space="preserve">27.8286113739014</t>
@@ -3152,7 +3152,7 @@
     <t xml:space="preserve">27.038818359375</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9459018707275</t>
+    <t xml:space="preserve">26.9458999633789</t>
   </si>
   <si>
     <t xml:space="preserve">26.760066986084</t>
@@ -3164,19 +3164,19 @@
     <t xml:space="preserve">26.2025661468506</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5742321014404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.481315612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8994426727295</t>
+    <t xml:space="preserve">26.5742340087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4813175201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8994445800781</t>
   </si>
   <si>
     <t xml:space="preserve">26.2490253448486</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7379837036133</t>
+    <t xml:space="preserve">25.7379817962646</t>
   </si>
   <si>
     <t xml:space="preserve">25.9238147735596</t>
@@ -3191,7 +3191,7 @@
     <t xml:space="preserve">27.271110534668</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2246513366699</t>
+    <t xml:space="preserve">27.2246494293213</t>
   </si>
   <si>
     <t xml:space="preserve">25.4127731323242</t>
@@ -3203,7 +3203,7 @@
     <t xml:space="preserve">24.5300617218018</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9017295837402</t>
+    <t xml:space="preserve">24.9017276763916</t>
   </si>
   <si>
     <t xml:space="preserve">25.0875625610352</t>
@@ -3212,76 +3212,76 @@
     <t xml:space="preserve">24.8088130950928</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5521469116211</t>
+    <t xml:space="preserve">25.5521488189697</t>
   </si>
   <si>
     <t xml:space="preserve">25.5056896209717</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7623538970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7158946990967</t>
+    <t xml:space="preserve">24.7623519897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7158966064453</t>
   </si>
   <si>
     <t xml:space="preserve">25.8308982849121</t>
   </si>
   <si>
-    <t xml:space="preserve">27.085277557373</t>
+    <t xml:space="preserve">27.0852756500244</t>
   </si>
   <si>
     <t xml:space="preserve">26.7136077880859</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0167331695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8773574829102</t>
+    <t xml:space="preserve">26.016731262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8773555755615</t>
   </si>
   <si>
     <t xml:space="preserve">25.7844390869141</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0631885528564</t>
+    <t xml:space="preserve">26.0631904602051</t>
   </si>
   <si>
     <t xml:space="preserve">26.1096496582031</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1340198516846</t>
+    <t xml:space="preserve">25.1340217590332</t>
   </si>
   <si>
     <t xml:space="preserve">25.0411052703857</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2977676391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4836044311523</t>
+    <t xml:space="preserve">24.2977695465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4836025238037</t>
   </si>
   <si>
     <t xml:space="preserve">24.0654773712158</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2513122558594</t>
+    <t xml:space="preserve">24.2513103485107</t>
   </si>
   <si>
     <t xml:space="preserve">24.5765209197998</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6008911132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0433921813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0898494720459</t>
+    <t xml:space="preserve">23.6008930206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0433902740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0898513793945</t>
   </si>
   <si>
     <t xml:space="preserve">22.114221572876</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0213050842285</t>
+    <t xml:space="preserve">22.0213069915771</t>
   </si>
   <si>
     <t xml:space="preserve">23.2756824493408</t>
@@ -3290,28 +3290,28 @@
     <t xml:space="preserve">23.4615173339844</t>
   </si>
   <si>
-    <t xml:space="preserve">23.415060043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1363086700439</t>
+    <t xml:space="preserve">23.4150581359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1363067626953</t>
   </si>
   <si>
     <t xml:space="preserve">23.6473522186279</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9504737854004</t>
+    <t xml:space="preserve">22.950475692749</t>
   </si>
   <si>
     <t xml:space="preserve">22.5788059234619</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2071399688721</t>
+    <t xml:space="preserve">22.2071380615234</t>
   </si>
   <si>
     <t xml:space="preserve">21.64963722229</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8598461151123</t>
+    <t xml:space="preserve">20.8598442077637</t>
   </si>
   <si>
     <t xml:space="preserve">21.0921363830566</t>
@@ -3326,7 +3326,7 @@
     <t xml:space="preserve">21.5567207336426</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7425537109375</t>
+    <t xml:space="preserve">21.7425556182861</t>
   </si>
   <si>
     <t xml:space="preserve">21.9283885955811</t>
@@ -3347,37 +3347,37 @@
     <t xml:space="preserve">21.4173450469971</t>
   </si>
   <si>
-    <t xml:space="preserve">21.603178024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.835470199585</t>
+    <t xml:space="preserve">21.6031799316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8354721069336</t>
   </si>
   <si>
     <t xml:space="preserve">22.160680770874</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7181835174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3000564575195</t>
+    <t xml:space="preserve">22.7181816101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3000545501709</t>
   </si>
   <si>
     <t xml:space="preserve">22.3465137481689</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2535972595215</t>
+    <t xml:space="preserve">22.2535991668701</t>
   </si>
   <si>
     <t xml:space="preserve">21.881929397583</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7890148162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1827659606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5986061096191</t>
+    <t xml:space="preserve">21.7890129089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.182767868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5986042022705</t>
   </si>
   <si>
     <t xml:space="preserve">25.3663120269775</t>
@@ -3398,10 +3398,10 @@
     <t xml:space="preserve">24.4371433258057</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8796424865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2048511505127</t>
+    <t xml:space="preserve">23.8796443939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2048530578613</t>
   </si>
   <si>
     <t xml:space="preserve">23.9261016845703</t>
@@ -3410,7 +3410,7 @@
     <t xml:space="preserve">24.6694355010986</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5544357299805</t>
+    <t xml:space="preserve">23.5544338226318</t>
   </si>
   <si>
     <t xml:space="preserve">23.6938095092773</t>
@@ -3419,7 +3419,7 @@
     <t xml:space="preserve">23.3221416473389</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7867259979248</t>
+    <t xml:space="preserve">23.7867279052734</t>
   </si>
   <si>
     <t xml:space="preserve">22.8575572967529</t>
@@ -3428,7 +3428,7 @@
     <t xml:space="preserve">21.5102615356445</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3708877563477</t>
+    <t xml:space="preserve">21.370885848999</t>
   </si>
   <si>
     <t xml:space="preserve">21.1850528717041</t>
@@ -3437,19 +3437,19 @@
     <t xml:space="preserve">20.7204685211182</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4881744384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9771327972412</t>
+    <t xml:space="preserve">20.4881763458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9771347045898</t>
   </si>
   <si>
     <t xml:space="preserve">20.2558822631836</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5346355438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9306774139404</t>
+    <t xml:space="preserve">20.5346336364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9306755065918</t>
   </si>
   <si>
     <t xml:space="preserve">20.5810928344727</t>
@@ -3461,7 +3461,7 @@
     <t xml:space="preserve">20.6275520324707</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0235919952393</t>
+    <t xml:space="preserve">20.0235900878906</t>
   </si>
   <si>
     <t xml:space="preserve">18.6298370361328</t>
@@ -3479,7 +3479,7 @@
     <t xml:space="preserve">17.8772106170654</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5427112579346</t>
+    <t xml:space="preserve">17.5427093505859</t>
   </si>
   <si>
     <t xml:space="preserve">17.2453765869141</t>
@@ -3491,10 +3491,10 @@
     <t xml:space="preserve">17.5612926483154</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4126262664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7471294403076</t>
+    <t xml:space="preserve">17.4126281738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.747127532959</t>
   </si>
   <si>
     <t xml:space="preserve">17.1896266937256</t>
@@ -3515,13 +3515,13 @@
     <t xml:space="preserve">16.3162078857422</t>
   </si>
   <si>
-    <t xml:space="preserve">15.981707572937</t>
+    <t xml:space="preserve">15.9817085266113</t>
   </si>
   <si>
     <t xml:space="preserve">16.5392074584961</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2976264953613</t>
+    <t xml:space="preserve">16.2976245880127</t>
   </si>
   <si>
     <t xml:space="preserve">16.1861248016357</t>
@@ -3533,7 +3533,7 @@
     <t xml:space="preserve">16.1489562988281</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2418727874756</t>
+    <t xml:space="preserve">16.2418746948242</t>
   </si>
   <si>
     <t xml:space="preserve">16.0746231079102</t>
@@ -4305,6 +4305,9 @@
   </si>
   <si>
     <t xml:space="preserve">18.7800006866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1399993896484</t>
   </si>
 </sst>
 </file>
@@ -69955,7 +69958,7 @@
     </row>
     <row r="2513">
       <c r="A2513" s="1" t="n">
-        <v>45978.69125</v>
+        <v>45978.3333333333</v>
       </c>
       <c r="B2513" t="n">
         <v>11460</v>
@@ -69976,6 +69979,32 @@
         <v>1430</v>
       </c>
       <c r="H2513" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2514">
+      <c r="A2514" s="1" t="n">
+        <v>45979.6909722222</v>
+      </c>
+      <c r="B2514" t="n">
+        <v>18241</v>
+      </c>
+      <c r="C2514" t="n">
+        <v>18.8999996185303</v>
+      </c>
+      <c r="D2514" t="n">
+        <v>18.0200004577637</v>
+      </c>
+      <c r="E2514" t="n">
+        <v>18.8999996185303</v>
+      </c>
+      <c r="F2514" t="n">
+        <v>18.1399993896484</v>
+      </c>
+      <c r="G2514" t="s">
+        <v>1431</v>
+      </c>
+      <c r="H2514" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ARN.MI.xlsx
+++ b/data/ARN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1433" uniqueCount="1433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1434" uniqueCount="1434">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,37 +38,37 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92215001583099</t>
+    <t xml:space="preserve">1.92215013504028</t>
   </si>
   <si>
     <t xml:space="preserve">ARN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94450104236603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.917360663414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90778195858002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8838347196579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93172895908356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91576397418976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83434426784515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83594059944153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91097486019135</t>
+    <t xml:space="preserve">1.94450056552887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91736030578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90778231620789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88383483886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93172883987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91576433181763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83434450626373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83594083786011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91097474098206</t>
   </si>
   <si>
     <t xml:space="preserve">1.807204246521</t>
@@ -80,166 +80,166 @@
     <t xml:space="preserve">1.71620559692383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80401134490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81039726734161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79602909088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77208185195923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70662677288055</t>
+    <t xml:space="preserve">1.80401122570038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81039714813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79602885246277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77208197116852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70662665367126</t>
   </si>
   <si>
     <t xml:space="preserve">1.6970477104187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69066190719604</t>
+    <t xml:space="preserve">1.69066214561462</t>
   </si>
   <si>
     <t xml:space="preserve">1.67629361152649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70024073123932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69864416122437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67469727993011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66671502590179</t>
+    <t xml:space="preserve">1.7002409696579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69864428043365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6746973991394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6667149066925</t>
   </si>
   <si>
     <t xml:space="preserve">1.66032898426056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81518650054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82795834541321</t>
+    <t xml:space="preserve">1.81518638134003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82795822620392</t>
   </si>
   <si>
     <t xml:space="preserve">1.86148416996002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88543128967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89181685447693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92853581905365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95407938957214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90618503093719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86786997318268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88064193725586</t>
+    <t xml:space="preserve">1.88543117046356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89181673526764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92853605747223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95407962799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90618586540222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86786985397339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88064205646515</t>
   </si>
   <si>
     <t xml:space="preserve">1.85190546512604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85988771915436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85509848594666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79283607006073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78804647922516</t>
+    <t xml:space="preserve">1.85988783836365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85509812831879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79283618927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78804636001587</t>
   </si>
   <si>
     <t xml:space="preserve">1.78006434440613</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7561172246933</t>
+    <t xml:space="preserve">1.75611746311188</t>
   </si>
   <si>
     <t xml:space="preserve">1.76888906955719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7640997171402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78485381603241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77048528194427</t>
+    <t xml:space="preserve">1.76409983634949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78485369682312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77048552036285</t>
   </si>
   <si>
     <t xml:space="preserve">1.72099483013153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73536336421967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80241513252258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76250326633453</t>
+    <t xml:space="preserve">1.73536312580109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80241465568542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76250314712524</t>
   </si>
   <si>
     <t xml:space="preserve">1.74494218826294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73217034339905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73695993423462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7433454990387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7513279914856</t>
+    <t xml:space="preserve">1.73217022418976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73695969581604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74334537982941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75132775306702</t>
   </si>
   <si>
     <t xml:space="preserve">1.68587255477905</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67789030075073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65234661102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62041735649109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64276802539825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59008467197418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60285592079163</t>
+    <t xml:space="preserve">1.67789006233215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65234649181366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62041711807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64276778697968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59008419513702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60285604000092</t>
   </si>
   <si>
     <t xml:space="preserve">1.54937434196472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51185739040375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45598089694977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43682312965393</t>
+    <t xml:space="preserve">1.51185750961304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45598077774048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43682324886322</t>
   </si>
   <si>
     <t xml:space="preserve">1.4695508480072</t>
@@ -251,13 +251,13 @@
     <t xml:space="preserve">1.47673499584198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47274386882782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46875250339508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49669075012207</t>
+    <t xml:space="preserve">1.47274398803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46875274181366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49669086933136</t>
   </si>
   <si>
     <t xml:space="preserve">1.47593677043915</t>
@@ -266,22 +266,22 @@
     <t xml:space="preserve">1.50626957416534</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47753310203552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43841958045959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40090262889862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3490172624588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30910551548004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34342956542969</t>
+    <t xml:space="preserve">1.47753322124481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43841969966888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40090274810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34901738166809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30910563468933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34342968463898</t>
   </si>
   <si>
     <t xml:space="preserve">1.32666671276093</t>
@@ -293,31 +293,31 @@
     <t xml:space="preserve">1.31708788871765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38653445243835</t>
+    <t xml:space="preserve">1.38653421401978</t>
   </si>
   <si>
     <t xml:space="preserve">1.39691138267517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40649032592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30671095848083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32347357273102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.305912733078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31229853630066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28994798660278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28515839576721</t>
+    <t xml:space="preserve">1.40649020671844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30671083927155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32347393035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30591261386871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31229841709137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28994786739349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28515863418579</t>
   </si>
   <si>
     <t xml:space="preserve">1.28595662117004</t>
@@ -326,40 +326,40 @@
     <t xml:space="preserve">1.33305263519287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33704388141632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30112302303314</t>
+    <t xml:space="preserve">1.33704376220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30112326145172</t>
   </si>
   <si>
     <t xml:space="preserve">1.36104869842529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3462723493576</t>
+    <t xml:space="preserve">1.34627258777618</t>
   </si>
   <si>
     <t xml:space="preserve">1.35283982753754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33806347846985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27157068252563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28880989551544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29291439056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30686974525452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33888471126556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34955620765686</t>
+    <t xml:space="preserve">1.33806383609772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2715710401535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28880977630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29291450977325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30686962604523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33888459205627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34955632686615</t>
   </si>
   <si>
     <t xml:space="preserve">1.34381008148193</t>
@@ -368,61 +368,61 @@
     <t xml:space="preserve">1.33642172813416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34709358215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30522799491882</t>
+    <t xml:space="preserve">1.34709346294403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30522775650024</t>
   </si>
   <si>
     <t xml:space="preserve">1.2912722826004</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31425750255585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32164561748505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26828730106354</t>
+    <t xml:space="preserve">1.31425762176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32164573669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26828742027283</t>
   </si>
   <si>
     <t xml:space="preserve">1.27239191532135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28798878192902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29701888561249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24858570098877</t>
+    <t xml:space="preserve">1.28798890113831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29701864719391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24858582019806</t>
   </si>
   <si>
     <t xml:space="preserve">1.32657110691071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33231747150421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35940706729889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42015326023102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48664617538452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53343737125397</t>
+    <t xml:space="preserve">1.33231735229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3594069480896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42015337944031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48664629459381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53343749046326</t>
   </si>
   <si>
     <t xml:space="preserve">1.51619851589203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51866114139557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43739235401154</t>
+    <t xml:space="preserve">1.51866126060486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43739247322083</t>
   </si>
   <si>
     <t xml:space="preserve">1.46776556968689</t>
@@ -431,7 +431,7 @@
     <t xml:space="preserve">1.43000423908234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40948176383972</t>
+    <t xml:space="preserve">1.4094820022583</t>
   </si>
   <si>
     <t xml:space="preserve">1.44478034973145</t>
@@ -443,37 +443,37 @@
     <t xml:space="preserve">1.61798977851868</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70582616329193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74851262569427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72388541698456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68284094333649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67463195323944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.651646733284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64179599285126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67134809494019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66478109359741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65657186508179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69597518444061</t>
+    <t xml:space="preserve">1.70582592487335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74851274490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72388565540314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68284058570862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67463171482086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65164685249329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64179587364197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67134821414948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6647812128067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65657210350037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69597506523132</t>
   </si>
   <si>
     <t xml:space="preserve">1.69433331489563</t>
@@ -482,28 +482,28 @@
     <t xml:space="preserve">1.65821385383606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68119919300079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68776619434357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66806471347809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6500049829483</t>
+    <t xml:space="preserve">1.6811990737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68776631355286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6680645942688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65000486373901</t>
   </si>
   <si>
     <t xml:space="preserve">1.66313922405243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67791545391083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03746891021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04403591156006</t>
+    <t xml:space="preserve">1.67791533470154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03746867179871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04403614997864</t>
   </si>
   <si>
     <t xml:space="preserve">2.0391104221344</t>
@@ -518,67 +518,67 @@
     <t xml:space="preserve">2.04731941223145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04239392280579</t>
+    <t xml:space="preserve">2.04239416122437</t>
   </si>
   <si>
     <t xml:space="preserve">2.19836473464966</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24105167388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18851399421692</t>
+    <t xml:space="preserve">2.241051197052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18851375579834</t>
   </si>
   <si>
     <t xml:space="preserve">2.17537975311279</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14582777023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00627470016479</t>
+    <t xml:space="preserve">2.14582753181458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00627446174622</t>
   </si>
   <si>
     <t xml:space="preserve">1.98821485042572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99313998222351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99806606769562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99642372131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99970746040344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00299096107483</t>
+    <t xml:space="preserve">1.99313986301422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99806547164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99642395973206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99970710277557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00299119949341</t>
   </si>
   <si>
     <t xml:space="preserve">2.00791621208191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01120018959045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02597570419312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03254294395447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02105093002319</t>
+    <t xml:space="preserve">2.0111997127533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02597594261169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03254389762878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02105069160461</t>
   </si>
   <si>
     <t xml:space="preserve">2.01940894126892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02433443069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07687163352966</t>
+    <t xml:space="preserve">2.02433466911316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07687187194824</t>
   </si>
   <si>
     <t xml:space="preserve">2.05881214141846</t>
@@ -587,70 +587,70 @@
     <t xml:space="preserve">2.09657335281372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14746904373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33955907821655</t>
+    <t xml:space="preserve">2.14746880531311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33955883979797</t>
   </si>
   <si>
     <t xml:space="preserve">2.27552914619446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32478332519531</t>
+    <t xml:space="preserve">2.32478308677673</t>
   </si>
   <si>
     <t xml:space="preserve">2.27881264686584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25746965408325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29851365089417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26075315475464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28045463562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30672311782837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35597681999207</t>
+    <t xml:space="preserve">2.25746941566467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29851412773132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26075291633606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28045439720154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30672335624695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35597705841064</t>
   </si>
   <si>
     <t xml:space="preserve">2.34120106697083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3428430557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3477680683136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44627594947815</t>
+    <t xml:space="preserve">2.34284281730652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34776782989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44627618789673</t>
   </si>
   <si>
     <t xml:space="preserve">2.39209651947021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3822455406189</t>
+    <t xml:space="preserve">2.38224577903748</t>
   </si>
   <si>
     <t xml:space="preserve">2.38717126846313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38388776779175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40523099899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38060402870178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42164897918701</t>
+    <t xml:space="preserve">2.38388752937317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40523076057434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38060450553894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42164874076843</t>
   </si>
   <si>
     <t xml:space="preserve">2.33791732788086</t>
@@ -659,22 +659,22 @@
     <t xml:space="preserve">2.32314109802246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35433530807495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40687274932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4380669593811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41836524009705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2903048992157</t>
+    <t xml:space="preserve">2.35433506965637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41015601158142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40687298774719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43806672096252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41836547851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29030537605286</t>
   </si>
   <si>
     <t xml:space="preserve">2.34940981864929</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">2.37567853927612</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40194749832153</t>
+    <t xml:space="preserve">2.40194725990295</t>
   </si>
   <si>
     <t xml:space="preserve">2.35761880874634</t>
@@ -701,13 +701,13 @@
     <t xml:space="preserve">2.37239527702332</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36254405975342</t>
+    <t xml:space="preserve">2.362544298172</t>
   </si>
   <si>
     <t xml:space="preserve">2.36582779884338</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39537978172302</t>
+    <t xml:space="preserve">2.39538025856018</t>
   </si>
   <si>
     <t xml:space="preserve">2.37732005119324</t>
@@ -722,13 +722,13 @@
     <t xml:space="preserve">2.39373850822449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39045524597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41344022750854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40358924865723</t>
+    <t xml:space="preserve">2.3904550075531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41343998908997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40358877182007</t>
   </si>
   <si>
     <t xml:space="preserve">2.40030574798584</t>
@@ -743,22 +743,22 @@
     <t xml:space="preserve">2.43149924278259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42000722885132</t>
+    <t xml:space="preserve">2.42000699043274</t>
   </si>
   <si>
     <t xml:space="preserve">2.35105180740356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33627557754517</t>
+    <t xml:space="preserve">2.33627533912659</t>
   </si>
   <si>
     <t xml:space="preserve">2.34612631797791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43642520904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42657423019409</t>
+    <t xml:space="preserve">2.43642497062683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42657446861267</t>
   </si>
   <si>
     <t xml:space="preserve">2.42985796928406</t>
@@ -767,31 +767,31 @@
     <t xml:space="preserve">2.4528431892395</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47701287269592</t>
+    <t xml:space="preserve">2.47701263427734</t>
   </si>
   <si>
     <t xml:space="preserve">2.478679895401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49201512336731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49368190765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.475346326828</t>
+    <t xml:space="preserve">2.49201536178589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49368214607239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47534608840942</t>
   </si>
   <si>
     <t xml:space="preserve">2.46534466743469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.482013463974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46867847442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4586775302887</t>
+    <t xml:space="preserve">2.48201394081116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46867823600769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45867705345154</t>
   </si>
   <si>
     <t xml:space="preserve">2.46201086044312</t>
@@ -800,25 +800,25 @@
     <t xml:space="preserve">2.45534348487854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41700482368469</t>
+    <t xml:space="preserve">2.41700530052185</t>
   </si>
   <si>
     <t xml:space="preserve">2.40867042541504</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36699724197388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34199380874634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36866450309753</t>
+    <t xml:space="preserve">2.36699748039246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3419942855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36866474151611</t>
   </si>
   <si>
     <t xml:space="preserve">2.35366249084473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38533329963684</t>
+    <t xml:space="preserve">2.38533353805542</t>
   </si>
   <si>
     <t xml:space="preserve">2.38366651535034</t>
@@ -827,28 +827,28 @@
     <t xml:space="preserve">2.36366391181946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32532501220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31699085235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28531956672668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28698635101318</t>
+    <t xml:space="preserve">2.32532525062561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31699061393738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28532004356384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28698658943176</t>
   </si>
   <si>
     <t xml:space="preserve">2.29698801040649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3153235912323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28365254402161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28865361213684</t>
+    <t xml:space="preserve">2.31532382965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28365302085876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28865337371826</t>
   </si>
   <si>
     <t xml:space="preserve">2.29032039642334</t>
@@ -857,40 +857,40 @@
     <t xml:space="preserve">2.30198860168457</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30365514755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2936544418335</t>
+    <t xml:space="preserve">2.30365562438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29365396499634</t>
   </si>
   <si>
     <t xml:space="preserve">2.24198031425476</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2669837474823</t>
+    <t xml:space="preserve">2.26698350906372</t>
   </si>
   <si>
     <t xml:space="preserve">2.2686505317688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32699251174927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31865763664246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31032299995422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24364709854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25031471252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22531127929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25198149681091</t>
+    <t xml:space="preserve">2.32699227333069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31865787506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3103232383728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24364733695984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25031495094299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2253110408783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25198173522949</t>
   </si>
   <si>
     <t xml:space="preserve">2.22197723388672</t>
@@ -905,73 +905,73 @@
     <t xml:space="preserve">2.16863656044006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17863798141479</t>
+    <t xml:space="preserve">2.17863845825195</t>
   </si>
   <si>
     <t xml:space="preserve">2.16696953773499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18697285652161</t>
+    <t xml:space="preserve">2.18697261810303</t>
   </si>
   <si>
     <t xml:space="preserve">2.19697403907776</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18363833427429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18530583381653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19197344779968</t>
+    <t xml:space="preserve">2.18363857269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18530607223511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1919732093811</t>
   </si>
   <si>
     <t xml:space="preserve">2.17530393600464</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14196610450745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15363454818726</t>
+    <t xml:space="preserve">2.14196634292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15363430976868</t>
   </si>
   <si>
     <t xml:space="preserve">2.1436333656311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13529872894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12696409225464</t>
+    <t xml:space="preserve">2.13529849052429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12696385383606</t>
   </si>
   <si>
     <t xml:space="preserve">2.12863111495972</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12029671669006</t>
+    <t xml:space="preserve">2.12029647827148</t>
   </si>
   <si>
     <t xml:space="preserve">2.13029837608337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11862969398499</t>
+    <t xml:space="preserve">2.11862993240356</t>
   </si>
   <si>
     <t xml:space="preserve">2.37366533279419</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37533235549927</t>
+    <t xml:space="preserve">2.37533187866211</t>
   </si>
   <si>
     <t xml:space="preserve">2.40700340270996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39533495903015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39200091362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49868273735046</t>
+    <t xml:space="preserve">2.39533519744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39200115203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49868297576904</t>
   </si>
   <si>
     <t xml:space="preserve">2.49534916877747</t>
@@ -980,16 +980,16 @@
     <t xml:space="preserve">2.50868439674377</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51201796531677</t>
+    <t xml:space="preserve">2.51201748847961</t>
   </si>
   <si>
     <t xml:space="preserve">2.51535153388977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51701855659485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52368640899658</t>
+    <t xml:space="preserve">2.51701879501343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.523686170578</t>
   </si>
   <si>
     <t xml:space="preserve">2.5253529548645</t>
@@ -1001,7 +1001,7 @@
     <t xml:space="preserve">2.53368759155273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53202080726624</t>
+    <t xml:space="preserve">2.53202056884766</t>
   </si>
   <si>
     <t xml:space="preserve">2.54035520553589</t>
@@ -1010,7 +1010,7 @@
     <t xml:space="preserve">2.52702021598816</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53868865966797</t>
+    <t xml:space="preserve">2.53868842124939</t>
   </si>
   <si>
     <t xml:space="preserve">2.53702163696289</t>
@@ -1025,79 +1025,79 @@
     <t xml:space="preserve">2.50034976005554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50535035133362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48368048667908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45200943946838</t>
+    <t xml:space="preserve">2.50535011291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48368096351624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45200967788696</t>
   </si>
   <si>
     <t xml:space="preserve">2.51368474960327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54202222824097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54868960380554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51035118103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52035212516785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47201228141785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50201630592346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48701429367065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0004198551178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81706094741821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75038433074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71704626083374</t>
+    <t xml:space="preserve">2.54202198982239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5486900806427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51035141944885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52035236358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.472012758255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5020170211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48701453208923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00041961669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81706047058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75038480758667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71704697608948</t>
   </si>
   <si>
     <t xml:space="preserve">2.8087260723114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80039143562317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83372950553894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78372287750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84206414222717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75871920585632</t>
+    <t xml:space="preserve">2.80039167404175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8337299823761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78372240066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84206438064575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7587194442749</t>
   </si>
   <si>
     <t xml:space="preserve">2.85039877891541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85873341560364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89207148551941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82539510726929</t>
+    <t xml:space="preserve">2.85873317718506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89207124710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82539534568787</t>
   </si>
   <si>
     <t xml:space="preserve">2.72538113594055</t>
@@ -1109,46 +1109,46 @@
     <t xml:space="preserve">2.6420361995697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70037794113159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65870547294617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62536716461182</t>
+    <t xml:space="preserve">2.70037746429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65870499610901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62536764144897</t>
   </si>
   <si>
     <t xml:space="preserve">2.63370156288147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59202909469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66703963279724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70871210098267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74205017089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65037059783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68370842933655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60036373138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58369445800781</t>
+    <t xml:space="preserve">2.59202885627747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66703987121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70871233940125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74204993247986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65037083625793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68370866775513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6003634929657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58369493484497</t>
   </si>
   <si>
     <t xml:space="preserve">2.56702566146851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7670533657074</t>
+    <t xml:space="preserve">2.76705384254456</t>
   </si>
   <si>
     <t xml:space="preserve">2.73371553421021</t>
@@ -1163,25 +1163,25 @@
     <t xml:space="preserve">2.87540221214294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88373684883118</t>
+    <t xml:space="preserve">2.8837366104126</t>
   </si>
   <si>
     <t xml:space="preserve">2.77538800239563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78091382980347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72174525260925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73019814491272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77246117591858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64567184448242</t>
+    <t xml:space="preserve">2.78091406822205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72174549102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73019790649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7724609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.645672082901</t>
   </si>
   <si>
     <t xml:space="preserve">2.70484042167664</t>
@@ -1190,22 +1190,22 @@
     <t xml:space="preserve">2.68793511390686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6625771522522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69638800621033</t>
+    <t xml:space="preserve">2.66257691383362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69638776779175</t>
   </si>
   <si>
     <t xml:space="preserve">2.65412449836731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60340881347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63721919059753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61186122894287</t>
+    <t xml:space="preserve">2.60340857505798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63721895217896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61186099052429</t>
   </si>
   <si>
     <t xml:space="preserve">2.5780508518219</t>
@@ -1220,16 +1220,16 @@
     <t xml:space="preserve">2.49352478981018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54424071311951</t>
+    <t xml:space="preserve">2.54423999786377</t>
   </si>
   <si>
     <t xml:space="preserve">2.56114554405212</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58650350570679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51888251304626</t>
+    <t xml:space="preserve">2.58650326728821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51888275146484</t>
   </si>
   <si>
     <t xml:space="preserve">2.53578782081604</t>
@@ -1241,19 +1241,19 @@
     <t xml:space="preserve">2.51042985916138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56959819793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46816658973694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48507189750671</t>
+    <t xml:space="preserve">2.56959795951843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46816682815552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48507213592529</t>
   </si>
   <si>
     <t xml:space="preserve">2.41745090484619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45126152038574</t>
+    <t xml:space="preserve">2.45126175880432</t>
   </si>
   <si>
     <t xml:space="preserve">2.39209318161011</t>
@@ -1262,7 +1262,7 @@
     <t xml:space="preserve">2.3836407661438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27375650405884</t>
+    <t xml:space="preserve">2.27375626564026</t>
   </si>
   <si>
     <t xml:space="preserve">2.29911422729492</t>
@@ -1277,34 +1277,34 @@
     <t xml:space="preserve">2.43435621261597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4259033203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34982991218567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28220891952515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32447195053101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40899848937988</t>
+    <t xml:space="preserve">2.42590355873108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34983015060425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28220868110657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32447242736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4089982509613</t>
   </si>
   <si>
     <t xml:space="preserve">2.45971417427063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44280910491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33292460441589</t>
+    <t xml:space="preserve">2.44280886650085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33292508125305</t>
   </si>
   <si>
     <t xml:space="preserve">2.34137725830078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40054535865784</t>
+    <t xml:space="preserve">2.40054559707642</t>
   </si>
   <si>
     <t xml:space="preserve">2.37518763542175</t>
@@ -1313,16 +1313,16 @@
     <t xml:space="preserve">2.47661924362183</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30756664276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23994588851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29430222511292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2343761920929</t>
+    <t xml:space="preserve">2.30756688117981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23994565010071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29430246353149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23437666893005</t>
   </si>
   <si>
     <t xml:space="preserve">2.2429370880127</t>
@@ -1334,10 +1334,10 @@
     <t xml:space="preserve">2.25149822235107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27718067169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26862001419067</t>
+    <t xml:space="preserve">2.27718091011047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26861977577209</t>
   </si>
   <si>
     <t xml:space="preserve">2.44839715957642</t>
@@ -1346,28 +1346,28 @@
     <t xml:space="preserve">2.37134981155396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31142377853394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28574156761169</t>
+    <t xml:space="preserve">2.31142401695251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28574109077454</t>
   </si>
   <si>
     <t xml:space="preserve">2.26005911827087</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35422801971436</t>
+    <t xml:space="preserve">2.35422825813293</t>
   </si>
   <si>
     <t xml:space="preserve">2.22581553459167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20869374275208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30286335945129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31998467445374</t>
+    <t xml:space="preserve">2.20869398117065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30286312103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31998491287231</t>
   </si>
   <si>
     <t xml:space="preserve">2.37991070747375</t>
@@ -1376,22 +1376,22 @@
     <t xml:space="preserve">2.405592918396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3970320224762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32854580879211</t>
+    <t xml:space="preserve">2.39703226089478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32854557037354</t>
   </si>
   <si>
     <t xml:space="preserve">2.38847136497498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36278891563416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34566712379456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20013308525085</t>
+    <t xml:space="preserve">2.36278915405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34566736221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20013284683228</t>
   </si>
   <si>
     <t xml:space="preserve">2.18301153182983</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">2.4398365020752</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54256653785706</t>
+    <t xml:space="preserve">2.54256629943848</t>
   </si>
   <si>
     <t xml:space="preserve">2.60249209403992</t>
@@ -1409,22 +1409,22 @@
     <t xml:space="preserve">2.69666147232056</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7737090587616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63673543930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67097878456116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61961388587952</t>
+    <t xml:space="preserve">2.77370882034302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63673520088196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67097854614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61961364746094</t>
   </si>
   <si>
     <t xml:space="preserve">2.65385699272156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68810057640076</t>
+    <t xml:space="preserve">2.68810033798218</t>
   </si>
   <si>
     <t xml:space="preserve">2.64529609680176</t>
@@ -1436,67 +1436,67 @@
     <t xml:space="preserve">2.72234392166138</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07333755493164</t>
+    <t xml:space="preserve">3.07333779335022</t>
   </si>
   <si>
     <t xml:space="preserve">3.52706170082092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59554839134216</t>
+    <t xml:space="preserve">3.59554815292358</t>
   </si>
   <si>
     <t xml:space="preserve">3.65547394752502</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58698749542236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6126697063446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5356228351593</t>
+    <t xml:space="preserve">3.58698773384094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61266994476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53562259674072</t>
   </si>
   <si>
     <t xml:space="preserve">3.42433190345764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54418325424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56986570358276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55274438858032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56130480766296</t>
+    <t xml:space="preserve">3.54418349266052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56986618041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5527446269989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56130456924438</t>
   </si>
   <si>
     <t xml:space="preserve">3.5099401473999</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48425769805908</t>
+    <t xml:space="preserve">3.48425793647766</t>
   </si>
   <si>
     <t xml:space="preserve">3.57842659950256</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63835310935974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74108266830444</t>
+    <t xml:space="preserve">3.63835287094116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74108242988586</t>
   </si>
   <si>
     <t xml:space="preserve">4.16912364959717</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60572671890259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15361976623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62284755706787</t>
+    <t xml:space="preserve">4.60572624206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15361928939819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62284803390503</t>
   </si>
   <si>
     <t xml:space="preserve">4.19480657577515</t>
@@ -1505,13 +1505,13 @@
     <t xml:space="preserve">4.45163106918335</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53724002838135</t>
+    <t xml:space="preserve">4.53723955154419</t>
   </si>
   <si>
     <t xml:space="preserve">4.52011823654175</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58860445022583</t>
+    <t xml:space="preserve">4.58860492706299</t>
   </si>
   <si>
     <t xml:space="preserve">4.34890127182007</t>
@@ -1520,55 +1520,55 @@
     <t xml:space="preserve">4.16056346893311</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23760986328125</t>
+    <t xml:space="preserve">4.23761034011841</t>
   </si>
   <si>
     <t xml:space="preserve">4.29753684997559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89517760276794</t>
+    <t xml:space="preserve">3.89517784118652</t>
   </si>
   <si>
     <t xml:space="preserve">3.27879762649536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25311541557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89356064796448</t>
+    <t xml:space="preserve">3.25311517715454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89356017112732</t>
   </si>
   <si>
     <t xml:space="preserve">3.15894627571106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16750693321228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03909468650818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44145369529724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38152766227722</t>
+    <t xml:space="preserve">3.16750717163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0390944480896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44145345687866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38152742385864</t>
   </si>
   <si>
     <t xml:space="preserve">3.39008855819702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84381222724915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83525085449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8780562877655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76676440238953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88661694526672</t>
+    <t xml:space="preserve">3.84381246566772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83525133132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87805581092834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76676487922668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88661646842957</t>
   </si>
   <si>
     <t xml:space="preserve">3.85237336158752</t>
@@ -1577,16 +1577,16 @@
     <t xml:space="preserve">3.92942047119141</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95510292053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93798160552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11775922775269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25473260879517</t>
+    <t xml:space="preserve">3.95510339736938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93798184394836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11775875091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25473213195801</t>
   </si>
   <si>
     <t xml:space="preserve">4.22904968261719</t>
@@ -1598,13 +1598,13 @@
     <t xml:space="preserve">4.28041458129883</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43451023101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20336675643921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00646781921387</t>
+    <t xml:space="preserve">4.43450927734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20336627960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00646829605103</t>
   </si>
   <si>
     <t xml:space="preserve">4.10919857025146</t>
@@ -1616,16 +1616,16 @@
     <t xml:space="preserve">4.08351564407349</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94654273986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07495450973511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02358961105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96366429328918</t>
+    <t xml:space="preserve">3.94654250144958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07495498657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02359008789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96366405487061</t>
   </si>
   <si>
     <t xml:space="preserve">4.13488054275513</t>
@@ -1637,13 +1637,13 @@
     <t xml:space="preserve">5.01664590835571</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70845603942871</t>
+    <t xml:space="preserve">4.70845651626587</t>
   </si>
   <si>
     <t xml:space="preserve">4.91391563415527</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96528100967407</t>
+    <t xml:space="preserve">4.96528196334839</t>
   </si>
   <si>
     <t xml:space="preserve">4.94815969467163</t>
@@ -1652,13 +1652,13 @@
     <t xml:space="preserve">5.20498418807983</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56453943252563</t>
+    <t xml:space="preserve">5.56453990936279</t>
   </si>
   <si>
     <t xml:space="preserve">5.68439054489136</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95833778381348</t>
+    <t xml:space="preserve">5.95833683013916</t>
   </si>
   <si>
     <t xml:space="preserve">5.90697240829468</t>
@@ -1667,58 +1667,58 @@
     <t xml:space="preserve">5.88985061645508</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57471704483032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12955331802368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40350103378296</t>
+    <t xml:space="preserve">6.57471752166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.129554271698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4035005569458</t>
   </si>
   <si>
     <t xml:space="preserve">7.0198802947998</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20821857452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32806968688965</t>
+    <t xml:space="preserve">7.20821905136108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32807064056396</t>
   </si>
   <si>
     <t xml:space="preserve">7.05412340164185</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00275850296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4239764213562</t>
+    <t xml:space="preserve">7.00275897979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42397689819336</t>
   </si>
   <si>
     <t xml:space="preserve">7.28357124328613</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8799033164978</t>
+    <t xml:space="preserve">6.87990283966064</t>
   </si>
   <si>
     <t xml:space="preserve">6.9676570892334</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59909057617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51133680343628</t>
+    <t xml:space="preserve">6.59909105300903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51133728027344</t>
   </si>
   <si>
     <t xml:space="preserve">6.73949670791626</t>
   </si>
   <si>
-    <t xml:space="preserve">6.844801902771</t>
+    <t xml:space="preserve">6.84480142593384</t>
   </si>
   <si>
     <t xml:space="preserve">6.82725095748901</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68684482574463</t>
+    <t xml:space="preserve">6.68684434890747</t>
   </si>
   <si>
     <t xml:space="preserve">6.66929340362549</t>
@@ -1727,40 +1727,40 @@
     <t xml:space="preserve">6.45868492126465</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4060320854187</t>
+    <t xml:space="preserve">6.40603256225586</t>
   </si>
   <si>
     <t xml:space="preserve">6.31827878952026</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80970048904419</t>
+    <t xml:space="preserve">6.80970001220703</t>
   </si>
   <si>
     <t xml:space="preserve">7.17826652526855</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3537745475769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26601982116699</t>
+    <t xml:space="preserve">7.35377407073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26602029800415</t>
   </si>
   <si>
     <t xml:space="preserve">7.05541086196899</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07296180725098</t>
+    <t xml:space="preserve">7.07296228408813</t>
   </si>
   <si>
     <t xml:space="preserve">6.63419246673584</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44113445281982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30072736740112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05501699447632</t>
+    <t xml:space="preserve">6.44113349914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30072784423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.055016040802</t>
   </si>
   <si>
     <t xml:space="preserve">6.03746604919434</t>
@@ -1769,43 +1769,43 @@
     <t xml:space="preserve">5.37053632736206</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40563821792603</t>
+    <t xml:space="preserve">5.40563774108887</t>
   </si>
   <si>
     <t xml:space="preserve">5.52849388122559</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65134906768799</t>
+    <t xml:space="preserve">5.65134954452515</t>
   </si>
   <si>
     <t xml:space="preserve">6.12521982192993</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96726322174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01991558074951</t>
+    <t xml:space="preserve">5.96726274490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01991510391235</t>
   </si>
   <si>
     <t xml:space="preserve">5.91461038589478</t>
   </si>
   <si>
-    <t xml:space="preserve">5.844407081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9497127532959</t>
+    <t xml:space="preserve">5.84440755844116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94971227645874</t>
   </si>
   <si>
     <t xml:space="preserve">5.86195802688599</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82685661315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93216180801392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87950897216797</t>
+    <t xml:space="preserve">5.82685708999634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93216133117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87950849533081</t>
   </si>
   <si>
     <t xml:space="preserve">5.79175519943237</t>
@@ -1817,13 +1817,13 @@
     <t xml:space="preserve">5.45829057693481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63379812240601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70400094985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58114671707153</t>
+    <t xml:space="preserve">5.63379859924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70400190353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58114624023438</t>
   </si>
   <si>
     <t xml:space="preserve">5.66889953613281</t>
@@ -1832,10 +1832,10 @@
     <t xml:space="preserve">5.56359529495239</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61624765396118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49339246749878</t>
+    <t xml:space="preserve">5.61624813079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49339199066162</t>
   </si>
   <si>
     <t xml:space="preserve">5.31788444519043</t>
@@ -1844,16 +1844,16 @@
     <t xml:space="preserve">5.17747783660889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26523208618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28278303146362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35298585891724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42318916320801</t>
+    <t xml:space="preserve">5.26523160934448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28278207778931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35298633575439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42318868637085</t>
   </si>
   <si>
     <t xml:space="preserve">5.47584104537964</t>
@@ -1871,7 +1871,7 @@
     <t xml:space="preserve">5.44073963165283</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54604434967041</t>
+    <t xml:space="preserve">5.54604482650757</t>
   </si>
   <si>
     <t xml:space="preserve">6.23052453994751</t>
@@ -1892,16 +1892,16 @@
     <t xml:space="preserve">6.42358350753784</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54643869400024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98520755767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33622360229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09051179885864</t>
+    <t xml:space="preserve">6.54643821716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98520803451538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33622312545776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09051275253296</t>
   </si>
   <si>
     <t xml:space="preserve">7.16071557998657</t>
@@ -1910,16 +1910,16 @@
     <t xml:space="preserve">7.19581699371338</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95010662078857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14316463470459</t>
+    <t xml:space="preserve">6.95010614395142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14316558837891</t>
   </si>
   <si>
     <t xml:space="preserve">7.12561416625977</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02030944824219</t>
+    <t xml:space="preserve">7.02030992507935</t>
   </si>
   <si>
     <t xml:space="preserve">7.84519481658936</t>
@@ -1940,13 +1940,13 @@
     <t xml:space="preserve">8.68763256072998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03864765167236</t>
+    <t xml:space="preserve">9.038649559021</t>
   </si>
   <si>
     <t xml:space="preserve">9.30191040039062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2763719558716</t>
+    <t xml:space="preserve">11.2763729095459</t>
   </si>
   <si>
     <t xml:space="preserve">13.1630802154541</t>
@@ -1958,19 +1958,19 @@
     <t xml:space="preserve">13.1192035675049</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8559408187866</t>
+    <t xml:space="preserve">12.8559417724609</t>
   </si>
   <si>
     <t xml:space="preserve">12.0222797393799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1100339889526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9345264434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3641262054443</t>
+    <t xml:space="preserve">12.110032081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9345254898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3641242980957</t>
   </si>
   <si>
     <t xml:space="preserve">10.8814792633057</t>
@@ -1979,13 +1979,13 @@
     <t xml:space="preserve">12.1539106369019</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6712636947632</t>
+    <t xml:space="preserve">11.6712646484375</t>
   </si>
   <si>
     <t xml:space="preserve">11.7151412963867</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4518804550171</t>
+    <t xml:space="preserve">11.4518795013428</t>
   </si>
   <si>
     <t xml:space="preserve">11.0569877624512</t>
@@ -1994,7 +1994,7 @@
     <t xml:space="preserve">11.4957571029663</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4080018997192</t>
+    <t xml:space="preserve">11.4080038070679</t>
   </si>
   <si>
     <t xml:space="preserve">11.8906497955322</t>
@@ -2003,25 +2003,25 @@
     <t xml:space="preserve">11.8028955459595</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3202486038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.627387046814</t>
+    <t xml:space="preserve">11.3202476501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6273880004883</t>
   </si>
   <si>
     <t xml:space="preserve">11.1447410583496</t>
   </si>
   <si>
-    <t xml:space="preserve">10.618218421936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5304641723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5743398666382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.749849319458</t>
+    <t xml:space="preserve">10.6182174682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.530463218689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5743408203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7498483657837</t>
   </si>
   <si>
     <t xml:space="preserve">10.6620941162109</t>
@@ -2033,37 +2033,37 @@
     <t xml:space="preserve">9.78455543518066</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91618633270264</t>
+    <t xml:space="preserve">9.91618728637695</t>
   </si>
   <si>
     <t xml:space="preserve">10.0916938781738</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2324953079224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1886177062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1008634567261</t>
+    <t xml:space="preserve">11.2324962615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1886167526245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1008644104004</t>
   </si>
   <si>
     <t xml:space="preserve">11.3553495407104</t>
   </si>
   <si>
-    <t xml:space="preserve">11.267596244812</t>
+    <t xml:space="preserve">11.2675971984863</t>
   </si>
   <si>
     <t xml:space="preserve">11.0218858718872</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2500448226929</t>
+    <t xml:space="preserve">11.2500457763672</t>
   </si>
   <si>
     <t xml:space="preserve">11.3729009628296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2851476669312</t>
+    <t xml:space="preserve">11.2851467132568</t>
   </si>
   <si>
     <t xml:space="preserve">11.1973943710327</t>
@@ -2072,10 +2072,10 @@
     <t xml:space="preserve">11.8467721939087</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9871768951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2855405807495</t>
+    <t xml:space="preserve">11.9871778488159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2855415344238</t>
   </si>
   <si>
     <t xml:space="preserve">12.2504396438599</t>
@@ -2087,7 +2087,7 @@
     <t xml:space="preserve">12.4672012329102</t>
   </si>
   <si>
-    <t xml:space="preserve">12.037296295166</t>
+    <t xml:space="preserve">12.0372972488403</t>
   </si>
   <si>
     <t xml:space="preserve">12.0910358428955</t>
@@ -2096,13 +2096,13 @@
     <t xml:space="preserve">11.5536556243896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6432199478149</t>
+    <t xml:space="preserve">11.6432209014893</t>
   </si>
   <si>
     <t xml:space="preserve">11.3924427032471</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9446258544922</t>
+    <t xml:space="preserve">10.9446268081665</t>
   </si>
   <si>
     <t xml:space="preserve">10.5505475997925</t>
@@ -2111,16 +2111,16 @@
     <t xml:space="preserve">10.6759376525879</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9088020324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7117624282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6580228805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9267129898071</t>
+    <t xml:space="preserve">10.9088010787964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7117614746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6580238342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9267139434814</t>
   </si>
   <si>
     <t xml:space="preserve">11.0521020889282</t>
@@ -2129,16 +2129,16 @@
     <t xml:space="preserve">11.4999189376831</t>
   </si>
   <si>
-    <t xml:space="preserve">11.482006072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4282674789429</t>
+    <t xml:space="preserve">11.4820051193237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4282684326172</t>
   </si>
   <si>
     <t xml:space="preserve">11.5715684890747</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3745288848877</t>
+    <t xml:space="preserve">11.374529838562</t>
   </si>
   <si>
     <t xml:space="preserve">11.3566179275513</t>
@@ -2150,13 +2150,13 @@
     <t xml:space="preserve">11.4461803436279</t>
   </si>
   <si>
-    <t xml:space="preserve">11.464093208313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7148685455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7327833175659</t>
+    <t xml:space="preserve">11.4640941619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7148704528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7327823638916</t>
   </si>
   <si>
     <t xml:space="preserve">11.7506952285767</t>
@@ -2180,34 +2180,34 @@
     <t xml:space="preserve">11.6969575881958</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1268606185913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0552110671997</t>
+    <t xml:space="preserve">12.1268615722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0552101135254</t>
   </si>
   <si>
     <t xml:space="preserve">11.8581705093384</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9298210144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2880754470825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5925912857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5030269622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9835605621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.323899269104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9804515838623</t>
+    <t xml:space="preserve">11.9298219680786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2880744934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5925893783569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.503026008606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9835596084595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3239002227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9804525375366</t>
   </si>
   <si>
     <t xml:space="preserve">11.177490234375</t>
@@ -2216,37 +2216,37 @@
     <t xml:space="preserve">11.284966468811</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3387050628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8939962387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.768609046936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6253070831299</t>
+    <t xml:space="preserve">11.3387041091919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8939971923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7686080932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6253061294556</t>
   </si>
   <si>
     <t xml:space="preserve">12.0014715194702</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1089487075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9656476974487</t>
+    <t xml:space="preserve">12.1089477539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9656467437744</t>
   </si>
   <si>
     <t xml:space="preserve">12.1985120773315</t>
   </si>
   <si>
-    <t xml:space="preserve">12.43137550354</t>
+    <t xml:space="preserve">12.4313764572144</t>
   </si>
   <si>
     <t xml:space="preserve">12.2522497177124</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8612785339355</t>
+    <t xml:space="preserve">12.8612794876099</t>
   </si>
   <si>
     <t xml:space="preserve">12.8433666229248</t>
@@ -2261,7 +2261,7 @@
     <t xml:space="preserve">13.3449201583862</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2405519485474</t>
+    <t xml:space="preserve">14.240553855896</t>
   </si>
   <si>
     <t xml:space="preserve">14.0972518920898</t>
@@ -2273,73 +2273,73 @@
     <t xml:space="preserve">14.4734172821045</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5988063812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8823013305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.864387512207</t>
+    <t xml:space="preserve">14.598804473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8823003768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8643865585327</t>
   </si>
   <si>
     <t xml:space="preserve">13.5777854919434</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4703092575073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6852617263794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6673488616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5598735809326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6136093139648</t>
+    <t xml:space="preserve">13.4703102111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6852607727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6673498153687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5598726272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6136102676392</t>
   </si>
   <si>
     <t xml:space="preserve">13.8285617828369</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9539499282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4344835281372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7210855484009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5240468978882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7031736373901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2553586959839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4523973464966</t>
+    <t xml:space="preserve">13.9539518356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4344844818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7210865020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5240478515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7031745910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2553577423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4523963928223</t>
   </si>
   <si>
     <t xml:space="preserve">13.3090944290161</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2763786315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4196796417236</t>
+    <t xml:space="preserve">14.2763776779175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4196786880493</t>
   </si>
   <si>
     <t xml:space="preserve">14.0256013870239</t>
   </si>
   <si>
-    <t xml:space="preserve">13.756911277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4375925064087</t>
+    <t xml:space="preserve">13.7569122314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.437593460083</t>
   </si>
   <si>
     <t xml:space="preserve">16.7124977111816</t>
@@ -2354,19 +2354,19 @@
     <t xml:space="preserve">17.2498760223389</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6591262817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3160457611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4503936767578</t>
+    <t xml:space="preserve">19.6591281890869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.316047668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4503955841064</t>
   </si>
   <si>
     <t xml:space="preserve">21.5399551391602</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2116813659668</t>
+    <t xml:space="preserve">22.2116794586182</t>
   </si>
   <si>
     <t xml:space="preserve">21.987771987915</t>
@@ -2393,52 +2393,52 @@
     <t xml:space="preserve">22.4355869293213</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4951725006104</t>
+    <t xml:space="preserve">21.495174407959</t>
   </si>
   <si>
     <t xml:space="preserve">21.7190818786621</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9429893493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7638645172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8534259796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3312187194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8086471557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3463935852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3016109466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2420234680176</t>
+    <t xml:space="preserve">21.9429912567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7638626098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8534278869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3312206268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8086452484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3463916778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3016128540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2420253753662</t>
   </si>
   <si>
     <t xml:space="preserve">25.525520324707</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2120475769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8837718963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4807395935059</t>
+    <t xml:space="preserve">25.2120494842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8837738037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4807376861572</t>
   </si>
   <si>
     <t xml:space="preserve">25.5703010559082</t>
   </si>
   <si>
-    <t xml:space="preserve">25.122486114502</t>
+    <t xml:space="preserve">25.1224842071533</t>
   </si>
   <si>
     <t xml:space="preserve">24.361198425293</t>
@@ -2447,19 +2447,19 @@
     <t xml:space="preserve">25.3911743164062</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7046489715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4211502075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0628967285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4659309387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1524639129639</t>
+    <t xml:space="preserve">25.704647064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4211521148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0628986358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.465934753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1524620056152</t>
   </si>
   <si>
     <t xml:space="preserve">28.6602325439453</t>
@@ -2474,7 +2474,7 @@
     <t xml:space="preserve">26.5554962158203</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9881401062012</t>
+    <t xml:space="preserve">24.9881381988525</t>
   </si>
   <si>
     <t xml:space="preserve">25.2568302154541</t>
@@ -2495,10 +2495,10 @@
     <t xml:space="preserve">22.0773334503174</t>
   </si>
   <si>
-    <t xml:space="preserve">22.928186416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1968765258789</t>
+    <t xml:space="preserve">22.9281883239746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1968746185303</t>
   </si>
   <si>
     <t xml:space="preserve">24.182071685791</t>
@@ -2510,10 +2510,10 @@
     <t xml:space="preserve">24.4955425262451</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3164157867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3908081054688</t>
+    <t xml:space="preserve">24.3164138793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3908061981201</t>
   </si>
   <si>
     <t xml:space="preserve">23.8238182067871</t>
@@ -2525,22 +2525,22 @@
     <t xml:space="preserve">23.7790355682373</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8834037780762</t>
+    <t xml:space="preserve">22.8834018707275</t>
   </si>
   <si>
     <t xml:space="preserve">23.2416572570801</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1672668457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3167839050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6002807617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6150817871094</t>
+    <t xml:space="preserve">25.1672687530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3167819976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6002788543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.615083694458</t>
   </si>
   <si>
     <t xml:space="preserve">25.4359550476074</t>
@@ -2549,58 +2549,58 @@
     <t xml:space="preserve">24.8985767364502</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9733352661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5107173919678</t>
+    <t xml:space="preserve">25.9733371734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5107154846191</t>
   </si>
   <si>
     <t xml:space="preserve">26.197244644165</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8689670562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6450576782227</t>
+    <t xml:space="preserve">26.868968963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6450595855713</t>
   </si>
   <si>
     <t xml:space="preserve">27.4959106445312</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0480937957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9437294006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8841400146484</t>
+    <t xml:space="preserve">27.048095703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9437274932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8841419219971</t>
   </si>
   <si>
     <t xml:space="preserve">28.9289207458496</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7050113677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7797718048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9885101318359</t>
+    <t xml:space="preserve">28.7050132751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7797756195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9885063171387</t>
   </si>
   <si>
     <t xml:space="preserve">27.6302547454834</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2272186279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4063472747803</t>
+    <t xml:space="preserve">27.2272205352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4063491821289</t>
   </si>
   <si>
     <t xml:space="preserve">26.6898403167725</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8389892578125</t>
+    <t xml:space="preserve">25.8389911651611</t>
   </si>
   <si>
     <t xml:space="preserve">25.79421043396</t>
@@ -2612,16 +2612,16 @@
     <t xml:space="preserve">24.7194499969482</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4507617950439</t>
+    <t xml:space="preserve">24.4507598876953</t>
   </si>
   <si>
     <t xml:space="preserve">23.599910736084</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4655666351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3615665435791</t>
+    <t xml:space="preserve">23.4655647277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3615646362305</t>
   </si>
   <si>
     <t xml:space="preserve">28.0332889556885</t>
@@ -2636,7 +2636,7 @@
     <t xml:space="preserve">27.6633834838867</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2979888916016</t>
+    <t xml:space="preserve">30.2979869842529</t>
   </si>
   <si>
     <t xml:space="preserve">26.891170501709</t>
@@ -2648,22 +2648,22 @@
     <t xml:space="preserve">29.662052154541</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4803524017334</t>
+    <t xml:space="preserve">29.480354309082</t>
   </si>
   <si>
     <t xml:space="preserve">29.3440799713135</t>
   </si>
   <si>
-    <t xml:space="preserve">30.525110244751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5705375671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0247802734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0702037811279</t>
+    <t xml:space="preserve">30.5251121520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.57053565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0247821807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0702018737793</t>
   </si>
   <si>
     <t xml:space="preserve">30.8885059356689</t>
@@ -2678,7 +2678,7 @@
     <t xml:space="preserve">27.9359283447266</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4362621307373</t>
+    <t xml:space="preserve">27.4362602233887</t>
   </si>
   <si>
     <t xml:space="preserve">28.0722007751465</t>
@@ -2687,7 +2687,7 @@
     <t xml:space="preserve">28.4355945587158</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5264434814453</t>
+    <t xml:space="preserve">28.5264415740967</t>
   </si>
   <si>
     <t xml:space="preserve">28.4810199737549</t>
@@ -2699,13 +2699,13 @@
     <t xml:space="preserve">29.1623821258545</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4349308013916</t>
+    <t xml:space="preserve">29.434928894043</t>
   </si>
   <si>
     <t xml:space="preserve">28.2538986206055</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1169567108154</t>
+    <t xml:space="preserve">29.1169605255127</t>
   </si>
   <si>
     <t xml:space="preserve">30.1162948608398</t>
@@ -2714,25 +2714,25 @@
     <t xml:space="preserve">30.9793529510498</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1610507965088</t>
+    <t xml:space="preserve">31.1610488891602</t>
   </si>
   <si>
     <t xml:space="preserve">31.479024887085</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5698680877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.796989440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7515659332275</t>
+    <t xml:space="preserve">31.5698719024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7969932556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7515678405762</t>
   </si>
   <si>
     <t xml:space="preserve">31.1156272888184</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2505683898926</t>
+    <t xml:space="preserve">33.2505645751953</t>
   </si>
   <si>
     <t xml:space="preserve">34.6587219238281</t>
@@ -2741,7 +2741,7 @@
     <t xml:space="preserve">33.8410835266113</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4770240783691</t>
+    <t xml:space="preserve">34.4770278930664</t>
   </si>
   <si>
     <t xml:space="preserve">34.386173248291</t>
@@ -2750,37 +2750,37 @@
     <t xml:space="preserve">34.5678672790527</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6132965087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3400840759277</t>
+    <t xml:space="preserve">34.6132926940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.340087890625</t>
   </si>
   <si>
     <t xml:space="preserve">34.4316024780273</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7048110961914</t>
+    <t xml:space="preserve">33.7048072814941</t>
   </si>
   <si>
     <t xml:space="preserve">33.9773559570312</t>
   </si>
   <si>
-    <t xml:space="preserve">34.931266784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5224456787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0682029724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7502365112305</t>
+    <t xml:space="preserve">34.9312705993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5224494934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0682067871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7502326965332</t>
   </si>
   <si>
     <t xml:space="preserve">33.9319305419922</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2499046325684</t>
+    <t xml:space="preserve">34.2499008178711</t>
   </si>
   <si>
     <t xml:space="preserve">33.6139640808105</t>
@@ -2792,13 +2792,13 @@
     <t xml:space="preserve">36.6573867797852</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7936630249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6106338500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5645446777344</t>
+    <t xml:space="preserve">36.7936592102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6106300354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5645408630371</t>
   </si>
   <si>
     <t xml:space="preserve">38.1109657287598</t>
@@ -2807,22 +2807,22 @@
     <t xml:space="preserve">36.4302635192871</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3868370056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8871726989746</t>
+    <t xml:space="preserve">33.3868408203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8871765136719</t>
   </si>
   <si>
     <t xml:space="preserve">33.0688743591309</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3414192199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8865051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2044830322266</t>
+    <t xml:space="preserve">33.3414154052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8865089416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2044792175293</t>
   </si>
   <si>
     <t xml:space="preserve">34.340747833252</t>
@@ -2837,7 +2837,7 @@
     <t xml:space="preserve">32.9780197143555</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7976551055908</t>
+    <t xml:space="preserve">30.7976570129395</t>
   </si>
   <si>
     <t xml:space="preserve">29.3895034790039</t>
@@ -2846,22 +2846,22 @@
     <t xml:space="preserve">29.5257778167725</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6172924041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.344747543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0254440307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9332675933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2058067321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1149597167969</t>
+    <t xml:space="preserve">28.6172904968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3447456359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0254459381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9332637786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.205810546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1149559020996</t>
   </si>
   <si>
     <t xml:space="preserve">32.2512359619141</t>
@@ -2870,13 +2870,13 @@
     <t xml:space="preserve">31.615291595459</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0241088867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1142959594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6146278381348</t>
+    <t xml:space="preserve">32.024112701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1142997741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.614631652832</t>
   </si>
   <si>
     <t xml:space="preserve">31.2064743041992</t>
@@ -2885,10 +2885,10 @@
     <t xml:space="preserve">32.0695381164551</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5244445800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3427486419678</t>
+    <t xml:space="preserve">31.5244464874268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3427467346191</t>
   </si>
   <si>
     <t xml:space="preserve">32.3420829772949</t>
@@ -2897,10 +2897,10 @@
     <t xml:space="preserve">32.5237770080566</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7054748535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1603889465332</t>
+    <t xml:space="preserve">32.7054786682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1603851318359</t>
   </si>
   <si>
     <t xml:space="preserve">34.159049987793</t>
@@ -2912,10 +2912,10 @@
     <t xml:space="preserve">34.976692199707</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9325981140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0234489440918</t>
+    <t xml:space="preserve">32.9325942993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0234451293945</t>
   </si>
   <si>
     <t xml:space="preserve">33.5231170654297</t>
@@ -2930,19 +2930,19 @@
     <t xml:space="preserve">31.8424167633057</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8878402709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4342613220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7074737548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7068099975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4796886444092</t>
+    <t xml:space="preserve">31.8878383636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4342651367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7074756622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.70680809021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4796867370605</t>
   </si>
   <si>
     <t xml:space="preserve">29.6166248321533</t>
@@ -2954,13 +2954,13 @@
     <t xml:space="preserve">29.2532329559326</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7535667419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0708694458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.889835357666</t>
+    <t xml:space="preserve">28.7535629272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0708656311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8898372650146</t>
   </si>
   <si>
     <t xml:space="preserve">28.6627159118652</t>
@@ -2969,28 +2969,28 @@
     <t xml:space="preserve">28.8444137573242</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7081413269043</t>
+    <t xml:space="preserve">28.7081432342529</t>
   </si>
   <si>
     <t xml:space="preserve">28.9806861877441</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7989883422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8891754150391</t>
+    <t xml:space="preserve">28.7989902496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8891735076904</t>
   </si>
   <si>
     <t xml:space="preserve">29.0715351104736</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2993202209473</t>
+    <t xml:space="preserve">28.2993221282959</t>
   </si>
   <si>
     <t xml:space="preserve">28.0267772674561</t>
   </si>
   <si>
-    <t xml:space="preserve">27.617956161499</t>
+    <t xml:space="preserve">27.6179580688477</t>
   </si>
   <si>
     <t xml:space="preserve">27.7542304992676</t>
@@ -3002,7 +3002,7 @@
     <t xml:space="preserve">28.5718688964844</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4816837310791</t>
+    <t xml:space="preserve">27.4816856384277</t>
   </si>
   <si>
     <t xml:space="preserve">27.5725345611572</t>
@@ -3017,46 +3017,46 @@
     <t xml:space="preserve">27.0274410247803</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9365921020508</t>
+    <t xml:space="preserve">26.9365940093994</t>
   </si>
   <si>
     <t xml:space="preserve">26.9820194244385</t>
   </si>
   <si>
-    <t xml:space="preserve">26.346076965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8918361663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6647129058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2552280426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8457431793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6640510559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4369258880615</t>
+    <t xml:space="preserve">26.3460788726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8918342590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6647148132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2552299499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8457450866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6640491485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4369277954102</t>
   </si>
   <si>
     <t xml:space="preserve">26.5732002258301</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3915023803711</t>
+    <t xml:space="preserve">26.3915004730225</t>
   </si>
   <si>
     <t xml:space="preserve">26.70947265625</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5277767181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9826850891113</t>
+    <t xml:space="preserve">26.527774810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9826831817627</t>
   </si>
   <si>
     <t xml:space="preserve">25.8009872436523</t>
@@ -3068,19 +3068,19 @@
     <t xml:space="preserve">23.6660442352295</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8477439880371</t>
+    <t xml:space="preserve">23.8477458953857</t>
   </si>
   <si>
     <t xml:space="preserve">25.437593460083</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7555618286133</t>
+    <t xml:space="preserve">25.7555637359619</t>
   </si>
   <si>
     <t xml:space="preserve">25.074197769165</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0735359191895</t>
+    <t xml:space="preserve">26.0735340118408</t>
   </si>
   <si>
     <t xml:space="preserve">27.6892356872559</t>
@@ -4311,6 +4311,9 @@
   </si>
   <si>
     <t xml:space="preserve">19.1800003051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8999996185303</t>
   </si>
 </sst>
 </file>
@@ -70039,7 +70042,7 @@
     </row>
     <row r="2516">
       <c r="A2516" s="1" t="n">
-        <v>45981.6910300926</v>
+        <v>45981.3333333333</v>
       </c>
       <c r="B2516" t="n">
         <v>21013</v>
@@ -70060,6 +70063,32 @@
         <v>1432</v>
       </c>
       <c r="H2516" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2517">
+      <c r="A2517" s="1" t="n">
+        <v>45982.6911226852</v>
+      </c>
+      <c r="B2517" t="n">
+        <v>10242</v>
+      </c>
+      <c r="C2517" t="n">
+        <v>19.0799999237061</v>
+      </c>
+      <c r="D2517" t="n">
+        <v>18.6399993896484</v>
+      </c>
+      <c r="E2517" t="n">
+        <v>19.0799999237061</v>
+      </c>
+      <c r="F2517" t="n">
+        <v>18.8999996185303</v>
+      </c>
+      <c r="G2517" t="s">
+        <v>1433</v>
+      </c>
+      <c r="H2517" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ARN.MI.xlsx
+++ b/data/ARN.MI.xlsx
@@ -38,43 +38,43 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92215025424957</t>
+    <t xml:space="preserve">1.92215001583099</t>
   </si>
   <si>
     <t xml:space="preserve">ARN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94450092315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91736090183258</t>
+    <t xml:space="preserve">1.94450056552887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91736078262329</t>
   </si>
   <si>
     <t xml:space="preserve">1.90778183937073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88383507728577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93172895908356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91576445102692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83434426784515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8359409570694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91097462177277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80720388889313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74973142147064</t>
+    <t xml:space="preserve">1.88383483886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93172883987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91576433181763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83434391021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83594083786011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91097438335419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.807204246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74973106384277</t>
   </si>
   <si>
     <t xml:space="preserve">1.71620559692383</t>
@@ -89,43 +89,43 @@
     <t xml:space="preserve">1.79602909088135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77208185195923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70662677288055</t>
+    <t xml:space="preserve">1.77208209037781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70662653446198</t>
   </si>
   <si>
     <t xml:space="preserve">1.69704782962799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69066214561462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67629373073578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70024085044861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69864451885223</t>
+    <t xml:space="preserve">1.69066202640533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67629361152649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7002409696579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69864439964294</t>
   </si>
   <si>
     <t xml:space="preserve">1.67469727993011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66671478748322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66032922267914</t>
+    <t xml:space="preserve">1.6667149066925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66032910346985</t>
   </si>
   <si>
     <t xml:space="preserve">1.81518650054932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82795870304108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86148416996002</t>
+    <t xml:space="preserve">1.8279584646225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86148428916931</t>
   </si>
   <si>
     <t xml:space="preserve">1.88543128967285</t>
@@ -134,28 +134,28 @@
     <t xml:space="preserve">1.89181697368622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92853617668152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95407950878143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90618538856506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86786997318268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88064205646515</t>
+    <t xml:space="preserve">1.92853605747223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95407974720001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90618550777435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86787009239197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88064181804657</t>
   </si>
   <si>
     <t xml:space="preserve">1.85190534591675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85988759994507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85509836673737</t>
+    <t xml:space="preserve">1.85988771915436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85509824752808</t>
   </si>
   <si>
     <t xml:space="preserve">1.79283618927002</t>
@@ -164,88 +164,88 @@
     <t xml:space="preserve">1.78804636001587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78006434440613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75611710548401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7688889503479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76409935951233</t>
+    <t xml:space="preserve">1.78006422519684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75611734390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76888906955719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7640997171402</t>
   </si>
   <si>
     <t xml:space="preserve">1.78485369682312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77048563957214</t>
+    <t xml:space="preserve">1.77048552036285</t>
   </si>
   <si>
     <t xml:space="preserve">1.72099483013153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73536336421967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80241453647614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76250326633453</t>
+    <t xml:space="preserve">1.7353630065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80241477489471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76250314712524</t>
   </si>
   <si>
     <t xml:space="preserve">1.74494206905365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73217010498047</t>
+    <t xml:space="preserve">1.73216998577118</t>
   </si>
   <si>
     <t xml:space="preserve">1.73695957660675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7433454990387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75132763385773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68587267398834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67789018154144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65234673023224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62041711807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64276778697968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59008419513702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60285615921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54937422275543</t>
+    <t xml:space="preserve">1.74334561824799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75132775306702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68587279319763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67789030075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65234661102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6204172372818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64276814460754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59008431434631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60285592079163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54937434196472</t>
   </si>
   <si>
     <t xml:space="preserve">1.51185727119446</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45598089694977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43682324886322</t>
+    <t xml:space="preserve">1.45598077774048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43682312965393</t>
   </si>
   <si>
     <t xml:space="preserve">1.4695508480072</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4974889755249</t>
+    <t xml:space="preserve">1.49748909473419</t>
   </si>
   <si>
     <t xml:space="preserve">1.47673487663269</t>
@@ -254,28 +254,28 @@
     <t xml:space="preserve">1.47274386882782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46875286102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49669098854065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47593653202057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50626969337463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47753322124481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43841969966888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40090250968933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3490172624588</t>
+    <t xml:space="preserve">1.46875262260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49669086933136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47593665122986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50626957416534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47753310203552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43841958045959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40090262889862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34901738166809</t>
   </si>
   <si>
     <t xml:space="preserve">1.30910563468933</t>
@@ -287,46 +287,46 @@
     <t xml:space="preserve">1.32666671276093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34103500843048</t>
+    <t xml:space="preserve">1.3410347700119</t>
   </si>
   <si>
     <t xml:space="preserve">1.31708788871765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38653433322906</t>
+    <t xml:space="preserve">1.38653421401978</t>
   </si>
   <si>
     <t xml:space="preserve">1.39691150188446</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40649032592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30671083927155</t>
+    <t xml:space="preserve">1.40649020671844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30671095848083</t>
   </si>
   <si>
     <t xml:space="preserve">1.3234738111496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.305912733078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31229865550995</t>
+    <t xml:space="preserve">1.30591261386871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31229853630066</t>
   </si>
   <si>
     <t xml:space="preserve">1.28994798660278</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2851585149765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28595662117004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33305263519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33704376220703</t>
+    <t xml:space="preserve">1.28515839576721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28595674037933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33305251598358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33704388141632</t>
   </si>
   <si>
     <t xml:space="preserve">1.30112314224243</t>
@@ -335,85 +335,85 @@
     <t xml:space="preserve">1.36104881763458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34627270698547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35283982753754</t>
+    <t xml:space="preserve">1.34627258777618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35283970832825</t>
   </si>
   <si>
     <t xml:space="preserve">1.33806359767914</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27157080173492</t>
+    <t xml:space="preserve">1.27157092094421</t>
   </si>
   <si>
     <t xml:space="preserve">1.28880977630615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29291439056396</t>
+    <t xml:space="preserve">1.29291427135468</t>
   </si>
   <si>
     <t xml:space="preserve">1.30686950683594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33888459205627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34955632686615</t>
+    <t xml:space="preserve">1.33888447284698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34955620765686</t>
   </si>
   <si>
     <t xml:space="preserve">1.34380996227264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33642184734344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34709358215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30522751808167</t>
+    <t xml:space="preserve">1.33642196655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34709370136261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30522775650024</t>
   </si>
   <si>
     <t xml:space="preserve">1.29127240180969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31425750255585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32164573669434</t>
+    <t xml:space="preserve">1.31425726413727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32164561748505</t>
   </si>
   <si>
     <t xml:space="preserve">1.26828742027283</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27239167690277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2879890203476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29701864719391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24858582019806</t>
+    <t xml:space="preserve">1.27239179611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28798890113831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29701900482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24858593940735</t>
   </si>
   <si>
     <t xml:space="preserve">1.32657110691071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3323175907135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35940706729889</t>
+    <t xml:space="preserve">1.33231747150421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3594069480896</t>
   </si>
   <si>
     <t xml:space="preserve">1.4201534986496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48664617538452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53343749046326</t>
+    <t xml:space="preserve">1.48664629459381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53343737125397</t>
   </si>
   <si>
     <t xml:space="preserve">1.51619851589203</t>
@@ -422,16 +422,16 @@
     <t xml:space="preserve">1.51866114139557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43739235401154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46776556968689</t>
+    <t xml:space="preserve">1.43739259243011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46776533126831</t>
   </si>
   <si>
     <t xml:space="preserve">1.43000423908234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40948176383972</t>
+    <t xml:space="preserve">1.40948188304901</t>
   </si>
   <si>
     <t xml:space="preserve">1.44478023052216</t>
@@ -443,7 +443,7 @@
     <t xml:space="preserve">1.61798977851868</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70582580566406</t>
+    <t xml:space="preserve">1.70582604408264</t>
   </si>
   <si>
     <t xml:space="preserve">1.74851274490356</t>
@@ -452,40 +452,40 @@
     <t xml:space="preserve">1.72388565540314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6828408241272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67463183403015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.651646733284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64179575443268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67134833335876</t>
+    <t xml:space="preserve">1.68284070491791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67463171482086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65164661407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64179599285126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67134821414948</t>
   </si>
   <si>
     <t xml:space="preserve">1.66478109359741</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65657198429108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69597518444061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69433319568634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65821385383606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6811990737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68776619434357</t>
+    <t xml:space="preserve">1.65657186508179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69597506523132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69433343410492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65821397304535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68119919300079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68776595592499</t>
   </si>
   <si>
     <t xml:space="preserve">1.66806471347809</t>
@@ -497,25 +497,25 @@
     <t xml:space="preserve">1.66313922405243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67791521549225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03746891021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04403614997864</t>
+    <t xml:space="preserve">1.67791533470154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03746867179871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04403567314148</t>
   </si>
   <si>
     <t xml:space="preserve">2.0391104221344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04075217247009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05224442481995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04731941223145</t>
+    <t xml:space="preserve">2.04075241088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0522449016571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04731917381287</t>
   </si>
   <si>
     <t xml:space="preserve">2.04239368438721</t>
@@ -527,10 +527,10 @@
     <t xml:space="preserve">2.24105143547058</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1885142326355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17537951469421</t>
+    <t xml:space="preserve">2.18851375579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17537975311279</t>
   </si>
   <si>
     <t xml:space="preserve">2.14582705497742</t>
@@ -539,49 +539,49 @@
     <t xml:space="preserve">2.00627446174622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98821485042572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9931401014328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99806571006775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9964234828949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99970757961273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00299096107483</t>
+    <t xml:space="preserve">1.9882150888443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99314022064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99806582927704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99642384052277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99970734119415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00299119949341</t>
   </si>
   <si>
     <t xml:space="preserve">2.00791668891907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01119995117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02597594261169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03254342079163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02105093002319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01940894126892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02433443069458</t>
+    <t xml:space="preserve">2.01119947433472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02597570419312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03254318237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02105045318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0194091796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02433466911316</t>
   </si>
   <si>
     <t xml:space="preserve">2.07687187194824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0588116645813</t>
+    <t xml:space="preserve">2.05881190299988</t>
   </si>
   <si>
     <t xml:space="preserve">2.09657335281372</t>
@@ -599,37 +599,37 @@
     <t xml:space="preserve">2.32478284835815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27881288528442</t>
+    <t xml:space="preserve">2.278813123703</t>
   </si>
   <si>
     <t xml:space="preserve">2.25746941566467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29851460456848</t>
+    <t xml:space="preserve">2.29851412773132</t>
   </si>
   <si>
     <t xml:space="preserve">2.26075291633606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28045415878296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30672335624695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35597729682922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34120106697083</t>
+    <t xml:space="preserve">2.2804548740387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30672311782837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35597705841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34120059013367</t>
   </si>
   <si>
     <t xml:space="preserve">2.34284281730652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34776782989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44627618789673</t>
+    <t xml:space="preserve">2.34776759147644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44627571105957</t>
   </si>
   <si>
     <t xml:space="preserve">2.39209651947021</t>
@@ -650,19 +650,19 @@
     <t xml:space="preserve">2.38060402870178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42164921760559</t>
+    <t xml:space="preserve">2.42164874076843</t>
   </si>
   <si>
     <t xml:space="preserve">2.33791732788086</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32314133644104</t>
+    <t xml:space="preserve">2.32314109802246</t>
   </si>
   <si>
     <t xml:space="preserve">2.35433554649353</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41015648841858</t>
+    <t xml:space="preserve">2.41015672683716</t>
   </si>
   <si>
     <t xml:space="preserve">2.40687298774719</t>
@@ -674,37 +674,37 @@
     <t xml:space="preserve">2.41836524009705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29030513763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34941005706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36418604850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37567853927612</t>
+    <t xml:space="preserve">2.29030537605286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34940981864929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36418628692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3756787776947</t>
   </si>
   <si>
     <t xml:space="preserve">2.40194749832153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35761857032776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36746954917908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37075328826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37239551544189</t>
+    <t xml:space="preserve">2.35761880874634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36746978759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37075304985046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37239503860474</t>
   </si>
   <si>
     <t xml:space="preserve">2.362544298172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36582779884338</t>
+    <t xml:space="preserve">2.36582803726196</t>
   </si>
   <si>
     <t xml:space="preserve">2.39538025856018</t>
@@ -713,19 +713,19 @@
     <t xml:space="preserve">2.37732028961182</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37403678894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38881325721741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39373826980591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39045476913452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41343998908997</t>
+    <t xml:space="preserve">2.37403702735901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38881301879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39373850822449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3904550075531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41343975067139</t>
   </si>
   <si>
     <t xml:space="preserve">2.40358901023865</t>
@@ -734,64 +734,64 @@
     <t xml:space="preserve">2.40030574798584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40851449966431</t>
+    <t xml:space="preserve">2.40851497650146</t>
   </si>
   <si>
     <t xml:space="preserve">2.42329049110413</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43149948120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42000699043274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35105180740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33627533912659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34612655639648</t>
+    <t xml:space="preserve">2.43149971961975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42000722885132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35105156898499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33627557754517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34612631797791</t>
   </si>
   <si>
     <t xml:space="preserve">2.43642497062683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42657446861267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42985796928406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45284295082092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4770131111145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47868013381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49201536178589</t>
+    <t xml:space="preserve">2.42657423019409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42985820770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45284271240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47701334953308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.478679895401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49201512336731</t>
   </si>
   <si>
     <t xml:space="preserve">2.49368214607239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.475346326828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46534466743469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48201394081116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46867847442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4586775302887</t>
+    <t xml:space="preserve">2.47534608840942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46534442901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48201370239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46867823600769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45867705345154</t>
   </si>
   <si>
     <t xml:space="preserve">2.46201086044312</t>
@@ -803,34 +803,34 @@
     <t xml:space="preserve">2.41700482368469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40867066383362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36699795722961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3419942855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36866474151611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35366225242615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.385333776474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38366651535034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36366367340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32532501220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31699085235596</t>
+    <t xml:space="preserve">2.40867018699646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36699771881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34199404716492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36866450309753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35366272926331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38533353805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38366627693176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36366391181946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32532525062561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31699061393738</t>
   </si>
   <si>
     <t xml:space="preserve">2.28531980514526</t>
@@ -842,7 +842,7 @@
     <t xml:space="preserve">2.29698801040649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3153235912323</t>
+    <t xml:space="preserve">2.31532382965088</t>
   </si>
   <si>
     <t xml:space="preserve">2.28365254402161</t>
@@ -854,25 +854,25 @@
     <t xml:space="preserve">2.29032039642334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30198884010315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30365562438965</t>
+    <t xml:space="preserve">2.30198860168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30365586280823</t>
   </si>
   <si>
     <t xml:space="preserve">2.2936544418335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24198055267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26698350906372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26865029335022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32699203491211</t>
+    <t xml:space="preserve">2.24198031425476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2669837474823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2686505317688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32699179649353</t>
   </si>
   <si>
     <t xml:space="preserve">2.31865763664246</t>
@@ -881,19 +881,19 @@
     <t xml:space="preserve">2.3103232383728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24364686012268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25031447410583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22531151771545</t>
+    <t xml:space="preserve">2.24364733695984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25031471252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22531127929688</t>
   </si>
   <si>
     <t xml:space="preserve">2.25198149681091</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22197771072388</t>
+    <t xml:space="preserve">2.2219774723053</t>
   </si>
   <si>
     <t xml:space="preserve">2.20697546005249</t>
@@ -905,22 +905,22 @@
     <t xml:space="preserve">2.16863656044006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17863798141479</t>
+    <t xml:space="preserve">2.17863774299622</t>
   </si>
   <si>
     <t xml:space="preserve">2.16696977615356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18697261810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19697427749634</t>
+    <t xml:space="preserve">2.18697285652161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19697403907776</t>
   </si>
   <si>
     <t xml:space="preserve">2.18363881111145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18530583381653</t>
+    <t xml:space="preserve">2.18530559539795</t>
   </si>
   <si>
     <t xml:space="preserve">2.19197344779968</t>
@@ -932,34 +932,34 @@
     <t xml:space="preserve">2.14196586608887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15363454818726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14363312721252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13529849052429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12696433067322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12863111495972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12029647827148</t>
+    <t xml:space="preserve">2.15363478660583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1436333656311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13529896736145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12696385383606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12863087654114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12029623985291</t>
   </si>
   <si>
     <t xml:space="preserve">2.13029789924622</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11862993240356</t>
+    <t xml:space="preserve">2.11862969398499</t>
   </si>
   <si>
     <t xml:space="preserve">2.37366533279419</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37533211708069</t>
+    <t xml:space="preserve">2.37533235549927</t>
   </si>
   <si>
     <t xml:space="preserve">2.40700340270996</t>
@@ -968,28 +968,28 @@
     <t xml:space="preserve">2.39533519744873</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39200139045715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49868249893188</t>
+    <t xml:space="preserve">2.39200115203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49868273735046</t>
   </si>
   <si>
     <t xml:space="preserve">2.49534893035889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50868391990662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51201820373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51535177230835</t>
+    <t xml:space="preserve">2.5086841583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51201772689819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51535153388977</t>
   </si>
   <si>
     <t xml:space="preserve">2.51701903343201</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52368640899658</t>
+    <t xml:space="preserve">2.52368664741516</t>
   </si>
   <si>
     <t xml:space="preserve">2.52535319328308</t>
@@ -998,55 +998,55 @@
     <t xml:space="preserve">2.54535603523254</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53368782997131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53202104568481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54035544395447</t>
+    <t xml:space="preserve">2.53368759155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53202080726624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54035520553589</t>
   </si>
   <si>
     <t xml:space="preserve">2.52702045440674</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53868842124939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53702139854431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49701595306396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42700600624084</t>
+    <t xml:space="preserve">2.53868818283081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53702163696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49701619148254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42700624465942</t>
   </si>
   <si>
     <t xml:space="preserve">2.50034976005554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5053505897522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48368096351624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4520092010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51368474960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54202222824097</t>
+    <t xml:space="preserve">2.50535035133362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48368048667908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45200943946838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51368498802185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54202198982239</t>
   </si>
   <si>
     <t xml:space="preserve">2.54868984222412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51035118103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.520352602005</t>
+    <t xml:space="preserve">2.51035094261169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52035236358643</t>
   </si>
   <si>
     <t xml:space="preserve">2.47201251983643</t>
@@ -1058,25 +1058,25 @@
     <t xml:space="preserve">2.48701477050781</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00041961669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81706047058105</t>
+    <t xml:space="preserve">3.00041937828064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81706094741821</t>
   </si>
   <si>
     <t xml:space="preserve">2.75038456916809</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71704649925232</t>
+    <t xml:space="preserve">2.7170467376709</t>
   </si>
   <si>
     <t xml:space="preserve">2.8087260723114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80039167404175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83372950553894</t>
+    <t xml:space="preserve">2.80039143562317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8337299823761</t>
   </si>
   <si>
     <t xml:space="preserve">2.78372263908386</t>
@@ -1088,67 +1088,67 @@
     <t xml:space="preserve">2.75871920585632</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85039901733398</t>
+    <t xml:space="preserve">2.85039877891541</t>
   </si>
   <si>
     <t xml:space="preserve">2.85873341560364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89207100868225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82539534568787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72538089752197</t>
+    <t xml:space="preserve">2.89207124710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82539510726929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72538113594055</t>
   </si>
   <si>
     <t xml:space="preserve">2.61703276634216</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6420361995697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70037770271301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65870523452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6253674030304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63370156288147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59202909469604</t>
+    <t xml:space="preserve">2.64203596115112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70037746429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65870499610901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62536716461182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63370203971863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59202885627747</t>
   </si>
   <si>
     <t xml:space="preserve">2.66703987121582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70871186256409</t>
+    <t xml:space="preserve">2.70871210098267</t>
   </si>
   <si>
     <t xml:space="preserve">2.74205017089844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65037035942078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68370890617371</t>
+    <t xml:space="preserve">2.65037059783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68370866775513</t>
   </si>
   <si>
     <t xml:space="preserve">2.6003634929657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58369445800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56702542304993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7670533657074</t>
+    <t xml:space="preserve">2.58369469642639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56702589988708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76705384254456</t>
   </si>
   <si>
     <t xml:space="preserve">2.73371577262878</t>
@@ -1160,37 +1160,37 @@
     <t xml:space="preserve">2.86706757545471</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87540197372437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88373684883118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77538824081421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78091382980347</t>
+    <t xml:space="preserve">2.87540221214294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8837366104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77538776397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78091430664062</t>
   </si>
   <si>
     <t xml:space="preserve">2.72174549102783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73019814491272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77246117591858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64567160606384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70484042167664</t>
+    <t xml:space="preserve">2.7301983833313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77246141433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.645672082901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70483994483948</t>
   </si>
   <si>
     <t xml:space="preserve">2.68793487548828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6625771522522</t>
+    <t xml:space="preserve">2.66257739067078</t>
   </si>
   <si>
     <t xml:space="preserve">2.69638752937317</t>
@@ -1202,34 +1202,34 @@
     <t xml:space="preserve">2.60340857505798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63721871376038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61186122894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57805061340332</t>
+    <t xml:space="preserve">2.63721895217896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61186146736145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5780508518219</t>
   </si>
   <si>
     <t xml:space="preserve">2.5949559211731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50197744369507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49352478981018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54424071311951</t>
+    <t xml:space="preserve">2.50197720527649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4935245513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54424023628235</t>
   </si>
   <si>
     <t xml:space="preserve">2.5611457824707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58650302886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51888251304626</t>
+    <t xml:space="preserve">2.58650326728821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51888227462769</t>
   </si>
   <si>
     <t xml:space="preserve">2.53578782081604</t>
@@ -1238,28 +1238,28 @@
     <t xml:space="preserve">2.55269312858582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51042985916138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56959795951843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46816682815552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48507213592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41745090484619</t>
+    <t xml:space="preserve">2.5104296207428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56959843635559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46816658973694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48507189750671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41745066642761</t>
   </si>
   <si>
     <t xml:space="preserve">2.45126175880432</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39209342002869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3836407661438</t>
+    <t xml:space="preserve">2.39209294319153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38364028930664</t>
   </si>
   <si>
     <t xml:space="preserve">2.27375650405884</t>
@@ -1274,76 +1274,76 @@
     <t xml:space="preserve">2.35828256607056</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43435668945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42590355873108</t>
+    <t xml:space="preserve">2.43435645103455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4259033203125</t>
   </si>
   <si>
     <t xml:space="preserve">2.34982991218567</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28220891952515</t>
+    <t xml:space="preserve">2.28220868110657</t>
   </si>
   <si>
     <t xml:space="preserve">2.32447218894958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4089982509613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45971417427063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44280934333801</t>
+    <t xml:space="preserve">2.40899848937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45971441268921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44280886650085</t>
   </si>
   <si>
     <t xml:space="preserve">2.33292484283447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34137725830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.400545835495</t>
+    <t xml:space="preserve">2.34137749671936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40054559707642</t>
   </si>
   <si>
     <t xml:space="preserve">2.37518787384033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47661948204041</t>
+    <t xml:space="preserve">2.47661924362183</t>
   </si>
   <si>
     <t xml:space="preserve">2.30756664276123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23994588851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29430246353149</t>
+    <t xml:space="preserve">2.23994612693787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29430222511292</t>
   </si>
   <si>
     <t xml:space="preserve">2.2343761920929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24293732643127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33710646629333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25149822235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27718091011047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26861977577209</t>
+    <t xml:space="preserve">2.2429370880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33710622787476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25149846076965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27718067169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26862001419067</t>
   </si>
   <si>
     <t xml:space="preserve">2.44839692115784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37134957313538</t>
+    <t xml:space="preserve">2.37135004997253</t>
   </si>
   <si>
     <t xml:space="preserve">2.31142377853394</t>
@@ -1355,28 +1355,28 @@
     <t xml:space="preserve">2.26005887985229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35422801971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22581577301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20869374275208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30286359786987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31998467445374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37991070747375</t>
+    <t xml:space="preserve">2.35422825813293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22581553459167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20869421958923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30286335945129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31998491287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37991046905518</t>
   </si>
   <si>
     <t xml:space="preserve">2.40559315681458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39703249931335</t>
+    <t xml:space="preserve">2.39703226089478</t>
   </si>
   <si>
     <t xml:space="preserve">2.32854557037354</t>
@@ -1385,7 +1385,7 @@
     <t xml:space="preserve">2.38847136497498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36278891563416</t>
+    <t xml:space="preserve">2.36278915405273</t>
   </si>
   <si>
     <t xml:space="preserve">2.34566712379456</t>
@@ -1394,19 +1394,19 @@
     <t xml:space="preserve">2.20013308525085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18301177024841</t>
+    <t xml:space="preserve">2.18301153182983</t>
   </si>
   <si>
     <t xml:space="preserve">2.4398365020752</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54256629943848</t>
+    <t xml:space="preserve">2.5425660610199</t>
   </si>
   <si>
     <t xml:space="preserve">2.6024923324585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69666123390198</t>
+    <t xml:space="preserve">2.69666147232056</t>
   </si>
   <si>
     <t xml:space="preserve">2.77370882034302</t>
@@ -1418,22 +1418,22 @@
     <t xml:space="preserve">2.67097854614258</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61961388587952</t>
+    <t xml:space="preserve">2.61961364746094</t>
   </si>
   <si>
     <t xml:space="preserve">2.65385723114014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68810033798218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64529609680176</t>
+    <t xml:space="preserve">2.68810057640076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64529633522034</t>
   </si>
   <si>
     <t xml:space="preserve">2.71378302574158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72234392166138</t>
+    <t xml:space="preserve">2.7223436832428</t>
   </si>
   <si>
     <t xml:space="preserve">3.07333755493164</t>
@@ -1442,40 +1442,40 @@
     <t xml:space="preserve">3.52706170082092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59554862976074</t>
+    <t xml:space="preserve">3.59554815292358</t>
   </si>
   <si>
     <t xml:space="preserve">3.65547442436218</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58698773384094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61266946792603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53562259674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42433166503906</t>
+    <t xml:space="preserve">3.58698797225952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6126697063446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5356228351593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42433214187622</t>
   </si>
   <si>
     <t xml:space="preserve">3.54418325424194</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56986594200134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5527446269989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56130504608154</t>
+    <t xml:space="preserve">3.56986618041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55274438858032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56130480766296</t>
   </si>
   <si>
     <t xml:space="preserve">3.50993990898132</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48425793647766</t>
+    <t xml:space="preserve">3.48425769805908</t>
   </si>
   <si>
     <t xml:space="preserve">3.57842683792114</t>
@@ -1484,13 +1484,13 @@
     <t xml:space="preserve">3.63835263252258</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74108219146729</t>
+    <t xml:space="preserve">3.74108266830444</t>
   </si>
   <si>
     <t xml:space="preserve">4.16912412643433</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60572719573975</t>
+    <t xml:space="preserve">4.60572671890259</t>
   </si>
   <si>
     <t xml:space="preserve">5.15361928939819</t>
@@ -1502,19 +1502,19 @@
     <t xml:space="preserve">4.19480609893799</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45163154602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53723955154419</t>
+    <t xml:space="preserve">4.45163106918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53724002838135</t>
   </si>
   <si>
     <t xml:space="preserve">4.52011775970459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58860492706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34890174865723</t>
+    <t xml:space="preserve">4.58860445022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34890127182007</t>
   </si>
   <si>
     <t xml:space="preserve">4.16056346893311</t>
@@ -1523,40 +1523,40 @@
     <t xml:space="preserve">4.23761034011841</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29753589630127</t>
+    <t xml:space="preserve">4.29753637313843</t>
   </si>
   <si>
     <t xml:space="preserve">3.89517760276794</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27879762649536</t>
+    <t xml:space="preserve">3.27879738807678</t>
   </si>
   <si>
     <t xml:space="preserve">3.25311517715454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8935604095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15894627571106</t>
+    <t xml:space="preserve">2.89356064796448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15894603729248</t>
   </si>
   <si>
     <t xml:space="preserve">3.1675066947937</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03909468650818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44145369529724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3815279006958</t>
+    <t xml:space="preserve">3.0390944480896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44145345687866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38152766227722</t>
   </si>
   <si>
     <t xml:space="preserve">3.39008855819702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84381222724915</t>
+    <t xml:space="preserve">3.84381246566772</t>
   </si>
   <si>
     <t xml:space="preserve">3.83525133132935</t>
@@ -1565,10 +1565,10 @@
     <t xml:space="preserve">3.87805581092834</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76676511764526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88661646842957</t>
+    <t xml:space="preserve">3.76676464080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88661694526672</t>
   </si>
   <si>
     <t xml:space="preserve">3.8523736000061</t>
@@ -1580,43 +1580,43 @@
     <t xml:space="preserve">3.95510292053223</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93798208236694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11775922775269</t>
+    <t xml:space="preserve">3.93798160552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11775875091553</t>
   </si>
   <si>
     <t xml:space="preserve">4.25473213195801</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22905015945435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26329326629639</t>
+    <t xml:space="preserve">4.22904968261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26329278945923</t>
   </si>
   <si>
     <t xml:space="preserve">4.28041410446167</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43450975418091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20336675643921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00646829605103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10919809341431</t>
+    <t xml:space="preserve">4.43450927734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20336723327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00646781921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10919857025146</t>
   </si>
   <si>
     <t xml:space="preserve">4.15200233459473</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08351564407349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94654273986816</t>
+    <t xml:space="preserve">4.08351612091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94654226303101</t>
   </si>
   <si>
     <t xml:space="preserve">4.07495498657227</t>
@@ -1625,28 +1625,28 @@
     <t xml:space="preserve">4.02358961105347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96366429328918</t>
+    <t xml:space="preserve">3.96366405487061</t>
   </si>
   <si>
     <t xml:space="preserve">4.13488101959229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12632036209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01664638519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70845603942871</t>
+    <t xml:space="preserve">4.12631988525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01664590835571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70845651626587</t>
   </si>
   <si>
     <t xml:space="preserve">4.91391563415527</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96528100967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94815921783447</t>
+    <t xml:space="preserve">4.96528148651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94815969467163</t>
   </si>
   <si>
     <t xml:space="preserve">5.20498466491699</t>
@@ -1655,13 +1655,13 @@
     <t xml:space="preserve">5.56453895568848</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68439102172852</t>
+    <t xml:space="preserve">5.68439054489136</t>
   </si>
   <si>
     <t xml:space="preserve">5.95833778381348</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90697240829468</t>
+    <t xml:space="preserve">5.90697193145752</t>
   </si>
   <si>
     <t xml:space="preserve">5.88985013961792</t>
@@ -1670,7 +1670,7 @@
     <t xml:space="preserve">6.57471656799316</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12955379486084</t>
+    <t xml:space="preserve">6.12955284118652</t>
   </si>
   <si>
     <t xml:space="preserve">6.40350103378296</t>
@@ -1691,10 +1691,10 @@
     <t xml:space="preserve">7.00275897979736</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4239764213562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28357172012329</t>
+    <t xml:space="preserve">7.42397689819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28357124328613</t>
   </si>
   <si>
     <t xml:space="preserve">6.8799033164978</t>
@@ -1706,7 +1706,7 @@
     <t xml:space="preserve">6.59909105300903</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51133680343628</t>
+    <t xml:space="preserve">6.51133728027344</t>
   </si>
   <si>
     <t xml:space="preserve">6.73949670791626</t>
@@ -1718,10 +1718,10 @@
     <t xml:space="preserve">6.82725095748901</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68684434890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66929340362549</t>
+    <t xml:space="preserve">6.68684482574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66929388046265</t>
   </si>
   <si>
     <t xml:space="preserve">6.45868492126465</t>
@@ -1733,13 +1733,13 @@
     <t xml:space="preserve">6.31827831268311</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80970048904419</t>
+    <t xml:space="preserve">6.80970001220703</t>
   </si>
   <si>
     <t xml:space="preserve">7.17826700210571</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3537745475769</t>
+    <t xml:space="preserve">7.35377502441406</t>
   </si>
   <si>
     <t xml:space="preserve">7.26601982116699</t>
@@ -1760,25 +1760,25 @@
     <t xml:space="preserve">6.30072736740112</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05501699447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03746604919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37053680419922</t>
+    <t xml:space="preserve">6.05501651763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03746557235718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37053632736206</t>
   </si>
   <si>
     <t xml:space="preserve">5.40563821792603</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52849435806274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65134859085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12521982192993</t>
+    <t xml:space="preserve">5.52849388122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65134906768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12522029876709</t>
   </si>
   <si>
     <t xml:space="preserve">5.96726322174072</t>
@@ -1793,7 +1793,7 @@
     <t xml:space="preserve">5.84440755844116</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94971227645874</t>
+    <t xml:space="preserve">5.94971179962158</t>
   </si>
   <si>
     <t xml:space="preserve">5.86195802688599</t>
@@ -1814,7 +1814,7 @@
     <t xml:space="preserve">5.68645048141479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45829010009766</t>
+    <t xml:space="preserve">5.4582896232605</t>
   </si>
   <si>
     <t xml:space="preserve">5.63379859924316</t>
@@ -1823,10 +1823,10 @@
     <t xml:space="preserve">5.70400094985962</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58114624023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66890001296997</t>
+    <t xml:space="preserve">5.58114576339722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66890048980713</t>
   </si>
   <si>
     <t xml:space="preserve">5.56359529495239</t>
@@ -1841,7 +1841,7 @@
     <t xml:space="preserve">5.31788444519043</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17747783660889</t>
+    <t xml:space="preserve">5.17747831344604</t>
   </si>
   <si>
     <t xml:space="preserve">5.26523208618164</t>
@@ -1856,7 +1856,7 @@
     <t xml:space="preserve">5.42318916320801</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47584104537964</t>
+    <t xml:space="preserve">5.47584056854248</t>
   </si>
   <si>
     <t xml:space="preserve">5.38808727264404</t>
@@ -1865,10 +1865,10 @@
     <t xml:space="preserve">5.5109429359436</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77420473098755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44073963165283</t>
+    <t xml:space="preserve">5.77420520782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44074010848999</t>
   </si>
   <si>
     <t xml:space="preserve">5.54604482650757</t>
@@ -1877,16 +1877,16 @@
     <t xml:space="preserve">6.23052453994751</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35337972640991</t>
+    <t xml:space="preserve">6.35338020324707</t>
   </si>
   <si>
     <t xml:space="preserve">6.16032123565674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37093114852905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47623586654663</t>
+    <t xml:space="preserve">6.37093067169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47623538970947</t>
   </si>
   <si>
     <t xml:space="preserve">6.42358303070068</t>
@@ -1895,22 +1895,22 @@
     <t xml:space="preserve">6.54643869400024</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98520755767822</t>
+    <t xml:space="preserve">6.98520803451538</t>
   </si>
   <si>
     <t xml:space="preserve">7.33622360229492</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0905122756958</t>
+    <t xml:space="preserve">7.09051275253296</t>
   </si>
   <si>
     <t xml:space="preserve">7.16071510314941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19581699371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00275802612305</t>
+    <t xml:space="preserve">7.19581651687622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00275850296021</t>
   </si>
   <si>
     <t xml:space="preserve">6.95010662078857</t>
@@ -1922,7 +1922,7 @@
     <t xml:space="preserve">7.12561368942261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02030944824219</t>
+    <t xml:space="preserve">7.02030992507935</t>
   </si>
   <si>
     <t xml:space="preserve">7.84519481658936</t>
@@ -1943,7 +1943,7 @@
     <t xml:space="preserve">8.68763256072998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03864765167236</t>
+    <t xml:space="preserve">9.03864860534668</t>
   </si>
   <si>
     <t xml:space="preserve">9.30191040039062</t>
@@ -1961,37 +1961,37 @@
     <t xml:space="preserve">13.1192026138306</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8559408187866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0222797393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1100339889526</t>
+    <t xml:space="preserve">12.8559417724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0222806930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1100330352783</t>
   </si>
   <si>
     <t xml:space="preserve">11.9345264434814</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3641262054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8814792633057</t>
+    <t xml:space="preserve">11.36412525177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.88148021698</t>
   </si>
   <si>
     <t xml:space="preserve">12.1539115905762</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6712636947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7151412963867</t>
+    <t xml:space="preserve">11.6712646484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.715142250061</t>
   </si>
   <si>
     <t xml:space="preserve">11.4518795013428</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0569887161255</t>
+    <t xml:space="preserve">11.0569877624512</t>
   </si>
   <si>
     <t xml:space="preserve">11.4957571029663</t>
@@ -2000,7 +2000,7 @@
     <t xml:space="preserve">11.4080018997192</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8906497955322</t>
+    <t xml:space="preserve">11.8906488418579</t>
   </si>
   <si>
     <t xml:space="preserve">11.8028955459595</t>
@@ -2009,7 +2009,7 @@
     <t xml:space="preserve">11.3202486038208</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6273889541626</t>
+    <t xml:space="preserve">11.6273880004883</t>
   </si>
   <si>
     <t xml:space="preserve">11.1447401046753</t>
@@ -2024,13 +2024,13 @@
     <t xml:space="preserve">10.5743398666382</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7498502731323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6620941162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3549556732178</t>
+    <t xml:space="preserve">10.749849319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6620950698853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3549566268921</t>
   </si>
   <si>
     <t xml:space="preserve">9.78455638885498</t>
@@ -2051,7 +2051,7 @@
     <t xml:space="preserve">11.1008634567261</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3553495407104</t>
+    <t xml:space="preserve">11.3553504943848</t>
   </si>
   <si>
     <t xml:space="preserve">11.2675971984863</t>
@@ -2075,13 +2075,13 @@
     <t xml:space="preserve">11.8467721939087</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9871778488159</t>
+    <t xml:space="preserve">11.9871788024902</t>
   </si>
   <si>
     <t xml:space="preserve">12.2855415344238</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2504396438599</t>
+    <t xml:space="preserve">12.2504405975342</t>
   </si>
   <si>
     <t xml:space="preserve">12.1626853942871</t>
@@ -2090,13 +2090,13 @@
     <t xml:space="preserve">12.4672012329102</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0372972488403</t>
+    <t xml:space="preserve">12.0372982025146</t>
   </si>
   <si>
     <t xml:space="preserve">12.0910348892212</t>
   </si>
   <si>
-    <t xml:space="preserve">11.553656578064</t>
+    <t xml:space="preserve">11.5536575317383</t>
   </si>
   <si>
     <t xml:space="preserve">11.6432189941406</t>
@@ -2114,22 +2114,22 @@
     <t xml:space="preserve">10.6759366989136</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9088020324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7117624282837</t>
+    <t xml:space="preserve">10.9088010787964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7117614746094</t>
   </si>
   <si>
     <t xml:space="preserve">10.6580228805542</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9267129898071</t>
+    <t xml:space="preserve">10.9267139434814</t>
   </si>
   <si>
     <t xml:space="preserve">11.0521030426025</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4999189376831</t>
+    <t xml:space="preserve">11.4999179840088</t>
   </si>
   <si>
     <t xml:space="preserve">11.482006072998</t>
@@ -2147,7 +2147,7 @@
     <t xml:space="preserve">11.356616973877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3207921981812</t>
+    <t xml:space="preserve">11.3207931518555</t>
   </si>
   <si>
     <t xml:space="preserve">11.4461803436279</t>
@@ -2156,13 +2156,13 @@
     <t xml:space="preserve">11.464093208313</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7148694992065</t>
+    <t xml:space="preserve">11.7148704528809</t>
   </si>
   <si>
     <t xml:space="preserve">11.7327833175659</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7506952285767</t>
+    <t xml:space="preserve">11.750696182251</t>
   </si>
   <si>
     <t xml:space="preserve">12.1805992126465</t>
@@ -2174,7 +2174,7 @@
     <t xml:space="preserve">12.0731220245361</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3418121337891</t>
+    <t xml:space="preserve">12.3418111801147</t>
   </si>
   <si>
     <t xml:space="preserve">12.3597249984741</t>
@@ -2186,7 +2186,7 @@
     <t xml:space="preserve">12.1268606185913</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0552110671997</t>
+    <t xml:space="preserve">12.0552101135254</t>
   </si>
   <si>
     <t xml:space="preserve">11.8581705093384</t>
@@ -2201,13 +2201,13 @@
     <t xml:space="preserve">12.5925903320312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5030269622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9835605621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.323899269104</t>
+    <t xml:space="preserve">12.503026008606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9835596084595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3239002227783</t>
   </si>
   <si>
     <t xml:space="preserve">10.9804515838623</t>
@@ -2225,7 +2225,7 @@
     <t xml:space="preserve">11.8939962387085</t>
   </si>
   <si>
-    <t xml:space="preserve">11.768609046936</t>
+    <t xml:space="preserve">11.7686080932617</t>
   </si>
   <si>
     <t xml:space="preserve">11.6253061294556</t>
@@ -2240,10 +2240,10 @@
     <t xml:space="preserve">11.9656476974487</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1985120773315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.43137550354</t>
+    <t xml:space="preserve">12.1985111236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4313764572144</t>
   </si>
   <si>
     <t xml:space="preserve">12.2522506713867</t>
@@ -2267,7 +2267,7 @@
     <t xml:space="preserve">14.2405519485474</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0972518920898</t>
+    <t xml:space="preserve">14.0972509384155</t>
   </si>
   <si>
     <t xml:space="preserve">14.3301162719727</t>
@@ -2276,10 +2276,10 @@
     <t xml:space="preserve">14.4734172821045</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5988063812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8823013305664</t>
+    <t xml:space="preserve">14.5988054275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8823003768921</t>
   </si>
   <si>
     <t xml:space="preserve">13.8643865585327</t>
@@ -2291,7 +2291,7 @@
     <t xml:space="preserve">13.4703102111816</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6852617263794</t>
+    <t xml:space="preserve">13.6852607727051</t>
   </si>
   <si>
     <t xml:space="preserve">13.6673488616943</t>
@@ -2309,25 +2309,25 @@
     <t xml:space="preserve">13.953950881958</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344835281372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7210855484009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5240468978882</t>
+    <t xml:space="preserve">13.4344844818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7210865020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5240478515625</t>
   </si>
   <si>
     <t xml:space="preserve">13.7031736373901</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2553577423096</t>
+    <t xml:space="preserve">13.2553567886353</t>
   </si>
   <si>
     <t xml:space="preserve">13.4523973464966</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3090944290161</t>
+    <t xml:space="preserve">13.3090953826904</t>
   </si>
   <si>
     <t xml:space="preserve">14.2763776779175</t>
@@ -2348,16 +2348,16 @@
     <t xml:space="preserve">16.7124996185303</t>
   </si>
   <si>
-    <t xml:space="preserve">16.336332321167</t>
+    <t xml:space="preserve">16.3363342285156</t>
   </si>
   <si>
     <t xml:space="preserve">17.7156047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2498760223389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6591281890869</t>
+    <t xml:space="preserve">17.2498779296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6591300964355</t>
   </si>
   <si>
     <t xml:space="preserve">21.3160457611084</t>
@@ -2369,19 +2369,19 @@
     <t xml:space="preserve">21.5399551391602</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2116813659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.987771987915</t>
+    <t xml:space="preserve">22.2116794586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9877700805664</t>
   </si>
   <si>
     <t xml:space="preserve">21.2712669372559</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0177516937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3460235595703</t>
+    <t xml:space="preserve">23.017749786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3460254669189</t>
   </si>
   <si>
     <t xml:space="preserve">22.1221160888672</t>
@@ -2393,13 +2393,13 @@
     <t xml:space="preserve">21.8982086181641</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4355869293213</t>
+    <t xml:space="preserve">22.4355888366699</t>
   </si>
   <si>
     <t xml:space="preserve">21.495174407959</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7190818786621</t>
+    <t xml:space="preserve">21.7190837860107</t>
   </si>
   <si>
     <t xml:space="preserve">21.9429912567139</t>
@@ -2408,7 +2408,7 @@
     <t xml:space="preserve">21.7638645172119</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8534259796143</t>
+    <t xml:space="preserve">21.8534278869629</t>
   </si>
   <si>
     <t xml:space="preserve">23.3312206268311</t>
@@ -2423,16 +2423,16 @@
     <t xml:space="preserve">25.3016128540039</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2420234680176</t>
+    <t xml:space="preserve">26.2420253753662</t>
   </si>
   <si>
     <t xml:space="preserve">25.525520324707</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2120475769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8837718963623</t>
+    <t xml:space="preserve">25.2120456695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8837699890137</t>
   </si>
   <si>
     <t xml:space="preserve">25.4807376861572</t>
@@ -2453,10 +2453,10 @@
     <t xml:space="preserve">25.704647064209</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4211502075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0628986358643</t>
+    <t xml:space="preserve">26.4211521148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0629005432129</t>
   </si>
   <si>
     <t xml:space="preserve">26.4659328460693</t>
@@ -2468,13 +2468,13 @@
     <t xml:space="preserve">28.6602325439453</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6750373840332</t>
+    <t xml:space="preserve">27.6750392913818</t>
   </si>
   <si>
     <t xml:space="preserve">26.7794036865234</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5554962158203</t>
+    <t xml:space="preserve">26.5554943084717</t>
   </si>
   <si>
     <t xml:space="preserve">24.9881401062012</t>
@@ -2501,7 +2501,7 @@
     <t xml:space="preserve">22.928186416626</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1968765258789</t>
+    <t xml:space="preserve">23.1968746185303</t>
   </si>
   <si>
     <t xml:space="preserve">24.1820697784424</t>
@@ -2510,7 +2510,7 @@
     <t xml:space="preserve">24.2268524169922</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4955425262451</t>
+    <t xml:space="preserve">24.4955406188965</t>
   </si>
   <si>
     <t xml:space="preserve">24.3164157867432</t>
@@ -2522,7 +2522,7 @@
     <t xml:space="preserve">23.8238182067871</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0625305175781</t>
+    <t xml:space="preserve">23.0625324249268</t>
   </si>
   <si>
     <t xml:space="preserve">23.7790355682373</t>
@@ -2534,52 +2534,52 @@
     <t xml:space="preserve">23.2416591644287</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1672687530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3167839050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6002807617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6150817871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4359550476074</t>
+    <t xml:space="preserve">25.1672668457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3167819976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6002788543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.615083694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4359569549561</t>
   </si>
   <si>
     <t xml:space="preserve">24.8985767364502</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9733371734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5107154846191</t>
+    <t xml:space="preserve">25.9733352661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5107135772705</t>
   </si>
   <si>
     <t xml:space="preserve">26.197244644165</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8689670562744</t>
+    <t xml:space="preserve">26.868968963623</t>
   </si>
   <si>
     <t xml:space="preserve">26.6450576782227</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4959106445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0480937957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9437274932861</t>
+    <t xml:space="preserve">27.4959125518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.048095703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9437255859375</t>
   </si>
   <si>
     <t xml:space="preserve">28.8841400146484</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9289207458496</t>
+    <t xml:space="preserve">28.9289226531982</t>
   </si>
   <si>
     <t xml:space="preserve">28.7050132751465</t>
@@ -2588,10 +2588,10 @@
     <t xml:space="preserve">29.7797737121582</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9885101318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6302547454834</t>
+    <t xml:space="preserve">27.9885082244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.630256652832</t>
   </si>
   <si>
     <t xml:space="preserve">27.2272205352783</t>
@@ -2606,7 +2606,7 @@
     <t xml:space="preserve">25.8389911651611</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7942085266113</t>
+    <t xml:space="preserve">25.7942066192627</t>
   </si>
   <si>
     <t xml:space="preserve">26.3315887451172</t>
@@ -2624,7 +2624,7 @@
     <t xml:space="preserve">23.4655666351318</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3615665435791</t>
+    <t xml:space="preserve">27.3615646362305</t>
   </si>
   <si>
     <t xml:space="preserve">28.0332889556885</t>
@@ -70097,7 +70097,7 @@
     </row>
     <row r="2518">
       <c r="A2518" s="1" t="n">
-        <v>45985.6911342593</v>
+        <v>45985.3333333333</v>
       </c>
       <c r="B2518" t="n">
         <v>2547</v>
@@ -70118,6 +70118,32 @@
         <v>1412</v>
       </c>
       <c r="H2518" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2519">
+      <c r="A2519" s="1" t="n">
+        <v>45986.6909953704</v>
+      </c>
+      <c r="B2519" t="n">
+        <v>8516</v>
+      </c>
+      <c r="C2519" t="n">
+        <v>19.1399993896484</v>
+      </c>
+      <c r="D2519" t="n">
+        <v>18.6000003814697</v>
+      </c>
+      <c r="E2519" t="n">
+        <v>18.9200000762939</v>
+      </c>
+      <c r="F2519" t="n">
+        <v>19.1000003814697</v>
+      </c>
+      <c r="G2519" t="s">
+        <v>1421</v>
+      </c>
+      <c r="H2519" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ARN.MI.xlsx
+++ b/data/ARN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1435" uniqueCount="1435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="1436">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,43 +38,43 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92215001583099</t>
+    <t xml:space="preserve">1.92215013504028</t>
   </si>
   <si>
     <t xml:space="preserve">ARN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94450056552887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91736078262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90778183937073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88383483886719</t>
+    <t xml:space="preserve">1.94450092315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91736054420471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90778195858002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88383448123932</t>
   </si>
   <si>
     <t xml:space="preserve">1.93172883987427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91576433181763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83434391021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83594083786011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91097438335419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.807204246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74973106384277</t>
+    <t xml:space="preserve">1.91576445102692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83434426784515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83594071865082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91097509860992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80720400810242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74973142147064</t>
   </si>
   <si>
     <t xml:space="preserve">1.71620559692383</t>
@@ -83,31 +83,31 @@
     <t xml:space="preserve">1.80401134490967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81039714813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79602909088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77208209037781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70662653446198</t>
+    <t xml:space="preserve">1.81039690971375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79602885246277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77208185195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70662665367126</t>
   </si>
   <si>
     <t xml:space="preserve">1.69704782962799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69066202640533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67629361152649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7002409696579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69864439964294</t>
+    <t xml:space="preserve">1.69066178798676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67629384994507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70024073123932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69864416122437</t>
   </si>
   <si>
     <t xml:space="preserve">1.67469727993011</t>
@@ -116,70 +116,70 @@
     <t xml:space="preserve">1.6667149066925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66032910346985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81518650054932</t>
+    <t xml:space="preserve">1.66032874584198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8151867389679</t>
   </si>
   <si>
     <t xml:space="preserve">1.8279584646225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86148428916931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88543128967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89181697368622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92853605747223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95407974720001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90618550777435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86787009239197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88064181804657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85190534591675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85988771915436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85509824752808</t>
+    <t xml:space="preserve">1.86148405075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88543140888214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89181709289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92853569984436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95407903194427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90618515014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86787021160126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88064193725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85190522670746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85988759994507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85509848594666</t>
   </si>
   <si>
     <t xml:space="preserve">1.79283618927002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78804636001587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78006422519684</t>
+    <t xml:space="preserve">1.78804671764374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78006410598755</t>
   </si>
   <si>
     <t xml:space="preserve">1.75611734390259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76888906955719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7640997171402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78485369682312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77048552036285</t>
+    <t xml:space="preserve">1.76888918876648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76409983634949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7848539352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77048528194427</t>
   </si>
   <si>
     <t xml:space="preserve">1.72099483013153</t>
@@ -188,61 +188,61 @@
     <t xml:space="preserve">1.7353630065918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80241477489471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76250314712524</t>
+    <t xml:space="preserve">1.802414894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76250302791595</t>
   </si>
   <si>
     <t xml:space="preserve">1.74494206905365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73216998577118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73695957660675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74334561824799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75132775306702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68587279319763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67789030075073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65234661102295</t>
+    <t xml:space="preserve">1.73217010498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73695969581604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74334526062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7513279914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68587267398834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67789018154144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65234649181366</t>
   </si>
   <si>
     <t xml:space="preserve">1.6204172372818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64276814460754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59008431434631</t>
+    <t xml:space="preserve">1.64276778697968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59008419513702</t>
   </si>
   <si>
     <t xml:space="preserve">1.60285592079163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54937434196472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51185727119446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45598077774048</t>
+    <t xml:space="preserve">1.54937446117401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51185739040375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45598089694977</t>
   </si>
   <si>
     <t xml:space="preserve">1.43682312965393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4695508480072</t>
+    <t xml:space="preserve">1.46955096721649</t>
   </si>
   <si>
     <t xml:space="preserve">1.49748909473419</t>
@@ -251,10 +251,10 @@
     <t xml:space="preserve">1.47673487663269</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47274386882782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46875262260437</t>
+    <t xml:space="preserve">1.47274374961853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46875250339508</t>
   </si>
   <si>
     <t xml:space="preserve">1.49669086933136</t>
@@ -263,49 +263,49 @@
     <t xml:space="preserve">1.47593665122986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50626957416534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47753310203552</t>
+    <t xml:space="preserve">1.50626969337463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4775333404541</t>
   </si>
   <si>
     <t xml:space="preserve">1.43841958045959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40090262889862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34901738166809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30910563468933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34342956542969</t>
+    <t xml:space="preserve">1.40090250968933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34901750087738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30910539627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34342968463898</t>
   </si>
   <si>
     <t xml:space="preserve">1.32666671276093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3410347700119</t>
+    <t xml:space="preserve">1.34103500843048</t>
   </si>
   <si>
     <t xml:space="preserve">1.31708788871765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38653421401978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39691150188446</t>
+    <t xml:space="preserve">1.38653433322906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39691138267517</t>
   </si>
   <si>
     <t xml:space="preserve">1.40649020671844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30671095848083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3234738111496</t>
+    <t xml:space="preserve">1.30671072006226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32347393035889</t>
   </si>
   <si>
     <t xml:space="preserve">1.30591261386871</t>
@@ -326,13 +326,13 @@
     <t xml:space="preserve">1.33305251598358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33704388141632</t>
+    <t xml:space="preserve">1.33704376220703</t>
   </si>
   <si>
     <t xml:space="preserve">1.30112314224243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36104881763458</t>
+    <t xml:space="preserve">1.36104893684387</t>
   </si>
   <si>
     <t xml:space="preserve">1.34627258777618</t>
@@ -341,76 +341,76 @@
     <t xml:space="preserve">1.35283970832825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33806359767914</t>
+    <t xml:space="preserve">1.33806371688843</t>
   </si>
   <si>
     <t xml:space="preserve">1.27157092094421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28880977630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29291427135468</t>
+    <t xml:space="preserve">1.28880965709686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29291439056396</t>
   </si>
   <si>
     <t xml:space="preserve">1.30686950683594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33888447284698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34955620765686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34380996227264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33642196655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34709370136261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30522775650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29127240180969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31425726413727</t>
+    <t xml:space="preserve">1.33888459205627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34955632686615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34380984306335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33642208576202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34709358215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30522763729095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29127264022827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31425762176514</t>
   </si>
   <si>
     <t xml:space="preserve">1.32164561748505</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26828742027283</t>
+    <t xml:space="preserve">1.26828730106354</t>
   </si>
   <si>
     <t xml:space="preserve">1.27239179611206</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28798890113831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29701900482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24858593940735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32657110691071</t>
+    <t xml:space="preserve">1.28798878192902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2970187664032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24858558177948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32657098770142</t>
   </si>
   <si>
     <t xml:space="preserve">1.33231747150421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3594069480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4201534986496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48664629459381</t>
+    <t xml:space="preserve">1.35940706729889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42015337944031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48664617538452</t>
   </si>
   <si>
     <t xml:space="preserve">1.53343737125397</t>
@@ -422,70 +422,70 @@
     <t xml:space="preserve">1.51866114139557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43739259243011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46776533126831</t>
+    <t xml:space="preserve">1.43739223480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46776556968689</t>
   </si>
   <si>
     <t xml:space="preserve">1.43000423908234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40948188304901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44478023052216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55970597267151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61798977851868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70582604408264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74851274490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72388565540314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68284070491791</t>
+    <t xml:space="preserve">1.40948176383972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44478034973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5597060918808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61799001693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70582592487335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74851286411285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72388577461243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68284094333649</t>
   </si>
   <si>
     <t xml:space="preserve">1.67463171482086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65164661407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64179599285126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67134821414948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66478109359741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65657186508179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69597506523132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69433343410492</t>
+    <t xml:space="preserve">1.65164649486542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64179587364197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67134809494019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6647812128067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65657210350037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69597518444061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69433319568634</t>
   </si>
   <si>
     <t xml:space="preserve">1.65821397304535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68119919300079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68776595592499</t>
+    <t xml:space="preserve">1.6811990737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68776619434357</t>
   </si>
   <si>
     <t xml:space="preserve">1.66806471347809</t>
@@ -494,34 +494,34 @@
     <t xml:space="preserve">1.65000486373901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66313922405243</t>
+    <t xml:space="preserve">1.66313946247101</t>
   </si>
   <si>
     <t xml:space="preserve">1.67791533470154</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03746867179871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04403567314148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0391104221344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04075241088867</t>
+    <t xml:space="preserve">2.03746843338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04403591156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03911018371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04075264930725</t>
   </si>
   <si>
     <t xml:space="preserve">2.0522449016571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04731917381287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04239368438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19836473464966</t>
+    <t xml:space="preserve">2.04731965065002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04239392280579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19836497306824</t>
   </si>
   <si>
     <t xml:space="preserve">2.24105143547058</t>
@@ -533,73 +533,73 @@
     <t xml:space="preserve">2.17537975311279</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14582705497742</t>
+    <t xml:space="preserve">2.145827293396</t>
   </si>
   <si>
     <t xml:space="preserve">2.00627446174622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9882150888443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99314022064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99806582927704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99642384052277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99970734119415</t>
+    <t xml:space="preserve">1.98821485042572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99313998222351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99806547164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99642336368561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99970722198486</t>
   </si>
   <si>
     <t xml:space="preserve">2.00299119949341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00791668891907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01119947433472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02597570419312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03254318237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02105045318604</t>
+    <t xml:space="preserve">2.00791645050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01120042800903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02597641944885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03254342079163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02105069160461</t>
   </si>
   <si>
     <t xml:space="preserve">2.0194091796875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02433466911316</t>
+    <t xml:space="preserve">2.02433443069458</t>
   </si>
   <si>
     <t xml:space="preserve">2.07687187194824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05881190299988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09657335281372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14746880531311</t>
+    <t xml:space="preserve">2.05881214141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0965735912323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14746856689453</t>
   </si>
   <si>
     <t xml:space="preserve">2.33955907821655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27552914619446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32478284835815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.278813123703</t>
+    <t xml:space="preserve">2.27552890777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32478308677673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27881288528442</t>
   </si>
   <si>
     <t xml:space="preserve">2.25746941566467</t>
@@ -608,46 +608,46 @@
     <t xml:space="preserve">2.29851412773132</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26075291633606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2804548740387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30672311782837</t>
+    <t xml:space="preserve">2.26075267791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28045439720154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30672335624695</t>
   </si>
   <si>
     <t xml:space="preserve">2.35597705841064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34120059013367</t>
+    <t xml:space="preserve">2.34120082855225</t>
   </si>
   <si>
     <t xml:space="preserve">2.34284281730652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34776759147644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44627571105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39209651947021</t>
+    <t xml:space="preserve">2.34776782989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44627594947815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39209675788879</t>
   </si>
   <si>
     <t xml:space="preserve">2.38224577903748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38717126846313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38388776779175</t>
+    <t xml:space="preserve">2.38717103004456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38388752937317</t>
   </si>
   <si>
     <t xml:space="preserve">2.40523099899292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38060402870178</t>
+    <t xml:space="preserve">2.38060426712036</t>
   </si>
   <si>
     <t xml:space="preserve">2.42164874076843</t>
@@ -656,22 +656,22 @@
     <t xml:space="preserve">2.33791732788086</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32314109802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35433554649353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41015672683716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40687298774719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4380669593811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41836524009705</t>
+    <t xml:space="preserve">2.32314157485962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35433530807495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40687251091003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43806719779968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41836547851562</t>
   </si>
   <si>
     <t xml:space="preserve">2.29030537605286</t>
@@ -686,16 +686,16 @@
     <t xml:space="preserve">2.3756787776947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40194749832153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35761880874634</t>
+    <t xml:space="preserve">2.40194773674011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35761857032776</t>
   </si>
   <si>
     <t xml:space="preserve">2.36746978759766</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37075304985046</t>
+    <t xml:space="preserve">2.37075328826904</t>
   </si>
   <si>
     <t xml:space="preserve">2.37239503860474</t>
@@ -704,28 +704,28 @@
     <t xml:space="preserve">2.362544298172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36582803726196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39538025856018</t>
+    <t xml:space="preserve">2.36582779884338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39538049697876</t>
   </si>
   <si>
     <t xml:space="preserve">2.37732028961182</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37403702735901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38881301879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39373850822449</t>
+    <t xml:space="preserve">2.37403678894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38881325721741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39373826980591</t>
   </si>
   <si>
     <t xml:space="preserve">2.3904550075531</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41343975067139</t>
+    <t xml:space="preserve">2.41344022750854</t>
   </si>
   <si>
     <t xml:space="preserve">2.40358901023865</t>
@@ -734,10 +734,10 @@
     <t xml:space="preserve">2.40030574798584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40851497650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42329049110413</t>
+    <t xml:space="preserve">2.40851449966431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42329025268555</t>
   </si>
   <si>
     <t xml:space="preserve">2.43149971961975</t>
@@ -746,64 +746,64 @@
     <t xml:space="preserve">2.42000722885132</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35105156898499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33627557754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34612631797791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43642497062683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42657423019409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42985820770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45284271240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47701334953308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.478679895401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49201512336731</t>
+    <t xml:space="preserve">2.35105204582214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33627533912659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34612655639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43642520904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42657446861267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42985773086548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45284295082092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47701287269592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47868013381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49201560020447</t>
   </si>
   <si>
     <t xml:space="preserve">2.49368214607239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47534608840942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46534442901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48201370239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46867823600769</t>
+    <t xml:space="preserve">2.475346326828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46534490585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48201394081116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46867847442627</t>
   </si>
   <si>
     <t xml:space="preserve">2.45867705345154</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46201086044312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45534324645996</t>
+    <t xml:space="preserve">2.46201109886169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45534348487854</t>
   </si>
   <si>
     <t xml:space="preserve">2.41700482368469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40867018699646</t>
+    <t xml:space="preserve">2.40866994857788</t>
   </si>
   <si>
     <t xml:space="preserve">2.36699771881104</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">2.34199404716492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36866450309753</t>
+    <t xml:space="preserve">2.36866474151611</t>
   </si>
   <si>
     <t xml:space="preserve">2.35366272926331</t>
@@ -821,7 +821,7 @@
     <t xml:space="preserve">2.38533353805542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38366627693176</t>
+    <t xml:space="preserve">2.38366651535034</t>
   </si>
   <si>
     <t xml:space="preserve">2.36366391181946</t>
@@ -842,25 +842,25 @@
     <t xml:space="preserve">2.29698801040649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31532382965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28365254402161</t>
+    <t xml:space="preserve">2.31532406806946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28365278244019</t>
   </si>
   <si>
     <t xml:space="preserve">2.28865337371826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29032039642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30198860168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30365586280823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2936544418335</t>
+    <t xml:space="preserve">2.29032015800476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30198884010315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30365538597107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29365420341492</t>
   </si>
   <si>
     <t xml:space="preserve">2.24198031425476</t>
@@ -869,10 +869,10 @@
     <t xml:space="preserve">2.2669837474823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2686505317688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32699179649353</t>
+    <t xml:space="preserve">2.26865029335022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32699227333069</t>
   </si>
   <si>
     <t xml:space="preserve">2.31865763664246</t>
@@ -881,43 +881,43 @@
     <t xml:space="preserve">2.3103232383728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24364733695984</t>
+    <t xml:space="preserve">2.24364709854126</t>
   </si>
   <si>
     <t xml:space="preserve">2.25031471252441</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22531127929688</t>
+    <t xml:space="preserve">2.22531151771545</t>
   </si>
   <si>
     <t xml:space="preserve">2.25198149681091</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2219774723053</t>
+    <t xml:space="preserve">2.22197699546814</t>
   </si>
   <si>
     <t xml:space="preserve">2.20697546005249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20030760765076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16863656044006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17863774299622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16696977615356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18697285652161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19697403907776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18363881111145</t>
+    <t xml:space="preserve">2.20030784606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16863632202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17863798141479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16697001457214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18697261810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19697427749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18363857269287</t>
   </si>
   <si>
     <t xml:space="preserve">2.18530559539795</t>
@@ -926,28 +926,28 @@
     <t xml:space="preserve">2.19197344779968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17530417442322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14196586608887</t>
+    <t xml:space="preserve">2.1753044128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14196634292603</t>
   </si>
   <si>
     <t xml:space="preserve">2.15363478660583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1436333656311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13529896736145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12696385383606</t>
+    <t xml:space="preserve">2.14363288879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13529849052429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12696409225464</t>
   </si>
   <si>
     <t xml:space="preserve">2.12863087654114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12029623985291</t>
+    <t xml:space="preserve">2.12029671669006</t>
   </si>
   <si>
     <t xml:space="preserve">2.13029789924622</t>
@@ -959,64 +959,64 @@
     <t xml:space="preserve">2.37366533279419</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37533235549927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40700340270996</t>
+    <t xml:space="preserve">2.37533211708069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40700364112854</t>
   </si>
   <si>
     <t xml:space="preserve">2.39533519744873</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39200115203857</t>
+    <t xml:space="preserve">2.39200139045715</t>
   </si>
   <si>
     <t xml:space="preserve">2.49868273735046</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49534893035889</t>
+    <t xml:space="preserve">2.49534869194031</t>
   </si>
   <si>
     <t xml:space="preserve">2.5086841583252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51201772689819</t>
+    <t xml:space="preserve">2.51201820373535</t>
   </si>
   <si>
     <t xml:space="preserve">2.51535153388977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51701903343201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52368664741516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52535319328308</t>
+    <t xml:space="preserve">2.51701879501343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.523686170578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5253529548645</t>
   </si>
   <si>
     <t xml:space="preserve">2.54535603523254</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53368759155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53202080726624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54035520553589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52702045440674</t>
+    <t xml:space="preserve">2.53368735313416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53202104568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54035544395447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52702021598816</t>
   </si>
   <si>
     <t xml:space="preserve">2.53868818283081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53702163696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49701619148254</t>
+    <t xml:space="preserve">2.53702139854431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49701571464539</t>
   </si>
   <si>
     <t xml:space="preserve">2.42700624465942</t>
@@ -1028,76 +1028,76 @@
     <t xml:space="preserve">2.50535035133362</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48368048667908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45200943946838</t>
+    <t xml:space="preserve">2.48368096351624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45200967788696</t>
   </si>
   <si>
     <t xml:space="preserve">2.51368498802185</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54202198982239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54868984222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51035094261169</t>
+    <t xml:space="preserve">2.54202222824097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5486900806427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51035141944885</t>
   </si>
   <si>
     <t xml:space="preserve">2.52035236358643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47201251983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50201678276062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48701477050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00041937828064</t>
+    <t xml:space="preserve">2.472012758255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5020170211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48701453208923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00041961669922</t>
   </si>
   <si>
     <t xml:space="preserve">2.81706094741821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75038456916809</t>
+    <t xml:space="preserve">2.75038433074951</t>
   </si>
   <si>
     <t xml:space="preserve">2.7170467376709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8087260723114</t>
+    <t xml:space="preserve">2.80872583389282</t>
   </si>
   <si>
     <t xml:space="preserve">2.80039143562317</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8337299823761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78372263908386</t>
+    <t xml:space="preserve">2.83372974395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78372287750244</t>
   </si>
   <si>
     <t xml:space="preserve">2.84206414222717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75871920585632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85039877891541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85873341560364</t>
+    <t xml:space="preserve">2.75871896743774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85039830207825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85873293876648</t>
   </si>
   <si>
     <t xml:space="preserve">2.89207124710083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82539510726929</t>
+    <t xml:space="preserve">2.82539558410645</t>
   </si>
   <si>
     <t xml:space="preserve">2.72538113594055</t>
@@ -1106,28 +1106,28 @@
     <t xml:space="preserve">2.61703276634216</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64203596115112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70037746429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65870499610901</t>
+    <t xml:space="preserve">2.6420361995697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70037770271301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65870523452759</t>
   </si>
   <si>
     <t xml:space="preserve">2.62536716461182</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63370203971863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59202885627747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66703987121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70871210098267</t>
+    <t xml:space="preserve">2.63370180130005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59202909469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66703963279724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70871233940125</t>
   </si>
   <si>
     <t xml:space="preserve">2.74205017089844</t>
@@ -1139,64 +1139,64 @@
     <t xml:space="preserve">2.68370866775513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6003634929657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58369469642639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56702589988708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76705384254456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73371577262878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79205727577209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86706757545471</t>
+    <t xml:space="preserve">2.60036325454712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58369493484497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56702566146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76705360412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73371553421021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79205703735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86706805229187</t>
   </si>
   <si>
     <t xml:space="preserve">2.87540221214294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8837366104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77538776397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78091430664062</t>
+    <t xml:space="preserve">2.88373637199402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77538824081421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78091382980347</t>
   </si>
   <si>
     <t xml:space="preserve">2.72174549102783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7301983833313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77246141433716</t>
+    <t xml:space="preserve">2.73019814491272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7724609375</t>
   </si>
   <si>
     <t xml:space="preserve">2.645672082901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70483994483948</t>
+    <t xml:space="preserve">2.70484042167664</t>
   </si>
   <si>
     <t xml:space="preserve">2.68793487548828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66257739067078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69638752937317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65412449836731</t>
+    <t xml:space="preserve">2.66257691383362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69638776779175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65412473678589</t>
   </si>
   <si>
     <t xml:space="preserve">2.60340857505798</t>
@@ -1205,7 +1205,7 @@
     <t xml:space="preserve">2.63721895217896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61186146736145</t>
+    <t xml:space="preserve">2.61186099052429</t>
   </si>
   <si>
     <t xml:space="preserve">2.5780508518219</t>
@@ -1220,46 +1220,46 @@
     <t xml:space="preserve">2.4935245513916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54424023628235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5611457824707</t>
+    <t xml:space="preserve">2.54424047470093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56114530563354</t>
   </si>
   <si>
     <t xml:space="preserve">2.58650326728821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51888227462769</t>
+    <t xml:space="preserve">2.51888251304626</t>
   </si>
   <si>
     <t xml:space="preserve">2.53578782081604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55269312858582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5104296207428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56959843635559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46816658973694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48507189750671</t>
+    <t xml:space="preserve">2.55269289016724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51043009757996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56959795951843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46816682815552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48507213592529</t>
   </si>
   <si>
     <t xml:space="preserve">2.41745066642761</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45126175880432</t>
+    <t xml:space="preserve">2.45126128196716</t>
   </si>
   <si>
     <t xml:space="preserve">2.39209294319153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38364028930664</t>
+    <t xml:space="preserve">2.3836407661438</t>
   </si>
   <si>
     <t xml:space="preserve">2.27375650405884</t>
@@ -1268,40 +1268,40 @@
     <t xml:space="preserve">2.29911422729492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36673521995544</t>
+    <t xml:space="preserve">2.36673498153687</t>
   </si>
   <si>
     <t xml:space="preserve">2.35828256607056</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43435645103455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4259033203125</t>
+    <t xml:space="preserve">2.43435668945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42590379714966</t>
   </si>
   <si>
     <t xml:space="preserve">2.34982991218567</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28220868110657</t>
+    <t xml:space="preserve">2.28220891952515</t>
   </si>
   <si>
     <t xml:space="preserve">2.32447218894958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40899848937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45971441268921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44280886650085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33292484283447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34137749671936</t>
+    <t xml:space="preserve">2.4089982509613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45971393585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44280862808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33292460441589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3413770198822</t>
   </si>
   <si>
     <t xml:space="preserve">2.40054559707642</t>
@@ -1310,103 +1310,103 @@
     <t xml:space="preserve">2.37518787384033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47661924362183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30756664276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23994612693787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29430222511292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2343761920929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2429370880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33710622787476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25149846076965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27718067169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26862001419067</t>
+    <t xml:space="preserve">2.47661948204041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30756711959839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23994541168213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29430246353149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23437666893005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24293732643127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33710670471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25149822235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27718091011047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26861953735352</t>
   </si>
   <si>
     <t xml:space="preserve">2.44839692115784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37135004997253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31142377853394</t>
+    <t xml:space="preserve">2.37134957313538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31142401695251</t>
   </si>
   <si>
     <t xml:space="preserve">2.28574156761169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26005887985229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35422825813293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22581553459167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20869421958923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30286335945129</t>
+    <t xml:space="preserve">2.26005911827087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35422801971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22581601142883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20869398117065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30286312103271</t>
   </si>
   <si>
     <t xml:space="preserve">2.31998491287231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37991046905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40559315681458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39703226089478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32854557037354</t>
+    <t xml:space="preserve">2.37991070747375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.405592918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3970320224762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32854580879211</t>
   </si>
   <si>
     <t xml:space="preserve">2.38847136497498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36278915405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34566712379456</t>
+    <t xml:space="preserve">2.36278891563416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34566736221313</t>
   </si>
   <si>
     <t xml:space="preserve">2.20013308525085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18301153182983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4398365020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5425660610199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6024923324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69666147232056</t>
+    <t xml:space="preserve">2.18301177024841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43983626365662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54256653785706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60249185562134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69666123390198</t>
   </si>
   <si>
     <t xml:space="preserve">2.77370882034302</t>
@@ -1427,7 +1427,7 @@
     <t xml:space="preserve">2.68810057640076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64529633522034</t>
+    <t xml:space="preserve">2.64529609680176</t>
   </si>
   <si>
     <t xml:space="preserve">2.71378302574158</t>
@@ -1439,28 +1439,28 @@
     <t xml:space="preserve">3.07333755493164</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52706170082092</t>
+    <t xml:space="preserve">3.52706146240234</t>
   </si>
   <si>
     <t xml:space="preserve">3.59554815292358</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65547442436218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58698797225952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6126697063446</t>
+    <t xml:space="preserve">3.6554741859436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58698725700378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61266946792603</t>
   </si>
   <si>
     <t xml:space="preserve">3.5356228351593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42433214187622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54418325424194</t>
+    <t xml:space="preserve">3.42433190345764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54418349266052</t>
   </si>
   <si>
     <t xml:space="preserve">3.56986618041992</t>
@@ -1475,43 +1475,43 @@
     <t xml:space="preserve">3.50993990898132</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48425769805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57842683792114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63835263252258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74108266830444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16912412643433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60572671890259</t>
+    <t xml:space="preserve">3.48425793647766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57842659950256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.638352394104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74108219146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16912364959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60572624206543</t>
   </si>
   <si>
     <t xml:space="preserve">5.15361928939819</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62284755706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19480609893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45163106918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53724002838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52011775970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58860445022583</t>
+    <t xml:space="preserve">4.62284803390503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1948070526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45163202285767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53723907470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52011823654175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58860492706299</t>
   </si>
   <si>
     <t xml:space="preserve">4.34890127182007</t>
@@ -1520,16 +1520,16 @@
     <t xml:space="preserve">4.16056346893311</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23761034011841</t>
+    <t xml:space="preserve">4.23761081695557</t>
   </si>
   <si>
     <t xml:space="preserve">4.29753637313843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89517760276794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27879738807678</t>
+    <t xml:space="preserve">3.89517712593079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27879762649536</t>
   </si>
   <si>
     <t xml:space="preserve">3.25311517715454</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">2.89356064796448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15894603729248</t>
+    <t xml:space="preserve">3.1589457988739</t>
   </si>
   <si>
     <t xml:space="preserve">3.1675066947937</t>
@@ -1553,37 +1553,37 @@
     <t xml:space="preserve">3.38152766227722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39008855819702</t>
+    <t xml:space="preserve">3.39008831977844</t>
   </si>
   <si>
     <t xml:space="preserve">3.84381246566772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83525133132935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87805581092834</t>
+    <t xml:space="preserve">3.83525156974792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87805604934692</t>
   </si>
   <si>
     <t xml:space="preserve">3.76676464080811</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88661694526672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8523736000061</t>
+    <t xml:space="preserve">3.88661670684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85237312316895</t>
   </si>
   <si>
     <t xml:space="preserve">3.92942142486572</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95510292053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93798160552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11775875091553</t>
+    <t xml:space="preserve">3.95510339736938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93798136711121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11775922775269</t>
   </si>
   <si>
     <t xml:space="preserve">4.25473213195801</t>
@@ -1592,10 +1592,10 @@
     <t xml:space="preserve">4.22904968261719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26329278945923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28041410446167</t>
+    <t xml:space="preserve">4.26329326629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28041505813599</t>
   </si>
   <si>
     <t xml:space="preserve">4.43450927734375</t>
@@ -1604,7 +1604,7 @@
     <t xml:space="preserve">4.20336723327637</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00646781921387</t>
+    <t xml:space="preserve">4.00646829605103</t>
   </si>
   <si>
     <t xml:space="preserve">4.10919857025146</t>
@@ -1613,13 +1613,13 @@
     <t xml:space="preserve">4.15200233459473</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08351612091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94654226303101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07495498657227</t>
+    <t xml:space="preserve">4.08351564407349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94654250144958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07495450973511</t>
   </si>
   <si>
     <t xml:space="preserve">4.02358961105347</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">3.96366405487061</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13488101959229</t>
+    <t xml:space="preserve">4.13488054275513</t>
   </si>
   <si>
     <t xml:space="preserve">4.12631988525391</t>
@@ -1637,73 +1637,73 @@
     <t xml:space="preserve">5.01664590835571</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70845651626587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91391563415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96528148651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94815969467163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20498466491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56453895568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68439054489136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95833778381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90697193145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88985013961792</t>
+    <t xml:space="preserve">4.70845603942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91391611099243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96528100967407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94815921783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20498371124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56453943252563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6843900680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95833683013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90697240829468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88985109329224</t>
   </si>
   <si>
     <t xml:space="preserve">6.57471656799316</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12955284118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40350103378296</t>
+    <t xml:space="preserve">6.12955379486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4035005569458</t>
   </si>
   <si>
     <t xml:space="preserve">7.01987981796265</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20821809768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32807016372681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05412340164185</t>
+    <t xml:space="preserve">7.20821857452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32807064056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05412292480469</t>
   </si>
   <si>
     <t xml:space="preserve">7.00275897979736</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42397689819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28357124328613</t>
+    <t xml:space="preserve">7.42397737503052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28357076644897</t>
   </si>
   <si>
     <t xml:space="preserve">6.8799033164978</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96765661239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59909105300903</t>
+    <t xml:space="preserve">6.9676570892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59909057617188</t>
   </si>
   <si>
     <t xml:space="preserve">6.51133728027344</t>
@@ -1712,19 +1712,19 @@
     <t xml:space="preserve">6.73949670791626</t>
   </si>
   <si>
-    <t xml:space="preserve">6.844801902771</t>
+    <t xml:space="preserve">6.84480142593384</t>
   </si>
   <si>
     <t xml:space="preserve">6.82725095748901</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68684482574463</t>
+    <t xml:space="preserve">6.68684434890747</t>
   </si>
   <si>
     <t xml:space="preserve">6.66929388046265</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45868492126465</t>
+    <t xml:space="preserve">6.45868539810181</t>
   </si>
   <si>
     <t xml:space="preserve">6.40603256225586</t>
@@ -1736,25 +1736,25 @@
     <t xml:space="preserve">6.80970001220703</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17826700210571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35377502441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26601982116699</t>
+    <t xml:space="preserve">7.17826652526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35377407073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26602077484131</t>
   </si>
   <si>
     <t xml:space="preserve">7.05541086196899</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07296228408813</t>
+    <t xml:space="preserve">7.07296276092529</t>
   </si>
   <si>
     <t xml:space="preserve">6.63419198989868</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44113445281982</t>
+    <t xml:space="preserve">6.44113397598267</t>
   </si>
   <si>
     <t xml:space="preserve">6.30072736740112</t>
@@ -1763,34 +1763,34 @@
     <t xml:space="preserve">6.05501651763916</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03746557235718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37053632736206</t>
+    <t xml:space="preserve">6.03746604919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37053680419922</t>
   </si>
   <si>
     <t xml:space="preserve">5.40563821792603</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52849388122559</t>
+    <t xml:space="preserve">5.52849340438843</t>
   </si>
   <si>
     <t xml:space="preserve">5.65134906768799</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12522029876709</t>
+    <t xml:space="preserve">6.12521982192993</t>
   </si>
   <si>
     <t xml:space="preserve">5.96726322174072</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01991558074951</t>
+    <t xml:space="preserve">6.01991510391235</t>
   </si>
   <si>
     <t xml:space="preserve">5.91460990905762</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84440755844116</t>
+    <t xml:space="preserve">5.844407081604</t>
   </si>
   <si>
     <t xml:space="preserve">5.94971179962158</t>
@@ -1814,22 +1814,22 @@
     <t xml:space="preserve">5.68645048141479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4582896232605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63379859924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70400094985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58114576339722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66890048980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56359529495239</t>
+    <t xml:space="preserve">5.45829057693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63379812240601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70400142669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58114624023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66890001296997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56359577178955</t>
   </si>
   <si>
     <t xml:space="preserve">5.61624717712402</t>
@@ -1850,25 +1850,25 @@
     <t xml:space="preserve">5.28278255462646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35298585891724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42318916320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47584056854248</t>
+    <t xml:space="preserve">5.35298633575439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42318868637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47584104537964</t>
   </si>
   <si>
     <t xml:space="preserve">5.38808727264404</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5109429359436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77420520782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44074010848999</t>
+    <t xml:space="preserve">5.51094341278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77420473098755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44073963165283</t>
   </si>
   <si>
     <t xml:space="preserve">5.54604482650757</t>
@@ -1880,7 +1880,7 @@
     <t xml:space="preserve">6.35338020324707</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16032123565674</t>
+    <t xml:space="preserve">6.1603217124939</t>
   </si>
   <si>
     <t xml:space="preserve">6.37093067169189</t>
@@ -1898,13 +1898,13 @@
     <t xml:space="preserve">6.98520803451538</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33622360229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09051275253296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16071510314941</t>
+    <t xml:space="preserve">7.33622312545776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0905122756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16071557998657</t>
   </si>
   <si>
     <t xml:space="preserve">7.19581651687622</t>
@@ -1913,22 +1913,22 @@
     <t xml:space="preserve">7.00275850296021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95010662078857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14316511154175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12561368942261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02030992507935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84519481658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3366174697876</t>
+    <t xml:space="preserve">6.95010614395142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14316558837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12561416625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02030944824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84519577026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33661651611328</t>
   </si>
   <si>
     <t xml:space="preserve">8.31906604766846</t>
@@ -1937,34 +1937,34 @@
     <t xml:space="preserve">8.42437171936035</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08252620697021</t>
+    <t xml:space="preserve">9.0825252532959</t>
   </si>
   <si>
     <t xml:space="preserve">8.68763256072998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03864860534668</t>
+    <t xml:space="preserve">9.038649559021</t>
   </si>
   <si>
     <t xml:space="preserve">9.30191040039062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2763719558716</t>
+    <t xml:space="preserve">11.2763729095459</t>
   </si>
   <si>
     <t xml:space="preserve">13.1630802154541</t>
   </si>
   <si>
-    <t xml:space="preserve">13.075325012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1192026138306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8559417724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0222806930542</t>
+    <t xml:space="preserve">13.0753259658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1192035675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8559408187866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0222797393799</t>
   </si>
   <si>
     <t xml:space="preserve">12.1100330352783</t>
@@ -1976,46 +1976,46 @@
     <t xml:space="preserve">11.36412525177</t>
   </si>
   <si>
-    <t xml:space="preserve">10.88148021698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1539115905762</t>
+    <t xml:space="preserve">10.8814792633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1539106369019</t>
   </si>
   <si>
     <t xml:space="preserve">11.6712646484375</t>
   </si>
   <si>
-    <t xml:space="preserve">11.715142250061</t>
+    <t xml:space="preserve">11.7151412963867</t>
   </si>
   <si>
     <t xml:space="preserve">11.4518795013428</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0569877624512</t>
+    <t xml:space="preserve">11.0569868087769</t>
   </si>
   <si>
     <t xml:space="preserve">11.4957571029663</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4080018997192</t>
+    <t xml:space="preserve">11.4080028533936</t>
   </si>
   <si>
     <t xml:space="preserve">11.8906488418579</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8028955459595</t>
+    <t xml:space="preserve">11.8028945922852</t>
   </si>
   <si>
     <t xml:space="preserve">11.3202486038208</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6273880004883</t>
+    <t xml:space="preserve">11.627387046814</t>
   </si>
   <si>
     <t xml:space="preserve">11.1447401046753</t>
   </si>
   <si>
-    <t xml:space="preserve">10.618218421936</t>
+    <t xml:space="preserve">10.6182174682617</t>
   </si>
   <si>
     <t xml:space="preserve">10.5304641723633</t>
@@ -2027,16 +2027,16 @@
     <t xml:space="preserve">10.749849319458</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6620950698853</t>
+    <t xml:space="preserve">10.6620941162109</t>
   </si>
   <si>
     <t xml:space="preserve">10.3549566268921</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78455638885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91618728637695</t>
+    <t xml:space="preserve">9.78455543518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91618633270264</t>
   </si>
   <si>
     <t xml:space="preserve">10.0916948318481</t>
@@ -2045,19 +2045,19 @@
     <t xml:space="preserve">11.232494354248</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1886186599731</t>
+    <t xml:space="preserve">11.1886177062988</t>
   </si>
   <si>
     <t xml:space="preserve">11.1008634567261</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3553504943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2675971984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0218858718872</t>
+    <t xml:space="preserve">11.3553495407104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.267596244812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0218868255615</t>
   </si>
   <si>
     <t xml:space="preserve">11.2500457763672</t>
@@ -2075,13 +2075,13 @@
     <t xml:space="preserve">11.8467721939087</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9871788024902</t>
+    <t xml:space="preserve">11.9871768951416</t>
   </si>
   <si>
     <t xml:space="preserve">12.2855415344238</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2504405975342</t>
+    <t xml:space="preserve">12.2504396438599</t>
   </si>
   <si>
     <t xml:space="preserve">12.1626853942871</t>
@@ -2093,22 +2093,22 @@
     <t xml:space="preserve">12.0372982025146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0910348892212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5536575317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6432189941406</t>
+    <t xml:space="preserve">12.0910358428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.553656578064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6432199478149</t>
   </si>
   <si>
     <t xml:space="preserve">11.3924427032471</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9446258544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5505475997925</t>
+    <t xml:space="preserve">10.9446268081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5505485534668</t>
   </si>
   <si>
     <t xml:space="preserve">10.6759366989136</t>
@@ -2120,22 +2120,22 @@
     <t xml:space="preserve">10.7117614746094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6580228805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9267139434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0521030426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4999179840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.482006072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4282674789429</t>
+    <t xml:space="preserve">10.6580238342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9267129898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0521020889282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4999189376831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4820051193237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4282684326172</t>
   </si>
   <si>
     <t xml:space="preserve">11.571569442749</t>
@@ -2144,10 +2144,10 @@
     <t xml:space="preserve">11.3745288848877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.356616973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3207931518555</t>
+    <t xml:space="preserve">11.3566179275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3207921981812</t>
   </si>
   <si>
     <t xml:space="preserve">11.4461803436279</t>
@@ -2159,7 +2159,7 @@
     <t xml:space="preserve">11.7148704528809</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7327833175659</t>
+    <t xml:space="preserve">11.7327823638916</t>
   </si>
   <si>
     <t xml:space="preserve">11.750696182251</t>
@@ -2171,19 +2171,19 @@
     <t xml:space="preserve">12.6284151077271</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0731220245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3418111801147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3597249984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6969585418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1268606185913</t>
+    <t xml:space="preserve">12.0731229782104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3418121337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3597259521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6969575881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1268615722656</t>
   </si>
   <si>
     <t xml:space="preserve">12.0552101135254</t>
@@ -2192,13 +2192,13 @@
     <t xml:space="preserve">11.8581705093384</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9298210144043</t>
+    <t xml:space="preserve">11.9298219680786</t>
   </si>
   <si>
     <t xml:space="preserve">12.2880754470825</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5925903320312</t>
+    <t xml:space="preserve">12.5925893783569</t>
   </si>
   <si>
     <t xml:space="preserve">12.503026008606</t>
@@ -2210,16 +2210,16 @@
     <t xml:space="preserve">12.3239002227783</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9804515838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.177490234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2849674224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3387050628662</t>
+    <t xml:space="preserve">10.9804525375366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1774892807007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.284966468811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3387041091919</t>
   </si>
   <si>
     <t xml:space="preserve">11.8939962387085</t>
@@ -2228,34 +2228,34 @@
     <t xml:space="preserve">11.7686080932617</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6253061294556</t>
+    <t xml:space="preserve">11.6253051757812</t>
   </si>
   <si>
     <t xml:space="preserve">12.0014724731445</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1089487075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9656476974487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1985111236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4313764572144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2522506713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8612785339355</t>
+    <t xml:space="preserve">12.1089477539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9656467437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1985120773315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.43137550354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2522497177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8612794876099</t>
   </si>
   <si>
     <t xml:space="preserve">12.8433666229248</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6821537017822</t>
+    <t xml:space="preserve">12.6821517944336</t>
   </si>
   <si>
     <t xml:space="preserve">12.7358913421631</t>
@@ -2264,10 +2264,10 @@
     <t xml:space="preserve">13.3449201583862</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2405519485474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0972509384155</t>
+    <t xml:space="preserve">14.2405529022217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0972518920898</t>
   </si>
   <si>
     <t xml:space="preserve">14.3301162719727</t>
@@ -2282,10 +2282,10 @@
     <t xml:space="preserve">13.8823003768921</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8643865585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.577784538269</t>
+    <t xml:space="preserve">13.864387512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5777854919434</t>
   </si>
   <si>
     <t xml:space="preserve">13.4703102111816</t>
@@ -2294,7 +2294,7 @@
     <t xml:space="preserve">13.6852607727051</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6673488616943</t>
+    <t xml:space="preserve">13.6673498153687</t>
   </si>
   <si>
     <t xml:space="preserve">13.5598726272583</t>
@@ -2306,7 +2306,7 @@
     <t xml:space="preserve">13.8285617828369</t>
   </si>
   <si>
-    <t xml:space="preserve">13.953950881958</t>
+    <t xml:space="preserve">13.9539518356323</t>
   </si>
   <si>
     <t xml:space="preserve">13.4344844818115</t>
@@ -2315,19 +2315,19 @@
     <t xml:space="preserve">13.7210865020752</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5240478515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7031736373901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2553567886353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4523973464966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3090953826904</t>
+    <t xml:space="preserve">13.5240468978882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7031745910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2553577423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4523963928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3090944290161</t>
   </si>
   <si>
     <t xml:space="preserve">14.2763776779175</t>
@@ -2342,37 +2342,37 @@
     <t xml:space="preserve">13.756911277771</t>
   </si>
   <si>
-    <t xml:space="preserve">14.437593460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7124996185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3363342285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7156047821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2498779296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6591300964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3160457611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4503917694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5399551391602</t>
+    <t xml:space="preserve">14.4375944137573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7124977111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.336332321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7156066894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2498760223389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6591281890869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.316047668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4503936767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5399570465088</t>
   </si>
   <si>
     <t xml:space="preserve">22.2116794586182</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9877700805664</t>
+    <t xml:space="preserve">21.987771987915</t>
   </si>
   <si>
     <t xml:space="preserve">21.2712669372559</t>
@@ -2384,7 +2384,7 @@
     <t xml:space="preserve">22.3460254669189</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1221160888672</t>
+    <t xml:space="preserve">22.1221179962158</t>
   </si>
   <si>
     <t xml:space="preserve">23.7342548370361</t>
@@ -2399,22 +2399,22 @@
     <t xml:space="preserve">21.495174407959</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7190837860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9429912567139</t>
+    <t xml:space="preserve">21.7190818786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9429931640625</t>
   </si>
   <si>
     <t xml:space="preserve">21.7638645172119</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8534278869629</t>
+    <t xml:space="preserve">21.8534259796143</t>
   </si>
   <si>
     <t xml:space="preserve">23.3312206268311</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8086471557617</t>
+    <t xml:space="preserve">21.8086452484131</t>
   </si>
   <si>
     <t xml:space="preserve">25.3463916778564</t>
@@ -2429,10 +2429,10 @@
     <t xml:space="preserve">25.525520324707</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2120456695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8837699890137</t>
+    <t xml:space="preserve">25.2120475769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8837718963623</t>
   </si>
   <si>
     <t xml:space="preserve">25.4807376861572</t>
@@ -2447,7 +2447,7 @@
     <t xml:space="preserve">24.361198425293</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3911762237549</t>
+    <t xml:space="preserve">25.3911743164062</t>
   </si>
   <si>
     <t xml:space="preserve">25.704647064209</t>
@@ -2456,37 +2456,37 @@
     <t xml:space="preserve">26.4211521148682</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0629005432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4659328460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1524639129639</t>
+    <t xml:space="preserve">26.0628986358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.465934753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1524620056152</t>
   </si>
   <si>
     <t xml:space="preserve">28.6602325439453</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6750392913818</t>
+    <t xml:space="preserve">27.6750354766846</t>
   </si>
   <si>
     <t xml:space="preserve">26.7794036865234</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5554943084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9881401062012</t>
+    <t xml:space="preserve">26.5554962158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9881381988525</t>
   </si>
   <si>
     <t xml:space="preserve">25.2568302154541</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9581623077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0477256774902</t>
+    <t xml:space="preserve">23.9581642150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0477275848389</t>
   </si>
   <si>
     <t xml:space="preserve">23.9133815765381</t>
@@ -2504,25 +2504,25 @@
     <t xml:space="preserve">23.1968746185303</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1820697784424</t>
+    <t xml:space="preserve">24.182071685791</t>
   </si>
   <si>
     <t xml:space="preserve">24.2268524169922</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4955406188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3164157867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3908081054688</t>
+    <t xml:space="preserve">24.4955425262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3164138793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3908061981201</t>
   </si>
   <si>
     <t xml:space="preserve">23.8238182067871</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0625324249268</t>
+    <t xml:space="preserve">23.0625305175781</t>
   </si>
   <si>
     <t xml:space="preserve">23.7790355682373</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">23.2416591644287</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1672668457031</t>
+    <t xml:space="preserve">25.1672687530518</t>
   </si>
   <si>
     <t xml:space="preserve">27.3167819976807</t>
@@ -2546,16 +2546,16 @@
     <t xml:space="preserve">25.615083694458</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4359569549561</t>
+    <t xml:space="preserve">25.4359550476074</t>
   </si>
   <si>
     <t xml:space="preserve">24.8985767364502</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9733352661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5107135772705</t>
+    <t xml:space="preserve">25.9733371734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5107154846191</t>
   </si>
   <si>
     <t xml:space="preserve">26.197244644165</t>
@@ -2564,13 +2564,13 @@
     <t xml:space="preserve">26.868968963623</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6450576782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4959125518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.048095703125</t>
+    <t xml:space="preserve">26.6450595855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4959106445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0480937957764</t>
   </si>
   <si>
     <t xml:space="preserve">27.9437255859375</t>
@@ -2579,16 +2579,16 @@
     <t xml:space="preserve">28.8841400146484</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9289226531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7050132751465</t>
+    <t xml:space="preserve">28.9289207458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7050151824951</t>
   </si>
   <si>
     <t xml:space="preserve">29.7797737121582</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9885082244873</t>
+    <t xml:space="preserve">27.9885063171387</t>
   </si>
   <si>
     <t xml:space="preserve">27.630256652832</t>
@@ -2597,40 +2597,40 @@
     <t xml:space="preserve">27.2272205352783</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4063472747803</t>
+    <t xml:space="preserve">27.4063491821289</t>
   </si>
   <si>
     <t xml:space="preserve">26.6898403167725</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8389911651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7942066192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3315887451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7194499969482</t>
+    <t xml:space="preserve">25.8389930725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.79421043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3315868377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7194519042969</t>
   </si>
   <si>
     <t xml:space="preserve">24.4507598876953</t>
   </si>
   <si>
-    <t xml:space="preserve">23.599910736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4655666351318</t>
+    <t xml:space="preserve">23.5999126434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4655647277832</t>
   </si>
   <si>
     <t xml:space="preserve">27.3615646362305</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0332889556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8541622161865</t>
+    <t xml:space="preserve">28.0332908630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8541641235352</t>
   </si>
   <si>
     <t xml:space="preserve">28.163049697876</t>
@@ -2642,7 +2642,7 @@
     <t xml:space="preserve">30.2979869842529</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8911685943604</t>
+    <t xml:space="preserve">26.891170501709</t>
   </si>
   <si>
     <t xml:space="preserve">27.3454132080078</t>
@@ -2663,10 +2663,10 @@
     <t xml:space="preserve">30.57053565979</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0247802734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0702037811279</t>
+    <t xml:space="preserve">31.0247821807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0702018737793</t>
   </si>
   <si>
     <t xml:space="preserve">30.8885059356689</t>
@@ -2681,19 +2681,19 @@
     <t xml:space="preserve">27.9359283447266</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4362621307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0722026824951</t>
+    <t xml:space="preserve">27.4362602233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0722007751465</t>
   </si>
   <si>
     <t xml:space="preserve">28.4355945587158</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5264434814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4810180664062</t>
+    <t xml:space="preserve">28.5264415740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4810199737549</t>
   </si>
   <si>
     <t xml:space="preserve">28.3901710510254</t>
@@ -2705,22 +2705,22 @@
     <t xml:space="preserve">29.434928894043</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2538967132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1169586181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1162929534912</t>
+    <t xml:space="preserve">28.2538986206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1169605255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1162948608398</t>
   </si>
   <si>
     <t xml:space="preserve">30.9793529510498</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1610507965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4790210723877</t>
+    <t xml:space="preserve">31.1610488891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.479024887085</t>
   </si>
   <si>
     <t xml:space="preserve">31.5698719024658</t>
@@ -2729,7 +2729,7 @@
     <t xml:space="preserve">31.7969932556152</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7515697479248</t>
+    <t xml:space="preserve">31.7515678405762</t>
   </si>
   <si>
     <t xml:space="preserve">31.1156272888184</t>
@@ -2744,43 +2744,43 @@
     <t xml:space="preserve">33.8410835266113</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4770240783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3861770629883</t>
+    <t xml:space="preserve">34.4770278930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.386173248291</t>
   </si>
   <si>
     <t xml:space="preserve">34.5678672790527</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6132965087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3400840759277</t>
+    <t xml:space="preserve">34.6132926940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.340087890625</t>
   </si>
   <si>
     <t xml:space="preserve">34.4316024780273</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7048110961914</t>
+    <t xml:space="preserve">33.7048072814941</t>
   </si>
   <si>
     <t xml:space="preserve">33.9773559570312</t>
   </si>
   <si>
-    <t xml:space="preserve">34.931266784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5224456787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0682029724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7502365112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9319343566895</t>
+    <t xml:space="preserve">34.9312705993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5224494934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0682067871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7502326965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9319305419922</t>
   </si>
   <si>
     <t xml:space="preserve">34.2499008178711</t>
@@ -2795,16 +2795,16 @@
     <t xml:space="preserve">36.6573867797852</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7936630249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6106338500977</t>
+    <t xml:space="preserve">36.7936592102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6106300354004</t>
   </si>
   <si>
     <t xml:space="preserve">39.5645408630371</t>
   </si>
   <si>
-    <t xml:space="preserve">38.110969543457</t>
+    <t xml:space="preserve">38.1109657287598</t>
   </si>
   <si>
     <t xml:space="preserve">36.4302635192871</t>
@@ -2819,13 +2819,13 @@
     <t xml:space="preserve">33.0688743591309</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3414192199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8865051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2044830322266</t>
+    <t xml:space="preserve">33.3414154052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8865089416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2044792175293</t>
   </si>
   <si>
     <t xml:space="preserve">34.340747833252</t>
@@ -2840,16 +2840,16 @@
     <t xml:space="preserve">32.9780197143555</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7976551055908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3895053863525</t>
+    <t xml:space="preserve">30.7976570129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3895034790039</t>
   </si>
   <si>
     <t xml:space="preserve">29.5257778167725</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6172924041748</t>
+    <t xml:space="preserve">28.6172904968262</t>
   </si>
   <si>
     <t xml:space="preserve">28.3447456359863</t>
@@ -2876,7 +2876,7 @@
     <t xml:space="preserve">32.024112701416</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1142959594727</t>
+    <t xml:space="preserve">33.1142997741699</t>
   </si>
   <si>
     <t xml:space="preserve">32.614631652832</t>
@@ -2888,10 +2888,10 @@
     <t xml:space="preserve">32.0695381164551</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5244483947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3427486419678</t>
+    <t xml:space="preserve">31.5244464874268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3427467346191</t>
   </si>
   <si>
     <t xml:space="preserve">32.3420829772949</t>
@@ -2900,13 +2900,13 @@
     <t xml:space="preserve">32.5237770080566</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7054748535156</t>
+    <t xml:space="preserve">32.7054786682129</t>
   </si>
   <si>
     <t xml:space="preserve">32.1603851318359</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1590538024902</t>
+    <t xml:space="preserve">34.159049987793</t>
   </si>
   <si>
     <t xml:space="preserve">33.7956581115723</t>
@@ -2915,7 +2915,7 @@
     <t xml:space="preserve">34.976692199707</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9325981140137</t>
+    <t xml:space="preserve">32.9325942993164</t>
   </si>
   <si>
     <t xml:space="preserve">33.0234451293945</t>
@@ -2933,37 +2933,37 @@
     <t xml:space="preserve">31.8424167633057</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8878364562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4342632293701</t>
+    <t xml:space="preserve">31.8878383636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4342651367188</t>
   </si>
   <si>
     <t xml:space="preserve">29.7074756622314</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7068099975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4796886444092</t>
+    <t xml:space="preserve">30.70680809021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4796867370605</t>
   </si>
   <si>
     <t xml:space="preserve">29.6166248321533</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8437461853027</t>
+    <t xml:space="preserve">29.8437442779541</t>
   </si>
   <si>
     <t xml:space="preserve">29.2532329559326</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7535648345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0708675384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.889835357666</t>
+    <t xml:space="preserve">28.7535629272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0708656311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8898372650146</t>
   </si>
   <si>
     <t xml:space="preserve">28.6627159118652</t>
@@ -2972,13 +2972,13 @@
     <t xml:space="preserve">28.8444137573242</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7081413269043</t>
+    <t xml:space="preserve">28.7081432342529</t>
   </si>
   <si>
     <t xml:space="preserve">28.9806861877441</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7989883422852</t>
+    <t xml:space="preserve">28.7989902496338</t>
   </si>
   <si>
     <t xml:space="preserve">29.8891735076904</t>
@@ -3005,10 +3005,10 @@
     <t xml:space="preserve">28.5718688964844</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4816837310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5725326538086</t>
+    <t xml:space="preserve">27.4816856384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5725345611572</t>
   </si>
   <si>
     <t xml:space="preserve">26.6186237335205</t>
@@ -3020,7 +3020,7 @@
     <t xml:space="preserve">27.0274410247803</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9365921020508</t>
+    <t xml:space="preserve">26.9365940093994</t>
   </si>
   <si>
     <t xml:space="preserve">26.9820194244385</t>
@@ -3029,13 +3029,13 @@
     <t xml:space="preserve">26.3460788726807</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8918361663818</t>
+    <t xml:space="preserve">25.8918342590332</t>
   </si>
   <si>
     <t xml:space="preserve">25.6647148132324</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2552280426025</t>
+    <t xml:space="preserve">26.2552299499512</t>
   </si>
   <si>
     <t xml:space="preserve">26.8457450866699</t>
@@ -3056,10 +3056,10 @@
     <t xml:space="preserve">26.70947265625</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5277767181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9826850891113</t>
+    <t xml:space="preserve">26.527774810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9826831817627</t>
   </si>
   <si>
     <t xml:space="preserve">25.8009872436523</t>
@@ -3068,13 +3068,13 @@
     <t xml:space="preserve">24.1657123565674</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6660461425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8477439880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4375953674316</t>
+    <t xml:space="preserve">23.6660442352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8477458953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.437593460083</t>
   </si>
   <si>
     <t xml:space="preserve">25.7555637359619</t>
@@ -4317,6 +4317,9 @@
   </si>
   <si>
     <t xml:space="preserve">18.8999996185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1399993896484</t>
   </si>
 </sst>
 </file>
@@ -70123,7 +70126,7 @@
     </row>
     <row r="2519">
       <c r="A2519" s="1" t="n">
-        <v>45986.6909953704</v>
+        <v>45986.3333333333</v>
       </c>
       <c r="B2519" t="n">
         <v>8516</v>
@@ -70144,6 +70147,32 @@
         <v>1421</v>
       </c>
       <c r="H2519" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2520">
+      <c r="A2520" s="1" t="n">
+        <v>45987.6912962963</v>
+      </c>
+      <c r="B2520" t="n">
+        <v>9471</v>
+      </c>
+      <c r="C2520" t="n">
+        <v>19.6800003051758</v>
+      </c>
+      <c r="D2520" t="n">
+        <v>18.8400001525879</v>
+      </c>
+      <c r="E2520" t="n">
+        <v>19.2800006866455</v>
+      </c>
+      <c r="F2520" t="n">
+        <v>19.1399993896484</v>
+      </c>
+      <c r="G2520" t="s">
+        <v>1435</v>
+      </c>
+      <c r="H2520" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ARN.MI.xlsx
+++ b/data/ARN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1435" uniqueCount="1435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="1436">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92215013504028</t>
+    <t xml:space="preserve">1.92215037345886</t>
   </si>
   <si>
     <t xml:space="preserve">ARN.MI</t>
@@ -47,28 +47,28 @@
     <t xml:space="preserve">1.94450068473816</t>
   </si>
   <si>
-    <t xml:space="preserve">1.917360663414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90778207778931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8838347196579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93172895908356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91576445102692</t>
+    <t xml:space="preserve">1.91736054420471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90778195858002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88383507728577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93172931671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91576409339905</t>
   </si>
   <si>
     <t xml:space="preserve">1.83434426784515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83594083786011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91097509860992</t>
+    <t xml:space="preserve">1.8359409570694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91097497940063</t>
   </si>
   <si>
     <t xml:space="preserve">1.80720412731171</t>
@@ -83,25 +83,25 @@
     <t xml:space="preserve">1.80401134490967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81039726734161</t>
+    <t xml:space="preserve">1.8103973865509</t>
   </si>
   <si>
     <t xml:space="preserve">1.79602921009064</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77208161354065</t>
+    <t xml:space="preserve">1.77208244800568</t>
   </si>
   <si>
     <t xml:space="preserve">1.70662677288055</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69704759120941</t>
+    <t xml:space="preserve">1.69704782962799</t>
   </si>
   <si>
     <t xml:space="preserve">1.69066190719604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67629361152649</t>
+    <t xml:space="preserve">1.67629373073578</t>
   </si>
   <si>
     <t xml:space="preserve">1.7002409696579</t>
@@ -110,136 +110,136 @@
     <t xml:space="preserve">1.69864428043365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67469727993011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6667149066925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66032898426056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81518661975861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8279584646225</t>
+    <t xml:space="preserve">1.67469716072083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66671466827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66032910346985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81518650054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82795834541321</t>
   </si>
   <si>
     <t xml:space="preserve">1.86148428916931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88543140888214</t>
+    <t xml:space="preserve">1.88543128967285</t>
   </si>
   <si>
     <t xml:space="preserve">1.89181697368622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92853581905365</t>
+    <t xml:space="preserve">1.92853605747223</t>
   </si>
   <si>
     <t xml:space="preserve">1.95407938957214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90618515014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86787009239197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88064193725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85190546512604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85988783836365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85509860515594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79283607006073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78804683685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78006410598755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7561172246933</t>
+    <t xml:space="preserve">1.90618538856506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86786985397339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88064169883728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85190558433533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85988759994507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85509836673737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79283630847931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78804659843445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78006434440613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75611710548401</t>
   </si>
   <si>
     <t xml:space="preserve">1.7688889503479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76409935951233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78485381603241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77048516273499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72099494934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73536312580109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80241477489471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76250290870667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74494183063507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73217010498047</t>
+    <t xml:space="preserve">1.76409959793091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78485369682312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77048552036285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72099471092224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73536324501038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.802414894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76250314712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74494194984436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73216998577118</t>
   </si>
   <si>
     <t xml:space="preserve">1.73695969581604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7433454990387</t>
+    <t xml:space="preserve">1.74334561824799</t>
   </si>
   <si>
     <t xml:space="preserve">1.75132763385773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68587255477905</t>
+    <t xml:space="preserve">1.68587267398834</t>
   </si>
   <si>
     <t xml:space="preserve">1.67789018154144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65234673023224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62041735649109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64276802539825</t>
+    <t xml:space="preserve">1.65234661102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6204172372818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64276790618896</t>
   </si>
   <si>
     <t xml:space="preserve">1.59008431434631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60285604000092</t>
+    <t xml:space="preserve">1.60285592079163</t>
   </si>
   <si>
     <t xml:space="preserve">1.54937446117401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51185727119446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45598077774048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43682301044464</t>
+    <t xml:space="preserve">1.51185715198517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45598089694977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43682312965393</t>
   </si>
   <si>
     <t xml:space="preserve">1.4695508480072</t>
@@ -248,64 +248,64 @@
     <t xml:space="preserve">1.49748909473419</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47673499584198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47274374961853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46875262260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49669063091278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47593677043915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50626945495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47753322124481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43841958045959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40090262889862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34901750087738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30910551548004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34342968463898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32666671276093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34103500843048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31708788871765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38653433322906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39691138267517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40648996829987</t>
+    <t xml:space="preserve">1.47673487663269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47274386882782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46875250339508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49669075012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47593641281128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50626969337463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47753298282623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43841969966888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40090239048004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34901738166809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30910563468933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34342980384827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32666659355164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34103488922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31708800792694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38653421401978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39691162109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40649008750916</t>
   </si>
   <si>
     <t xml:space="preserve">1.30671083927155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3234738111496</t>
+    <t xml:space="preserve">1.32347393035889</t>
   </si>
   <si>
     <t xml:space="preserve">1.30591261386871</t>
@@ -314,91 +314,91 @@
     <t xml:space="preserve">1.31229841709137</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28994798660278</t>
+    <t xml:space="preserve">1.28994786739349</t>
   </si>
   <si>
     <t xml:space="preserve">1.2851585149765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28595674037933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33305275440216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33704364299774</t>
+    <t xml:space="preserve">1.28595662117004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33305251598358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33704376220703</t>
   </si>
   <si>
     <t xml:space="preserve">1.30112326145172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36104893684387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34627246856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35283994674683</t>
+    <t xml:space="preserve">1.361048579216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34627270698547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35283982753754</t>
   </si>
   <si>
     <t xml:space="preserve">1.33806371688843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27157092094421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28880965709686</t>
+    <t xml:space="preserve">1.2715710401535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28880977630615</t>
   </si>
   <si>
     <t xml:space="preserve">1.29291427135468</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30686962604523</t>
+    <t xml:space="preserve">1.30686950683594</t>
   </si>
   <si>
     <t xml:space="preserve">1.33888459205627</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34955632686615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34380996227264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33642184734344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34709346294403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30522787570953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29127252101898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31425762176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32164561748505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26828730106354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27239179611206</t>
+    <t xml:space="preserve">1.34955620765686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34380984306335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33642196655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34709358215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30522775650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2912722826004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31425750255585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32164573669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26828753948212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27239191532135</t>
   </si>
   <si>
     <t xml:space="preserve">1.2879890203476</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2970187664032</t>
+    <t xml:space="preserve">1.29701888561249</t>
   </si>
   <si>
     <t xml:space="preserve">1.24858582019806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32657122612</t>
+    <t xml:space="preserve">1.32657110691071</t>
   </si>
   <si>
     <t xml:space="preserve">1.33231735229492</t>
@@ -407,91 +407,91 @@
     <t xml:space="preserve">1.35940706729889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42015337944031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48664629459381</t>
+    <t xml:space="preserve">1.42015361785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48664617538452</t>
   </si>
   <si>
     <t xml:space="preserve">1.53343749046326</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51619851589203</t>
+    <t xml:space="preserve">1.51619863510132</t>
   </si>
   <si>
     <t xml:space="preserve">1.51866114139557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43739223480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4677654504776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43000411987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40948188304901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44478046894073</t>
+    <t xml:space="preserve">1.43739247322083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46776556968689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43000423908234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40948176383972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44478034973145</t>
   </si>
   <si>
     <t xml:space="preserve">1.55970597267151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61798977851868</t>
+    <t xml:space="preserve">1.61798989772797</t>
   </si>
   <si>
     <t xml:space="preserve">1.70582604408264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74851286411285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72388553619385</t>
+    <t xml:space="preserve">1.74851274490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72388589382172</t>
   </si>
   <si>
     <t xml:space="preserve">1.68284070491791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67463159561157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65164685249329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64179599285126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67134809494019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66478109359741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65657186508179</t>
+    <t xml:space="preserve">1.67463183403015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.651646733284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64179587364197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67134821414948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6647812128067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65657198429108</t>
   </si>
   <si>
     <t xml:space="preserve">1.69597518444061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69433343410492</t>
+    <t xml:space="preserve">1.69433319568634</t>
   </si>
   <si>
     <t xml:space="preserve">1.65821373462677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68119883537292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68776631355286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6680645942688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65000486373901</t>
+    <t xml:space="preserve">1.68119895458221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68776619434357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66806471347809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6500049829483</t>
   </si>
   <si>
     <t xml:space="preserve">1.66313922405243</t>
@@ -503,16 +503,16 @@
     <t xml:space="preserve">2.03746867179871</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04403567314148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0391104221344</t>
+    <t xml:space="preserve">2.04403614997864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03911066055298</t>
   </si>
   <si>
     <t xml:space="preserve">2.04075217247009</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05224514007568</t>
+    <t xml:space="preserve">2.0522449016571</t>
   </si>
   <si>
     <t xml:space="preserve">2.04731941223145</t>
@@ -521,46 +521,46 @@
     <t xml:space="preserve">2.04239416122437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1983642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.241051197052</t>
+    <t xml:space="preserve">2.19836497306824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24105143547058</t>
   </si>
   <si>
     <t xml:space="preserve">2.18851375579834</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17537999153137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14582753181458</t>
+    <t xml:space="preserve">2.17537951469421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14582777023315</t>
   </si>
   <si>
     <t xml:space="preserve">2.00627446174622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98821485042572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99314022064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99806582927704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99642384052277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99970746040344</t>
+    <t xml:space="preserve">1.98821496963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99313998222351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99806547164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99642395973206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9997079372406</t>
   </si>
   <si>
     <t xml:space="preserve">2.00299096107483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00791645050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01119995117188</t>
+    <t xml:space="preserve">2.00791668891907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01120018959045</t>
   </si>
   <si>
     <t xml:space="preserve">2.02597594261169</t>
@@ -569,70 +569,70 @@
     <t xml:space="preserve">2.03254318237305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02105045318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0194091796875</t>
+    <t xml:space="preserve">2.02105093002319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01940870285034</t>
   </si>
   <si>
     <t xml:space="preserve">2.02433443069458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07687187194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05881190299988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09657335281372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14746904373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33955860137939</t>
+    <t xml:space="preserve">2.07687163352966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0588116645813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09657311439514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14746928215027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33955931663513</t>
   </si>
   <si>
     <t xml:space="preserve">2.27552914619446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32478260993958</t>
+    <t xml:space="preserve">2.32478308677673</t>
   </si>
   <si>
     <t xml:space="preserve">2.27881288528442</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25746941566467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2985143661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26075291633606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2804548740387</t>
+    <t xml:space="preserve">2.25746965408325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29851388931274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26075315475464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28045463562012</t>
   </si>
   <si>
     <t xml:space="preserve">2.30672335624695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35597681999207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34120106697083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34284257888794</t>
+    <t xml:space="preserve">2.35597705841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3412013053894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3428430557251</t>
   </si>
   <si>
     <t xml:space="preserve">2.34776782989502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44627571105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39209675788879</t>
+    <t xml:space="preserve">2.44627594947815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39209651947021</t>
   </si>
   <si>
     <t xml:space="preserve">2.38224577903748</t>
@@ -647,76 +647,76 @@
     <t xml:space="preserve">2.40523099899292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38060426712036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42164897918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33791708946228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32314133644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35433506965637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41015648841858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40687298774719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43806672096252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41836547851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29030537605286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34941005706787</t>
+    <t xml:space="preserve">2.38060402870178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42164874076843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33791756629944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32314109802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35433554649353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41015601158142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40687251091003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4380669593811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4183657169342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29030513763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34940981864929</t>
   </si>
   <si>
     <t xml:space="preserve">2.36418628692627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37567853927612</t>
+    <t xml:space="preserve">2.3756787776947</t>
   </si>
   <si>
     <t xml:space="preserve">2.40194749832153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35761904716492</t>
+    <t xml:space="preserve">2.35761880874634</t>
   </si>
   <si>
     <t xml:space="preserve">2.36746954917908</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37075328826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37239551544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.362544298172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36582779884338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39538025856018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3773205280304</t>
+    <t xml:space="preserve">2.37075304985046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37239527702332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36254453659058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36582803726196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3953800201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37732005119324</t>
   </si>
   <si>
     <t xml:space="preserve">2.37403678894043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38881301879883</t>
+    <t xml:space="preserve">2.38881278038025</t>
   </si>
   <si>
     <t xml:space="preserve">2.39373850822449</t>
@@ -725,16 +725,16 @@
     <t xml:space="preserve">2.39045476913452</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41344022750854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40358924865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40030574798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40851473808289</t>
+    <t xml:space="preserve">2.41343998908997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40358877182007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40030550956726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40851449966431</t>
   </si>
   <si>
     <t xml:space="preserve">2.42329049110413</t>
@@ -743,7 +743,7 @@
     <t xml:space="preserve">2.43149948120117</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42000699043274</t>
+    <t xml:space="preserve">2.42000722885132</t>
   </si>
   <si>
     <t xml:space="preserve">2.35105180740356</t>
@@ -755,7 +755,7 @@
     <t xml:space="preserve">2.34612631797791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43642520904541</t>
+    <t xml:space="preserve">2.43642544746399</t>
   </si>
   <si>
     <t xml:space="preserve">2.42657446861267</t>
@@ -764,16 +764,16 @@
     <t xml:space="preserve">2.42985796928406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45284271240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4770131111145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47867965698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49201512336731</t>
+    <t xml:space="preserve">2.4528431892395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47701334953308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47868013381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49201536178589</t>
   </si>
   <si>
     <t xml:space="preserve">2.49368214607239</t>
@@ -812,43 +812,43 @@
     <t xml:space="preserve">2.3419942855835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36866450309753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35366225242615</t>
+    <t xml:space="preserve">2.36866474151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35366272926331</t>
   </si>
   <si>
     <t xml:space="preserve">2.38533353805542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38366675376892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36366391181946</t>
+    <t xml:space="preserve">2.38366651535034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36366415023804</t>
   </si>
   <si>
     <t xml:space="preserve">2.32532525062561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31699085235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28531956672668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28698658943176</t>
+    <t xml:space="preserve">2.31699061393738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28531980514526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28698635101318</t>
   </si>
   <si>
     <t xml:space="preserve">2.29698777198792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31532406806946</t>
+    <t xml:space="preserve">2.31532382965088</t>
   </si>
   <si>
     <t xml:space="preserve">2.28365254402161</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28865337371826</t>
+    <t xml:space="preserve">2.28865361213684</t>
   </si>
   <si>
     <t xml:space="preserve">2.29032015800476</t>
@@ -860,25 +860,25 @@
     <t xml:space="preserve">2.30365562438965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2936544418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24198007583618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26698398590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26865029335022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32699251174927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31865787506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31032299995422</t>
+    <t xml:space="preserve">2.29365420341492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24198031425476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2669837474823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2686505317688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32699179649353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31865739822388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3103232383728</t>
   </si>
   <si>
     <t xml:space="preserve">2.24364709854126</t>
@@ -887,37 +887,37 @@
     <t xml:space="preserve">2.25031471252441</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2253110408783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25198149681091</t>
+    <t xml:space="preserve">2.22531127929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25198173522949</t>
   </si>
   <si>
     <t xml:space="preserve">2.22197723388672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20697546005249</t>
+    <t xml:space="preserve">2.20697522163391</t>
   </si>
   <si>
     <t xml:space="preserve">2.20030784606934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16863656044006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17863821983337</t>
+    <t xml:space="preserve">2.16863679885864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17863845825195</t>
   </si>
   <si>
     <t xml:space="preserve">2.16696953773499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18697285652161</t>
+    <t xml:space="preserve">2.18697237968445</t>
   </si>
   <si>
     <t xml:space="preserve">2.19697380065918</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18363857269287</t>
+    <t xml:space="preserve">2.18363881111145</t>
   </si>
   <si>
     <t xml:space="preserve">2.18530559539795</t>
@@ -938,73 +938,73 @@
     <t xml:space="preserve">2.1436333656311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13529849052429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12696409225464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1286313533783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12029647827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13029789924622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11862969398499</t>
+    <t xml:space="preserve">2.13529872894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12696433067322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12863111495972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12029671669006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13029813766479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11862993240356</t>
   </si>
   <si>
     <t xml:space="preserve">2.37366533279419</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37533187866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40700340270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39533495903015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39200115203857</t>
+    <t xml:space="preserve">2.37533235549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40700316429138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39533519744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39200091362</t>
   </si>
   <si>
     <t xml:space="preserve">2.49868249893188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49534869194031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5086841583252</t>
+    <t xml:space="preserve">2.49534893035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50868439674377</t>
   </si>
   <si>
     <t xml:space="preserve">2.51201772689819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51535153388977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51701855659485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52368640899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52535343170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54535603523254</t>
+    <t xml:space="preserve">2.51535177230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51701879501343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.523686170578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5253529548645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54535579681396</t>
   </si>
   <si>
     <t xml:space="preserve">2.53368735313416</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53202104568481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54035544395447</t>
+    <t xml:space="preserve">2.53202080726624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54035568237305</t>
   </si>
   <si>
     <t xml:space="preserve">2.52702021598816</t>
@@ -1013,31 +1013,31 @@
     <t xml:space="preserve">2.53868818283081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53702187538147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49701547622681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42700600624084</t>
+    <t xml:space="preserve">2.53702139854431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49701595306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42700624465942</t>
   </si>
   <si>
     <t xml:space="preserve">2.50034976005554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50535035133362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48368048667908</t>
+    <t xml:space="preserve">2.5053505897522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48368072509766</t>
   </si>
   <si>
     <t xml:space="preserve">2.45200991630554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51368474960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54202246665955</t>
+    <t xml:space="preserve">2.51368498802185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54202175140381</t>
   </si>
   <si>
     <t xml:space="preserve">2.54868984222412</t>
@@ -1046,22 +1046,22 @@
     <t xml:space="preserve">2.51035118103027</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52035236358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.472012758255</t>
+    <t xml:space="preserve">2.52035212516785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47201228141785</t>
   </si>
   <si>
     <t xml:space="preserve">2.50201654434204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48701453208923</t>
+    <t xml:space="preserve">2.48701477050781</t>
   </si>
   <si>
     <t xml:space="preserve">3.00041961669922</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81706094741821</t>
+    <t xml:space="preserve">2.81706070899963</t>
   </si>
   <si>
     <t xml:space="preserve">2.75038456916809</t>
@@ -1070,7 +1070,7 @@
     <t xml:space="preserve">2.7170467376709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80872583389282</t>
+    <t xml:space="preserve">2.80872654914856</t>
   </si>
   <si>
     <t xml:space="preserve">2.80039167404175</t>
@@ -1079,25 +1079,25 @@
     <t xml:space="preserve">2.83372974395752</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78372287750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84206414222717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75871896743774</t>
+    <t xml:space="preserve">2.78372263908386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84206438064575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75871872901917</t>
   </si>
   <si>
     <t xml:space="preserve">2.85039877891541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85873317718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89207077026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82539558410645</t>
+    <t xml:space="preserve">2.85873341560364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89207124710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82539486885071</t>
   </si>
   <si>
     <t xml:space="preserve">2.72538137435913</t>
@@ -1106,7 +1106,7 @@
     <t xml:space="preserve">2.61703252792358</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64203643798828</t>
+    <t xml:space="preserve">2.6420361995697</t>
   </si>
   <si>
     <t xml:space="preserve">2.70037770271301</t>
@@ -1115,46 +1115,46 @@
     <t xml:space="preserve">2.65870499610901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62536716461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63370156288147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59202933311462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66703963279724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70871186256409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74205040931702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65037083625793</t>
+    <t xml:space="preserve">2.6253674030304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63370203971863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59202909469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66703987121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70871210098267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74204993247986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65037059783936</t>
   </si>
   <si>
     <t xml:space="preserve">2.68370866775513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60036396980286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58369469642639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56702589988708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76705384254456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73371553421021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79205703735352</t>
+    <t xml:space="preserve">2.6003634929657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58369493484497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56702566146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76705360412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73371577262878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79205727577209</t>
   </si>
   <si>
     <t xml:space="preserve">2.86706757545471</t>
@@ -1163,22 +1163,22 @@
     <t xml:space="preserve">2.87540221214294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8837366104126</t>
+    <t xml:space="preserve">2.88373684883118</t>
   </si>
   <si>
     <t xml:space="preserve">2.77538847923279</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78091382980347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72174525260925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73019814491272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77246117591858</t>
+    <t xml:space="preserve">2.78091406822205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72174549102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7301983833313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77246141433716</t>
   </si>
   <si>
     <t xml:space="preserve">2.645672082901</t>
@@ -1196,70 +1196,70 @@
     <t xml:space="preserve">2.69638776779175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65412449836731</t>
+    <t xml:space="preserve">2.65412473678589</t>
   </si>
   <si>
     <t xml:space="preserve">2.60340881347656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63721942901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61186122894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57805109024048</t>
+    <t xml:space="preserve">2.63721919059753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61186146736145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5780508518219</t>
   </si>
   <si>
     <t xml:space="preserve">2.59495615959167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50197720527649</t>
+    <t xml:space="preserve">2.50197744369507</t>
   </si>
   <si>
     <t xml:space="preserve">2.49352478981018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54424023628235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5611457824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58650326728821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51888275146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53578782081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55269289016724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51042985916138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56959819793701</t>
+    <t xml:space="preserve">2.54424071311951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56114554405212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58650350570679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51888227462769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53578805923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55269312858582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5104296207428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56959795951843</t>
   </si>
   <si>
     <t xml:space="preserve">2.46816682815552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48507189750671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41745090484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45126152038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39209270477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38364052772522</t>
+    <t xml:space="preserve">2.48507213592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41745042800903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45126128196716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39209318161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38364028930664</t>
   </si>
   <si>
     <t xml:space="preserve">2.27375626564026</t>
@@ -1268,10 +1268,10 @@
     <t xml:space="preserve">2.29911422729492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36673521995544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35828256607056</t>
+    <t xml:space="preserve">2.36673498153687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35828232765198</t>
   </si>
   <si>
     <t xml:space="preserve">2.43435621261597</t>
@@ -1280,13 +1280,13 @@
     <t xml:space="preserve">2.4259033203125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34982967376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28220868110657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32447218894958</t>
+    <t xml:space="preserve">2.34982991218567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28220891952515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32447195053101</t>
   </si>
   <si>
     <t xml:space="preserve">2.4089982509613</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">2.45971417427063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44280910491943</t>
+    <t xml:space="preserve">2.44280886650085</t>
   </si>
   <si>
     <t xml:space="preserve">2.33292484283447</t>
@@ -1304,37 +1304,37 @@
     <t xml:space="preserve">2.34137725830078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.400545835495</t>
+    <t xml:space="preserve">2.40054559707642</t>
   </si>
   <si>
     <t xml:space="preserve">2.37518763542175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47661924362183</t>
+    <t xml:space="preserve">2.47661948204041</t>
   </si>
   <si>
     <t xml:space="preserve">2.30756664276123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23994565010071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29430246353149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23437666893005</t>
+    <t xml:space="preserve">2.23994588851929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29430222511292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23437643051147</t>
   </si>
   <si>
     <t xml:space="preserve">2.2429370880127</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33710646629333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25149822235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27718091011047</t>
+    <t xml:space="preserve">2.33710670471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25149846076965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27718067169189</t>
   </si>
   <si>
     <t xml:space="preserve">2.26861977577209</t>
@@ -1349,16 +1349,16 @@
     <t xml:space="preserve">2.31142377853394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28574156761169</t>
+    <t xml:space="preserve">2.28574180603027</t>
   </si>
   <si>
     <t xml:space="preserve">2.26005887985229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35422801971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2258152961731</t>
+    <t xml:space="preserve">2.35422825813293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22581553459167</t>
   </si>
   <si>
     <t xml:space="preserve">2.20869398117065</t>
@@ -1367,46 +1367,46 @@
     <t xml:space="preserve">2.30286312103271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31998491287231</t>
+    <t xml:space="preserve">2.31998467445374</t>
   </si>
   <si>
     <t xml:space="preserve">2.37991046905518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.405592918396</t>
+    <t xml:space="preserve">2.40559315681458</t>
   </si>
   <si>
     <t xml:space="preserve">2.39703226089478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32854557037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38847160339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36278891563416</t>
+    <t xml:space="preserve">2.32854533195496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38847136497498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36278915405273</t>
   </si>
   <si>
     <t xml:space="preserve">2.34566736221313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20013308525085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18301129341125</t>
+    <t xml:space="preserve">2.20013284683228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18301153182983</t>
   </si>
   <si>
     <t xml:space="preserve">2.4398365020752</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54256653785706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60249209403992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69666147232056</t>
+    <t xml:space="preserve">2.5425660610199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60249185562134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69666123390198</t>
   </si>
   <si>
     <t xml:space="preserve">2.77370882034302</t>
@@ -1415,19 +1415,19 @@
     <t xml:space="preserve">2.63673543930054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67097878456116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61961340904236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65385723114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68810057640076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64529609680176</t>
+    <t xml:space="preserve">2.670978307724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61961364746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65385699272156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68810033798218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64529633522034</t>
   </si>
   <si>
     <t xml:space="preserve">2.71378302574158</t>
@@ -1439,52 +1439,52 @@
     <t xml:space="preserve">3.07333779335022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52706146240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59554815292358</t>
+    <t xml:space="preserve">3.52706170082092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59554839134216</t>
   </si>
   <si>
     <t xml:space="preserve">3.65547394752502</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58698773384094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61267018318176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53562307357788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42433166503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54418301582336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56986570358276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55274438858032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56130504608154</t>
+    <t xml:space="preserve">3.58698797225952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61266946792603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5356228351593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42433190345764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54418325424194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56986618041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5527446269989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56130480766296</t>
   </si>
   <si>
     <t xml:space="preserve">3.5099401473999</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4842574596405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57842659950256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63835287094116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74108219146729</t>
+    <t xml:space="preserve">3.48425769805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57842683792114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63835263252258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74108242988586</t>
   </si>
   <si>
     <t xml:space="preserve">4.16912364959717</t>
@@ -1493,16 +1493,16 @@
     <t xml:space="preserve">4.60572624206543</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15361928939819</t>
+    <t xml:space="preserve">5.15361976623535</t>
   </si>
   <si>
     <t xml:space="preserve">4.62284755706787</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19480657577515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45163059234619</t>
+    <t xml:space="preserve">4.19480609893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45163106918335</t>
   </si>
   <si>
     <t xml:space="preserve">4.53723955154419</t>
@@ -1511,7 +1511,7 @@
     <t xml:space="preserve">4.52011775970459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58860492706299</t>
+    <t xml:space="preserve">4.58860445022583</t>
   </si>
   <si>
     <t xml:space="preserve">4.34890127182007</t>
@@ -1526,25 +1526,25 @@
     <t xml:space="preserve">4.29753637313843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89517688751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27879762649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25311493873596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8935604095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15894627571106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1675066947937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0390944480896</t>
+    <t xml:space="preserve">3.89517784118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27879786491394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25311517715454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89356017112732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15894603729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16750693321228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03909420967102</t>
   </si>
   <si>
     <t xml:space="preserve">3.44145369529724</t>
@@ -1559,25 +1559,25 @@
     <t xml:space="preserve">3.84381222724915</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83525133132935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87805652618408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76676511764526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88661694526672</t>
+    <t xml:space="preserve">3.83525156974792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87805581092834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76676487922668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88661623001099</t>
   </si>
   <si>
     <t xml:space="preserve">3.85237312316895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92942070960999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95510315895081</t>
+    <t xml:space="preserve">3.92942118644714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95510339736938</t>
   </si>
   <si>
     <t xml:space="preserve">3.93798136711121</t>
@@ -1586,16 +1586,16 @@
     <t xml:space="preserve">4.11775875091553</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25473213195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22904968261719</t>
+    <t xml:space="preserve">4.25473165512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22905015945435</t>
   </si>
   <si>
     <t xml:space="preserve">4.26329326629639</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28041458129883</t>
+    <t xml:space="preserve">4.28041505813599</t>
   </si>
   <si>
     <t xml:space="preserve">4.43450975418091</t>
@@ -1604,52 +1604,52 @@
     <t xml:space="preserve">4.20336723327637</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00646781921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10919857025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15200281143188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08351612091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94654273986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07495450973511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02358961105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96366405487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13488054275513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12631988525391</t>
+    <t xml:space="preserve">4.00646829605103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10919809341431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15200185775757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08351564407349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94654202461243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07495498657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02359008789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96366357803345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13488101959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12632036209106</t>
   </si>
   <si>
     <t xml:space="preserve">5.01664638519287</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70845603942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91391611099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96528100967407</t>
+    <t xml:space="preserve">4.70845651626587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91391563415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96528148651123</t>
   </si>
   <si>
     <t xml:space="preserve">4.94815969467163</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20498418807983</t>
+    <t xml:space="preserve">5.20498371124268</t>
   </si>
   <si>
     <t xml:space="preserve">5.56453943252563</t>
@@ -1658,16 +1658,16 @@
     <t xml:space="preserve">5.68439054489136</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95833778381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90697240829468</t>
+    <t xml:space="preserve">5.95833730697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90697288513184</t>
   </si>
   <si>
     <t xml:space="preserve">5.88985061645508</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57471704483032</t>
+    <t xml:space="preserve">6.57471656799316</t>
   </si>
   <si>
     <t xml:space="preserve">6.12955379486084</t>
@@ -1685,25 +1685,25 @@
     <t xml:space="preserve">7.32807016372681</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05412292480469</t>
+    <t xml:space="preserve">7.05412340164185</t>
   </si>
   <si>
     <t xml:space="preserve">7.00275897979736</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42397785186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28357076644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8799033164978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9676570892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59909057617188</t>
+    <t xml:space="preserve">7.42397737503052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28357124328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87990283966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96765661239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59909105300903</t>
   </si>
   <si>
     <t xml:space="preserve">6.51133728027344</t>
@@ -1712,61 +1712,61 @@
     <t xml:space="preserve">6.73949670791626</t>
   </si>
   <si>
-    <t xml:space="preserve">6.844801902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82725143432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68684482574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6692943572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45868492126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40603256225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31827831268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80970001220703</t>
+    <t xml:space="preserve">6.84480142593384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82725095748901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68684434890747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66929388046265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45868539810181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4060320854187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31827878952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80970048904419</t>
   </si>
   <si>
     <t xml:space="preserve">7.17826700210571</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35377407073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26602029800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05541038513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07296180725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63419198989868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44113445281982</t>
+    <t xml:space="preserve">7.35377502441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26601982116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05541133880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07296276092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63419246673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44113397598267</t>
   </si>
   <si>
     <t xml:space="preserve">6.30072784423828</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05501651763916</t>
+    <t xml:space="preserve">6.05501699447632</t>
   </si>
   <si>
     <t xml:space="preserve">6.03746604919434</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3705358505249</t>
+    <t xml:space="preserve">5.37053632736206</t>
   </si>
   <si>
     <t xml:space="preserve">5.40563821792603</t>
@@ -1778,19 +1778,19 @@
     <t xml:space="preserve">5.65134906768799</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12522029876709</t>
+    <t xml:space="preserve">6.12521982192993</t>
   </si>
   <si>
     <t xml:space="preserve">5.96726322174072</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01991510391235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91461038589478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.844407081604</t>
+    <t xml:space="preserve">6.01991558074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91461086273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84440755844116</t>
   </si>
   <si>
     <t xml:space="preserve">5.94971227645874</t>
@@ -1802,7 +1802,7 @@
     <t xml:space="preserve">5.82685661315918</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93216180801392</t>
+    <t xml:space="preserve">5.93216133117676</t>
   </si>
   <si>
     <t xml:space="preserve">5.87950897216797</t>
@@ -1817,19 +1817,19 @@
     <t xml:space="preserve">5.45829010009766</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63379812240601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70400094985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58114576339722</t>
+    <t xml:space="preserve">5.63379859924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70400142669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58114624023438</t>
   </si>
   <si>
     <t xml:space="preserve">5.66890001296997</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56359529495239</t>
+    <t xml:space="preserve">5.56359577178955</t>
   </si>
   <si>
     <t xml:space="preserve">5.61624765396118</t>
@@ -1841,16 +1841,16 @@
     <t xml:space="preserve">5.31788396835327</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17747831344604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2652325630188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28278255462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35298585891724</t>
+    <t xml:space="preserve">5.17747783660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26523208618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28278303146362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35298538208008</t>
   </si>
   <si>
     <t xml:space="preserve">5.42318916320801</t>
@@ -1859,22 +1859,22 @@
     <t xml:space="preserve">5.47584056854248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38808679580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51094341278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77420520782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44074010848999</t>
+    <t xml:space="preserve">5.38808727264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51094245910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77420473098755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44073963165283</t>
   </si>
   <si>
     <t xml:space="preserve">5.54604434967041</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23052453994751</t>
+    <t xml:space="preserve">6.23052406311035</t>
   </si>
   <si>
     <t xml:space="preserve">6.35338020324707</t>
@@ -1883,10 +1883,10 @@
     <t xml:space="preserve">6.16032123565674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37093019485474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47623538970947</t>
+    <t xml:space="preserve">6.37093114852905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47623586654663</t>
   </si>
   <si>
     <t xml:space="preserve">6.42358303070068</t>
@@ -1901,13 +1901,13 @@
     <t xml:space="preserve">7.33622360229492</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09051275253296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16071510314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19581651687622</t>
+    <t xml:space="preserve">7.0905122756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16071557998657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19581747055054</t>
   </si>
   <si>
     <t xml:space="preserve">6.95010614395142</t>
@@ -1916,13 +1916,13 @@
     <t xml:space="preserve">7.14316511154175</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12561416625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02030992507935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84519577026367</t>
+    <t xml:space="preserve">7.12561368942261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02030944824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8451943397522</t>
   </si>
   <si>
     <t xml:space="preserve">8.3366174697876</t>
@@ -1937,25 +1937,25 @@
     <t xml:space="preserve">9.0825252532959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68763256072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03864860534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30191040039062</t>
+    <t xml:space="preserve">8.68763160705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03864765167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30190944671631</t>
   </si>
   <si>
     <t xml:space="preserve">11.2763719558716</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1630792617798</t>
+    <t xml:space="preserve">13.1630802154541</t>
   </si>
   <si>
     <t xml:space="preserve">13.0753259658813</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1192035675049</t>
+    <t xml:space="preserve">13.1192026138306</t>
   </si>
   <si>
     <t xml:space="preserve">12.8559417724609</t>
@@ -1964,7 +1964,7 @@
     <t xml:space="preserve">12.0222806930542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1100330352783</t>
+    <t xml:space="preserve">12.1100339889526</t>
   </si>
   <si>
     <t xml:space="preserve">11.9345264434814</t>
@@ -1973,7 +1973,7 @@
     <t xml:space="preserve">11.36412525177</t>
   </si>
   <si>
-    <t xml:space="preserve">10.88148021698</t>
+    <t xml:space="preserve">10.8814792633057</t>
   </si>
   <si>
     <t xml:space="preserve">12.1539106369019</t>
@@ -1982,52 +1982,52 @@
     <t xml:space="preserve">11.6712646484375</t>
   </si>
   <si>
-    <t xml:space="preserve">11.715142250061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4518795013428</t>
+    <t xml:space="preserve">11.7151412963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4518804550171</t>
   </si>
   <si>
     <t xml:space="preserve">11.0569868087769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4957571029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4080018997192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8906478881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8028955459595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3202486038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6273860931396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1447410583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.618218421936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5304651260376</t>
+    <t xml:space="preserve">11.495756149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4080028533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8906497955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8028945922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3202495574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.627387046814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1447401046753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6182193756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5304641723633</t>
   </si>
   <si>
     <t xml:space="preserve">10.5743398666382</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7498483657837</t>
+    <t xml:space="preserve">10.7498502731323</t>
   </si>
   <si>
     <t xml:space="preserve">10.6620950698853</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3549566268921</t>
+    <t xml:space="preserve">10.3549556732178</t>
   </si>
   <si>
     <t xml:space="preserve">9.78455543518066</t>
@@ -2036,7 +2036,7 @@
     <t xml:space="preserve">9.91618728637695</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0916938781738</t>
+    <t xml:space="preserve">10.0916948318481</t>
   </si>
   <si>
     <t xml:space="preserve">11.2324953079224</t>
@@ -2045,16 +2045,16 @@
     <t xml:space="preserve">11.1886177062988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1008634567261</t>
+    <t xml:space="preserve">11.1008644104004</t>
   </si>
   <si>
     <t xml:space="preserve">11.3553504943848</t>
   </si>
   <si>
-    <t xml:space="preserve">11.267596244812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0218868255615</t>
+    <t xml:space="preserve">11.2675971984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0218849182129</t>
   </si>
   <si>
     <t xml:space="preserve">11.2500448226929</t>
@@ -2063,7 +2063,7 @@
     <t xml:space="preserve">11.3729009628296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2851476669312</t>
+    <t xml:space="preserve">11.2851467132568</t>
   </si>
   <si>
     <t xml:space="preserve">11.1973943710327</t>
@@ -2072,22 +2072,22 @@
     <t xml:space="preserve">11.8467721939087</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9871788024902</t>
+    <t xml:space="preserve">11.9871778488159</t>
   </si>
   <si>
     <t xml:space="preserve">12.2855415344238</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2504405975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1626853942871</t>
+    <t xml:space="preserve">12.2504396438599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1626863479614</t>
   </si>
   <si>
     <t xml:space="preserve">12.4672012329102</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0372972488403</t>
+    <t xml:space="preserve">12.0372982025146</t>
   </si>
   <si>
     <t xml:space="preserve">12.0910358428955</t>
@@ -2102,40 +2102,40 @@
     <t xml:space="preserve">11.3924427032471</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9446258544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5505475997925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6759376525879</t>
+    <t xml:space="preserve">10.9446268081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5505485534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6759366989136</t>
   </si>
   <si>
     <t xml:space="preserve">10.9088010787964</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7117624282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6580228805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9267139434814</t>
+    <t xml:space="preserve">10.7117614746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6580238342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9267129898071</t>
   </si>
   <si>
     <t xml:space="preserve">11.0521020889282</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4999179840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.482006072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4282674789429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5715684890747</t>
+    <t xml:space="preserve">11.4999189376831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4820051193237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4282684326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.571569442749</t>
   </si>
   <si>
     <t xml:space="preserve">11.3745288848877</t>
@@ -2144,7 +2144,7 @@
     <t xml:space="preserve">11.3566179275513</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3207931518555</t>
+    <t xml:space="preserve">11.3207921981812</t>
   </si>
   <si>
     <t xml:space="preserve">11.4461803436279</t>
@@ -2153,10 +2153,10 @@
     <t xml:space="preserve">11.464093208313</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7148694992065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7327833175659</t>
+    <t xml:space="preserve">11.7148704528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7327823638916</t>
   </si>
   <si>
     <t xml:space="preserve">11.750696182251</t>
@@ -2165,22 +2165,22 @@
     <t xml:space="preserve">12.1805992126465</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6284160614014</t>
+    <t xml:space="preserve">12.6284151077271</t>
   </si>
   <si>
     <t xml:space="preserve">12.0731229782104</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3418111801147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3597249984741</t>
+    <t xml:space="preserve">12.3418121337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3597259521484</t>
   </si>
   <si>
     <t xml:space="preserve">11.6969575881958</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1268606185913</t>
+    <t xml:space="preserve">12.1268615722656</t>
   </si>
   <si>
     <t xml:space="preserve">12.0552101135254</t>
@@ -2189,13 +2189,13 @@
     <t xml:space="preserve">11.8581705093384</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9298210144043</t>
+    <t xml:space="preserve">11.9298219680786</t>
   </si>
   <si>
     <t xml:space="preserve">12.2880754470825</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5925912857056</t>
+    <t xml:space="preserve">12.5925893783569</t>
   </si>
   <si>
     <t xml:space="preserve">12.503026008606</t>
@@ -2207,16 +2207,16 @@
     <t xml:space="preserve">12.3239002227783</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9804515838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.177490234375</t>
+    <t xml:space="preserve">10.9804525375366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1774892807007</t>
   </si>
   <si>
     <t xml:space="preserve">11.284966468811</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3387050628662</t>
+    <t xml:space="preserve">11.3387041091919</t>
   </si>
   <si>
     <t xml:space="preserve">11.8939962387085</t>
@@ -2225,34 +2225,34 @@
     <t xml:space="preserve">11.7686080932617</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6253070831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0014715194702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1089487075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9656476974487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1985111236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4313764572144</t>
+    <t xml:space="preserve">11.6253051757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0014724731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1089477539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9656467437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1985120773315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.43137550354</t>
   </si>
   <si>
     <t xml:space="preserve">12.2522497177124</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8612785339355</t>
+    <t xml:space="preserve">12.8612794876099</t>
   </si>
   <si>
     <t xml:space="preserve">12.8433666229248</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6821527481079</t>
+    <t xml:space="preserve">12.6821517944336</t>
   </si>
   <si>
     <t xml:space="preserve">12.7358913421631</t>
@@ -2261,10 +2261,10 @@
     <t xml:space="preserve">13.3449201583862</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2405519485474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0972509384155</t>
+    <t xml:space="preserve">14.2405529022217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0972518920898</t>
   </si>
   <si>
     <t xml:space="preserve">14.3301162719727</t>
@@ -2285,25 +2285,25 @@
     <t xml:space="preserve">13.5777854919434</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4703092575073</t>
+    <t xml:space="preserve">13.4703102111816</t>
   </si>
   <si>
     <t xml:space="preserve">13.6852607727051</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6673488616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5598735809326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6136093139648</t>
+    <t xml:space="preserve">13.6673498153687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5598726272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6136102676392</t>
   </si>
   <si>
     <t xml:space="preserve">13.8285617828369</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9539499282837</t>
+    <t xml:space="preserve">13.9539518356323</t>
   </si>
   <si>
     <t xml:space="preserve">13.4344844818115</t>
@@ -2312,22 +2312,22 @@
     <t xml:space="preserve">13.7210865020752</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5240478515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7031736373901</t>
+    <t xml:space="preserve">13.5240468978882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7031745910645</t>
   </si>
   <si>
     <t xml:space="preserve">13.2553577423096</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4523973464966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3090953826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2763786315918</t>
+    <t xml:space="preserve">13.4523963928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3090944290161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2763776779175</t>
   </si>
   <si>
     <t xml:space="preserve">14.4196796417236</t>
@@ -2339,46 +2339,46 @@
     <t xml:space="preserve">13.756911277771</t>
   </si>
   <si>
-    <t xml:space="preserve">14.437593460083</t>
+    <t xml:space="preserve">14.4375944137573</t>
   </si>
   <si>
     <t xml:space="preserve">16.7124977111816</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3363342285156</t>
+    <t xml:space="preserve">16.336332321167</t>
   </si>
   <si>
     <t xml:space="preserve">17.7156066894531</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2498779296875</t>
+    <t xml:space="preserve">17.2498760223389</t>
   </si>
   <si>
     <t xml:space="preserve">19.6591281890869</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3160457611084</t>
+    <t xml:space="preserve">21.316047668457</t>
   </si>
   <si>
     <t xml:space="preserve">21.4503936767578</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5399551391602</t>
+    <t xml:space="preserve">21.5399570465088</t>
   </si>
   <si>
     <t xml:space="preserve">22.2116794586182</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9877700805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2712650299072</t>
+    <t xml:space="preserve">21.987771987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2712669372559</t>
   </si>
   <si>
     <t xml:space="preserve">23.017749786377</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3460273742676</t>
+    <t xml:space="preserve">22.3460254669189</t>
   </si>
   <si>
     <t xml:space="preserve">22.1221179962158</t>
@@ -2393,31 +2393,31 @@
     <t xml:space="preserve">22.4355888366699</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4951725006104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7190837860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9429893493652</t>
+    <t xml:space="preserve">21.495174407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7190818786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9429931640625</t>
   </si>
   <si>
     <t xml:space="preserve">21.7638645172119</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8534278869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3312187194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8086471557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3463935852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3016109466553</t>
+    <t xml:space="preserve">21.8534259796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3312206268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8086452484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3463916778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3016128540039</t>
   </si>
   <si>
     <t xml:space="preserve">26.2420253753662</t>
@@ -2429,10 +2429,10 @@
     <t xml:space="preserve">25.2120475769043</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8837699890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4807395935059</t>
+    <t xml:space="preserve">25.8837718963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4807376861572</t>
   </si>
   <si>
     <t xml:space="preserve">25.5703010559082</t>
@@ -2447,7 +2447,7 @@
     <t xml:space="preserve">25.3911743164062</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7046489715576</t>
+    <t xml:space="preserve">25.704647064209</t>
   </si>
   <si>
     <t xml:space="preserve">26.4211521148682</t>
@@ -2456,28 +2456,28 @@
     <t xml:space="preserve">26.0628986358643</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4659309387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1524639129639</t>
+    <t xml:space="preserve">26.465934753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1524620056152</t>
   </si>
   <si>
     <t xml:space="preserve">28.6602325439453</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6750373840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7794055938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5554943084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9881401062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2568321228027</t>
+    <t xml:space="preserve">27.6750354766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7794036865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5554962158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9881381988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2568302154541</t>
   </si>
   <si>
     <t xml:space="preserve">23.9581642150879</t>
@@ -2492,13 +2492,13 @@
     <t xml:space="preserve">24.5851058959961</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0773334503174</t>
+    <t xml:space="preserve">22.077335357666</t>
   </si>
   <si>
     <t xml:space="preserve">22.928186416626</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1968765258789</t>
+    <t xml:space="preserve">23.1968746185303</t>
   </si>
   <si>
     <t xml:space="preserve">24.182071685791</t>
@@ -2507,34 +2507,34 @@
     <t xml:space="preserve">24.2268524169922</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4955406188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3164157867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3908081054688</t>
+    <t xml:space="preserve">24.4955425262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3164138793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3908061981201</t>
   </si>
   <si>
     <t xml:space="preserve">23.8238182067871</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0625324249268</t>
+    <t xml:space="preserve">23.0625305175781</t>
   </si>
   <si>
     <t xml:space="preserve">23.7790355682373</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8834037780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2416572570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1672649383545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3167839050293</t>
+    <t xml:space="preserve">22.8834018707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2416591644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1672687530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3167819976807</t>
   </si>
   <si>
     <t xml:space="preserve">26.6002788543701</t>
@@ -2543,13 +2543,13 @@
     <t xml:space="preserve">25.615083694458</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4359569549561</t>
+    <t xml:space="preserve">25.4359550476074</t>
   </si>
   <si>
     <t xml:space="preserve">24.8985767364502</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9733352661133</t>
+    <t xml:space="preserve">25.9733371734619</t>
   </si>
   <si>
     <t xml:space="preserve">26.5107154846191</t>
@@ -2561,70 +2561,70 @@
     <t xml:space="preserve">26.868968963623</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6450576782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4959125518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.048095703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9437274932861</t>
+    <t xml:space="preserve">26.6450595855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4959106445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0480937957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9437255859375</t>
   </si>
   <si>
     <t xml:space="preserve">28.8841400146484</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9289226531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7050113677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7797718048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9885082244873</t>
+    <t xml:space="preserve">28.9289207458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7050151824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7797737121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9885063171387</t>
   </si>
   <si>
     <t xml:space="preserve">27.630256652832</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2272186279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4063472747803</t>
+    <t xml:space="preserve">27.2272205352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4063491821289</t>
   </si>
   <si>
     <t xml:space="preserve">26.6898403167725</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8389892578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7942085266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3315887451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7194499969482</t>
+    <t xml:space="preserve">25.8389930725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.79421043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3315868377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7194519042969</t>
   </si>
   <si>
     <t xml:space="preserve">24.4507598876953</t>
   </si>
   <si>
-    <t xml:space="preserve">23.599910736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4655666351318</t>
+    <t xml:space="preserve">23.5999126434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4655647277832</t>
   </si>
   <si>
     <t xml:space="preserve">27.3615646362305</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0332889556885</t>
+    <t xml:space="preserve">28.0332908630371</t>
   </si>
   <si>
     <t xml:space="preserve">27.8541641235352</t>
@@ -2636,7 +2636,7 @@
     <t xml:space="preserve">27.6633834838867</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2979888916016</t>
+    <t xml:space="preserve">30.2979869842529</t>
   </si>
   <si>
     <t xml:space="preserve">26.891170501709</t>
@@ -2648,22 +2648,22 @@
     <t xml:space="preserve">29.662052154541</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4803524017334</t>
+    <t xml:space="preserve">29.480354309082</t>
   </si>
   <si>
     <t xml:space="preserve">29.3440799713135</t>
   </si>
   <si>
-    <t xml:space="preserve">30.525110244751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5705375671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0247802734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0702037811279</t>
+    <t xml:space="preserve">30.5251121520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.57053565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0247821807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0702018737793</t>
   </si>
   <si>
     <t xml:space="preserve">30.8885059356689</t>
@@ -2678,7 +2678,7 @@
     <t xml:space="preserve">27.9359283447266</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4362621307373</t>
+    <t xml:space="preserve">27.4362602233887</t>
   </si>
   <si>
     <t xml:space="preserve">28.0722007751465</t>
@@ -2687,7 +2687,7 @@
     <t xml:space="preserve">28.4355945587158</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5264434814453</t>
+    <t xml:space="preserve">28.5264415740967</t>
   </si>
   <si>
     <t xml:space="preserve">28.4810199737549</t>
@@ -2699,13 +2699,13 @@
     <t xml:space="preserve">29.1623821258545</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4349308013916</t>
+    <t xml:space="preserve">29.434928894043</t>
   </si>
   <si>
     <t xml:space="preserve">28.2538986206055</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1169567108154</t>
+    <t xml:space="preserve">29.1169605255127</t>
   </si>
   <si>
     <t xml:space="preserve">30.1162948608398</t>
@@ -2714,25 +2714,25 @@
     <t xml:space="preserve">30.9793529510498</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1610507965088</t>
+    <t xml:space="preserve">31.1610488891602</t>
   </si>
   <si>
     <t xml:space="preserve">31.479024887085</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5698680877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.796989440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7515659332275</t>
+    <t xml:space="preserve">31.5698719024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7969932556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7515678405762</t>
   </si>
   <si>
     <t xml:space="preserve">31.1156272888184</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2505683898926</t>
+    <t xml:space="preserve">33.2505645751953</t>
   </si>
   <si>
     <t xml:space="preserve">34.6587219238281</t>
@@ -2741,7 +2741,7 @@
     <t xml:space="preserve">33.8410835266113</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4770240783691</t>
+    <t xml:space="preserve">34.4770278930664</t>
   </si>
   <si>
     <t xml:space="preserve">34.386173248291</t>
@@ -2750,37 +2750,37 @@
     <t xml:space="preserve">34.5678672790527</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6132965087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3400840759277</t>
+    <t xml:space="preserve">34.6132926940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.340087890625</t>
   </si>
   <si>
     <t xml:space="preserve">34.4316024780273</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7048110961914</t>
+    <t xml:space="preserve">33.7048072814941</t>
   </si>
   <si>
     <t xml:space="preserve">33.9773559570312</t>
   </si>
   <si>
-    <t xml:space="preserve">34.931266784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5224456787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0682029724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7502365112305</t>
+    <t xml:space="preserve">34.9312705993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5224494934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0682067871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7502326965332</t>
   </si>
   <si>
     <t xml:space="preserve">33.9319305419922</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2499046325684</t>
+    <t xml:space="preserve">34.2499008178711</t>
   </si>
   <si>
     <t xml:space="preserve">33.6139640808105</t>
@@ -2792,13 +2792,13 @@
     <t xml:space="preserve">36.6573867797852</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7936630249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6106338500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5645446777344</t>
+    <t xml:space="preserve">36.7936592102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6106300354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5645408630371</t>
   </si>
   <si>
     <t xml:space="preserve">38.1109657287598</t>
@@ -2807,22 +2807,22 @@
     <t xml:space="preserve">36.4302635192871</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3868370056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8871726989746</t>
+    <t xml:space="preserve">33.3868408203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8871765136719</t>
   </si>
   <si>
     <t xml:space="preserve">33.0688743591309</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3414192199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8865051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2044830322266</t>
+    <t xml:space="preserve">33.3414154052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8865089416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2044792175293</t>
   </si>
   <si>
     <t xml:space="preserve">34.340747833252</t>
@@ -2837,7 +2837,7 @@
     <t xml:space="preserve">32.9780197143555</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7976551055908</t>
+    <t xml:space="preserve">30.7976570129395</t>
   </si>
   <si>
     <t xml:space="preserve">29.3895034790039</t>
@@ -2846,22 +2846,22 @@
     <t xml:space="preserve">29.5257778167725</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6172924041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.344747543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0254440307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9332675933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2058067321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1149597167969</t>
+    <t xml:space="preserve">28.6172904968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3447456359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0254459381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9332637786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.205810546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1149559020996</t>
   </si>
   <si>
     <t xml:space="preserve">32.2512359619141</t>
@@ -2870,13 +2870,13 @@
     <t xml:space="preserve">31.615291595459</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0241088867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1142959594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6146278381348</t>
+    <t xml:space="preserve">32.024112701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1142997741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.614631652832</t>
   </si>
   <si>
     <t xml:space="preserve">31.2064743041992</t>
@@ -2885,10 +2885,10 @@
     <t xml:space="preserve">32.0695381164551</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5244445800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3427486419678</t>
+    <t xml:space="preserve">31.5244464874268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3427467346191</t>
   </si>
   <si>
     <t xml:space="preserve">32.3420829772949</t>
@@ -2897,10 +2897,10 @@
     <t xml:space="preserve">32.5237770080566</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7054748535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1603889465332</t>
+    <t xml:space="preserve">32.7054786682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1603851318359</t>
   </si>
   <si>
     <t xml:space="preserve">34.159049987793</t>
@@ -2912,10 +2912,10 @@
     <t xml:space="preserve">34.976692199707</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9325981140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0234489440918</t>
+    <t xml:space="preserve">32.9325942993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0234451293945</t>
   </si>
   <si>
     <t xml:space="preserve">33.5231170654297</t>
@@ -2930,19 +2930,19 @@
     <t xml:space="preserve">31.8424167633057</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8878402709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4342613220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7074737548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7068099975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4796886444092</t>
+    <t xml:space="preserve">31.8878383636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4342651367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7074756622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.70680809021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4796867370605</t>
   </si>
   <si>
     <t xml:space="preserve">29.6166248321533</t>
@@ -2954,13 +2954,13 @@
     <t xml:space="preserve">29.2532329559326</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7535667419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0708694458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.889835357666</t>
+    <t xml:space="preserve">28.7535629272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0708656311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8898372650146</t>
   </si>
   <si>
     <t xml:space="preserve">28.6627159118652</t>
@@ -2969,28 +2969,28 @@
     <t xml:space="preserve">28.8444137573242</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7081413269043</t>
+    <t xml:space="preserve">28.7081432342529</t>
   </si>
   <si>
     <t xml:space="preserve">28.9806861877441</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7989883422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8891754150391</t>
+    <t xml:space="preserve">28.7989902496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8891735076904</t>
   </si>
   <si>
     <t xml:space="preserve">29.0715351104736</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2993202209473</t>
+    <t xml:space="preserve">28.2993221282959</t>
   </si>
   <si>
     <t xml:space="preserve">28.0267772674561</t>
   </si>
   <si>
-    <t xml:space="preserve">27.617956161499</t>
+    <t xml:space="preserve">27.6179580688477</t>
   </si>
   <si>
     <t xml:space="preserve">27.7542304992676</t>
@@ -3002,7 +3002,7 @@
     <t xml:space="preserve">28.5718688964844</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4816837310791</t>
+    <t xml:space="preserve">27.4816856384277</t>
   </si>
   <si>
     <t xml:space="preserve">27.5725345611572</t>
@@ -3017,46 +3017,46 @@
     <t xml:space="preserve">27.0274410247803</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9365921020508</t>
+    <t xml:space="preserve">26.9365940093994</t>
   </si>
   <si>
     <t xml:space="preserve">26.9820194244385</t>
   </si>
   <si>
-    <t xml:space="preserve">26.346076965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8918361663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6647129058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2552280426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8457431793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6640510559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4369258880615</t>
+    <t xml:space="preserve">26.3460788726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8918342590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6647148132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2552299499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8457450866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6640491485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4369277954102</t>
   </si>
   <si>
     <t xml:space="preserve">26.5732002258301</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3915023803711</t>
+    <t xml:space="preserve">26.3915004730225</t>
   </si>
   <si>
     <t xml:space="preserve">26.70947265625</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5277767181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9826850891113</t>
+    <t xml:space="preserve">26.527774810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9826831817627</t>
   </si>
   <si>
     <t xml:space="preserve">25.8009872436523</t>
@@ -3068,19 +3068,19 @@
     <t xml:space="preserve">23.6660442352295</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8477439880371</t>
+    <t xml:space="preserve">23.8477458953857</t>
   </si>
   <si>
     <t xml:space="preserve">25.437593460083</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7555618286133</t>
+    <t xml:space="preserve">25.7555637359619</t>
   </si>
   <si>
     <t xml:space="preserve">25.074197769165</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0735359191895</t>
+    <t xml:space="preserve">26.0735340118408</t>
   </si>
   <si>
     <t xml:space="preserve">27.6892356872559</t>
@@ -4317,6 +4317,9 @@
   </si>
   <si>
     <t xml:space="preserve">19.1399993896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9599990844727</t>
   </si>
 </sst>
 </file>
@@ -70175,7 +70178,7 @@
     </row>
     <row r="2521">
       <c r="A2521" s="1" t="n">
-        <v>45988.6911458333</v>
+        <v>45988.3333333333</v>
       </c>
       <c r="B2521" t="n">
         <v>3606</v>
@@ -70184,7 +70187,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="D2521" t="n">
-        <v>19</v>
+        <v>18.8999996185303</v>
       </c>
       <c r="E2521" t="n">
         <v>19.0799999237061</v>
@@ -70196,6 +70199,32 @@
         <v>1433</v>
       </c>
       <c r="H2521" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2522">
+      <c r="A2522" s="1" t="n">
+        <v>45989.6911111111</v>
+      </c>
+      <c r="B2522" t="n">
+        <v>8409</v>
+      </c>
+      <c r="C2522" t="n">
+        <v>19.0599994659424</v>
+      </c>
+      <c r="D2522" t="n">
+        <v>18.8400001525879</v>
+      </c>
+      <c r="E2522" t="n">
+        <v>18.8799991607666</v>
+      </c>
+      <c r="F2522" t="n">
+        <v>18.9599990844727</v>
+      </c>
+      <c r="G2522" t="s">
+        <v>1435</v>
+      </c>
+      <c r="H2522" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ARN.MI.xlsx
+++ b/data/ARN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="1436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1437" uniqueCount="1437">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,34 +38,34 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92215037345886</t>
+    <t xml:space="preserve">1.9221498966217</t>
   </si>
   <si>
     <t xml:space="preserve">ARN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94450068473816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91736054420471</t>
+    <t xml:space="preserve">1.94450080394745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91736042499542</t>
   </si>
   <si>
     <t xml:space="preserve">1.90778195858002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88383507728577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93172931671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91576409339905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83434426784515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8359409570694</t>
+    <t xml:space="preserve">1.88383460044861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93172907829285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91576397418976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83434438705444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83594059944153</t>
   </si>
   <si>
     <t xml:space="preserve">1.91097497940063</t>
@@ -77,22 +77,22 @@
     <t xml:space="preserve">1.74973118305206</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71620559692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80401134490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8103973865509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79602921009064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77208244800568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70662677288055</t>
+    <t xml:space="preserve">1.71620535850525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8040109872818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81039714813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79602909088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77208185195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70662665367126</t>
   </si>
   <si>
     <t xml:space="preserve">1.69704782962799</t>
@@ -101,73 +101,73 @@
     <t xml:space="preserve">1.69066190719604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67629373073578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7002409696579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69864428043365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67469716072083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66671466827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66032910346985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81518650054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82795834541321</t>
+    <t xml:space="preserve">1.67629361152649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70024073123932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69864416122437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67469751834869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66671478748322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66032898426056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81518661975861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82795858383179</t>
   </si>
   <si>
     <t xml:space="preserve">1.86148428916931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88543128967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89181697368622</t>
+    <t xml:space="preserve">1.88543105125427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89181756973267</t>
   </si>
   <si>
     <t xml:space="preserve">1.92853605747223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95407938957214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90618538856506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86786985397339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88064169883728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85190558433533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85988759994507</t>
+    <t xml:space="preserve">1.95407915115356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90618550777435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86786961555481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88064193725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85190522670746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85988771915436</t>
   </si>
   <si>
     <t xml:space="preserve">1.85509836673737</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79283630847931</t>
+    <t xml:space="preserve">1.79283607006073</t>
   </si>
   <si>
     <t xml:space="preserve">1.78804659843445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78006434440613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75611710548401</t>
+    <t xml:space="preserve">1.78006422519684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75611698627472</t>
   </si>
   <si>
     <t xml:space="preserve">1.7688889503479</t>
@@ -176,7 +176,7 @@
     <t xml:space="preserve">1.76409959793091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78485369682312</t>
+    <t xml:space="preserve">1.78485345840454</t>
   </si>
   <si>
     <t xml:space="preserve">1.77048552036285</t>
@@ -185,10 +185,10 @@
     <t xml:space="preserve">1.72099471092224</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73536324501038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.802414894104</t>
+    <t xml:space="preserve">1.73536312580109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80241477489471</t>
   </si>
   <si>
     <t xml:space="preserve">1.76250314712524</t>
@@ -197,34 +197,34 @@
     <t xml:space="preserve">1.74494194984436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73216998577118</t>
+    <t xml:space="preserve">1.73217034339905</t>
   </si>
   <si>
     <t xml:space="preserve">1.73695969581604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74334561824799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75132763385773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68587267398834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67789018154144</t>
+    <t xml:space="preserve">1.7433454990387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75132787227631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68587255477905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67789006233215</t>
   </si>
   <si>
     <t xml:space="preserve">1.65234661102295</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6204172372818</t>
+    <t xml:space="preserve">1.62041711807251</t>
   </si>
   <si>
     <t xml:space="preserve">1.64276790618896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59008431434631</t>
+    <t xml:space="preserve">1.59008419513702</t>
   </si>
   <si>
     <t xml:space="preserve">1.60285592079163</t>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">1.54937446117401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51185715198517</t>
+    <t xml:space="preserve">1.51185727119446</t>
   </si>
   <si>
     <t xml:space="preserve">1.45598089694977</t>
@@ -242,7 +242,7 @@
     <t xml:space="preserve">1.43682312965393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4695508480072</t>
+    <t xml:space="preserve">1.46955096721649</t>
   </si>
   <si>
     <t xml:space="preserve">1.49748909473419</t>
@@ -254,76 +254,76 @@
     <t xml:space="preserve">1.47274386882782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46875250339508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49669075012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47593641281128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50626969337463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47753298282623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43841969966888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40090239048004</t>
+    <t xml:space="preserve">1.46875262260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49669086933136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47593677043915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50626957416534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47753322124481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43841958045959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40090274810791</t>
   </si>
   <si>
     <t xml:space="preserve">1.34901738166809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30910563468933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34342980384827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32666659355164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34103488922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31708800792694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38653421401978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39691162109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40649008750916</t>
+    <t xml:space="preserve">1.30910539627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34342968463898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32666671276093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3410347700119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31708776950836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38653433322906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39691138267517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40649020671844</t>
   </si>
   <si>
     <t xml:space="preserve">1.30671083927155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32347393035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30591261386871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31229841709137</t>
+    <t xml:space="preserve">1.32347369194031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.305912733078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31229865550995</t>
   </si>
   <si>
     <t xml:space="preserve">1.28994786739349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2851585149765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28595662117004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33305251598358</t>
+    <t xml:space="preserve">1.28515863418579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28595685958862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33305263519287</t>
   </si>
   <si>
     <t xml:space="preserve">1.33704376220703</t>
@@ -332,28 +332,28 @@
     <t xml:space="preserve">1.30112326145172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.361048579216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34627270698547</t>
+    <t xml:space="preserve">1.36104869842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34627258777618</t>
   </si>
   <si>
     <t xml:space="preserve">1.35283982753754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33806371688843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2715710401535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28880977630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29291427135468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30686950683594</t>
+    <t xml:space="preserve">1.33806359767914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27157092094421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28880989551544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29291439056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30686962604523</t>
   </si>
   <si>
     <t xml:space="preserve">1.33888459205627</t>
@@ -362,34 +362,34 @@
     <t xml:space="preserve">1.34955620765686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34380984306335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33642196655273</t>
+    <t xml:space="preserve">1.34380996227264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33642172813416</t>
   </si>
   <si>
     <t xml:space="preserve">1.34709358215332</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30522775650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2912722826004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31425750255585</t>
+    <t xml:space="preserve">1.30522787570953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29127252101898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31425762176514</t>
   </si>
   <si>
     <t xml:space="preserve">1.32164573669434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26828753948212</t>
+    <t xml:space="preserve">1.26828742027283</t>
   </si>
   <si>
     <t xml:space="preserve">1.27239191532135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2879890203476</t>
+    <t xml:space="preserve">1.28798890113831</t>
   </si>
   <si>
     <t xml:space="preserve">1.29701888561249</t>
@@ -398,34 +398,34 @@
     <t xml:space="preserve">1.24858582019806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32657110691071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33231735229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35940706729889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42015361785889</t>
+    <t xml:space="preserve">1.32657098770142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33231747150421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3594069480896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42015337944031</t>
   </si>
   <si>
     <t xml:space="preserve">1.48664617538452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53343749046326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51619863510132</t>
+    <t xml:space="preserve">1.53343737125397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51619839668274</t>
   </si>
   <si>
     <t xml:space="preserve">1.51866114139557</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43739247322083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46776556968689</t>
+    <t xml:space="preserve">1.43739223480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46776533126831</t>
   </si>
   <si>
     <t xml:space="preserve">1.43000423908234</t>
@@ -434,166 +434,166 @@
     <t xml:space="preserve">1.40948176383972</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44478034973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55970597267151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61798989772797</t>
+    <t xml:space="preserve">1.44478023052216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5597060918808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61798977851868</t>
   </si>
   <si>
     <t xml:space="preserve">1.70582604408264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74851274490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72388589382172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68284070491791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67463183403015</t>
+    <t xml:space="preserve">1.74851250648499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72388529777527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6828408241272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67463171482086</t>
   </si>
   <si>
     <t xml:space="preserve">1.651646733284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64179587364197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67134821414948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6647812128067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65657198429108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69597518444061</t>
+    <t xml:space="preserve">1.64179575443268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67134809494019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66478097438812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65657186508179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69597506523132</t>
   </si>
   <si>
     <t xml:space="preserve">1.69433319568634</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65821373462677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68119895458221</t>
+    <t xml:space="preserve">1.65821385383606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6811990737915</t>
   </si>
   <si>
     <t xml:space="preserve">1.68776619434357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66806471347809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6500049829483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66313922405243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67791533470154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03746867179871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04403614997864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03911066055298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04075217247009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0522449016571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04731941223145</t>
+    <t xml:space="preserve">1.66806483268738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65000486373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66313910484314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67791545391083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03746891021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04403591156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0391104221344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04075264930725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05224514007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04731965065002</t>
   </si>
   <si>
     <t xml:space="preserve">2.04239416122437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19836497306824</t>
+    <t xml:space="preserve">2.19836449623108</t>
   </si>
   <si>
     <t xml:space="preserve">2.24105143547058</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18851375579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17537951469421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14582777023315</t>
+    <t xml:space="preserve">2.18851399421692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17537999153137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14582753181458</t>
   </si>
   <si>
     <t xml:space="preserve">2.00627446174622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98821496963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99313998222351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99806547164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99642395973206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9997079372406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00299096107483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00791668891907</t>
+    <t xml:space="preserve">1.98821449279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99314022064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99806559085846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99642372131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99970769882202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00299119949341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00791645050049</t>
   </si>
   <si>
     <t xml:space="preserve">2.01120018959045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02597594261169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03254318237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02105093002319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01940870285034</t>
+    <t xml:space="preserve">2.02597618103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03254365921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02105069160461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01940894126892</t>
   </si>
   <si>
     <t xml:space="preserve">2.02433443069458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07687163352966</t>
+    <t xml:space="preserve">2.07687211036682</t>
   </si>
   <si>
     <t xml:space="preserve">2.0588116645813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09657311439514</t>
+    <t xml:space="preserve">2.09657335281372</t>
   </si>
   <si>
     <t xml:space="preserve">2.14746928215027</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33955931663513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27552914619446</t>
+    <t xml:space="preserve">2.33955907821655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27552938461304</t>
   </si>
   <si>
     <t xml:space="preserve">2.32478308677673</t>
@@ -602,10 +602,10 @@
     <t xml:space="preserve">2.27881288528442</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25746965408325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29851388931274</t>
+    <t xml:space="preserve">2.25746941566467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2985143661499</t>
   </si>
   <si>
     <t xml:space="preserve">2.26075315475464</t>
@@ -617,13 +617,13 @@
     <t xml:space="preserve">2.30672335624695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35597705841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3412013053894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3428430557251</t>
+    <t xml:space="preserve">2.35597729682922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34120082855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34284329414368</t>
   </si>
   <si>
     <t xml:space="preserve">2.34776782989502</t>
@@ -632,64 +632,64 @@
     <t xml:space="preserve">2.44627594947815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39209651947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38224577903748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38717126846313</t>
+    <t xml:space="preserve">2.39209723472595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38224601745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38717103004456</t>
   </si>
   <si>
     <t xml:space="preserve">2.38388776779175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40523099899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38060402870178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42164874076843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33791756629944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32314109802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35433554649353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41015601158142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40687251091003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4380669593811</t>
+    <t xml:space="preserve">2.4052312374115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38060426712036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42164945602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33791732788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32314133644104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35433530807495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41015648841858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40687274932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43806743621826</t>
   </si>
   <si>
     <t xml:space="preserve">2.4183657169342</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29030513763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34940981864929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36418628692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3756787776947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40194749832153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35761880874634</t>
+    <t xml:space="preserve">2.29030561447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34941005706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36418604850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37567925453186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40194773674011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35761904716492</t>
   </si>
   <si>
     <t xml:space="preserve">2.36746954917908</t>
@@ -698,28 +698,28 @@
     <t xml:space="preserve">2.37075304985046</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37239527702332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36254453659058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36582803726196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3953800201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37732005119324</t>
+    <t xml:space="preserve">2.37239551544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36254405975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36582827568054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39538049697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37732028961182</t>
   </si>
   <si>
     <t xml:space="preserve">2.37403678894043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38881278038025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39373850822449</t>
+    <t xml:space="preserve">2.38881349563599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39373803138733</t>
   </si>
   <si>
     <t xml:space="preserve">2.39045476913452</t>
@@ -728,34 +728,34 @@
     <t xml:space="preserve">2.41343998908997</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40358877182007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40030550956726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40851449966431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42329049110413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43149948120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42000722885132</t>
+    <t xml:space="preserve">2.40358924865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40030574798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40851473808289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42329072952271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43149971961975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42000699043274</t>
   </si>
   <si>
     <t xml:space="preserve">2.35105180740356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33627557754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34612631797791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43642544746399</t>
+    <t xml:space="preserve">2.33627581596375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34612655639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43642497062683</t>
   </si>
   <si>
     <t xml:space="preserve">2.42657446861267</t>
@@ -767,22 +767,22 @@
     <t xml:space="preserve">2.4528431892395</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47701334953308</t>
+    <t xml:space="preserve">2.4770131111145</t>
   </si>
   <si>
     <t xml:space="preserve">2.47868013381958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49201536178589</t>
+    <t xml:space="preserve">2.49201512336731</t>
   </si>
   <si>
     <t xml:space="preserve">2.49368214607239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47534608840942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46534490585327</t>
+    <t xml:space="preserve">2.47534656524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46534442901611</t>
   </si>
   <si>
     <t xml:space="preserve">2.48201370239258</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">2.46867847442627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45867729187012</t>
+    <t xml:space="preserve">2.45867776870728</t>
   </si>
   <si>
     <t xml:space="preserve">2.46201109886169</t>
@@ -803,7 +803,7 @@
     <t xml:space="preserve">2.41700482368469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40867042541504</t>
+    <t xml:space="preserve">2.40867018699646</t>
   </si>
   <si>
     <t xml:space="preserve">2.36699771881104</t>
@@ -815,25 +815,25 @@
     <t xml:space="preserve">2.36866474151611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35366272926331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38533353805542</t>
+    <t xml:space="preserve">2.35366225242615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.385333776474</t>
   </si>
   <si>
     <t xml:space="preserve">2.38366651535034</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36366415023804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32532525062561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31699061393738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28531980514526</t>
+    <t xml:space="preserve">2.36366391181946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32532548904419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3169903755188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28531956672668</t>
   </si>
   <si>
     <t xml:space="preserve">2.28698635101318</t>
@@ -842,7 +842,7 @@
     <t xml:space="preserve">2.29698777198792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31532382965088</t>
+    <t xml:space="preserve">2.31532406806946</t>
   </si>
   <si>
     <t xml:space="preserve">2.28365254402161</t>
@@ -851,73 +851,73 @@
     <t xml:space="preserve">2.28865361213684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29032015800476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30198884010315</t>
+    <t xml:space="preserve">2.29031991958618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30198860168457</t>
   </si>
   <si>
     <t xml:space="preserve">2.30365562438965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29365420341492</t>
+    <t xml:space="preserve">2.2936544418335</t>
   </si>
   <si>
     <t xml:space="preserve">2.24198031425476</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2669837474823</t>
+    <t xml:space="preserve">2.26698350906372</t>
   </si>
   <si>
     <t xml:space="preserve">2.2686505317688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32699179649353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31865739822388</t>
+    <t xml:space="preserve">2.32699227333069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31865763664246</t>
   </si>
   <si>
     <t xml:space="preserve">2.3103232383728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24364709854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25031471252441</t>
+    <t xml:space="preserve">2.24364686012268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25031447410583</t>
   </si>
   <si>
     <t xml:space="preserve">2.22531127929688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25198173522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22197723388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20697522163391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20030784606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16863679885864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17863845825195</t>
+    <t xml:space="preserve">2.25198149681091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2219774723053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20697546005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20030760765076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16863703727722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17863821983337</t>
   </si>
   <si>
     <t xml:space="preserve">2.16696953773499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18697237968445</t>
+    <t xml:space="preserve">2.18697261810303</t>
   </si>
   <si>
     <t xml:space="preserve">2.19697380065918</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18363881111145</t>
+    <t xml:space="preserve">2.18363857269287</t>
   </si>
   <si>
     <t xml:space="preserve">2.18530559539795</t>
@@ -929,25 +929,25 @@
     <t xml:space="preserve">2.17530417442322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14196610450745</t>
+    <t xml:space="preserve">2.1419665813446</t>
   </si>
   <si>
     <t xml:space="preserve">2.15363454818726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1436333656311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13529872894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12696433067322</t>
+    <t xml:space="preserve">2.14363312721252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13529849052429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12696409225464</t>
   </si>
   <si>
     <t xml:space="preserve">2.12863111495972</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12029671669006</t>
+    <t xml:space="preserve">2.12029623985291</t>
   </si>
   <si>
     <t xml:space="preserve">2.13029813766479</t>
@@ -956,10 +956,10 @@
     <t xml:space="preserve">2.11862993240356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37366533279419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37533235549927</t>
+    <t xml:space="preserve">2.37366557121277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37533187866211</t>
   </si>
   <si>
     <t xml:space="preserve">2.40700316429138</t>
@@ -968,61 +968,61 @@
     <t xml:space="preserve">2.39533519744873</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39200091362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49868249893188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49534893035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50868439674377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51201772689819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51535177230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51701879501343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.523686170578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5253529548645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54535579681396</t>
+    <t xml:space="preserve">2.39200139045715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49868273735046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49534916877747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50868463516235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51201796531677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51535153388977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51701831817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52368640899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52535343170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54535627365112</t>
   </si>
   <si>
     <t xml:space="preserve">2.53368735313416</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53202080726624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54035568237305</t>
+    <t xml:space="preserve">2.53202128410339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54035520553589</t>
   </si>
   <si>
     <t xml:space="preserve">2.52702021598816</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53868818283081</t>
+    <t xml:space="preserve">2.53868842124939</t>
   </si>
   <si>
     <t xml:space="preserve">2.53702139854431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49701595306396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42700624465942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50034976005554</t>
+    <t xml:space="preserve">2.49701571464539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42700600624084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50034952163696</t>
   </si>
   <si>
     <t xml:space="preserve">2.5053505897522</t>
@@ -1031,13 +1031,13 @@
     <t xml:space="preserve">2.48368072509766</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45200991630554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51368498802185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54202175140381</t>
+    <t xml:space="preserve">2.45200967788696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51368474960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54202222824097</t>
   </si>
   <si>
     <t xml:space="preserve">2.54868984222412</t>
@@ -1046,46 +1046,46 @@
     <t xml:space="preserve">2.51035118103027</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52035212516785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47201228141785</t>
+    <t xml:space="preserve">2.52035236358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47201251983643</t>
   </si>
   <si>
     <t xml:space="preserve">2.50201654434204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48701477050781</t>
+    <t xml:space="preserve">2.48701453208923</t>
   </si>
   <si>
     <t xml:space="preserve">3.00041961669922</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81706070899963</t>
+    <t xml:space="preserve">2.81706094741821</t>
   </si>
   <si>
     <t xml:space="preserve">2.75038456916809</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7170467376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80872654914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80039167404175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83372974395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78372263908386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84206438064575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75871872901917</t>
+    <t xml:space="preserve">2.71704649925232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80872631072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80039143562317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83372950553894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78372240066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84206414222717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75871968269348</t>
   </si>
   <si>
     <t xml:space="preserve">2.85039877891541</t>
@@ -1094,46 +1094,46 @@
     <t xml:space="preserve">2.85873341560364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89207124710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82539486885071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72538137435913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61703252792358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6420361995697</t>
+    <t xml:space="preserve">2.89207148551941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82539558410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72538113594055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61703276634216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64203643798828</t>
   </si>
   <si>
     <t xml:space="preserve">2.70037770271301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65870499610901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6253674030304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63370203971863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59202909469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66703987121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70871210098267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74204993247986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65037059783936</t>
+    <t xml:space="preserve">2.65870547294617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62536716461182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63370180130005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59202933311462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66703963279724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70871233940125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74205017089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65037083625793</t>
   </si>
   <si>
     <t xml:space="preserve">2.68370866775513</t>
@@ -1142,7 +1142,7 @@
     <t xml:space="preserve">2.6003634929657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58369493484497</t>
+    <t xml:space="preserve">2.58369469642639</t>
   </si>
   <si>
     <t xml:space="preserve">2.56702566146851</t>
@@ -1151,40 +1151,40 @@
     <t xml:space="preserve">2.76705360412598</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73371577262878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79205727577209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86706757545471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87540221214294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88373684883118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77538847923279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78091406822205</t>
+    <t xml:space="preserve">2.73371529579163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79205703735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86706781387329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87540245056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8837366104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77538824081421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78091382980347</t>
   </si>
   <si>
     <t xml:space="preserve">2.72174549102783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7301983833313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77246141433716</t>
+    <t xml:space="preserve">2.73019814491272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7724609375</t>
   </si>
   <si>
     <t xml:space="preserve">2.645672082901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70483994483948</t>
+    <t xml:space="preserve">2.70484018325806</t>
   </si>
   <si>
     <t xml:space="preserve">2.68793511390686</t>
@@ -1196,13 +1196,13 @@
     <t xml:space="preserve">2.69638776779175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65412473678589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60340881347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63721919059753</t>
+    <t xml:space="preserve">2.65412449836731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60340857505798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63721895217896</t>
   </si>
   <si>
     <t xml:space="preserve">2.61186146736145</t>
@@ -1211,85 +1211,85 @@
     <t xml:space="preserve">2.5780508518219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59495615959167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50197744369507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49352478981018</t>
+    <t xml:space="preserve">2.5949559211731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50197696685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49352502822876</t>
   </si>
   <si>
     <t xml:space="preserve">2.54424071311951</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56114554405212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58650350570679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51888227462769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53578805923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55269312858582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5104296207428</t>
+    <t xml:space="preserve">2.5611457824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58650326728821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51888251304626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53578758239746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55269265174866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51043009757996</t>
   </si>
   <si>
     <t xml:space="preserve">2.56959795951843</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46816682815552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48507213592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41745042800903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45126128196716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39209318161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38364028930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27375626564026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29911422729492</t>
+    <t xml:space="preserve">2.46816658973694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48507189750671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41745066642761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45126152038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39209294319153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38364052772522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27375650405884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29911398887634</t>
   </si>
   <si>
     <t xml:space="preserve">2.36673498153687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35828232765198</t>
+    <t xml:space="preserve">2.35828280448914</t>
   </si>
   <si>
     <t xml:space="preserve">2.43435621261597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4259033203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34982991218567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28220891952515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32447195053101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4089982509613</t>
+    <t xml:space="preserve">2.42590379714966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34982967376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28220868110657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32447218894958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40899801254272</t>
   </si>
   <si>
     <t xml:space="preserve">2.45971417427063</t>
@@ -1307,13 +1307,13 @@
     <t xml:space="preserve">2.40054559707642</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37518763542175</t>
+    <t xml:space="preserve">2.37518787384033</t>
   </si>
   <si>
     <t xml:space="preserve">2.47661948204041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30756664276123</t>
+    <t xml:space="preserve">2.30756688117981</t>
   </si>
   <si>
     <t xml:space="preserve">2.23994588851929</t>
@@ -1325,10 +1325,10 @@
     <t xml:space="preserve">2.23437643051147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2429370880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33710670471191</t>
+    <t xml:space="preserve">2.24293732643127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33710646629333</t>
   </si>
   <si>
     <t xml:space="preserve">2.25149846076965</t>
@@ -1337,31 +1337,31 @@
     <t xml:space="preserve">2.27718067169189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26861977577209</t>
+    <t xml:space="preserve">2.26862001419067</t>
   </si>
   <si>
     <t xml:space="preserve">2.44839715957642</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37134981155396</t>
+    <t xml:space="preserve">2.37134957313538</t>
   </si>
   <si>
     <t xml:space="preserve">2.31142377853394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28574180603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26005887985229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35422825813293</t>
+    <t xml:space="preserve">2.28574132919312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26005911827087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35422801971436</t>
   </si>
   <si>
     <t xml:space="preserve">2.22581553459167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20869398117065</t>
+    <t xml:space="preserve">2.20869421958923</t>
   </si>
   <si>
     <t xml:space="preserve">2.30286312103271</t>
@@ -1373,40 +1373,40 @@
     <t xml:space="preserve">2.37991046905518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40559315681458</t>
+    <t xml:space="preserve">2.405592918396</t>
   </si>
   <si>
     <t xml:space="preserve">2.39703226089478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32854533195496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38847136497498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36278915405273</t>
+    <t xml:space="preserve">2.32854557037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38847160339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36278891563416</t>
   </si>
   <si>
     <t xml:space="preserve">2.34566736221313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20013284683228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18301153182983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4398365020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5425660610199</t>
+    <t xml:space="preserve">2.20013332366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18301129341125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43983626365662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54256653785706</t>
   </si>
   <si>
     <t xml:space="preserve">2.60249185562134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69666123390198</t>
+    <t xml:space="preserve">2.69666147232056</t>
   </si>
   <si>
     <t xml:space="preserve">2.77370882034302</t>
@@ -1415,7 +1415,7 @@
     <t xml:space="preserve">2.63673543930054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.670978307724</t>
+    <t xml:space="preserve">2.67097854614258</t>
   </si>
   <si>
     <t xml:space="preserve">2.61961364746094</t>
@@ -1430,7 +1430,7 @@
     <t xml:space="preserve">2.64529633522034</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71378302574158</t>
+    <t xml:space="preserve">2.71378326416016</t>
   </si>
   <si>
     <t xml:space="preserve">2.72234392166138</t>
@@ -1439,19 +1439,19 @@
     <t xml:space="preserve">3.07333779335022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52706170082092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59554839134216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65547394752502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58698797225952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61266946792603</t>
+    <t xml:space="preserve">3.52706146240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59554767608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6554741859436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58698773384094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61266994476318</t>
   </si>
   <si>
     <t xml:space="preserve">3.5356228351593</t>
@@ -1460,55 +1460,55 @@
     <t xml:space="preserve">3.42433190345764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54418325424194</t>
+    <t xml:space="preserve">3.54418301582336</t>
   </si>
   <si>
     <t xml:space="preserve">3.56986618041992</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5527446269989</t>
+    <t xml:space="preserve">3.55274415016174</t>
   </si>
   <si>
     <t xml:space="preserve">3.56130480766296</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5099401473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48425769805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57842683792114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63835263252258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74108242988586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16912364959717</t>
+    <t xml:space="preserve">3.50993990898132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48425793647766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57842659950256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63835287094116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74108266830444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16912412643433</t>
   </si>
   <si>
     <t xml:space="preserve">4.60572624206543</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15361976623535</t>
+    <t xml:space="preserve">5.15361928939819</t>
   </si>
   <si>
     <t xml:space="preserve">4.62284755706787</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19480609893799</t>
+    <t xml:space="preserve">4.19480657577515</t>
   </si>
   <si>
     <t xml:space="preserve">4.45163106918335</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53723955154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52011775970459</t>
+    <t xml:space="preserve">4.53724002838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52011823654175</t>
   </si>
   <si>
     <t xml:space="preserve">4.58860445022583</t>
@@ -1517,19 +1517,19 @@
     <t xml:space="preserve">4.34890127182007</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16056394577026</t>
+    <t xml:space="preserve">4.16056346893311</t>
   </si>
   <si>
     <t xml:space="preserve">4.23761034011841</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29753637313843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89517784118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27879786491394</t>
+    <t xml:space="preserve">4.29753684997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89517736434937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27879762649536</t>
   </si>
   <si>
     <t xml:space="preserve">3.25311517715454</t>
@@ -1538,13 +1538,13 @@
     <t xml:space="preserve">2.89356017112732</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15894603729248</t>
+    <t xml:space="preserve">3.15894627571106</t>
   </si>
   <si>
     <t xml:space="preserve">3.16750693321228</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03909420967102</t>
+    <t xml:space="preserve">3.0390944480896</t>
   </si>
   <si>
     <t xml:space="preserve">3.44145369529724</t>
@@ -1556,91 +1556,91 @@
     <t xml:space="preserve">3.39008855819702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84381222724915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83525156974792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87805581092834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76676487922668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88661623001099</t>
+    <t xml:space="preserve">3.84381246566772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83525133132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8780562877655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76676464080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88661646842957</t>
   </si>
   <si>
     <t xml:space="preserve">3.85237312316895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92942118644714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95510339736938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93798136711121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11775875091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25473165512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22905015945435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26329326629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28041505813599</t>
+    <t xml:space="preserve">3.92942047119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95510292053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93798184394836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11775922775269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25473213195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22904968261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26329278945923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28041458129883</t>
   </si>
   <si>
     <t xml:space="preserve">4.43450975418091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20336723327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00646829605103</t>
+    <t xml:space="preserve">4.20336675643921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00646734237671</t>
   </si>
   <si>
     <t xml:space="preserve">4.10919809341431</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15200185775757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08351564407349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94654202461243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07495498657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02359008789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96366357803345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13488101959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12632036209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01664638519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70845651626587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91391563415527</t>
+    <t xml:space="preserve">4.15200281143188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08351612091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94654250144958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07495450973511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02358961105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96366453170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13488054275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12631988525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01664590835571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70845603942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91391611099243</t>
   </si>
   <si>
     <t xml:space="preserve">4.96528148651123</t>
@@ -1658,7 +1658,7 @@
     <t xml:space="preserve">5.68439054489136</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95833730697632</t>
+    <t xml:space="preserve">5.95833683013916</t>
   </si>
   <si>
     <t xml:space="preserve">5.90697288513184</t>
@@ -1667,16 +1667,16 @@
     <t xml:space="preserve">5.88985061645508</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57471656799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12955379486084</t>
+    <t xml:space="preserve">6.57471704483032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.129554271698</t>
   </si>
   <si>
     <t xml:space="preserve">6.4035005569458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0198802947998</t>
+    <t xml:space="preserve">7.01987981796265</t>
   </si>
   <si>
     <t xml:space="preserve">7.20821857452393</t>
@@ -1685,10 +1685,10 @@
     <t xml:space="preserve">7.32807016372681</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05412340164185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00275897979736</t>
+    <t xml:space="preserve">7.05412292480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00275850296021</t>
   </si>
   <si>
     <t xml:space="preserve">7.42397737503052</t>
@@ -1700,16 +1700,16 @@
     <t xml:space="preserve">6.87990283966064</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96765661239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59909105300903</t>
+    <t xml:space="preserve">6.9676570892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59909057617188</t>
   </si>
   <si>
     <t xml:space="preserve">6.51133728027344</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73949670791626</t>
+    <t xml:space="preserve">6.7394962310791</t>
   </si>
   <si>
     <t xml:space="preserve">6.84480142593384</t>
@@ -1724,34 +1724,34 @@
     <t xml:space="preserve">6.66929388046265</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45868539810181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4060320854187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31827878952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80970048904419</t>
+    <t xml:space="preserve">6.45868492126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40603303909302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31827831268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80970001220703</t>
   </si>
   <si>
     <t xml:space="preserve">7.17826700210571</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35377502441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26601982116699</t>
+    <t xml:space="preserve">7.35377407073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26602029800415</t>
   </si>
   <si>
     <t xml:space="preserve">7.05541133880615</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07296276092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63419246673584</t>
+    <t xml:space="preserve">7.07296228408813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63419198989868</t>
   </si>
   <si>
     <t xml:space="preserve">6.44113397598267</t>
@@ -1760,37 +1760,37 @@
     <t xml:space="preserve">6.30072784423828</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05501699447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03746604919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37053632736206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40563821792603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52849340438843</t>
+    <t xml:space="preserve">6.055016040802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03746557235718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37053680419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40563869476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52849388122559</t>
   </si>
   <si>
     <t xml:space="preserve">5.65134906768799</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12521982192993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96726322174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01991558074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91461086273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84440755844116</t>
+    <t xml:space="preserve">6.12521934509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96726274490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01991510391235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91460990905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.844407081604</t>
   </si>
   <si>
     <t xml:space="preserve">5.94971227645874</t>
@@ -1808,16 +1808,16 @@
     <t xml:space="preserve">5.87950897216797</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79175519943237</t>
+    <t xml:space="preserve">5.79175472259521</t>
   </si>
   <si>
     <t xml:space="preserve">5.68645048141479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45829010009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63379859924316</t>
+    <t xml:space="preserve">5.45829057693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63379812240601</t>
   </si>
   <si>
     <t xml:space="preserve">5.70400142669678</t>
@@ -1835,10 +1835,10 @@
     <t xml:space="preserve">5.61624765396118</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49339199066162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31788396835327</t>
+    <t xml:space="preserve">5.49339246749878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31788444519043</t>
   </si>
   <si>
     <t xml:space="preserve">5.17747783660889</t>
@@ -1847,85 +1847,85 @@
     <t xml:space="preserve">5.26523208618164</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28278303146362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35298538208008</t>
+    <t xml:space="preserve">5.28278255462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35298633575439</t>
   </si>
   <si>
     <t xml:space="preserve">5.42318916320801</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47584056854248</t>
+    <t xml:space="preserve">5.47584104537964</t>
   </si>
   <si>
     <t xml:space="preserve">5.38808727264404</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51094245910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77420473098755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44073963165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54604434967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23052406311035</t>
+    <t xml:space="preserve">5.51094341278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77420425415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44074010848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54604482650757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23052501678467</t>
   </si>
   <si>
     <t xml:space="preserve">6.35338020324707</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16032123565674</t>
+    <t xml:space="preserve">6.1603217124939</t>
   </si>
   <si>
     <t xml:space="preserve">6.37093114852905</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47623586654663</t>
+    <t xml:space="preserve">6.47623538970947</t>
   </si>
   <si>
     <t xml:space="preserve">6.42358303070068</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54643821716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98520803451538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33622360229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0905122756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16071557998657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19581747055054</t>
+    <t xml:space="preserve">6.54643869400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98520851135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33622312545776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09051275253296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16071510314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19581699371338</t>
   </si>
   <si>
     <t xml:space="preserve">6.95010614395142</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14316511154175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12561368942261</t>
+    <t xml:space="preserve">7.14316558837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12561416625977</t>
   </si>
   <si>
     <t xml:space="preserve">7.02030944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8451943397522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3366174697876</t>
+    <t xml:space="preserve">7.84519577026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33661842346191</t>
   </si>
   <si>
     <t xml:space="preserve">8.31906604766846</t>
@@ -1937,58 +1937,58 @@
     <t xml:space="preserve">9.0825252532959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68763160705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03864765167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30190944671631</t>
+    <t xml:space="preserve">8.68763256072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03864860534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30191040039062</t>
   </si>
   <si>
     <t xml:space="preserve">11.2763719558716</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1630802154541</t>
+    <t xml:space="preserve">13.1630792617798</t>
   </si>
   <si>
     <t xml:space="preserve">13.0753259658813</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1192026138306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8559417724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0222806930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1100339889526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9345264434814</t>
+    <t xml:space="preserve">13.1192035675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8559408187866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0222797393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.110032081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9345254898071</t>
   </si>
   <si>
     <t xml:space="preserve">11.36412525177</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8814792633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1539106369019</t>
+    <t xml:space="preserve">10.88148021698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1539115905762</t>
   </si>
   <si>
     <t xml:space="preserve">11.6712646484375</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7151412963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4518804550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0569868087769</t>
+    <t xml:space="preserve">11.715142250061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4518795013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0569877624512</t>
   </si>
   <si>
     <t xml:space="preserve">11.495756149292</t>
@@ -2003,28 +2003,28 @@
     <t xml:space="preserve">11.8028945922852</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3202495574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.627387046814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1447401046753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6182193756104</t>
+    <t xml:space="preserve">11.3202486038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6273880004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1447410583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6182174682617</t>
   </si>
   <si>
     <t xml:space="preserve">10.5304641723633</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5743398666382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7498502731323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6620950698853</t>
+    <t xml:space="preserve">10.5743417739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7498483657837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6620941162109</t>
   </si>
   <si>
     <t xml:space="preserve">10.3549556732178</t>
@@ -2045,16 +2045,16 @@
     <t xml:space="preserve">11.1886177062988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1008644104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3553504943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2675971984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0218849182129</t>
+    <t xml:space="preserve">11.1008634567261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3553495407104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.267596244812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0218868255615</t>
   </si>
   <si>
     <t xml:space="preserve">11.2500448226929</t>
@@ -2066,10 +2066,10 @@
     <t xml:space="preserve">11.2851467132568</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1973943710327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8467721939087</t>
+    <t xml:space="preserve">11.1973934173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8467712402344</t>
   </si>
   <si>
     <t xml:space="preserve">11.9871778488159</t>
@@ -2078,10 +2078,10 @@
     <t xml:space="preserve">12.2855415344238</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2504396438599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1626863479614</t>
+    <t xml:space="preserve">12.2504386901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1626853942871</t>
   </si>
   <si>
     <t xml:space="preserve">12.4672012329102</t>
@@ -2093,19 +2093,19 @@
     <t xml:space="preserve">12.0910358428955</t>
   </si>
   <si>
-    <t xml:space="preserve">11.553656578064</t>
+    <t xml:space="preserve">11.5536556243896</t>
   </si>
   <si>
     <t xml:space="preserve">11.6432199478149</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3924427032471</t>
+    <t xml:space="preserve">11.3924417495728</t>
   </si>
   <si>
     <t xml:space="preserve">10.9446268081665</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5505485534668</t>
+    <t xml:space="preserve">10.5505475997925</t>
   </si>
   <si>
     <t xml:space="preserve">10.6759366989136</t>
@@ -2120,10 +2120,10 @@
     <t xml:space="preserve">10.6580238342285</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9267129898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0521020889282</t>
+    <t xml:space="preserve">10.9267139434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0521030426025</t>
   </si>
   <si>
     <t xml:space="preserve">11.4999189376831</t>
@@ -2132,13 +2132,13 @@
     <t xml:space="preserve">11.4820051193237</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4282684326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.571569442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3745288848877</t>
+    <t xml:space="preserve">11.4282674789429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5715684890747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.374529838562</t>
   </si>
   <si>
     <t xml:space="preserve">11.3566179275513</t>
@@ -2147,13 +2147,13 @@
     <t xml:space="preserve">11.3207921981812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4461803436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.464093208313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7148704528809</t>
+    <t xml:space="preserve">11.4461793899536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4640941619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7148694992065</t>
   </si>
   <si>
     <t xml:space="preserve">11.7327823638916</t>
@@ -2180,7 +2180,7 @@
     <t xml:space="preserve">11.6969575881958</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1268615722656</t>
+    <t xml:space="preserve">12.1268606185913</t>
   </si>
   <si>
     <t xml:space="preserve">12.0552101135254</t>
@@ -2192,7 +2192,7 @@
     <t xml:space="preserve">11.9298219680786</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2880754470825</t>
+    <t xml:space="preserve">12.2880744934082</t>
   </si>
   <si>
     <t xml:space="preserve">12.5925893783569</t>
@@ -2201,22 +2201,22 @@
     <t xml:space="preserve">12.503026008606</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9835596084595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3239002227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9804525375366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1774892807007</t>
+    <t xml:space="preserve">11.9835605621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3239011764526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9804515838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1774911880493</t>
   </si>
   <si>
     <t xml:space="preserve">11.284966468811</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3387041091919</t>
+    <t xml:space="preserve">11.3387050628662</t>
   </si>
   <si>
     <t xml:space="preserve">11.8939962387085</t>
@@ -2225,16 +2225,16 @@
     <t xml:space="preserve">11.7686080932617</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6253051757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0014724731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1089477539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9656467437744</t>
+    <t xml:space="preserve">11.6253070831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0014715194702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1089487075806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9656457901001</t>
   </si>
   <si>
     <t xml:space="preserve">12.1985120773315</t>
@@ -2243,16 +2243,16 @@
     <t xml:space="preserve">12.43137550354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2522497177124</t>
+    <t xml:space="preserve">12.2522487640381</t>
   </si>
   <si>
     <t xml:space="preserve">12.8612794876099</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8433666229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6821517944336</t>
+    <t xml:space="preserve">12.8433675765991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6821527481079</t>
   </si>
   <si>
     <t xml:space="preserve">12.7358913421631</t>
@@ -2279,22 +2279,22 @@
     <t xml:space="preserve">13.8823003768921</t>
   </si>
   <si>
-    <t xml:space="preserve">13.864387512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5777854919434</t>
+    <t xml:space="preserve">13.8643884658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5777864456177</t>
   </si>
   <si>
     <t xml:space="preserve">13.4703102111816</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6852607727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6673498153687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5598726272583</t>
+    <t xml:space="preserve">13.6852598190308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6673488616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.559871673584</t>
   </si>
   <si>
     <t xml:space="preserve">13.6136102676392</t>
@@ -2303,7 +2303,7 @@
     <t xml:space="preserve">13.8285617828369</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9539518356323</t>
+    <t xml:space="preserve">13.953950881958</t>
   </si>
   <si>
     <t xml:space="preserve">13.4344844818115</t>
@@ -2312,10 +2312,10 @@
     <t xml:space="preserve">13.7210865020752</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5240468978882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7031745910645</t>
+    <t xml:space="preserve">13.5240478515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7031736373901</t>
   </si>
   <si>
     <t xml:space="preserve">13.2553577423096</t>
@@ -2324,10 +2324,10 @@
     <t xml:space="preserve">13.4523963928223</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3090944290161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2763776779175</t>
+    <t xml:space="preserve">13.3090953826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2763786315918</t>
   </si>
   <si>
     <t xml:space="preserve">14.4196796417236</t>
@@ -2336,7 +2336,7 @@
     <t xml:space="preserve">14.0256013870239</t>
   </si>
   <si>
-    <t xml:space="preserve">13.756911277771</t>
+    <t xml:space="preserve">13.7569122314453</t>
   </si>
   <si>
     <t xml:space="preserve">14.4375944137573</t>
@@ -2360,7 +2360,7 @@
     <t xml:space="preserve">21.316047668457</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4503936767578</t>
+    <t xml:space="preserve">21.4503955841064</t>
   </si>
   <si>
     <t xml:space="preserve">21.5399570465088</t>
@@ -2378,10 +2378,10 @@
     <t xml:space="preserve">23.017749786377</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3460254669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1221179962158</t>
+    <t xml:space="preserve">22.3460273742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1221199035645</t>
   </si>
   <si>
     <t xml:space="preserve">23.7342548370361</t>
@@ -2390,22 +2390,22 @@
     <t xml:space="preserve">21.8982086181641</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4355888366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.495174407959</t>
+    <t xml:space="preserve">22.4355869293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4951725006104</t>
   </si>
   <si>
     <t xml:space="preserve">21.7190818786621</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9429931640625</t>
+    <t xml:space="preserve">21.9429912567139</t>
   </si>
   <si>
     <t xml:space="preserve">21.7638645172119</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8534259796143</t>
+    <t xml:space="preserve">21.8534278869629</t>
   </si>
   <si>
     <t xml:space="preserve">23.3312206268311</t>
@@ -2420,13 +2420,13 @@
     <t xml:space="preserve">25.3016128540039</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2420253753662</t>
+    <t xml:space="preserve">26.2420234680176</t>
   </si>
   <si>
     <t xml:space="preserve">25.525520324707</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2120475769043</t>
+    <t xml:space="preserve">25.2120494842529</t>
   </si>
   <si>
     <t xml:space="preserve">25.8837718963623</t>
@@ -2435,10 +2435,10 @@
     <t xml:space="preserve">25.4807376861572</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5703010559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1224842071533</t>
+    <t xml:space="preserve">25.5702991485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.122486114502</t>
   </si>
   <si>
     <t xml:space="preserve">24.361198425293</t>
@@ -2474,7 +2474,7 @@
     <t xml:space="preserve">26.5554962158203</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9881381988525</t>
+    <t xml:space="preserve">24.9881401062012</t>
   </si>
   <si>
     <t xml:space="preserve">25.2568302154541</t>
@@ -2492,13 +2492,13 @@
     <t xml:space="preserve">24.5851058959961</t>
   </si>
   <si>
-    <t xml:space="preserve">22.077335357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.928186416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1968746185303</t>
+    <t xml:space="preserve">22.0773334503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9281883239746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1968765258789</t>
   </si>
   <si>
     <t xml:space="preserve">24.182071685791</t>
@@ -2510,13 +2510,13 @@
     <t xml:space="preserve">24.4955425262451</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3164138793945</t>
+    <t xml:space="preserve">24.3164157867432</t>
   </si>
   <si>
     <t xml:space="preserve">22.3908061981201</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8238182067871</t>
+    <t xml:space="preserve">23.8238201141357</t>
   </si>
   <si>
     <t xml:space="preserve">23.0625305175781</t>
@@ -2528,28 +2528,28 @@
     <t xml:space="preserve">22.8834018707275</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2416591644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1672687530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3167819976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6002788543701</t>
+    <t xml:space="preserve">23.2416572570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1672668457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3167839050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6002807617188</t>
   </si>
   <si>
     <t xml:space="preserve">25.615083694458</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4359550476074</t>
+    <t xml:space="preserve">25.4359569549561</t>
   </si>
   <si>
     <t xml:space="preserve">24.8985767364502</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9733371734619</t>
+    <t xml:space="preserve">25.9733352661133</t>
   </si>
   <si>
     <t xml:space="preserve">26.5107154846191</t>
@@ -2564,16 +2564,16 @@
     <t xml:space="preserve">26.6450595855713</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4959106445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0480937957764</t>
+    <t xml:space="preserve">27.4959125518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.048095703125</t>
   </si>
   <si>
     <t xml:space="preserve">27.9437255859375</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8841400146484</t>
+    <t xml:space="preserve">28.8841419219971</t>
   </si>
   <si>
     <t xml:space="preserve">28.9289207458496</t>
@@ -2582,10 +2582,10 @@
     <t xml:space="preserve">28.7050151824951</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7797737121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9885063171387</t>
+    <t xml:space="preserve">29.7797718048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9885082244873</t>
   </si>
   <si>
     <t xml:space="preserve">27.630256652832</t>
@@ -2594,13 +2594,13 @@
     <t xml:space="preserve">27.2272205352783</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4063491821289</t>
+    <t xml:space="preserve">27.4063472747803</t>
   </si>
   <si>
     <t xml:space="preserve">26.6898403167725</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8389930725098</t>
+    <t xml:space="preserve">25.8389892578125</t>
   </si>
   <si>
     <t xml:space="preserve">25.79421043396</t>
@@ -2615,7 +2615,7 @@
     <t xml:space="preserve">24.4507598876953</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5999126434326</t>
+    <t xml:space="preserve">23.599910736084</t>
   </si>
   <si>
     <t xml:space="preserve">23.4655647277832</t>
@@ -2624,7 +2624,7 @@
     <t xml:space="preserve">27.3615646362305</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0332908630371</t>
+    <t xml:space="preserve">28.0332889556885</t>
   </si>
   <si>
     <t xml:space="preserve">27.8541641235352</t>
@@ -2654,19 +2654,19 @@
     <t xml:space="preserve">29.3440799713135</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5251121520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.57053565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0247821807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0702018737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8885059356689</t>
+    <t xml:space="preserve">30.5251083374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5705375671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0247802734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0702056884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8885040283203</t>
   </si>
   <si>
     <t xml:space="preserve">28.9352626800537</t>
@@ -2681,7 +2681,7 @@
     <t xml:space="preserve">27.4362602233887</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0722007751465</t>
+    <t xml:space="preserve">28.0721988677979</t>
   </si>
   <si>
     <t xml:space="preserve">28.4355945587158</t>
@@ -2753,7 +2753,7 @@
     <t xml:space="preserve">34.6132926940918</t>
   </si>
   <si>
-    <t xml:space="preserve">35.340087890625</t>
+    <t xml:space="preserve">35.3400840759277</t>
   </si>
   <si>
     <t xml:space="preserve">34.4316024780273</t>
@@ -2762,10 +2762,10 @@
     <t xml:space="preserve">33.7048072814941</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9773559570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9312705993652</t>
+    <t xml:space="preserve">33.9773597717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.931266784668</t>
   </si>
   <si>
     <t xml:space="preserve">34.5224494934082</t>
@@ -2780,7 +2780,7 @@
     <t xml:space="preserve">33.9319305419922</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2499008178711</t>
+    <t xml:space="preserve">34.2499046325684</t>
   </si>
   <si>
     <t xml:space="preserve">33.6139640808105</t>
@@ -2789,7 +2789,7 @@
     <t xml:space="preserve">36.2485733032227</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6573867797852</t>
+    <t xml:space="preserve">36.6573905944824</t>
   </si>
   <si>
     <t xml:space="preserve">36.7936592102051</t>
@@ -2831,13 +2831,13 @@
     <t xml:space="preserve">32.7509002685547</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6600532531738</t>
+    <t xml:space="preserve">32.6600570678711</t>
   </si>
   <si>
     <t xml:space="preserve">32.9780197143555</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7976570129395</t>
+    <t xml:space="preserve">30.7976589202881</t>
   </si>
   <si>
     <t xml:space="preserve">29.3895034790039</t>
@@ -2846,7 +2846,7 @@
     <t xml:space="preserve">29.5257778167725</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6172904968262</t>
+    <t xml:space="preserve">28.6172924041748</t>
   </si>
   <si>
     <t xml:space="preserve">28.3447456359863</t>
@@ -2861,7 +2861,7 @@
     <t xml:space="preserve">32.205810546875</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1149559020996</t>
+    <t xml:space="preserve">32.1149597167969</t>
   </si>
   <si>
     <t xml:space="preserve">32.2512359619141</t>
@@ -2873,7 +2873,7 @@
     <t xml:space="preserve">32.024112701416</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1142997741699</t>
+    <t xml:space="preserve">33.1142959594727</t>
   </si>
   <si>
     <t xml:space="preserve">32.614631652832</t>
@@ -2897,7 +2897,7 @@
     <t xml:space="preserve">32.5237770080566</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7054786682129</t>
+    <t xml:space="preserve">32.7054748535156</t>
   </si>
   <si>
     <t xml:space="preserve">32.1603851318359</t>
@@ -2912,13 +2912,13 @@
     <t xml:space="preserve">34.976692199707</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9325942993164</t>
+    <t xml:space="preserve">32.9325981140137</t>
   </si>
   <si>
     <t xml:space="preserve">33.0234451293945</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5231170654297</t>
+    <t xml:space="preserve">33.5231132507324</t>
   </si>
   <si>
     <t xml:space="preserve">32.4783554077148</t>
@@ -2939,7 +2939,7 @@
     <t xml:space="preserve">29.7074756622314</t>
   </si>
   <si>
-    <t xml:space="preserve">30.70680809021</t>
+    <t xml:space="preserve">30.7068061828613</t>
   </si>
   <si>
     <t xml:space="preserve">30.4796867370605</t>
@@ -2957,7 +2957,7 @@
     <t xml:space="preserve">28.7535629272461</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0708656311035</t>
+    <t xml:space="preserve">30.0708675384521</t>
   </si>
   <si>
     <t xml:space="preserve">28.8898372650146</t>
@@ -3008,7 +3008,7 @@
     <t xml:space="preserve">27.5725345611572</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6186237335205</t>
+    <t xml:space="preserve">26.6186218261719</t>
   </si>
   <si>
     <t xml:space="preserve">27.1182918548584</t>
@@ -3023,10 +3023,10 @@
     <t xml:space="preserve">26.9820194244385</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3460788726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8918342590332</t>
+    <t xml:space="preserve">26.346076965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8918361663818</t>
   </si>
   <si>
     <t xml:space="preserve">25.6647148132324</t>
@@ -3047,7 +3047,7 @@
     <t xml:space="preserve">26.5732002258301</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3915004730225</t>
+    <t xml:space="preserve">26.3915023803711</t>
   </si>
   <si>
     <t xml:space="preserve">26.70947265625</t>
@@ -3056,28 +3056,28 @@
     <t xml:space="preserve">26.527774810791</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9826831817627</t>
+    <t xml:space="preserve">25.9826850891113</t>
   </si>
   <si>
     <t xml:space="preserve">25.8009872436523</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1657123565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6660442352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8477458953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.437593460083</t>
+    <t xml:space="preserve">24.165714263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6660461425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8477439880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4375915527344</t>
   </si>
   <si>
     <t xml:space="preserve">25.7555637359619</t>
   </si>
   <si>
-    <t xml:space="preserve">25.074197769165</t>
+    <t xml:space="preserve">25.0741996765137</t>
   </si>
   <si>
     <t xml:space="preserve">26.0735340118408</t>
@@ -3089,7 +3089,7 @@
     <t xml:space="preserve">26.3419418334961</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6671524047852</t>
+    <t xml:space="preserve">26.6671504974365</t>
   </si>
   <si>
     <t xml:space="preserve">27.1317348480225</t>
@@ -3098,7 +3098,7 @@
     <t xml:space="preserve">27.6427764892578</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3396530151367</t>
+    <t xml:space="preserve">28.3396549224854</t>
   </si>
   <si>
     <t xml:space="preserve">27.8286113739014</t>
@@ -3152,7 +3152,7 @@
     <t xml:space="preserve">27.038818359375</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9459018707275</t>
+    <t xml:space="preserve">26.9458999633789</t>
   </si>
   <si>
     <t xml:space="preserve">26.760066986084</t>
@@ -3164,19 +3164,19 @@
     <t xml:space="preserve">26.2025661468506</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5742321014404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.481315612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8994426727295</t>
+    <t xml:space="preserve">26.5742340087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4813175201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8994445800781</t>
   </si>
   <si>
     <t xml:space="preserve">26.2490253448486</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7379837036133</t>
+    <t xml:space="preserve">25.7379817962646</t>
   </si>
   <si>
     <t xml:space="preserve">25.9238147735596</t>
@@ -3191,7 +3191,7 @@
     <t xml:space="preserve">27.271110534668</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2246513366699</t>
+    <t xml:space="preserve">27.2246494293213</t>
   </si>
   <si>
     <t xml:space="preserve">25.4127731323242</t>
@@ -3203,7 +3203,7 @@
     <t xml:space="preserve">24.5300617218018</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9017295837402</t>
+    <t xml:space="preserve">24.9017276763916</t>
   </si>
   <si>
     <t xml:space="preserve">25.0875625610352</t>
@@ -3212,76 +3212,76 @@
     <t xml:space="preserve">24.8088130950928</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5521469116211</t>
+    <t xml:space="preserve">25.5521488189697</t>
   </si>
   <si>
     <t xml:space="preserve">25.5056896209717</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7623538970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7158946990967</t>
+    <t xml:space="preserve">24.7623519897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7158966064453</t>
   </si>
   <si>
     <t xml:space="preserve">25.8308982849121</t>
   </si>
   <si>
-    <t xml:space="preserve">27.085277557373</t>
+    <t xml:space="preserve">27.0852756500244</t>
   </si>
   <si>
     <t xml:space="preserve">26.7136077880859</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0167331695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8773574829102</t>
+    <t xml:space="preserve">26.016731262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8773555755615</t>
   </si>
   <si>
     <t xml:space="preserve">25.7844390869141</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0631885528564</t>
+    <t xml:space="preserve">26.0631904602051</t>
   </si>
   <si>
     <t xml:space="preserve">26.1096496582031</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1340198516846</t>
+    <t xml:space="preserve">25.1340217590332</t>
   </si>
   <si>
     <t xml:space="preserve">25.0411052703857</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2977676391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4836044311523</t>
+    <t xml:space="preserve">24.2977695465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4836025238037</t>
   </si>
   <si>
     <t xml:space="preserve">24.0654773712158</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2513122558594</t>
+    <t xml:space="preserve">24.2513103485107</t>
   </si>
   <si>
     <t xml:space="preserve">24.5765209197998</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6008911132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0433921813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0898494720459</t>
+    <t xml:space="preserve">23.6008930206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0433902740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0898513793945</t>
   </si>
   <si>
     <t xml:space="preserve">22.114221572876</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0213050842285</t>
+    <t xml:space="preserve">22.0213069915771</t>
   </si>
   <si>
     <t xml:space="preserve">23.2756824493408</t>
@@ -3290,28 +3290,28 @@
     <t xml:space="preserve">23.4615173339844</t>
   </si>
   <si>
-    <t xml:space="preserve">23.415060043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1363086700439</t>
+    <t xml:space="preserve">23.4150581359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1363067626953</t>
   </si>
   <si>
     <t xml:space="preserve">23.6473522186279</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9504737854004</t>
+    <t xml:space="preserve">22.950475692749</t>
   </si>
   <si>
     <t xml:space="preserve">22.5788059234619</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2071399688721</t>
+    <t xml:space="preserve">22.2071380615234</t>
   </si>
   <si>
     <t xml:space="preserve">21.64963722229</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8598461151123</t>
+    <t xml:space="preserve">20.8598442077637</t>
   </si>
   <si>
     <t xml:space="preserve">21.0921363830566</t>
@@ -3326,7 +3326,7 @@
     <t xml:space="preserve">21.5567207336426</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7425537109375</t>
+    <t xml:space="preserve">21.7425556182861</t>
   </si>
   <si>
     <t xml:space="preserve">21.9283885955811</t>
@@ -3347,37 +3347,37 @@
     <t xml:space="preserve">21.4173450469971</t>
   </si>
   <si>
-    <t xml:space="preserve">21.603178024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.835470199585</t>
+    <t xml:space="preserve">21.6031799316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8354721069336</t>
   </si>
   <si>
     <t xml:space="preserve">22.160680770874</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7181835174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3000564575195</t>
+    <t xml:space="preserve">22.7181816101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3000545501709</t>
   </si>
   <si>
     <t xml:space="preserve">22.3465137481689</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2535972595215</t>
+    <t xml:space="preserve">22.2535991668701</t>
   </si>
   <si>
     <t xml:space="preserve">21.881929397583</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7890148162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1827659606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5986061096191</t>
+    <t xml:space="preserve">21.7890129089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.182767868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5986042022705</t>
   </si>
   <si>
     <t xml:space="preserve">25.3663120269775</t>
@@ -3398,10 +3398,10 @@
     <t xml:space="preserve">24.4371433258057</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8796424865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2048511505127</t>
+    <t xml:space="preserve">23.8796443939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2048530578613</t>
   </si>
   <si>
     <t xml:space="preserve">23.9261016845703</t>
@@ -3410,7 +3410,7 @@
     <t xml:space="preserve">24.6694355010986</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5544357299805</t>
+    <t xml:space="preserve">23.5544338226318</t>
   </si>
   <si>
     <t xml:space="preserve">23.6938095092773</t>
@@ -3419,7 +3419,7 @@
     <t xml:space="preserve">23.3221416473389</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7867259979248</t>
+    <t xml:space="preserve">23.7867279052734</t>
   </si>
   <si>
     <t xml:space="preserve">22.8575572967529</t>
@@ -3428,7 +3428,7 @@
     <t xml:space="preserve">21.5102615356445</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3708877563477</t>
+    <t xml:space="preserve">21.370885848999</t>
   </si>
   <si>
     <t xml:space="preserve">21.1850528717041</t>
@@ -3437,19 +3437,19 @@
     <t xml:space="preserve">20.7204685211182</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4881744384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9771327972412</t>
+    <t xml:space="preserve">20.4881763458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9771347045898</t>
   </si>
   <si>
     <t xml:space="preserve">20.2558822631836</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5346355438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9306774139404</t>
+    <t xml:space="preserve">20.5346336364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9306755065918</t>
   </si>
   <si>
     <t xml:space="preserve">20.5810928344727</t>
@@ -3461,7 +3461,7 @@
     <t xml:space="preserve">20.6275520324707</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0235919952393</t>
+    <t xml:space="preserve">20.0235900878906</t>
   </si>
   <si>
     <t xml:space="preserve">18.6298370361328</t>
@@ -3479,7 +3479,7 @@
     <t xml:space="preserve">17.8772106170654</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5427112579346</t>
+    <t xml:space="preserve">17.5427093505859</t>
   </si>
   <si>
     <t xml:space="preserve">17.2453765869141</t>
@@ -3491,10 +3491,10 @@
     <t xml:space="preserve">17.5612926483154</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4126262664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7471294403076</t>
+    <t xml:space="preserve">17.4126281738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.747127532959</t>
   </si>
   <si>
     <t xml:space="preserve">17.1896266937256</t>
@@ -3515,13 +3515,13 @@
     <t xml:space="preserve">16.3162078857422</t>
   </si>
   <si>
-    <t xml:space="preserve">15.981707572937</t>
+    <t xml:space="preserve">15.9817085266113</t>
   </si>
   <si>
     <t xml:space="preserve">16.5392074584961</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2976264953613</t>
+    <t xml:space="preserve">16.2976245880127</t>
   </si>
   <si>
     <t xml:space="preserve">16.1861248016357</t>
@@ -3533,7 +3533,7 @@
     <t xml:space="preserve">16.1489562988281</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2418727874756</t>
+    <t xml:space="preserve">16.2418746948242</t>
   </si>
   <si>
     <t xml:space="preserve">16.0746231079102</t>
@@ -4320,6 +4320,9 @@
   </si>
   <si>
     <t xml:space="preserve">18.9599990844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8400001525879</t>
   </si>
 </sst>
 </file>
@@ -70204,7 +70207,7 @@
     </row>
     <row r="2522">
       <c r="A2522" s="1" t="n">
-        <v>45989.6911111111</v>
+        <v>45989.3333333333</v>
       </c>
       <c r="B2522" t="n">
         <v>8409</v>
@@ -70225,6 +70228,32 @@
         <v>1435</v>
       </c>
       <c r="H2522" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2523">
+      <c r="A2523" s="1" t="n">
+        <v>45992.6911342593</v>
+      </c>
+      <c r="B2523" t="n">
+        <v>3100</v>
+      </c>
+      <c r="C2523" t="n">
+        <v>18.9400005340576</v>
+      </c>
+      <c r="D2523" t="n">
+        <v>18.6000003814697</v>
+      </c>
+      <c r="E2523" t="n">
+        <v>18.9200000762939</v>
+      </c>
+      <c r="F2523" t="n">
+        <v>18.8400001525879</v>
+      </c>
+      <c r="G2523" t="s">
+        <v>1436</v>
+      </c>
+      <c r="H2523" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ARN.MI.xlsx
+++ b/data/ARN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1437" uniqueCount="1437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1438" uniqueCount="1438">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9221498966217</t>
+    <t xml:space="preserve">1.92215037345886</t>
   </si>
   <si>
     <t xml:space="preserve">ARN.MI</t>
@@ -47,46 +47,46 @@
     <t xml:space="preserve">1.94450080394745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91736042499542</t>
+    <t xml:space="preserve">1.917360663414</t>
   </si>
   <si>
     <t xml:space="preserve">1.90778195858002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88383460044861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93172907829285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91576397418976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83434438705444</t>
+    <t xml:space="preserve">1.88383495807648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93172919750214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91576433181763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83434462547302</t>
   </si>
   <si>
     <t xml:space="preserve">1.83594059944153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91097497940063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80720412731171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74973118305206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71620535850525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8040109872818</t>
+    <t xml:space="preserve">1.91097486019135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80720436573029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74973106384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71620547771454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80401134490967</t>
   </si>
   <si>
     <t xml:space="preserve">1.81039714813232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79602909088135</t>
+    <t xml:space="preserve">1.79602932929993</t>
   </si>
   <si>
     <t xml:space="preserve">1.77208185195923</t>
@@ -95,25 +95,25 @@
     <t xml:space="preserve">1.70662665367126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69704782962799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69066190719604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67629361152649</t>
+    <t xml:space="preserve">1.69704759120941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69066202640533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67629373073578</t>
   </si>
   <si>
     <t xml:space="preserve">1.70024073123932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69864416122437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67469751834869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66671478748322</t>
+    <t xml:space="preserve">1.69864439964294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67469727993011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6667149066925</t>
   </si>
   <si>
     <t xml:space="preserve">1.66032898426056</t>
@@ -122,106 +122,106 @@
     <t xml:space="preserve">1.81518661975861</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82795858383179</t>
+    <t xml:space="preserve">1.82795810699463</t>
   </si>
   <si>
     <t xml:space="preserve">1.86148428916931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88543105125427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89181756973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92853605747223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95407915115356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90618550777435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86786961555481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88064193725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85190522670746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85988771915436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85509836673737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79283607006073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78804659843445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78006422519684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75611698627472</t>
+    <t xml:space="preserve">1.88543128967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8918172121048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92853581905365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95407950878143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90618562698364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86787021160126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88064157962799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85190546512604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85988783836365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85509812831879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79283618927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78804647922516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78006434440613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7561172246933</t>
   </si>
   <si>
     <t xml:space="preserve">1.7688889503479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76409959793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78485345840454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77048552036285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72099471092224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73536312580109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80241477489471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76250314712524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74494194984436</t>
+    <t xml:space="preserve">1.76409983634949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78485381603241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77048528194427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72099506855011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7353630065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.802414894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76250302791595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74494218826294</t>
   </si>
   <si>
     <t xml:space="preserve">1.73217034339905</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73695969581604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7433454990387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75132787227631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68587255477905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67789006233215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65234661102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62041711807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64276790618896</t>
+    <t xml:space="preserve">1.73695957660675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74334561824799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75132775306702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68587267398834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67789030075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65234637260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6204172372818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64276778697968</t>
   </si>
   <si>
     <t xml:space="preserve">1.59008419513702</t>
@@ -230,67 +230,67 @@
     <t xml:space="preserve">1.60285592079163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54937446117401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51185727119446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45598089694977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43682312965393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46955096721649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49748909473419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47673487663269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47274386882782</t>
+    <t xml:space="preserve">1.54937422275543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51185739040375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45598077774048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43682324886322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46955060958862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49748921394348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47673511505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47274374961853</t>
   </si>
   <si>
     <t xml:space="preserve">1.46875262260437</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49669086933136</t>
+    <t xml:space="preserve">1.49669075012207</t>
   </si>
   <si>
     <t xml:space="preserve">1.47593677043915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50626957416534</t>
+    <t xml:space="preserve">1.50626969337463</t>
   </si>
   <si>
     <t xml:space="preserve">1.47753322124481</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43841958045959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40090274810791</t>
+    <t xml:space="preserve">1.43841981887817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40090262889862</t>
   </si>
   <si>
     <t xml:space="preserve">1.34901738166809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30910539627075</t>
+    <t xml:space="preserve">1.30910563468933</t>
   </si>
   <si>
     <t xml:space="preserve">1.34342968463898</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32666671276093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3410347700119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31708776950836</t>
+    <t xml:space="preserve">1.32666659355164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34103488922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31708800792694</t>
   </si>
   <si>
     <t xml:space="preserve">1.38653433322906</t>
@@ -299,28 +299,28 @@
     <t xml:space="preserve">1.39691138267517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40649020671844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30671083927155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32347369194031</t>
+    <t xml:space="preserve">1.40649032592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30671072006226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3234738111496</t>
   </si>
   <si>
     <t xml:space="preserve">1.305912733078</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31229865550995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28994786739349</t>
+    <t xml:space="preserve">1.31229841709137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28994798660278</t>
   </si>
   <si>
     <t xml:space="preserve">1.28515863418579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28595685958862</t>
+    <t xml:space="preserve">1.28595662117004</t>
   </si>
   <si>
     <t xml:space="preserve">1.33305263519287</t>
@@ -329,52 +329,52 @@
     <t xml:space="preserve">1.33704376220703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30112326145172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36104869842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34627258777618</t>
+    <t xml:space="preserve">1.30112314224243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36104881763458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34627246856689</t>
   </si>
   <si>
     <t xml:space="preserve">1.35283982753754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33806359767914</t>
+    <t xml:space="preserve">1.33806347846985</t>
   </si>
   <si>
     <t xml:space="preserve">1.27157092094421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28880989551544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29291439056396</t>
+    <t xml:space="preserve">1.28880977630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29291427135468</t>
   </si>
   <si>
     <t xml:space="preserve">1.30686962604523</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33888459205627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34955620765686</t>
+    <t xml:space="preserve">1.33888471126556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34955608844757</t>
   </si>
   <si>
     <t xml:space="preserve">1.34380996227264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33642172813416</t>
+    <t xml:space="preserve">1.33642184734344</t>
   </si>
   <si>
     <t xml:space="preserve">1.34709358215332</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30522787570953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29127252101898</t>
+    <t xml:space="preserve">1.30522775650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29127240180969</t>
   </si>
   <si>
     <t xml:space="preserve">1.31425762176514</t>
@@ -383,49 +383,49 @@
     <t xml:space="preserve">1.32164573669434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26828742027283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27239191532135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28798890113831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29701888561249</t>
+    <t xml:space="preserve">1.26828730106354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27239179611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2879890203476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2970187664032</t>
   </si>
   <si>
     <t xml:space="preserve">1.24858582019806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32657098770142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33231747150421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3594069480896</t>
+    <t xml:space="preserve">1.32657122612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33231723308563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35940706729889</t>
   </si>
   <si>
     <t xml:space="preserve">1.42015337944031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48664617538452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53343737125397</t>
+    <t xml:space="preserve">1.48664629459381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53343749046326</t>
   </si>
   <si>
     <t xml:space="preserve">1.51619839668274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51866114139557</t>
+    <t xml:space="preserve">1.51866126060486</t>
   </si>
   <si>
     <t xml:space="preserve">1.43739223480225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46776533126831</t>
+    <t xml:space="preserve">1.46776568889618</t>
   </si>
   <si>
     <t xml:space="preserve">1.43000423908234</t>
@@ -440,37 +440,37 @@
     <t xml:space="preserve">1.5597060918808</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61798977851868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70582604408264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74851250648499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72388529777527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6828408241272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67463171482086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.651646733284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64179575443268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67134809494019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66478097438812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65657186508179</t>
+    <t xml:space="preserve">1.61798965930939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70582592487335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74851274490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72388577461243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68284094333649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67463183403015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65164685249329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64179587364197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67134821414948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66478109359741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65657210350037</t>
   </si>
   <si>
     <t xml:space="preserve">1.69597506523132</t>
@@ -479,16 +479,16 @@
     <t xml:space="preserve">1.69433319568634</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65821385383606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6811990737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68776619434357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66806483268738</t>
+    <t xml:space="preserve">1.65821397304535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68119883537292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68776631355286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66806471347809</t>
   </si>
   <si>
     <t xml:space="preserve">1.65000486373901</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">1.66313910484314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67791545391083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03746891021729</t>
+    <t xml:space="preserve">1.67791533470154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03746867179871</t>
   </si>
   <si>
     <t xml:space="preserve">2.04403591156006</t>
@@ -509,40 +509,40 @@
     <t xml:space="preserve">2.0391104221344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04075264930725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05224514007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04731965065002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04239416122437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19836449623108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24105143547058</t>
+    <t xml:space="preserve">2.04075241088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05224466323853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04731941223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04239368438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19836473464966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24105167388916</t>
   </si>
   <si>
     <t xml:space="preserve">2.18851399421692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17537999153137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14582753181458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00627446174622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98821449279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99314022064209</t>
+    <t xml:space="preserve">2.17537927627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.145827293396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00627470016479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98821473121643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99313986301422</t>
   </si>
   <si>
     <t xml:space="preserve">1.99806559085846</t>
@@ -554,31 +554,31 @@
     <t xml:space="preserve">1.99970769882202</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00299119949341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00791645050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01120018959045</t>
+    <t xml:space="preserve">2.00299096107483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00791668891907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01119995117188</t>
   </si>
   <si>
     <t xml:space="preserve">2.02597618103027</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03254365921021</t>
+    <t xml:space="preserve">2.03254342079163</t>
   </si>
   <si>
     <t xml:space="preserve">2.02105069160461</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01940894126892</t>
+    <t xml:space="preserve">2.01940870285034</t>
   </si>
   <si>
     <t xml:space="preserve">2.02433443069458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07687211036682</t>
+    <t xml:space="preserve">2.07687187194824</t>
   </si>
   <si>
     <t xml:space="preserve">2.0588116645813</t>
@@ -587,79 +587,79 @@
     <t xml:space="preserve">2.09657335281372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14746928215027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33955907821655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27552938461304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32478308677673</t>
+    <t xml:space="preserve">2.14746904373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33955931663513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27552914619446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32478284835815</t>
   </si>
   <si>
     <t xml:space="preserve">2.27881288528442</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25746941566467</t>
+    <t xml:space="preserve">2.25746917724609</t>
   </si>
   <si>
     <t xml:space="preserve">2.2985143661499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26075315475464</t>
+    <t xml:space="preserve">2.26075339317322</t>
   </si>
   <si>
     <t xml:space="preserve">2.28045463562012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30672335624695</t>
+    <t xml:space="preserve">2.30672311782837</t>
   </si>
   <si>
     <t xml:space="preserve">2.35597729682922</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34120082855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34284329414368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34776782989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44627594947815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39209723472595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38224601745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38717103004456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38388776779175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4052312374115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38060426712036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42164945602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33791732788086</t>
+    <t xml:space="preserve">2.34120059013367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34284281730652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34776830673218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44627571105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39209699630737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38224577903748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38717150688171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38388800621033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40523099899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38060402870178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42164897918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33791756629944</t>
   </si>
   <si>
     <t xml:space="preserve">2.32314133644104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35433530807495</t>
+    <t xml:space="preserve">2.35433554649353</t>
   </si>
   <si>
     <t xml:space="preserve">2.41015648841858</t>
@@ -668,31 +668,31 @@
     <t xml:space="preserve">2.40687274932861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43806743621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4183657169342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29030561447144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34941005706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36418604850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37567925453186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40194773674011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35761904716492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36746954917908</t>
+    <t xml:space="preserve">2.43806672096252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41836524009705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29030537605286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34940981864929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36418652534485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3756787776947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40194749832153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35761880874634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36746978759766</t>
   </si>
   <si>
     <t xml:space="preserve">2.37075304985046</t>
@@ -701,13 +701,13 @@
     <t xml:space="preserve">2.37239551544189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36254405975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36582827568054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39538049697876</t>
+    <t xml:space="preserve">2.36254453659058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3658275604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39538025856018</t>
   </si>
   <si>
     <t xml:space="preserve">2.37732028961182</t>
@@ -716,13 +716,13 @@
     <t xml:space="preserve">2.37403678894043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38881349563599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39373803138733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39045476913452</t>
+    <t xml:space="preserve">2.38881325721741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39373826980591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39045453071594</t>
   </si>
   <si>
     <t xml:space="preserve">2.41343998908997</t>
@@ -737,112 +737,112 @@
     <t xml:space="preserve">2.40851473808289</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42329072952271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43149971961975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42000699043274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35105180740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33627581596375</t>
+    <t xml:space="preserve">2.42329049110413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43149948120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42000722885132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35105156898499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33627533912659</t>
   </si>
   <si>
     <t xml:space="preserve">2.34612655639648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43642497062683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42657446861267</t>
+    <t xml:space="preserve">2.43642520904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42657423019409</t>
   </si>
   <si>
     <t xml:space="preserve">2.42985796928406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4528431892395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4770131111145</t>
+    <t xml:space="preserve">2.45284295082092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47701287269592</t>
   </si>
   <si>
     <t xml:space="preserve">2.47868013381958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49201512336731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49368214607239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47534656524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46534442901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48201370239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46867847442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45867776870728</t>
+    <t xml:space="preserve">2.49201536178589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49368190765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47534608840942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46534466743469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48201394081116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46867823600769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45867729187012</t>
   </si>
   <si>
     <t xml:space="preserve">2.46201109886169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45534348487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41700482368469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40867018699646</t>
+    <t xml:space="preserve">2.45534324645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41700458526611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40867066383362</t>
   </si>
   <si>
     <t xml:space="preserve">2.36699771881104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3419942855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36866474151611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35366225242615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.385333776474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38366651535034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36366391181946</t>
+    <t xml:space="preserve">2.34199452400208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36866450309753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35366249084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38533329963684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38366675376892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36366367340088</t>
   </si>
   <si>
     <t xml:space="preserve">2.32532548904419</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3169903755188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28531956672668</t>
+    <t xml:space="preserve">2.31699085235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28531980514526</t>
   </si>
   <si>
     <t xml:space="preserve">2.28698635101318</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29698777198792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31532406806946</t>
+    <t xml:space="preserve">2.29698801040649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31532382965088</t>
   </si>
   <si>
     <t xml:space="preserve">2.28365254402161</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">2.28865361213684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29031991958618</t>
+    <t xml:space="preserve">2.29032063484192</t>
   </si>
   <si>
     <t xml:space="preserve">2.30198860168457</t>
@@ -860,19 +860,19 @@
     <t xml:space="preserve">2.30365562438965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2936544418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24198031425476</t>
+    <t xml:space="preserve">2.29365420341492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24198055267334</t>
   </si>
   <si>
     <t xml:space="preserve">2.26698350906372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2686505317688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32699227333069</t>
+    <t xml:space="preserve">2.26865029335022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32699203491211</t>
   </si>
   <si>
     <t xml:space="preserve">2.31865763664246</t>
@@ -884,55 +884,55 @@
     <t xml:space="preserve">2.24364686012268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25031447410583</t>
+    <t xml:space="preserve">2.25031471252441</t>
   </si>
   <si>
     <t xml:space="preserve">2.22531127929688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25198149681091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2219774723053</t>
+    <t xml:space="preserve">2.25198173522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22197771072388</t>
   </si>
   <si>
     <t xml:space="preserve">2.20697546005249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20030760765076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16863703727722</t>
+    <t xml:space="preserve">2.20030784606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16863632202148</t>
   </si>
   <si>
     <t xml:space="preserve">2.17863821983337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16696953773499</t>
+    <t xml:space="preserve">2.16696977615356</t>
   </si>
   <si>
     <t xml:space="preserve">2.18697261810303</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19697380065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18363857269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18530559539795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19197344779968</t>
+    <t xml:space="preserve">2.19697403907776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18363881111145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18530535697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19197368621826</t>
   </si>
   <si>
     <t xml:space="preserve">2.17530417442322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1419665813446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15363454818726</t>
+    <t xml:space="preserve">2.14196634292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15363478660583</t>
   </si>
   <si>
     <t xml:space="preserve">2.14363312721252</t>
@@ -941,16 +941,16 @@
     <t xml:space="preserve">2.13529849052429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12696409225464</t>
+    <t xml:space="preserve">2.12696433067322</t>
   </si>
   <si>
     <t xml:space="preserve">2.12863111495972</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12029623985291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13029813766479</t>
+    <t xml:space="preserve">2.12029647827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13029789924622</t>
   </si>
   <si>
     <t xml:space="preserve">2.11862993240356</t>
@@ -959,37 +959,37 @@
     <t xml:space="preserve">2.37366557121277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37533187866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40700316429138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39533519744873</t>
+    <t xml:space="preserve">2.37533211708069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40700340270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39533495903015</t>
   </si>
   <si>
     <t xml:space="preserve">2.39200139045715</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49868273735046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49534916877747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50868463516235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51201796531677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51535153388977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51701831817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52368640899658</t>
+    <t xml:space="preserve">2.49868249893188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49534893035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5086841583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51201820373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51535177230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51701903343201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.523686170578</t>
   </si>
   <si>
     <t xml:space="preserve">2.52535343170166</t>
@@ -998,46 +998,46 @@
     <t xml:space="preserve">2.54535627365112</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53368735313416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53202128410339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54035520553589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52702021598816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53868842124939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53702139854431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49701571464539</t>
+    <t xml:space="preserve">2.53368782997131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53202104568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54035544395447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52702045440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53868818283081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53702163696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49701619148254</t>
   </si>
   <si>
     <t xml:space="preserve">2.42700600624084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50034952163696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5053505897522</t>
+    <t xml:space="preserve">2.50034976005554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50535035133362</t>
   </si>
   <si>
     <t xml:space="preserve">2.48368072509766</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45200967788696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51368474960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54202222824097</t>
+    <t xml:space="preserve">2.45200943946838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51368451118469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54202246665955</t>
   </si>
   <si>
     <t xml:space="preserve">2.54868984222412</t>
@@ -1052,28 +1052,28 @@
     <t xml:space="preserve">2.47201251983643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50201654434204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48701453208923</t>
+    <t xml:space="preserve">2.50201678276062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48701477050781</t>
   </si>
   <si>
     <t xml:space="preserve">3.00041961669922</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81706094741821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75038456916809</t>
+    <t xml:space="preserve">2.81706047058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75038433074951</t>
   </si>
   <si>
     <t xml:space="preserve">2.71704649925232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80872631072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80039143562317</t>
+    <t xml:space="preserve">2.80872583389282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80039167404175</t>
   </si>
   <si>
     <t xml:space="preserve">2.83372950553894</t>
@@ -1085,55 +1085,55 @@
     <t xml:space="preserve">2.84206414222717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75871968269348</t>
+    <t xml:space="preserve">2.75871920585632</t>
   </si>
   <si>
     <t xml:space="preserve">2.85039877891541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85873341560364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89207148551941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82539558410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72538113594055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61703276634216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64203643798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70037770271301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65870547294617</t>
+    <t xml:space="preserve">2.85873317718506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89207100868225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82539510726929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72538089752197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61703252792358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64203596115112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70037746429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65870499610901</t>
   </si>
   <si>
     <t xml:space="preserve">2.62536716461182</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63370180130005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59202933311462</t>
+    <t xml:space="preserve">2.63370156288147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59202885627747</t>
   </si>
   <si>
     <t xml:space="preserve">2.66703963279724</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70871233940125</t>
+    <t xml:space="preserve">2.70871210098267</t>
   </si>
   <si>
     <t xml:space="preserve">2.74205017089844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65037083625793</t>
+    <t xml:space="preserve">2.65037059783936</t>
   </si>
   <si>
     <t xml:space="preserve">2.68370866775513</t>
@@ -1151,22 +1151,22 @@
     <t xml:space="preserve">2.76705360412598</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73371529579163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79205703735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86706781387329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87540245056152</t>
+    <t xml:space="preserve">2.73371577262878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79205727577209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86706757545471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87540197372437</t>
   </si>
   <si>
     <t xml:space="preserve">2.8837366104126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77538824081421</t>
+    <t xml:space="preserve">2.77538800239563</t>
   </si>
   <si>
     <t xml:space="preserve">2.78091382980347</t>
@@ -1175,88 +1175,88 @@
     <t xml:space="preserve">2.72174549102783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73019814491272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7724609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.645672082901</t>
+    <t xml:space="preserve">2.73019790649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77246117591858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64567184448242</t>
   </si>
   <si>
     <t xml:space="preserve">2.70484018325806</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68793511390686</t>
+    <t xml:space="preserve">2.68793487548828</t>
   </si>
   <si>
     <t xml:space="preserve">2.6625771522522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69638776779175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65412449836731</t>
+    <t xml:space="preserve">2.69638752937317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65412425994873</t>
   </si>
   <si>
     <t xml:space="preserve">2.60340857505798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63721895217896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61186146736145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5780508518219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5949559211731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50197696685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49352502822876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54424071311951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5611457824707</t>
+    <t xml:space="preserve">2.63721871376038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61186122894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57805061340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59495568275452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50197720527649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49352478981018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54424023628235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56114554405212</t>
   </si>
   <si>
     <t xml:space="preserve">2.58650326728821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51888251304626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53578758239746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55269265174866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51043009757996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56959795951843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46816658973694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48507189750671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41745066642761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45126152038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39209294319153</t>
+    <t xml:space="preserve">2.51888227462769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53578782081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55269312858582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51042985916138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56959819793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4681670665741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48507213592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41745114326477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45126175880432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39209318161011</t>
   </si>
   <si>
     <t xml:space="preserve">2.38364052772522</t>
@@ -1265,37 +1265,37 @@
     <t xml:space="preserve">2.27375650405884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29911398887634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36673498153687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35828280448914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43435621261597</t>
+    <t xml:space="preserve">2.29911422729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36673521995544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35828256607056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43435645103455</t>
   </si>
   <si>
     <t xml:space="preserve">2.42590379714966</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34982967376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28220868110657</t>
+    <t xml:space="preserve">2.34982991218567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28220891952515</t>
   </si>
   <si>
     <t xml:space="preserve">2.32447218894958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40899801254272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45971417427063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44280886650085</t>
+    <t xml:space="preserve">2.4089982509613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45971441268921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44280934333801</t>
   </si>
   <si>
     <t xml:space="preserve">2.33292484283447</t>
@@ -1304,13 +1304,13 @@
     <t xml:space="preserve">2.34137725830078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40054559707642</t>
+    <t xml:space="preserve">2.400545835495</t>
   </si>
   <si>
     <t xml:space="preserve">2.37518787384033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47661948204041</t>
+    <t xml:space="preserve">2.47661995887756</t>
   </si>
   <si>
     <t xml:space="preserve">2.30756688117981</t>
@@ -1319,52 +1319,52 @@
     <t xml:space="preserve">2.23994588851929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29430222511292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23437643051147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24293732643127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33710646629333</t>
+    <t xml:space="preserve">2.29430246353149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2343761920929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2429370880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33710622787476</t>
   </si>
   <si>
     <t xml:space="preserve">2.25149846076965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27718067169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26862001419067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44839715957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37134957313538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31142377853394</t>
+    <t xml:space="preserve">2.27718091011047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26861977577209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44839692115784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37134981155396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31142354011536</t>
   </si>
   <si>
     <t xml:space="preserve">2.28574132919312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26005911827087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35422801971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22581553459167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20869421958923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30286312103271</t>
+    <t xml:space="preserve">2.26005887985229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35422825813293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22581577301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20869398117065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30286335945129</t>
   </si>
   <si>
     <t xml:space="preserve">2.31998467445374</t>
@@ -1373,37 +1373,37 @@
     <t xml:space="preserve">2.37991046905518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.405592918396</t>
+    <t xml:space="preserve">2.40559315681458</t>
   </si>
   <si>
     <t xml:space="preserve">2.39703226089478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32854557037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38847160339355</t>
+    <t xml:space="preserve">2.32854533195496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38847136497498</t>
   </si>
   <si>
     <t xml:space="preserve">2.36278891563416</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34566736221313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20013332366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18301129341125</t>
+    <t xml:space="preserve">2.34566712379456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20013308525085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18301177024841</t>
   </si>
   <si>
     <t xml:space="preserve">2.43983626365662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54256653785706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60249185562134</t>
+    <t xml:space="preserve">2.54256629943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60249209403992</t>
   </si>
   <si>
     <t xml:space="preserve">2.69666147232056</t>
@@ -1415,172 +1415,172 @@
     <t xml:space="preserve">2.63673543930054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67097854614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61961364746094</t>
+    <t xml:space="preserve">2.67097878456116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61961388587952</t>
   </si>
   <si>
     <t xml:space="preserve">2.65385699272156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68810033798218</t>
+    <t xml:space="preserve">2.68810057640076</t>
   </si>
   <si>
     <t xml:space="preserve">2.64529633522034</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71378326416016</t>
+    <t xml:space="preserve">2.713782787323</t>
   </si>
   <si>
     <t xml:space="preserve">2.72234392166138</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07333779335022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52706146240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59554767608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6554741859436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58698773384094</t>
+    <t xml:space="preserve">3.07333731651306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52706170082092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59554839134216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65547442436218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58698749542236</t>
   </si>
   <si>
     <t xml:space="preserve">3.61266994476318</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5356228351593</t>
+    <t xml:space="preserve">3.53562259674072</t>
   </si>
   <si>
     <t xml:space="preserve">3.42433190345764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54418301582336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56986618041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55274415016174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56130480766296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50993990898132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48425793647766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57842659950256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63835287094116</t>
+    <t xml:space="preserve">3.54418325424194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56986594200134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55274438858032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56130504608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5099401473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48425769805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57842683792114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63835263252258</t>
   </si>
   <si>
     <t xml:space="preserve">3.74108266830444</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16912412643433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60572624206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15361928939819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62284755706787</t>
+    <t xml:space="preserve">4.16912364959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60572671890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15361976623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62284708023071</t>
   </si>
   <si>
     <t xml:space="preserve">4.19480657577515</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45163106918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53724002838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52011823654175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58860445022583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34890127182007</t>
+    <t xml:space="preserve">4.45163154602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53723955154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52011775970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58860492706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34890174865723</t>
   </si>
   <si>
     <t xml:space="preserve">4.16056346893311</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23761034011841</t>
+    <t xml:space="preserve">4.23760986328125</t>
   </si>
   <si>
     <t xml:space="preserve">4.29753684997559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89517736434937</t>
+    <t xml:space="preserve">3.8951780796051</t>
   </si>
   <si>
     <t xml:space="preserve">3.27879762649536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25311517715454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89356017112732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15894627571106</t>
+    <t xml:space="preserve">3.25311493873596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89356064796448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15894603729248</t>
   </si>
   <si>
     <t xml:space="preserve">3.16750693321228</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0390944480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44145369529724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3815279006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39008855819702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84381246566772</t>
+    <t xml:space="preserve">3.03909468650818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44145345687866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38152766227722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3900887966156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84381222724915</t>
   </si>
   <si>
     <t xml:space="preserve">3.83525133132935</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8780562877655</t>
+    <t xml:space="preserve">3.87805581092834</t>
   </si>
   <si>
     <t xml:space="preserve">3.76676464080811</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88661646842957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85237312316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92942047119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95510292053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93798184394836</t>
+    <t xml:space="preserve">3.88661670684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85237336158752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92942142486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95510244369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93798208236694</t>
   </si>
   <si>
     <t xml:space="preserve">4.11775922775269</t>
@@ -1589,37 +1589,37 @@
     <t xml:space="preserve">4.25473213195801</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22904968261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26329278945923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28041458129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43450975418091</t>
+    <t xml:space="preserve">4.22905015945435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26329326629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28041410446167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43450927734375</t>
   </si>
   <si>
     <t xml:space="preserve">4.20336675643921</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00646734237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10919809341431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15200281143188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08351612091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94654250144958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07495450973511</t>
+    <t xml:space="preserve">4.00646781921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10919857025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15200233459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08351564407349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94654273986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07495498657227</t>
   </si>
   <si>
     <t xml:space="preserve">4.02358961105347</t>
@@ -1631,13 +1631,13 @@
     <t xml:space="preserve">4.13488054275513</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12631988525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01664590835571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70845603942871</t>
+    <t xml:space="preserve">4.12632036209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01664638519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70845651626587</t>
   </si>
   <si>
     <t xml:space="preserve">4.91391611099243</t>
@@ -1649,103 +1649,103 @@
     <t xml:space="preserve">4.94815969467163</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20498371124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56453943252563</t>
+    <t xml:space="preserve">5.20498418807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56453895568848</t>
   </si>
   <si>
     <t xml:space="preserve">5.68439054489136</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95833683013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90697288513184</t>
+    <t xml:space="preserve">5.95833730697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90697240829468</t>
   </si>
   <si>
     <t xml:space="preserve">5.88985061645508</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57471704483032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.129554271698</t>
+    <t xml:space="preserve">6.57471656799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12955331802368</t>
   </si>
   <si>
     <t xml:space="preserve">6.4035005569458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01987981796265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20821857452393</t>
+    <t xml:space="preserve">7.0198802947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20821809768677</t>
   </si>
   <si>
     <t xml:space="preserve">7.32807016372681</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05412292480469</t>
+    <t xml:space="preserve">7.05412340164185</t>
   </si>
   <si>
     <t xml:space="preserve">7.00275850296021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42397737503052</t>
+    <t xml:space="preserve">7.4239764213562</t>
   </si>
   <si>
     <t xml:space="preserve">7.28357124328613</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87990283966064</t>
+    <t xml:space="preserve">6.8799033164978</t>
   </si>
   <si>
     <t xml:space="preserve">6.9676570892334</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59909057617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51133728027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7394962310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84480142593384</t>
+    <t xml:space="preserve">6.59909105300903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51133680343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73949670791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.844801902771</t>
   </si>
   <si>
     <t xml:space="preserve">6.82725095748901</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68684434890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66929388046265</t>
+    <t xml:space="preserve">6.68684482574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66929340362549</t>
   </si>
   <si>
     <t xml:space="preserve">6.45868492126465</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40603303909302</t>
+    <t xml:space="preserve">6.4060320854187</t>
   </si>
   <si>
     <t xml:space="preserve">6.31827831268311</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80970001220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17826700210571</t>
+    <t xml:space="preserve">6.80970048904419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17826652526855</t>
   </si>
   <si>
     <t xml:space="preserve">7.35377407073975</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26602029800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05541133880615</t>
+    <t xml:space="preserve">7.26601982116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05541086196899</t>
   </si>
   <si>
     <t xml:space="preserve">7.07296228408813</t>
@@ -1757,34 +1757,34 @@
     <t xml:space="preserve">6.44113397598267</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30072784423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.055016040802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03746557235718</t>
+    <t xml:space="preserve">6.30072689056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05501699447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03746604919434</t>
   </si>
   <si>
     <t xml:space="preserve">5.37053680419922</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40563869476318</t>
+    <t xml:space="preserve">5.40563821792603</t>
   </si>
   <si>
     <t xml:space="preserve">5.52849388122559</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65134906768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12521934509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96726274490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01991510391235</t>
+    <t xml:space="preserve">5.65134859085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12522029876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96726322174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01991558074951</t>
   </si>
   <si>
     <t xml:space="preserve">5.91460990905762</t>
@@ -1802,25 +1802,25 @@
     <t xml:space="preserve">5.82685661315918</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93216133117676</t>
+    <t xml:space="preserve">5.93216180801392</t>
   </si>
   <si>
     <t xml:space="preserve">5.87950897216797</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79175472259521</t>
+    <t xml:space="preserve">5.79175519943237</t>
   </si>
   <si>
     <t xml:space="preserve">5.68645048141479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45829057693481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63379812240601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70400142669678</t>
+    <t xml:space="preserve">5.4582896232605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63379859924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70400094985962</t>
   </si>
   <si>
     <t xml:space="preserve">5.58114624023438</t>
@@ -1829,25 +1829,25 @@
     <t xml:space="preserve">5.66890001296997</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56359577178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61624765396118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49339246749878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31788444519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17747783660889</t>
+    <t xml:space="preserve">5.56359481811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61624717712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49339199066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31788492202759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17747831344604</t>
   </si>
   <si>
     <t xml:space="preserve">5.26523208618164</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28278255462646</t>
+    <t xml:space="preserve">5.28278303146362</t>
   </si>
   <si>
     <t xml:space="preserve">5.35298633575439</t>
@@ -1862,13 +1862,13 @@
     <t xml:space="preserve">5.38808727264404</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51094341278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77420425415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44074010848999</t>
+    <t xml:space="preserve">5.5109429359436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77420473098755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44073963165283</t>
   </si>
   <si>
     <t xml:space="preserve">5.54604482650757</t>
@@ -1877,13 +1877,13 @@
     <t xml:space="preserve">6.23052501678467</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35338020324707</t>
+    <t xml:space="preserve">6.35337972640991</t>
   </si>
   <si>
     <t xml:space="preserve">6.1603217124939</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37093114852905</t>
+    <t xml:space="preserve">6.37093067169189</t>
   </si>
   <si>
     <t xml:space="preserve">6.47623538970947</t>
@@ -1895,13 +1895,13 @@
     <t xml:space="preserve">6.54643869400024</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98520851135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33622312545776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09051275253296</t>
+    <t xml:space="preserve">6.98520755767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33622360229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0905122756958</t>
   </si>
   <si>
     <t xml:space="preserve">7.16071510314941</t>
@@ -1910,70 +1910,70 @@
     <t xml:space="preserve">7.19581699371338</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95010614395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14316558837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12561416625977</t>
+    <t xml:space="preserve">6.95010709762573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14316511154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12561368942261</t>
   </si>
   <si>
     <t xml:space="preserve">7.02030944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84519577026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33661842346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31906604766846</t>
+    <t xml:space="preserve">7.84519481658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3366174697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31906509399414</t>
   </si>
   <si>
     <t xml:space="preserve">8.42437171936035</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0825252532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68763256072998</t>
+    <t xml:space="preserve">9.08252620697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68763160705566</t>
   </si>
   <si>
     <t xml:space="preserve">9.03864860534668</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30191040039062</t>
+    <t xml:space="preserve">9.30190944671631</t>
   </si>
   <si>
     <t xml:space="preserve">11.2763719558716</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1630792617798</t>
+    <t xml:space="preserve">13.1630802154541</t>
   </si>
   <si>
     <t xml:space="preserve">13.0753259658813</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1192035675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8559408187866</t>
+    <t xml:space="preserve">13.1192026138306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8559417724609</t>
   </si>
   <si>
     <t xml:space="preserve">12.0222797393799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.110032081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9345254898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.36412525177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.88148021698</t>
+    <t xml:space="preserve">12.1100339889526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9345264434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3641262054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8814792633057</t>
   </si>
   <si>
     <t xml:space="preserve">12.1539115905762</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">11.6712646484375</t>
   </si>
   <si>
-    <t xml:space="preserve">11.715142250061</t>
+    <t xml:space="preserve">11.7151412963867</t>
   </si>
   <si>
     <t xml:space="preserve">11.4518795013428</t>
@@ -1991,25 +1991,25 @@
     <t xml:space="preserve">11.0569877624512</t>
   </si>
   <si>
-    <t xml:space="preserve">11.495756149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4080028533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8906497955322</t>
+    <t xml:space="preserve">11.4957571029663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4080018997192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8906507492065</t>
   </si>
   <si>
     <t xml:space="preserve">11.8028945922852</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3202486038208</t>
+    <t xml:space="preserve">11.3202495574951</t>
   </si>
   <si>
     <t xml:space="preserve">11.6273880004883</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1447410583496</t>
+    <t xml:space="preserve">11.1447401046753</t>
   </si>
   <si>
     <t xml:space="preserve">10.6182174682617</t>
@@ -2018,28 +2018,28 @@
     <t xml:space="preserve">10.5304641723633</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5743417739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7498483657837</t>
+    <t xml:space="preserve">10.5743398666382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7498502731323</t>
   </si>
   <si>
     <t xml:space="preserve">10.6620941162109</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3549556732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78455543518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91618728637695</t>
+    <t xml:space="preserve">10.3549566268921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78455638885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91618824005127</t>
   </si>
   <si>
     <t xml:space="preserve">10.0916948318481</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2324953079224</t>
+    <t xml:space="preserve">11.232494354248</t>
   </si>
   <si>
     <t xml:space="preserve">11.1886177062988</t>
@@ -2051,34 +2051,34 @@
     <t xml:space="preserve">11.3553495407104</t>
   </si>
   <si>
-    <t xml:space="preserve">11.267596244812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0218868255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2500448226929</t>
+    <t xml:space="preserve">11.2675971984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0218858718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2500457763672</t>
   </si>
   <si>
     <t xml:space="preserve">11.3729009628296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2851467132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1973934173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8467712402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9871778488159</t>
+    <t xml:space="preserve">11.2851476669312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1973924636841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8467721939087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9871768951416</t>
   </si>
   <si>
     <t xml:space="preserve">12.2855415344238</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2504386901855</t>
+    <t xml:space="preserve">12.2504405975342</t>
   </si>
   <si>
     <t xml:space="preserve">12.1626853942871</t>
@@ -2090,16 +2090,16 @@
     <t xml:space="preserve">12.0372982025146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0910358428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5536556243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6432199478149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3924417495728</t>
+    <t xml:space="preserve">12.0910348892212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.553656578064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6432189941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3924427032471</t>
   </si>
   <si>
     <t xml:space="preserve">10.9446268081665</t>
@@ -2111,25 +2111,25 @@
     <t xml:space="preserve">10.6759366989136</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9088010787964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7117614746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6580238342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9267139434814</t>
+    <t xml:space="preserve">10.9088020324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7117624282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6580228805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9267129898071</t>
   </si>
   <si>
     <t xml:space="preserve">11.0521030426025</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4999189376831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4820051193237</t>
+    <t xml:space="preserve">11.4999179840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.482006072998</t>
   </si>
   <si>
     <t xml:space="preserve">11.4282674789429</t>
@@ -2138,28 +2138,28 @@
     <t xml:space="preserve">11.5715684890747</t>
   </si>
   <si>
-    <t xml:space="preserve">11.374529838562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3566179275513</t>
+    <t xml:space="preserve">11.3745288848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.356616973877</t>
   </si>
   <si>
     <t xml:space="preserve">11.3207921981812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4461793899536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4640941619873</t>
+    <t xml:space="preserve">11.4461803436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4640922546387</t>
   </si>
   <si>
     <t xml:space="preserve">11.7148694992065</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7327823638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.750696182251</t>
+    <t xml:space="preserve">11.7327833175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7506952285767</t>
   </si>
   <si>
     <t xml:space="preserve">12.1805992126465</t>
@@ -2183,7 +2183,7 @@
     <t xml:space="preserve">12.1268606185913</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0552101135254</t>
+    <t xml:space="preserve">12.0552110671997</t>
   </si>
   <si>
     <t xml:space="preserve">11.8581705093384</t>
@@ -2192,25 +2192,25 @@
     <t xml:space="preserve">11.9298219680786</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2880744934082</t>
+    <t xml:space="preserve">12.2880754470825</t>
   </si>
   <si>
     <t xml:space="preserve">12.5925893783569</t>
   </si>
   <si>
-    <t xml:space="preserve">12.503026008606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9835605621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3239011764526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9804515838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1774911880493</t>
+    <t xml:space="preserve">12.5030269622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9835596084595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3239002227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9804525375366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1774892807007</t>
   </si>
   <si>
     <t xml:space="preserve">11.284966468811</t>
@@ -2222,19 +2222,19 @@
     <t xml:space="preserve">11.8939962387085</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7686080932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6253070831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0014715194702</t>
+    <t xml:space="preserve">11.768609046936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6253061294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0014724731445</t>
   </si>
   <si>
     <t xml:space="preserve">12.1089487075806</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9656457901001</t>
+    <t xml:space="preserve">11.9656476974487</t>
   </si>
   <si>
     <t xml:space="preserve">12.1985120773315</t>
@@ -2243,28 +2243,28 @@
     <t xml:space="preserve">12.43137550354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2522487640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8612794876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8433675765991</t>
+    <t xml:space="preserve">12.2522506713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8612785339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8433666229248</t>
   </si>
   <si>
     <t xml:space="preserve">12.6821527481079</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7358913421631</t>
+    <t xml:space="preserve">12.7358922958374</t>
   </si>
   <si>
     <t xml:space="preserve">13.3449201583862</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2405529022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0972518920898</t>
+    <t xml:space="preserve">14.2405519485474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0972509384155</t>
   </si>
   <si>
     <t xml:space="preserve">14.3301162719727</t>
@@ -2273,61 +2273,61 @@
     <t xml:space="preserve">14.4734172821045</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5988054275513</t>
+    <t xml:space="preserve">14.5988063812256</t>
   </si>
   <si>
     <t xml:space="preserve">13.8823003768921</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8643884658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5777864456177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4703102111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6852598190308</t>
+    <t xml:space="preserve">13.864387512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.577784538269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4703092575073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6852617263794</t>
   </si>
   <si>
     <t xml:space="preserve">13.6673488616943</t>
   </si>
   <si>
-    <t xml:space="preserve">13.559871673584</t>
+    <t xml:space="preserve">13.5598726272583</t>
   </si>
   <si>
     <t xml:space="preserve">13.6136102676392</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8285617828369</t>
+    <t xml:space="preserve">13.8285627365112</t>
   </si>
   <si>
     <t xml:space="preserve">13.953950881958</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4344844818115</t>
+    <t xml:space="preserve">13.4344835281372</t>
   </si>
   <si>
     <t xml:space="preserve">13.7210865020752</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5240478515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7031736373901</t>
+    <t xml:space="preserve">13.5240468978882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7031745910645</t>
   </si>
   <si>
     <t xml:space="preserve">13.2553577423096</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4523963928223</t>
+    <t xml:space="preserve">13.4523973464966</t>
   </si>
   <si>
     <t xml:space="preserve">13.3090953826904</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2763786315918</t>
+    <t xml:space="preserve">14.2763776779175</t>
   </si>
   <si>
     <t xml:space="preserve">14.4196796417236</t>
@@ -2336,10 +2336,10 @@
     <t xml:space="preserve">14.0256013870239</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7569122314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4375944137573</t>
+    <t xml:space="preserve">13.756911277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.437593460083</t>
   </si>
   <si>
     <t xml:space="preserve">16.7124977111816</t>
@@ -2357,16 +2357,16 @@
     <t xml:space="preserve">19.6591281890869</t>
   </si>
   <si>
-    <t xml:space="preserve">21.316047668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4503955841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5399570465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2116794586182</t>
+    <t xml:space="preserve">21.3160457611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4503936767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5399551391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2116813659668</t>
   </si>
   <si>
     <t xml:space="preserve">21.987771987915</t>
@@ -2378,10 +2378,10 @@
     <t xml:space="preserve">23.017749786377</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3460273742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1221199035645</t>
+    <t xml:space="preserve">22.3460235595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1221160888672</t>
   </si>
   <si>
     <t xml:space="preserve">23.7342548370361</t>
@@ -2390,10 +2390,10 @@
     <t xml:space="preserve">21.8982086181641</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4355869293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4951725006104</t>
+    <t xml:space="preserve">22.4355888366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.495174407959</t>
   </si>
   <si>
     <t xml:space="preserve">21.7190818786621</t>
@@ -2405,13 +2405,13 @@
     <t xml:space="preserve">21.7638645172119</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8534278869629</t>
+    <t xml:space="preserve">21.8534259796143</t>
   </si>
   <si>
     <t xml:space="preserve">23.3312206268311</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8086452484131</t>
+    <t xml:space="preserve">21.8086471557617</t>
   </si>
   <si>
     <t xml:space="preserve">25.3463916778564</t>
@@ -2420,13 +2420,13 @@
     <t xml:space="preserve">25.3016128540039</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2420234680176</t>
+    <t xml:space="preserve">26.2420253753662</t>
   </si>
   <si>
     <t xml:space="preserve">25.525520324707</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2120494842529</t>
+    <t xml:space="preserve">25.2120456695557</t>
   </si>
   <si>
     <t xml:space="preserve">25.8837718963623</t>
@@ -2435,16 +2435,16 @@
     <t xml:space="preserve">25.4807376861572</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5702991485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.122486114502</t>
+    <t xml:space="preserve">25.5703010559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1224842071533</t>
   </si>
   <si>
     <t xml:space="preserve">24.361198425293</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3911743164062</t>
+    <t xml:space="preserve">25.3911762237549</t>
   </si>
   <si>
     <t xml:space="preserve">25.704647064209</t>
@@ -2456,7 +2456,7 @@
     <t xml:space="preserve">26.0628986358643</t>
   </si>
   <si>
-    <t xml:space="preserve">26.465934753418</t>
+    <t xml:space="preserve">26.4659328460693</t>
   </si>
   <si>
     <t xml:space="preserve">26.1524620056152</t>
@@ -2474,13 +2474,13 @@
     <t xml:space="preserve">26.5554962158203</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9881401062012</t>
+    <t xml:space="preserve">24.9881381988525</t>
   </si>
   <si>
     <t xml:space="preserve">25.2568302154541</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9581642150879</t>
+    <t xml:space="preserve">23.9581623077393</t>
   </si>
   <si>
     <t xml:space="preserve">24.0477275848389</t>
@@ -2492,28 +2492,28 @@
     <t xml:space="preserve">24.5851058959961</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0773334503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9281883239746</t>
+    <t xml:space="preserve">22.077335357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9281845092773</t>
   </si>
   <si>
     <t xml:space="preserve">23.1968765258789</t>
   </si>
   <si>
-    <t xml:space="preserve">24.182071685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2268524169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4955425262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3164157867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3908061981201</t>
+    <t xml:space="preserve">24.1820697784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2268543243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4955444335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3164138793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3908081054688</t>
   </si>
   <si>
     <t xml:space="preserve">23.8238201141357</t>
@@ -2525,31 +2525,31 @@
     <t xml:space="preserve">23.7790355682373</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8834018707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2416572570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1672668457031</t>
+    <t xml:space="preserve">22.8834037780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2416591644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1672687530518</t>
   </si>
   <si>
     <t xml:space="preserve">27.3167839050293</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6002807617188</t>
+    <t xml:space="preserve">26.6002788543701</t>
   </si>
   <si>
     <t xml:space="preserve">25.615083694458</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4359569549561</t>
+    <t xml:space="preserve">25.4359550476074</t>
   </si>
   <si>
     <t xml:space="preserve">24.8985767364502</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9733352661133</t>
+    <t xml:space="preserve">25.9733371734619</t>
   </si>
   <si>
     <t xml:space="preserve">26.5107154846191</t>
@@ -2558,31 +2558,31 @@
     <t xml:space="preserve">26.197244644165</t>
   </si>
   <si>
-    <t xml:space="preserve">26.868968963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6450595855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4959125518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.048095703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9437255859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8841419219971</t>
+    <t xml:space="preserve">26.8689670562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6450576782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4959106445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0480937957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9437274932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8841400146484</t>
   </si>
   <si>
     <t xml:space="preserve">28.9289207458496</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7050151824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7797718048096</t>
+    <t xml:space="preserve">28.7050132751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7797737121582</t>
   </si>
   <si>
     <t xml:space="preserve">27.9885082244873</t>
@@ -2594,34 +2594,34 @@
     <t xml:space="preserve">27.2272205352783</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4063472747803</t>
+    <t xml:space="preserve">27.4063491821289</t>
   </si>
   <si>
     <t xml:space="preserve">26.6898403167725</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8389892578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.79421043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3315868377686</t>
+    <t xml:space="preserve">25.8389911651611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7942085266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3315887451172</t>
   </si>
   <si>
     <t xml:space="preserve">24.7194519042969</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4507598876953</t>
+    <t xml:space="preserve">24.4507617950439</t>
   </si>
   <si>
     <t xml:space="preserve">23.599910736084</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4655647277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3615646362305</t>
+    <t xml:space="preserve">23.4655666351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3615665435791</t>
   </si>
   <si>
     <t xml:space="preserve">28.0332889556885</t>
@@ -2639,7 +2639,7 @@
     <t xml:space="preserve">30.2979869842529</t>
   </si>
   <si>
-    <t xml:space="preserve">26.891170501709</t>
+    <t xml:space="preserve">26.8911685943604</t>
   </si>
   <si>
     <t xml:space="preserve">27.3454132080078</t>
@@ -2654,19 +2654,19 @@
     <t xml:space="preserve">29.3440799713135</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5251083374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5705375671387</t>
+    <t xml:space="preserve">30.5251121520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.57053565979</t>
   </si>
   <si>
     <t xml:space="preserve">31.0247802734375</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0702056884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8885040283203</t>
+    <t xml:space="preserve">31.0702037811279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8885059356689</t>
   </si>
   <si>
     <t xml:space="preserve">28.9352626800537</t>
@@ -2678,19 +2678,19 @@
     <t xml:space="preserve">27.9359283447266</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4362602233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0721988677979</t>
+    <t xml:space="preserve">27.4362621307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0722026824951</t>
   </si>
   <si>
     <t xml:space="preserve">28.4355945587158</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5264415740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4810199737549</t>
+    <t xml:space="preserve">28.5264434814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4810180664062</t>
   </si>
   <si>
     <t xml:space="preserve">28.3901710510254</t>
@@ -2702,22 +2702,22 @@
     <t xml:space="preserve">29.434928894043</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2538986206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1169605255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1162948608398</t>
+    <t xml:space="preserve">28.2538967132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1169586181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1162929534912</t>
   </si>
   <si>
     <t xml:space="preserve">30.9793529510498</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1610488891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.479024887085</t>
+    <t xml:space="preserve">31.1610507965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4790210723877</t>
   </si>
   <si>
     <t xml:space="preserve">31.5698719024658</t>
@@ -2726,7 +2726,7 @@
     <t xml:space="preserve">31.7969932556152</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7515678405762</t>
+    <t xml:space="preserve">31.7515697479248</t>
   </si>
   <si>
     <t xml:space="preserve">31.1156272888184</t>
@@ -2741,16 +2741,16 @@
     <t xml:space="preserve">33.8410835266113</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4770278930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.386173248291</t>
+    <t xml:space="preserve">34.4770240783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3861770629883</t>
   </si>
   <si>
     <t xml:space="preserve">34.5678672790527</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6132926940918</t>
+    <t xml:space="preserve">34.6132965087891</t>
   </si>
   <si>
     <t xml:space="preserve">35.3400840759277</t>
@@ -2759,28 +2759,28 @@
     <t xml:space="preserve">34.4316024780273</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7048072814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9773597717285</t>
+    <t xml:space="preserve">33.7048110961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9773559570312</t>
   </si>
   <si>
     <t xml:space="preserve">34.931266784668</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5224494934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0682067871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7502326965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9319305419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2499046325684</t>
+    <t xml:space="preserve">34.5224456787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0682029724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7502365112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9319343566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2499008178711</t>
   </si>
   <si>
     <t xml:space="preserve">33.6139640808105</t>
@@ -2789,19 +2789,19 @@
     <t xml:space="preserve">36.2485733032227</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6573905944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7936592102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6106300354004</t>
+    <t xml:space="preserve">36.6573867797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7936630249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6106338500977</t>
   </si>
   <si>
     <t xml:space="preserve">39.5645408630371</t>
   </si>
   <si>
-    <t xml:space="preserve">38.1109657287598</t>
+    <t xml:space="preserve">38.110969543457</t>
   </si>
   <si>
     <t xml:space="preserve">36.4302635192871</t>
@@ -2816,13 +2816,13 @@
     <t xml:space="preserve">33.0688743591309</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3414154052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8865089416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2044792175293</t>
+    <t xml:space="preserve">33.3414192199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8865051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2044830322266</t>
   </si>
   <si>
     <t xml:space="preserve">34.340747833252</t>
@@ -2831,16 +2831,16 @@
     <t xml:space="preserve">32.7509002685547</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6600570678711</t>
+    <t xml:space="preserve">32.6600532531738</t>
   </si>
   <si>
     <t xml:space="preserve">32.9780197143555</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7976589202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3895034790039</t>
+    <t xml:space="preserve">30.7976551055908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3895053863525</t>
   </si>
   <si>
     <t xml:space="preserve">29.5257778167725</t>
@@ -2861,7 +2861,7 @@
     <t xml:space="preserve">32.205810546875</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1149597167969</t>
+    <t xml:space="preserve">32.1149559020996</t>
   </si>
   <si>
     <t xml:space="preserve">32.2512359619141</t>
@@ -2885,10 +2885,10 @@
     <t xml:space="preserve">32.0695381164551</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5244464874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3427467346191</t>
+    <t xml:space="preserve">31.5244483947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3427486419678</t>
   </si>
   <si>
     <t xml:space="preserve">32.3420829772949</t>
@@ -2903,7 +2903,7 @@
     <t xml:space="preserve">32.1603851318359</t>
   </si>
   <si>
-    <t xml:space="preserve">34.159049987793</t>
+    <t xml:space="preserve">34.1590538024902</t>
   </si>
   <si>
     <t xml:space="preserve">33.7956581115723</t>
@@ -2918,7 +2918,7 @@
     <t xml:space="preserve">33.0234451293945</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5231132507324</t>
+    <t xml:space="preserve">33.5231170654297</t>
   </si>
   <si>
     <t xml:space="preserve">32.4783554077148</t>
@@ -2930,37 +2930,37 @@
     <t xml:space="preserve">31.8424167633057</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8878383636475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4342651367188</t>
+    <t xml:space="preserve">31.8878364562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4342632293701</t>
   </si>
   <si>
     <t xml:space="preserve">29.7074756622314</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7068061828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4796867370605</t>
+    <t xml:space="preserve">30.7068099975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4796886444092</t>
   </si>
   <si>
     <t xml:space="preserve">29.6166248321533</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8437442779541</t>
+    <t xml:space="preserve">29.8437461853027</t>
   </si>
   <si>
     <t xml:space="preserve">29.2532329559326</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7535629272461</t>
+    <t xml:space="preserve">28.7535648345947</t>
   </si>
   <si>
     <t xml:space="preserve">30.0708675384521</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8898372650146</t>
+    <t xml:space="preserve">28.889835357666</t>
   </si>
   <si>
     <t xml:space="preserve">28.6627159118652</t>
@@ -2969,13 +2969,13 @@
     <t xml:space="preserve">28.8444137573242</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7081432342529</t>
+    <t xml:space="preserve">28.7081413269043</t>
   </si>
   <si>
     <t xml:space="preserve">28.9806861877441</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7989902496338</t>
+    <t xml:space="preserve">28.7989883422852</t>
   </si>
   <si>
     <t xml:space="preserve">29.8891735076904</t>
@@ -3002,13 +3002,13 @@
     <t xml:space="preserve">28.5718688964844</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4816856384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5725345611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6186218261719</t>
+    <t xml:space="preserve">27.4816837310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5725326538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6186237335205</t>
   </si>
   <si>
     <t xml:space="preserve">27.1182918548584</t>
@@ -3017,13 +3017,13 @@
     <t xml:space="preserve">27.0274410247803</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9365940093994</t>
+    <t xml:space="preserve">26.9365921020508</t>
   </si>
   <si>
     <t xml:space="preserve">26.9820194244385</t>
   </si>
   <si>
-    <t xml:space="preserve">26.346076965332</t>
+    <t xml:space="preserve">26.3460788726807</t>
   </si>
   <si>
     <t xml:space="preserve">25.8918361663818</t>
@@ -3032,7 +3032,7 @@
     <t xml:space="preserve">25.6647148132324</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2552299499512</t>
+    <t xml:space="preserve">26.2552280426025</t>
   </si>
   <si>
     <t xml:space="preserve">26.8457450866699</t>
@@ -3047,13 +3047,13 @@
     <t xml:space="preserve">26.5732002258301</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3915023803711</t>
+    <t xml:space="preserve">26.3915004730225</t>
   </si>
   <si>
     <t xml:space="preserve">26.70947265625</t>
   </si>
   <si>
-    <t xml:space="preserve">26.527774810791</t>
+    <t xml:space="preserve">26.5277767181396</t>
   </si>
   <si>
     <t xml:space="preserve">25.9826850891113</t>
@@ -3062,7 +3062,7 @@
     <t xml:space="preserve">25.8009872436523</t>
   </si>
   <si>
-    <t xml:space="preserve">24.165714263916</t>
+    <t xml:space="preserve">24.1657123565674</t>
   </si>
   <si>
     <t xml:space="preserve">23.6660461425781</t>
@@ -3071,13 +3071,13 @@
     <t xml:space="preserve">23.8477439880371</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4375915527344</t>
+    <t xml:space="preserve">25.4375953674316</t>
   </si>
   <si>
     <t xml:space="preserve">25.7555637359619</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0741996765137</t>
+    <t xml:space="preserve">25.074197769165</t>
   </si>
   <si>
     <t xml:space="preserve">26.0735340118408</t>
@@ -3089,7 +3089,7 @@
     <t xml:space="preserve">26.3419418334961</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6671504974365</t>
+    <t xml:space="preserve">26.6671524047852</t>
   </si>
   <si>
     <t xml:space="preserve">27.1317348480225</t>
@@ -3098,7 +3098,7 @@
     <t xml:space="preserve">27.6427764892578</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3396549224854</t>
+    <t xml:space="preserve">28.3396530151367</t>
   </si>
   <si>
     <t xml:space="preserve">27.8286113739014</t>
@@ -3152,7 +3152,7 @@
     <t xml:space="preserve">27.038818359375</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9458999633789</t>
+    <t xml:space="preserve">26.9459018707275</t>
   </si>
   <si>
     <t xml:space="preserve">26.760066986084</t>
@@ -3164,19 +3164,19 @@
     <t xml:space="preserve">26.2025661468506</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5742340087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4813175201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8994445800781</t>
+    <t xml:space="preserve">26.5742321014404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.481315612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8994426727295</t>
   </si>
   <si>
     <t xml:space="preserve">26.2490253448486</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7379817962646</t>
+    <t xml:space="preserve">25.7379837036133</t>
   </si>
   <si>
     <t xml:space="preserve">25.9238147735596</t>
@@ -3191,7 +3191,7 @@
     <t xml:space="preserve">27.271110534668</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2246494293213</t>
+    <t xml:space="preserve">27.2246513366699</t>
   </si>
   <si>
     <t xml:space="preserve">25.4127731323242</t>
@@ -3203,7 +3203,7 @@
     <t xml:space="preserve">24.5300617218018</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9017276763916</t>
+    <t xml:space="preserve">24.9017295837402</t>
   </si>
   <si>
     <t xml:space="preserve">25.0875625610352</t>
@@ -3212,76 +3212,76 @@
     <t xml:space="preserve">24.8088130950928</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5521488189697</t>
+    <t xml:space="preserve">25.5521469116211</t>
   </si>
   <si>
     <t xml:space="preserve">25.5056896209717</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7623519897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7158966064453</t>
+    <t xml:space="preserve">24.7623538970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7158946990967</t>
   </si>
   <si>
     <t xml:space="preserve">25.8308982849121</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0852756500244</t>
+    <t xml:space="preserve">27.085277557373</t>
   </si>
   <si>
     <t xml:space="preserve">26.7136077880859</t>
   </si>
   <si>
-    <t xml:space="preserve">26.016731262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8773555755615</t>
+    <t xml:space="preserve">26.0167331695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8773574829102</t>
   </si>
   <si>
     <t xml:space="preserve">25.7844390869141</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0631904602051</t>
+    <t xml:space="preserve">26.0631885528564</t>
   </si>
   <si>
     <t xml:space="preserve">26.1096496582031</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1340217590332</t>
+    <t xml:space="preserve">25.1340198516846</t>
   </si>
   <si>
     <t xml:space="preserve">25.0411052703857</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2977695465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4836025238037</t>
+    <t xml:space="preserve">24.2977676391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4836044311523</t>
   </si>
   <si>
     <t xml:space="preserve">24.0654773712158</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2513103485107</t>
+    <t xml:space="preserve">24.2513122558594</t>
   </si>
   <si>
     <t xml:space="preserve">24.5765209197998</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6008930206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0433902740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0898513793945</t>
+    <t xml:space="preserve">23.6008911132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0433921813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0898494720459</t>
   </si>
   <si>
     <t xml:space="preserve">22.114221572876</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0213069915771</t>
+    <t xml:space="preserve">22.0213050842285</t>
   </si>
   <si>
     <t xml:space="preserve">23.2756824493408</t>
@@ -3290,28 +3290,28 @@
     <t xml:space="preserve">23.4615173339844</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4150581359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1363067626953</t>
+    <t xml:space="preserve">23.415060043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1363086700439</t>
   </si>
   <si>
     <t xml:space="preserve">23.6473522186279</t>
   </si>
   <si>
-    <t xml:space="preserve">22.950475692749</t>
+    <t xml:space="preserve">22.9504737854004</t>
   </si>
   <si>
     <t xml:space="preserve">22.5788059234619</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2071380615234</t>
+    <t xml:space="preserve">22.2071399688721</t>
   </si>
   <si>
     <t xml:space="preserve">21.64963722229</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8598442077637</t>
+    <t xml:space="preserve">20.8598461151123</t>
   </si>
   <si>
     <t xml:space="preserve">21.0921363830566</t>
@@ -3326,7 +3326,7 @@
     <t xml:space="preserve">21.5567207336426</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7425556182861</t>
+    <t xml:space="preserve">21.7425537109375</t>
   </si>
   <si>
     <t xml:space="preserve">21.9283885955811</t>
@@ -3347,37 +3347,37 @@
     <t xml:space="preserve">21.4173450469971</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6031799316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8354721069336</t>
+    <t xml:space="preserve">21.603178024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.835470199585</t>
   </si>
   <si>
     <t xml:space="preserve">22.160680770874</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7181816101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3000545501709</t>
+    <t xml:space="preserve">22.7181835174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3000564575195</t>
   </si>
   <si>
     <t xml:space="preserve">22.3465137481689</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2535991668701</t>
+    <t xml:space="preserve">22.2535972595215</t>
   </si>
   <si>
     <t xml:space="preserve">21.881929397583</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7890129089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.182767868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5986042022705</t>
+    <t xml:space="preserve">21.7890148162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1827659606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5986061096191</t>
   </si>
   <si>
     <t xml:space="preserve">25.3663120269775</t>
@@ -3398,10 +3398,10 @@
     <t xml:space="preserve">24.4371433258057</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8796443939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2048530578613</t>
+    <t xml:space="preserve">23.8796424865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2048511505127</t>
   </si>
   <si>
     <t xml:space="preserve">23.9261016845703</t>
@@ -3410,7 +3410,7 @@
     <t xml:space="preserve">24.6694355010986</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5544338226318</t>
+    <t xml:space="preserve">23.5544357299805</t>
   </si>
   <si>
     <t xml:space="preserve">23.6938095092773</t>
@@ -3419,7 +3419,7 @@
     <t xml:space="preserve">23.3221416473389</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7867279052734</t>
+    <t xml:space="preserve">23.7867259979248</t>
   </si>
   <si>
     <t xml:space="preserve">22.8575572967529</t>
@@ -3428,7 +3428,7 @@
     <t xml:space="preserve">21.5102615356445</t>
   </si>
   <si>
-    <t xml:space="preserve">21.370885848999</t>
+    <t xml:space="preserve">21.3708877563477</t>
   </si>
   <si>
     <t xml:space="preserve">21.1850528717041</t>
@@ -3437,19 +3437,19 @@
     <t xml:space="preserve">20.7204685211182</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4881763458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9771347045898</t>
+    <t xml:space="preserve">20.4881744384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9771327972412</t>
   </si>
   <si>
     <t xml:space="preserve">20.2558822631836</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5346336364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9306755065918</t>
+    <t xml:space="preserve">20.5346355438232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9306774139404</t>
   </si>
   <si>
     <t xml:space="preserve">20.5810928344727</t>
@@ -3461,7 +3461,7 @@
     <t xml:space="preserve">20.6275520324707</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0235900878906</t>
+    <t xml:space="preserve">20.0235919952393</t>
   </si>
   <si>
     <t xml:space="preserve">18.6298370361328</t>
@@ -3479,7 +3479,7 @@
     <t xml:space="preserve">17.8772106170654</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5427093505859</t>
+    <t xml:space="preserve">17.5427112579346</t>
   </si>
   <si>
     <t xml:space="preserve">17.2453765869141</t>
@@ -3491,10 +3491,10 @@
     <t xml:space="preserve">17.5612926483154</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4126281738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.747127532959</t>
+    <t xml:space="preserve">17.4126262664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7471294403076</t>
   </si>
   <si>
     <t xml:space="preserve">17.1896266937256</t>
@@ -3515,13 +3515,13 @@
     <t xml:space="preserve">16.3162078857422</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9817085266113</t>
+    <t xml:space="preserve">15.981707572937</t>
   </si>
   <si>
     <t xml:space="preserve">16.5392074584961</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2976245880127</t>
+    <t xml:space="preserve">16.2976264953613</t>
   </si>
   <si>
     <t xml:space="preserve">16.1861248016357</t>
@@ -3533,7 +3533,7 @@
     <t xml:space="preserve">16.1489562988281</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2418746948242</t>
+    <t xml:space="preserve">16.2418727874756</t>
   </si>
   <si>
     <t xml:space="preserve">16.0746231079102</t>
@@ -4323,6 +4323,9 @@
   </si>
   <si>
     <t xml:space="preserve">18.8400001525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7399997711182</t>
   </si>
 </sst>
 </file>
@@ -70233,7 +70236,7 @@
     </row>
     <row r="2523">
       <c r="A2523" s="1" t="n">
-        <v>45992.6911342593</v>
+        <v>45992.3333333333</v>
       </c>
       <c r="B2523" t="n">
         <v>3100</v>
@@ -70254,6 +70257,32 @@
         <v>1436</v>
       </c>
       <c r="H2523" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2524">
+      <c r="A2524" s="1" t="n">
+        <v>45993.692349537</v>
+      </c>
+      <c r="B2524" t="n">
+        <v>3287</v>
+      </c>
+      <c r="C2524" t="n">
+        <v>18.9799995422363</v>
+      </c>
+      <c r="D2524" t="n">
+        <v>18.7000007629395</v>
+      </c>
+      <c r="E2524" t="n">
+        <v>18.7999992370605</v>
+      </c>
+      <c r="F2524" t="n">
+        <v>18.7399997711182</v>
+      </c>
+      <c r="G2524" t="s">
+        <v>1437</v>
+      </c>
+      <c r="H2524" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ARN.MI.xlsx
+++ b/data/ARN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="1440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="1441">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,82 +44,82 @@
     <t xml:space="preserve">ARN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94450068473816</t>
+    <t xml:space="preserve">1.94450092315674</t>
   </si>
   <si>
     <t xml:space="preserve">1.91736054420471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90778207778931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88383519649506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93172907829285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91576409339905</t>
+    <t xml:space="preserve">1.90778195858002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8838347196579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93172919750214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91576421260834</t>
   </si>
   <si>
     <t xml:space="preserve">1.83434414863586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83594071865082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91097486019135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.807204246521</t>
+    <t xml:space="preserve">1.83594059944153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91097462177277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80720448493958</t>
   </si>
   <si>
     <t xml:space="preserve">1.74973106384277</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71620571613312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80401110649109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81039702892303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79602909088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7720822095871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70662665367126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69704794883728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69066202640533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67629361152649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70024085044861</t>
+    <t xml:space="preserve">1.71620547771454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80401122570038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81039690971375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79602885246277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77208185195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70662677288055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6970477104187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69066190719604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67629337310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7002409696579</t>
   </si>
   <si>
     <t xml:space="preserve">1.69864428043365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67469704151154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66671478748322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66032910346985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81518638134003</t>
+    <t xml:space="preserve">1.67469716072083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66671502590179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66032922267914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81518661975861</t>
   </si>
   <si>
     <t xml:space="preserve">1.82795834541321</t>
@@ -128,43 +128,43 @@
     <t xml:space="preserve">1.86148416996002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88543152809143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89181685447693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92853605747223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95407938957214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90618526935577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86787021160126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88064169883728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85190510749817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85988795757294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85509824752808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79283618927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78804671764374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78006434440613</t>
+    <t xml:space="preserve">1.88543117046356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8918172121048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92853629589081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95407950878143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90618562698364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86787009239197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88064205646515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85190558433533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85988759994507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8550980091095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7928364276886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78804683685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78006458282471</t>
   </si>
   <si>
     <t xml:space="preserve">1.7561172246933</t>
@@ -173,43 +173,43 @@
     <t xml:space="preserve">1.76888883113861</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7640997171402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78485369682312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77048563957214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72099483013153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73536336421967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80241465568542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76250314712524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74494194984436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73217022418976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73695969581604</t>
+    <t xml:space="preserve">1.76409935951233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78485357761383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77048540115356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72099471092224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73536312580109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80241501331329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76250290870667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74494206905365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73217034339905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73695981502533</t>
   </si>
   <si>
     <t xml:space="preserve">1.7433454990387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75132763385773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68587267398834</t>
+    <t xml:space="preserve">1.7513279914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68587243556976</t>
   </si>
   <si>
     <t xml:space="preserve">1.67789018154144</t>
@@ -218,22 +218,22 @@
     <t xml:space="preserve">1.65234673023224</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6204172372818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64276802539825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5900844335556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60285580158234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54937422275543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51185715198517</t>
+    <t xml:space="preserve">1.62041735649109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64276790618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59008419513702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60285604000092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54937446117401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51185727119446</t>
   </si>
   <si>
     <t xml:space="preserve">1.45598089694977</t>
@@ -242,40 +242,40 @@
     <t xml:space="preserve">1.43682312965393</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46955096721649</t>
+    <t xml:space="preserve">1.46955072879791</t>
   </si>
   <si>
     <t xml:space="preserve">1.49748921394348</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47673487663269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47274374961853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46875274181366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49669086933136</t>
+    <t xml:space="preserve">1.47673499584198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47274386882782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46875250339508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49669075012207</t>
   </si>
   <si>
     <t xml:space="preserve">1.47593665122986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50626957416534</t>
+    <t xml:space="preserve">1.50626945495605</t>
   </si>
   <si>
     <t xml:space="preserve">1.47753310203552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43841958045959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40090239048004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34901738166809</t>
+    <t xml:space="preserve">1.43841969966888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40090262889862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34901750087738</t>
   </si>
   <si>
     <t xml:space="preserve">1.30910551548004</t>
@@ -284,43 +284,43 @@
     <t xml:space="preserve">1.34342968463898</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3266669511795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3410347700119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31708800792694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38653421401978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39691162109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40649044513702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30671083927155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32347393035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30591261386871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31229841709137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28994786739349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2851585149765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28595662117004</t>
+    <t xml:space="preserve">1.32666671276093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34103488922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31708776950836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38653433322906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39691150188446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40649020671844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30671095848083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3234738111496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30591285228729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31229865550995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28994798660278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28515863418579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28595674037933</t>
   </si>
   <si>
     <t xml:space="preserve">1.33305263519287</t>
@@ -332,88 +332,88 @@
     <t xml:space="preserve">1.30112326145172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36104881763458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34627246856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35283970832825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33806359767914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27157092094421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28880989551544</t>
+    <t xml:space="preserve">1.36104893684387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34627258777618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35283982753754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33806347846985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27157080173492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28880977630615</t>
   </si>
   <si>
     <t xml:space="preserve">1.29291415214539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30686950683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33888447284698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34955608844757</t>
+    <t xml:space="preserve">1.30686974525452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33888459205627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34955620765686</t>
   </si>
   <si>
     <t xml:space="preserve">1.34380984306335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33642172813416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34709346294403</t>
+    <t xml:space="preserve">1.33642184734344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34709358215332</t>
   </si>
   <si>
     <t xml:space="preserve">1.30522763729095</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2912722826004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31425762176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32164585590363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26828742027283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27239179611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2879890203476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2970187664032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24858582019806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32657110691071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33231735229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35940682888031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4201534986496</t>
+    <t xml:space="preserve">1.29127252101898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31425750255585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32164573669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26828730106354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27239167690277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28798890113831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29701888561249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24858593940735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32657098770142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33231747150421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3594069480896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42015337944031</t>
   </si>
   <si>
     <t xml:space="preserve">1.48664617538452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53343749046326</t>
+    <t xml:space="preserve">1.53343737125397</t>
   </si>
   <si>
     <t xml:space="preserve">1.51619851589203</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">1.43739235401154</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46776568889618</t>
+    <t xml:space="preserve">1.46776556968689</t>
   </si>
   <si>
     <t xml:space="preserve">1.43000423908234</t>
@@ -434,7 +434,7 @@
     <t xml:space="preserve">1.40948188304901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44478046894073</t>
+    <t xml:space="preserve">1.44478034973145</t>
   </si>
   <si>
     <t xml:space="preserve">1.5597060918808</t>
@@ -443,22 +443,22 @@
     <t xml:space="preserve">1.61798989772797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70582616329193</t>
+    <t xml:space="preserve">1.70582568645477</t>
   </si>
   <si>
     <t xml:space="preserve">1.74851274490356</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72388565540314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68284094333649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67463171482086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.651646733284</t>
+    <t xml:space="preserve">1.72388553619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68284058570862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67463159561157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65164661407471</t>
   </si>
   <si>
     <t xml:space="preserve">1.64179587364197</t>
@@ -467,61 +467,61 @@
     <t xml:space="preserve">1.67134821414948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6647812128067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65657186508179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69597518444061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69433319568634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65821373462677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6811990737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68776631355286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6680645942688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65000474452972</t>
+    <t xml:space="preserve">1.66478109359741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65657198429108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69597494602203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69433331489563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65821385383606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68119919300079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68776607513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66806471347809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6500049829483</t>
   </si>
   <si>
     <t xml:space="preserve">1.66313922405243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67791557312012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03746891021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04403614997864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0391104221344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04075264930725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0522449016571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04731965065002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04239439964294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19836497306824</t>
+    <t xml:space="preserve">1.67791533470154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03746867179871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04403591156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03911066055298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04075217247009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05224514007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04731917381287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04239416122437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1983642578125</t>
   </si>
   <si>
     <t xml:space="preserve">2.24105143547058</t>
@@ -530,193 +530,193 @@
     <t xml:space="preserve">2.18851375579834</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17537975311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.145827293396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00627470016479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98821496963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99314022064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99806523323059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99642395973206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99970746040344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00299119949341</t>
+    <t xml:space="preserve">2.17537951469421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14582753181458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00627493858337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98821485042572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99313998222351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99806582927704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99642360210419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99970781803131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00299096107483</t>
   </si>
   <si>
     <t xml:space="preserve">2.00791645050049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01119995117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02597594261169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03254318237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02105069160461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01940870285034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02433443069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07687163352966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0588116645813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09657311439514</t>
+    <t xml:space="preserve">2.0111997127533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02597618103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03254342079163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02105045318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01940894126892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02433466911316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07687187194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05881190299988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09657335281372</t>
   </si>
   <si>
     <t xml:space="preserve">2.14746928215027</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33955907821655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27552962303162</t>
+    <t xml:space="preserve">2.33955883979797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27552914619446</t>
   </si>
   <si>
     <t xml:space="preserve">2.32478284835815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27881240844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25746941566467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29851388931274</t>
+    <t xml:space="preserve">2.27881264686584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25746965408325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2985143661499</t>
   </si>
   <si>
     <t xml:space="preserve">2.26075267791748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28045463562012</t>
+    <t xml:space="preserve">2.2804548740387</t>
   </si>
   <si>
     <t xml:space="preserve">2.30672311782837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35597705841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34120106697083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34284329414368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34776830673218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44627594947815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39209628105164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38224601745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38717126846313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38388752937317</t>
+    <t xml:space="preserve">2.35597729682922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34120082855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34284281730652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34776759147644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44627571105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39209651947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38224577903748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38717150688171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38388776779175</t>
   </si>
   <si>
     <t xml:space="preserve">2.40523076057434</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38060402870178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42164874076843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33791756629944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32314109802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35433554649353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41015648841858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40687274932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4380669593811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41836500167847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29030537605286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34941029548645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36418604850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37567830085754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40194749832153</t>
+    <t xml:space="preserve">2.3806037902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42164897918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33791732788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32314085960388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35433530807495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41015672683716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40687298774719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43806672096252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41836547851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29030561447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34940958023071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36418628692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3756787776947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40194725990295</t>
   </si>
   <si>
     <t xml:space="preserve">2.35761904716492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36746978759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37075328826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37239480018616</t>
+    <t xml:space="preserve">2.36746954917908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37075304985046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37239527702332</t>
   </si>
   <si>
     <t xml:space="preserve">2.362544298172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3658275604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39538025856018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37732028961182</t>
+    <t xml:space="preserve">2.36582827568054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3953800201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37732076644897</t>
   </si>
   <si>
     <t xml:space="preserve">2.37403678894043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38881325721741</t>
+    <t xml:space="preserve">2.38881301879883</t>
   </si>
   <si>
     <t xml:space="preserve">2.39373803138733</t>
@@ -725,7 +725,7 @@
     <t xml:space="preserve">2.39045476913452</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41343998908997</t>
+    <t xml:space="preserve">2.41343975067139</t>
   </si>
   <si>
     <t xml:space="preserve">2.40358901023865</t>
@@ -734,49 +734,49 @@
     <t xml:space="preserve">2.40030574798584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40851449966431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42329049110413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43149948120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42000722885132</t>
+    <t xml:space="preserve">2.40851521492004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42329072952271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43149995803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42000699043274</t>
   </si>
   <si>
     <t xml:space="preserve">2.35105180740356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33627557754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34612655639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43642520904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42657446861267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42985773086548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45284295082092</t>
+    <t xml:space="preserve">2.33627581596375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34612631797791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43642497062683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42657423019409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42985820770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45284342765808</t>
   </si>
   <si>
     <t xml:space="preserve">2.4770131111145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.478679895401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49201512336731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49368214607239</t>
+    <t xml:space="preserve">2.47867965698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49201536178589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49368190765381</t>
   </si>
   <si>
     <t xml:space="preserve">2.47534608840942</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">2.46534490585327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48201394081116</t>
+    <t xml:space="preserve">2.48201370239258</t>
   </si>
   <si>
     <t xml:space="preserve">2.46867847442627</t>
@@ -794,22 +794,22 @@
     <t xml:space="preserve">2.45867729187012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46201109886169</t>
+    <t xml:space="preserve">2.46201062202454</t>
   </si>
   <si>
     <t xml:space="preserve">2.45534324645996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41700506210327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40867018699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36699771881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34199404716492</t>
+    <t xml:space="preserve">2.41700482368469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40867042541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36699748039246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3419942855835</t>
   </si>
   <si>
     <t xml:space="preserve">2.36866450309753</t>
@@ -818,31 +818,31 @@
     <t xml:space="preserve">2.35366225242615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.385333776474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38366675376892</t>
+    <t xml:space="preserve">2.38533329963684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38366651535034</t>
   </si>
   <si>
     <t xml:space="preserve">2.36366391181946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32532548904419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31699061393738</t>
+    <t xml:space="preserve">2.32532525062561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31699085235596</t>
   </si>
   <si>
     <t xml:space="preserve">2.28531956672668</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28698658943176</t>
+    <t xml:space="preserve">2.28698635101318</t>
   </si>
   <si>
     <t xml:space="preserve">2.29698801040649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31532382965088</t>
+    <t xml:space="preserve">2.31532406806946</t>
   </si>
   <si>
     <t xml:space="preserve">2.28365278244019</t>
@@ -854,37 +854,37 @@
     <t xml:space="preserve">2.29032039642334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30198860168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30365562438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29365420341492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24198031425476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26698398590088</t>
+    <t xml:space="preserve">2.30198884010315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30365538597107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2936544418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24198007583618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2669837474823</t>
   </si>
   <si>
     <t xml:space="preserve">2.2686505317688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32699203491211</t>
+    <t xml:space="preserve">2.32699227333069</t>
   </si>
   <si>
     <t xml:space="preserve">2.31865763664246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31032371520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24364686012268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25031423568726</t>
+    <t xml:space="preserve">2.31032347679138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24364709854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25031495094299</t>
   </si>
   <si>
     <t xml:space="preserve">2.22531127929688</t>
@@ -893,40 +893,40 @@
     <t xml:space="preserve">2.25198173522949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22197723388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20697522163391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20030760765076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16863656044006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17863798141479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16696929931641</t>
+    <t xml:space="preserve">2.2219774723053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20697546005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20030808448792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16863632202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17863821983337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16697001457214</t>
   </si>
   <si>
     <t xml:space="preserve">2.18697237968445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1969735622406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18363881111145</t>
+    <t xml:space="preserve">2.19697380065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18363857269287</t>
   </si>
   <si>
     <t xml:space="preserve">2.18530559539795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19197368621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17530393600464</t>
+    <t xml:space="preserve">2.1919732093811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17530417442322</t>
   </si>
   <si>
     <t xml:space="preserve">2.14196634292603</t>
@@ -935,25 +935,25 @@
     <t xml:space="preserve">2.15363478660583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14363288879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13529872894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12696409225464</t>
+    <t xml:space="preserve">2.14363312721252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13529849052429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1269645690918</t>
   </si>
   <si>
     <t xml:space="preserve">2.12863087654114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12029671669006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13029789924622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11862993240356</t>
+    <t xml:space="preserve">2.12029647827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13029813766479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11862969398499</t>
   </si>
   <si>
     <t xml:space="preserve">2.37366557121277</t>
@@ -962,37 +962,37 @@
     <t xml:space="preserve">2.37533211708069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40700316429138</t>
+    <t xml:space="preserve">2.40700340270996</t>
   </si>
   <si>
     <t xml:space="preserve">2.39533495903015</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39200091362</t>
+    <t xml:space="preserve">2.39200115203857</t>
   </si>
   <si>
     <t xml:space="preserve">2.49868249893188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49534869194031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50868439674377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51201820373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51535177230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51701879501343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.523686170578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52535319328308</t>
+    <t xml:space="preserve">2.49534893035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5086841583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51201796531677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51535153388977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51701903343201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52368640899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5253529548645</t>
   </si>
   <si>
     <t xml:space="preserve">2.54535579681396</t>
@@ -1001,10 +1001,10 @@
     <t xml:space="preserve">2.53368759155273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53202080726624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54035568237305</t>
+    <t xml:space="preserve">2.53202104568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54035544395447</t>
   </si>
   <si>
     <t xml:space="preserve">2.52702021598816</t>
@@ -1016,10 +1016,10 @@
     <t xml:space="preserve">2.53702163696289</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49701642990112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42700624465942</t>
+    <t xml:space="preserve">2.49701595306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42700600624084</t>
   </si>
   <si>
     <t xml:space="preserve">2.50034976005554</t>
@@ -1034,10 +1034,10 @@
     <t xml:space="preserve">2.45200943946838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51368474960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54202198982239</t>
+    <t xml:space="preserve">2.51368498802185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54202222824097</t>
   </si>
   <si>
     <t xml:space="preserve">2.54868984222412</t>
@@ -1052,52 +1052,52 @@
     <t xml:space="preserve">2.47201251983643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50201654434204</t>
+    <t xml:space="preserve">2.50201630592346</t>
   </si>
   <si>
     <t xml:space="preserve">2.48701453208923</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0004198551178</t>
+    <t xml:space="preserve">3.00041961669922</t>
   </si>
   <si>
     <t xml:space="preserve">2.81706094741821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75038480758667</t>
+    <t xml:space="preserve">2.75038456916809</t>
   </si>
   <si>
     <t xml:space="preserve">2.71704649925232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8087260723114</t>
+    <t xml:space="preserve">2.80872631072998</t>
   </si>
   <si>
     <t xml:space="preserve">2.80039167404175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83372950553894</t>
+    <t xml:space="preserve">2.83372974395752</t>
   </si>
   <si>
     <t xml:space="preserve">2.78372263908386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84206461906433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75871896743774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85039877891541</t>
+    <t xml:space="preserve">2.84206414222717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75871920585632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85039901733398</t>
   </si>
   <si>
     <t xml:space="preserve">2.85873317718506</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89207124710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82539534568787</t>
+    <t xml:space="preserve">2.89207100868225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82539510726929</t>
   </si>
   <si>
     <t xml:space="preserve">2.72538113594055</t>
@@ -1109,28 +1109,28 @@
     <t xml:space="preserve">2.6420361995697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70037746429443</t>
+    <t xml:space="preserve">2.70037770271301</t>
   </si>
   <si>
     <t xml:space="preserve">2.65870523452759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6253674030304</t>
+    <t xml:space="preserve">2.62536716461182</t>
   </si>
   <si>
     <t xml:space="preserve">2.63370180130005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59202933311462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66703987121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70871233940125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74205040931702</t>
+    <t xml:space="preserve">2.59202909469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66703963279724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70871186256409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74204993247986</t>
   </si>
   <si>
     <t xml:space="preserve">2.65037059783936</t>
@@ -1139,16 +1139,16 @@
     <t xml:space="preserve">2.68370890617371</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6003634929657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58369493484497</t>
+    <t xml:space="preserve">2.60036373138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58369469642639</t>
   </si>
   <si>
     <t xml:space="preserve">2.56702542304993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76705384254456</t>
+    <t xml:space="preserve">2.7670533657074</t>
   </si>
   <si>
     <t xml:space="preserve">2.73371577262878</t>
@@ -1163,31 +1163,31 @@
     <t xml:space="preserve">2.87540221214294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88373684883118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77538824081421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78091406822205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72174549102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7301983833313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77246117591858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64567232131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70484042167664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68793511390686</t>
+    <t xml:space="preserve">2.8837366104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77538776397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78091382980347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72174572944641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73019790649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77246141433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.645672082901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70484018325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68793487548828</t>
   </si>
   <si>
     <t xml:space="preserve">2.6625771522522</t>
@@ -1196,16 +1196,16 @@
     <t xml:space="preserve">2.69638776779175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65412473678589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60340857505798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63721895217896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61186170578003</t>
+    <t xml:space="preserve">2.65412449836731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6034083366394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63721919059753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61186122894287</t>
   </si>
   <si>
     <t xml:space="preserve">2.5780508518219</t>
@@ -1217,28 +1217,28 @@
     <t xml:space="preserve">2.50197720527649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49352478981018</t>
+    <t xml:space="preserve">2.4935245513916</t>
   </si>
   <si>
     <t xml:space="preserve">2.54424023628235</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5611457824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58650350570679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51888275146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53578782081604</t>
+    <t xml:space="preserve">2.56114554405212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58650326728821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51888251304626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53578758239746</t>
   </si>
   <si>
     <t xml:space="preserve">2.55269312858582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5104296207428</t>
+    <t xml:space="preserve">2.51042985916138</t>
   </si>
   <si>
     <t xml:space="preserve">2.56959819793701</t>
@@ -1247,19 +1247,19 @@
     <t xml:space="preserve">2.46816682815552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48507213592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41745090484619</t>
+    <t xml:space="preserve">2.48507189750671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41745066642761</t>
   </si>
   <si>
     <t xml:space="preserve">2.45126152038574</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39209318161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38364052772522</t>
+    <t xml:space="preserve">2.39209246635437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38364028930664</t>
   </si>
   <si>
     <t xml:space="preserve">2.27375626564026</t>
@@ -1268,58 +1268,58 @@
     <t xml:space="preserve">2.29911422729492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36673474311829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35828256607056</t>
+    <t xml:space="preserve">2.36673521995544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35828280448914</t>
   </si>
   <si>
     <t xml:space="preserve">2.43435621261597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42590308189392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34982991218567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28220868110657</t>
+    <t xml:space="preserve">2.42590355873108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34983015060425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28220891952515</t>
   </si>
   <si>
     <t xml:space="preserve">2.32447218894958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40899801254272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45971417427063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44280862808228</t>
+    <t xml:space="preserve">2.4089982509613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45971393585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44280910491943</t>
   </si>
   <si>
     <t xml:space="preserve">2.33292460441589</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3413770198822</t>
+    <t xml:space="preserve">2.34137725830078</t>
   </si>
   <si>
     <t xml:space="preserve">2.40054559707642</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37518763542175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47661948204041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30756688117981</t>
+    <t xml:space="preserve">2.37518787384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47661924362183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30756711959839</t>
   </si>
   <si>
     <t xml:space="preserve">2.23994588851929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29430222511292</t>
+    <t xml:space="preserve">2.29430198669434</t>
   </si>
   <si>
     <t xml:space="preserve">2.23437643051147</t>
@@ -1331,19 +1331,19 @@
     <t xml:space="preserve">2.33710670471191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25149846076965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27718067169189</t>
+    <t xml:space="preserve">2.25149822235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27718043327332</t>
   </si>
   <si>
     <t xml:space="preserve">2.26861977577209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44839715957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37134957313538</t>
+    <t xml:space="preserve">2.44839692115784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37134981155396</t>
   </si>
   <si>
     <t xml:space="preserve">2.31142401695251</t>
@@ -1352,16 +1352,16 @@
     <t xml:space="preserve">2.28574156761169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26005911827087</t>
+    <t xml:space="preserve">2.26005935668945</t>
   </si>
   <si>
     <t xml:space="preserve">2.35422825813293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2258152961731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20869398117065</t>
+    <t xml:space="preserve">2.22581577301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20869374275208</t>
   </si>
   <si>
     <t xml:space="preserve">2.30286312103271</t>
@@ -1370,37 +1370,37 @@
     <t xml:space="preserve">2.31998467445374</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37991046905518</t>
+    <t xml:space="preserve">2.37991070747375</t>
   </si>
   <si>
     <t xml:space="preserve">2.40559315681458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39703178405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32854580879211</t>
+    <t xml:space="preserve">2.39703226089478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32854557037354</t>
   </si>
   <si>
     <t xml:space="preserve">2.38847160339355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36278915405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34566712379456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20013308525085</t>
+    <t xml:space="preserve">2.36278891563416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34566736221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20013332366943</t>
   </si>
   <si>
     <t xml:space="preserve">2.18301153182983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4398365020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5425660610199</t>
+    <t xml:space="preserve">2.43983626365662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54256629943848</t>
   </si>
   <si>
     <t xml:space="preserve">2.60249209403992</t>
@@ -1409,28 +1409,28 @@
     <t xml:space="preserve">2.69666123390198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77370858192444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63673543930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67097854614258</t>
+    <t xml:space="preserve">2.77370882034302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63673520088196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67097878456116</t>
   </si>
   <si>
     <t xml:space="preserve">2.61961364746094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65385723114014</t>
+    <t xml:space="preserve">2.65385699272156</t>
   </si>
   <si>
     <t xml:space="preserve">2.68810057640076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64529633522034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71378254890442</t>
+    <t xml:space="preserve">2.64529609680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71378302574158</t>
   </si>
   <si>
     <t xml:space="preserve">2.7223436832428</t>
@@ -1439,10 +1439,10 @@
     <t xml:space="preserve">3.07333779335022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52706170082092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59554839134216</t>
+    <t xml:space="preserve">3.5270619392395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59554815292358</t>
   </si>
   <si>
     <t xml:space="preserve">3.6554741859436</t>
@@ -1451,34 +1451,34 @@
     <t xml:space="preserve">3.58698773384094</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61266946792603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53562235832214</t>
+    <t xml:space="preserve">3.6126697063446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53562259674072</t>
   </si>
   <si>
     <t xml:space="preserve">3.42433190345764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54418349266052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56986618041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5527446269989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56130504608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5099401473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48425769805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57842683792114</t>
+    <t xml:space="preserve">3.54418325424194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56986594200134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55274438858032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56130528450012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50993967056274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4842574596405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57842636108398</t>
   </si>
   <si>
     <t xml:space="preserve">3.638352394104</t>
@@ -1502,22 +1502,22 @@
     <t xml:space="preserve">4.19480609893799</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45163059234619</t>
+    <t xml:space="preserve">4.45163154602051</t>
   </si>
   <si>
     <t xml:space="preserve">4.53723955154419</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52011823654175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58860445022583</t>
+    <t xml:space="preserve">4.52011871337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58860397338867</t>
   </si>
   <si>
     <t xml:space="preserve">4.34890127182007</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16056394577026</t>
+    <t xml:space="preserve">4.16056299209595</t>
   </si>
   <si>
     <t xml:space="preserve">4.23761034011841</t>
@@ -1526,70 +1526,70 @@
     <t xml:space="preserve">4.29753589630127</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89517784118652</t>
+    <t xml:space="preserve">3.8951780796051</t>
   </si>
   <si>
     <t xml:space="preserve">3.27879762649536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25311541557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8935604095459</t>
+    <t xml:space="preserve">3.25311517715454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89356064796448</t>
   </si>
   <si>
     <t xml:space="preserve">3.15894603729248</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1675066947937</t>
+    <t xml:space="preserve">3.16750693321228</t>
   </si>
   <si>
     <t xml:space="preserve">3.0390944480896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44145345687866</t>
+    <t xml:space="preserve">3.44145369529724</t>
   </si>
   <si>
     <t xml:space="preserve">3.3815279006958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3900887966156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84381246566772</t>
+    <t xml:space="preserve">3.39008831977844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84381222724915</t>
   </si>
   <si>
     <t xml:space="preserve">3.8352518081665</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87805604934692</t>
+    <t xml:space="preserve">3.87805581092834</t>
   </si>
   <si>
     <t xml:space="preserve">3.76676511764526</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88661670684814</t>
+    <t xml:space="preserve">3.88661646842957</t>
   </si>
   <si>
     <t xml:space="preserve">3.85237336158752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92942118644714</t>
+    <t xml:space="preserve">3.92942023277283</t>
   </si>
   <si>
     <t xml:space="preserve">3.95510292053223</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93798184394836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11775922775269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25473165512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22905015945435</t>
+    <t xml:space="preserve">3.93798136711121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11775875091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25473213195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22904968261719</t>
   </si>
   <si>
     <t xml:space="preserve">4.26329326629639</t>
@@ -1601,10 +1601,10 @@
     <t xml:space="preserve">4.43450975418091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20336723327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00646829605103</t>
+    <t xml:space="preserve">4.20336675643921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00646781921387</t>
   </si>
   <si>
     <t xml:space="preserve">4.10919809341431</t>
@@ -1616,10 +1616,10 @@
     <t xml:space="preserve">4.08351612091064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94654202461243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07495498657227</t>
+    <t xml:space="preserve">3.94654250144958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07495546340942</t>
   </si>
   <si>
     <t xml:space="preserve">4.02359008789062</t>
@@ -1631,67 +1631,67 @@
     <t xml:space="preserve">4.13488054275513</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12632036209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01664638519287</t>
+    <t xml:space="preserve">4.12631940841675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01664590835571</t>
   </si>
   <si>
     <t xml:space="preserve">4.70845651626587</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91391563415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96528148651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94815921783447</t>
+    <t xml:space="preserve">4.91391611099243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96528100967407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94816017150879</t>
   </si>
   <si>
     <t xml:space="preserve">5.20498418807983</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56453943252563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68439054489136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95833826065063</t>
+    <t xml:space="preserve">5.56453895568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6843900680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95833683013916</t>
   </si>
   <si>
     <t xml:space="preserve">5.90697240829468</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88985013961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57471609115601</t>
+    <t xml:space="preserve">5.88985061645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57471704483032</t>
   </si>
   <si>
     <t xml:space="preserve">6.12955331802368</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4035005569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0198802947998</t>
+    <t xml:space="preserve">6.40350103378296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01987934112549</t>
   </si>
   <si>
     <t xml:space="preserve">7.20821857452393</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32807016372681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05412340164185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00275945663452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42397689819336</t>
+    <t xml:space="preserve">7.32807064056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.054123878479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00275897979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42397785186768</t>
   </si>
   <si>
     <t xml:space="preserve">7.28357124328613</t>
@@ -1703,7 +1703,7 @@
     <t xml:space="preserve">6.96765661239624</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59909105300903</t>
+    <t xml:space="preserve">6.59909057617188</t>
   </si>
   <si>
     <t xml:space="preserve">6.51133728027344</t>
@@ -1712,43 +1712,43 @@
     <t xml:space="preserve">6.73949670791626</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84480142593384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82725143432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68684482574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66929388046265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45868539810181</t>
+    <t xml:space="preserve">6.844801902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82725095748901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68684434890747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66929340362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45868444442749</t>
   </si>
   <si>
     <t xml:space="preserve">6.4060320854187</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31827878952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80970048904419</t>
+    <t xml:space="preserve">6.31827831268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80970001220703</t>
   </si>
   <si>
     <t xml:space="preserve">7.17826652526855</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35377502441406</t>
+    <t xml:space="preserve">7.3537745475769</t>
   </si>
   <si>
     <t xml:space="preserve">7.26601982116699</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05541133880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07296276092529</t>
+    <t xml:space="preserve">7.05541086196899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07296228408813</t>
   </si>
   <si>
     <t xml:space="preserve">6.63419246673584</t>
@@ -1757,10 +1757,10 @@
     <t xml:space="preserve">6.44113397598267</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30072736740112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05501651763916</t>
+    <t xml:space="preserve">6.30072784423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05501699447632</t>
   </si>
   <si>
     <t xml:space="preserve">6.03746604919434</t>
@@ -1772,43 +1772,43 @@
     <t xml:space="preserve">5.40563821792603</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52849388122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65134906768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12522029876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96726322174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01991558074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91461038589478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84440755844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9497127532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86195755004883</t>
+    <t xml:space="preserve">5.52849340438843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65134954452515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12521982192993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96726274490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01991510391235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91461086273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.844407081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94971179962158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86195802688599</t>
   </si>
   <si>
     <t xml:space="preserve">5.82685661315918</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93216133117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87950897216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79175519943237</t>
+    <t xml:space="preserve">5.93216180801392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87950849533081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79175567626953</t>
   </si>
   <si>
     <t xml:space="preserve">5.68645048141479</t>
@@ -1823,10 +1823,10 @@
     <t xml:space="preserve">5.70400142669678</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58114576339722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66890001296997</t>
+    <t xml:space="preserve">5.58114624023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66889953613281</t>
   </si>
   <si>
     <t xml:space="preserve">5.56359577178955</t>
@@ -1835,31 +1835,31 @@
     <t xml:space="preserve">5.61624765396118</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49339199066162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31788444519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17747783660889</t>
+    <t xml:space="preserve">5.49339246749878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31788396835327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17747831344604</t>
   </si>
   <si>
     <t xml:space="preserve">5.26523208618164</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28278303146362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35298538208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42318916320801</t>
+    <t xml:space="preserve">5.28278255462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35298585891724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42318868637085</t>
   </si>
   <si>
     <t xml:space="preserve">5.47584104537964</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3880877494812</t>
+    <t xml:space="preserve">5.38808727264404</t>
   </si>
   <si>
     <t xml:space="preserve">5.5109429359436</t>
@@ -1868,7 +1868,7 @@
     <t xml:space="preserve">5.77420473098755</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44073963165283</t>
+    <t xml:space="preserve">5.44073915481567</t>
   </si>
   <si>
     <t xml:space="preserve">5.54604434967041</t>
@@ -1877,7 +1877,7 @@
     <t xml:space="preserve">6.23052453994751</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35337972640991</t>
+    <t xml:space="preserve">6.35338020324707</t>
   </si>
   <si>
     <t xml:space="preserve">6.16032123565674</t>
@@ -1889,7 +1889,7 @@
     <t xml:space="preserve">6.47623538970947</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42358255386353</t>
+    <t xml:space="preserve">6.42358303070068</t>
   </si>
   <si>
     <t xml:space="preserve">6.54643821716309</t>
@@ -1898,25 +1898,25 @@
     <t xml:space="preserve">6.98520755767822</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33622360229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09051179885864</t>
+    <t xml:space="preserve">7.33622264862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09051275253296</t>
   </si>
   <si>
     <t xml:space="preserve">7.16071557998657</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19581747055054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00275897979736</t>
+    <t xml:space="preserve">7.19581699371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00275850296021</t>
   </si>
   <si>
     <t xml:space="preserve">6.95010614395142</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14316511154175</t>
+    <t xml:space="preserve">7.14316463470459</t>
   </si>
   <si>
     <t xml:space="preserve">7.12561368942261</t>
@@ -1928,10 +1928,10 @@
     <t xml:space="preserve">7.84519529342651</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3366174697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31906604766846</t>
+    <t xml:space="preserve">8.33661651611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31906700134277</t>
   </si>
   <si>
     <t xml:space="preserve">8.42437171936035</t>
@@ -1940,13 +1940,13 @@
     <t xml:space="preserve">9.08252429962158</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68763160705566</t>
+    <t xml:space="preserve">8.68763256072998</t>
   </si>
   <si>
     <t xml:space="preserve">9.03864765167236</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30190944671631</t>
+    <t xml:space="preserve">9.30191040039062</t>
   </si>
   <si>
     <t xml:space="preserve">11.2763719558716</t>
@@ -1961,37 +1961,37 @@
     <t xml:space="preserve">13.1192026138306</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8559417724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0222806930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1100330352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9345264434814</t>
+    <t xml:space="preserve">12.8559408187866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0222816467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1100339889526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9345254898071</t>
   </si>
   <si>
     <t xml:space="preserve">11.3641262054443</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8814792633057</t>
+    <t xml:space="preserve">10.8814783096313</t>
   </si>
   <si>
     <t xml:space="preserve">12.1539115905762</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6712646484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7151412963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4518814086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0569877624512</t>
+    <t xml:space="preserve">11.6712656021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.715142250061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4518795013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0569868087769</t>
   </si>
   <si>
     <t xml:space="preserve">11.495756149292</t>
@@ -2006,16 +2006,16 @@
     <t xml:space="preserve">11.8028955459595</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3202495574951</t>
+    <t xml:space="preserve">11.3202486038208</t>
   </si>
   <si>
     <t xml:space="preserve">11.627387046814</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1447401046753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6182193756104</t>
+    <t xml:space="preserve">11.1447410583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.618218421936</t>
   </si>
   <si>
     <t xml:space="preserve">10.5304641723633</t>
@@ -2030,16 +2030,16 @@
     <t xml:space="preserve">10.6620950698853</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3549556732178</t>
+    <t xml:space="preserve">10.3549566268921</t>
   </si>
   <si>
     <t xml:space="preserve">9.78455543518066</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91618728637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0916948318481</t>
+    <t xml:space="preserve">9.91618824005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0916938781738</t>
   </si>
   <si>
     <t xml:space="preserve">11.2324953079224</t>
@@ -2048,10 +2048,10 @@
     <t xml:space="preserve">11.1886177062988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1008634567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3553504943848</t>
+    <t xml:space="preserve">11.1008644104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3553495407104</t>
   </si>
   <si>
     <t xml:space="preserve">11.2675971984863</t>
@@ -2075,40 +2075,40 @@
     <t xml:space="preserve">11.8467721939087</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9871778488159</t>
+    <t xml:space="preserve">11.9871788024902</t>
   </si>
   <si>
     <t xml:space="preserve">12.2855415344238</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2504405975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1626853942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4672012329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0372982025146</t>
+    <t xml:space="preserve">12.2504396438599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1626863479614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4672002792358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0372972488403</t>
   </si>
   <si>
     <t xml:space="preserve">12.0910358428955</t>
   </si>
   <si>
-    <t xml:space="preserve">11.553656578064</t>
+    <t xml:space="preserve">11.5536556243896</t>
   </si>
   <si>
     <t xml:space="preserve">11.6432199478149</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3924417495728</t>
+    <t xml:space="preserve">11.3924427032471</t>
   </si>
   <si>
     <t xml:space="preserve">10.9446268081665</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5505485534668</t>
+    <t xml:space="preserve">10.5505466461182</t>
   </si>
   <si>
     <t xml:space="preserve">10.6759366989136</t>
@@ -2123,7 +2123,7 @@
     <t xml:space="preserve">10.6580238342285</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9267129898071</t>
+    <t xml:space="preserve">10.9267139434814</t>
   </si>
   <si>
     <t xml:space="preserve">11.0521030426025</t>
@@ -2138,10 +2138,10 @@
     <t xml:space="preserve">11.4282674789429</t>
   </si>
   <si>
-    <t xml:space="preserve">11.571569442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3745288848877</t>
+    <t xml:space="preserve">11.5715684890747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.374529838562</t>
   </si>
   <si>
     <t xml:space="preserve">11.3566179275513</t>
@@ -2150,13 +2150,13 @@
     <t xml:space="preserve">11.3207921981812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4461803436279</t>
+    <t xml:space="preserve">11.4461793899536</t>
   </si>
   <si>
     <t xml:space="preserve">11.464093208313</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7148694992065</t>
+    <t xml:space="preserve">11.7148704528809</t>
   </si>
   <si>
     <t xml:space="preserve">11.7327823638916</t>
@@ -2165,46 +2165,46 @@
     <t xml:space="preserve">11.750696182251</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1805992126465</t>
+    <t xml:space="preserve">12.1805982589722</t>
   </si>
   <si>
     <t xml:space="preserve">12.6284151077271</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0731220245361</t>
+    <t xml:space="preserve">12.0731229782104</t>
   </si>
   <si>
     <t xml:space="preserve">12.3418121337891</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3597249984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6969585418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1268606185913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0552110671997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8581714630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9298219680786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2880754470825</t>
+    <t xml:space="preserve">12.3597259521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6969566345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1268615722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0552101135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8581705093384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9298210144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2880744934082</t>
   </si>
   <si>
     <t xml:space="preserve">12.5925893783569</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5030269622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9835605621338</t>
+    <t xml:space="preserve">12.503026008606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9835596084595</t>
   </si>
   <si>
     <t xml:space="preserve">12.3239002227783</t>
@@ -2216,10 +2216,10 @@
     <t xml:space="preserve">11.177490234375</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2849674224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3387050628662</t>
+    <t xml:space="preserve">11.284966468811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3387041091919</t>
   </si>
   <si>
     <t xml:space="preserve">11.8939962387085</t>
@@ -2231,34 +2231,34 @@
     <t xml:space="preserve">11.6253061294556</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0014724731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1089477539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9656457901001</t>
+    <t xml:space="preserve">12.0014715194702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1089487075806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9656467437744</t>
   </si>
   <si>
     <t xml:space="preserve">12.1985120773315</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4313764572144</t>
+    <t xml:space="preserve">12.43137550354</t>
   </si>
   <si>
     <t xml:space="preserve">12.2522497177124</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8612785339355</t>
+    <t xml:space="preserve">12.8612794876099</t>
   </si>
   <si>
     <t xml:space="preserve">12.8433675765991</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6821527481079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7358913421631</t>
+    <t xml:space="preserve">12.6821537017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7358903884888</t>
   </si>
   <si>
     <t xml:space="preserve">13.3449201583862</t>
@@ -2267,16 +2267,16 @@
     <t xml:space="preserve">14.2405529022217</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0972528457642</t>
+    <t xml:space="preserve">14.0972509384155</t>
   </si>
   <si>
     <t xml:space="preserve">14.3301162719727</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4734163284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5988054275513</t>
+    <t xml:space="preserve">14.4734182357788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5988063812256</t>
   </si>
   <si>
     <t xml:space="preserve">13.8823003768921</t>
@@ -2288,7 +2288,7 @@
     <t xml:space="preserve">13.5777854919434</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4703102111816</t>
+    <t xml:space="preserve">13.4703092575073</t>
   </si>
   <si>
     <t xml:space="preserve">13.6852607727051</t>
@@ -2297,13 +2297,13 @@
     <t xml:space="preserve">13.6673488616943</t>
   </si>
   <si>
-    <t xml:space="preserve">13.559871673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6136102676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8285617828369</t>
+    <t xml:space="preserve">13.5598735809326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6136093139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8285627365112</t>
   </si>
   <si>
     <t xml:space="preserve">13.953950881958</t>
@@ -2318,34 +2318,34 @@
     <t xml:space="preserve">13.5240478515625</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7031745910645</t>
+    <t xml:space="preserve">13.7031736373901</t>
   </si>
   <si>
     <t xml:space="preserve">13.2553577423096</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4523973464966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3090944290161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2763776779175</t>
+    <t xml:space="preserve">13.4523963928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3090953826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2763786315918</t>
   </si>
   <si>
     <t xml:space="preserve">14.4196796417236</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0256004333496</t>
+    <t xml:space="preserve">14.0256023406982</t>
   </si>
   <si>
     <t xml:space="preserve">13.756911277771</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4375944137573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7124996185303</t>
+    <t xml:space="preserve">14.437593460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7124977111816</t>
   </si>
   <si>
     <t xml:space="preserve">16.336332321167</t>
@@ -2354,7 +2354,7 @@
     <t xml:space="preserve">17.7156066894531</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2498760223389</t>
+    <t xml:space="preserve">17.2498779296875</t>
   </si>
   <si>
     <t xml:space="preserve">19.6591281890869</t>
@@ -2366,13 +2366,13 @@
     <t xml:space="preserve">21.4503936767578</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5399570465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2116794586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.987771987915</t>
+    <t xml:space="preserve">21.5399532318115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2116775512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9877700805664</t>
   </si>
   <si>
     <t xml:space="preserve">21.2712669372559</t>
@@ -2381,25 +2381,25 @@
     <t xml:space="preserve">23.017749786377</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3460254669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1221179962158</t>
+    <t xml:space="preserve">22.3460273742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1221160888672</t>
   </si>
   <si>
     <t xml:space="preserve">23.7342548370361</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8982105255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4355869293213</t>
+    <t xml:space="preserve">21.8982086181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4355888366699</t>
   </si>
   <si>
     <t xml:space="preserve">21.495174407959</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7190799713135</t>
+    <t xml:space="preserve">21.7190837860107</t>
   </si>
   <si>
     <t xml:space="preserve">21.9429912567139</t>
@@ -2408,10 +2408,10 @@
     <t xml:space="preserve">21.7638645172119</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8534259796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3312187194824</t>
+    <t xml:space="preserve">21.8534278869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3312206268311</t>
   </si>
   <si>
     <t xml:space="preserve">21.8086471557617</t>
@@ -2423,43 +2423,43 @@
     <t xml:space="preserve">25.3016128540039</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2420253753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5255184173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2120494842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8837718963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4807376861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5703010559082</t>
+    <t xml:space="preserve">26.2420234680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.525520324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2120475769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8837699890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4807395935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5702991485596</t>
   </si>
   <si>
     <t xml:space="preserve">25.1224842071533</t>
   </si>
   <si>
-    <t xml:space="preserve">24.361198425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3911743164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7046489715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4211502075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0628986358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.465934753418</t>
+    <t xml:space="preserve">24.3611965179443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3911762237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.704647064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4211540222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0629005432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4659309387207</t>
   </si>
   <si>
     <t xml:space="preserve">26.1524620056152</t>
@@ -2474,7 +2474,7 @@
     <t xml:space="preserve">26.7794036865234</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5554962158203</t>
+    <t xml:space="preserve">26.5554943084717</t>
   </si>
   <si>
     <t xml:space="preserve">24.9881401062012</t>
@@ -2486,13 +2486,13 @@
     <t xml:space="preserve">23.9581642150879</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0477256774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9133815765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5851058959961</t>
+    <t xml:space="preserve">24.0477275848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9133834838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5851078033447</t>
   </si>
   <si>
     <t xml:space="preserve">22.077335357666</t>
@@ -2507,19 +2507,19 @@
     <t xml:space="preserve">24.182071685791</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2268505096436</t>
+    <t xml:space="preserve">24.2268524169922</t>
   </si>
   <si>
     <t xml:space="preserve">24.4955425262451</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3164138793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3908061981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8238182067871</t>
+    <t xml:space="preserve">24.3164157867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3908081054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8238201141357</t>
   </si>
   <si>
     <t xml:space="preserve">23.0625305175781</t>
@@ -2531,19 +2531,19 @@
     <t xml:space="preserve">22.8834018707275</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2416572570801</t>
+    <t xml:space="preserve">23.2416591644287</t>
   </si>
   <si>
     <t xml:space="preserve">25.1672668457031</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3167819976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6002807617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6150817871094</t>
+    <t xml:space="preserve">27.3167858123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6002788543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.615083694458</t>
   </si>
   <si>
     <t xml:space="preserve">25.4359569549561</t>
@@ -2552,7 +2552,7 @@
     <t xml:space="preserve">24.8985767364502</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9733371734619</t>
+    <t xml:space="preserve">25.9733352661133</t>
   </si>
   <si>
     <t xml:space="preserve">26.5107154846191</t>
@@ -2573,52 +2573,52 @@
     <t xml:space="preserve">27.048095703125</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9437255859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8841419219971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9289207458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7050151824951</t>
+    <t xml:space="preserve">27.9437274932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8841400146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9289226531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7050132751465</t>
   </si>
   <si>
     <t xml:space="preserve">29.7797737121582</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9885082244873</t>
+    <t xml:space="preserve">27.9885101318359</t>
   </si>
   <si>
     <t xml:space="preserve">27.630256652832</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2272205352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4063491821289</t>
+    <t xml:space="preserve">27.2272186279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4063472747803</t>
   </si>
   <si>
     <t xml:space="preserve">26.6898403167725</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8389911651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.79421043396</t>
+    <t xml:space="preserve">25.8389892578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7942085266113</t>
   </si>
   <si>
     <t xml:space="preserve">26.3315868377686</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7194499969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4507598876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5999126434326</t>
+    <t xml:space="preserve">24.7194519042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4507579803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.599910736084</t>
   </si>
   <si>
     <t xml:space="preserve">23.4655647277832</t>
@@ -2627,7 +2627,7 @@
     <t xml:space="preserve">27.3615646362305</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0332889556885</t>
+    <t xml:space="preserve">28.0332870483398</t>
   </si>
   <si>
     <t xml:space="preserve">27.8541641235352</t>
@@ -2648,7 +2648,7 @@
     <t xml:space="preserve">27.3454132080078</t>
   </si>
   <si>
-    <t xml:space="preserve">29.662052154541</t>
+    <t xml:space="preserve">29.6620502471924</t>
   </si>
   <si>
     <t xml:space="preserve">29.480354309082</t>
@@ -2657,19 +2657,19 @@
     <t xml:space="preserve">29.3440799713135</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5251121520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.57053565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0247821807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0702018737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8885059356689</t>
+    <t xml:space="preserve">30.525110244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5705375671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0247802734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0702037811279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8885040283203</t>
   </si>
   <si>
     <t xml:space="preserve">28.9352626800537</t>
@@ -2681,13 +2681,13 @@
     <t xml:space="preserve">27.9359283447266</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4362602233887</t>
+    <t xml:space="preserve">27.4362621307373</t>
   </si>
   <si>
     <t xml:space="preserve">28.0722007751465</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4355945587158</t>
+    <t xml:space="preserve">28.4355926513672</t>
   </si>
   <si>
     <t xml:space="preserve">28.5264415740967</t>
@@ -2696,7 +2696,7 @@
     <t xml:space="preserve">28.4810199737549</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3901710510254</t>
+    <t xml:space="preserve">28.390172958374</t>
   </si>
   <si>
     <t xml:space="preserve">29.1623821258545</t>
@@ -2708,7 +2708,7 @@
     <t xml:space="preserve">28.2538986206055</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1169605255127</t>
+    <t xml:space="preserve">29.1169586181641</t>
   </si>
   <si>
     <t xml:space="preserve">30.1162948608398</t>
@@ -2717,16 +2717,16 @@
     <t xml:space="preserve">30.9793529510498</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1610488891602</t>
+    <t xml:space="preserve">31.1610507965088</t>
   </si>
   <si>
     <t xml:space="preserve">31.479024887085</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5698719024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7969932556152</t>
+    <t xml:space="preserve">31.5698699951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7969913482666</t>
   </si>
   <si>
     <t xml:space="preserve">31.7515678405762</t>
@@ -2735,13 +2735,13 @@
     <t xml:space="preserve">31.1156272888184</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2505645751953</t>
+    <t xml:space="preserve">33.2505683898926</t>
   </si>
   <si>
     <t xml:space="preserve">34.6587219238281</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8410835266113</t>
+    <t xml:space="preserve">33.8410873413086</t>
   </si>
   <si>
     <t xml:space="preserve">34.4770278930664</t>
@@ -2753,10 +2753,10 @@
     <t xml:space="preserve">34.5678672790527</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6132926940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.340087890625</t>
+    <t xml:space="preserve">34.6132965087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3400840759277</t>
   </si>
   <si>
     <t xml:space="preserve">34.4316024780273</t>
@@ -2765,31 +2765,31 @@
     <t xml:space="preserve">33.7048072814941</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9773559570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9312705993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5224494934082</t>
+    <t xml:space="preserve">33.9773597717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.931266784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5224456787109</t>
   </si>
   <si>
     <t xml:space="preserve">34.0682067871094</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7502326965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9319305419922</t>
+    <t xml:space="preserve">33.7502365112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9319267272949</t>
   </si>
   <si>
     <t xml:space="preserve">34.2499008178711</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6139640808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2485733032227</t>
+    <t xml:space="preserve">33.6139602661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2485694885254</t>
   </si>
   <si>
     <t xml:space="preserve">36.6573867797852</t>
@@ -2801,13 +2801,13 @@
     <t xml:space="preserve">38.6106300354004</t>
   </si>
   <si>
-    <t xml:space="preserve">39.5645408630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1109657287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4302635192871</t>
+    <t xml:space="preserve">39.5645370483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.110969543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4302673339844</t>
   </si>
   <si>
     <t xml:space="preserve">33.3868408203125</t>
@@ -2831,7 +2831,7 @@
     <t xml:space="preserve">34.340747833252</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7509002685547</t>
+    <t xml:space="preserve">32.7508964538574</t>
   </si>
   <si>
     <t xml:space="preserve">32.6600532531738</t>
@@ -2840,7 +2840,7 @@
     <t xml:space="preserve">32.9780197143555</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7976570129395</t>
+    <t xml:space="preserve">30.7976589202881</t>
   </si>
   <si>
     <t xml:space="preserve">29.3895034790039</t>
@@ -2849,13 +2849,13 @@
     <t xml:space="preserve">29.5257778167725</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6172904968262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3447456359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0254459381104</t>
+    <t xml:space="preserve">28.6172943115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.344747543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0254440307617</t>
   </si>
   <si>
     <t xml:space="preserve">31.9332637786865</t>
@@ -2870,13 +2870,13 @@
     <t xml:space="preserve">32.2512359619141</t>
   </si>
   <si>
-    <t xml:space="preserve">31.615291595459</t>
+    <t xml:space="preserve">31.6152935028076</t>
   </si>
   <si>
     <t xml:space="preserve">32.024112701416</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1142997741699</t>
+    <t xml:space="preserve">33.1142959594727</t>
   </si>
   <si>
     <t xml:space="preserve">32.614631652832</t>
@@ -2888,34 +2888,34 @@
     <t xml:space="preserve">32.0695381164551</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5244464874268</t>
+    <t xml:space="preserve">31.5244445800781</t>
   </si>
   <si>
     <t xml:space="preserve">31.3427467346191</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3420829772949</t>
+    <t xml:space="preserve">32.3420791625977</t>
   </si>
   <si>
     <t xml:space="preserve">32.5237770080566</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7054786682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1603851318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.159049987793</t>
+    <t xml:space="preserve">32.7054748535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1603889465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1590538024902</t>
   </si>
   <si>
     <t xml:space="preserve">33.7956581115723</t>
   </si>
   <si>
-    <t xml:space="preserve">34.976692199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9325942993164</t>
+    <t xml:space="preserve">34.9766883850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9325981140137</t>
   </si>
   <si>
     <t xml:space="preserve">33.0234451293945</t>
@@ -2924,34 +2924,34 @@
     <t xml:space="preserve">33.5231170654297</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4783554077148</t>
+    <t xml:space="preserve">32.4783592224121</t>
   </si>
   <si>
     <t xml:space="preserve">32.4329299926758</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8424167633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8878383636475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4342651367188</t>
+    <t xml:space="preserve">31.842414855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8878402709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4342632293701</t>
   </si>
   <si>
     <t xml:space="preserve">29.7074756622314</t>
   </si>
   <si>
-    <t xml:space="preserve">30.70680809021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4796867370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6166248321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8437442779541</t>
+    <t xml:space="preserve">30.7068061828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4796886444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.616626739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8437461853027</t>
   </si>
   <si>
     <t xml:space="preserve">29.2532329559326</t>
@@ -2960,7 +2960,7 @@
     <t xml:space="preserve">28.7535629272461</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0708656311035</t>
+    <t xml:space="preserve">30.0708675384521</t>
   </si>
   <si>
     <t xml:space="preserve">28.8898372650146</t>
@@ -2972,7 +2972,7 @@
     <t xml:space="preserve">28.8444137573242</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7081432342529</t>
+    <t xml:space="preserve">28.7081413269043</t>
   </si>
   <si>
     <t xml:space="preserve">28.9806861877441</t>
@@ -2993,7 +2993,7 @@
     <t xml:space="preserve">28.0267772674561</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6179580688477</t>
+    <t xml:space="preserve">27.617956161499</t>
   </si>
   <si>
     <t xml:space="preserve">27.7542304992676</t>
@@ -3011,16 +3011,16 @@
     <t xml:space="preserve">27.5725345611572</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6186237335205</t>
+    <t xml:space="preserve">26.6186218261719</t>
   </si>
   <si>
     <t xml:space="preserve">27.1182918548584</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0274410247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9365940093994</t>
+    <t xml:space="preserve">27.0274429321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9365921020508</t>
   </si>
   <si>
     <t xml:space="preserve">26.9820194244385</t>
@@ -3029,16 +3029,16 @@
     <t xml:space="preserve">26.3460788726807</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8918342590332</t>
+    <t xml:space="preserve">25.8918361663818</t>
   </si>
   <si>
     <t xml:space="preserve">25.6647148132324</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2552299499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8457450866699</t>
+    <t xml:space="preserve">26.2552280426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8457431793213</t>
   </si>
   <si>
     <t xml:space="preserve">26.6640491485596</t>
@@ -3050,28 +3050,28 @@
     <t xml:space="preserve">26.5732002258301</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3915004730225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.70947265625</t>
+    <t xml:space="preserve">26.3915023803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7094707489014</t>
   </si>
   <si>
     <t xml:space="preserve">26.527774810791</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9826831817627</t>
+    <t xml:space="preserve">25.9826850891113</t>
   </si>
   <si>
     <t xml:space="preserve">25.8009872436523</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1657123565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6660442352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8477458953857</t>
+    <t xml:space="preserve">24.165714263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6660461425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8477439880371</t>
   </si>
   <si>
     <t xml:space="preserve">25.437593460083</t>
@@ -3080,7 +3080,7 @@
     <t xml:space="preserve">25.7555637359619</t>
   </si>
   <si>
-    <t xml:space="preserve">25.074197769165</t>
+    <t xml:space="preserve">25.0741996765137</t>
   </si>
   <si>
     <t xml:space="preserve">26.0735340118408</t>
@@ -3092,7 +3092,7 @@
     <t xml:space="preserve">26.3419418334961</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6671524047852</t>
+    <t xml:space="preserve">26.6671504974365</t>
   </si>
   <si>
     <t xml:space="preserve">27.1317348480225</t>
@@ -3101,7 +3101,7 @@
     <t xml:space="preserve">27.6427764892578</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3396530151367</t>
+    <t xml:space="preserve">28.3396549224854</t>
   </si>
   <si>
     <t xml:space="preserve">27.8286113739014</t>
@@ -3155,7 +3155,7 @@
     <t xml:space="preserve">27.038818359375</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9459018707275</t>
+    <t xml:space="preserve">26.9458999633789</t>
   </si>
   <si>
     <t xml:space="preserve">26.760066986084</t>
@@ -3167,19 +3167,19 @@
     <t xml:space="preserve">26.2025661468506</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5742321014404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.481315612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8994426727295</t>
+    <t xml:space="preserve">26.5742340087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4813175201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8994445800781</t>
   </si>
   <si>
     <t xml:space="preserve">26.2490253448486</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7379837036133</t>
+    <t xml:space="preserve">25.7379817962646</t>
   </si>
   <si>
     <t xml:space="preserve">25.9238147735596</t>
@@ -3194,7 +3194,7 @@
     <t xml:space="preserve">27.271110534668</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2246513366699</t>
+    <t xml:space="preserve">27.2246494293213</t>
   </si>
   <si>
     <t xml:space="preserve">25.4127731323242</t>
@@ -3206,7 +3206,7 @@
     <t xml:space="preserve">24.5300617218018</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9017295837402</t>
+    <t xml:space="preserve">24.9017276763916</t>
   </si>
   <si>
     <t xml:space="preserve">25.0875625610352</t>
@@ -3215,76 +3215,76 @@
     <t xml:space="preserve">24.8088130950928</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5521469116211</t>
+    <t xml:space="preserve">25.5521488189697</t>
   </si>
   <si>
     <t xml:space="preserve">25.5056896209717</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7623538970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7158946990967</t>
+    <t xml:space="preserve">24.7623519897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7158966064453</t>
   </si>
   <si>
     <t xml:space="preserve">25.8308982849121</t>
   </si>
   <si>
-    <t xml:space="preserve">27.085277557373</t>
+    <t xml:space="preserve">27.0852756500244</t>
   </si>
   <si>
     <t xml:space="preserve">26.7136077880859</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0167331695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8773574829102</t>
+    <t xml:space="preserve">26.016731262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8773555755615</t>
   </si>
   <si>
     <t xml:space="preserve">25.7844390869141</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0631885528564</t>
+    <t xml:space="preserve">26.0631904602051</t>
   </si>
   <si>
     <t xml:space="preserve">26.1096496582031</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1340198516846</t>
+    <t xml:space="preserve">25.1340217590332</t>
   </si>
   <si>
     <t xml:space="preserve">25.0411052703857</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2977676391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4836044311523</t>
+    <t xml:space="preserve">24.2977695465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4836025238037</t>
   </si>
   <si>
     <t xml:space="preserve">24.0654773712158</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2513122558594</t>
+    <t xml:space="preserve">24.2513103485107</t>
   </si>
   <si>
     <t xml:space="preserve">24.5765209197998</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6008911132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0433921813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0898494720459</t>
+    <t xml:space="preserve">23.6008930206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0433902740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0898513793945</t>
   </si>
   <si>
     <t xml:space="preserve">22.114221572876</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0213050842285</t>
+    <t xml:space="preserve">22.0213069915771</t>
   </si>
   <si>
     <t xml:space="preserve">23.2756824493408</t>
@@ -3293,28 +3293,28 @@
     <t xml:space="preserve">23.4615173339844</t>
   </si>
   <si>
-    <t xml:space="preserve">23.415060043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1363086700439</t>
+    <t xml:space="preserve">23.4150581359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1363067626953</t>
   </si>
   <si>
     <t xml:space="preserve">23.6473522186279</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9504737854004</t>
+    <t xml:space="preserve">22.950475692749</t>
   </si>
   <si>
     <t xml:space="preserve">22.5788059234619</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2071399688721</t>
+    <t xml:space="preserve">22.2071380615234</t>
   </si>
   <si>
     <t xml:space="preserve">21.64963722229</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8598461151123</t>
+    <t xml:space="preserve">20.8598442077637</t>
   </si>
   <si>
     <t xml:space="preserve">21.0921363830566</t>
@@ -3329,7 +3329,7 @@
     <t xml:space="preserve">21.5567207336426</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7425537109375</t>
+    <t xml:space="preserve">21.7425556182861</t>
   </si>
   <si>
     <t xml:space="preserve">21.9283885955811</t>
@@ -3350,37 +3350,37 @@
     <t xml:space="preserve">21.4173450469971</t>
   </si>
   <si>
-    <t xml:space="preserve">21.603178024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.835470199585</t>
+    <t xml:space="preserve">21.6031799316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8354721069336</t>
   </si>
   <si>
     <t xml:space="preserve">22.160680770874</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7181835174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3000564575195</t>
+    <t xml:space="preserve">22.7181816101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3000545501709</t>
   </si>
   <si>
     <t xml:space="preserve">22.3465137481689</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2535972595215</t>
+    <t xml:space="preserve">22.2535991668701</t>
   </si>
   <si>
     <t xml:space="preserve">21.881929397583</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7890148162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1827659606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5986061096191</t>
+    <t xml:space="preserve">21.7890129089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.182767868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5986042022705</t>
   </si>
   <si>
     <t xml:space="preserve">25.3663120269775</t>
@@ -3401,10 +3401,10 @@
     <t xml:space="preserve">24.4371433258057</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8796424865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2048511505127</t>
+    <t xml:space="preserve">23.8796443939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2048530578613</t>
   </si>
   <si>
     <t xml:space="preserve">23.9261016845703</t>
@@ -3413,7 +3413,7 @@
     <t xml:space="preserve">24.6694355010986</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5544357299805</t>
+    <t xml:space="preserve">23.5544338226318</t>
   </si>
   <si>
     <t xml:space="preserve">23.6938095092773</t>
@@ -3422,7 +3422,7 @@
     <t xml:space="preserve">23.3221416473389</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7867259979248</t>
+    <t xml:space="preserve">23.7867279052734</t>
   </si>
   <si>
     <t xml:space="preserve">22.8575572967529</t>
@@ -3431,7 +3431,7 @@
     <t xml:space="preserve">21.5102615356445</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3708877563477</t>
+    <t xml:space="preserve">21.370885848999</t>
   </si>
   <si>
     <t xml:space="preserve">21.1850528717041</t>
@@ -3440,19 +3440,19 @@
     <t xml:space="preserve">20.7204685211182</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4881744384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9771327972412</t>
+    <t xml:space="preserve">20.4881763458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9771347045898</t>
   </si>
   <si>
     <t xml:space="preserve">20.2558822631836</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5346355438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9306774139404</t>
+    <t xml:space="preserve">20.5346336364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9306755065918</t>
   </si>
   <si>
     <t xml:space="preserve">20.5810928344727</t>
@@ -3464,7 +3464,7 @@
     <t xml:space="preserve">20.6275520324707</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0235919952393</t>
+    <t xml:space="preserve">20.0235900878906</t>
   </si>
   <si>
     <t xml:space="preserve">18.6298370361328</t>
@@ -3482,7 +3482,7 @@
     <t xml:space="preserve">17.8772106170654</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5427112579346</t>
+    <t xml:space="preserve">17.5427093505859</t>
   </si>
   <si>
     <t xml:space="preserve">17.2453765869141</t>
@@ -3494,10 +3494,10 @@
     <t xml:space="preserve">17.5612926483154</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4126262664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7471294403076</t>
+    <t xml:space="preserve">17.4126281738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.747127532959</t>
   </si>
   <si>
     <t xml:space="preserve">17.1896266937256</t>
@@ -3518,13 +3518,13 @@
     <t xml:space="preserve">16.3162078857422</t>
   </si>
   <si>
-    <t xml:space="preserve">15.981707572937</t>
+    <t xml:space="preserve">15.9817085266113</t>
   </si>
   <si>
     <t xml:space="preserve">16.5392074584961</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2976264953613</t>
+    <t xml:space="preserve">16.2976245880127</t>
   </si>
   <si>
     <t xml:space="preserve">16.1861248016357</t>
@@ -3536,7 +3536,7 @@
     <t xml:space="preserve">16.1489562988281</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2418727874756</t>
+    <t xml:space="preserve">16.2418746948242</t>
   </si>
   <si>
     <t xml:space="preserve">16.0746231079102</t>
@@ -4332,6 +4332,9 @@
   </si>
   <si>
     <t xml:space="preserve">18.5400009155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3999996185303</t>
   </si>
 </sst>
 </file>
@@ -70294,7 +70297,7 @@
     </row>
     <row r="2525">
       <c r="A2525" s="1" t="n">
-        <v>45994.6909837963</v>
+        <v>45994.3333333333</v>
       </c>
       <c r="B2525" t="n">
         <v>16841</v>
@@ -70315,6 +70318,32 @@
         <v>1439</v>
       </c>
       <c r="H2525" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2526">
+      <c r="A2526" s="1" t="n">
+        <v>45995.6912384259</v>
+      </c>
+      <c r="B2526" t="n">
+        <v>5959</v>
+      </c>
+      <c r="C2526" t="n">
+        <v>18.6000003814697</v>
+      </c>
+      <c r="D2526" t="n">
+        <v>18.2999992370605</v>
+      </c>
+      <c r="E2526" t="n">
+        <v>18.6000003814697</v>
+      </c>
+      <c r="F2526" t="n">
+        <v>18.3999996185303</v>
+      </c>
+      <c r="G2526" t="s">
+        <v>1440</v>
+      </c>
+      <c r="H2526" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ARN.MI.xlsx
+++ b/data/ARN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="1441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="1442">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,205 +38,205 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92215013504028</t>
+    <t xml:space="preserve">1.92215049266815</t>
   </si>
   <si>
     <t xml:space="preserve">ARN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94450092315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91736054420471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90778195858002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8838347196579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93172919750214</t>
+    <t xml:space="preserve">1.94450080394745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91736030578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9077821969986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88383483886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93172895908356</t>
   </si>
   <si>
     <t xml:space="preserve">1.91576421260834</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83434414863586</t>
+    <t xml:space="preserve">1.83434426784515</t>
   </si>
   <si>
     <t xml:space="preserve">1.83594059944153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91097462177277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80720448493958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74973106384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71620547771454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80401122570038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81039690971375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79602885246277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77208185195923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70662677288055</t>
+    <t xml:space="preserve">1.91097486019135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.807204246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74973142147064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71620559692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80401146411896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81039714813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79602897167206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77208197116852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70662665367126</t>
   </si>
   <si>
     <t xml:space="preserve">1.6970477104187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69066190719604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67629337310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7002409696579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69864428043365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67469716072083</t>
+    <t xml:space="preserve">1.69066202640533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67629361152649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70024085044861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69864439964294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67469727993011</t>
   </si>
   <si>
     <t xml:space="preserve">1.66671502590179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66032922267914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81518661975861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82795834541321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86148416996002</t>
+    <t xml:space="preserve">1.66032886505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81518626213074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82795822620392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86148428916931</t>
   </si>
   <si>
     <t xml:space="preserve">1.88543117046356</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8918172121048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92853629589081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95407950878143</t>
+    <t xml:space="preserve">1.89181745052338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92853581905365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95407938957214</t>
   </si>
   <si>
     <t xml:space="preserve">1.90618562698364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86787009239197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88064205646515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85190558433533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85988759994507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8550980091095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7928364276886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78804683685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78006458282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7561172246933</t>
+    <t xml:space="preserve">1.86787021160126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88064169883728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85190546512604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85988771915436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85509812831879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79283607006073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78804659843445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78006446361542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75611734390259</t>
   </si>
   <si>
     <t xml:space="preserve">1.76888883113861</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76409935951233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78485357761383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77048540115356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72099471092224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73536312580109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80241501331329</t>
+    <t xml:space="preserve">1.76409959793091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78485369682312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77048492431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72099483013153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7353630065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.802414894104</t>
   </si>
   <si>
     <t xml:space="preserve">1.76250290870667</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74494206905365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73217034339905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73695981502533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7433454990387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7513279914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68587243556976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67789018154144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65234673023224</t>
+    <t xml:space="preserve">1.74494218826294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73217022418976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73695969581604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74334537982941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75132775306702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68587255477905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67789030075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65234649181366</t>
   </si>
   <si>
     <t xml:space="preserve">1.62041735649109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64276790618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59008419513702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60285604000092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54937446117401</t>
+    <t xml:space="preserve">1.64276778697968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59008431434631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60285592079163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54937434196472</t>
   </si>
   <si>
     <t xml:space="preserve">1.51185727119446</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45598089694977</t>
+    <t xml:space="preserve">1.45598077774048</t>
   </si>
   <si>
     <t xml:space="preserve">1.43682312965393</t>
@@ -245,40 +245,40 @@
     <t xml:space="preserve">1.46955072879791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49748921394348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47673499584198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47274386882782</t>
+    <t xml:space="preserve">1.49748933315277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47673487663269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47274374961853</t>
   </si>
   <si>
     <t xml:space="preserve">1.46875250339508</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49669075012207</t>
+    <t xml:space="preserve">1.49669086933136</t>
   </si>
   <si>
     <t xml:space="preserve">1.47593665122986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50626945495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47753310203552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43841969966888</t>
+    <t xml:space="preserve">1.50626957416534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47753322124481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43841958045959</t>
   </si>
   <si>
     <t xml:space="preserve">1.40090262889862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34901750087738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30910551548004</t>
+    <t xml:space="preserve">1.34901738166809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30910563468933</t>
   </si>
   <si>
     <t xml:space="preserve">1.34342968463898</t>
@@ -290,19 +290,19 @@
     <t xml:space="preserve">1.34103488922119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31708776950836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38653433322906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39691150188446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40649020671844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30671095848083</t>
+    <t xml:space="preserve">1.31708800792694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38653457164764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39691138267517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40649032592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30671083927155</t>
   </si>
   <si>
     <t xml:space="preserve">1.3234738111496</t>
@@ -311,13 +311,13 @@
     <t xml:space="preserve">1.30591285228729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31229865550995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28994798660278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28515863418579</t>
+    <t xml:space="preserve">1.31229841709137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28994810581207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2851585149765</t>
   </si>
   <si>
     <t xml:space="preserve">1.28595674037933</t>
@@ -326,10 +326,10 @@
     <t xml:space="preserve">1.33305263519287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33704364299774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30112326145172</t>
+    <t xml:space="preserve">1.33704388141632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30112302303314</t>
   </si>
   <si>
     <t xml:space="preserve">1.36104893684387</t>
@@ -341,28 +341,28 @@
     <t xml:space="preserve">1.35283982753754</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33806347846985</t>
+    <t xml:space="preserve">1.33806359767914</t>
   </si>
   <si>
     <t xml:space="preserve">1.27157080173492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28880977630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29291415214539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30686974525452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33888459205627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34955620765686</t>
-  </si>
-  <si>
-    <t 